--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\1. doc\HKMC_AIR_PTC\일정\HKMC_PTC_DOC\hkmc_ptc_heater\1. 일정\1. Weekly Plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\2.project\hkmc_ptc_heater\Doc\1. 일정\1. Weekly Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685"/>
   </bookViews>
   <sheets>
     <sheet name="대일정" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="230">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1307,6 +1307,38 @@
      ex) SRS.V0.1_JH_250625_01, SRS.V0.1_JH_250625_02</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>NEaW
+(자율주행 차)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Proto
+8/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LP1
+7/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SP1
+4/15
+북미-&gt;평택
+한온대전 3/14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LP2
+TBD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M
+1/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1315,7 +1347,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2460,7 +2492,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2873,6 +2905,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2898,13 +2933,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>2243942</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>790452</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>404500</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>1442356</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2942,7 +2977,7 @@
     <xdr:to>
       <xdr:col>32</xdr:col>
       <xdr:colOff>259133</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>163285</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -3463,8 +3498,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BL23"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:BL24"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="4.375" customWidth="1"/>
     <col min="2" max="2" width="18.875" customWidth="1"/>
@@ -3475,7 +3510,7 @@
     <col min="36" max="64" width="8.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" s="20" customFormat="1" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:64" s="20" customFormat="1" ht="32.25" thickBot="1">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -3485,7 +3520,7 @@
       <c r="C1" s="21"/>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1">
       <c r="B2" s="123" t="s">
         <v>2</v>
       </c>
@@ -3566,7 +3601,7 @@
       <c r="BK2" s="127"/>
       <c r="BL2" s="128"/>
     </row>
-    <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1">
       <c r="B3" s="124"/>
       <c r="C3" s="126"/>
       <c r="D3" s="126"/>
@@ -3751,7 +3786,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:64" ht="183" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:64" ht="183" customHeight="1" thickBot="1">
       <c r="B4" s="63" t="s">
         <v>122</v>
       </c>
@@ -3832,7 +3867,7 @@
       <c r="BK4" s="2"/>
       <c r="BL4" s="5"/>
     </row>
-    <row r="5" spans="1:64" ht="81" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:64" ht="81">
       <c r="B5" s="28" t="s">
         <v>123</v>
       </c>
@@ -3911,7 +3946,7 @@
       <c r="BK5" s="31"/>
       <c r="BL5" s="10"/>
     </row>
-    <row r="6" spans="1:64" ht="67.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:64" ht="67.5">
       <c r="B6" s="28" t="s">
         <v>124</v>
       </c>
@@ -3994,7 +4029,7 @@
       <c r="BK6" s="31"/>
       <c r="BL6" s="10"/>
     </row>
-    <row r="7" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:64" ht="61.5" customHeight="1">
       <c r="B7" s="28" t="s">
         <v>125</v>
       </c>
@@ -4075,13 +4110,11 @@
       <c r="BK7" s="31"/>
       <c r="BL7" s="10"/>
     </row>
-    <row r="8" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="59" t="s">
-        <v>79</v>
-      </c>
+    <row r="8" spans="1:64" ht="81">
+      <c r="B8" s="28" t="s">
+        <v>224</v>
+      </c>
+      <c r="C8" s="58"/>
       <c r="D8" s="33"/>
       <c r="E8" s="6"/>
       <c r="F8" s="7"/>
@@ -4094,39 +4127,45 @@
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="7"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7"/>
-      <c r="V8" s="7"/>
-      <c r="W8" s="7"/>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
-      <c r="Z8" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA8" s="7"/>
-      <c r="AB8" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC8" s="9"/>
-      <c r="AD8" s="7"/>
-      <c r="AE8" s="7"/>
-      <c r="AF8" s="7"/>
-      <c r="AG8" s="13"/>
-      <c r="AH8" s="7"/>
-      <c r="AI8" s="13"/>
-      <c r="AJ8" s="7"/>
-      <c r="AK8" s="7"/>
-      <c r="AL8" s="7"/>
-      <c r="AM8" s="7"/>
-      <c r="AN8" s="8"/>
-      <c r="AO8" s="9"/>
-      <c r="AP8" s="7"/>
-      <c r="AQ8" s="7"/>
-      <c r="AR8" s="7"/>
+      <c r="P8" s="32"/>
+      <c r="Q8" s="29"/>
+      <c r="R8" s="31"/>
+      <c r="S8" s="31"/>
+      <c r="T8" s="31"/>
+      <c r="U8" s="31"/>
+      <c r="V8" s="30"/>
+      <c r="W8" s="30"/>
+      <c r="X8" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y8" s="31"/>
+      <c r="Z8" s="30"/>
+      <c r="AA8" s="30"/>
+      <c r="AB8" s="138"/>
+      <c r="AC8" s="29"/>
+      <c r="AD8" s="31"/>
+      <c r="AE8" s="31"/>
+      <c r="AF8" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="AG8" s="31"/>
+      <c r="AH8" s="31"/>
+      <c r="AI8" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ8" s="31"/>
+      <c r="AK8" s="31"/>
+      <c r="AL8" s="31"/>
+      <c r="AM8" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="AN8" s="138"/>
+      <c r="AO8" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="AP8" s="31"/>
+      <c r="AQ8" s="31"/>
+      <c r="AR8" s="31"/>
       <c r="AS8" s="7"/>
       <c r="AT8" s="7"/>
       <c r="AU8" s="7"/>
@@ -4148,11 +4187,11 @@
       <c r="BK8" s="31"/>
       <c r="BL8" s="10"/>
     </row>
-    <row r="9" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:64" ht="61.5" customHeight="1">
       <c r="B9" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="59" t="s">
         <v>79</v>
       </c>
       <c r="D9" s="33"/>
@@ -4175,26 +4214,22 @@
       <c r="U9" s="7"/>
       <c r="V9" s="7"/>
       <c r="W9" s="7"/>
-      <c r="X9" s="13" t="s">
-        <v>49</v>
-      </c>
+      <c r="X9" s="7"/>
       <c r="Y9" s="7"/>
-      <c r="Z9" s="13" t="s">
-        <v>48</v>
+      <c r="Z9" s="17" t="s">
+        <v>50</v>
       </c>
       <c r="AA9" s="7"/>
-      <c r="AB9" s="8"/>
+      <c r="AB9" s="14" t="s">
+        <v>51</v>
+      </c>
       <c r="AC9" s="9"/>
       <c r="AD9" s="7"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="7"/>
-      <c r="AG9" s="17" t="s">
-        <v>37</v>
-      </c>
+      <c r="AG9" s="13"/>
       <c r="AH9" s="7"/>
-      <c r="AI9" s="13" t="s">
-        <v>47</v>
-      </c>
+      <c r="AI9" s="13"/>
       <c r="AJ9" s="7"/>
       <c r="AK9" s="7"/>
       <c r="AL9" s="7"/>
@@ -4225,12 +4260,12 @@
       <c r="BK9" s="31"/>
       <c r="BL9" s="10"/>
     </row>
-    <row r="10" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="28" t="s">
-        <v>130</v>
+    <row r="10" spans="1:64" ht="61.5" customHeight="1">
+      <c r="B10" s="27" t="s">
+        <v>46</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="6"/>
@@ -4238,53 +4273,49 @@
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
-      <c r="J10" s="13"/>
+      <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
-      <c r="O10" s="30"/>
-      <c r="P10" s="14"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="8"/>
       <c r="Q10" s="9"/>
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
       <c r="T10" s="7"/>
       <c r="U10" s="7"/>
       <c r="V10" s="7"/>
-      <c r="W10" s="13"/>
-      <c r="X10" s="7"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="13" t="s">
+        <v>49</v>
+      </c>
       <c r="Y10" s="7"/>
-      <c r="Z10" s="7"/>
-      <c r="AA10" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="AB10" s="14" t="s">
-        <v>57</v>
-      </c>
+      <c r="Z10" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA10" s="7"/>
+      <c r="AB10" s="8"/>
       <c r="AC10" s="9"/>
-      <c r="AD10" s="30"/>
-      <c r="AE10" s="31"/>
-      <c r="AF10" s="31"/>
-      <c r="AG10" s="13" t="s">
-        <v>133</v>
+      <c r="AD10" s="7"/>
+      <c r="AE10" s="7"/>
+      <c r="AF10" s="7"/>
+      <c r="AG10" s="17" t="s">
+        <v>37</v>
       </c>
       <c r="AH10" s="7"/>
-      <c r="AI10" s="13"/>
+      <c r="AI10" s="13" t="s">
+        <v>47</v>
+      </c>
       <c r="AJ10" s="7"/>
-      <c r="AK10" s="17" t="s">
-        <v>134</v>
-      </c>
+      <c r="AK10" s="7"/>
       <c r="AL10" s="7"/>
       <c r="AM10" s="7"/>
       <c r="AN10" s="8"/>
       <c r="AO10" s="9"/>
-      <c r="AP10" s="17" t="s">
-        <v>135</v>
-      </c>
+      <c r="AP10" s="7"/>
       <c r="AQ10" s="7"/>
-      <c r="AR10" s="13" t="s">
-        <v>136</v>
-      </c>
+      <c r="AR10" s="7"/>
       <c r="AS10" s="7"/>
       <c r="AT10" s="7"/>
       <c r="AU10" s="7"/>
@@ -4306,12 +4337,12 @@
       <c r="BK10" s="31"/>
       <c r="BL10" s="10"/>
     </row>
-    <row r="11" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:64" ht="61.5" customHeight="1">
       <c r="B11" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C11" s="58" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="D11" s="33"/>
       <c r="E11" s="6"/>
@@ -4336,43 +4367,45 @@
       <c r="X11" s="7"/>
       <c r="Y11" s="7"/>
       <c r="Z11" s="7"/>
-      <c r="AA11" s="37"/>
-      <c r="AB11" s="14"/>
+      <c r="AA11" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB11" s="14" t="s">
+        <v>57</v>
+      </c>
       <c r="AC11" s="9"/>
       <c r="AD11" s="30"/>
       <c r="AE11" s="31"/>
       <c r="AF11" s="31"/>
-      <c r="AG11" s="30"/>
+      <c r="AG11" s="13" t="s">
+        <v>133</v>
+      </c>
       <c r="AH11" s="7"/>
       <c r="AI11" s="13"/>
-      <c r="AJ11" s="101" t="s">
-        <v>132</v>
-      </c>
-      <c r="AK11" s="36"/>
-      <c r="AL11" s="13"/>
-      <c r="AM11" s="13" t="s">
-        <v>137</v>
-      </c>
+      <c r="AJ11" s="7"/>
+      <c r="AK11" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="AL11" s="7"/>
+      <c r="AM11" s="7"/>
       <c r="AN11" s="8"/>
-      <c r="AO11" s="12"/>
-      <c r="AP11" s="7"/>
-      <c r="AQ11" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="AR11" s="7"/>
+      <c r="AO11" s="9"/>
+      <c r="AP11" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="AQ11" s="7"/>
+      <c r="AR11" s="13" t="s">
+        <v>136</v>
+      </c>
       <c r="AS11" s="7"/>
       <c r="AT11" s="7"/>
       <c r="AU11" s="7"/>
-      <c r="AV11" s="17" t="s">
-        <v>37</v>
-      </c>
+      <c r="AV11" s="7"/>
       <c r="AW11" s="7"/>
-      <c r="AX11" s="13" t="s">
-        <v>222</v>
-      </c>
+      <c r="AX11" s="7"/>
       <c r="AY11" s="7"/>
       <c r="AZ11" s="10"/>
-      <c r="BA11" s="12"/>
+      <c r="BA11" s="9"/>
       <c r="BB11" s="31"/>
       <c r="BC11" s="31"/>
       <c r="BD11" s="31"/>
@@ -4385,88 +4418,78 @@
       <c r="BK11" s="31"/>
       <c r="BL11" s="10"/>
     </row>
-    <row r="12" spans="1:64" ht="183.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:64" ht="61.5" customHeight="1">
       <c r="B12" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" s="59" t="s">
-        <v>83</v>
-      </c>
-      <c r="D12" s="34" t="s">
-        <v>43</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="C12" s="58" t="s">
+        <v>108</v>
+      </c>
+      <c r="D12" s="33"/>
       <c r="E12" s="6"/>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
+      <c r="J12" s="13"/>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="8"/>
+      <c r="O12" s="30"/>
+      <c r="P12" s="14"/>
       <c r="Q12" s="9"/>
-      <c r="R12" s="13" t="s">
-        <v>23</v>
-      </c>
+      <c r="R12" s="7"/>
       <c r="S12" s="7"/>
       <c r="T12" s="7"/>
       <c r="U12" s="7"/>
       <c r="V12" s="7"/>
-      <c r="W12" s="13" t="s">
-        <v>44</v>
-      </c>
+      <c r="W12" s="13"/>
       <c r="X12" s="7"/>
       <c r="Y12" s="7"/>
       <c r="Z12" s="7"/>
-      <c r="AA12" s="7"/>
+      <c r="AA12" s="37"/>
       <c r="AB12" s="14"/>
-      <c r="AC12" s="29"/>
-      <c r="AD12" s="7"/>
-      <c r="AE12" s="7"/>
-      <c r="AF12" s="7"/>
-      <c r="AG12" s="7"/>
-      <c r="AH12" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI12" s="36"/>
-      <c r="AJ12" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="AK12" s="30"/>
-      <c r="AL12" s="7"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="30"/>
+      <c r="AE12" s="31"/>
+      <c r="AF12" s="31"/>
+      <c r="AG12" s="30"/>
+      <c r="AH12" s="7"/>
+      <c r="AI12" s="13"/>
+      <c r="AJ12" s="101" t="s">
+        <v>132</v>
+      </c>
+      <c r="AK12" s="36"/>
+      <c r="AL12" s="13"/>
       <c r="AM12" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN12" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO12" s="9"/>
+        <v>137</v>
+      </c>
+      <c r="AN12" s="8"/>
+      <c r="AO12" s="12"/>
       <c r="AP12" s="7"/>
       <c r="AQ12" s="17" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="AR12" s="7"/>
-      <c r="AS12" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="AT12" s="13" t="s">
-        <v>64</v>
-      </c>
+      <c r="AS12" s="7"/>
+      <c r="AT12" s="7"/>
       <c r="AU12" s="7"/>
-      <c r="AV12" s="7"/>
+      <c r="AV12" s="17" t="s">
+        <v>37</v>
+      </c>
       <c r="AW12" s="7"/>
-      <c r="AX12" s="7"/>
+      <c r="AX12" s="13" t="s">
+        <v>222</v>
+      </c>
       <c r="AY12" s="7"/>
       <c r="AZ12" s="10"/>
-      <c r="BA12" s="9"/>
+      <c r="BA12" s="12"/>
       <c r="BB12" s="31"/>
-      <c r="BC12" s="30"/>
+      <c r="BC12" s="31"/>
       <c r="BD12" s="31"/>
-      <c r="BE12" s="30"/>
-      <c r="BF12" s="30"/>
+      <c r="BE12" s="31"/>
+      <c r="BF12" s="31"/>
       <c r="BG12" s="31"/>
       <c r="BH12" s="31"/>
       <c r="BI12" s="31"/>
@@ -4474,15 +4497,15 @@
       <c r="BK12" s="31"/>
       <c r="BL12" s="10"/>
     </row>
-    <row r="13" spans="1:64" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="B13" s="27" t="s">
-        <v>74</v>
+    <row r="13" spans="1:64" ht="183.75" customHeight="1">
+      <c r="B13" s="28" t="s">
+        <v>63</v>
       </c>
       <c r="C13" s="59" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="7"/>
@@ -4497,54 +4520,54 @@
       <c r="O13" s="7"/>
       <c r="P13" s="8"/>
       <c r="Q13" s="9"/>
-      <c r="R13" s="7"/>
+      <c r="R13" s="13" t="s">
+        <v>23</v>
+      </c>
       <c r="S13" s="7"/>
-      <c r="T13" s="13" t="s">
-        <v>16</v>
-      </c>
+      <c r="T13" s="7"/>
       <c r="U13" s="7"/>
       <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
+      <c r="W13" s="13" t="s">
+        <v>44</v>
+      </c>
       <c r="X13" s="7"/>
-      <c r="Y13" s="13" t="s">
-        <v>11</v>
-      </c>
+      <c r="Y13" s="7"/>
       <c r="Z13" s="7"/>
       <c r="AA13" s="7"/>
-      <c r="AB13" s="8"/>
-      <c r="AC13" s="9"/>
+      <c r="AB13" s="14"/>
+      <c r="AC13" s="29"/>
       <c r="AD13" s="7"/>
       <c r="AE13" s="7"/>
-      <c r="AF13" s="13" t="s">
-        <v>12</v>
-      </c>
+      <c r="AF13" s="7"/>
       <c r="AG13" s="7"/>
-      <c r="AH13" s="7"/>
-      <c r="AI13" s="7"/>
-      <c r="AJ13" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="AK13" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="AL13" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="AM13" s="7"/>
-      <c r="AN13" s="8"/>
+      <c r="AH13" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI13" s="36"/>
+      <c r="AJ13" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="AK13" s="30"/>
+      <c r="AL13" s="7"/>
+      <c r="AM13" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN13" s="14" t="s">
+        <v>45</v>
+      </c>
       <c r="AO13" s="9"/>
       <c r="AP13" s="7"/>
-      <c r="AQ13" s="7"/>
-      <c r="AR13" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="AS13" s="7"/>
+      <c r="AQ13" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="AR13" s="7"/>
+      <c r="AS13" s="13" t="s">
+        <v>55</v>
+      </c>
       <c r="AT13" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="AU13" s="13" t="s">
-        <v>62</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="AU13" s="7"/>
       <c r="AV13" s="7"/>
       <c r="AW13" s="7"/>
       <c r="AX13" s="7"/>
@@ -4552,25 +4575,27 @@
       <c r="AZ13" s="10"/>
       <c r="BA13" s="9"/>
       <c r="BB13" s="31"/>
-      <c r="BC13" s="31"/>
-      <c r="BD13" s="30"/>
-      <c r="BE13" s="31"/>
+      <c r="BC13" s="30"/>
+      <c r="BD13" s="31"/>
+      <c r="BE13" s="30"/>
       <c r="BF13" s="30"/>
-      <c r="BG13" s="30"/>
+      <c r="BG13" s="31"/>
       <c r="BH13" s="31"/>
       <c r="BI13" s="31"/>
       <c r="BJ13" s="31"/>
       <c r="BK13" s="31"/>
       <c r="BL13" s="10"/>
     </row>
-    <row r="14" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:64" ht="67.5">
       <c r="B14" s="27" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>85</v>
-      </c>
-      <c r="D14" s="33"/>
+        <v>84</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>75</v>
+      </c>
       <c r="E14" s="6"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
@@ -4579,74 +4604,80 @@
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
-      <c r="M14" s="13"/>
+      <c r="M14" s="7"/>
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
       <c r="P14" s="8"/>
-      <c r="Q14" s="12"/>
+      <c r="Q14" s="9"/>
       <c r="R14" s="7"/>
-      <c r="S14" s="13"/>
-      <c r="T14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="13" t="s">
+        <v>16</v>
+      </c>
       <c r="U14" s="7"/>
       <c r="V14" s="7"/>
       <c r="W14" s="7"/>
       <c r="X14" s="7"/>
       <c r="Y14" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z14" s="13"/>
+        <v>11</v>
+      </c>
+      <c r="Z14" s="7"/>
       <c r="AA14" s="7"/>
-      <c r="AB14" s="32"/>
-      <c r="AC14" s="12"/>
+      <c r="AB14" s="8"/>
+      <c r="AC14" s="9"/>
       <c r="AD14" s="7"/>
-      <c r="AE14" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="AF14" s="38"/>
-      <c r="AG14" s="37" t="s">
-        <v>68</v>
-      </c>
+      <c r="AE14" s="7"/>
+      <c r="AF14" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG14" s="7"/>
       <c r="AH14" s="7"/>
-      <c r="AI14" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ14" s="30"/>
-      <c r="AK14" s="7"/>
-      <c r="AL14" s="13"/>
-      <c r="AM14" s="13"/>
-      <c r="AN14" s="17" t="s">
-        <v>60</v>
-      </c>
+      <c r="AI14" s="7"/>
+      <c r="AJ14" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="AK14" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL14" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="AM14" s="7"/>
+      <c r="AN14" s="8"/>
       <c r="AO14" s="9"/>
-      <c r="AP14" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ14" s="13"/>
-      <c r="AR14" s="7"/>
+      <c r="AP14" s="7"/>
+      <c r="AQ14" s="7"/>
+      <c r="AR14" s="17" t="s">
+        <v>14</v>
+      </c>
       <c r="AS14" s="7"/>
-      <c r="AT14" s="7"/>
-      <c r="AU14" s="7"/>
+      <c r="AT14" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="AU14" s="13" t="s">
+        <v>62</v>
+      </c>
       <c r="AV14" s="7"/>
       <c r="AW14" s="7"/>
       <c r="AX14" s="7"/>
       <c r="AY14" s="7"/>
       <c r="AZ14" s="10"/>
       <c r="BA14" s="9"/>
-      <c r="BB14" s="30"/>
-      <c r="BC14" s="30"/>
-      <c r="BD14" s="31"/>
+      <c r="BB14" s="31"/>
+      <c r="BC14" s="31"/>
+      <c r="BD14" s="30"/>
       <c r="BE14" s="31"/>
-      <c r="BF14" s="31"/>
-      <c r="BG14" s="31"/>
+      <c r="BF14" s="30"/>
+      <c r="BG14" s="30"/>
       <c r="BH14" s="31"/>
       <c r="BI14" s="31"/>
       <c r="BJ14" s="31"/>
       <c r="BK14" s="31"/>
       <c r="BL14" s="10"/>
     </row>
-    <row r="15" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:64" ht="61.5" customHeight="1">
       <c r="B15" s="27" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C15" s="59" t="s">
         <v>85</v>
@@ -4654,78 +4685,70 @@
       <c r="D15" s="33"/>
       <c r="E15" s="6"/>
       <c r="F15" s="7"/>
-      <c r="G15" s="13"/>
+      <c r="G15" s="7"/>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
-      <c r="J15" s="13" t="s">
-        <v>28</v>
-      </c>
+      <c r="J15" s="7"/>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
+      <c r="M15" s="13"/>
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
-      <c r="P15" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q15" s="9"/>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="12"/>
       <c r="R15" s="7"/>
-      <c r="S15" s="7"/>
+      <c r="S15" s="13"/>
       <c r="T15" s="7"/>
       <c r="U15" s="7"/>
       <c r="V15" s="7"/>
-      <c r="W15" s="13" t="s">
-        <v>30</v>
-      </c>
+      <c r="W15" s="7"/>
       <c r="X15" s="7"/>
-      <c r="Y15" s="7"/>
-      <c r="Z15" s="7"/>
+      <c r="Y15" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z15" s="13"/>
       <c r="AA15" s="7"/>
-      <c r="AB15" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="AC15" s="9"/>
-      <c r="AD15" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE15" s="7"/>
-      <c r="AF15" s="7"/>
-      <c r="AG15" s="30"/>
+      <c r="AB15" s="32"/>
+      <c r="AC15" s="12"/>
+      <c r="AD15" s="7"/>
+      <c r="AE15" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF15" s="38"/>
+      <c r="AG15" s="37" t="s">
+        <v>68</v>
+      </c>
       <c r="AH15" s="7"/>
-      <c r="AI15" s="13"/>
-      <c r="AJ15" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="AK15" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="AL15" s="7"/>
-      <c r="AM15" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="AN15" s="8"/>
-      <c r="AO15" s="12"/>
-      <c r="AP15" s="13"/>
+      <c r="AI15" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ15" s="30"/>
+      <c r="AK15" s="7"/>
+      <c r="AL15" s="13"/>
+      <c r="AM15" s="13"/>
+      <c r="AN15" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="AO15" s="9"/>
+      <c r="AP15" s="13" t="s">
+        <v>72</v>
+      </c>
       <c r="AQ15" s="13"/>
-      <c r="AR15" s="17" t="s">
-        <v>61</v>
-      </c>
+      <c r="AR15" s="7"/>
       <c r="AS15" s="7"/>
-      <c r="AT15" s="13" t="s">
-        <v>73</v>
-      </c>
+      <c r="AT15" s="7"/>
       <c r="AU15" s="7"/>
       <c r="AV15" s="7"/>
       <c r="AW15" s="7"/>
       <c r="AX15" s="7"/>
       <c r="AY15" s="7"/>
       <c r="AZ15" s="10"/>
-      <c r="BA15" s="12"/>
+      <c r="BA15" s="9"/>
       <c r="BB15" s="30"/>
       <c r="BC15" s="30"/>
-      <c r="BD15" s="30"/>
+      <c r="BD15" s="31"/>
       <c r="BE15" s="31"/>
-      <c r="BF15" s="30"/>
+      <c r="BF15" s="31"/>
       <c r="BG15" s="31"/>
       <c r="BH15" s="31"/>
       <c r="BI15" s="31"/>
@@ -4733,190 +4756,188 @@
       <c r="BK15" s="31"/>
       <c r="BL15" s="10"/>
     </row>
-    <row r="16" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="57" t="s">
+    <row r="16" spans="1:64" ht="61.5" customHeight="1">
+      <c r="B16" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="59" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="33"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="X16" s="7"/>
+      <c r="Y16" s="7"/>
+      <c r="Z16" s="7"/>
+      <c r="AA16" s="7"/>
+      <c r="AB16" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC16" s="9"/>
+      <c r="AD16" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE16" s="7"/>
+      <c r="AF16" s="7"/>
+      <c r="AG16" s="30"/>
+      <c r="AH16" s="7"/>
+      <c r="AI16" s="13"/>
+      <c r="AJ16" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="AK16" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL16" s="7"/>
+      <c r="AM16" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="AN16" s="8"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="13"/>
+      <c r="AQ16" s="13"/>
+      <c r="AR16" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS16" s="7"/>
+      <c r="AT16" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU16" s="7"/>
+      <c r="AV16" s="7"/>
+      <c r="AW16" s="7"/>
+      <c r="AX16" s="7"/>
+      <c r="AY16" s="7"/>
+      <c r="AZ16" s="10"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="30"/>
+      <c r="BC16" s="30"/>
+      <c r="BD16" s="30"/>
+      <c r="BE16" s="31"/>
+      <c r="BF16" s="30"/>
+      <c r="BG16" s="31"/>
+      <c r="BH16" s="31"/>
+      <c r="BI16" s="31"/>
+      <c r="BJ16" s="31"/>
+      <c r="BK16" s="31"/>
+      <c r="BL16" s="10"/>
+    </row>
+    <row r="17" spans="2:64" ht="61.5" customHeight="1">
+      <c r="B17" s="57" t="s">
         <v>76</v>
       </c>
-      <c r="C16" s="60" t="s">
+      <c r="C17" s="60" t="s">
         <v>107</v>
       </c>
-      <c r="D16" s="76" t="s">
+      <c r="D17" s="76" t="s">
         <v>106</v>
       </c>
-      <c r="E16" s="40"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="42"/>
-      <c r="K16" s="41"/>
-      <c r="L16" s="41"/>
-      <c r="M16" s="13" t="s">
+      <c r="E17" s="40"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="41"/>
+      <c r="M17" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="N16" s="41"/>
-      <c r="O16" s="41"/>
-      <c r="P16" s="43"/>
-      <c r="Q16" s="104" t="s">
+      <c r="N17" s="41"/>
+      <c r="O17" s="41"/>
+      <c r="P17" s="43"/>
+      <c r="Q17" s="104" t="s">
         <v>140</v>
       </c>
-      <c r="R16" s="103"/>
-      <c r="S16" s="41"/>
-      <c r="T16" s="41"/>
-      <c r="U16" s="41"/>
-      <c r="V16" s="41"/>
-      <c r="W16" s="42"/>
-      <c r="X16" s="41"/>
-      <c r="Y16" s="30" t="s">
+      <c r="R17" s="103"/>
+      <c r="S17" s="41"/>
+      <c r="T17" s="41"/>
+      <c r="U17" s="41"/>
+      <c r="V17" s="41"/>
+      <c r="W17" s="42"/>
+      <c r="X17" s="41"/>
+      <c r="Y17" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="Z16" s="41"/>
-      <c r="AA16" s="41"/>
-      <c r="AB16" s="43"/>
-      <c r="AC16" s="44"/>
-      <c r="AD16" s="45"/>
-      <c r="AE16" s="13"/>
-      <c r="AF16" s="41"/>
-      <c r="AG16" s="37"/>
-      <c r="AH16" s="41"/>
-      <c r="AI16" s="37"/>
-      <c r="AJ16" s="30" t="s">
+      <c r="Z17" s="41"/>
+      <c r="AA17" s="41"/>
+      <c r="AB17" s="43"/>
+      <c r="AC17" s="44"/>
+      <c r="AD17" s="45"/>
+      <c r="AE17" s="13"/>
+      <c r="AF17" s="41"/>
+      <c r="AG17" s="37"/>
+      <c r="AH17" s="41"/>
+      <c r="AI17" s="37"/>
+      <c r="AJ17" s="30" t="s">
         <v>199</v>
       </c>
-      <c r="AK16" s="46"/>
-      <c r="AL16" s="41"/>
-      <c r="AM16" s="46"/>
-      <c r="AN16" s="8"/>
-      <c r="AO16" s="47"/>
-      <c r="AP16" s="13" t="s">
+      <c r="AK17" s="46"/>
+      <c r="AL17" s="41"/>
+      <c r="AM17" s="46"/>
+      <c r="AN17" s="8"/>
+      <c r="AO17" s="47"/>
+      <c r="AP17" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="AQ16" s="42"/>
-      <c r="AR16" s="37" t="s">
+      <c r="AQ17" s="42"/>
+      <c r="AR17" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="AS16" s="41"/>
-      <c r="AT16" s="42"/>
-      <c r="AU16" s="41"/>
-      <c r="AV16" s="41"/>
-      <c r="AW16" s="41"/>
-      <c r="AX16" s="17" t="s">
+      <c r="AS17" s="41"/>
+      <c r="AT17" s="42"/>
+      <c r="AU17" s="41"/>
+      <c r="AV17" s="41"/>
+      <c r="AW17" s="41"/>
+      <c r="AX17" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="AY16" s="41"/>
-      <c r="AZ16" s="48"/>
-      <c r="BA16" s="47"/>
-      <c r="BB16" s="45"/>
-      <c r="BC16" s="45"/>
-      <c r="BD16" s="13" t="s">
+      <c r="AY17" s="41"/>
+      <c r="AZ17" s="48"/>
+      <c r="BA17" s="47"/>
+      <c r="BB17" s="45"/>
+      <c r="BC17" s="45"/>
+      <c r="BD17" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="BE16" s="71"/>
-      <c r="BF16" s="45"/>
-      <c r="BG16" s="71"/>
-      <c r="BH16" s="71"/>
-      <c r="BI16" s="71"/>
-      <c r="BJ16" s="71"/>
-      <c r="BK16" s="71"/>
-      <c r="BL16" s="48"/>
+      <c r="BE17" s="71"/>
+      <c r="BF17" s="45"/>
+      <c r="BG17" s="71"/>
+      <c r="BH17" s="71"/>
+      <c r="BI17" s="71"/>
+      <c r="BJ17" s="71"/>
+      <c r="BK17" s="71"/>
+      <c r="BL17" s="48"/>
     </row>
-    <row r="17" spans="2:64" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="27" t="s">
+    <row r="18" spans="2:64" ht="76.5" customHeight="1">
+      <c r="B18" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="C17" s="59" t="s">
+      <c r="C18" s="59" t="s">
         <v>108</v>
-      </c>
-      <c r="D17" s="33"/>
-      <c r="E17" s="64"/>
-      <c r="F17" s="65"/>
-      <c r="G17" s="65"/>
-      <c r="H17" s="65"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="65"/>
-      <c r="K17" s="65"/>
-      <c r="L17" s="65"/>
-      <c r="M17" s="65"/>
-      <c r="N17" s="65"/>
-      <c r="O17" s="65"/>
-      <c r="P17" s="66"/>
-      <c r="Q17" s="67"/>
-      <c r="R17" s="65"/>
-      <c r="S17" s="65"/>
-      <c r="T17" s="65"/>
-      <c r="U17" s="65"/>
-      <c r="V17" s="65"/>
-      <c r="W17" s="65"/>
-      <c r="X17" s="65"/>
-      <c r="Y17" s="65"/>
-      <c r="Z17" s="65"/>
-      <c r="AA17" s="65"/>
-      <c r="AB17" s="66"/>
-      <c r="AC17" s="67"/>
-      <c r="AD17" s="65"/>
-      <c r="AE17" s="68" t="s">
-        <v>87</v>
-      </c>
-      <c r="AF17" s="65"/>
-      <c r="AG17" s="68"/>
-      <c r="AH17" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="AI17" s="69"/>
-      <c r="AJ17" s="65"/>
-      <c r="AK17" s="65"/>
-      <c r="AL17" s="65"/>
-      <c r="AM17" s="65"/>
-      <c r="AN17" s="66"/>
-      <c r="AO17" s="67"/>
-      <c r="AP17" s="69" t="s">
-        <v>18</v>
-      </c>
-      <c r="AQ17" s="69"/>
-      <c r="AR17" s="65"/>
-      <c r="AS17" s="65"/>
-      <c r="AT17" s="69" t="s">
-        <v>25</v>
-      </c>
-      <c r="AU17" s="73"/>
-      <c r="AV17" s="65"/>
-      <c r="AW17" s="69" t="s">
-        <v>89</v>
-      </c>
-      <c r="AX17" s="69" t="s">
-        <v>90</v>
-      </c>
-      <c r="AY17" s="69" t="s">
-        <v>91</v>
-      </c>
-      <c r="AZ17" s="70" t="s">
-        <v>92</v>
-      </c>
-      <c r="BA17" s="67"/>
-      <c r="BB17" s="73" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC17" s="73"/>
-      <c r="BD17" s="73" t="s">
-        <v>94</v>
-      </c>
-      <c r="BE17" s="73" t="s">
-        <v>95</v>
-      </c>
-      <c r="BF17" s="72"/>
-      <c r="BG17" s="73"/>
-      <c r="BH17" s="72"/>
-      <c r="BI17" s="72"/>
-      <c r="BJ17" s="72"/>
-      <c r="BK17" s="73"/>
-      <c r="BL17" s="70"/>
-    </row>
-    <row r="18" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="77" t="s">
-        <v>144</v>
-      </c>
-      <c r="C18" s="78" t="s">
-        <v>107</v>
       </c>
       <c r="D18" s="33"/>
       <c r="E18" s="64"/>
@@ -4945,10 +4966,14 @@
       <c r="AB18" s="66"/>
       <c r="AC18" s="67"/>
       <c r="AD18" s="65"/>
-      <c r="AE18" s="65"/>
+      <c r="AE18" s="68" t="s">
+        <v>87</v>
+      </c>
       <c r="AF18" s="65"/>
       <c r="AG18" s="68"/>
-      <c r="AH18" s="65"/>
+      <c r="AH18" s="56" t="s">
+        <v>88</v>
+      </c>
       <c r="AI18" s="69"/>
       <c r="AJ18" s="65"/>
       <c r="AK18" s="65"/>
@@ -4957,53 +4982,55 @@
       <c r="AN18" s="66"/>
       <c r="AO18" s="67"/>
       <c r="AP18" s="69" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="AQ18" s="69"/>
-      <c r="AR18" s="69" t="s">
-        <v>97</v>
-      </c>
+      <c r="AR18" s="65"/>
       <c r="AS18" s="65"/>
-      <c r="AT18" s="65"/>
-      <c r="AU18" s="69"/>
+      <c r="AT18" s="69" t="s">
+        <v>25</v>
+      </c>
+      <c r="AU18" s="73"/>
       <c r="AV18" s="65"/>
-      <c r="AW18" s="65"/>
-      <c r="AX18" s="65"/>
-      <c r="AY18" s="69"/>
+      <c r="AW18" s="69" t="s">
+        <v>89</v>
+      </c>
+      <c r="AX18" s="69" t="s">
+        <v>90</v>
+      </c>
+      <c r="AY18" s="69" t="s">
+        <v>91</v>
+      </c>
       <c r="AZ18" s="70" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="BA18" s="67"/>
-      <c r="BB18" s="72"/>
+      <c r="BB18" s="73" t="s">
+        <v>93</v>
+      </c>
       <c r="BC18" s="73"/>
-      <c r="BD18" s="72"/>
-      <c r="BE18" s="72"/>
-      <c r="BF18" s="73" t="s">
-        <v>99</v>
-      </c>
+      <c r="BD18" s="73" t="s">
+        <v>94</v>
+      </c>
+      <c r="BE18" s="73" t="s">
+        <v>95</v>
+      </c>
+      <c r="BF18" s="72"/>
       <c r="BG18" s="73"/>
-      <c r="BH18" s="73" t="s">
-        <v>100</v>
-      </c>
-      <c r="BI18" s="73" t="s">
-        <v>101</v>
-      </c>
-      <c r="BJ18" s="73" t="s">
-        <v>102</v>
-      </c>
+      <c r="BH18" s="72"/>
+      <c r="BI18" s="72"/>
+      <c r="BJ18" s="72"/>
       <c r="BK18" s="73"/>
-      <c r="BL18" s="70" t="s">
-        <v>103</v>
-      </c>
+      <c r="BL18" s="70"/>
     </row>
-    <row r="19" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:64" ht="61.5" customHeight="1">
       <c r="B19" s="77" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="C19" s="78" t="s">
         <v>107</v>
       </c>
-      <c r="D19" s="39"/>
+      <c r="D19" s="33"/>
       <c r="E19" s="64"/>
       <c r="F19" s="65"/>
       <c r="G19" s="65"/>
@@ -5041,9 +5068,13 @@
       <c r="AM19" s="65"/>
       <c r="AN19" s="66"/>
       <c r="AO19" s="67"/>
-      <c r="AP19" s="69"/>
+      <c r="AP19" s="69" t="s">
+        <v>96</v>
+      </c>
       <c r="AQ19" s="69"/>
-      <c r="AR19" s="69"/>
+      <c r="AR19" s="69" t="s">
+        <v>97</v>
+      </c>
       <c r="AS19" s="65"/>
       <c r="AT19" s="65"/>
       <c r="AU19" s="69"/>
@@ -5051,26 +5082,38 @@
       <c r="AW19" s="65"/>
       <c r="AX19" s="65"/>
       <c r="AY19" s="69"/>
-      <c r="AZ19" s="70"/>
+      <c r="AZ19" s="70" t="s">
+        <v>98</v>
+      </c>
       <c r="BA19" s="67"/>
       <c r="BB19" s="72"/>
       <c r="BC19" s="73"/>
       <c r="BD19" s="72"/>
       <c r="BE19" s="72"/>
-      <c r="BF19" s="73"/>
+      <c r="BF19" s="73" t="s">
+        <v>99</v>
+      </c>
       <c r="BG19" s="73"/>
-      <c r="BH19" s="73"/>
-      <c r="BI19" s="73"/>
-      <c r="BJ19" s="73"/>
+      <c r="BH19" s="73" t="s">
+        <v>100</v>
+      </c>
+      <c r="BI19" s="73" t="s">
+        <v>101</v>
+      </c>
+      <c r="BJ19" s="73" t="s">
+        <v>102</v>
+      </c>
       <c r="BK19" s="73"/>
-      <c r="BL19" s="70"/>
+      <c r="BL19" s="70" t="s">
+        <v>103</v>
+      </c>
     </row>
-    <row r="20" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="C20" s="82" t="s">
-        <v>110</v>
+    <row r="20" spans="2:64" ht="61.5" customHeight="1">
+      <c r="B20" s="77" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" s="78" t="s">
+        <v>107</v>
       </c>
       <c r="D20" s="39"/>
       <c r="E20" s="64"/>
@@ -5134,9 +5177,9 @@
       <c r="BK20" s="73"/>
       <c r="BL20" s="70"/>
     </row>
-    <row r="21" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:64" ht="61.5" customHeight="1">
       <c r="B21" s="57" t="s">
-        <v>169</v>
+        <v>112</v>
       </c>
       <c r="C21" s="82" t="s">
         <v>110</v>
@@ -5203,76 +5246,145 @@
       <c r="BK21" s="73"/>
       <c r="BL21" s="70"/>
     </row>
-    <row r="22" spans="2:64" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="79" t="s">
+    <row r="22" spans="2:64" ht="61.5" customHeight="1">
+      <c r="B22" s="57" t="s">
+        <v>169</v>
+      </c>
+      <c r="C22" s="82" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" s="39"/>
+      <c r="E22" s="64"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="65"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="65"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="65"/>
+      <c r="M22" s="65"/>
+      <c r="N22" s="65"/>
+      <c r="O22" s="65"/>
+      <c r="P22" s="66"/>
+      <c r="Q22" s="67"/>
+      <c r="R22" s="65"/>
+      <c r="S22" s="65"/>
+      <c r="T22" s="65"/>
+      <c r="U22" s="65"/>
+      <c r="V22" s="65"/>
+      <c r="W22" s="65"/>
+      <c r="X22" s="65"/>
+      <c r="Y22" s="65"/>
+      <c r="Z22" s="65"/>
+      <c r="AA22" s="65"/>
+      <c r="AB22" s="66"/>
+      <c r="AC22" s="67"/>
+      <c r="AD22" s="65"/>
+      <c r="AE22" s="65"/>
+      <c r="AF22" s="65"/>
+      <c r="AG22" s="68"/>
+      <c r="AH22" s="65"/>
+      <c r="AI22" s="69"/>
+      <c r="AJ22" s="65"/>
+      <c r="AK22" s="65"/>
+      <c r="AL22" s="65"/>
+      <c r="AM22" s="65"/>
+      <c r="AN22" s="66"/>
+      <c r="AO22" s="67"/>
+      <c r="AP22" s="69"/>
+      <c r="AQ22" s="69"/>
+      <c r="AR22" s="69"/>
+      <c r="AS22" s="65"/>
+      <c r="AT22" s="65"/>
+      <c r="AU22" s="69"/>
+      <c r="AV22" s="65"/>
+      <c r="AW22" s="65"/>
+      <c r="AX22" s="65"/>
+      <c r="AY22" s="69"/>
+      <c r="AZ22" s="70"/>
+      <c r="BA22" s="67"/>
+      <c r="BB22" s="72"/>
+      <c r="BC22" s="73"/>
+      <c r="BD22" s="72"/>
+      <c r="BE22" s="72"/>
+      <c r="BF22" s="73"/>
+      <c r="BG22" s="73"/>
+      <c r="BH22" s="73"/>
+      <c r="BI22" s="73"/>
+      <c r="BJ22" s="73"/>
+      <c r="BK22" s="73"/>
+      <c r="BL22" s="70"/>
+    </row>
+    <row r="23" spans="2:64" ht="61.5" customHeight="1" thickBot="1">
+      <c r="B23" s="79" t="s">
         <v>170</v>
       </c>
-      <c r="C22" s="80" t="s">
+      <c r="C23" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="D22" s="81"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="50"/>
-      <c r="G22" s="50"/>
-      <c r="H22" s="50"/>
-      <c r="I22" s="50"/>
-      <c r="J22" s="50"/>
-      <c r="K22" s="50"/>
-      <c r="L22" s="50"/>
-      <c r="M22" s="50"/>
-      <c r="N22" s="50"/>
-      <c r="O22" s="50"/>
-      <c r="P22" s="51"/>
-      <c r="Q22" s="52"/>
-      <c r="R22" s="50"/>
-      <c r="S22" s="50"/>
-      <c r="T22" s="50"/>
-      <c r="U22" s="50"/>
-      <c r="V22" s="50"/>
-      <c r="W22" s="50"/>
-      <c r="X22" s="50"/>
-      <c r="Y22" s="50"/>
-      <c r="Z22" s="50"/>
-      <c r="AA22" s="50"/>
-      <c r="AB22" s="51"/>
-      <c r="AC22" s="52"/>
-      <c r="AD22" s="50"/>
-      <c r="AE22" s="50"/>
-      <c r="AF22" s="50"/>
-      <c r="AG22" s="53"/>
-      <c r="AH22" s="50"/>
-      <c r="AI22" s="54"/>
-      <c r="AJ22" s="50"/>
-      <c r="AK22" s="50"/>
-      <c r="AL22" s="50"/>
-      <c r="AM22" s="50"/>
-      <c r="AN22" s="51"/>
-      <c r="AO22" s="52"/>
-      <c r="AP22" s="54"/>
-      <c r="AQ22" s="54"/>
-      <c r="AR22" s="54"/>
-      <c r="AS22" s="50"/>
-      <c r="AT22" s="50"/>
-      <c r="AU22" s="54"/>
-      <c r="AV22" s="50"/>
-      <c r="AW22" s="50"/>
-      <c r="AX22" s="50"/>
-      <c r="AY22" s="54"/>
-      <c r="AZ22" s="55"/>
-      <c r="BA22" s="52"/>
-      <c r="BB22" s="74"/>
-      <c r="BC22" s="75"/>
-      <c r="BD22" s="74"/>
-      <c r="BE22" s="74"/>
-      <c r="BF22" s="75"/>
-      <c r="BG22" s="75"/>
-      <c r="BH22" s="75"/>
-      <c r="BI22" s="75"/>
-      <c r="BJ22" s="75"/>
-      <c r="BK22" s="75"/>
-      <c r="BL22" s="55"/>
+      <c r="D23" s="81"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="50"/>
+      <c r="I23" s="50"/>
+      <c r="J23" s="50"/>
+      <c r="K23" s="50"/>
+      <c r="L23" s="50"/>
+      <c r="M23" s="50"/>
+      <c r="N23" s="50"/>
+      <c r="O23" s="50"/>
+      <c r="P23" s="51"/>
+      <c r="Q23" s="52"/>
+      <c r="R23" s="50"/>
+      <c r="S23" s="50"/>
+      <c r="T23" s="50"/>
+      <c r="U23" s="50"/>
+      <c r="V23" s="50"/>
+      <c r="W23" s="50"/>
+      <c r="X23" s="50"/>
+      <c r="Y23" s="50"/>
+      <c r="Z23" s="50"/>
+      <c r="AA23" s="50"/>
+      <c r="AB23" s="51"/>
+      <c r="AC23" s="52"/>
+      <c r="AD23" s="50"/>
+      <c r="AE23" s="50"/>
+      <c r="AF23" s="50"/>
+      <c r="AG23" s="53"/>
+      <c r="AH23" s="50"/>
+      <c r="AI23" s="54"/>
+      <c r="AJ23" s="50"/>
+      <c r="AK23" s="50"/>
+      <c r="AL23" s="50"/>
+      <c r="AM23" s="50"/>
+      <c r="AN23" s="51"/>
+      <c r="AO23" s="52"/>
+      <c r="AP23" s="54"/>
+      <c r="AQ23" s="54"/>
+      <c r="AR23" s="54"/>
+      <c r="AS23" s="50"/>
+      <c r="AT23" s="50"/>
+      <c r="AU23" s="54"/>
+      <c r="AV23" s="50"/>
+      <c r="AW23" s="50"/>
+      <c r="AX23" s="50"/>
+      <c r="AY23" s="54"/>
+      <c r="AZ23" s="55"/>
+      <c r="BA23" s="52"/>
+      <c r="BB23" s="74"/>
+      <c r="BC23" s="75"/>
+      <c r="BD23" s="74"/>
+      <c r="BE23" s="74"/>
+      <c r="BF23" s="75"/>
+      <c r="BG23" s="75"/>
+      <c r="BH23" s="75"/>
+      <c r="BI23" s="75"/>
+      <c r="BJ23" s="75"/>
+      <c r="BK23" s="75"/>
+      <c r="BL23" s="55"/>
     </row>
-    <row r="23" spans="2:64" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="2:64" ht="17.25" thickTop="1"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B2:B3"/>
@@ -5294,7 +5406,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="3.375" style="83" customWidth="1"/>
     <col min="2" max="2" width="9" style="83"/>
@@ -5306,7 +5418,7 @@
     <col min="15" max="16384" width="9" style="83"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="32.25" thickBot="1">
       <c r="A1" s="110" t="s">
         <v>151</v>
       </c>
@@ -5317,7 +5429,7 @@
       <c r="D1" s="111"/>
       <c r="E1" s="109"/>
     </row>
-    <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1">
       <c r="B2" s="132" t="s">
         <v>2</v>
       </c>
@@ -5346,7 +5458,7 @@
       <c r="M2" s="130"/>
       <c r="N2" s="131"/>
     </row>
-    <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1">
       <c r="B3" s="133"/>
       <c r="C3" s="137"/>
       <c r="D3" s="137"/>
@@ -5379,7 +5491,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="108" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="108">
       <c r="B4" s="84" t="s">
         <v>120</v>
       </c>
@@ -5414,7 +5526,7 @@
       <c r="M4" s="107"/>
       <c r="N4" s="94"/>
     </row>
-    <row r="5" spans="1:14" ht="108" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="108">
       <c r="B5" s="85" t="s">
         <v>126</v>
       </c>
@@ -5449,7 +5561,7 @@
       <c r="M5" s="107"/>
       <c r="N5" s="95"/>
     </row>
-    <row r="6" spans="1:14" ht="108" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="108">
       <c r="B6" s="85" t="s">
         <v>127</v>
       </c>
@@ -5484,7 +5596,7 @@
       <c r="M6" s="107"/>
       <c r="N6" s="95"/>
     </row>
-    <row r="7" spans="1:14" ht="108" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="108">
       <c r="B7" s="85" t="s">
         <v>128</v>
       </c>
@@ -5519,7 +5631,7 @@
       <c r="M7" s="107"/>
       <c r="N7" s="95"/>
     </row>
-    <row r="8" spans="1:14" ht="108" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="108">
       <c r="B8" s="86" t="s">
         <v>3</v>
       </c>
@@ -5554,7 +5666,7 @@
       <c r="M8" s="107"/>
       <c r="N8" s="95"/>
     </row>
-    <row r="9" spans="1:14" ht="175.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="175.5">
       <c r="B9" s="86" t="s">
         <v>46</v>
       </c>
@@ -5589,7 +5701,7 @@
       <c r="M9" s="107"/>
       <c r="N9" s="95"/>
     </row>
-    <row r="10" spans="1:14" ht="121.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="121.5">
       <c r="B10" s="86" t="s">
         <v>56</v>
       </c>
@@ -5624,7 +5736,7 @@
       <c r="M10" s="107"/>
       <c r="N10" s="95"/>
     </row>
-    <row r="11" spans="1:14" ht="108" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="108">
       <c r="B11" s="85" t="s">
         <v>63</v>
       </c>
@@ -5659,7 +5771,7 @@
       <c r="M11" s="107"/>
       <c r="N11" s="95"/>
     </row>
-    <row r="12" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="57" customHeight="1">
       <c r="B12" s="86" t="s">
         <v>74</v>
       </c>
@@ -5694,7 +5806,7 @@
       <c r="M12" s="107"/>
       <c r="N12" s="95"/>
     </row>
-    <row r="13" spans="1:14" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="347.25" customHeight="1">
       <c r="B13" s="86" t="s">
         <v>121</v>
       </c>
@@ -5729,7 +5841,7 @@
       <c r="M13" s="107"/>
       <c r="N13" s="95"/>
     </row>
-    <row r="14" spans="1:14" ht="175.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="175.5">
       <c r="B14" s="87" t="s">
         <v>184</v>
       </c>
@@ -5758,7 +5870,7 @@
       <c r="M14" s="107"/>
       <c r="N14" s="95"/>
     </row>
-    <row r="15" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="57" customHeight="1">
       <c r="B15" s="87" t="s">
         <v>76</v>
       </c>
@@ -5791,7 +5903,7 @@
       <c r="M15" s="107"/>
       <c r="N15" s="95"/>
     </row>
-    <row r="16" spans="1:14" ht="121.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="121.5">
       <c r="B16" s="86" t="s">
         <v>86</v>
       </c>
@@ -5824,7 +5936,7 @@
       <c r="M16" s="107"/>
       <c r="N16" s="95"/>
     </row>
-    <row r="17" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:14" ht="57" customHeight="1">
       <c r="B17" s="88" t="s">
         <v>144</v>
       </c>
@@ -5857,7 +5969,7 @@
       <c r="M17" s="91"/>
       <c r="N17" s="95"/>
     </row>
-    <row r="18" spans="2:14" ht="162" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:14" ht="162">
       <c r="B18" s="88" t="s">
         <v>109</v>
       </c>
@@ -5892,7 +6004,7 @@
       <c r="M18" s="107"/>
       <c r="N18" s="95"/>
     </row>
-    <row r="19" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:14" ht="57" customHeight="1">
       <c r="B19" s="87" t="s">
         <v>112</v>
       </c>
@@ -5927,7 +6039,7 @@
       <c r="M19" s="107"/>
       <c r="N19" s="95"/>
     </row>
-    <row r="20" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:14" ht="57" customHeight="1">
       <c r="B20" s="87" t="s">
         <v>171</v>
       </c>
@@ -5962,7 +6074,7 @@
       <c r="M20" s="107"/>
       <c r="N20" s="114"/>
     </row>
-    <row r="21" spans="2:14" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:14" ht="57" customHeight="1" thickBot="1">
       <c r="B21" s="89" t="s">
         <v>111</v>
       </c>
@@ -5997,7 +6109,7 @@
       <c r="M21" s="122"/>
       <c r="N21" s="97"/>
     </row>
-    <row r="22" spans="2:14" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="2:14" ht="14.25" thickTop="1"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="K2:N2"/>
@@ -6070,7 +6182,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="3.375" style="83" customWidth="1"/>
     <col min="2" max="2" width="9" style="83"/>
@@ -6081,7 +6193,7 @@
     <col min="10" max="16384" width="9" style="83"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="32.25" thickBot="1">
       <c r="A1" s="110" t="s">
         <v>0</v>
       </c>
@@ -6092,7 +6204,7 @@
       <c r="D1" s="111"/>
       <c r="E1" s="109"/>
     </row>
-    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1">
       <c r="B2" s="132" t="s">
         <v>2</v>
       </c>
@@ -6112,7 +6224,7 @@
       <c r="H2" s="130"/>
       <c r="I2" s="131"/>
     </row>
-    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1">
       <c r="B3" s="133"/>
       <c r="C3" s="137"/>
       <c r="D3" s="137"/>
@@ -6130,7 +6242,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="57" customHeight="1">
       <c r="B4" s="84" t="s">
         <v>120</v>
       </c>
@@ -6148,7 +6260,7 @@
       <c r="H4" s="90"/>
       <c r="I4" s="94"/>
     </row>
-    <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="57" customHeight="1">
       <c r="B5" s="85" t="s">
         <v>126</v>
       </c>
@@ -6166,7 +6278,7 @@
       <c r="H5" s="91"/>
       <c r="I5" s="95"/>
     </row>
-    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="57" customHeight="1">
       <c r="B6" s="85" t="s">
         <v>127</v>
       </c>
@@ -6184,7 +6296,7 @@
       <c r="H6" s="91"/>
       <c r="I6" s="95"/>
     </row>
-    <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="57" customHeight="1">
       <c r="B7" s="85" t="s">
         <v>128</v>
       </c>
@@ -6202,7 +6314,7 @@
       <c r="H7" s="91"/>
       <c r="I7" s="95"/>
     </row>
-    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="57" customHeight="1">
       <c r="B8" s="86" t="s">
         <v>3</v>
       </c>
@@ -6220,7 +6332,7 @@
       <c r="H8" s="91"/>
       <c r="I8" s="95"/>
     </row>
-    <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="27">
       <c r="B9" s="86" t="s">
         <v>46</v>
       </c>
@@ -6238,7 +6350,7 @@
       <c r="H9" s="91"/>
       <c r="I9" s="95"/>
     </row>
-    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="57" customHeight="1">
       <c r="B10" s="86" t="s">
         <v>56</v>
       </c>
@@ -6256,7 +6368,7 @@
       <c r="H10" s="91"/>
       <c r="I10" s="95"/>
     </row>
-    <row r="11" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="40.5">
       <c r="B11" s="85" t="s">
         <v>63</v>
       </c>
@@ -6274,7 +6386,7 @@
       <c r="H11" s="91"/>
       <c r="I11" s="95"/>
     </row>
-    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="57" customHeight="1">
       <c r="B12" s="86" t="s">
         <v>74</v>
       </c>
@@ -6292,7 +6404,7 @@
       <c r="H12" s="91"/>
       <c r="I12" s="95"/>
     </row>
-    <row r="13" spans="1:9" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="347.25" customHeight="1">
       <c r="B13" s="86" t="s">
         <v>121</v>
       </c>
@@ -6310,7 +6422,7 @@
       <c r="H13" s="91"/>
       <c r="I13" s="95"/>
     </row>
-    <row r="14" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="409.5">
       <c r="B14" s="87" t="s">
         <v>184</v>
       </c>
@@ -6328,7 +6440,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="57" customHeight="1">
       <c r="B15" s="87" t="s">
         <v>76</v>
       </c>
@@ -6346,7 +6458,7 @@
       <c r="H15" s="91"/>
       <c r="I15" s="95"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9">
       <c r="B16" s="86" t="s">
         <v>86</v>
       </c>
@@ -6364,7 +6476,7 @@
       <c r="H16" s="91"/>
       <c r="I16" s="95"/>
     </row>
-    <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="57" customHeight="1">
       <c r="B17" s="88" t="s">
         <v>144</v>
       </c>
@@ -6382,7 +6494,7 @@
       <c r="H17" s="91"/>
       <c r="I17" s="95"/>
     </row>
-    <row r="18" spans="2:9" ht="27" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" ht="27">
       <c r="B18" s="88" t="s">
         <v>109</v>
       </c>
@@ -6400,7 +6512,7 @@
       <c r="H18" s="91"/>
       <c r="I18" s="95"/>
     </row>
-    <row r="19" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" ht="57" customHeight="1">
       <c r="B19" s="87" t="s">
         <v>112</v>
       </c>
@@ -6418,7 +6530,7 @@
       <c r="H19" s="91"/>
       <c r="I19" s="95"/>
     </row>
-    <row r="20" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" ht="57" customHeight="1">
       <c r="B20" s="87" t="s">
         <v>170</v>
       </c>
@@ -6436,7 +6548,7 @@
       <c r="H20" s="113"/>
       <c r="I20" s="114"/>
     </row>
-    <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1">
       <c r="B21" s="89" t="s">
         <v>111</v>
       </c>
@@ -6454,7 +6566,7 @@
       <c r="H21" s="96"/>
       <c r="I21" s="97"/>
     </row>
-    <row r="22" spans="2:9" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="2:9" ht="14.25" thickTop="1"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:B3"/>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -9,12 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="대일정" sheetId="1" r:id="rId1"/>
     <sheet name="2025.5" sheetId="2" r:id="rId2"/>
     <sheet name="2025.6" sheetId="3" r:id="rId3"/>
+    <sheet name="2025.7" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="231">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1337,6 +1338,10 @@
   <si>
     <t>M
 1/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7월</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2862,6 +2867,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2905,9 +2913,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3521,90 +3526,90 @@
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1">
-      <c r="B2" s="123" t="s">
+      <c r="B2" s="124" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="125" t="s">
+      <c r="C2" s="126" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="125" t="s">
+      <c r="D2" s="126" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="129">
+      <c r="E2" s="130">
         <v>23</v>
       </c>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="127"/>
-      <c r="K2" s="127"/>
-      <c r="L2" s="127"/>
-      <c r="M2" s="127"/>
-      <c r="N2" s="127"/>
-      <c r="O2" s="127"/>
-      <c r="P2" s="127"/>
-      <c r="Q2" s="127">
+      <c r="F2" s="128"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="128"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="128"/>
+      <c r="O2" s="128"/>
+      <c r="P2" s="128"/>
+      <c r="Q2" s="128">
         <v>24</v>
       </c>
-      <c r="R2" s="127"/>
-      <c r="S2" s="127"/>
-      <c r="T2" s="127"/>
-      <c r="U2" s="127"/>
-      <c r="V2" s="127"/>
-      <c r="W2" s="127"/>
-      <c r="X2" s="127"/>
-      <c r="Y2" s="127"/>
-      <c r="Z2" s="127"/>
-      <c r="AA2" s="127"/>
-      <c r="AB2" s="127"/>
-      <c r="AC2" s="127">
+      <c r="R2" s="128"/>
+      <c r="S2" s="128"/>
+      <c r="T2" s="128"/>
+      <c r="U2" s="128"/>
+      <c r="V2" s="128"/>
+      <c r="W2" s="128"/>
+      <c r="X2" s="128"/>
+      <c r="Y2" s="128"/>
+      <c r="Z2" s="128"/>
+      <c r="AA2" s="128"/>
+      <c r="AB2" s="128"/>
+      <c r="AC2" s="128">
         <v>25</v>
       </c>
-      <c r="AD2" s="127"/>
-      <c r="AE2" s="127"/>
-      <c r="AF2" s="127"/>
-      <c r="AG2" s="127"/>
-      <c r="AH2" s="127"/>
-      <c r="AI2" s="127"/>
-      <c r="AJ2" s="127"/>
-      <c r="AK2" s="127"/>
-      <c r="AL2" s="127"/>
-      <c r="AM2" s="127"/>
-      <c r="AN2" s="127"/>
-      <c r="AO2" s="127">
+      <c r="AD2" s="128"/>
+      <c r="AE2" s="128"/>
+      <c r="AF2" s="128"/>
+      <c r="AG2" s="128"/>
+      <c r="AH2" s="128"/>
+      <c r="AI2" s="128"/>
+      <c r="AJ2" s="128"/>
+      <c r="AK2" s="128"/>
+      <c r="AL2" s="128"/>
+      <c r="AM2" s="128"/>
+      <c r="AN2" s="128"/>
+      <c r="AO2" s="128">
         <v>26</v>
       </c>
-      <c r="AP2" s="127"/>
-      <c r="AQ2" s="127"/>
-      <c r="AR2" s="127"/>
-      <c r="AS2" s="127"/>
-      <c r="AT2" s="127"/>
-      <c r="AU2" s="127"/>
-      <c r="AV2" s="127"/>
-      <c r="AW2" s="127"/>
-      <c r="AX2" s="127"/>
-      <c r="AY2" s="127"/>
-      <c r="AZ2" s="128"/>
-      <c r="BA2" s="127">
+      <c r="AP2" s="128"/>
+      <c r="AQ2" s="128"/>
+      <c r="AR2" s="128"/>
+      <c r="AS2" s="128"/>
+      <c r="AT2" s="128"/>
+      <c r="AU2" s="128"/>
+      <c r="AV2" s="128"/>
+      <c r="AW2" s="128"/>
+      <c r="AX2" s="128"/>
+      <c r="AY2" s="128"/>
+      <c r="AZ2" s="129"/>
+      <c r="BA2" s="128">
         <v>27</v>
       </c>
-      <c r="BB2" s="127"/>
-      <c r="BC2" s="127"/>
-      <c r="BD2" s="127"/>
-      <c r="BE2" s="127"/>
-      <c r="BF2" s="127"/>
-      <c r="BG2" s="127"/>
-      <c r="BH2" s="127"/>
-      <c r="BI2" s="127"/>
-      <c r="BJ2" s="127"/>
-      <c r="BK2" s="127"/>
-      <c r="BL2" s="128"/>
+      <c r="BB2" s="128"/>
+      <c r="BC2" s="128"/>
+      <c r="BD2" s="128"/>
+      <c r="BE2" s="128"/>
+      <c r="BF2" s="128"/>
+      <c r="BG2" s="128"/>
+      <c r="BH2" s="128"/>
+      <c r="BI2" s="128"/>
+      <c r="BJ2" s="128"/>
+      <c r="BK2" s="128"/>
+      <c r="BL2" s="129"/>
     </row>
     <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1">
-      <c r="B3" s="124"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="126"/>
+      <c r="B3" s="125"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
       <c r="E3" s="22">
         <v>1</v>
       </c>
@@ -4141,7 +4146,7 @@
       <c r="Y8" s="31"/>
       <c r="Z8" s="30"/>
       <c r="AA8" s="30"/>
-      <c r="AB8" s="138"/>
+      <c r="AB8" s="123"/>
       <c r="AC8" s="29"/>
       <c r="AD8" s="31"/>
       <c r="AE8" s="31"/>
@@ -4159,7 +4164,7 @@
       <c r="AM8" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="AN8" s="138"/>
+      <c r="AN8" s="123"/>
       <c r="AO8" s="29" t="s">
         <v>229</v>
       </c>
@@ -5430,39 +5435,39 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1">
-      <c r="B2" s="132" t="s">
+      <c r="B2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="136" t="s">
+      <c r="C2" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="D2" s="136" t="s">
+      <c r="D2" s="137" t="s">
         <v>180</v>
       </c>
-      <c r="E2" s="134" t="s">
+      <c r="E2" s="135" t="s">
         <v>129</v>
       </c>
       <c r="F2" s="98" t="s">
         <v>115</v>
       </c>
-      <c r="G2" s="130" t="s">
+      <c r="G2" s="131" t="s">
         <v>116</v>
       </c>
-      <c r="H2" s="130"/>
-      <c r="I2" s="130"/>
-      <c r="J2" s="131"/>
-      <c r="K2" s="130" t="s">
+      <c r="H2" s="131"/>
+      <c r="I2" s="131"/>
+      <c r="J2" s="132"/>
+      <c r="K2" s="131" t="s">
         <v>185</v>
       </c>
-      <c r="L2" s="130"/>
-      <c r="M2" s="130"/>
-      <c r="N2" s="131"/>
+      <c r="L2" s="131"/>
+      <c r="M2" s="131"/>
+      <c r="N2" s="132"/>
     </row>
     <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1">
-      <c r="B3" s="133"/>
-      <c r="C3" s="137"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="135"/>
+      <c r="B3" s="134"/>
+      <c r="C3" s="138"/>
+      <c r="D3" s="138"/>
+      <c r="E3" s="136"/>
       <c r="F3" s="99" t="s">
         <v>114</v>
       </c>
@@ -6205,30 +6210,431 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1">
-      <c r="B2" s="132" t="s">
+      <c r="B2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="136" t="s">
+      <c r="C2" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="D2" s="136" t="s">
+      <c r="D2" s="137" t="s">
         <v>180</v>
       </c>
-      <c r="E2" s="134" t="s">
+      <c r="E2" s="135" t="s">
         <v>129</v>
       </c>
-      <c r="F2" s="130" t="s">
+      <c r="F2" s="131" t="s">
         <v>185</v>
       </c>
-      <c r="G2" s="130"/>
-      <c r="H2" s="130"/>
-      <c r="I2" s="131"/>
+      <c r="G2" s="131"/>
+      <c r="H2" s="131"/>
+      <c r="I2" s="132"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1">
-      <c r="B3" s="133"/>
-      <c r="C3" s="137"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="135"/>
+      <c r="B3" s="134"/>
+      <c r="C3" s="138"/>
+      <c r="D3" s="138"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="99" t="s">
+        <v>117</v>
+      </c>
+      <c r="G3" s="99" t="s">
+        <v>118</v>
+      </c>
+      <c r="H3" s="99" t="s">
+        <v>119</v>
+      </c>
+      <c r="I3" s="100" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="57" customHeight="1">
+      <c r="B4" s="84" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4" s="118" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" s="118" t="s">
+        <v>181</v>
+      </c>
+      <c r="E4" s="92" t="s">
+        <v>155</v>
+      </c>
+      <c r="F4" s="116"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="94"/>
+    </row>
+    <row r="5" spans="1:9" ht="57" customHeight="1">
+      <c r="B5" s="85" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" s="119" t="s">
+        <v>178</v>
+      </c>
+      <c r="D5" s="119" t="s">
+        <v>181</v>
+      </c>
+      <c r="E5" s="93" t="s">
+        <v>156</v>
+      </c>
+      <c r="F5" s="116"/>
+      <c r="G5" s="107"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="95"/>
+    </row>
+    <row r="6" spans="1:9" ht="57" customHeight="1">
+      <c r="B6" s="85" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="119" t="s">
+        <v>178</v>
+      </c>
+      <c r="D6" s="119" t="s">
+        <v>181</v>
+      </c>
+      <c r="E6" s="93" t="s">
+        <v>157</v>
+      </c>
+      <c r="F6" s="116"/>
+      <c r="G6" s="107"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="95"/>
+    </row>
+    <row r="7" spans="1:9" ht="57" customHeight="1">
+      <c r="B7" s="85" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" s="119" t="s">
+        <v>178</v>
+      </c>
+      <c r="D7" s="119" t="s">
+        <v>181</v>
+      </c>
+      <c r="E7" s="93" t="s">
+        <v>158</v>
+      </c>
+      <c r="F7" s="116"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="91"/>
+      <c r="I7" s="95"/>
+    </row>
+    <row r="8" spans="1:9" ht="57" customHeight="1">
+      <c r="B8" s="86" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="119" t="s">
+        <v>178</v>
+      </c>
+      <c r="D8" s="119" t="s">
+        <v>181</v>
+      </c>
+      <c r="E8" s="93" t="s">
+        <v>159</v>
+      </c>
+      <c r="F8" s="116"/>
+      <c r="G8" s="107"/>
+      <c r="H8" s="91"/>
+      <c r="I8" s="95"/>
+    </row>
+    <row r="9" spans="1:9" ht="27">
+      <c r="B9" s="86" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="119" t="s">
+        <v>178</v>
+      </c>
+      <c r="D9" s="119" t="s">
+        <v>181</v>
+      </c>
+      <c r="E9" s="102" t="s">
+        <v>160</v>
+      </c>
+      <c r="F9" s="116"/>
+      <c r="G9" s="107"/>
+      <c r="H9" s="91"/>
+      <c r="I9" s="95"/>
+    </row>
+    <row r="10" spans="1:9" ht="57" customHeight="1">
+      <c r="B10" s="86" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="119" t="s">
+        <v>178</v>
+      </c>
+      <c r="D10" s="119" t="s">
+        <v>181</v>
+      </c>
+      <c r="E10" s="102" t="s">
+        <v>161</v>
+      </c>
+      <c r="F10" s="116"/>
+      <c r="G10" s="107"/>
+      <c r="H10" s="91"/>
+      <c r="I10" s="95"/>
+    </row>
+    <row r="11" spans="1:9" ht="40.5">
+      <c r="B11" s="85" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="119" t="s">
+        <v>178</v>
+      </c>
+      <c r="D11" s="119" t="s">
+        <v>181</v>
+      </c>
+      <c r="E11" s="102" t="s">
+        <v>162</v>
+      </c>
+      <c r="F11" s="116"/>
+      <c r="G11" s="107"/>
+      <c r="H11" s="91"/>
+      <c r="I11" s="95"/>
+    </row>
+    <row r="12" spans="1:9" ht="57" customHeight="1">
+      <c r="B12" s="86" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="119" t="s">
+        <v>178</v>
+      </c>
+      <c r="D12" s="119" t="s">
+        <v>181</v>
+      </c>
+      <c r="E12" s="102" t="s">
+        <v>163</v>
+      </c>
+      <c r="F12" s="116"/>
+      <c r="G12" s="107"/>
+      <c r="H12" s="91"/>
+      <c r="I12" s="95"/>
+    </row>
+    <row r="13" spans="1:9" ht="347.25" customHeight="1">
+      <c r="B13" s="86" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" s="119" t="s">
+        <v>178</v>
+      </c>
+      <c r="D13" s="119" t="s">
+        <v>181</v>
+      </c>
+      <c r="E13" s="102" t="s">
+        <v>164</v>
+      </c>
+      <c r="F13" s="116"/>
+      <c r="G13" s="107"/>
+      <c r="H13" s="91"/>
+      <c r="I13" s="95"/>
+    </row>
+    <row r="14" spans="1:9" ht="409.5">
+      <c r="B14" s="87" t="s">
+        <v>184</v>
+      </c>
+      <c r="C14" s="119" t="s">
+        <v>182</v>
+      </c>
+      <c r="D14" s="119" t="s">
+        <v>183</v>
+      </c>
+      <c r="E14" s="102"/>
+      <c r="F14" s="116"/>
+      <c r="G14" s="107"/>
+      <c r="H14" s="91"/>
+      <c r="I14" s="107" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="57" customHeight="1">
+      <c r="B15" s="87" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="119" t="s">
+        <v>178</v>
+      </c>
+      <c r="D15" s="119" t="s">
+        <v>181</v>
+      </c>
+      <c r="E15" s="102" t="s">
+        <v>165</v>
+      </c>
+      <c r="F15" s="116"/>
+      <c r="G15" s="107"/>
+      <c r="H15" s="91"/>
+      <c r="I15" s="95"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="B16" s="86" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="119" t="s">
+        <v>178</v>
+      </c>
+      <c r="D16" s="119" t="s">
+        <v>181</v>
+      </c>
+      <c r="E16" s="93" t="s">
+        <v>166</v>
+      </c>
+      <c r="F16" s="116"/>
+      <c r="G16" s="107"/>
+      <c r="H16" s="91"/>
+      <c r="I16" s="95"/>
+    </row>
+    <row r="17" spans="2:9" ht="57" customHeight="1">
+      <c r="B17" s="88" t="s">
+        <v>144</v>
+      </c>
+      <c r="C17" s="119" t="s">
+        <v>178</v>
+      </c>
+      <c r="D17" s="119" t="s">
+        <v>181</v>
+      </c>
+      <c r="E17" s="93" t="s">
+        <v>108</v>
+      </c>
+      <c r="F17" s="116"/>
+      <c r="G17" s="91"/>
+      <c r="H17" s="91"/>
+      <c r="I17" s="95"/>
+    </row>
+    <row r="18" spans="2:9" ht="27">
+      <c r="B18" s="88" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" s="119" t="s">
+        <v>178</v>
+      </c>
+      <c r="D18" s="119" t="s">
+        <v>181</v>
+      </c>
+      <c r="E18" s="102" t="s">
+        <v>167</v>
+      </c>
+      <c r="F18" s="116"/>
+      <c r="G18" s="107"/>
+      <c r="H18" s="91"/>
+      <c r="I18" s="95"/>
+    </row>
+    <row r="19" spans="2:9" ht="57" customHeight="1">
+      <c r="B19" s="87" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" s="119" t="s">
+        <v>178</v>
+      </c>
+      <c r="D19" s="119" t="s">
+        <v>181</v>
+      </c>
+      <c r="E19" s="93" t="s">
+        <v>142</v>
+      </c>
+      <c r="F19" s="116"/>
+      <c r="G19" s="106"/>
+      <c r="H19" s="91"/>
+      <c r="I19" s="95"/>
+    </row>
+    <row r="20" spans="2:9" ht="57" customHeight="1">
+      <c r="B20" s="87" t="s">
+        <v>170</v>
+      </c>
+      <c r="C20" s="119" t="s">
+        <v>178</v>
+      </c>
+      <c r="D20" s="119" t="s">
+        <v>181</v>
+      </c>
+      <c r="E20" s="115" t="s">
+        <v>172</v>
+      </c>
+      <c r="F20" s="116"/>
+      <c r="G20" s="112"/>
+      <c r="H20" s="113"/>
+      <c r="I20" s="114"/>
+    </row>
+    <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1">
+      <c r="B21" s="89" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="120" t="s">
+        <v>178</v>
+      </c>
+      <c r="D21" s="120" t="s">
+        <v>181</v>
+      </c>
+      <c r="E21" s="105" t="s">
+        <v>143</v>
+      </c>
+      <c r="F21" s="117"/>
+      <c r="G21" s="108"/>
+      <c r="H21" s="96"/>
+      <c r="I21" s="97"/>
+    </row>
+    <row r="22" spans="2:9" ht="14.25" thickTop="1"/>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:I2"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="3.375" style="83" customWidth="1"/>
+    <col min="2" max="2" width="9" style="83"/>
+    <col min="3" max="4" width="14.75" style="83" customWidth="1"/>
+    <col min="5" max="5" width="43" style="83" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="83" customWidth="1"/>
+    <col min="7" max="9" width="62.125" style="83" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="83"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="32.25" thickBot="1">
+      <c r="A1" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="111" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="109"/>
+    </row>
+    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1">
+      <c r="B2" s="133" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="137" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2" s="137" t="s">
+        <v>180</v>
+      </c>
+      <c r="E2" s="135" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2" s="131" t="s">
+        <v>230</v>
+      </c>
+      <c r="G2" s="131"/>
+      <c r="H2" s="131"/>
+      <c r="I2" s="132"/>
+    </row>
+    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1">
+      <c r="B3" s="134"/>
+      <c r="C3" s="138"/>
+      <c r="D3" s="138"/>
+      <c r="E3" s="136"/>
       <c r="F3" s="99" t="s">
         <v>117</v>
       </c>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\2.project\hkmc_ptc_heater\Doc\1. 일정\1. Weekly Plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\1. doc\HKMC_AIR_PTC\일정\PTC_HEATER_DOC (250626 Repo 변경, 해당 Repo 사용)\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="대일정" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="232">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1344,6 +1344,22 @@
     <t>7월</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>[조현진 전임, 임제훈 사원]
+- SWE.1 SRS 작성 완료 : ~ 6/30
+   : 3.1 Hardware - Software Interface
+   : 3.2 CAN Communication - Software Interface
+   : 4.1 Software State Transition Requirements
+   : 4.2.1.1 LV Sensor Fault / LV Over Voltage_Under Voltage Fault
+   : 4.2.1.2 HV Sensor Fault / HV Over Voltage_Under Voltage Fault
+- SWE.2 SADS 작성 계획
+   : Component 다이어그램 작성
+   : LV Sensor Fault / LV Over Voltage_Under Voltage Fault 정적, 동적 작성
+   : HV Sensor Fault / HV Over Voltage_Under Voltage Fault 정적, 동적 작성
+- SWE.3 SDDS 작성 계획
+   : LV Sensor Fault 작성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1352,7 +1368,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2497,7 +2513,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2914,6 +2930,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3504,7 +3526,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BL24"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.375" customWidth="1"/>
     <col min="2" max="2" width="18.875" customWidth="1"/>
@@ -3515,7 +3537,7 @@
     <col min="36" max="64" width="8.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" s="20" customFormat="1" ht="32.25" thickBot="1">
+    <row r="1" spans="1:64" s="20" customFormat="1" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -3525,7 +3547,7 @@
       <c r="C1" s="21"/>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1">
+    <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B2" s="124" t="s">
         <v>2</v>
       </c>
@@ -3606,7 +3628,7 @@
       <c r="BK2" s="128"/>
       <c r="BL2" s="129"/>
     </row>
-    <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1">
+    <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="125"/>
       <c r="C3" s="127"/>
       <c r="D3" s="127"/>
@@ -3791,7 +3813,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:64" ht="183" customHeight="1" thickBot="1">
+    <row r="4" spans="1:64" ht="183" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="63" t="s">
         <v>122</v>
       </c>
@@ -3872,7 +3894,7 @@
       <c r="BK4" s="2"/>
       <c r="BL4" s="5"/>
     </row>
-    <row r="5" spans="1:64" ht="81">
+    <row r="5" spans="1:64" ht="81" x14ac:dyDescent="0.3">
       <c r="B5" s="28" t="s">
         <v>123</v>
       </c>
@@ -3951,7 +3973,7 @@
       <c r="BK5" s="31"/>
       <c r="BL5" s="10"/>
     </row>
-    <row r="6" spans="1:64" ht="67.5">
+    <row r="6" spans="1:64" ht="67.5" x14ac:dyDescent="0.3">
       <c r="B6" s="28" t="s">
         <v>124</v>
       </c>
@@ -4034,7 +4056,7 @@
       <c r="BK6" s="31"/>
       <c r="BL6" s="10"/>
     </row>
-    <row r="7" spans="1:64" ht="61.5" customHeight="1">
+    <row r="7" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="28" t="s">
         <v>125</v>
       </c>
@@ -4115,7 +4137,7 @@
       <c r="BK7" s="31"/>
       <c r="BL7" s="10"/>
     </row>
-    <row r="8" spans="1:64" ht="81">
+    <row r="8" spans="1:64" ht="81" x14ac:dyDescent="0.3">
       <c r="B8" s="28" t="s">
         <v>224</v>
       </c>
@@ -4192,7 +4214,7 @@
       <c r="BK8" s="31"/>
       <c r="BL8" s="10"/>
     </row>
-    <row r="9" spans="1:64" ht="61.5" customHeight="1">
+    <row r="9" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="27" t="s">
         <v>3</v>
       </c>
@@ -4265,7 +4287,7 @@
       <c r="BK9" s="31"/>
       <c r="BL9" s="10"/>
     </row>
-    <row r="10" spans="1:64" ht="61.5" customHeight="1">
+    <row r="10" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="27" t="s">
         <v>46</v>
       </c>
@@ -4342,7 +4364,7 @@
       <c r="BK10" s="31"/>
       <c r="BL10" s="10"/>
     </row>
-    <row r="11" spans="1:64" ht="61.5" customHeight="1">
+    <row r="11" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="28" t="s">
         <v>130</v>
       </c>
@@ -4423,7 +4445,7 @@
       <c r="BK11" s="31"/>
       <c r="BL11" s="10"/>
     </row>
-    <row r="12" spans="1:64" ht="61.5" customHeight="1">
+    <row r="12" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="28" t="s">
         <v>131</v>
       </c>
@@ -4502,7 +4524,7 @@
       <c r="BK12" s="31"/>
       <c r="BL12" s="10"/>
     </row>
-    <row r="13" spans="1:64" ht="183.75" customHeight="1">
+    <row r="13" spans="1:64" ht="183.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="28" t="s">
         <v>63</v>
       </c>
@@ -4591,7 +4613,7 @@
       <c r="BK13" s="31"/>
       <c r="BL13" s="10"/>
     </row>
-    <row r="14" spans="1:64" ht="67.5">
+    <row r="14" spans="1:64" ht="67.5" x14ac:dyDescent="0.3">
       <c r="B14" s="27" t="s">
         <v>74</v>
       </c>
@@ -4680,7 +4702,7 @@
       <c r="BK14" s="31"/>
       <c r="BL14" s="10"/>
     </row>
-    <row r="15" spans="1:64" ht="61.5" customHeight="1">
+    <row r="15" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="27" t="s">
         <v>65</v>
       </c>
@@ -4761,7 +4783,7 @@
       <c r="BK15" s="31"/>
       <c r="BL15" s="10"/>
     </row>
-    <row r="16" spans="1:64" ht="61.5" customHeight="1">
+    <row r="16" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="27" t="s">
         <v>66</v>
       </c>
@@ -4850,7 +4872,7 @@
       <c r="BK16" s="31"/>
       <c r="BL16" s="10"/>
     </row>
-    <row r="17" spans="2:64" ht="61.5" customHeight="1">
+    <row r="17" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="57" t="s">
         <v>76</v>
       </c>
@@ -4937,7 +4959,7 @@
       <c r="BK17" s="71"/>
       <c r="BL17" s="48"/>
     </row>
-    <row r="18" spans="2:64" ht="76.5" customHeight="1">
+    <row r="18" spans="2:64" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="27" t="s">
         <v>86</v>
       </c>
@@ -5028,7 +5050,7 @@
       <c r="BK18" s="73"/>
       <c r="BL18" s="70"/>
     </row>
-    <row r="19" spans="2:64" ht="61.5" customHeight="1">
+    <row r="19" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="77" t="s">
         <v>144</v>
       </c>
@@ -5113,7 +5135,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="2:64" ht="61.5" customHeight="1">
+    <row r="20" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="77" t="s">
         <v>109</v>
       </c>
@@ -5182,7 +5204,7 @@
       <c r="BK20" s="73"/>
       <c r="BL20" s="70"/>
     </row>
-    <row r="21" spans="2:64" ht="61.5" customHeight="1">
+    <row r="21" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="57" t="s">
         <v>112</v>
       </c>
@@ -5251,7 +5273,7 @@
       <c r="BK21" s="73"/>
       <c r="BL21" s="70"/>
     </row>
-    <row r="22" spans="2:64" ht="61.5" customHeight="1">
+    <row r="22" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="57" t="s">
         <v>169</v>
       </c>
@@ -5320,7 +5342,7 @@
       <c r="BK22" s="73"/>
       <c r="BL22" s="70"/>
     </row>
-    <row r="23" spans="2:64" ht="61.5" customHeight="1" thickBot="1">
+    <row r="23" spans="2:64" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="79" t="s">
         <v>170</v>
       </c>
@@ -5389,7 +5411,7 @@
       <c r="BK23" s="75"/>
       <c r="BL23" s="55"/>
     </row>
-    <row r="24" spans="2:64" ht="17.25" thickTop="1"/>
+    <row r="24" spans="2:64" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B2:B3"/>
@@ -5411,7 +5433,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.375" style="83" customWidth="1"/>
     <col min="2" max="2" width="9" style="83"/>
@@ -5423,7 +5445,7 @@
     <col min="15" max="16384" width="9" style="83"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="32.25" thickBot="1">
+    <row r="1" spans="1:14" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="110" t="s">
         <v>151</v>
       </c>
@@ -5434,7 +5456,7 @@
       <c r="D1" s="111"/>
       <c r="E1" s="109"/>
     </row>
-    <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1">
+    <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B2" s="133" t="s">
         <v>2</v>
       </c>
@@ -5463,7 +5485,7 @@
       <c r="M2" s="131"/>
       <c r="N2" s="132"/>
     </row>
-    <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1">
+    <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="134"/>
       <c r="C3" s="138"/>
       <c r="D3" s="138"/>
@@ -5496,7 +5518,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="108">
+    <row r="4" spans="1:14" ht="108" x14ac:dyDescent="0.3">
       <c r="B4" s="84" t="s">
         <v>120</v>
       </c>
@@ -5531,7 +5553,7 @@
       <c r="M4" s="107"/>
       <c r="N4" s="94"/>
     </row>
-    <row r="5" spans="1:14" ht="108">
+    <row r="5" spans="1:14" ht="108" x14ac:dyDescent="0.3">
       <c r="B5" s="85" t="s">
         <v>126</v>
       </c>
@@ -5566,7 +5588,7 @@
       <c r="M5" s="107"/>
       <c r="N5" s="95"/>
     </row>
-    <row r="6" spans="1:14" ht="108">
+    <row r="6" spans="1:14" ht="108" x14ac:dyDescent="0.3">
       <c r="B6" s="85" t="s">
         <v>127</v>
       </c>
@@ -5601,7 +5623,7 @@
       <c r="M6" s="107"/>
       <c r="N6" s="95"/>
     </row>
-    <row r="7" spans="1:14" ht="108">
+    <row r="7" spans="1:14" ht="108" x14ac:dyDescent="0.3">
       <c r="B7" s="85" t="s">
         <v>128</v>
       </c>
@@ -5636,7 +5658,7 @@
       <c r="M7" s="107"/>
       <c r="N7" s="95"/>
     </row>
-    <row r="8" spans="1:14" ht="108">
+    <row r="8" spans="1:14" ht="108" x14ac:dyDescent="0.3">
       <c r="B8" s="86" t="s">
         <v>3</v>
       </c>
@@ -5671,7 +5693,7 @@
       <c r="M8" s="107"/>
       <c r="N8" s="95"/>
     </row>
-    <row r="9" spans="1:14" ht="175.5">
+    <row r="9" spans="1:14" ht="175.5" x14ac:dyDescent="0.3">
       <c r="B9" s="86" t="s">
         <v>46</v>
       </c>
@@ -5706,7 +5728,7 @@
       <c r="M9" s="107"/>
       <c r="N9" s="95"/>
     </row>
-    <row r="10" spans="1:14" ht="121.5">
+    <row r="10" spans="1:14" ht="121.5" x14ac:dyDescent="0.3">
       <c r="B10" s="86" t="s">
         <v>56</v>
       </c>
@@ -5741,7 +5763,7 @@
       <c r="M10" s="107"/>
       <c r="N10" s="95"/>
     </row>
-    <row r="11" spans="1:14" ht="108">
+    <row r="11" spans="1:14" ht="108" x14ac:dyDescent="0.3">
       <c r="B11" s="85" t="s">
         <v>63</v>
       </c>
@@ -5776,7 +5798,7 @@
       <c r="M11" s="107"/>
       <c r="N11" s="95"/>
     </row>
-    <row r="12" spans="1:14" ht="57" customHeight="1">
+    <row r="12" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="86" t="s">
         <v>74</v>
       </c>
@@ -5811,7 +5833,7 @@
       <c r="M12" s="107"/>
       <c r="N12" s="95"/>
     </row>
-    <row r="13" spans="1:14" ht="347.25" customHeight="1">
+    <row r="13" spans="1:14" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="86" t="s">
         <v>121</v>
       </c>
@@ -5846,7 +5868,7 @@
       <c r="M13" s="107"/>
       <c r="N13" s="95"/>
     </row>
-    <row r="14" spans="1:14" ht="175.5">
+    <row r="14" spans="1:14" ht="175.5" x14ac:dyDescent="0.3">
       <c r="B14" s="87" t="s">
         <v>184</v>
       </c>
@@ -5875,7 +5897,7 @@
       <c r="M14" s="107"/>
       <c r="N14" s="95"/>
     </row>
-    <row r="15" spans="1:14" ht="57" customHeight="1">
+    <row r="15" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="87" t="s">
         <v>76</v>
       </c>
@@ -5908,7 +5930,7 @@
       <c r="M15" s="107"/>
       <c r="N15" s="95"/>
     </row>
-    <row r="16" spans="1:14" ht="121.5">
+    <row r="16" spans="1:14" ht="121.5" x14ac:dyDescent="0.3">
       <c r="B16" s="86" t="s">
         <v>86</v>
       </c>
@@ -5941,7 +5963,7 @@
       <c r="M16" s="107"/>
       <c r="N16" s="95"/>
     </row>
-    <row r="17" spans="2:14" ht="57" customHeight="1">
+    <row r="17" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="88" t="s">
         <v>144</v>
       </c>
@@ -5974,7 +5996,7 @@
       <c r="M17" s="91"/>
       <c r="N17" s="95"/>
     </row>
-    <row r="18" spans="2:14" ht="162">
+    <row r="18" spans="2:14" ht="162" x14ac:dyDescent="0.3">
       <c r="B18" s="88" t="s">
         <v>109</v>
       </c>
@@ -6009,7 +6031,7 @@
       <c r="M18" s="107"/>
       <c r="N18" s="95"/>
     </row>
-    <row r="19" spans="2:14" ht="57" customHeight="1">
+    <row r="19" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="87" t="s">
         <v>112</v>
       </c>
@@ -6044,7 +6066,7 @@
       <c r="M19" s="107"/>
       <c r="N19" s="95"/>
     </row>
-    <row r="20" spans="2:14" ht="57" customHeight="1">
+    <row r="20" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="87" t="s">
         <v>171</v>
       </c>
@@ -6079,7 +6101,7 @@
       <c r="M20" s="107"/>
       <c r="N20" s="114"/>
     </row>
-    <row r="21" spans="2:14" ht="57" customHeight="1" thickBot="1">
+    <row r="21" spans="2:14" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="89" t="s">
         <v>111</v>
       </c>
@@ -6114,7 +6136,7 @@
       <c r="M21" s="122"/>
       <c r="N21" s="97"/>
     </row>
-    <row r="22" spans="2:14" ht="14.25" thickTop="1"/>
+    <row r="22" spans="2:14" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="K2:N2"/>
@@ -6187,7 +6209,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.375" style="83" customWidth="1"/>
     <col min="2" max="2" width="9" style="83"/>
@@ -6198,7 +6220,7 @@
     <col min="10" max="16384" width="9" style="83"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="32.25" thickBot="1">
+    <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="110" t="s">
         <v>0</v>
       </c>
@@ -6209,7 +6231,7 @@
       <c r="D1" s="111"/>
       <c r="E1" s="109"/>
     </row>
-    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1">
+    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B2" s="133" t="s">
         <v>2</v>
       </c>
@@ -6229,7 +6251,7 @@
       <c r="H2" s="131"/>
       <c r="I2" s="132"/>
     </row>
-    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1">
+    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="134"/>
       <c r="C3" s="138"/>
       <c r="D3" s="138"/>
@@ -6247,7 +6269,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="57" customHeight="1">
+    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="84" t="s">
         <v>120</v>
       </c>
@@ -6265,7 +6287,7 @@
       <c r="H4" s="90"/>
       <c r="I4" s="94"/>
     </row>
-    <row r="5" spans="1:9" ht="57" customHeight="1">
+    <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="85" t="s">
         <v>126</v>
       </c>
@@ -6283,7 +6305,7 @@
       <c r="H5" s="91"/>
       <c r="I5" s="95"/>
     </row>
-    <row r="6" spans="1:9" ht="57" customHeight="1">
+    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="85" t="s">
         <v>127</v>
       </c>
@@ -6301,7 +6323,7 @@
       <c r="H6" s="91"/>
       <c r="I6" s="95"/>
     </row>
-    <row r="7" spans="1:9" ht="57" customHeight="1">
+    <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="85" t="s">
         <v>128</v>
       </c>
@@ -6319,7 +6341,7 @@
       <c r="H7" s="91"/>
       <c r="I7" s="95"/>
     </row>
-    <row r="8" spans="1:9" ht="57" customHeight="1">
+    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="86" t="s">
         <v>3</v>
       </c>
@@ -6337,7 +6359,7 @@
       <c r="H8" s="91"/>
       <c r="I8" s="95"/>
     </row>
-    <row r="9" spans="1:9" ht="27">
+    <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.3">
       <c r="B9" s="86" t="s">
         <v>46</v>
       </c>
@@ -6355,7 +6377,7 @@
       <c r="H9" s="91"/>
       <c r="I9" s="95"/>
     </row>
-    <row r="10" spans="1:9" ht="57" customHeight="1">
+    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="86" t="s">
         <v>56</v>
       </c>
@@ -6373,7 +6395,7 @@
       <c r="H10" s="91"/>
       <c r="I10" s="95"/>
     </row>
-    <row r="11" spans="1:9" ht="40.5">
+    <row r="11" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
       <c r="B11" s="85" t="s">
         <v>63</v>
       </c>
@@ -6391,7 +6413,7 @@
       <c r="H11" s="91"/>
       <c r="I11" s="95"/>
     </row>
-    <row r="12" spans="1:9" ht="57" customHeight="1">
+    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="86" t="s">
         <v>74</v>
       </c>
@@ -6409,7 +6431,7 @@
       <c r="H12" s="91"/>
       <c r="I12" s="95"/>
     </row>
-    <row r="13" spans="1:9" ht="347.25" customHeight="1">
+    <row r="13" spans="1:9" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="86" t="s">
         <v>121</v>
       </c>
@@ -6427,7 +6449,7 @@
       <c r="H13" s="91"/>
       <c r="I13" s="95"/>
     </row>
-    <row r="14" spans="1:9" ht="409.5">
+    <row r="14" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
       <c r="B14" s="87" t="s">
         <v>184</v>
       </c>
@@ -6441,11 +6463,11 @@
       <c r="F14" s="116"/>
       <c r="G14" s="107"/>
       <c r="H14" s="91"/>
-      <c r="I14" s="107" t="s">
+      <c r="I14" s="139" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="57" customHeight="1">
+    <row r="15" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="87" t="s">
         <v>76</v>
       </c>
@@ -6463,7 +6485,7 @@
       <c r="H15" s="91"/>
       <c r="I15" s="95"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" s="86" t="s">
         <v>86</v>
       </c>
@@ -6481,7 +6503,7 @@
       <c r="H16" s="91"/>
       <c r="I16" s="95"/>
     </row>
-    <row r="17" spans="2:9" ht="57" customHeight="1">
+    <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="88" t="s">
         <v>144</v>
       </c>
@@ -6499,7 +6521,7 @@
       <c r="H17" s="91"/>
       <c r="I17" s="95"/>
     </row>
-    <row r="18" spans="2:9" ht="27">
+    <row r="18" spans="2:9" ht="27" x14ac:dyDescent="0.3">
       <c r="B18" s="88" t="s">
         <v>109</v>
       </c>
@@ -6517,7 +6539,7 @@
       <c r="H18" s="91"/>
       <c r="I18" s="95"/>
     </row>
-    <row r="19" spans="2:9" ht="57" customHeight="1">
+    <row r="19" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="87" t="s">
         <v>112</v>
       </c>
@@ -6535,7 +6557,7 @@
       <c r="H19" s="91"/>
       <c r="I19" s="95"/>
     </row>
-    <row r="20" spans="2:9" ht="57" customHeight="1">
+    <row r="20" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="87" t="s">
         <v>170</v>
       </c>
@@ -6553,7 +6575,7 @@
       <c r="H20" s="113"/>
       <c r="I20" s="114"/>
     </row>
-    <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1">
+    <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="89" t="s">
         <v>111</v>
       </c>
@@ -6571,7 +6593,7 @@
       <c r="H21" s="96"/>
       <c r="I21" s="97"/>
     </row>
-    <row r="22" spans="2:9" ht="14.25" thickTop="1"/>
+    <row r="22" spans="2:9" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:B3"/>
@@ -6588,7 +6610,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.375" style="83" customWidth="1"/>
     <col min="2" max="2" width="9" style="83"/>
@@ -6599,7 +6621,7 @@
     <col min="10" max="16384" width="9" style="83"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="32.25" thickBot="1">
+    <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="110" t="s">
         <v>0</v>
       </c>
@@ -6610,7 +6632,7 @@
       <c r="D1" s="111"/>
       <c r="E1" s="109"/>
     </row>
-    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1">
+    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B2" s="133" t="s">
         <v>2</v>
       </c>
@@ -6630,7 +6652,7 @@
       <c r="H2" s="131"/>
       <c r="I2" s="132"/>
     </row>
-    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1">
+    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="134"/>
       <c r="C3" s="138"/>
       <c r="D3" s="138"/>
@@ -6648,7 +6670,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="57" customHeight="1">
+    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="84" t="s">
         <v>120</v>
       </c>
@@ -6666,7 +6688,7 @@
       <c r="H4" s="90"/>
       <c r="I4" s="94"/>
     </row>
-    <row r="5" spans="1:9" ht="57" customHeight="1">
+    <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="85" t="s">
         <v>126</v>
       </c>
@@ -6684,7 +6706,7 @@
       <c r="H5" s="91"/>
       <c r="I5" s="95"/>
     </row>
-    <row r="6" spans="1:9" ht="57" customHeight="1">
+    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="85" t="s">
         <v>127</v>
       </c>
@@ -6702,7 +6724,7 @@
       <c r="H6" s="91"/>
       <c r="I6" s="95"/>
     </row>
-    <row r="7" spans="1:9" ht="57" customHeight="1">
+    <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="85" t="s">
         <v>128</v>
       </c>
@@ -6720,7 +6742,7 @@
       <c r="H7" s="91"/>
       <c r="I7" s="95"/>
     </row>
-    <row r="8" spans="1:9" ht="57" customHeight="1">
+    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="86" t="s">
         <v>3</v>
       </c>
@@ -6738,7 +6760,7 @@
       <c r="H8" s="91"/>
       <c r="I8" s="95"/>
     </row>
-    <row r="9" spans="1:9" ht="27">
+    <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.3">
       <c r="B9" s="86" t="s">
         <v>46</v>
       </c>
@@ -6756,7 +6778,7 @@
       <c r="H9" s="91"/>
       <c r="I9" s="95"/>
     </row>
-    <row r="10" spans="1:9" ht="57" customHeight="1">
+    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="86" t="s">
         <v>56</v>
       </c>
@@ -6774,7 +6796,7 @@
       <c r="H10" s="91"/>
       <c r="I10" s="95"/>
     </row>
-    <row r="11" spans="1:9" ht="40.5">
+    <row r="11" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
       <c r="B11" s="85" t="s">
         <v>63</v>
       </c>
@@ -6792,7 +6814,7 @@
       <c r="H11" s="91"/>
       <c r="I11" s="95"/>
     </row>
-    <row r="12" spans="1:9" ht="57" customHeight="1">
+    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="86" t="s">
         <v>74</v>
       </c>
@@ -6810,7 +6832,7 @@
       <c r="H12" s="91"/>
       <c r="I12" s="95"/>
     </row>
-    <row r="13" spans="1:9" ht="347.25" customHeight="1">
+    <row r="13" spans="1:9" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="86" t="s">
         <v>121</v>
       </c>
@@ -6828,7 +6850,7 @@
       <c r="H13" s="91"/>
       <c r="I13" s="95"/>
     </row>
-    <row r="14" spans="1:9" ht="409.5">
+    <row r="14" spans="1:9" ht="229.5" x14ac:dyDescent="0.3">
       <c r="B14" s="87" t="s">
         <v>184</v>
       </c>
@@ -6839,14 +6861,14 @@
         <v>183</v>
       </c>
       <c r="E14" s="102"/>
-      <c r="F14" s="116"/>
+      <c r="F14" s="140" t="s">
+        <v>231</v>
+      </c>
       <c r="G14" s="107"/>
       <c r="H14" s="91"/>
-      <c r="I14" s="107" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="57" customHeight="1">
+      <c r="I14" s="139"/>
+    </row>
+    <row r="15" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="87" t="s">
         <v>76</v>
       </c>
@@ -6864,7 +6886,7 @@
       <c r="H15" s="91"/>
       <c r="I15" s="95"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" s="86" t="s">
         <v>86</v>
       </c>
@@ -6882,7 +6904,7 @@
       <c r="H16" s="91"/>
       <c r="I16" s="95"/>
     </row>
-    <row r="17" spans="2:9" ht="57" customHeight="1">
+    <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="88" t="s">
         <v>144</v>
       </c>
@@ -6900,7 +6922,7 @@
       <c r="H17" s="91"/>
       <c r="I17" s="95"/>
     </row>
-    <row r="18" spans="2:9" ht="27">
+    <row r="18" spans="2:9" ht="27" x14ac:dyDescent="0.3">
       <c r="B18" s="88" t="s">
         <v>109</v>
       </c>
@@ -6918,7 +6940,7 @@
       <c r="H18" s="91"/>
       <c r="I18" s="95"/>
     </row>
-    <row r="19" spans="2:9" ht="57" customHeight="1">
+    <row r="19" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="87" t="s">
         <v>112</v>
       </c>
@@ -6936,7 +6958,7 @@
       <c r="H19" s="91"/>
       <c r="I19" s="95"/>
     </row>
-    <row r="20" spans="2:9" ht="57" customHeight="1">
+    <row r="20" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="87" t="s">
         <v>170</v>
       </c>
@@ -6954,7 +6976,7 @@
       <c r="H20" s="113"/>
       <c r="I20" s="114"/>
     </row>
-    <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1">
+    <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="89" t="s">
         <v>111</v>
       </c>
@@ -6972,7 +6994,7 @@
       <c r="H21" s="96"/>
       <c r="I21" s="97"/>
     </row>
-    <row r="22" spans="2:9" ht="14.25" thickTop="1"/>
+    <row r="22" spans="2:9" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:B3"/>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\1. doc\HKMC_AIR_PTC\일정\PTC_HEATER_DOC (250626 Repo 변경, 해당 Repo 사용)\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\일정\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="대일정" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="235">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1346,18 +1346,82 @@
   </si>
   <si>
     <t>[조현진 전임, 임제훈 사원]
-- SWE.1 SRS 작성 완료 : ~ 6/30
-   : 3.1 Hardware - Software Interface
-   : 3.2 CAN Communication - Software Interface
-   : 4.1 Software State Transition Requirements
-   : 4.2.1.1 LV Sensor Fault / LV Over Voltage_Under Voltage Fault
-   : 4.2.1.2 HV Sensor Fault / HV Over Voltage_Under Voltage Fault
-- SWE.2 SADS 작성 계획
-   : Component 다이어그램 작성
-   : LV Sensor Fault / LV Over Voltage_Under Voltage Fault 정적, 동적 작성
-   : HV Sensor Fault / HV Over Voltage_Under Voltage Fault 정적, 동적 작성
-- SWE.3 SDDS 작성 계획
-   : LV Sensor Fault 작성</t>
+- SWE.1 SRS 작성
+   : PCB Sensor Protection 작성
+   : PCB Temp Over Fault Detection 작성
+- SWE.2 SADS 작성
+   : PCB Sensor Protection 작성
+   : PCB Temp Over Fault Detection 작성
+- SWE.3 SDDS 작성
+   : HV Over Current Fault Detection Static Design, Dynamic Behavior 작성
+   : Current Sensor Protection Static Design, Dynamic Behavior 작성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[조현진 전임, 임제훈 사원]
+- SWE.1 SRS 작성
+   : Hardware - Software Interface 작성
+   : CAN Communication - Software Interface 작성
+   : LV Sensor Protection 작성
+   : Low Voltage Battery Protection 작성
+   : HV Sensor Protection 작성
+   : High Voltage Battery Protection 작성
+- SWE.2 SADS 작성
+   : Software Component Overview Diagram 작성
+   : Software Component Overview Description 작성
+   : Protection Composition Diagram 작성
+   : Protection Composition attributes 작성
+   : Protection Component Diagram 작성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[조현진 전임, 임제훈 사원]
+- SWE.1 SRS 작성
+   : Hardware - Software Interface (6/30)
+   : CAN Communication - Software Interface (6/30)
+   : Software State Transition Requirements (6/30)
+   : LV Sensor Protection (6/30)
+   : Low Voltage Battery Protection (6/30)
+   : HV Sensor Protection (6/30)
+   : High Voltage Battery Protection (6/30)
+   : Review Report 결과를 토대로 개선점 반영
+- SWE.2 SADS 작성
+   : Software Component Overview Diagram (7/1)
+   : Software Component Overview Description (7/2)
+   : Protection Composition Diagram (7/3)
+   : Protection Composition attributes (7/4)
+   : Protection Component Diagram (7/4)
+   : Structure Specification 작성
+   : Software Composition Design 작성
+   : Software Composition Attributes 작성
+   : LV Sensor Protection Static Design, Dynamic Behavior 작성
+   : Low Voltage Battery Protection Static Design, Dynamic Behavior 작성
+   : HV Sensor Protection Static Design, Dynamic Behavior 작성
+   : High Voltage Battery Protection Static Design, Dynamic Behavior 작성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[조현진 전임, 임제훈 사원]
+- SWE.1 SRS 작성
+   : Review Report 결과를 토대로 개선점 반영 (7/11)
+   : Hardware - Software Interface의 SW Description 재작성
+   : HV Over Current Fault Detection 작성
+   : Current Sensor Protection 작성
+- SWE.2 SADS 작성
+   : Structure Specification (7/7)
+   : Software Composition Design (7/7)
+   : Software Composition Attributes (7/7)
+   : LV Sensor Protection Static Design, Dynamic Behavior (7/8)
+   : Low Voltage Battery Protection Static Design, Dynamic Behavior (7/8)
+   : HV Sensor Protection Static Design, Dynamic Behavior (7/11)
+   : High Voltage Battery Protection Static Design, Dynamic Behavior (7/11)
+   : HV Over Current Fault Detection 작성
+   : Current Sensor Protection 작성
+- SWE.3 SDDS 작성
+   : LV Sensor Protection Static Design, Dynamic Behavior 작성
+   : Low Voltage Battery Protection Static Design, Dynamic Behavior 작성
+   : HV Sensor Protection Static Design, Dynamic Behavior 작성
+   : High Voltage Battery Protection Static Design, Dynamic Behavior 작성</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2886,6 +2950,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2930,12 +3000,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3548,90 +3612,90 @@
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="124" t="s">
+      <c r="B2" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="126" t="s">
+      <c r="C2" s="128" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="126" t="s">
+      <c r="D2" s="128" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="130">
+      <c r="E2" s="132">
         <v>23</v>
       </c>
-      <c r="F2" s="128"/>
-      <c r="G2" s="128"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="128"/>
-      <c r="J2" s="128"/>
-      <c r="K2" s="128"/>
-      <c r="L2" s="128"/>
-      <c r="M2" s="128"/>
-      <c r="N2" s="128"/>
-      <c r="O2" s="128"/>
-      <c r="P2" s="128"/>
-      <c r="Q2" s="128">
+      <c r="F2" s="130"/>
+      <c r="G2" s="130"/>
+      <c r="H2" s="130"/>
+      <c r="I2" s="130"/>
+      <c r="J2" s="130"/>
+      <c r="K2" s="130"/>
+      <c r="L2" s="130"/>
+      <c r="M2" s="130"/>
+      <c r="N2" s="130"/>
+      <c r="O2" s="130"/>
+      <c r="P2" s="130"/>
+      <c r="Q2" s="130">
         <v>24</v>
       </c>
-      <c r="R2" s="128"/>
-      <c r="S2" s="128"/>
-      <c r="T2" s="128"/>
-      <c r="U2" s="128"/>
-      <c r="V2" s="128"/>
-      <c r="W2" s="128"/>
-      <c r="X2" s="128"/>
-      <c r="Y2" s="128"/>
-      <c r="Z2" s="128"/>
-      <c r="AA2" s="128"/>
-      <c r="AB2" s="128"/>
-      <c r="AC2" s="128">
+      <c r="R2" s="130"/>
+      <c r="S2" s="130"/>
+      <c r="T2" s="130"/>
+      <c r="U2" s="130"/>
+      <c r="V2" s="130"/>
+      <c r="W2" s="130"/>
+      <c r="X2" s="130"/>
+      <c r="Y2" s="130"/>
+      <c r="Z2" s="130"/>
+      <c r="AA2" s="130"/>
+      <c r="AB2" s="130"/>
+      <c r="AC2" s="130">
         <v>25</v>
       </c>
-      <c r="AD2" s="128"/>
-      <c r="AE2" s="128"/>
-      <c r="AF2" s="128"/>
-      <c r="AG2" s="128"/>
-      <c r="AH2" s="128"/>
-      <c r="AI2" s="128"/>
-      <c r="AJ2" s="128"/>
-      <c r="AK2" s="128"/>
-      <c r="AL2" s="128"/>
-      <c r="AM2" s="128"/>
-      <c r="AN2" s="128"/>
-      <c r="AO2" s="128">
+      <c r="AD2" s="130"/>
+      <c r="AE2" s="130"/>
+      <c r="AF2" s="130"/>
+      <c r="AG2" s="130"/>
+      <c r="AH2" s="130"/>
+      <c r="AI2" s="130"/>
+      <c r="AJ2" s="130"/>
+      <c r="AK2" s="130"/>
+      <c r="AL2" s="130"/>
+      <c r="AM2" s="130"/>
+      <c r="AN2" s="130"/>
+      <c r="AO2" s="130">
         <v>26</v>
       </c>
-      <c r="AP2" s="128"/>
-      <c r="AQ2" s="128"/>
-      <c r="AR2" s="128"/>
-      <c r="AS2" s="128"/>
-      <c r="AT2" s="128"/>
-      <c r="AU2" s="128"/>
-      <c r="AV2" s="128"/>
-      <c r="AW2" s="128"/>
-      <c r="AX2" s="128"/>
-      <c r="AY2" s="128"/>
-      <c r="AZ2" s="129"/>
-      <c r="BA2" s="128">
+      <c r="AP2" s="130"/>
+      <c r="AQ2" s="130"/>
+      <c r="AR2" s="130"/>
+      <c r="AS2" s="130"/>
+      <c r="AT2" s="130"/>
+      <c r="AU2" s="130"/>
+      <c r="AV2" s="130"/>
+      <c r="AW2" s="130"/>
+      <c r="AX2" s="130"/>
+      <c r="AY2" s="130"/>
+      <c r="AZ2" s="131"/>
+      <c r="BA2" s="130">
         <v>27</v>
       </c>
-      <c r="BB2" s="128"/>
-      <c r="BC2" s="128"/>
-      <c r="BD2" s="128"/>
-      <c r="BE2" s="128"/>
-      <c r="BF2" s="128"/>
-      <c r="BG2" s="128"/>
-      <c r="BH2" s="128"/>
-      <c r="BI2" s="128"/>
-      <c r="BJ2" s="128"/>
-      <c r="BK2" s="128"/>
-      <c r="BL2" s="129"/>
+      <c r="BB2" s="130"/>
+      <c r="BC2" s="130"/>
+      <c r="BD2" s="130"/>
+      <c r="BE2" s="130"/>
+      <c r="BF2" s="130"/>
+      <c r="BG2" s="130"/>
+      <c r="BH2" s="130"/>
+      <c r="BI2" s="130"/>
+      <c r="BJ2" s="130"/>
+      <c r="BK2" s="130"/>
+      <c r="BL2" s="131"/>
     </row>
     <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="125"/>
-      <c r="C3" s="127"/>
-      <c r="D3" s="127"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="129"/>
       <c r="E3" s="22">
         <v>1</v>
       </c>
@@ -5457,39 +5521,39 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="133" t="s">
+      <c r="B2" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="137" t="s">
+      <c r="C2" s="139" t="s">
         <v>179</v>
       </c>
-      <c r="D2" s="137" t="s">
+      <c r="D2" s="139" t="s">
         <v>180</v>
       </c>
-      <c r="E2" s="135" t="s">
+      <c r="E2" s="137" t="s">
         <v>129</v>
       </c>
       <c r="F2" s="98" t="s">
         <v>115</v>
       </c>
-      <c r="G2" s="131" t="s">
+      <c r="G2" s="133" t="s">
         <v>116</v>
       </c>
-      <c r="H2" s="131"/>
-      <c r="I2" s="131"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="131" t="s">
+      <c r="H2" s="133"/>
+      <c r="I2" s="133"/>
+      <c r="J2" s="134"/>
+      <c r="K2" s="133" t="s">
         <v>185</v>
       </c>
-      <c r="L2" s="131"/>
-      <c r="M2" s="131"/>
-      <c r="N2" s="132"/>
+      <c r="L2" s="133"/>
+      <c r="M2" s="133"/>
+      <c r="N2" s="134"/>
     </row>
     <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="134"/>
-      <c r="C3" s="138"/>
-      <c r="D3" s="138"/>
-      <c r="E3" s="136"/>
+      <c r="B3" s="136"/>
+      <c r="C3" s="140"/>
+      <c r="D3" s="140"/>
+      <c r="E3" s="138"/>
       <c r="F3" s="99" t="s">
         <v>114</v>
       </c>
@@ -6232,30 +6296,30 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="133" t="s">
+      <c r="B2" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="137" t="s">
+      <c r="C2" s="139" t="s">
         <v>179</v>
       </c>
-      <c r="D2" s="137" t="s">
+      <c r="D2" s="139" t="s">
         <v>180</v>
       </c>
-      <c r="E2" s="135" t="s">
+      <c r="E2" s="137" t="s">
         <v>129</v>
       </c>
-      <c r="F2" s="131" t="s">
+      <c r="F2" s="133" t="s">
         <v>185</v>
       </c>
-      <c r="G2" s="131"/>
-      <c r="H2" s="131"/>
-      <c r="I2" s="132"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+      <c r="I2" s="134"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="134"/>
-      <c r="C3" s="138"/>
-      <c r="D3" s="138"/>
-      <c r="E3" s="136"/>
+      <c r="B3" s="136"/>
+      <c r="C3" s="140"/>
+      <c r="D3" s="140"/>
+      <c r="E3" s="138"/>
       <c r="F3" s="99" t="s">
         <v>117</v>
       </c>
@@ -6463,7 +6527,7 @@
       <c r="F14" s="116"/>
       <c r="G14" s="107"/>
       <c r="H14" s="91"/>
-      <c r="I14" s="139" t="s">
+      <c r="I14" s="124" t="s">
         <v>223</v>
       </c>
     </row>
@@ -6633,30 +6697,30 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="133" t="s">
+      <c r="B2" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="137" t="s">
+      <c r="C2" s="139" t="s">
         <v>179</v>
       </c>
-      <c r="D2" s="137" t="s">
+      <c r="D2" s="139" t="s">
         <v>180</v>
       </c>
-      <c r="E2" s="135" t="s">
+      <c r="E2" s="137" t="s">
         <v>129</v>
       </c>
-      <c r="F2" s="131" t="s">
+      <c r="F2" s="133" t="s">
         <v>230</v>
       </c>
-      <c r="G2" s="131"/>
-      <c r="H2" s="131"/>
-      <c r="I2" s="132"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+      <c r="I2" s="134"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="134"/>
-      <c r="C3" s="138"/>
-      <c r="D3" s="138"/>
-      <c r="E3" s="136"/>
+      <c r="B3" s="136"/>
+      <c r="C3" s="140"/>
+      <c r="D3" s="140"/>
+      <c r="E3" s="138"/>
       <c r="F3" s="99" t="s">
         <v>117</v>
       </c>
@@ -6850,7 +6914,7 @@
       <c r="H13" s="91"/>
       <c r="I13" s="95"/>
     </row>
-    <row r="14" spans="1:9" ht="229.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="337.5" x14ac:dyDescent="0.3">
       <c r="B14" s="87" t="s">
         <v>184</v>
       </c>
@@ -6861,12 +6925,18 @@
         <v>183</v>
       </c>
       <c r="E14" s="102"/>
-      <c r="F14" s="140" t="s">
+      <c r="F14" s="125" t="s">
+        <v>232</v>
+      </c>
+      <c r="G14" s="125" t="s">
+        <v>233</v>
+      </c>
+      <c r="H14" s="125" t="s">
+        <v>234</v>
+      </c>
+      <c r="I14" s="125" t="s">
         <v>231</v>
       </c>
-      <c r="G14" s="107"/>
-      <c r="H14" s="91"/>
-      <c r="I14" s="139"/>
     </row>
     <row r="15" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="87" t="s">

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\일정\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\2.project\hkmc_ptc_heater\Doc\1. 일정\1. Weekly Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685"/>
   </bookViews>
   <sheets>
     <sheet name="대일정" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="239">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1424,6 +1424,26 @@
    : High Voltage Battery Protection Static Design, Dynamic Behavior 작성</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>ALL출도
+3/31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P1
+4/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P2
+6/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOP
+9/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1432,7 +1452,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3590,7 +3610,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BL24"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="4.375" customWidth="1"/>
     <col min="2" max="2" width="18.875" customWidth="1"/>
@@ -3601,7 +3621,7 @@
     <col min="36" max="64" width="8.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" s="20" customFormat="1" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:64" s="20" customFormat="1" ht="32.25" thickBot="1">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -3611,7 +3631,7 @@
       <c r="C1" s="21"/>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1">
       <c r="B2" s="126" t="s">
         <v>2</v>
       </c>
@@ -3692,7 +3712,7 @@
       <c r="BK2" s="130"/>
       <c r="BL2" s="131"/>
     </row>
-    <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1">
       <c r="B3" s="127"/>
       <c r="C3" s="129"/>
       <c r="D3" s="129"/>
@@ -3877,7 +3897,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:64" ht="183" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:64" ht="183" customHeight="1" thickBot="1">
       <c r="B4" s="63" t="s">
         <v>122</v>
       </c>
@@ -3958,7 +3978,7 @@
       <c r="BK4" s="2"/>
       <c r="BL4" s="5"/>
     </row>
-    <row r="5" spans="1:64" ht="81" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:64" ht="81">
       <c r="B5" s="28" t="s">
         <v>123</v>
       </c>
@@ -4037,7 +4057,7 @@
       <c r="BK5" s="31"/>
       <c r="BL5" s="10"/>
     </row>
-    <row r="6" spans="1:64" ht="67.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:64" ht="67.5">
       <c r="B6" s="28" t="s">
         <v>124</v>
       </c>
@@ -4120,7 +4140,7 @@
       <c r="BK6" s="31"/>
       <c r="BL6" s="10"/>
     </row>
-    <row r="7" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:64" ht="61.5" customHeight="1">
       <c r="B7" s="28" t="s">
         <v>125</v>
       </c>
@@ -4201,7 +4221,7 @@
       <c r="BK7" s="31"/>
       <c r="BL7" s="10"/>
     </row>
-    <row r="8" spans="1:64" ht="81" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:64" ht="81">
       <c r="B8" s="28" t="s">
         <v>224</v>
       </c>
@@ -4278,7 +4298,7 @@
       <c r="BK8" s="31"/>
       <c r="BL8" s="10"/>
     </row>
-    <row r="9" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:64" ht="61.5" customHeight="1">
       <c r="B9" s="27" t="s">
         <v>3</v>
       </c>
@@ -4351,7 +4371,7 @@
       <c r="BK9" s="31"/>
       <c r="BL9" s="10"/>
     </row>
-    <row r="10" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:64" ht="61.5" customHeight="1">
       <c r="B10" s="27" t="s">
         <v>46</v>
       </c>
@@ -4428,7 +4448,7 @@
       <c r="BK10" s="31"/>
       <c r="BL10" s="10"/>
     </row>
-    <row r="11" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:64" ht="61.5" customHeight="1">
       <c r="B11" s="28" t="s">
         <v>130</v>
       </c>
@@ -4509,7 +4529,7 @@
       <c r="BK11" s="31"/>
       <c r="BL11" s="10"/>
     </row>
-    <row r="12" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:64" ht="61.5" customHeight="1">
       <c r="B12" s="28" t="s">
         <v>131</v>
       </c>
@@ -4588,7 +4608,7 @@
       <c r="BK12" s="31"/>
       <c r="BL12" s="10"/>
     </row>
-    <row r="13" spans="1:64" ht="183.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:64" ht="183.75" customHeight="1">
       <c r="B13" s="28" t="s">
         <v>63</v>
       </c>
@@ -4677,7 +4697,7 @@
       <c r="BK13" s="31"/>
       <c r="BL13" s="10"/>
     </row>
-    <row r="14" spans="1:64" ht="67.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:64" ht="67.5">
       <c r="B14" s="27" t="s">
         <v>74</v>
       </c>
@@ -4766,7 +4786,7 @@
       <c r="BK14" s="31"/>
       <c r="BL14" s="10"/>
     </row>
-    <row r="15" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:64" ht="61.5" customHeight="1">
       <c r="B15" s="27" t="s">
         <v>65</v>
       </c>
@@ -4847,7 +4867,7 @@
       <c r="BK15" s="31"/>
       <c r="BL15" s="10"/>
     </row>
-    <row r="16" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:64" ht="61.5" customHeight="1">
       <c r="B16" s="27" t="s">
         <v>66</v>
       </c>
@@ -4936,7 +4956,7 @@
       <c r="BK16" s="31"/>
       <c r="BL16" s="10"/>
     </row>
-    <row r="17" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:64" ht="61.5" customHeight="1">
       <c r="B17" s="57" t="s">
         <v>76</v>
       </c>
@@ -5023,7 +5043,7 @@
       <c r="BK17" s="71"/>
       <c r="BL17" s="48"/>
     </row>
-    <row r="18" spans="2:64" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:64" ht="76.5" customHeight="1">
       <c r="B18" s="27" t="s">
         <v>86</v>
       </c>
@@ -5114,7 +5134,7 @@
       <c r="BK18" s="73"/>
       <c r="BL18" s="70"/>
     </row>
-    <row r="19" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:64" ht="61.5" customHeight="1">
       <c r="B19" s="77" t="s">
         <v>144</v>
       </c>
@@ -5199,7 +5219,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:64" ht="61.5" customHeight="1">
       <c r="B20" s="77" t="s">
         <v>109</v>
       </c>
@@ -5268,7 +5288,7 @@
       <c r="BK20" s="73"/>
       <c r="BL20" s="70"/>
     </row>
-    <row r="21" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:64" ht="61.5" customHeight="1">
       <c r="B21" s="57" t="s">
         <v>112</v>
       </c>
@@ -5314,30 +5334,42 @@
       <c r="AN21" s="66"/>
       <c r="AO21" s="67"/>
       <c r="AP21" s="69"/>
-      <c r="AQ21" s="69"/>
+      <c r="AQ21" s="69" t="s">
+        <v>235</v>
+      </c>
       <c r="AR21" s="69"/>
       <c r="AS21" s="65"/>
       <c r="AT21" s="65"/>
       <c r="AU21" s="69"/>
-      <c r="AV21" s="65"/>
+      <c r="AV21" s="13" t="s">
+        <v>225</v>
+      </c>
       <c r="AW21" s="65"/>
       <c r="AX21" s="65"/>
       <c r="AY21" s="69"/>
       <c r="AZ21" s="70"/>
       <c r="BA21" s="67"/>
-      <c r="BB21" s="72"/>
+      <c r="BB21" s="13" t="s">
+        <v>198</v>
+      </c>
       <c r="BC21" s="73"/>
-      <c r="BD21" s="72"/>
+      <c r="BD21" s="69" t="s">
+        <v>236</v>
+      </c>
       <c r="BE21" s="72"/>
       <c r="BF21" s="73"/>
-      <c r="BG21" s="73"/>
+      <c r="BG21" s="69" t="s">
+        <v>237</v>
+      </c>
       <c r="BH21" s="73"/>
-      <c r="BI21" s="73"/>
+      <c r="BI21" s="69" t="s">
+        <v>238</v>
+      </c>
       <c r="BJ21" s="73"/>
       <c r="BK21" s="73"/>
       <c r="BL21" s="70"/>
     </row>
-    <row r="22" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:64" ht="61.5" customHeight="1">
       <c r="B22" s="57" t="s">
         <v>169</v>
       </c>
@@ -5406,7 +5438,7 @@
       <c r="BK22" s="73"/>
       <c r="BL22" s="70"/>
     </row>
-    <row r="23" spans="2:64" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:64" ht="61.5" customHeight="1" thickBot="1">
       <c r="B23" s="79" t="s">
         <v>170</v>
       </c>
@@ -5475,7 +5507,7 @@
       <c r="BK23" s="75"/>
       <c r="BL23" s="55"/>
     </row>
-    <row r="24" spans="2:64" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="2:64" ht="17.25" thickTop="1"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B2:B3"/>
@@ -5497,7 +5529,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="3.375" style="83" customWidth="1"/>
     <col min="2" max="2" width="9" style="83"/>
@@ -5509,7 +5541,7 @@
     <col min="15" max="16384" width="9" style="83"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="32.25" thickBot="1">
       <c r="A1" s="110" t="s">
         <v>151</v>
       </c>
@@ -5520,7 +5552,7 @@
       <c r="D1" s="111"/>
       <c r="E1" s="109"/>
     </row>
-    <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1">
       <c r="B2" s="135" t="s">
         <v>2</v>
       </c>
@@ -5549,7 +5581,7 @@
       <c r="M2" s="133"/>
       <c r="N2" s="134"/>
     </row>
-    <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1">
       <c r="B3" s="136"/>
       <c r="C3" s="140"/>
       <c r="D3" s="140"/>
@@ -5582,7 +5614,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="108" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="108">
       <c r="B4" s="84" t="s">
         <v>120</v>
       </c>
@@ -5617,7 +5649,7 @@
       <c r="M4" s="107"/>
       <c r="N4" s="94"/>
     </row>
-    <row r="5" spans="1:14" ht="108" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="108">
       <c r="B5" s="85" t="s">
         <v>126</v>
       </c>
@@ -5652,7 +5684,7 @@
       <c r="M5" s="107"/>
       <c r="N5" s="95"/>
     </row>
-    <row r="6" spans="1:14" ht="108" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="108">
       <c r="B6" s="85" t="s">
         <v>127</v>
       </c>
@@ -5687,7 +5719,7 @@
       <c r="M6" s="107"/>
       <c r="N6" s="95"/>
     </row>
-    <row r="7" spans="1:14" ht="108" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="108">
       <c r="B7" s="85" t="s">
         <v>128</v>
       </c>
@@ -5722,7 +5754,7 @@
       <c r="M7" s="107"/>
       <c r="N7" s="95"/>
     </row>
-    <row r="8" spans="1:14" ht="108" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="108">
       <c r="B8" s="86" t="s">
         <v>3</v>
       </c>
@@ -5757,7 +5789,7 @@
       <c r="M8" s="107"/>
       <c r="N8" s="95"/>
     </row>
-    <row r="9" spans="1:14" ht="175.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="175.5">
       <c r="B9" s="86" t="s">
         <v>46</v>
       </c>
@@ -5792,7 +5824,7 @@
       <c r="M9" s="107"/>
       <c r="N9" s="95"/>
     </row>
-    <row r="10" spans="1:14" ht="121.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="121.5">
       <c r="B10" s="86" t="s">
         <v>56</v>
       </c>
@@ -5827,7 +5859,7 @@
       <c r="M10" s="107"/>
       <c r="N10" s="95"/>
     </row>
-    <row r="11" spans="1:14" ht="108" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="108">
       <c r="B11" s="85" t="s">
         <v>63</v>
       </c>
@@ -5862,7 +5894,7 @@
       <c r="M11" s="107"/>
       <c r="N11" s="95"/>
     </row>
-    <row r="12" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="57" customHeight="1">
       <c r="B12" s="86" t="s">
         <v>74</v>
       </c>
@@ -5897,7 +5929,7 @@
       <c r="M12" s="107"/>
       <c r="N12" s="95"/>
     </row>
-    <row r="13" spans="1:14" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="347.25" customHeight="1">
       <c r="B13" s="86" t="s">
         <v>121</v>
       </c>
@@ -5932,7 +5964,7 @@
       <c r="M13" s="107"/>
       <c r="N13" s="95"/>
     </row>
-    <row r="14" spans="1:14" ht="175.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="175.5">
       <c r="B14" s="87" t="s">
         <v>184</v>
       </c>
@@ -5961,7 +5993,7 @@
       <c r="M14" s="107"/>
       <c r="N14" s="95"/>
     </row>
-    <row r="15" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="57" customHeight="1">
       <c r="B15" s="87" t="s">
         <v>76</v>
       </c>
@@ -5994,7 +6026,7 @@
       <c r="M15" s="107"/>
       <c r="N15" s="95"/>
     </row>
-    <row r="16" spans="1:14" ht="121.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="121.5">
       <c r="B16" s="86" t="s">
         <v>86</v>
       </c>
@@ -6027,7 +6059,7 @@
       <c r="M16" s="107"/>
       <c r="N16" s="95"/>
     </row>
-    <row r="17" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:14" ht="57" customHeight="1">
       <c r="B17" s="88" t="s">
         <v>144</v>
       </c>
@@ -6060,7 +6092,7 @@
       <c r="M17" s="91"/>
       <c r="N17" s="95"/>
     </row>
-    <row r="18" spans="2:14" ht="162" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:14" ht="162">
       <c r="B18" s="88" t="s">
         <v>109</v>
       </c>
@@ -6095,7 +6127,7 @@
       <c r="M18" s="107"/>
       <c r="N18" s="95"/>
     </row>
-    <row r="19" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:14" ht="57" customHeight="1">
       <c r="B19" s="87" t="s">
         <v>112</v>
       </c>
@@ -6130,7 +6162,7 @@
       <c r="M19" s="107"/>
       <c r="N19" s="95"/>
     </row>
-    <row r="20" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:14" ht="57" customHeight="1">
       <c r="B20" s="87" t="s">
         <v>171</v>
       </c>
@@ -6165,7 +6197,7 @@
       <c r="M20" s="107"/>
       <c r="N20" s="114"/>
     </row>
-    <row r="21" spans="2:14" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:14" ht="57" customHeight="1" thickBot="1">
       <c r="B21" s="89" t="s">
         <v>111</v>
       </c>
@@ -6200,7 +6232,7 @@
       <c r="M21" s="122"/>
       <c r="N21" s="97"/>
     </row>
-    <row r="22" spans="2:14" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="2:14" ht="14.25" thickTop="1"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="K2:N2"/>
@@ -6273,7 +6305,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="3.375" style="83" customWidth="1"/>
     <col min="2" max="2" width="9" style="83"/>
@@ -6284,7 +6316,7 @@
     <col min="10" max="16384" width="9" style="83"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="32.25" thickBot="1">
       <c r="A1" s="110" t="s">
         <v>0</v>
       </c>
@@ -6295,7 +6327,7 @@
       <c r="D1" s="111"/>
       <c r="E1" s="109"/>
     </row>
-    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1">
       <c r="B2" s="135" t="s">
         <v>2</v>
       </c>
@@ -6315,7 +6347,7 @@
       <c r="H2" s="133"/>
       <c r="I2" s="134"/>
     </row>
-    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1">
       <c r="B3" s="136"/>
       <c r="C3" s="140"/>
       <c r="D3" s="140"/>
@@ -6333,7 +6365,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="57" customHeight="1">
       <c r="B4" s="84" t="s">
         <v>120</v>
       </c>
@@ -6351,7 +6383,7 @@
       <c r="H4" s="90"/>
       <c r="I4" s="94"/>
     </row>
-    <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="57" customHeight="1">
       <c r="B5" s="85" t="s">
         <v>126</v>
       </c>
@@ -6369,7 +6401,7 @@
       <c r="H5" s="91"/>
       <c r="I5" s="95"/>
     </row>
-    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="57" customHeight="1">
       <c r="B6" s="85" t="s">
         <v>127</v>
       </c>
@@ -6387,7 +6419,7 @@
       <c r="H6" s="91"/>
       <c r="I6" s="95"/>
     </row>
-    <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="57" customHeight="1">
       <c r="B7" s="85" t="s">
         <v>128</v>
       </c>
@@ -6405,7 +6437,7 @@
       <c r="H7" s="91"/>
       <c r="I7" s="95"/>
     </row>
-    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="57" customHeight="1">
       <c r="B8" s="86" t="s">
         <v>3</v>
       </c>
@@ -6423,7 +6455,7 @@
       <c r="H8" s="91"/>
       <c r="I8" s="95"/>
     </row>
-    <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="27">
       <c r="B9" s="86" t="s">
         <v>46</v>
       </c>
@@ -6441,7 +6473,7 @@
       <c r="H9" s="91"/>
       <c r="I9" s="95"/>
     </row>
-    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="57" customHeight="1">
       <c r="B10" s="86" t="s">
         <v>56</v>
       </c>
@@ -6459,7 +6491,7 @@
       <c r="H10" s="91"/>
       <c r="I10" s="95"/>
     </row>
-    <row r="11" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="40.5">
       <c r="B11" s="85" t="s">
         <v>63</v>
       </c>
@@ -6477,7 +6509,7 @@
       <c r="H11" s="91"/>
       <c r="I11" s="95"/>
     </row>
-    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="57" customHeight="1">
       <c r="B12" s="86" t="s">
         <v>74</v>
       </c>
@@ -6495,7 +6527,7 @@
       <c r="H12" s="91"/>
       <c r="I12" s="95"/>
     </row>
-    <row r="13" spans="1:9" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="347.25" customHeight="1">
       <c r="B13" s="86" t="s">
         <v>121</v>
       </c>
@@ -6513,7 +6545,7 @@
       <c r="H13" s="91"/>
       <c r="I13" s="95"/>
     </row>
-    <row r="14" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="409.5">
       <c r="B14" s="87" t="s">
         <v>184</v>
       </c>
@@ -6531,7 +6563,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="57" customHeight="1">
       <c r="B15" s="87" t="s">
         <v>76</v>
       </c>
@@ -6549,7 +6581,7 @@
       <c r="H15" s="91"/>
       <c r="I15" s="95"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9">
       <c r="B16" s="86" t="s">
         <v>86</v>
       </c>
@@ -6567,7 +6599,7 @@
       <c r="H16" s="91"/>
       <c r="I16" s="95"/>
     </row>
-    <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="57" customHeight="1">
       <c r="B17" s="88" t="s">
         <v>144</v>
       </c>
@@ -6585,7 +6617,7 @@
       <c r="H17" s="91"/>
       <c r="I17" s="95"/>
     </row>
-    <row r="18" spans="2:9" ht="27" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" ht="27">
       <c r="B18" s="88" t="s">
         <v>109</v>
       </c>
@@ -6603,7 +6635,7 @@
       <c r="H18" s="91"/>
       <c r="I18" s="95"/>
     </row>
-    <row r="19" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" ht="57" customHeight="1">
       <c r="B19" s="87" t="s">
         <v>112</v>
       </c>
@@ -6621,7 +6653,7 @@
       <c r="H19" s="91"/>
       <c r="I19" s="95"/>
     </row>
-    <row r="20" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" ht="57" customHeight="1">
       <c r="B20" s="87" t="s">
         <v>170</v>
       </c>
@@ -6639,7 +6671,7 @@
       <c r="H20" s="113"/>
       <c r="I20" s="114"/>
     </row>
-    <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1">
       <c r="B21" s="89" t="s">
         <v>111</v>
       </c>
@@ -6657,7 +6689,7 @@
       <c r="H21" s="96"/>
       <c r="I21" s="97"/>
     </row>
-    <row r="22" spans="2:9" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="2:9" ht="14.25" thickTop="1"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:B3"/>
@@ -6674,7 +6706,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="3.375" style="83" customWidth="1"/>
     <col min="2" max="2" width="9" style="83"/>
@@ -6685,7 +6717,7 @@
     <col min="10" max="16384" width="9" style="83"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="32.25" thickBot="1">
       <c r="A1" s="110" t="s">
         <v>0</v>
       </c>
@@ -6696,7 +6728,7 @@
       <c r="D1" s="111"/>
       <c r="E1" s="109"/>
     </row>
-    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1">
       <c r="B2" s="135" t="s">
         <v>2</v>
       </c>
@@ -6716,7 +6748,7 @@
       <c r="H2" s="133"/>
       <c r="I2" s="134"/>
     </row>
-    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1">
       <c r="B3" s="136"/>
       <c r="C3" s="140"/>
       <c r="D3" s="140"/>
@@ -6734,7 +6766,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="57" customHeight="1">
       <c r="B4" s="84" t="s">
         <v>120</v>
       </c>
@@ -6752,7 +6784,7 @@
       <c r="H4" s="90"/>
       <c r="I4" s="94"/>
     </row>
-    <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="57" customHeight="1">
       <c r="B5" s="85" t="s">
         <v>126</v>
       </c>
@@ -6770,7 +6802,7 @@
       <c r="H5" s="91"/>
       <c r="I5" s="95"/>
     </row>
-    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="57" customHeight="1">
       <c r="B6" s="85" t="s">
         <v>127</v>
       </c>
@@ -6788,7 +6820,7 @@
       <c r="H6" s="91"/>
       <c r="I6" s="95"/>
     </row>
-    <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="57" customHeight="1">
       <c r="B7" s="85" t="s">
         <v>128</v>
       </c>
@@ -6806,7 +6838,7 @@
       <c r="H7" s="91"/>
       <c r="I7" s="95"/>
     </row>
-    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="57" customHeight="1">
       <c r="B8" s="86" t="s">
         <v>3</v>
       </c>
@@ -6824,7 +6856,7 @@
       <c r="H8" s="91"/>
       <c r="I8" s="95"/>
     </row>
-    <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="27">
       <c r="B9" s="86" t="s">
         <v>46</v>
       </c>
@@ -6842,7 +6874,7 @@
       <c r="H9" s="91"/>
       <c r="I9" s="95"/>
     </row>
-    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="57" customHeight="1">
       <c r="B10" s="86" t="s">
         <v>56</v>
       </c>
@@ -6860,7 +6892,7 @@
       <c r="H10" s="91"/>
       <c r="I10" s="95"/>
     </row>
-    <row r="11" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="40.5">
       <c r="B11" s="85" t="s">
         <v>63</v>
       </c>
@@ -6878,7 +6910,7 @@
       <c r="H11" s="91"/>
       <c r="I11" s="95"/>
     </row>
-    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="57" customHeight="1">
       <c r="B12" s="86" t="s">
         <v>74</v>
       </c>
@@ -6896,7 +6928,7 @@
       <c r="H12" s="91"/>
       <c r="I12" s="95"/>
     </row>
-    <row r="13" spans="1:9" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="347.25" customHeight="1">
       <c r="B13" s="86" t="s">
         <v>121</v>
       </c>
@@ -6914,7 +6946,7 @@
       <c r="H13" s="91"/>
       <c r="I13" s="95"/>
     </row>
-    <row r="14" spans="1:9" ht="337.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="337.5">
       <c r="B14" s="87" t="s">
         <v>184</v>
       </c>
@@ -6938,7 +6970,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="57" customHeight="1">
       <c r="B15" s="87" t="s">
         <v>76</v>
       </c>
@@ -6956,7 +6988,7 @@
       <c r="H15" s="91"/>
       <c r="I15" s="95"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9">
       <c r="B16" s="86" t="s">
         <v>86</v>
       </c>
@@ -6974,7 +7006,7 @@
       <c r="H16" s="91"/>
       <c r="I16" s="95"/>
     </row>
-    <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="57" customHeight="1">
       <c r="B17" s="88" t="s">
         <v>144</v>
       </c>
@@ -6992,7 +7024,7 @@
       <c r="H17" s="91"/>
       <c r="I17" s="95"/>
     </row>
-    <row r="18" spans="2:9" ht="27" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" ht="27">
       <c r="B18" s="88" t="s">
         <v>109</v>
       </c>
@@ -7010,7 +7042,7 @@
       <c r="H18" s="91"/>
       <c r="I18" s="95"/>
     </row>
-    <row r="19" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" ht="57" customHeight="1">
       <c r="B19" s="87" t="s">
         <v>112</v>
       </c>
@@ -7028,7 +7060,7 @@
       <c r="H19" s="91"/>
       <c r="I19" s="95"/>
     </row>
-    <row r="20" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" ht="57" customHeight="1">
       <c r="B20" s="87" t="s">
         <v>170</v>
       </c>
@@ -7046,7 +7078,7 @@
       <c r="H20" s="113"/>
       <c r="I20" s="114"/>
     </row>
-    <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1">
       <c r="B21" s="89" t="s">
         <v>111</v>
       </c>
@@ -7064,7 +7096,7 @@
       <c r="H21" s="96"/>
       <c r="I21" s="97"/>
     </row>
-    <row r="22" spans="2:9" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="2:9" ht="14.25" thickTop="1"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:B3"/>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -569,16 +569,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>AP2
-8/15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SP
-11/01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[공조시스템설계팀] 
 박해룡 책임연구원
 01053904301</t>
@@ -1442,6 +1432,16 @@
   <si>
     <t>SOP
 9/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AP2
+8/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SP
+10/15</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3899,7 +3899,7 @@
     </row>
     <row r="4" spans="1:64" ht="183" customHeight="1" thickBot="1">
       <c r="B4" s="63" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C4" s="61" t="s">
         <v>80</v>
@@ -3980,7 +3980,7 @@
     </row>
     <row r="5" spans="1:64" ht="81">
       <c r="B5" s="28" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C5" s="62" t="s">
         <v>80</v>
@@ -4059,7 +4059,7 @@
     </row>
     <row r="6" spans="1:64" ht="67.5">
       <c r="B6" s="28" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C6" s="58" t="s">
         <v>81</v>
@@ -4142,7 +4142,7 @@
     </row>
     <row r="7" spans="1:64" ht="61.5" customHeight="1">
       <c r="B7" s="28" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C7" s="58" t="s">
         <v>82</v>
@@ -4223,7 +4223,7 @@
     </row>
     <row r="8" spans="1:64" ht="81">
       <c r="B8" s="28" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C8" s="58"/>
       <c r="D8" s="33"/>
@@ -4247,7 +4247,7 @@
       <c r="V8" s="30"/>
       <c r="W8" s="30"/>
       <c r="X8" s="15" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Y8" s="31"/>
       <c r="Z8" s="30"/>
@@ -4257,22 +4257,22 @@
       <c r="AD8" s="31"/>
       <c r="AE8" s="31"/>
       <c r="AF8" s="15" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AG8" s="31"/>
       <c r="AH8" s="31"/>
       <c r="AI8" s="17" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AJ8" s="31"/>
       <c r="AK8" s="31"/>
       <c r="AL8" s="31"/>
       <c r="AM8" s="17" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AN8" s="123"/>
       <c r="AO8" s="29" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AP8" s="31"/>
       <c r="AQ8" s="31"/>
@@ -4450,7 +4450,7 @@
     </row>
     <row r="11" spans="1:64" ht="61.5" customHeight="1">
       <c r="B11" s="28" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C11" s="58" t="s">
         <v>78</v>
@@ -4489,24 +4489,24 @@
       <c r="AE11" s="31"/>
       <c r="AF11" s="31"/>
       <c r="AG11" s="13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AH11" s="7"/>
       <c r="AI11" s="13"/>
       <c r="AJ11" s="7"/>
       <c r="AK11" s="17" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AL11" s="7"/>
       <c r="AM11" s="7"/>
       <c r="AN11" s="8"/>
       <c r="AO11" s="9"/>
       <c r="AP11" s="17" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AQ11" s="7"/>
       <c r="AR11" s="13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AS11" s="7"/>
       <c r="AT11" s="7"/>
@@ -4531,10 +4531,10 @@
     </row>
     <row r="12" spans="1:64" ht="61.5" customHeight="1">
       <c r="B12" s="28" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D12" s="33"/>
       <c r="E12" s="6"/>
@@ -4569,12 +4569,12 @@
       <c r="AH12" s="7"/>
       <c r="AI12" s="13"/>
       <c r="AJ12" s="101" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AK12" s="36"/>
       <c r="AL12" s="13"/>
       <c r="AM12" s="13" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AN12" s="8"/>
       <c r="AO12" s="12"/>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="AW12" s="7"/>
       <c r="AX12" s="13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AY12" s="7"/>
       <c r="AZ12" s="10"/>
@@ -4745,13 +4745,13 @@
       <c r="AH14" s="7"/>
       <c r="AI14" s="7"/>
       <c r="AJ14" s="13" t="s">
-        <v>104</v>
+        <v>237</v>
       </c>
       <c r="AK14" s="13" t="s">
         <v>13</v>
       </c>
       <c r="AL14" s="17" t="s">
-        <v>105</v>
+        <v>238</v>
       </c>
       <c r="AM14" s="7"/>
       <c r="AN14" s="8"/>
@@ -4961,10 +4961,10 @@
         <v>76</v>
       </c>
       <c r="C17" s="60" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D17" s="76" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E17" s="40"/>
       <c r="F17" s="41"/>
@@ -4975,13 +4975,13 @@
       <c r="K17" s="41"/>
       <c r="L17" s="41"/>
       <c r="M17" s="13" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="N17" s="41"/>
       <c r="O17" s="41"/>
       <c r="P17" s="43"/>
       <c r="Q17" s="104" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="R17" s="103"/>
       <c r="S17" s="41"/>
@@ -4991,7 +4991,7 @@
       <c r="W17" s="42"/>
       <c r="X17" s="41"/>
       <c r="Y17" s="30" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="Z17" s="41"/>
       <c r="AA17" s="41"/>
@@ -5004,7 +5004,7 @@
       <c r="AH17" s="41"/>
       <c r="AI17" s="37"/>
       <c r="AJ17" s="30" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AK17" s="46"/>
       <c r="AL17" s="41"/>
@@ -5012,11 +5012,11 @@
       <c r="AN17" s="8"/>
       <c r="AO17" s="47"/>
       <c r="AP17" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AQ17" s="42"/>
       <c r="AR17" s="37" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AS17" s="41"/>
       <c r="AT17" s="42"/>
@@ -5024,7 +5024,7 @@
       <c r="AV17" s="41"/>
       <c r="AW17" s="41"/>
       <c r="AX17" s="17" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AY17" s="41"/>
       <c r="AZ17" s="48"/>
@@ -5032,7 +5032,7 @@
       <c r="BB17" s="45"/>
       <c r="BC17" s="45"/>
       <c r="BD17" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="BE17" s="71"/>
       <c r="BF17" s="45"/>
@@ -5048,7 +5048,7 @@
         <v>86</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D18" s="33"/>
       <c r="E18" s="64"/>
@@ -5136,10 +5136,10 @@
     </row>
     <row r="19" spans="2:64" ht="61.5" customHeight="1">
       <c r="B19" s="77" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C19" s="78" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D19" s="33"/>
       <c r="E19" s="64"/>
@@ -5221,10 +5221,10 @@
     </row>
     <row r="20" spans="2:64" ht="61.5" customHeight="1">
       <c r="B20" s="77" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C20" s="78" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D20" s="39"/>
       <c r="E20" s="64"/>
@@ -5290,10 +5290,10 @@
     </row>
     <row r="21" spans="2:64" ht="61.5" customHeight="1">
       <c r="B21" s="57" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C21" s="82" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D21" s="39"/>
       <c r="E21" s="64"/>
@@ -5335,14 +5335,14 @@
       <c r="AO21" s="67"/>
       <c r="AP21" s="69"/>
       <c r="AQ21" s="69" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AR21" s="69"/>
       <c r="AS21" s="65"/>
       <c r="AT21" s="65"/>
       <c r="AU21" s="69"/>
       <c r="AV21" s="13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AW21" s="65"/>
       <c r="AX21" s="65"/>
@@ -5350,20 +5350,20 @@
       <c r="AZ21" s="70"/>
       <c r="BA21" s="67"/>
       <c r="BB21" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="BC21" s="73"/>
       <c r="BD21" s="69" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="BE21" s="72"/>
       <c r="BF21" s="73"/>
       <c r="BG21" s="69" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="BH21" s="73"/>
       <c r="BI21" s="69" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="BJ21" s="73"/>
       <c r="BK21" s="73"/>
@@ -5371,10 +5371,10 @@
     </row>
     <row r="22" spans="2:64" ht="61.5" customHeight="1">
       <c r="B22" s="57" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C22" s="82" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D22" s="39"/>
       <c r="E22" s="64"/>
@@ -5440,10 +5440,10 @@
     </row>
     <row r="23" spans="2:64" ht="61.5" customHeight="1" thickBot="1">
       <c r="B23" s="79" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C23" s="80" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D23" s="81"/>
       <c r="E23" s="49"/>
@@ -5543,10 +5543,10 @@
   <sheetData>
     <row r="1" spans="1:14" ht="32.25" thickBot="1">
       <c r="A1" s="110" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B1" s="111" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C1" s="111"/>
       <c r="D1" s="111"/>
@@ -5557,25 +5557,25 @@
         <v>2</v>
       </c>
       <c r="C2" s="139" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D2" s="139" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E2" s="137" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F2" s="98" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G2" s="133" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H2" s="133"/>
       <c r="I2" s="133"/>
       <c r="J2" s="134"/>
       <c r="K2" s="133" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="L2" s="133"/>
       <c r="M2" s="133"/>
@@ -5587,169 +5587,169 @@
       <c r="D3" s="140"/>
       <c r="E3" s="138"/>
       <c r="F3" s="99" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G3" s="99" t="s">
+        <v>115</v>
+      </c>
+      <c r="H3" s="99" t="s">
+        <v>116</v>
+      </c>
+      <c r="I3" s="99" t="s">
         <v>117</v>
       </c>
-      <c r="H3" s="99" t="s">
-        <v>118</v>
-      </c>
-      <c r="I3" s="99" t="s">
-        <v>119</v>
-      </c>
       <c r="J3" s="100" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K3" s="99" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L3" s="99" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M3" s="99" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N3" s="100" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="108">
       <c r="B4" s="84" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C4" s="118" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D4" s="118" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E4" s="92" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F4" s="107" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G4" s="116" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H4" s="107" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I4" s="107" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J4" s="94"/>
       <c r="K4" s="107" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="L4" s="107" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M4" s="107"/>
       <c r="N4" s="94"/>
     </row>
     <row r="5" spans="1:14" ht="108">
       <c r="B5" s="85" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C5" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D5" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E5" s="93" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F5" s="107" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G5" s="116" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H5" s="107" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I5" s="107" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J5" s="95"/>
       <c r="K5" s="107" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="L5" s="107" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M5" s="107"/>
       <c r="N5" s="95"/>
     </row>
     <row r="6" spans="1:14" ht="108">
       <c r="B6" s="85" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C6" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D6" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E6" s="93" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F6" s="107" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G6" s="116" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H6" s="107" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I6" s="107" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J6" s="95"/>
       <c r="K6" s="107" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="L6" s="107" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M6" s="107"/>
       <c r="N6" s="95"/>
     </row>
     <row r="7" spans="1:14" ht="108">
       <c r="B7" s="85" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C7" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D7" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E7" s="93" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F7" s="107" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G7" s="116" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H7" s="107" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I7" s="107" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J7" s="95"/>
       <c r="K7" s="107" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="L7" s="107" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M7" s="107"/>
       <c r="N7" s="95"/>
@@ -5759,32 +5759,32 @@
         <v>3</v>
       </c>
       <c r="C8" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D8" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E8" s="93" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F8" s="107" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G8" s="116" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H8" s="107" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I8" s="107" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J8" s="95"/>
       <c r="K8" s="107" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="L8" s="107" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M8" s="107"/>
       <c r="N8" s="95"/>
@@ -5794,32 +5794,32 @@
         <v>46</v>
       </c>
       <c r="C9" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D9" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E9" s="102" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F9" s="107" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G9" s="116" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H9" s="107" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I9" s="107" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J9" s="95"/>
       <c r="K9" s="107" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="L9" s="107" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="M9" s="107"/>
       <c r="N9" s="95"/>
@@ -5829,32 +5829,32 @@
         <v>56</v>
       </c>
       <c r="C10" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D10" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E10" s="102" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F10" s="107" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G10" s="116" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H10" s="107" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I10" s="107" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="J10" s="95"/>
       <c r="K10" s="107" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="L10" s="107" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M10" s="107"/>
       <c r="N10" s="95"/>
@@ -5864,32 +5864,32 @@
         <v>63</v>
       </c>
       <c r="C11" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D11" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E11" s="102" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F11" s="107" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G11" s="116" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H11" s="107" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I11" s="107" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J11" s="95"/>
       <c r="K11" s="107" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L11" s="107" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M11" s="107"/>
       <c r="N11" s="95"/>
@@ -5899,96 +5899,96 @@
         <v>74</v>
       </c>
       <c r="C12" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D12" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E12" s="102" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F12" s="107" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G12" s="116" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H12" s="107" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I12" s="107" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J12" s="95"/>
       <c r="K12" s="107" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="L12" s="107" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M12" s="107"/>
       <c r="N12" s="95"/>
     </row>
     <row r="13" spans="1:14" ht="347.25" customHeight="1">
       <c r="B13" s="86" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C13" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D13" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E13" s="102" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F13" s="107" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G13" s="116" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H13" s="107" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I13" s="107" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="J13" s="95"/>
       <c r="K13" s="107" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="L13" s="107" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="M13" s="107"/>
       <c r="N13" s="95"/>
     </row>
     <row r="14" spans="1:14" ht="175.5">
       <c r="B14" s="87" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C14" s="119" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D14" s="119" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E14" s="102"/>
       <c r="F14" s="107"/>
       <c r="G14" s="116"/>
       <c r="H14" s="107" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I14" s="107" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J14" s="95"/>
       <c r="K14" s="107" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L14" s="107" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="M14" s="107"/>
       <c r="N14" s="95"/>
@@ -5998,29 +5998,29 @@
         <v>76</v>
       </c>
       <c r="C15" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D15" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E15" s="102" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F15" s="107" t="s">
+        <v>173</v>
+      </c>
+      <c r="G15" s="116" t="s">
+        <v>172</v>
+      </c>
+      <c r="H15" s="107" t="s">
+        <v>191</v>
+      </c>
+      <c r="I15" s="107" t="s">
         <v>175</v>
-      </c>
-      <c r="G15" s="116" t="s">
-        <v>174</v>
-      </c>
-      <c r="H15" s="107" t="s">
-        <v>193</v>
-      </c>
-      <c r="I15" s="107" t="s">
-        <v>177</v>
       </c>
       <c r="J15" s="95"/>
       <c r="K15" s="107" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="L15" s="107"/>
       <c r="M15" s="107"/>
@@ -6031,29 +6031,29 @@
         <v>86</v>
       </c>
       <c r="C16" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D16" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E16" s="93" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F16" s="107" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G16" s="116" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H16" s="107" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I16" s="107" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J16" s="95"/>
       <c r="K16" s="107" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L16" s="107"/>
       <c r="M16" s="107"/>
@@ -6061,173 +6061,173 @@
     </row>
     <row r="17" spans="2:14" ht="57" customHeight="1">
       <c r="B17" s="88" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C17" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D17" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E17" s="93" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F17" s="91"/>
       <c r="G17" s="116" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H17" s="91" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I17" s="91" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J17" s="95"/>
       <c r="K17" s="91" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="L17" s="91" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="M17" s="91"/>
       <c r="N17" s="95"/>
     </row>
     <row r="18" spans="2:14" ht="162">
       <c r="B18" s="88" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C18" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D18" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E18" s="102" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F18" s="107" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G18" s="116" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H18" s="107" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I18" s="107" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J18" s="95"/>
       <c r="K18" s="107" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="L18" s="107" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="M18" s="107"/>
       <c r="N18" s="95"/>
     </row>
     <row r="19" spans="2:14" ht="57" customHeight="1">
       <c r="B19" s="87" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C19" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D19" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E19" s="93" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F19" s="106" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G19" s="116" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H19" s="107" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I19" s="107" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J19" s="95"/>
       <c r="K19" s="107" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="L19" s="107" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M19" s="107"/>
       <c r="N19" s="95"/>
     </row>
     <row r="20" spans="2:14" ht="57" customHeight="1">
       <c r="B20" s="87" t="s">
+        <v>169</v>
+      </c>
+      <c r="C20" s="119" t="s">
+        <v>176</v>
+      </c>
+      <c r="D20" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E20" s="115" t="s">
+        <v>170</v>
+      </c>
+      <c r="F20" s="112" t="s">
         <v>171</v>
       </c>
-      <c r="C20" s="119" t="s">
-        <v>178</v>
-      </c>
-      <c r="D20" s="119" t="s">
-        <v>181</v>
-      </c>
-      <c r="E20" s="115" t="s">
+      <c r="G20" s="116" t="s">
         <v>172</v>
       </c>
-      <c r="F20" s="112" t="s">
-        <v>173</v>
-      </c>
-      <c r="G20" s="116" t="s">
-        <v>174</v>
-      </c>
       <c r="H20" s="121" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I20" s="107" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J20" s="114"/>
       <c r="K20" s="107" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="L20" s="107" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M20" s="107"/>
       <c r="N20" s="114"/>
     </row>
     <row r="21" spans="2:14" ht="57" customHeight="1" thickBot="1">
       <c r="B21" s="89" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C21" s="120" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D21" s="120" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E21" s="105" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F21" s="108" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G21" s="117" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H21" s="122" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I21" s="122" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J21" s="97"/>
       <c r="K21" s="122" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="L21" s="122" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M21" s="122"/>
       <c r="N21" s="97"/>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="111" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C1" s="111"/>
       <c r="D1" s="111"/>
@@ -6332,16 +6332,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="139" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D2" s="139" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E2" s="137" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F2" s="133" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G2" s="133"/>
       <c r="H2" s="133"/>
@@ -6353,30 +6353,30 @@
       <c r="D3" s="140"/>
       <c r="E3" s="138"/>
       <c r="F3" s="99" t="s">
+        <v>115</v>
+      </c>
+      <c r="G3" s="99" t="s">
+        <v>116</v>
+      </c>
+      <c r="H3" s="99" t="s">
         <v>117</v>
       </c>
-      <c r="G3" s="99" t="s">
-        <v>118</v>
-      </c>
-      <c r="H3" s="99" t="s">
-        <v>119</v>
-      </c>
       <c r="I3" s="100" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1">
       <c r="B4" s="84" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C4" s="118" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D4" s="118" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E4" s="92" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F4" s="116"/>
       <c r="G4" s="107"/>
@@ -6385,16 +6385,16 @@
     </row>
     <row r="5" spans="1:9" ht="57" customHeight="1">
       <c r="B5" s="85" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C5" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D5" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E5" s="93" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F5" s="116"/>
       <c r="G5" s="107"/>
@@ -6403,16 +6403,16 @@
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1">
       <c r="B6" s="85" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C6" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D6" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E6" s="93" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F6" s="116"/>
       <c r="G6" s="107"/>
@@ -6421,16 +6421,16 @@
     </row>
     <row r="7" spans="1:9" ht="57" customHeight="1">
       <c r="B7" s="85" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C7" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D7" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E7" s="93" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F7" s="116"/>
       <c r="G7" s="107"/>
@@ -6442,13 +6442,13 @@
         <v>3</v>
       </c>
       <c r="C8" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D8" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E8" s="93" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F8" s="116"/>
       <c r="G8" s="107"/>
@@ -6460,13 +6460,13 @@
         <v>46</v>
       </c>
       <c r="C9" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D9" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E9" s="102" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F9" s="116"/>
       <c r="G9" s="107"/>
@@ -6478,13 +6478,13 @@
         <v>56</v>
       </c>
       <c r="C10" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D10" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E10" s="102" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F10" s="116"/>
       <c r="G10" s="107"/>
@@ -6496,13 +6496,13 @@
         <v>63</v>
       </c>
       <c r="C11" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D11" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E11" s="102" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F11" s="116"/>
       <c r="G11" s="107"/>
@@ -6514,13 +6514,13 @@
         <v>74</v>
       </c>
       <c r="C12" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D12" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E12" s="102" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F12" s="116"/>
       <c r="G12" s="107"/>
@@ -6529,16 +6529,16 @@
     </row>
     <row r="13" spans="1:9" ht="347.25" customHeight="1">
       <c r="B13" s="86" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C13" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D13" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E13" s="102" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F13" s="116"/>
       <c r="G13" s="107"/>
@@ -6547,20 +6547,20 @@
     </row>
     <row r="14" spans="1:9" ht="409.5">
       <c r="B14" s="87" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C14" s="119" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D14" s="119" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E14" s="102"/>
       <c r="F14" s="116"/>
       <c r="G14" s="107"/>
       <c r="H14" s="91"/>
       <c r="I14" s="124" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="57" customHeight="1">
@@ -6568,13 +6568,13 @@
         <v>76</v>
       </c>
       <c r="C15" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D15" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E15" s="102" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F15" s="116"/>
       <c r="G15" s="107"/>
@@ -6586,13 +6586,13 @@
         <v>86</v>
       </c>
       <c r="C16" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D16" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E16" s="93" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F16" s="116"/>
       <c r="G16" s="107"/>
@@ -6601,16 +6601,16 @@
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1">
       <c r="B17" s="88" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C17" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D17" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E17" s="93" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F17" s="116"/>
       <c r="G17" s="91"/>
@@ -6619,16 +6619,16 @@
     </row>
     <row r="18" spans="2:9" ht="27">
       <c r="B18" s="88" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C18" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D18" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E18" s="102" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F18" s="116"/>
       <c r="G18" s="107"/>
@@ -6637,16 +6637,16 @@
     </row>
     <row r="19" spans="2:9" ht="57" customHeight="1">
       <c r="B19" s="87" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C19" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D19" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E19" s="93" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F19" s="116"/>
       <c r="G19" s="106"/>
@@ -6655,16 +6655,16 @@
     </row>
     <row r="20" spans="2:9" ht="57" customHeight="1">
       <c r="B20" s="87" t="s">
+        <v>168</v>
+      </c>
+      <c r="C20" s="119" t="s">
+        <v>176</v>
+      </c>
+      <c r="D20" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E20" s="115" t="s">
         <v>170</v>
-      </c>
-      <c r="C20" s="119" t="s">
-        <v>178</v>
-      </c>
-      <c r="D20" s="119" t="s">
-        <v>181</v>
-      </c>
-      <c r="E20" s="115" t="s">
-        <v>172</v>
       </c>
       <c r="F20" s="116"/>
       <c r="G20" s="112"/>
@@ -6673,16 +6673,16 @@
     </row>
     <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1">
       <c r="B21" s="89" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C21" s="120" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D21" s="120" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E21" s="105" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F21" s="117"/>
       <c r="G21" s="108"/>
@@ -6722,7 +6722,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="111" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C1" s="111"/>
       <c r="D1" s="111"/>
@@ -6733,16 +6733,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="139" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D2" s="139" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E2" s="137" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F2" s="133" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G2" s="133"/>
       <c r="H2" s="133"/>
@@ -6754,30 +6754,30 @@
       <c r="D3" s="140"/>
       <c r="E3" s="138"/>
       <c r="F3" s="99" t="s">
+        <v>115</v>
+      </c>
+      <c r="G3" s="99" t="s">
+        <v>116</v>
+      </c>
+      <c r="H3" s="99" t="s">
         <v>117</v>
       </c>
-      <c r="G3" s="99" t="s">
-        <v>118</v>
-      </c>
-      <c r="H3" s="99" t="s">
-        <v>119</v>
-      </c>
       <c r="I3" s="100" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1">
       <c r="B4" s="84" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C4" s="118" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D4" s="118" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E4" s="92" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F4" s="116"/>
       <c r="G4" s="107"/>
@@ -6786,16 +6786,16 @@
     </row>
     <row r="5" spans="1:9" ht="57" customHeight="1">
       <c r="B5" s="85" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C5" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D5" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E5" s="93" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F5" s="116"/>
       <c r="G5" s="107"/>
@@ -6804,16 +6804,16 @@
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1">
       <c r="B6" s="85" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C6" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D6" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E6" s="93" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F6" s="116"/>
       <c r="G6" s="107"/>
@@ -6822,16 +6822,16 @@
     </row>
     <row r="7" spans="1:9" ht="57" customHeight="1">
       <c r="B7" s="85" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C7" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D7" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E7" s="93" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F7" s="116"/>
       <c r="G7" s="107"/>
@@ -6843,13 +6843,13 @@
         <v>3</v>
       </c>
       <c r="C8" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D8" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E8" s="93" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F8" s="116"/>
       <c r="G8" s="107"/>
@@ -6861,13 +6861,13 @@
         <v>46</v>
       </c>
       <c r="C9" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D9" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E9" s="102" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F9" s="116"/>
       <c r="G9" s="107"/>
@@ -6879,13 +6879,13 @@
         <v>56</v>
       </c>
       <c r="C10" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D10" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E10" s="102" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F10" s="116"/>
       <c r="G10" s="107"/>
@@ -6897,13 +6897,13 @@
         <v>63</v>
       </c>
       <c r="C11" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D11" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E11" s="102" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F11" s="116"/>
       <c r="G11" s="107"/>
@@ -6915,13 +6915,13 @@
         <v>74</v>
       </c>
       <c r="C12" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D12" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E12" s="102" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F12" s="116"/>
       <c r="G12" s="107"/>
@@ -6930,16 +6930,16 @@
     </row>
     <row r="13" spans="1:9" ht="347.25" customHeight="1">
       <c r="B13" s="86" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C13" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D13" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E13" s="102" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F13" s="116"/>
       <c r="G13" s="107"/>
@@ -6948,26 +6948,26 @@
     </row>
     <row r="14" spans="1:9" ht="337.5">
       <c r="B14" s="87" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C14" s="119" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D14" s="119" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E14" s="102"/>
       <c r="F14" s="125" t="s">
+        <v>230</v>
+      </c>
+      <c r="G14" s="125" t="s">
+        <v>231</v>
+      </c>
+      <c r="H14" s="125" t="s">
         <v>232</v>
       </c>
-      <c r="G14" s="125" t="s">
-        <v>233</v>
-      </c>
-      <c r="H14" s="125" t="s">
-        <v>234</v>
-      </c>
       <c r="I14" s="125" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="57" customHeight="1">
@@ -6975,13 +6975,13 @@
         <v>76</v>
       </c>
       <c r="C15" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D15" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E15" s="102" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F15" s="116"/>
       <c r="G15" s="107"/>
@@ -6993,13 +6993,13 @@
         <v>86</v>
       </c>
       <c r="C16" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D16" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E16" s="93" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F16" s="116"/>
       <c r="G16" s="107"/>
@@ -7008,16 +7008,16 @@
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1">
       <c r="B17" s="88" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C17" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D17" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E17" s="93" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F17" s="116"/>
       <c r="G17" s="91"/>
@@ -7026,16 +7026,16 @@
     </row>
     <row r="18" spans="2:9" ht="27">
       <c r="B18" s="88" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C18" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D18" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E18" s="102" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F18" s="116"/>
       <c r="G18" s="107"/>
@@ -7044,16 +7044,16 @@
     </row>
     <row r="19" spans="2:9" ht="57" customHeight="1">
       <c r="B19" s="87" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C19" s="119" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D19" s="119" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E19" s="93" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F19" s="116"/>
       <c r="G19" s="106"/>
@@ -7062,16 +7062,16 @@
     </row>
     <row r="20" spans="2:9" ht="57" customHeight="1">
       <c r="B20" s="87" t="s">
+        <v>168</v>
+      </c>
+      <c r="C20" s="119" t="s">
+        <v>176</v>
+      </c>
+      <c r="D20" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E20" s="115" t="s">
         <v>170</v>
-      </c>
-      <c r="C20" s="119" t="s">
-        <v>178</v>
-      </c>
-      <c r="D20" s="119" t="s">
-        <v>181</v>
-      </c>
-      <c r="E20" s="115" t="s">
-        <v>172</v>
       </c>
       <c r="F20" s="116"/>
       <c r="G20" s="112"/>
@@ -7080,16 +7080,16 @@
     </row>
     <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1">
       <c r="B21" s="89" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C21" s="120" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D21" s="120" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E21" s="105" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F21" s="117"/>
       <c r="G21" s="108"/>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\2.project\hkmc_ptc_heater\Doc\1. 일정\1. Weekly Plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\일정\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="대일정" sheetId="1" r:id="rId1"/>
-    <sheet name="2025.5" sheetId="2" r:id="rId2"/>
-    <sheet name="2025.6" sheetId="3" r:id="rId3"/>
-    <sheet name="2025.7" sheetId="4" r:id="rId4"/>
+    <sheet name="업무 분배" sheetId="5" r:id="rId2"/>
+    <sheet name="2025.5" sheetId="2" r:id="rId3"/>
+    <sheet name="2025.6" sheetId="3" r:id="rId4"/>
+    <sheet name="2025.7" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="259">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1444,6 +1445,86 @@
 10/15</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>양산 중</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진행 중</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mva</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조현진 전임</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AY, HE1I</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>임제훈 사원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nea</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QV</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mea</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cva</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BJ1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SU2I</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NX5e, NQ6e</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SX3e</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NEaW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MX5a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SUZUKI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오세영 수석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1452,7 +1533,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1550,8 +1631,40 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1582,6 +1695,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="73">
     <border>
@@ -2592,12 +2731,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3021,8 +3175,28 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" xfId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
+    <cellStyle name="60% - 강조색3" xfId="4" builtinId="40"/>
+    <cellStyle name="강조색5" xfId="5" builtinId="45"/>
+    <cellStyle name="나쁨" xfId="2" builtinId="27"/>
+    <cellStyle name="보통" xfId="3" builtinId="28"/>
+    <cellStyle name="좋음" xfId="1" builtinId="26"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3610,7 +3784,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BL24"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.375" customWidth="1"/>
     <col min="2" max="2" width="18.875" customWidth="1"/>
@@ -3621,7 +3795,7 @@
     <col min="36" max="64" width="8.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" s="20" customFormat="1" ht="32.25" thickBot="1">
+    <row r="1" spans="1:64" s="20" customFormat="1" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -3631,7 +3805,7 @@
       <c r="C1" s="21"/>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1">
+    <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B2" s="126" t="s">
         <v>2</v>
       </c>
@@ -3712,7 +3886,7 @@
       <c r="BK2" s="130"/>
       <c r="BL2" s="131"/>
     </row>
-    <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1">
+    <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="127"/>
       <c r="C3" s="129"/>
       <c r="D3" s="129"/>
@@ -3897,7 +4071,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:64" ht="183" customHeight="1" thickBot="1">
+    <row r="4" spans="1:64" ht="183" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="63" t="s">
         <v>120</v>
       </c>
@@ -3978,7 +4152,7 @@
       <c r="BK4" s="2"/>
       <c r="BL4" s="5"/>
     </row>
-    <row r="5" spans="1:64" ht="81">
+    <row r="5" spans="1:64" ht="81" x14ac:dyDescent="0.3">
       <c r="B5" s="28" t="s">
         <v>121</v>
       </c>
@@ -4057,7 +4231,7 @@
       <c r="BK5" s="31"/>
       <c r="BL5" s="10"/>
     </row>
-    <row r="6" spans="1:64" ht="67.5">
+    <row r="6" spans="1:64" ht="67.5" x14ac:dyDescent="0.3">
       <c r="B6" s="28" t="s">
         <v>122</v>
       </c>
@@ -4140,7 +4314,7 @@
       <c r="BK6" s="31"/>
       <c r="BL6" s="10"/>
     </row>
-    <row r="7" spans="1:64" ht="61.5" customHeight="1">
+    <row r="7" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="28" t="s">
         <v>123</v>
       </c>
@@ -4221,7 +4395,7 @@
       <c r="BK7" s="31"/>
       <c r="BL7" s="10"/>
     </row>
-    <row r="8" spans="1:64" ht="81">
+    <row r="8" spans="1:64" ht="81" x14ac:dyDescent="0.3">
       <c r="B8" s="28" t="s">
         <v>222</v>
       </c>
@@ -4298,7 +4472,7 @@
       <c r="BK8" s="31"/>
       <c r="BL8" s="10"/>
     </row>
-    <row r="9" spans="1:64" ht="61.5" customHeight="1">
+    <row r="9" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="27" t="s">
         <v>3</v>
       </c>
@@ -4371,7 +4545,7 @@
       <c r="BK9" s="31"/>
       <c r="BL9" s="10"/>
     </row>
-    <row r="10" spans="1:64" ht="61.5" customHeight="1">
+    <row r="10" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="27" t="s">
         <v>46</v>
       </c>
@@ -4448,7 +4622,7 @@
       <c r="BK10" s="31"/>
       <c r="BL10" s="10"/>
     </row>
-    <row r="11" spans="1:64" ht="61.5" customHeight="1">
+    <row r="11" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="28" t="s">
         <v>128</v>
       </c>
@@ -4529,7 +4703,7 @@
       <c r="BK11" s="31"/>
       <c r="BL11" s="10"/>
     </row>
-    <row r="12" spans="1:64" ht="61.5" customHeight="1">
+    <row r="12" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="28" t="s">
         <v>129</v>
       </c>
@@ -4608,7 +4782,7 @@
       <c r="BK12" s="31"/>
       <c r="BL12" s="10"/>
     </row>
-    <row r="13" spans="1:64" ht="183.75" customHeight="1">
+    <row r="13" spans="1:64" ht="183.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="28" t="s">
         <v>63</v>
       </c>
@@ -4697,7 +4871,7 @@
       <c r="BK13" s="31"/>
       <c r="BL13" s="10"/>
     </row>
-    <row r="14" spans="1:64" ht="67.5">
+    <row r="14" spans="1:64" ht="67.5" x14ac:dyDescent="0.3">
       <c r="B14" s="27" t="s">
         <v>74</v>
       </c>
@@ -4786,7 +4960,7 @@
       <c r="BK14" s="31"/>
       <c r="BL14" s="10"/>
     </row>
-    <row r="15" spans="1:64" ht="61.5" customHeight="1">
+    <row r="15" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="27" t="s">
         <v>65</v>
       </c>
@@ -4867,7 +5041,7 @@
       <c r="BK15" s="31"/>
       <c r="BL15" s="10"/>
     </row>
-    <row r="16" spans="1:64" ht="61.5" customHeight="1">
+    <row r="16" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="27" t="s">
         <v>66</v>
       </c>
@@ -4956,7 +5130,7 @@
       <c r="BK16" s="31"/>
       <c r="BL16" s="10"/>
     </row>
-    <row r="17" spans="2:64" ht="61.5" customHeight="1">
+    <row r="17" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="57" t="s">
         <v>76</v>
       </c>
@@ -5043,7 +5217,7 @@
       <c r="BK17" s="71"/>
       <c r="BL17" s="48"/>
     </row>
-    <row r="18" spans="2:64" ht="76.5" customHeight="1">
+    <row r="18" spans="2:64" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="27" t="s">
         <v>86</v>
       </c>
@@ -5134,7 +5308,7 @@
       <c r="BK18" s="73"/>
       <c r="BL18" s="70"/>
     </row>
-    <row r="19" spans="2:64" ht="61.5" customHeight="1">
+    <row r="19" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="77" t="s">
         <v>142</v>
       </c>
@@ -5219,7 +5393,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="2:64" ht="61.5" customHeight="1">
+    <row r="20" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="77" t="s">
         <v>107</v>
       </c>
@@ -5288,7 +5462,7 @@
       <c r="BK20" s="73"/>
       <c r="BL20" s="70"/>
     </row>
-    <row r="21" spans="2:64" ht="61.5" customHeight="1">
+    <row r="21" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="57" t="s">
         <v>110</v>
       </c>
@@ -5369,7 +5543,7 @@
       <c r="BK21" s="73"/>
       <c r="BL21" s="70"/>
     </row>
-    <row r="22" spans="2:64" ht="61.5" customHeight="1">
+    <row r="22" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="57" t="s">
         <v>167</v>
       </c>
@@ -5438,7 +5612,7 @@
       <c r="BK22" s="73"/>
       <c r="BL22" s="70"/>
     </row>
-    <row r="23" spans="2:64" ht="61.5" customHeight="1" thickBot="1">
+    <row r="23" spans="2:64" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="79" t="s">
         <v>168</v>
       </c>
@@ -5507,7 +5681,7 @@
       <c r="BK23" s="75"/>
       <c r="BL23" s="55"/>
     </row>
-    <row r="24" spans="2:64" ht="17.25" thickTop="1"/>
+    <row r="24" spans="2:64" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B2:B3"/>
@@ -5527,9 +5701,140 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="141" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" s="142" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="141" t="s">
+        <v>245</v>
+      </c>
+      <c r="B3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C3" s="143" t="s">
+        <v>246</v>
+      </c>
+      <c r="D3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="141" t="s">
+        <v>247</v>
+      </c>
+      <c r="B4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C4" s="143" t="s">
+        <v>248</v>
+      </c>
+      <c r="D4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="144" t="s">
+        <v>249</v>
+      </c>
+      <c r="B5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C5" s="143" t="s">
+        <v>250</v>
+      </c>
+      <c r="D5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="142" t="s">
+        <v>251</v>
+      </c>
+      <c r="B6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C6" s="145" t="s">
+        <v>252</v>
+      </c>
+      <c r="D6" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="142" t="s">
+        <v>253</v>
+      </c>
+      <c r="B7" t="s">
+        <v>244</v>
+      </c>
+      <c r="C7" s="145" t="s">
+        <v>254</v>
+      </c>
+      <c r="D7" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C8" s="141" t="s">
+        <v>255</v>
+      </c>
+      <c r="D8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C9" s="141" t="s">
+        <v>256</v>
+      </c>
+      <c r="D9" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C10" s="145" t="s">
+        <v>257</v>
+      </c>
+      <c r="D10" t="s">
+        <v>258</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.375" style="83" customWidth="1"/>
     <col min="2" max="2" width="9" style="83"/>
@@ -5541,7 +5846,7 @@
     <col min="15" max="16384" width="9" style="83"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="32.25" thickBot="1">
+    <row r="1" spans="1:14" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="110" t="s">
         <v>149</v>
       </c>
@@ -5552,7 +5857,7 @@
       <c r="D1" s="111"/>
       <c r="E1" s="109"/>
     </row>
-    <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1">
+    <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B2" s="135" t="s">
         <v>2</v>
       </c>
@@ -5581,7 +5886,7 @@
       <c r="M2" s="133"/>
       <c r="N2" s="134"/>
     </row>
-    <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1">
+    <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="136"/>
       <c r="C3" s="140"/>
       <c r="D3" s="140"/>
@@ -5614,7 +5919,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="108">
+    <row r="4" spans="1:14" ht="108" x14ac:dyDescent="0.3">
       <c r="B4" s="84" t="s">
         <v>118</v>
       </c>
@@ -5649,7 +5954,7 @@
       <c r="M4" s="107"/>
       <c r="N4" s="94"/>
     </row>
-    <row r="5" spans="1:14" ht="108">
+    <row r="5" spans="1:14" ht="108" x14ac:dyDescent="0.3">
       <c r="B5" s="85" t="s">
         <v>124</v>
       </c>
@@ -5684,7 +5989,7 @@
       <c r="M5" s="107"/>
       <c r="N5" s="95"/>
     </row>
-    <row r="6" spans="1:14" ht="108">
+    <row r="6" spans="1:14" ht="108" x14ac:dyDescent="0.3">
       <c r="B6" s="85" t="s">
         <v>125</v>
       </c>
@@ -5719,7 +6024,7 @@
       <c r="M6" s="107"/>
       <c r="N6" s="95"/>
     </row>
-    <row r="7" spans="1:14" ht="108">
+    <row r="7" spans="1:14" ht="108" x14ac:dyDescent="0.3">
       <c r="B7" s="85" t="s">
         <v>126</v>
       </c>
@@ -5754,7 +6059,7 @@
       <c r="M7" s="107"/>
       <c r="N7" s="95"/>
     </row>
-    <row r="8" spans="1:14" ht="108">
+    <row r="8" spans="1:14" ht="108" x14ac:dyDescent="0.3">
       <c r="B8" s="86" t="s">
         <v>3</v>
       </c>
@@ -5789,7 +6094,7 @@
       <c r="M8" s="107"/>
       <c r="N8" s="95"/>
     </row>
-    <row r="9" spans="1:14" ht="175.5">
+    <row r="9" spans="1:14" ht="175.5" x14ac:dyDescent="0.3">
       <c r="B9" s="86" t="s">
         <v>46</v>
       </c>
@@ -5824,7 +6129,7 @@
       <c r="M9" s="107"/>
       <c r="N9" s="95"/>
     </row>
-    <row r="10" spans="1:14" ht="121.5">
+    <row r="10" spans="1:14" ht="121.5" x14ac:dyDescent="0.3">
       <c r="B10" s="86" t="s">
         <v>56</v>
       </c>
@@ -5859,7 +6164,7 @@
       <c r="M10" s="107"/>
       <c r="N10" s="95"/>
     </row>
-    <row r="11" spans="1:14" ht="108">
+    <row r="11" spans="1:14" ht="108" x14ac:dyDescent="0.3">
       <c r="B11" s="85" t="s">
         <v>63</v>
       </c>
@@ -5894,7 +6199,7 @@
       <c r="M11" s="107"/>
       <c r="N11" s="95"/>
     </row>
-    <row r="12" spans="1:14" ht="57" customHeight="1">
+    <row r="12" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="86" t="s">
         <v>74</v>
       </c>
@@ -5929,7 +6234,7 @@
       <c r="M12" s="107"/>
       <c r="N12" s="95"/>
     </row>
-    <row r="13" spans="1:14" ht="347.25" customHeight="1">
+    <row r="13" spans="1:14" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="86" t="s">
         <v>119</v>
       </c>
@@ -5964,7 +6269,7 @@
       <c r="M13" s="107"/>
       <c r="N13" s="95"/>
     </row>
-    <row r="14" spans="1:14" ht="175.5">
+    <row r="14" spans="1:14" ht="175.5" x14ac:dyDescent="0.3">
       <c r="B14" s="87" t="s">
         <v>182</v>
       </c>
@@ -5993,7 +6298,7 @@
       <c r="M14" s="107"/>
       <c r="N14" s="95"/>
     </row>
-    <row r="15" spans="1:14" ht="57" customHeight="1">
+    <row r="15" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="87" t="s">
         <v>76</v>
       </c>
@@ -6026,7 +6331,7 @@
       <c r="M15" s="107"/>
       <c r="N15" s="95"/>
     </row>
-    <row r="16" spans="1:14" ht="121.5">
+    <row r="16" spans="1:14" ht="121.5" x14ac:dyDescent="0.3">
       <c r="B16" s="86" t="s">
         <v>86</v>
       </c>
@@ -6059,7 +6364,7 @@
       <c r="M16" s="107"/>
       <c r="N16" s="95"/>
     </row>
-    <row r="17" spans="2:14" ht="57" customHeight="1">
+    <row r="17" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="88" t="s">
         <v>142</v>
       </c>
@@ -6092,7 +6397,7 @@
       <c r="M17" s="91"/>
       <c r="N17" s="95"/>
     </row>
-    <row r="18" spans="2:14" ht="162">
+    <row r="18" spans="2:14" ht="162" x14ac:dyDescent="0.3">
       <c r="B18" s="88" t="s">
         <v>107</v>
       </c>
@@ -6127,7 +6432,7 @@
       <c r="M18" s="107"/>
       <c r="N18" s="95"/>
     </row>
-    <row r="19" spans="2:14" ht="57" customHeight="1">
+    <row r="19" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="87" t="s">
         <v>110</v>
       </c>
@@ -6162,7 +6467,7 @@
       <c r="M19" s="107"/>
       <c r="N19" s="95"/>
     </row>
-    <row r="20" spans="2:14" ht="57" customHeight="1">
+    <row r="20" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="87" t="s">
         <v>169</v>
       </c>
@@ -6197,7 +6502,7 @@
       <c r="M20" s="107"/>
       <c r="N20" s="114"/>
     </row>
-    <row r="21" spans="2:14" ht="57" customHeight="1" thickBot="1">
+    <row r="21" spans="2:14" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="89" t="s">
         <v>109</v>
       </c>
@@ -6232,7 +6537,7 @@
       <c r="M21" s="122"/>
       <c r="N21" s="97"/>
     </row>
-    <row r="22" spans="2:14" ht="14.25" thickTop="1"/>
+    <row r="22" spans="2:14" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="K2:N2"/>
@@ -6302,10 +6607,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.375" style="83" customWidth="1"/>
     <col min="2" max="2" width="9" style="83"/>
@@ -6316,7 +6621,7 @@
     <col min="10" max="16384" width="9" style="83"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="32.25" thickBot="1">
+    <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="110" t="s">
         <v>0</v>
       </c>
@@ -6327,7 +6632,7 @@
       <c r="D1" s="111"/>
       <c r="E1" s="109"/>
     </row>
-    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1">
+    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B2" s="135" t="s">
         <v>2</v>
       </c>
@@ -6347,7 +6652,7 @@
       <c r="H2" s="133"/>
       <c r="I2" s="134"/>
     </row>
-    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1">
+    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="136"/>
       <c r="C3" s="140"/>
       <c r="D3" s="140"/>
@@ -6365,7 +6670,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="57" customHeight="1">
+    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="84" t="s">
         <v>118</v>
       </c>
@@ -6383,7 +6688,7 @@
       <c r="H4" s="90"/>
       <c r="I4" s="94"/>
     </row>
-    <row r="5" spans="1:9" ht="57" customHeight="1">
+    <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="85" t="s">
         <v>124</v>
       </c>
@@ -6401,7 +6706,7 @@
       <c r="H5" s="91"/>
       <c r="I5" s="95"/>
     </row>
-    <row r="6" spans="1:9" ht="57" customHeight="1">
+    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="85" t="s">
         <v>125</v>
       </c>
@@ -6419,7 +6724,7 @@
       <c r="H6" s="91"/>
       <c r="I6" s="95"/>
     </row>
-    <row r="7" spans="1:9" ht="57" customHeight="1">
+    <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="85" t="s">
         <v>126</v>
       </c>
@@ -6437,7 +6742,7 @@
       <c r="H7" s="91"/>
       <c r="I7" s="95"/>
     </row>
-    <row r="8" spans="1:9" ht="57" customHeight="1">
+    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="86" t="s">
         <v>3</v>
       </c>
@@ -6455,7 +6760,7 @@
       <c r="H8" s="91"/>
       <c r="I8" s="95"/>
     </row>
-    <row r="9" spans="1:9" ht="27">
+    <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.3">
       <c r="B9" s="86" t="s">
         <v>46</v>
       </c>
@@ -6473,7 +6778,7 @@
       <c r="H9" s="91"/>
       <c r="I9" s="95"/>
     </row>
-    <row r="10" spans="1:9" ht="57" customHeight="1">
+    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="86" t="s">
         <v>56</v>
       </c>
@@ -6491,7 +6796,7 @@
       <c r="H10" s="91"/>
       <c r="I10" s="95"/>
     </row>
-    <row r="11" spans="1:9" ht="40.5">
+    <row r="11" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
       <c r="B11" s="85" t="s">
         <v>63</v>
       </c>
@@ -6509,7 +6814,7 @@
       <c r="H11" s="91"/>
       <c r="I11" s="95"/>
     </row>
-    <row r="12" spans="1:9" ht="57" customHeight="1">
+    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="86" t="s">
         <v>74</v>
       </c>
@@ -6527,7 +6832,7 @@
       <c r="H12" s="91"/>
       <c r="I12" s="95"/>
     </row>
-    <row r="13" spans="1:9" ht="347.25" customHeight="1">
+    <row r="13" spans="1:9" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="86" t="s">
         <v>119</v>
       </c>
@@ -6545,7 +6850,7 @@
       <c r="H13" s="91"/>
       <c r="I13" s="95"/>
     </row>
-    <row r="14" spans="1:9" ht="409.5">
+    <row r="14" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
       <c r="B14" s="87" t="s">
         <v>182</v>
       </c>
@@ -6563,7 +6868,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="57" customHeight="1">
+    <row r="15" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="87" t="s">
         <v>76</v>
       </c>
@@ -6581,7 +6886,7 @@
       <c r="H15" s="91"/>
       <c r="I15" s="95"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" s="86" t="s">
         <v>86</v>
       </c>
@@ -6599,7 +6904,7 @@
       <c r="H16" s="91"/>
       <c r="I16" s="95"/>
     </row>
-    <row r="17" spans="2:9" ht="57" customHeight="1">
+    <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="88" t="s">
         <v>142</v>
       </c>
@@ -6617,7 +6922,7 @@
       <c r="H17" s="91"/>
       <c r="I17" s="95"/>
     </row>
-    <row r="18" spans="2:9" ht="27">
+    <row r="18" spans="2:9" ht="27" x14ac:dyDescent="0.3">
       <c r="B18" s="88" t="s">
         <v>107</v>
       </c>
@@ -6635,7 +6940,7 @@
       <c r="H18" s="91"/>
       <c r="I18" s="95"/>
     </row>
-    <row r="19" spans="2:9" ht="57" customHeight="1">
+    <row r="19" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="87" t="s">
         <v>110</v>
       </c>
@@ -6653,7 +6958,7 @@
       <c r="H19" s="91"/>
       <c r="I19" s="95"/>
     </row>
-    <row r="20" spans="2:9" ht="57" customHeight="1">
+    <row r="20" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="87" t="s">
         <v>168</v>
       </c>
@@ -6671,7 +6976,7 @@
       <c r="H20" s="113"/>
       <c r="I20" s="114"/>
     </row>
-    <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1">
+    <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="89" t="s">
         <v>109</v>
       </c>
@@ -6689,7 +6994,7 @@
       <c r="H21" s="96"/>
       <c r="I21" s="97"/>
     </row>
-    <row r="22" spans="2:9" ht="14.25" thickTop="1"/>
+    <row r="22" spans="2:9" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:B3"/>
@@ -6703,10 +7008,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.375" style="83" customWidth="1"/>
     <col min="2" max="2" width="9" style="83"/>
@@ -6717,7 +7022,7 @@
     <col min="10" max="16384" width="9" style="83"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="32.25" thickBot="1">
+    <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="110" t="s">
         <v>0</v>
       </c>
@@ -6728,7 +7033,7 @@
       <c r="D1" s="111"/>
       <c r="E1" s="109"/>
     </row>
-    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1">
+    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B2" s="135" t="s">
         <v>2</v>
       </c>
@@ -6748,7 +7053,7 @@
       <c r="H2" s="133"/>
       <c r="I2" s="134"/>
     </row>
-    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1">
+    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="136"/>
       <c r="C3" s="140"/>
       <c r="D3" s="140"/>
@@ -6766,7 +7071,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="57" customHeight="1">
+    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="84" t="s">
         <v>118</v>
       </c>
@@ -6784,7 +7089,7 @@
       <c r="H4" s="90"/>
       <c r="I4" s="94"/>
     </row>
-    <row r="5" spans="1:9" ht="57" customHeight="1">
+    <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="85" t="s">
         <v>124</v>
       </c>
@@ -6802,7 +7107,7 @@
       <c r="H5" s="91"/>
       <c r="I5" s="95"/>
     </row>
-    <row r="6" spans="1:9" ht="57" customHeight="1">
+    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="85" t="s">
         <v>125</v>
       </c>
@@ -6820,7 +7125,7 @@
       <c r="H6" s="91"/>
       <c r="I6" s="95"/>
     </row>
-    <row r="7" spans="1:9" ht="57" customHeight="1">
+    <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="85" t="s">
         <v>126</v>
       </c>
@@ -6838,7 +7143,7 @@
       <c r="H7" s="91"/>
       <c r="I7" s="95"/>
     </row>
-    <row r="8" spans="1:9" ht="57" customHeight="1">
+    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="86" t="s">
         <v>3</v>
       </c>
@@ -6856,7 +7161,7 @@
       <c r="H8" s="91"/>
       <c r="I8" s="95"/>
     </row>
-    <row r="9" spans="1:9" ht="27">
+    <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.3">
       <c r="B9" s="86" t="s">
         <v>46</v>
       </c>
@@ -6874,7 +7179,7 @@
       <c r="H9" s="91"/>
       <c r="I9" s="95"/>
     </row>
-    <row r="10" spans="1:9" ht="57" customHeight="1">
+    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="86" t="s">
         <v>56</v>
       </c>
@@ -6892,7 +7197,7 @@
       <c r="H10" s="91"/>
       <c r="I10" s="95"/>
     </row>
-    <row r="11" spans="1:9" ht="40.5">
+    <row r="11" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
       <c r="B11" s="85" t="s">
         <v>63</v>
       </c>
@@ -6910,7 +7215,7 @@
       <c r="H11" s="91"/>
       <c r="I11" s="95"/>
     </row>
-    <row r="12" spans="1:9" ht="57" customHeight="1">
+    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="86" t="s">
         <v>74</v>
       </c>
@@ -6928,7 +7233,7 @@
       <c r="H12" s="91"/>
       <c r="I12" s="95"/>
     </row>
-    <row r="13" spans="1:9" ht="347.25" customHeight="1">
+    <row r="13" spans="1:9" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="86" t="s">
         <v>119</v>
       </c>
@@ -6946,7 +7251,7 @@
       <c r="H13" s="91"/>
       <c r="I13" s="95"/>
     </row>
-    <row r="14" spans="1:9" ht="337.5">
+    <row r="14" spans="1:9" ht="337.5" x14ac:dyDescent="0.3">
       <c r="B14" s="87" t="s">
         <v>182</v>
       </c>
@@ -6970,7 +7275,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="57" customHeight="1">
+    <row r="15" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="87" t="s">
         <v>76</v>
       </c>
@@ -6988,7 +7293,7 @@
       <c r="H15" s="91"/>
       <c r="I15" s="95"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" s="86" t="s">
         <v>86</v>
       </c>
@@ -7006,7 +7311,7 @@
       <c r="H16" s="91"/>
       <c r="I16" s="95"/>
     </row>
-    <row r="17" spans="2:9" ht="57" customHeight="1">
+    <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="88" t="s">
         <v>142</v>
       </c>
@@ -7024,7 +7329,7 @@
       <c r="H17" s="91"/>
       <c r="I17" s="95"/>
     </row>
-    <row r="18" spans="2:9" ht="27">
+    <row r="18" spans="2:9" ht="27" x14ac:dyDescent="0.3">
       <c r="B18" s="88" t="s">
         <v>107</v>
       </c>
@@ -7042,7 +7347,7 @@
       <c r="H18" s="91"/>
       <c r="I18" s="95"/>
     </row>
-    <row r="19" spans="2:9" ht="57" customHeight="1">
+    <row r="19" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="87" t="s">
         <v>110</v>
       </c>
@@ -7060,7 +7365,7 @@
       <c r="H19" s="91"/>
       <c r="I19" s="95"/>
     </row>
-    <row r="20" spans="2:9" ht="57" customHeight="1">
+    <row r="20" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="87" t="s">
         <v>168</v>
       </c>
@@ -7078,7 +7383,7 @@
       <c r="H20" s="113"/>
       <c r="I20" s="114"/>
     </row>
-    <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1">
+    <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="89" t="s">
         <v>109</v>
       </c>
@@ -7096,7 +7401,7 @@
       <c r="H21" s="96"/>
       <c r="I21" s="97"/>
     </row>
-    <row r="22" spans="2:9" ht="14.25" thickTop="1"/>
+    <row r="22" spans="2:9" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:B3"/>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685"/>
   </bookViews>
   <sheets>
     <sheet name="대일정" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="260">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1523,6 +1523,10 @@
   </si>
   <si>
     <t>오세영 수석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>97191NU000(LHD)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3130,6 +3134,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" xfId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3174,21 +3193,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" xfId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="3">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -3806,90 +3810,90 @@
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="126" t="s">
+      <c r="B2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="128" t="s">
+      <c r="C2" s="133" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="128" t="s">
+      <c r="D2" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="132">
+      <c r="E2" s="137">
         <v>23</v>
       </c>
-      <c r="F2" s="130"/>
-      <c r="G2" s="130"/>
-      <c r="H2" s="130"/>
-      <c r="I2" s="130"/>
-      <c r="J2" s="130"/>
-      <c r="K2" s="130"/>
-      <c r="L2" s="130"/>
-      <c r="M2" s="130"/>
-      <c r="N2" s="130"/>
-      <c r="O2" s="130"/>
-      <c r="P2" s="130"/>
-      <c r="Q2" s="130">
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="135"/>
+      <c r="O2" s="135"/>
+      <c r="P2" s="135"/>
+      <c r="Q2" s="135">
         <v>24</v>
       </c>
-      <c r="R2" s="130"/>
-      <c r="S2" s="130"/>
-      <c r="T2" s="130"/>
-      <c r="U2" s="130"/>
-      <c r="V2" s="130"/>
-      <c r="W2" s="130"/>
-      <c r="X2" s="130"/>
-      <c r="Y2" s="130"/>
-      <c r="Z2" s="130"/>
-      <c r="AA2" s="130"/>
-      <c r="AB2" s="130"/>
-      <c r="AC2" s="130">
+      <c r="R2" s="135"/>
+      <c r="S2" s="135"/>
+      <c r="T2" s="135"/>
+      <c r="U2" s="135"/>
+      <c r="V2" s="135"/>
+      <c r="W2" s="135"/>
+      <c r="X2" s="135"/>
+      <c r="Y2" s="135"/>
+      <c r="Z2" s="135"/>
+      <c r="AA2" s="135"/>
+      <c r="AB2" s="135"/>
+      <c r="AC2" s="135">
         <v>25</v>
       </c>
-      <c r="AD2" s="130"/>
-      <c r="AE2" s="130"/>
-      <c r="AF2" s="130"/>
-      <c r="AG2" s="130"/>
-      <c r="AH2" s="130"/>
-      <c r="AI2" s="130"/>
-      <c r="AJ2" s="130"/>
-      <c r="AK2" s="130"/>
-      <c r="AL2" s="130"/>
-      <c r="AM2" s="130"/>
-      <c r="AN2" s="130"/>
-      <c r="AO2" s="130">
+      <c r="AD2" s="135"/>
+      <c r="AE2" s="135"/>
+      <c r="AF2" s="135"/>
+      <c r="AG2" s="135"/>
+      <c r="AH2" s="135"/>
+      <c r="AI2" s="135"/>
+      <c r="AJ2" s="135"/>
+      <c r="AK2" s="135"/>
+      <c r="AL2" s="135"/>
+      <c r="AM2" s="135"/>
+      <c r="AN2" s="135"/>
+      <c r="AO2" s="135">
         <v>26</v>
       </c>
-      <c r="AP2" s="130"/>
-      <c r="AQ2" s="130"/>
-      <c r="AR2" s="130"/>
-      <c r="AS2" s="130"/>
-      <c r="AT2" s="130"/>
-      <c r="AU2" s="130"/>
-      <c r="AV2" s="130"/>
-      <c r="AW2" s="130"/>
-      <c r="AX2" s="130"/>
-      <c r="AY2" s="130"/>
-      <c r="AZ2" s="131"/>
-      <c r="BA2" s="130">
+      <c r="AP2" s="135"/>
+      <c r="AQ2" s="135"/>
+      <c r="AR2" s="135"/>
+      <c r="AS2" s="135"/>
+      <c r="AT2" s="135"/>
+      <c r="AU2" s="135"/>
+      <c r="AV2" s="135"/>
+      <c r="AW2" s="135"/>
+      <c r="AX2" s="135"/>
+      <c r="AY2" s="135"/>
+      <c r="AZ2" s="136"/>
+      <c r="BA2" s="135">
         <v>27</v>
       </c>
-      <c r="BB2" s="130"/>
-      <c r="BC2" s="130"/>
-      <c r="BD2" s="130"/>
-      <c r="BE2" s="130"/>
-      <c r="BF2" s="130"/>
-      <c r="BG2" s="130"/>
-      <c r="BH2" s="130"/>
-      <c r="BI2" s="130"/>
-      <c r="BJ2" s="130"/>
-      <c r="BK2" s="130"/>
-      <c r="BL2" s="131"/>
+      <c r="BB2" s="135"/>
+      <c r="BC2" s="135"/>
+      <c r="BD2" s="135"/>
+      <c r="BE2" s="135"/>
+      <c r="BF2" s="135"/>
+      <c r="BG2" s="135"/>
+      <c r="BH2" s="135"/>
+      <c r="BI2" s="135"/>
+      <c r="BJ2" s="135"/>
+      <c r="BK2" s="135"/>
+      <c r="BL2" s="136"/>
     </row>
     <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="127"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="129"/>
+      <c r="B3" s="132"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="134"/>
       <c r="E3" s="22">
         <v>1</v>
       </c>
@@ -5222,7 +5226,7 @@
         <v>86</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>106</v>
+        <v>259</v>
       </c>
       <c r="D18" s="33"/>
       <c r="E18" s="64"/>
@@ -5718,13 +5722,13 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="141" t="s">
+      <c r="A2" s="126" t="s">
         <v>241</v>
       </c>
       <c r="B2" t="s">
         <v>242</v>
       </c>
-      <c r="C2" s="142" t="s">
+      <c r="C2" s="127" t="s">
         <v>243</v>
       </c>
       <c r="D2" t="s">
@@ -5732,13 +5736,13 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="141" t="s">
+      <c r="A3" s="126" t="s">
         <v>245</v>
       </c>
       <c r="B3" t="s">
         <v>242</v>
       </c>
-      <c r="C3" s="143" t="s">
+      <c r="C3" s="128" t="s">
         <v>246</v>
       </c>
       <c r="D3" t="s">
@@ -5746,13 +5750,13 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="141" t="s">
+      <c r="A4" s="126" t="s">
         <v>247</v>
       </c>
       <c r="B4" t="s">
         <v>242</v>
       </c>
-      <c r="C4" s="143" t="s">
+      <c r="C4" s="128" t="s">
         <v>248</v>
       </c>
       <c r="D4" t="s">
@@ -5760,13 +5764,13 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="129" t="s">
         <v>249</v>
       </c>
       <c r="B5" t="s">
         <v>242</v>
       </c>
-      <c r="C5" s="143" t="s">
+      <c r="C5" s="128" t="s">
         <v>250</v>
       </c>
       <c r="D5" t="s">
@@ -5774,13 +5778,13 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="142" t="s">
+      <c r="A6" s="127" t="s">
         <v>251</v>
       </c>
       <c r="B6" t="s">
         <v>244</v>
       </c>
-      <c r="C6" s="145" t="s">
+      <c r="C6" s="130" t="s">
         <v>252</v>
       </c>
       <c r="D6" t="s">
@@ -5788,13 +5792,13 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="142" t="s">
+      <c r="A7" s="127" t="s">
         <v>253</v>
       </c>
       <c r="B7" t="s">
         <v>244</v>
       </c>
-      <c r="C7" s="145" t="s">
+      <c r="C7" s="130" t="s">
         <v>254</v>
       </c>
       <c r="D7" t="s">
@@ -5802,7 +5806,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C8" s="141" t="s">
+      <c r="C8" s="126" t="s">
         <v>255</v>
       </c>
       <c r="D8" t="s">
@@ -5810,7 +5814,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C9" s="141" t="s">
+      <c r="C9" s="126" t="s">
         <v>256</v>
       </c>
       <c r="D9" t="s">
@@ -5818,7 +5822,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C10" s="145" t="s">
+      <c r="C10" s="130" t="s">
         <v>257</v>
       </c>
       <c r="D10" t="s">
@@ -5858,39 +5862,39 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="135" t="s">
+      <c r="B2" s="140" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="139" t="s">
+      <c r="C2" s="144" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="139" t="s">
+      <c r="D2" s="144" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="137" t="s">
+      <c r="E2" s="142" t="s">
         <v>127</v>
       </c>
       <c r="F2" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="133" t="s">
+      <c r="G2" s="138" t="s">
         <v>114</v>
       </c>
-      <c r="H2" s="133"/>
-      <c r="I2" s="133"/>
-      <c r="J2" s="134"/>
-      <c r="K2" s="133" t="s">
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="139"/>
+      <c r="K2" s="138" t="s">
         <v>183</v>
       </c>
-      <c r="L2" s="133"/>
-      <c r="M2" s="133"/>
-      <c r="N2" s="134"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="139"/>
     </row>
     <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="136"/>
-      <c r="C3" s="140"/>
-      <c r="D3" s="140"/>
-      <c r="E3" s="138"/>
+      <c r="B3" s="141"/>
+      <c r="C3" s="145"/>
+      <c r="D3" s="145"/>
+      <c r="E3" s="143"/>
       <c r="F3" s="99" t="s">
         <v>112</v>
       </c>
@@ -6633,30 +6637,30 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="135" t="s">
+      <c r="B2" s="140" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="139" t="s">
+      <c r="C2" s="144" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="139" t="s">
+      <c r="D2" s="144" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="137" t="s">
+      <c r="E2" s="142" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="133" t="s">
+      <c r="F2" s="138" t="s">
         <v>183</v>
       </c>
-      <c r="G2" s="133"/>
-      <c r="H2" s="133"/>
-      <c r="I2" s="134"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="139"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="136"/>
-      <c r="C3" s="140"/>
-      <c r="D3" s="140"/>
-      <c r="E3" s="138"/>
+      <c r="B3" s="141"/>
+      <c r="C3" s="145"/>
+      <c r="D3" s="145"/>
+      <c r="E3" s="143"/>
       <c r="F3" s="99" t="s">
         <v>115</v>
       </c>
@@ -7034,30 +7038,30 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="135" t="s">
+      <c r="B2" s="140" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="139" t="s">
+      <c r="C2" s="144" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="139" t="s">
+      <c r="D2" s="144" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="137" t="s">
+      <c r="E2" s="142" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="133" t="s">
+      <c r="F2" s="138" t="s">
         <v>228</v>
       </c>
-      <c r="G2" s="133"/>
-      <c r="H2" s="133"/>
-      <c r="I2" s="134"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="139"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="136"/>
-      <c r="C3" s="140"/>
-      <c r="D3" s="140"/>
-      <c r="E3" s="138"/>
+      <c r="B3" s="141"/>
+      <c r="C3" s="145"/>
+      <c r="D3" s="145"/>
+      <c r="E3" s="143"/>
       <c r="F3" s="99" t="s">
         <v>115</v>
       </c>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="대일정" sheetId="1" r:id="rId1"/>
@@ -17,6 +17,7 @@
     <sheet name="2025.5" sheetId="2" r:id="rId3"/>
     <sheet name="2025.6" sheetId="3" r:id="rId4"/>
     <sheet name="2025.7" sheetId="4" r:id="rId5"/>
+    <sheet name="2025.10" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="285">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1529,6 +1530,212 @@
     <t>97191NU000(LHD)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>10월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5주차</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4주차</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오세영
+임제훈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오세영
+임제훈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오세영
+임제훈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오세영
+임제훈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오세영
+임제훈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- SWE.3 SDDS 후속 작업 (진행률 : 90%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 온도 정합성 테스트 (10/20)
+- 제어기 선행품질 검증 현황 작성
+- 제어기 선행품질 검증 현황 관련 기아 오토랜드 방문 (10/23)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- LHD R로직 튜닝
+- RHD R로직 튜닝 (HVAC 미보유, 보류)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- ESIR 계획서 등록
+- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신
+- Core Temp 튜닝 결과 확인
+- 최신 승인도 확인
+- R로직 튜닝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>최신 승인도 확인 (10/16)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">[임제훈 사원]
+- </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>양산 중 (25/07/15)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RHD P1 (진행 중)
+RHD P2 (26/02/01)
+LHD Proto (진행 중)
+LHD MCAR (25/11/15)
+LHD P1 (26/02/15)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P1 (진행 중)
+P2 (26/03/30)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P1 (진행 중)
+LP2 (26/04/15)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Proto (진행 중)
+MCAR (확인 필요)
+P1 (26/02/15)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SU2i CARRY OVER
+Proto (25/10/15)
+P1 (06/05/15)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- AY 회의 진행 (25/10/20)
+- LHD ESIR
+- R로직 튜닝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- AY 회의 진행 (25/10/20)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 이슈 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SU2i 고품 접수 (25/10/14)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : 원인 - SU2i 인도 생산 라인에서 EOL 95% Duty로 측정 중, Fail 발생.
+            Timerout Fault 발생으로 인해 고품 접수
+    분석 - HW 신지훈 전임, SW 임제훈 사원
+    결과 - SW 확인 결과, Timeout Fault 발생하지 않음, HALT State 발생
+            과전류 PIN Scope 측정 결과 과전류 발생
+            → 이후 진행 HW 신지훈 전임</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AY 회의 진행 (25/10/13)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : HVAC 4대 수령, 2대는 안받아도 된다고 하여 안건 종료
+    ESIR 내부 일정 9월 30일 → 10월 말 변경, 고객사 공식 일정 아직 없음</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1537,7 +1744,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1667,8 +1874,17 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1725,8 +1941,14 @@
         <fgColor theme="8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="73">
+  <borders count="78">
     <border>
       <left/>
       <right/>
@@ -2734,6 +2956,69 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2755,7 +3040,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="158">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3193,6 +3478,42 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -7417,4 +7738,447 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.375" style="83" customWidth="1"/>
+    <col min="2" max="2" width="9" style="83"/>
+    <col min="3" max="4" width="14.75" style="83" customWidth="1"/>
+    <col min="5" max="5" width="43" style="83" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="83" customWidth="1"/>
+    <col min="7" max="10" width="62.125" style="83" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="83"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="111" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="109"/>
+    </row>
+    <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="140" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="144" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2" s="144" t="s">
+        <v>178</v>
+      </c>
+      <c r="E2" s="142" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2" s="138" t="s">
+        <v>260</v>
+      </c>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="146"/>
+      <c r="J2" s="139"/>
+    </row>
+    <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="141"/>
+      <c r="C3" s="145"/>
+      <c r="D3" s="145"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="99" t="s">
+        <v>115</v>
+      </c>
+      <c r="G3" s="99" t="s">
+        <v>116</v>
+      </c>
+      <c r="H3" s="99" t="s">
+        <v>117</v>
+      </c>
+      <c r="I3" s="99" t="s">
+        <v>262</v>
+      </c>
+      <c r="J3" s="100" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="84" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="118" t="s">
+        <v>176</v>
+      </c>
+      <c r="D4" s="118" t="s">
+        <v>179</v>
+      </c>
+      <c r="E4" s="92" t="s">
+        <v>153</v>
+      </c>
+      <c r="F4" s="116"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="94"/>
+    </row>
+    <row r="5" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="85" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="119" t="s">
+        <v>176</v>
+      </c>
+      <c r="D5" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E5" s="93" t="s">
+        <v>154</v>
+      </c>
+      <c r="F5" s="116"/>
+      <c r="G5" s="107"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="148"/>
+      <c r="J5" s="95"/>
+    </row>
+    <row r="6" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="85" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" s="119" t="s">
+        <v>176</v>
+      </c>
+      <c r="D6" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E6" s="93" t="s">
+        <v>155</v>
+      </c>
+      <c r="F6" s="116"/>
+      <c r="G6" s="107"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="148"/>
+      <c r="J6" s="95"/>
+    </row>
+    <row r="7" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="85" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="119" t="s">
+        <v>176</v>
+      </c>
+      <c r="D7" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E7" s="93" t="s">
+        <v>156</v>
+      </c>
+      <c r="F7" s="116"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="91"/>
+      <c r="I7" s="148"/>
+      <c r="J7" s="95"/>
+    </row>
+    <row r="8" spans="1:10" ht="108" x14ac:dyDescent="0.3">
+      <c r="B8" s="153" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="119" t="s">
+        <v>263</v>
+      </c>
+      <c r="D8" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E8" s="93" t="s">
+        <v>157</v>
+      </c>
+      <c r="F8" s="116"/>
+      <c r="G8" s="107"/>
+      <c r="H8" s="156" t="s">
+        <v>283</v>
+      </c>
+      <c r="I8" s="148"/>
+      <c r="J8" s="95"/>
+    </row>
+    <row r="9" spans="1:10" ht="27" x14ac:dyDescent="0.3">
+      <c r="B9" s="153" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="119" t="s">
+        <v>264</v>
+      </c>
+      <c r="D9" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E9" s="102" t="s">
+        <v>274</v>
+      </c>
+      <c r="F9" s="116"/>
+      <c r="G9" s="107"/>
+      <c r="H9" s="106" t="s">
+        <v>282</v>
+      </c>
+      <c r="I9" s="148"/>
+      <c r="J9" s="95"/>
+    </row>
+    <row r="10" spans="1:10" ht="67.5" x14ac:dyDescent="0.3">
+      <c r="B10" s="153" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="119" t="s">
+        <v>265</v>
+      </c>
+      <c r="D10" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E10" s="102" t="s">
+        <v>275</v>
+      </c>
+      <c r="F10" s="116"/>
+      <c r="G10" s="107"/>
+      <c r="H10" s="156" t="s">
+        <v>284</v>
+      </c>
+      <c r="I10" s="150" t="s">
+        <v>280</v>
+      </c>
+      <c r="J10" s="157" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="54" x14ac:dyDescent="0.3">
+      <c r="B11" s="155" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="119" t="s">
+        <v>263</v>
+      </c>
+      <c r="D11" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E11" s="102" t="s">
+        <v>276</v>
+      </c>
+      <c r="F11" s="116"/>
+      <c r="G11" s="107"/>
+      <c r="H11" s="91"/>
+      <c r="I11" s="150" t="s">
+        <v>269</v>
+      </c>
+      <c r="J11" s="95"/>
+    </row>
+    <row r="12" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="153" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="119" t="s">
+        <v>180</v>
+      </c>
+      <c r="D12" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E12" s="102" t="s">
+        <v>277</v>
+      </c>
+      <c r="F12" s="116"/>
+      <c r="G12" s="107"/>
+      <c r="H12" s="91"/>
+      <c r="I12" s="150" t="s">
+        <v>270</v>
+      </c>
+      <c r="J12" s="95"/>
+    </row>
+    <row r="13" spans="1:10" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="86" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" s="119" t="s">
+        <v>176</v>
+      </c>
+      <c r="D13" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E13" s="102" t="s">
+        <v>162</v>
+      </c>
+      <c r="F13" s="116"/>
+      <c r="G13" s="107"/>
+      <c r="H13" s="91"/>
+      <c r="I13" s="148"/>
+      <c r="J13" s="95"/>
+    </row>
+    <row r="14" spans="1:10" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="B14" s="87" t="s">
+        <v>182</v>
+      </c>
+      <c r="C14" s="119" t="s">
+        <v>180</v>
+      </c>
+      <c r="D14" s="119" t="s">
+        <v>181</v>
+      </c>
+      <c r="E14" s="102"/>
+      <c r="F14" s="125"/>
+      <c r="G14" s="125"/>
+      <c r="H14" s="125"/>
+      <c r="I14" s="125" t="s">
+        <v>268</v>
+      </c>
+      <c r="J14" s="95"/>
+    </row>
+    <row r="15" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="87" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="119" t="s">
+        <v>176</v>
+      </c>
+      <c r="D15" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E15" s="102" t="s">
+        <v>163</v>
+      </c>
+      <c r="F15" s="116"/>
+      <c r="G15" s="107"/>
+      <c r="H15" s="91"/>
+      <c r="I15" s="148"/>
+      <c r="J15" s="95"/>
+    </row>
+    <row r="16" spans="1:10" ht="81" x14ac:dyDescent="0.3">
+      <c r="B16" s="153" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="119" t="s">
+        <v>266</v>
+      </c>
+      <c r="D16" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E16" s="102" t="s">
+        <v>278</v>
+      </c>
+      <c r="F16" s="116"/>
+      <c r="G16" s="107"/>
+      <c r="H16" s="91"/>
+      <c r="I16" s="150" t="s">
+        <v>271</v>
+      </c>
+      <c r="J16" s="95"/>
+    </row>
+    <row r="17" spans="2:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="154" t="s">
+        <v>142</v>
+      </c>
+      <c r="C17" s="119" t="s">
+        <v>180</v>
+      </c>
+      <c r="D17" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E17" s="93" t="s">
+        <v>106</v>
+      </c>
+      <c r="F17" s="116"/>
+      <c r="G17" s="91"/>
+      <c r="H17" s="91"/>
+      <c r="I17" s="148"/>
+      <c r="J17" s="95"/>
+    </row>
+    <row r="18" spans="2:10" ht="27" x14ac:dyDescent="0.3">
+      <c r="B18" s="88" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="119" t="s">
+        <v>176</v>
+      </c>
+      <c r="D18" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E18" s="102" t="s">
+        <v>165</v>
+      </c>
+      <c r="F18" s="116"/>
+      <c r="G18" s="107"/>
+      <c r="H18" s="91"/>
+      <c r="I18" s="148"/>
+      <c r="J18" s="95"/>
+    </row>
+    <row r="19" spans="2:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="87" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" s="119" t="s">
+        <v>176</v>
+      </c>
+      <c r="D19" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E19" s="93" t="s">
+        <v>140</v>
+      </c>
+      <c r="F19" s="116"/>
+      <c r="G19" s="106"/>
+      <c r="H19" s="91"/>
+      <c r="I19" s="148"/>
+      <c r="J19" s="95"/>
+    </row>
+    <row r="20" spans="2:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="152" t="s">
+        <v>168</v>
+      </c>
+      <c r="C20" s="119" t="s">
+        <v>267</v>
+      </c>
+      <c r="D20" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E20" s="115" t="s">
+        <v>279</v>
+      </c>
+      <c r="F20" s="116"/>
+      <c r="G20" s="112"/>
+      <c r="H20" s="151" t="s">
+        <v>272</v>
+      </c>
+      <c r="I20" s="151" t="s">
+        <v>273</v>
+      </c>
+      <c r="J20" s="114"/>
+    </row>
+    <row r="21" spans="2:10" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="89" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="120" t="s">
+        <v>176</v>
+      </c>
+      <c r="D21" s="120" t="s">
+        <v>179</v>
+      </c>
+      <c r="E21" s="105" t="s">
+        <v>141</v>
+      </c>
+      <c r="F21" s="117"/>
+      <c r="G21" s="108"/>
+      <c r="H21" s="96"/>
+      <c r="I21" s="149"/>
+      <c r="J21" s="97"/>
+    </row>
+    <row r="22" spans="2:10" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:J2"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -1570,13 +1570,6 @@
   <si>
     <t>[임제훈 사원]
 - SWE.3 SDDS 후속 작업 (진행률 : 90%)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- 온도 정합성 테스트 (10/20)
-- 제어기 선행품질 검증 현황 작성
-- 제어기 선행품질 검증 현황 관련 기아 오토랜드 방문 (10/23)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1734,6 +1727,14 @@
   : HVAC 4대 수령, 2대는 안받아도 된다고 하여 안건 종료
     ESIR 내부 일정 9월 30일 → 10월 말 변경, 고객사 공식 일정 아직 없음</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 온도 정합성 테스트 (10/20)
+- 제어기 선행품질 검증 현황 작성
+- 제어기 선행품질 검증 현황 관련 기아 오토랜드 방문 (10/23)
+- 설계 변경 진행</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3434,6 +3435,39 @@
     <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3481,39 +3515,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -4131,90 +4132,90 @@
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="131" t="s">
+      <c r="B2" s="142" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="133" t="s">
+      <c r="C2" s="144" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="133" t="s">
+      <c r="D2" s="144" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="137">
+      <c r="E2" s="148">
         <v>23</v>
       </c>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="135"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="135"/>
-      <c r="N2" s="135"/>
-      <c r="O2" s="135"/>
-      <c r="P2" s="135"/>
-      <c r="Q2" s="135">
+      <c r="F2" s="146"/>
+      <c r="G2" s="146"/>
+      <c r="H2" s="146"/>
+      <c r="I2" s="146"/>
+      <c r="J2" s="146"/>
+      <c r="K2" s="146"/>
+      <c r="L2" s="146"/>
+      <c r="M2" s="146"/>
+      <c r="N2" s="146"/>
+      <c r="O2" s="146"/>
+      <c r="P2" s="146"/>
+      <c r="Q2" s="146">
         <v>24</v>
       </c>
-      <c r="R2" s="135"/>
-      <c r="S2" s="135"/>
-      <c r="T2" s="135"/>
-      <c r="U2" s="135"/>
-      <c r="V2" s="135"/>
-      <c r="W2" s="135"/>
-      <c r="X2" s="135"/>
-      <c r="Y2" s="135"/>
-      <c r="Z2" s="135"/>
-      <c r="AA2" s="135"/>
-      <c r="AB2" s="135"/>
-      <c r="AC2" s="135">
+      <c r="R2" s="146"/>
+      <c r="S2" s="146"/>
+      <c r="T2" s="146"/>
+      <c r="U2" s="146"/>
+      <c r="V2" s="146"/>
+      <c r="W2" s="146"/>
+      <c r="X2" s="146"/>
+      <c r="Y2" s="146"/>
+      <c r="Z2" s="146"/>
+      <c r="AA2" s="146"/>
+      <c r="AB2" s="146"/>
+      <c r="AC2" s="146">
         <v>25</v>
       </c>
-      <c r="AD2" s="135"/>
-      <c r="AE2" s="135"/>
-      <c r="AF2" s="135"/>
-      <c r="AG2" s="135"/>
-      <c r="AH2" s="135"/>
-      <c r="AI2" s="135"/>
-      <c r="AJ2" s="135"/>
-      <c r="AK2" s="135"/>
-      <c r="AL2" s="135"/>
-      <c r="AM2" s="135"/>
-      <c r="AN2" s="135"/>
-      <c r="AO2" s="135">
+      <c r="AD2" s="146"/>
+      <c r="AE2" s="146"/>
+      <c r="AF2" s="146"/>
+      <c r="AG2" s="146"/>
+      <c r="AH2" s="146"/>
+      <c r="AI2" s="146"/>
+      <c r="AJ2" s="146"/>
+      <c r="AK2" s="146"/>
+      <c r="AL2" s="146"/>
+      <c r="AM2" s="146"/>
+      <c r="AN2" s="146"/>
+      <c r="AO2" s="146">
         <v>26</v>
       </c>
-      <c r="AP2" s="135"/>
-      <c r="AQ2" s="135"/>
-      <c r="AR2" s="135"/>
-      <c r="AS2" s="135"/>
-      <c r="AT2" s="135"/>
-      <c r="AU2" s="135"/>
-      <c r="AV2" s="135"/>
-      <c r="AW2" s="135"/>
-      <c r="AX2" s="135"/>
-      <c r="AY2" s="135"/>
-      <c r="AZ2" s="136"/>
-      <c r="BA2" s="135">
+      <c r="AP2" s="146"/>
+      <c r="AQ2" s="146"/>
+      <c r="AR2" s="146"/>
+      <c r="AS2" s="146"/>
+      <c r="AT2" s="146"/>
+      <c r="AU2" s="146"/>
+      <c r="AV2" s="146"/>
+      <c r="AW2" s="146"/>
+      <c r="AX2" s="146"/>
+      <c r="AY2" s="146"/>
+      <c r="AZ2" s="147"/>
+      <c r="BA2" s="146">
         <v>27</v>
       </c>
-      <c r="BB2" s="135"/>
-      <c r="BC2" s="135"/>
-      <c r="BD2" s="135"/>
-      <c r="BE2" s="135"/>
-      <c r="BF2" s="135"/>
-      <c r="BG2" s="135"/>
-      <c r="BH2" s="135"/>
-      <c r="BI2" s="135"/>
-      <c r="BJ2" s="135"/>
-      <c r="BK2" s="135"/>
-      <c r="BL2" s="136"/>
+      <c r="BB2" s="146"/>
+      <c r="BC2" s="146"/>
+      <c r="BD2" s="146"/>
+      <c r="BE2" s="146"/>
+      <c r="BF2" s="146"/>
+      <c r="BG2" s="146"/>
+      <c r="BH2" s="146"/>
+      <c r="BI2" s="146"/>
+      <c r="BJ2" s="146"/>
+      <c r="BK2" s="146"/>
+      <c r="BL2" s="147"/>
     </row>
     <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="132"/>
-      <c r="C3" s="134"/>
-      <c r="D3" s="134"/>
+      <c r="B3" s="143"/>
+      <c r="C3" s="145"/>
+      <c r="D3" s="145"/>
       <c r="E3" s="22">
         <v>1</v>
       </c>
@@ -6183,39 +6184,39 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="140" t="s">
+      <c r="B2" s="151" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="144" t="s">
+      <c r="C2" s="155" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="144" t="s">
+      <c r="D2" s="155" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="142" t="s">
+      <c r="E2" s="153" t="s">
         <v>127</v>
       </c>
       <c r="F2" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="138" t="s">
+      <c r="G2" s="149" t="s">
         <v>114</v>
       </c>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="139"/>
-      <c r="K2" s="138" t="s">
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="150"/>
+      <c r="K2" s="149" t="s">
         <v>183</v>
       </c>
-      <c r="L2" s="138"/>
-      <c r="M2" s="138"/>
-      <c r="N2" s="139"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
+      <c r="N2" s="150"/>
     </row>
     <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="141"/>
-      <c r="C3" s="145"/>
-      <c r="D3" s="145"/>
-      <c r="E3" s="143"/>
+      <c r="B3" s="152"/>
+      <c r="C3" s="156"/>
+      <c r="D3" s="156"/>
+      <c r="E3" s="154"/>
       <c r="F3" s="99" t="s">
         <v>112</v>
       </c>
@@ -6958,30 +6959,30 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="140" t="s">
+      <c r="B2" s="151" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="144" t="s">
+      <c r="C2" s="155" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="144" t="s">
+      <c r="D2" s="155" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="142" t="s">
+      <c r="E2" s="153" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="138" t="s">
+      <c r="F2" s="149" t="s">
         <v>183</v>
       </c>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="139"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="150"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="141"/>
-      <c r="C3" s="145"/>
-      <c r="D3" s="145"/>
-      <c r="E3" s="143"/>
+      <c r="B3" s="152"/>
+      <c r="C3" s="156"/>
+      <c r="D3" s="156"/>
+      <c r="E3" s="154"/>
       <c r="F3" s="99" t="s">
         <v>115</v>
       </c>
@@ -7359,30 +7360,30 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="140" t="s">
+      <c r="B2" s="151" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="144" t="s">
+      <c r="C2" s="155" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="144" t="s">
+      <c r="D2" s="155" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="142" t="s">
+      <c r="E2" s="153" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="138" t="s">
+      <c r="F2" s="149" t="s">
         <v>228</v>
       </c>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="139"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="150"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="141"/>
-      <c r="C3" s="145"/>
-      <c r="D3" s="145"/>
-      <c r="E3" s="143"/>
+      <c r="B3" s="152"/>
+      <c r="C3" s="156"/>
+      <c r="D3" s="156"/>
+      <c r="E3" s="154"/>
       <c r="F3" s="99" t="s">
         <v>115</v>
       </c>
@@ -7766,31 +7767,31 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="140" t="s">
+      <c r="B2" s="151" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="144" t="s">
+      <c r="C2" s="155" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="144" t="s">
+      <c r="D2" s="155" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="142" t="s">
+      <c r="E2" s="153" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="138" t="s">
+      <c r="F2" s="149" t="s">
         <v>260</v>
       </c>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="146"/>
-      <c r="J2" s="139"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="157"/>
+      <c r="J2" s="150"/>
     </row>
     <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="141"/>
-      <c r="C3" s="145"/>
-      <c r="D3" s="145"/>
-      <c r="E3" s="143"/>
+      <c r="B3" s="152"/>
+      <c r="C3" s="156"/>
+      <c r="D3" s="156"/>
+      <c r="E3" s="154"/>
       <c r="F3" s="99" t="s">
         <v>115</v>
       </c>
@@ -7823,7 +7824,7 @@
       <c r="F4" s="116"/>
       <c r="G4" s="107"/>
       <c r="H4" s="90"/>
-      <c r="I4" s="147"/>
+      <c r="I4" s="131"/>
       <c r="J4" s="94"/>
     </row>
     <row r="5" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -7842,7 +7843,7 @@
       <c r="F5" s="116"/>
       <c r="G5" s="107"/>
       <c r="H5" s="91"/>
-      <c r="I5" s="148"/>
+      <c r="I5" s="132"/>
       <c r="J5" s="95"/>
     </row>
     <row r="6" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -7861,7 +7862,7 @@
       <c r="F6" s="116"/>
       <c r="G6" s="107"/>
       <c r="H6" s="91"/>
-      <c r="I6" s="148"/>
+      <c r="I6" s="132"/>
       <c r="J6" s="95"/>
     </row>
     <row r="7" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -7880,11 +7881,11 @@
       <c r="F7" s="116"/>
       <c r="G7" s="107"/>
       <c r="H7" s="91"/>
-      <c r="I7" s="148"/>
+      <c r="I7" s="132"/>
       <c r="J7" s="95"/>
     </row>
     <row r="8" spans="1:10" ht="108" x14ac:dyDescent="0.3">
-      <c r="B8" s="153" t="s">
+      <c r="B8" s="137" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="119" t="s">
@@ -7898,14 +7899,14 @@
       </c>
       <c r="F8" s="116"/>
       <c r="G8" s="107"/>
-      <c r="H8" s="156" t="s">
-        <v>283</v>
-      </c>
-      <c r="I8" s="148"/>
+      <c r="H8" s="140" t="s">
+        <v>282</v>
+      </c>
+      <c r="I8" s="132"/>
       <c r="J8" s="95"/>
     </row>
     <row r="9" spans="1:10" ht="27" x14ac:dyDescent="0.3">
-      <c r="B9" s="153" t="s">
+      <c r="B9" s="137" t="s">
         <v>46</v>
       </c>
       <c r="C9" s="119" t="s">
@@ -7915,18 +7916,18 @@
         <v>179</v>
       </c>
       <c r="E9" s="102" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F9" s="116"/>
       <c r="G9" s="107"/>
       <c r="H9" s="106" t="s">
-        <v>282</v>
-      </c>
-      <c r="I9" s="148"/>
+        <v>281</v>
+      </c>
+      <c r="I9" s="132"/>
       <c r="J9" s="95"/>
     </row>
     <row r="10" spans="1:10" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="153" t="s">
+      <c r="B10" s="137" t="s">
         <v>56</v>
       </c>
       <c r="C10" s="119" t="s">
@@ -7936,22 +7937,22 @@
         <v>179</v>
       </c>
       <c r="E10" s="102" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F10" s="116"/>
       <c r="G10" s="107"/>
-      <c r="H10" s="156" t="s">
-        <v>284</v>
-      </c>
-      <c r="I10" s="150" t="s">
+      <c r="H10" s="140" t="s">
+        <v>283</v>
+      </c>
+      <c r="I10" s="134" t="s">
+        <v>279</v>
+      </c>
+      <c r="J10" s="141" t="s">
         <v>280</v>
       </c>
-      <c r="J10" s="157" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="54" x14ac:dyDescent="0.3">
-      <c r="B11" s="155" t="s">
+    </row>
+    <row r="11" spans="1:10" ht="67.5" x14ac:dyDescent="0.3">
+      <c r="B11" s="139" t="s">
         <v>63</v>
       </c>
       <c r="C11" s="119" t="s">
@@ -7961,18 +7962,18 @@
         <v>179</v>
       </c>
       <c r="E11" s="102" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F11" s="116"/>
       <c r="G11" s="107"/>
       <c r="H11" s="91"/>
-      <c r="I11" s="150" t="s">
-        <v>269</v>
+      <c r="I11" s="134" t="s">
+        <v>284</v>
       </c>
       <c r="J11" s="95"/>
     </row>
     <row r="12" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="153" t="s">
+      <c r="B12" s="137" t="s">
         <v>74</v>
       </c>
       <c r="C12" s="119" t="s">
@@ -7982,13 +7983,13 @@
         <v>179</v>
       </c>
       <c r="E12" s="102" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F12" s="116"/>
       <c r="G12" s="107"/>
       <c r="H12" s="91"/>
-      <c r="I12" s="150" t="s">
-        <v>270</v>
+      <c r="I12" s="134" t="s">
+        <v>269</v>
       </c>
       <c r="J12" s="95"/>
     </row>
@@ -8008,7 +8009,7 @@
       <c r="F13" s="116"/>
       <c r="G13" s="107"/>
       <c r="H13" s="91"/>
-      <c r="I13" s="148"/>
+      <c r="I13" s="132"/>
       <c r="J13" s="95"/>
     </row>
     <row r="14" spans="1:10" ht="40.5" x14ac:dyDescent="0.3">
@@ -8046,11 +8047,11 @@
       <c r="F15" s="116"/>
       <c r="G15" s="107"/>
       <c r="H15" s="91"/>
-      <c r="I15" s="148"/>
+      <c r="I15" s="132"/>
       <c r="J15" s="95"/>
     </row>
     <row r="16" spans="1:10" ht="81" x14ac:dyDescent="0.3">
-      <c r="B16" s="153" t="s">
+      <c r="B16" s="137" t="s">
         <v>86</v>
       </c>
       <c r="C16" s="119" t="s">
@@ -8060,18 +8061,18 @@
         <v>179</v>
       </c>
       <c r="E16" s="102" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F16" s="116"/>
       <c r="G16" s="107"/>
       <c r="H16" s="91"/>
-      <c r="I16" s="150" t="s">
-        <v>271</v>
+      <c r="I16" s="134" t="s">
+        <v>270</v>
       </c>
       <c r="J16" s="95"/>
     </row>
     <row r="17" spans="2:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="154" t="s">
+      <c r="B17" s="138" t="s">
         <v>142</v>
       </c>
       <c r="C17" s="119" t="s">
@@ -8086,7 +8087,7 @@
       <c r="F17" s="116"/>
       <c r="G17" s="91"/>
       <c r="H17" s="91"/>
-      <c r="I17" s="148"/>
+      <c r="I17" s="132"/>
       <c r="J17" s="95"/>
     </row>
     <row r="18" spans="2:10" ht="27" x14ac:dyDescent="0.3">
@@ -8105,7 +8106,7 @@
       <c r="F18" s="116"/>
       <c r="G18" s="107"/>
       <c r="H18" s="91"/>
-      <c r="I18" s="148"/>
+      <c r="I18" s="132"/>
       <c r="J18" s="95"/>
     </row>
     <row r="19" spans="2:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -8124,11 +8125,11 @@
       <c r="F19" s="116"/>
       <c r="G19" s="106"/>
       <c r="H19" s="91"/>
-      <c r="I19" s="148"/>
+      <c r="I19" s="132"/>
       <c r="J19" s="95"/>
     </row>
     <row r="20" spans="2:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="152" t="s">
+      <c r="B20" s="136" t="s">
         <v>168</v>
       </c>
       <c r="C20" s="119" t="s">
@@ -8138,15 +8139,15 @@
         <v>179</v>
       </c>
       <c r="E20" s="115" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F20" s="116"/>
       <c r="G20" s="112"/>
-      <c r="H20" s="151" t="s">
+      <c r="H20" s="135" t="s">
+        <v>271</v>
+      </c>
+      <c r="I20" s="135" t="s">
         <v>272</v>
-      </c>
-      <c r="I20" s="151" t="s">
-        <v>273</v>
       </c>
       <c r="J20" s="114"/>
     </row>
@@ -8166,7 +8167,7 @@
       <c r="F21" s="117"/>
       <c r="G21" s="108"/>
       <c r="H21" s="96"/>
-      <c r="I21" s="149"/>
+      <c r="I21" s="133"/>
       <c r="J21" s="97"/>
     </row>
     <row r="22" spans="2:10" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -1637,12 +1637,6 @@
     <t>Proto (진행 중)
 MCAR (확인 필요)
 P1 (26/02/15)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SU2i CARRY OVER
-Proto (25/10/15)
-P1 (06/05/15)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1735,6 +1729,12 @@
 - 제어기 선행품질 검증 현황 작성
 - 제어기 선행품질 검증 현황 관련 기아 오토랜드 방문 (10/23)
 - 설계 변경 진행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SU2i CARRY OVER
+Proto (25/10/15)
+P1 (26/05/15)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7900,7 +7900,7 @@
       <c r="F8" s="116"/>
       <c r="G8" s="107"/>
       <c r="H8" s="140" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I8" s="132"/>
       <c r="J8" s="95"/>
@@ -7921,7 +7921,7 @@
       <c r="F9" s="116"/>
       <c r="G9" s="107"/>
       <c r="H9" s="106" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I9" s="132"/>
       <c r="J9" s="95"/>
@@ -7942,13 +7942,13 @@
       <c r="F10" s="116"/>
       <c r="G10" s="107"/>
       <c r="H10" s="140" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I10" s="134" t="s">
+        <v>278</v>
+      </c>
+      <c r="J10" s="141" t="s">
         <v>279</v>
-      </c>
-      <c r="J10" s="141" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="67.5" x14ac:dyDescent="0.3">
@@ -7968,7 +7968,7 @@
       <c r="G11" s="107"/>
       <c r="H11" s="91"/>
       <c r="I11" s="134" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J11" s="95"/>
     </row>
@@ -8139,7 +8139,7 @@
         <v>179</v>
       </c>
       <c r="E20" s="115" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="F20" s="116"/>
       <c r="G20" s="112"/>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -18,6 +18,7 @@
     <sheet name="2025.6" sheetId="3" r:id="rId4"/>
     <sheet name="2025.7" sheetId="4" r:id="rId5"/>
     <sheet name="2025.10" sheetId="6" r:id="rId6"/>
+    <sheet name="2025.11" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="302">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1535,59 +1536,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>5주차</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4주차</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오세영
-임제훈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오세영
-임제훈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오세영
-임제훈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오세영
-임제훈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오세영
-임제훈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- SWE.3 SDDS 후속 작업 (진행률 : 90%)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- LHD R로직 튜닝
-- RHD R로직 튜닝 (HVAC 미보유, 보류)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- ESIR 계획서 등록
-- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신
-- Core Temp 튜닝 결과 확인
-- 최신 승인도 확인
-- R로직 튜닝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">[임제훈 사원]
 - </t>
@@ -1607,11 +1555,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">[임제훈 사원]
-- </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>양산 중 (25/07/15)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1637,18 +1580,6 @@
     <t>Proto (진행 중)
 MCAR (확인 필요)
 P1 (26/02/15)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- AY 회의 진행 (25/10/20)
-- LHD ESIR
-- R로직 튜닝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- AY 회의 진행 (25/10/20)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1724,6 +1655,38 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>SU2i CARRY OVER
+Proto (25/10/15)
+P1 (26/05/15)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2주차 (10/10 ~ 10/15)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3주차 (10/16 ~ 10/22)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4주차 (10/23 ~ 10/29)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- AY 회의 진행 (25/10/20)
+- LHD ESIR
+- R로직 튜닝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- AY 회의 진행 (25/10/20)
+- LHD ESIR
+- R로직 튜닝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>[임제훈 사원]
 - 온도 정합성 테스트 (10/20)
 - 제어기 선행품질 검증 현황 작성
@@ -1732,9 +1695,130 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SU2i CARRY OVER
-Proto (25/10/15)
-P1 (26/05/15)</t>
+    <t>[임제훈 사원]
+- 온도 정합성 테스트 (10/20)
+- 제어기 선행품질 검증 현황 작성
+- 제어기 선행품질 검증 현황 관련 기아 오토랜드 방문 (10/23)
+- 설계 변경 진행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- LHD R로직 튜닝
+- RHD R로직 튜닝 (HVAC 미보유, 보류)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- LHD R로직 튜닝
+- RHD R로직 튜닝 (HVAC 미보유, 보류)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- SWE.3 SDDS 후속 작업 (진행률 : 90%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- SWE.3 SDDS 후속 작업 (진행률 : 90%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- ESIR 계획서 등록
+- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신
+- Core Temp 튜닝 결과 확인
+- 최신 승인도 확인
+- R로직 튜닝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">[임제훈 사원]
+- </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오세영
+조현진
+임제훈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조현진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조현진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>임제훈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>임제훈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>임제훈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>임제훈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>임제훈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QV</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1주차 (10/30 ~ 11/05)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1주차 (10/02)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2주차 (11/06 ~ 11/12)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3주차 (11/13 ~ 11/19)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4주차 (11/20 ~ 11/26)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- LHD ESIR
+- R로직 튜닝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- ESIR 계획서 등록 (~10/21)
+- Core Temp 튜닝 결과 확인 (~10/21)
+- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/24)
+- R로직 튜닝 (~10/24)
+- 최신 승인도 확인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>출도 (26/02/01)
+Proto (26/04/06)
+정확한 일정인지 확인 필요</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1885,7 +1969,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1948,8 +2032,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="78">
+  <borders count="80">
     <border>
       <left/>
       <right/>
@@ -2962,45 +3058,6 @@
         <color auto="1"/>
       </left>
       <right/>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
       <top style="hair">
         <color auto="1"/>
       </top>
@@ -3008,14 +3065,81 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="thick">
         <color auto="1"/>
       </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
-      <top style="hair">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
+      <top/>
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -3041,7 +3165,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3435,19 +3559,7 @@
     <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3456,9 +3568,6 @@
     <xf numFmtId="0" fontId="8" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3513,8 +3622,65 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -4132,90 +4298,90 @@
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="137" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="144" t="s">
+      <c r="C2" s="139" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="144" t="s">
+      <c r="D2" s="139" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="148">
+      <c r="E2" s="143">
         <v>23</v>
       </c>
-      <c r="F2" s="146"/>
-      <c r="G2" s="146"/>
-      <c r="H2" s="146"/>
-      <c r="I2" s="146"/>
-      <c r="J2" s="146"/>
-      <c r="K2" s="146"/>
-      <c r="L2" s="146"/>
-      <c r="M2" s="146"/>
-      <c r="N2" s="146"/>
-      <c r="O2" s="146"/>
-      <c r="P2" s="146"/>
-      <c r="Q2" s="146">
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
+      <c r="M2" s="141"/>
+      <c r="N2" s="141"/>
+      <c r="O2" s="141"/>
+      <c r="P2" s="141"/>
+      <c r="Q2" s="141">
         <v>24</v>
       </c>
-      <c r="R2" s="146"/>
-      <c r="S2" s="146"/>
-      <c r="T2" s="146"/>
-      <c r="U2" s="146"/>
-      <c r="V2" s="146"/>
-      <c r="W2" s="146"/>
-      <c r="X2" s="146"/>
-      <c r="Y2" s="146"/>
-      <c r="Z2" s="146"/>
-      <c r="AA2" s="146"/>
-      <c r="AB2" s="146"/>
-      <c r="AC2" s="146">
+      <c r="R2" s="141"/>
+      <c r="S2" s="141"/>
+      <c r="T2" s="141"/>
+      <c r="U2" s="141"/>
+      <c r="V2" s="141"/>
+      <c r="W2" s="141"/>
+      <c r="X2" s="141"/>
+      <c r="Y2" s="141"/>
+      <c r="Z2" s="141"/>
+      <c r="AA2" s="141"/>
+      <c r="AB2" s="141"/>
+      <c r="AC2" s="141">
         <v>25</v>
       </c>
-      <c r="AD2" s="146"/>
-      <c r="AE2" s="146"/>
-      <c r="AF2" s="146"/>
-      <c r="AG2" s="146"/>
-      <c r="AH2" s="146"/>
-      <c r="AI2" s="146"/>
-      <c r="AJ2" s="146"/>
-      <c r="AK2" s="146"/>
-      <c r="AL2" s="146"/>
-      <c r="AM2" s="146"/>
-      <c r="AN2" s="146"/>
-      <c r="AO2" s="146">
+      <c r="AD2" s="141"/>
+      <c r="AE2" s="141"/>
+      <c r="AF2" s="141"/>
+      <c r="AG2" s="141"/>
+      <c r="AH2" s="141"/>
+      <c r="AI2" s="141"/>
+      <c r="AJ2" s="141"/>
+      <c r="AK2" s="141"/>
+      <c r="AL2" s="141"/>
+      <c r="AM2" s="141"/>
+      <c r="AN2" s="141"/>
+      <c r="AO2" s="141">
         <v>26</v>
       </c>
-      <c r="AP2" s="146"/>
-      <c r="AQ2" s="146"/>
-      <c r="AR2" s="146"/>
-      <c r="AS2" s="146"/>
-      <c r="AT2" s="146"/>
-      <c r="AU2" s="146"/>
-      <c r="AV2" s="146"/>
-      <c r="AW2" s="146"/>
-      <c r="AX2" s="146"/>
-      <c r="AY2" s="146"/>
-      <c r="AZ2" s="147"/>
-      <c r="BA2" s="146">
+      <c r="AP2" s="141"/>
+      <c r="AQ2" s="141"/>
+      <c r="AR2" s="141"/>
+      <c r="AS2" s="141"/>
+      <c r="AT2" s="141"/>
+      <c r="AU2" s="141"/>
+      <c r="AV2" s="141"/>
+      <c r="AW2" s="141"/>
+      <c r="AX2" s="141"/>
+      <c r="AY2" s="141"/>
+      <c r="AZ2" s="142"/>
+      <c r="BA2" s="141">
         <v>27</v>
       </c>
-      <c r="BB2" s="146"/>
-      <c r="BC2" s="146"/>
-      <c r="BD2" s="146"/>
-      <c r="BE2" s="146"/>
-      <c r="BF2" s="146"/>
-      <c r="BG2" s="146"/>
-      <c r="BH2" s="146"/>
-      <c r="BI2" s="146"/>
-      <c r="BJ2" s="146"/>
-      <c r="BK2" s="146"/>
-      <c r="BL2" s="147"/>
+      <c r="BB2" s="141"/>
+      <c r="BC2" s="141"/>
+      <c r="BD2" s="141"/>
+      <c r="BE2" s="141"/>
+      <c r="BF2" s="141"/>
+      <c r="BG2" s="141"/>
+      <c r="BH2" s="141"/>
+      <c r="BI2" s="141"/>
+      <c r="BJ2" s="141"/>
+      <c r="BK2" s="141"/>
+      <c r="BL2" s="142"/>
     </row>
     <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="143"/>
-      <c r="C3" s="145"/>
-      <c r="D3" s="145"/>
+      <c r="B3" s="138"/>
+      <c r="C3" s="140"/>
+      <c r="D3" s="140"/>
       <c r="E3" s="22">
         <v>1</v>
       </c>
@@ -6184,39 +6350,39 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="151" t="s">
+      <c r="B2" s="146" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="155" t="s">
+      <c r="C2" s="150" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="155" t="s">
+      <c r="D2" s="150" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="153" t="s">
+      <c r="E2" s="148" t="s">
         <v>127</v>
       </c>
       <c r="F2" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="149" t="s">
+      <c r="G2" s="144" t="s">
         <v>114</v>
       </c>
-      <c r="H2" s="149"/>
-      <c r="I2" s="149"/>
-      <c r="J2" s="150"/>
-      <c r="K2" s="149" t="s">
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="145"/>
+      <c r="K2" s="144" t="s">
         <v>183</v>
       </c>
-      <c r="L2" s="149"/>
-      <c r="M2" s="149"/>
-      <c r="N2" s="150"/>
+      <c r="L2" s="144"/>
+      <c r="M2" s="144"/>
+      <c r="N2" s="145"/>
     </row>
     <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="152"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="154"/>
+      <c r="B3" s="147"/>
+      <c r="C3" s="151"/>
+      <c r="D3" s="151"/>
+      <c r="E3" s="149"/>
       <c r="F3" s="99" t="s">
         <v>112</v>
       </c>
@@ -6959,30 +7125,30 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="151" t="s">
+      <c r="B2" s="146" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="155" t="s">
+      <c r="C2" s="150" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="155" t="s">
+      <c r="D2" s="150" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="153" t="s">
+      <c r="E2" s="148" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="149" t="s">
+      <c r="F2" s="144" t="s">
         <v>183</v>
       </c>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
-      <c r="I2" s="150"/>
+      <c r="G2" s="144"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="145"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="152"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="154"/>
+      <c r="B3" s="147"/>
+      <c r="C3" s="151"/>
+      <c r="D3" s="151"/>
+      <c r="E3" s="149"/>
       <c r="F3" s="99" t="s">
         <v>115</v>
       </c>
@@ -7360,30 +7526,30 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="151" t="s">
+      <c r="B2" s="146" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="155" t="s">
+      <c r="C2" s="150" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="155" t="s">
+      <c r="D2" s="150" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="153" t="s">
+      <c r="E2" s="148" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="149" t="s">
+      <c r="F2" s="144" t="s">
         <v>228</v>
       </c>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
-      <c r="I2" s="150"/>
+      <c r="G2" s="144"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="145"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="152"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="154"/>
+      <c r="B3" s="147"/>
+      <c r="C3" s="151"/>
+      <c r="D3" s="151"/>
+      <c r="E3" s="149"/>
       <c r="F3" s="99" t="s">
         <v>115</v>
       </c>
@@ -7743,7 +7909,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.375" style="83" customWidth="1"/>
@@ -7751,11 +7917,11 @@
     <col min="3" max="4" width="14.75" style="83" customWidth="1"/>
     <col min="5" max="5" width="43" style="83" customWidth="1"/>
     <col min="6" max="6" width="61.875" style="83" customWidth="1"/>
-    <col min="7" max="10" width="62.125" style="83" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="83"/>
+    <col min="7" max="9" width="62.125" style="83" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="83"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="110" t="s">
         <v>0</v>
       </c>
@@ -7766,51 +7932,47 @@
       <c r="D1" s="111"/>
       <c r="E1" s="109"/>
     </row>
-    <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="151" t="s">
+    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="146" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="155" t="s">
+      <c r="C2" s="150" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="155" t="s">
+      <c r="D2" s="150" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="153" t="s">
+      <c r="E2" s="148" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="149" t="s">
+      <c r="F2" s="144" t="s">
         <v>260</v>
       </c>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="150"/>
-    </row>
-    <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="152"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="154"/>
+      <c r="G2" s="144"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="145"/>
+    </row>
+    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="147"/>
+      <c r="C3" s="151"/>
+      <c r="D3" s="151"/>
+      <c r="E3" s="149"/>
       <c r="F3" s="99" t="s">
-        <v>115</v>
+        <v>295</v>
       </c>
       <c r="G3" s="99" t="s">
-        <v>116</v>
+        <v>271</v>
       </c>
       <c r="H3" s="99" t="s">
-        <v>117</v>
-      </c>
-      <c r="I3" s="99" t="s">
-        <v>262</v>
-      </c>
-      <c r="J3" s="100" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="84" t="s">
-        <v>118</v>
+        <v>272</v>
+      </c>
+      <c r="I3" s="100" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="168" t="s">
+        <v>109</v>
       </c>
       <c r="C4" s="118" t="s">
         <v>176</v>
@@ -7818,366 +7980,737 @@
       <c r="D4" s="118" t="s">
         <v>179</v>
       </c>
-      <c r="E4" s="92" t="s">
-        <v>153</v>
-      </c>
-      <c r="F4" s="116"/>
-      <c r="G4" s="107"/>
+      <c r="E4" s="157" t="s">
+        <v>141</v>
+      </c>
+      <c r="F4" s="158"/>
+      <c r="G4" s="159"/>
       <c r="H4" s="90"/>
-      <c r="I4" s="131"/>
-      <c r="J4" s="94"/>
-    </row>
-    <row r="5" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="85" t="s">
-        <v>124</v>
+      <c r="I4" s="94"/>
+    </row>
+    <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="171" t="s">
+        <v>182</v>
       </c>
       <c r="C5" s="119" t="s">
-        <v>176</v>
+        <v>284</v>
       </c>
       <c r="D5" s="119" t="s">
-        <v>179</v>
-      </c>
-      <c r="E5" s="93" t="s">
-        <v>154</v>
+        <v>181</v>
+      </c>
+      <c r="E5" s="102" t="s">
+        <v>162</v>
       </c>
       <c r="F5" s="116"/>
       <c r="G5" s="107"/>
-      <c r="H5" s="91"/>
-      <c r="I5" s="132"/>
-      <c r="J5" s="95"/>
-    </row>
-    <row r="6" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="85" t="s">
-        <v>125</v>
+      <c r="H5" s="125" t="s">
+        <v>281</v>
+      </c>
+      <c r="I5" s="152" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="169" t="s">
+        <v>292</v>
       </c>
       <c r="C6" s="119" t="s">
-        <v>176</v>
+        <v>285</v>
       </c>
       <c r="D6" s="119" t="s">
         <v>179</v>
       </c>
-      <c r="E6" s="93" t="s">
-        <v>155</v>
-      </c>
-      <c r="F6" s="116"/>
-      <c r="G6" s="107"/>
-      <c r="H6" s="91"/>
-      <c r="I6" s="132"/>
-      <c r="J6" s="95"/>
-    </row>
-    <row r="7" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="85" t="s">
-        <v>126</v>
+      <c r="E6" s="102" t="s">
+        <v>162</v>
+      </c>
+      <c r="F6" s="125"/>
+      <c r="G6" s="125"/>
+      <c r="H6" s="125"/>
+      <c r="I6" s="152"/>
+    </row>
+    <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="169" t="s">
+        <v>76</v>
       </c>
       <c r="C7" s="119" t="s">
-        <v>176</v>
+        <v>286</v>
       </c>
       <c r="D7" s="119" t="s">
         <v>179</v>
       </c>
-      <c r="E7" s="93" t="s">
-        <v>156</v>
+      <c r="E7" s="102" t="s">
+        <v>163</v>
       </c>
       <c r="F7" s="116"/>
       <c r="G7" s="107"/>
       <c r="H7" s="91"/>
-      <c r="I7" s="132"/>
-      <c r="J7" s="95"/>
-    </row>
-    <row r="8" spans="1:10" ht="108" x14ac:dyDescent="0.3">
-      <c r="B8" s="137" t="s">
-        <v>3</v>
+      <c r="I7" s="95"/>
+    </row>
+    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="169" t="s">
+        <v>110</v>
       </c>
       <c r="C8" s="119" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="D8" s="119" t="s">
         <v>179</v>
       </c>
       <c r="E8" s="93" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="F8" s="116"/>
-      <c r="G8" s="107"/>
-      <c r="H8" s="140" t="s">
-        <v>281</v>
-      </c>
-      <c r="I8" s="132"/>
-      <c r="J8" s="95"/>
-    </row>
-    <row r="9" spans="1:10" ht="27" x14ac:dyDescent="0.3">
-      <c r="B9" s="137" t="s">
-        <v>46</v>
+      <c r="G8" s="106"/>
+      <c r="H8" s="91"/>
+      <c r="I8" s="95"/>
+    </row>
+    <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="170" t="s">
+        <v>118</v>
       </c>
       <c r="C9" s="119" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="D9" s="119" t="s">
         <v>179</v>
       </c>
-      <c r="E9" s="102" t="s">
-        <v>273</v>
+      <c r="E9" s="93" t="s">
+        <v>153</v>
       </c>
       <c r="F9" s="116"/>
       <c r="G9" s="107"/>
-      <c r="H9" s="106" t="s">
-        <v>280</v>
-      </c>
-      <c r="I9" s="132"/>
-      <c r="J9" s="95"/>
-    </row>
-    <row r="10" spans="1:10" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="137" t="s">
-        <v>56</v>
+      <c r="H9" s="155"/>
+      <c r="I9" s="95"/>
+    </row>
+    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="170" t="s">
+        <v>124</v>
       </c>
       <c r="C10" s="119" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="D10" s="119" t="s">
         <v>179</v>
       </c>
-      <c r="E10" s="102" t="s">
-        <v>274</v>
+      <c r="E10" s="93" t="s">
+        <v>154</v>
       </c>
       <c r="F10" s="116"/>
       <c r="G10" s="107"/>
-      <c r="H10" s="140" t="s">
-        <v>282</v>
-      </c>
-      <c r="I10" s="134" t="s">
-        <v>278</v>
-      </c>
-      <c r="J10" s="141" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="B11" s="139" t="s">
-        <v>63</v>
+      <c r="H10" s="155"/>
+      <c r="I10" s="95"/>
+    </row>
+    <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="170" t="s">
+        <v>125</v>
       </c>
       <c r="C11" s="119" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="D11" s="119" t="s">
         <v>179</v>
       </c>
-      <c r="E11" s="102" t="s">
-        <v>275</v>
+      <c r="E11" s="93" t="s">
+        <v>155</v>
       </c>
       <c r="F11" s="116"/>
       <c r="G11" s="107"/>
-      <c r="H11" s="91"/>
-      <c r="I11" s="134" t="s">
-        <v>283</v>
-      </c>
-      <c r="J11" s="95"/>
-    </row>
-    <row r="12" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="137" t="s">
-        <v>74</v>
+      <c r="H11" s="155"/>
+      <c r="I11" s="95"/>
+    </row>
+    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="170" t="s">
+        <v>126</v>
       </c>
       <c r="C12" s="119" t="s">
-        <v>180</v>
+        <v>285</v>
       </c>
       <c r="D12" s="119" t="s">
         <v>179</v>
       </c>
-      <c r="E12" s="102" t="s">
-        <v>276</v>
+      <c r="E12" s="93" t="s">
+        <v>156</v>
       </c>
       <c r="F12" s="116"/>
       <c r="G12" s="107"/>
-      <c r="H12" s="91"/>
-      <c r="I12" s="134" t="s">
-        <v>269</v>
-      </c>
-      <c r="J12" s="95"/>
-    </row>
-    <row r="13" spans="1:10" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="86" t="s">
-        <v>119</v>
+      <c r="H12" s="155"/>
+      <c r="I12" s="95"/>
+    </row>
+    <row r="13" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
+      <c r="B13" s="134" t="s">
+        <v>63</v>
       </c>
       <c r="C13" s="119" t="s">
-        <v>176</v>
+        <v>287</v>
       </c>
       <c r="D13" s="119" t="s">
         <v>179</v>
       </c>
       <c r="E13" s="102" t="s">
-        <v>162</v>
+        <v>264</v>
       </c>
       <c r="F13" s="116"/>
       <c r="G13" s="107"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="132"/>
-      <c r="J13" s="95"/>
-    </row>
-    <row r="14" spans="1:10" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="87" t="s">
-        <v>182</v>
+      <c r="H13" s="135" t="s">
+        <v>277</v>
+      </c>
+      <c r="I13" s="136"/>
+    </row>
+    <row r="14" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="133" t="s">
+        <v>74</v>
       </c>
       <c r="C14" s="119" t="s">
-        <v>180</v>
+        <v>287</v>
       </c>
       <c r="D14" s="119" t="s">
-        <v>181</v>
-      </c>
-      <c r="E14" s="102"/>
-      <c r="F14" s="125"/>
-      <c r="G14" s="125"/>
-      <c r="H14" s="125"/>
-      <c r="I14" s="125" t="s">
-        <v>268</v>
-      </c>
-      <c r="J14" s="95"/>
-    </row>
-    <row r="15" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="87" t="s">
-        <v>76</v>
+        <v>179</v>
+      </c>
+      <c r="E14" s="102" t="s">
+        <v>265</v>
+      </c>
+      <c r="F14" s="116"/>
+      <c r="G14" s="107"/>
+      <c r="H14" s="135" t="s">
+        <v>279</v>
+      </c>
+      <c r="I14" s="136"/>
+    </row>
+    <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
+      <c r="B15" s="133" t="s">
+        <v>56</v>
       </c>
       <c r="C15" s="119" t="s">
-        <v>176</v>
+        <v>288</v>
       </c>
       <c r="D15" s="119" t="s">
         <v>179</v>
       </c>
       <c r="E15" s="102" t="s">
-        <v>163</v>
+        <v>263</v>
       </c>
       <c r="F15" s="116"/>
-      <c r="G15" s="107"/>
-      <c r="H15" s="91"/>
-      <c r="I15" s="132"/>
-      <c r="J15" s="95"/>
-    </row>
-    <row r="16" spans="1:10" ht="81" x14ac:dyDescent="0.3">
-      <c r="B16" s="137" t="s">
+      <c r="G15" s="135" t="s">
+        <v>269</v>
+      </c>
+      <c r="H15" s="154" t="s">
+        <v>299</v>
+      </c>
+      <c r="I15" s="136"/>
+    </row>
+    <row r="16" spans="1:9" ht="81" x14ac:dyDescent="0.3">
+      <c r="B16" s="133" t="s">
         <v>86</v>
       </c>
       <c r="C16" s="119" t="s">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="D16" s="119" t="s">
         <v>179</v>
       </c>
       <c r="E16" s="102" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="F16" s="116"/>
       <c r="G16" s="107"/>
-      <c r="H16" s="91"/>
-      <c r="I16" s="134" t="s">
-        <v>270</v>
-      </c>
-      <c r="J16" s="95"/>
-    </row>
-    <row r="17" spans="2:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="138" t="s">
-        <v>142</v>
+      <c r="H16" s="135" t="s">
+        <v>300</v>
+      </c>
+      <c r="I16" s="136"/>
+    </row>
+    <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="132" t="s">
+        <v>168</v>
       </c>
       <c r="C17" s="119" t="s">
-        <v>180</v>
+        <v>287</v>
       </c>
       <c r="D17" s="119" t="s">
         <v>179</v>
       </c>
-      <c r="E17" s="93" t="s">
-        <v>106</v>
+      <c r="E17" s="115" t="s">
+        <v>270</v>
       </c>
       <c r="F17" s="116"/>
-      <c r="G17" s="91"/>
-      <c r="H17" s="91"/>
-      <c r="I17" s="132"/>
-      <c r="J17" s="95"/>
-    </row>
-    <row r="18" spans="2:10" ht="27" x14ac:dyDescent="0.3">
-      <c r="B18" s="88" t="s">
-        <v>107</v>
+      <c r="G17" s="131" t="s">
+        <v>261</v>
+      </c>
+      <c r="H17" s="154" t="s">
+        <v>283</v>
+      </c>
+      <c r="I17" s="153"/>
+    </row>
+    <row r="18" spans="2:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="133" t="s">
+        <v>142</v>
       </c>
       <c r="C18" s="119" t="s">
-        <v>176</v>
+        <v>290</v>
       </c>
       <c r="D18" s="119" t="s">
         <v>179</v>
       </c>
-      <c r="E18" s="102" t="s">
-        <v>165</v>
+      <c r="E18" s="115" t="s">
+        <v>301</v>
       </c>
       <c r="F18" s="116"/>
-      <c r="G18" s="107"/>
-      <c r="H18" s="91"/>
-      <c r="I18" s="132"/>
-      <c r="J18" s="95"/>
-    </row>
-    <row r="19" spans="2:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="87" t="s">
-        <v>110</v>
-      </c>
-      <c r="C19" s="119" t="s">
-        <v>176</v>
-      </c>
-      <c r="D19" s="119" t="s">
+      <c r="G18" s="131"/>
+      <c r="H18" s="154"/>
+      <c r="I18" s="153"/>
+    </row>
+    <row r="19" spans="2:9" ht="108" x14ac:dyDescent="0.3">
+      <c r="B19" s="167" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="156" t="s">
+        <v>287</v>
+      </c>
+      <c r="D19" s="156" t="s">
         <v>179</v>
       </c>
       <c r="E19" s="93" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="F19" s="116"/>
-      <c r="G19" s="106"/>
-      <c r="H19" s="91"/>
-      <c r="I19" s="132"/>
-      <c r="J19" s="95"/>
-    </row>
-    <row r="20" spans="2:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="136" t="s">
-        <v>168</v>
-      </c>
-      <c r="C20" s="119" t="s">
+      <c r="G19" s="135" t="s">
+        <v>268</v>
+      </c>
+      <c r="I19" s="95"/>
+    </row>
+    <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="160" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="161" t="s">
+        <v>291</v>
+      </c>
+      <c r="D20" s="161" t="s">
+        <v>179</v>
+      </c>
+      <c r="E20" s="162" t="s">
+        <v>262</v>
+      </c>
+      <c r="F20" s="163"/>
+      <c r="G20" s="164" t="s">
         <v>267</v>
       </c>
-      <c r="D20" s="119" t="s">
-        <v>179</v>
-      </c>
-      <c r="E20" s="115" t="s">
-        <v>284</v>
-      </c>
-      <c r="F20" s="116"/>
-      <c r="G20" s="112"/>
-      <c r="H20" s="135" t="s">
-        <v>271</v>
-      </c>
-      <c r="I20" s="135" t="s">
-        <v>272</v>
-      </c>
-      <c r="J20" s="114"/>
-    </row>
-    <row r="21" spans="2:10" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="89" t="s">
-        <v>109</v>
-      </c>
-      <c r="C21" s="120" t="s">
-        <v>176</v>
-      </c>
-      <c r="D21" s="120" t="s">
-        <v>179</v>
-      </c>
-      <c r="E21" s="105" t="s">
-        <v>141</v>
-      </c>
-      <c r="F21" s="117"/>
-      <c r="G21" s="108"/>
-      <c r="H21" s="96"/>
-      <c r="I21" s="133"/>
-      <c r="J21" s="97"/>
-    </row>
-    <row r="22" spans="2:10" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="H20" s="165"/>
+      <c r="I20" s="166"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="F2:I2"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.375" style="83" customWidth="1"/>
+    <col min="2" max="2" width="9" style="83"/>
+    <col min="3" max="4" width="14.75" style="83" customWidth="1"/>
+    <col min="5" max="5" width="43" style="83" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="83" customWidth="1"/>
+    <col min="7" max="9" width="62.125" style="83" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="83"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="111" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="109"/>
+    </row>
+    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="146" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="150" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2" s="150" t="s">
+        <v>178</v>
+      </c>
+      <c r="E2" s="148" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2" s="144" t="s">
+        <v>293</v>
+      </c>
+      <c r="G2" s="144"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="145"/>
+    </row>
+    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="147"/>
+      <c r="C3" s="151"/>
+      <c r="D3" s="151"/>
+      <c r="E3" s="149"/>
+      <c r="F3" s="99" t="s">
+        <v>294</v>
+      </c>
+      <c r="G3" s="99" t="s">
+        <v>296</v>
+      </c>
+      <c r="H3" s="99" t="s">
+        <v>297</v>
+      </c>
+      <c r="I3" s="100" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="168" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" s="118" t="s">
+        <v>176</v>
+      </c>
+      <c r="D4" s="118" t="s">
+        <v>179</v>
+      </c>
+      <c r="E4" s="157" t="s">
+        <v>141</v>
+      </c>
+      <c r="F4" s="158"/>
+      <c r="G4" s="159"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="94"/>
+    </row>
+    <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="171" t="s">
+        <v>182</v>
+      </c>
+      <c r="C5" s="119" t="s">
+        <v>284</v>
+      </c>
+      <c r="D5" s="119" t="s">
+        <v>181</v>
+      </c>
+      <c r="E5" s="102" t="s">
+        <v>162</v>
+      </c>
+      <c r="F5" s="116"/>
+      <c r="G5" s="107"/>
+      <c r="H5" s="125" t="s">
+        <v>281</v>
+      </c>
+      <c r="I5" s="152" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="169" t="s">
+        <v>292</v>
+      </c>
+      <c r="C6" s="119" t="s">
+        <v>285</v>
+      </c>
+      <c r="D6" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E6" s="102" t="s">
+        <v>162</v>
+      </c>
+      <c r="F6" s="125"/>
+      <c r="G6" s="125"/>
+      <c r="H6" s="125"/>
+      <c r="I6" s="152"/>
+    </row>
+    <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="169" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="119" t="s">
+        <v>286</v>
+      </c>
+      <c r="D7" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E7" s="102" t="s">
+        <v>163</v>
+      </c>
+      <c r="F7" s="116"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="91"/>
+      <c r="I7" s="95"/>
+    </row>
+    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="169" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" s="119" t="s">
+        <v>285</v>
+      </c>
+      <c r="D8" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E8" s="93" t="s">
+        <v>140</v>
+      </c>
+      <c r="F8" s="116"/>
+      <c r="G8" s="106"/>
+      <c r="H8" s="91"/>
+      <c r="I8" s="95"/>
+    </row>
+    <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="170" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="119" t="s">
+        <v>285</v>
+      </c>
+      <c r="D9" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E9" s="93" t="s">
+        <v>153</v>
+      </c>
+      <c r="F9" s="116"/>
+      <c r="G9" s="107"/>
+      <c r="H9" s="155"/>
+      <c r="I9" s="95"/>
+    </row>
+    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="170" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="119" t="s">
+        <v>285</v>
+      </c>
+      <c r="D10" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E10" s="93" t="s">
+        <v>154</v>
+      </c>
+      <c r="F10" s="116"/>
+      <c r="G10" s="107"/>
+      <c r="H10" s="155"/>
+      <c r="I10" s="95"/>
+    </row>
+    <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="170" t="s">
+        <v>125</v>
+      </c>
+      <c r="C11" s="119" t="s">
+        <v>285</v>
+      </c>
+      <c r="D11" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E11" s="93" t="s">
+        <v>155</v>
+      </c>
+      <c r="F11" s="116"/>
+      <c r="G11" s="107"/>
+      <c r="H11" s="155"/>
+      <c r="I11" s="95"/>
+    </row>
+    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="170" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" s="119" t="s">
+        <v>285</v>
+      </c>
+      <c r="D12" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E12" s="93" t="s">
+        <v>156</v>
+      </c>
+      <c r="F12" s="116"/>
+      <c r="G12" s="107"/>
+      <c r="H12" s="155"/>
+      <c r="I12" s="95"/>
+    </row>
+    <row r="13" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
+      <c r="B13" s="134" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="119" t="s">
+        <v>287</v>
+      </c>
+      <c r="D13" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E13" s="102" t="s">
+        <v>264</v>
+      </c>
+      <c r="F13" s="116"/>
+      <c r="G13" s="107"/>
+      <c r="H13" s="135" t="s">
+        <v>277</v>
+      </c>
+      <c r="I13" s="136" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="133" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" s="119" t="s">
+        <v>287</v>
+      </c>
+      <c r="D14" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E14" s="102" t="s">
+        <v>265</v>
+      </c>
+      <c r="F14" s="116"/>
+      <c r="G14" s="107"/>
+      <c r="H14" s="135" t="s">
+        <v>279</v>
+      </c>
+      <c r="I14" s="136" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
+      <c r="B15" s="133" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="119" t="s">
+        <v>288</v>
+      </c>
+      <c r="D15" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E15" s="102" t="s">
+        <v>263</v>
+      </c>
+      <c r="F15" s="116"/>
+      <c r="G15" s="135" t="s">
+        <v>269</v>
+      </c>
+      <c r="H15" s="154" t="s">
+        <v>275</v>
+      </c>
+      <c r="I15" s="136" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="81" x14ac:dyDescent="0.3">
+      <c r="B16" s="133" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="119" t="s">
+        <v>289</v>
+      </c>
+      <c r="D16" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E16" s="102" t="s">
+        <v>266</v>
+      </c>
+      <c r="F16" s="116"/>
+      <c r="G16" s="107"/>
+      <c r="H16" s="135" t="s">
+        <v>282</v>
+      </c>
+      <c r="I16" s="136"/>
+    </row>
+    <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="132" t="s">
+        <v>168</v>
+      </c>
+      <c r="C17" s="119" t="s">
+        <v>287</v>
+      </c>
+      <c r="D17" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E17" s="115" t="s">
+        <v>270</v>
+      </c>
+      <c r="F17" s="116"/>
+      <c r="G17" s="131" t="s">
+        <v>261</v>
+      </c>
+      <c r="H17" s="154" t="s">
+        <v>283</v>
+      </c>
+      <c r="I17" s="153"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B18" s="133" t="s">
+        <v>142</v>
+      </c>
+      <c r="C18" s="119" t="s">
+        <v>290</v>
+      </c>
+      <c r="D18" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="E18" s="115"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="131"/>
+      <c r="H18" s="154"/>
+      <c r="I18" s="153"/>
+    </row>
+    <row r="19" spans="2:9" ht="108" x14ac:dyDescent="0.3">
+      <c r="B19" s="167" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="156" t="s">
+        <v>287</v>
+      </c>
+      <c r="D19" s="156" t="s">
+        <v>179</v>
+      </c>
+      <c r="E19" s="93" t="s">
+        <v>157</v>
+      </c>
+      <c r="F19" s="116"/>
+      <c r="G19" s="135" t="s">
+        <v>268</v>
+      </c>
+      <c r="I19" s="95"/>
+    </row>
+    <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="160" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="161" t="s">
+        <v>291</v>
+      </c>
+      <c r="D20" s="161" t="s">
+        <v>179</v>
+      </c>
+      <c r="E20" s="162" t="s">
+        <v>262</v>
+      </c>
+      <c r="F20" s="163"/>
+      <c r="G20" s="164" t="s">
+        <v>267</v>
+      </c>
+      <c r="H20" s="165"/>
+      <c r="I20" s="166"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:I2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\일정\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Task\000_PJT\111_PTC\1.doc\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="304">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1819,6 +1819,18 @@
     <t>출도 (26/02/01)
 Proto (26/04/06)
 정확한 일정인지 확인 필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Proto (26/08/01)
+P1 (27/04/01)
+P2 (27/06/15)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Proto (진행 중)
+P1 (26/04/01)
+P2 (26/10/01)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3577,6 +3589,66 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3621,66 +3693,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -3693,6 +3705,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF0000FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -4298,90 +4315,90 @@
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="157" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="139" t="s">
+      <c r="C2" s="159" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="139" t="s">
+      <c r="D2" s="159" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="143">
+      <c r="E2" s="163">
         <v>23</v>
       </c>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
-      <c r="H2" s="141"/>
-      <c r="I2" s="141"/>
-      <c r="J2" s="141"/>
-      <c r="K2" s="141"/>
-      <c r="L2" s="141"/>
-      <c r="M2" s="141"/>
-      <c r="N2" s="141"/>
-      <c r="O2" s="141"/>
-      <c r="P2" s="141"/>
-      <c r="Q2" s="141">
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="161"/>
+      <c r="L2" s="161"/>
+      <c r="M2" s="161"/>
+      <c r="N2" s="161"/>
+      <c r="O2" s="161"/>
+      <c r="P2" s="161"/>
+      <c r="Q2" s="161">
         <v>24</v>
       </c>
-      <c r="R2" s="141"/>
-      <c r="S2" s="141"/>
-      <c r="T2" s="141"/>
-      <c r="U2" s="141"/>
-      <c r="V2" s="141"/>
-      <c r="W2" s="141"/>
-      <c r="X2" s="141"/>
-      <c r="Y2" s="141"/>
-      <c r="Z2" s="141"/>
-      <c r="AA2" s="141"/>
-      <c r="AB2" s="141"/>
-      <c r="AC2" s="141">
+      <c r="R2" s="161"/>
+      <c r="S2" s="161"/>
+      <c r="T2" s="161"/>
+      <c r="U2" s="161"/>
+      <c r="V2" s="161"/>
+      <c r="W2" s="161"/>
+      <c r="X2" s="161"/>
+      <c r="Y2" s="161"/>
+      <c r="Z2" s="161"/>
+      <c r="AA2" s="161"/>
+      <c r="AB2" s="161"/>
+      <c r="AC2" s="161">
         <v>25</v>
       </c>
-      <c r="AD2" s="141"/>
-      <c r="AE2" s="141"/>
-      <c r="AF2" s="141"/>
-      <c r="AG2" s="141"/>
-      <c r="AH2" s="141"/>
-      <c r="AI2" s="141"/>
-      <c r="AJ2" s="141"/>
-      <c r="AK2" s="141"/>
-      <c r="AL2" s="141"/>
-      <c r="AM2" s="141"/>
-      <c r="AN2" s="141"/>
-      <c r="AO2" s="141">
+      <c r="AD2" s="161"/>
+      <c r="AE2" s="161"/>
+      <c r="AF2" s="161"/>
+      <c r="AG2" s="161"/>
+      <c r="AH2" s="161"/>
+      <c r="AI2" s="161"/>
+      <c r="AJ2" s="161"/>
+      <c r="AK2" s="161"/>
+      <c r="AL2" s="161"/>
+      <c r="AM2" s="161"/>
+      <c r="AN2" s="161"/>
+      <c r="AO2" s="161">
         <v>26</v>
       </c>
-      <c r="AP2" s="141"/>
-      <c r="AQ2" s="141"/>
-      <c r="AR2" s="141"/>
-      <c r="AS2" s="141"/>
-      <c r="AT2" s="141"/>
-      <c r="AU2" s="141"/>
-      <c r="AV2" s="141"/>
-      <c r="AW2" s="141"/>
-      <c r="AX2" s="141"/>
-      <c r="AY2" s="141"/>
-      <c r="AZ2" s="142"/>
-      <c r="BA2" s="141">
+      <c r="AP2" s="161"/>
+      <c r="AQ2" s="161"/>
+      <c r="AR2" s="161"/>
+      <c r="AS2" s="161"/>
+      <c r="AT2" s="161"/>
+      <c r="AU2" s="161"/>
+      <c r="AV2" s="161"/>
+      <c r="AW2" s="161"/>
+      <c r="AX2" s="161"/>
+      <c r="AY2" s="161"/>
+      <c r="AZ2" s="162"/>
+      <c r="BA2" s="161">
         <v>27</v>
       </c>
-      <c r="BB2" s="141"/>
-      <c r="BC2" s="141"/>
-      <c r="BD2" s="141"/>
-      <c r="BE2" s="141"/>
-      <c r="BF2" s="141"/>
-      <c r="BG2" s="141"/>
-      <c r="BH2" s="141"/>
-      <c r="BI2" s="141"/>
-      <c r="BJ2" s="141"/>
-      <c r="BK2" s="141"/>
-      <c r="BL2" s="142"/>
+      <c r="BB2" s="161"/>
+      <c r="BC2" s="161"/>
+      <c r="BD2" s="161"/>
+      <c r="BE2" s="161"/>
+      <c r="BF2" s="161"/>
+      <c r="BG2" s="161"/>
+      <c r="BH2" s="161"/>
+      <c r="BI2" s="161"/>
+      <c r="BJ2" s="161"/>
+      <c r="BK2" s="161"/>
+      <c r="BL2" s="162"/>
     </row>
     <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="138"/>
-      <c r="C3" s="140"/>
-      <c r="D3" s="140"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="160"/>
+      <c r="D3" s="160"/>
       <c r="E3" s="22">
         <v>1</v>
       </c>
@@ -6350,39 +6367,39 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="146" t="s">
+      <c r="B2" s="166" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="150" t="s">
+      <c r="C2" s="170" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="150" t="s">
+      <c r="D2" s="170" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="148" t="s">
+      <c r="E2" s="168" t="s">
         <v>127</v>
       </c>
       <c r="F2" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="144" t="s">
+      <c r="G2" s="164" t="s">
         <v>114</v>
       </c>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="145"/>
-      <c r="K2" s="144" t="s">
+      <c r="H2" s="164"/>
+      <c r="I2" s="164"/>
+      <c r="J2" s="165"/>
+      <c r="K2" s="164" t="s">
         <v>183</v>
       </c>
-      <c r="L2" s="144"/>
-      <c r="M2" s="144"/>
-      <c r="N2" s="145"/>
+      <c r="L2" s="164"/>
+      <c r="M2" s="164"/>
+      <c r="N2" s="165"/>
     </row>
     <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="147"/>
-      <c r="C3" s="151"/>
-      <c r="D3" s="151"/>
-      <c r="E3" s="149"/>
+      <c r="B3" s="167"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="169"/>
       <c r="F3" s="99" t="s">
         <v>112</v>
       </c>
@@ -7125,30 +7142,30 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="146" t="s">
+      <c r="B2" s="166" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="150" t="s">
+      <c r="C2" s="170" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="150" t="s">
+      <c r="D2" s="170" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="148" t="s">
+      <c r="E2" s="168" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="144" t="s">
+      <c r="F2" s="164" t="s">
         <v>183</v>
       </c>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="145"/>
+      <c r="G2" s="164"/>
+      <c r="H2" s="164"/>
+      <c r="I2" s="165"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="147"/>
-      <c r="C3" s="151"/>
-      <c r="D3" s="151"/>
-      <c r="E3" s="149"/>
+      <c r="B3" s="167"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="169"/>
       <c r="F3" s="99" t="s">
         <v>115</v>
       </c>
@@ -7526,30 +7543,30 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="146" t="s">
+      <c r="B2" s="166" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="150" t="s">
+      <c r="C2" s="170" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="150" t="s">
+      <c r="D2" s="170" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="148" t="s">
+      <c r="E2" s="168" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="144" t="s">
+      <c r="F2" s="164" t="s">
         <v>228</v>
       </c>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="145"/>
+      <c r="G2" s="164"/>
+      <c r="H2" s="164"/>
+      <c r="I2" s="165"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="147"/>
-      <c r="C3" s="151"/>
-      <c r="D3" s="151"/>
-      <c r="E3" s="149"/>
+      <c r="B3" s="167"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="169"/>
       <c r="F3" s="99" t="s">
         <v>115</v>
       </c>
@@ -7933,30 +7950,30 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="146" t="s">
+      <c r="B2" s="166" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="150" t="s">
+      <c r="C2" s="170" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="150" t="s">
+      <c r="D2" s="170" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="148" t="s">
+      <c r="E2" s="168" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="144" t="s">
+      <c r="F2" s="164" t="s">
         <v>260</v>
       </c>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="145"/>
+      <c r="G2" s="164"/>
+      <c r="H2" s="164"/>
+      <c r="I2" s="165"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="147"/>
-      <c r="C3" s="151"/>
-      <c r="D3" s="151"/>
-      <c r="E3" s="149"/>
+      <c r="B3" s="167"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="169"/>
       <c r="F3" s="99" t="s">
         <v>295</v>
       </c>
@@ -7971,7 +7988,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="168" t="s">
+      <c r="B4" s="153" t="s">
         <v>109</v>
       </c>
       <c r="C4" s="118" t="s">
@@ -7980,16 +7997,16 @@
       <c r="D4" s="118" t="s">
         <v>179</v>
       </c>
-      <c r="E4" s="157" t="s">
+      <c r="E4" s="142" t="s">
         <v>141</v>
       </c>
-      <c r="F4" s="158"/>
-      <c r="G4" s="159"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="144"/>
       <c r="H4" s="90"/>
       <c r="I4" s="94"/>
     </row>
     <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="171" t="s">
+      <c r="B5" s="156" t="s">
         <v>182</v>
       </c>
       <c r="C5" s="119" t="s">
@@ -8006,12 +8023,12 @@
       <c r="H5" s="125" t="s">
         <v>281</v>
       </c>
-      <c r="I5" s="152" t="s">
+      <c r="I5" s="137" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="169" t="s">
+      <c r="B6" s="154" t="s">
         <v>292</v>
       </c>
       <c r="C6" s="119" t="s">
@@ -8026,10 +8043,10 @@
       <c r="F6" s="125"/>
       <c r="G6" s="125"/>
       <c r="H6" s="125"/>
-      <c r="I6" s="152"/>
+      <c r="I6" s="137"/>
     </row>
     <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="169" t="s">
+      <c r="B7" s="154" t="s">
         <v>76</v>
       </c>
       <c r="C7" s="119" t="s">
@@ -8039,15 +8056,15 @@
         <v>179</v>
       </c>
       <c r="E7" s="102" t="s">
-        <v>163</v>
+        <v>303</v>
       </c>
       <c r="F7" s="116"/>
       <c r="G7" s="107"/>
       <c r="H7" s="91"/>
       <c r="I7" s="95"/>
     </row>
-    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="169" t="s">
+    <row r="8" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="154" t="s">
         <v>110</v>
       </c>
       <c r="C8" s="119" t="s">
@@ -8056,8 +8073,8 @@
       <c r="D8" s="119" t="s">
         <v>179</v>
       </c>
-      <c r="E8" s="93" t="s">
-        <v>140</v>
+      <c r="E8" s="102" t="s">
+        <v>302</v>
       </c>
       <c r="F8" s="116"/>
       <c r="G8" s="106"/>
@@ -8065,7 +8082,7 @@
       <c r="I8" s="95"/>
     </row>
     <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="170" t="s">
+      <c r="B9" s="155" t="s">
         <v>118</v>
       </c>
       <c r="C9" s="119" t="s">
@@ -8079,11 +8096,11 @@
       </c>
       <c r="F9" s="116"/>
       <c r="G9" s="107"/>
-      <c r="H9" s="155"/>
+      <c r="H9" s="140"/>
       <c r="I9" s="95"/>
     </row>
     <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="170" t="s">
+      <c r="B10" s="155" t="s">
         <v>124</v>
       </c>
       <c r="C10" s="119" t="s">
@@ -8097,11 +8114,11 @@
       </c>
       <c r="F10" s="116"/>
       <c r="G10" s="107"/>
-      <c r="H10" s="155"/>
+      <c r="H10" s="140"/>
       <c r="I10" s="95"/>
     </row>
     <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="170" t="s">
+      <c r="B11" s="155" t="s">
         <v>125</v>
       </c>
       <c r="C11" s="119" t="s">
@@ -8115,11 +8132,11 @@
       </c>
       <c r="F11" s="116"/>
       <c r="G11" s="107"/>
-      <c r="H11" s="155"/>
+      <c r="H11" s="140"/>
       <c r="I11" s="95"/>
     </row>
     <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="170" t="s">
+      <c r="B12" s="155" t="s">
         <v>126</v>
       </c>
       <c r="C12" s="119" t="s">
@@ -8133,7 +8150,7 @@
       </c>
       <c r="F12" s="116"/>
       <c r="G12" s="107"/>
-      <c r="H12" s="155"/>
+      <c r="H12" s="140"/>
       <c r="I12" s="95"/>
     </row>
     <row r="13" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -8193,7 +8210,7 @@
       <c r="G15" s="135" t="s">
         <v>269</v>
       </c>
-      <c r="H15" s="154" t="s">
+      <c r="H15" s="139" t="s">
         <v>299</v>
       </c>
       <c r="I15" s="136"/>
@@ -8235,10 +8252,10 @@
       <c r="G17" s="131" t="s">
         <v>261</v>
       </c>
-      <c r="H17" s="154" t="s">
+      <c r="H17" s="139" t="s">
         <v>283</v>
       </c>
-      <c r="I17" s="153"/>
+      <c r="I17" s="138"/>
     </row>
     <row r="18" spans="2:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="133" t="s">
@@ -8255,17 +8272,17 @@
       </c>
       <c r="F18" s="116"/>
       <c r="G18" s="131"/>
-      <c r="H18" s="154"/>
-      <c r="I18" s="153"/>
+      <c r="H18" s="139"/>
+      <c r="I18" s="138"/>
     </row>
     <row r="19" spans="2:9" ht="108" x14ac:dyDescent="0.3">
-      <c r="B19" s="167" t="s">
+      <c r="B19" s="152" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="156" t="s">
+      <c r="C19" s="141" t="s">
         <v>287</v>
       </c>
-      <c r="D19" s="156" t="s">
+      <c r="D19" s="141" t="s">
         <v>179</v>
       </c>
       <c r="E19" s="93" t="s">
@@ -8278,24 +8295,24 @@
       <c r="I19" s="95"/>
     </row>
     <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="160" t="s">
+      <c r="B20" s="145" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="161" t="s">
+      <c r="C20" s="146" t="s">
         <v>291</v>
       </c>
-      <c r="D20" s="161" t="s">
+      <c r="D20" s="146" t="s">
         <v>179</v>
       </c>
-      <c r="E20" s="162" t="s">
+      <c r="E20" s="147" t="s">
         <v>262</v>
       </c>
-      <c r="F20" s="163"/>
-      <c r="G20" s="164" t="s">
+      <c r="F20" s="148"/>
+      <c r="G20" s="149" t="s">
         <v>267</v>
       </c>
-      <c r="H20" s="165"/>
-      <c r="I20" s="166"/>
+      <c r="H20" s="150"/>
+      <c r="I20" s="151"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -8336,30 +8353,30 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="146" t="s">
+      <c r="B2" s="166" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="150" t="s">
+      <c r="C2" s="170" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="150" t="s">
+      <c r="D2" s="170" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="148" t="s">
+      <c r="E2" s="168" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="144" t="s">
+      <c r="F2" s="164" t="s">
         <v>293</v>
       </c>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="145"/>
+      <c r="G2" s="164"/>
+      <c r="H2" s="164"/>
+      <c r="I2" s="165"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="147"/>
-      <c r="C3" s="151"/>
-      <c r="D3" s="151"/>
-      <c r="E3" s="149"/>
+      <c r="B3" s="167"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="169"/>
       <c r="F3" s="99" t="s">
         <v>294</v>
       </c>
@@ -8374,7 +8391,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="168" t="s">
+      <c r="B4" s="153" t="s">
         <v>109</v>
       </c>
       <c r="C4" s="118" t="s">
@@ -8383,16 +8400,16 @@
       <c r="D4" s="118" t="s">
         <v>179</v>
       </c>
-      <c r="E4" s="157" t="s">
+      <c r="E4" s="142" t="s">
         <v>141</v>
       </c>
-      <c r="F4" s="158"/>
-      <c r="G4" s="159"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="144"/>
       <c r="H4" s="90"/>
       <c r="I4" s="94"/>
     </row>
     <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="171" t="s">
+      <c r="B5" s="156" t="s">
         <v>182</v>
       </c>
       <c r="C5" s="119" t="s">
@@ -8409,12 +8426,12 @@
       <c r="H5" s="125" t="s">
         <v>281</v>
       </c>
-      <c r="I5" s="152" t="s">
+      <c r="I5" s="137" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="169" t="s">
+      <c r="B6" s="154" t="s">
         <v>292</v>
       </c>
       <c r="C6" s="119" t="s">
@@ -8429,10 +8446,10 @@
       <c r="F6" s="125"/>
       <c r="G6" s="125"/>
       <c r="H6" s="125"/>
-      <c r="I6" s="152"/>
+      <c r="I6" s="137"/>
     </row>
     <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="169" t="s">
+      <c r="B7" s="154" t="s">
         <v>76</v>
       </c>
       <c r="C7" s="119" t="s">
@@ -8450,7 +8467,7 @@
       <c r="I7" s="95"/>
     </row>
     <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="169" t="s">
+      <c r="B8" s="154" t="s">
         <v>110</v>
       </c>
       <c r="C8" s="119" t="s">
@@ -8468,7 +8485,7 @@
       <c r="I8" s="95"/>
     </row>
     <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="170" t="s">
+      <c r="B9" s="155" t="s">
         <v>118</v>
       </c>
       <c r="C9" s="119" t="s">
@@ -8482,11 +8499,11 @@
       </c>
       <c r="F9" s="116"/>
       <c r="G9" s="107"/>
-      <c r="H9" s="155"/>
+      <c r="H9" s="140"/>
       <c r="I9" s="95"/>
     </row>
     <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="170" t="s">
+      <c r="B10" s="155" t="s">
         <v>124</v>
       </c>
       <c r="C10" s="119" t="s">
@@ -8500,11 +8517,11 @@
       </c>
       <c r="F10" s="116"/>
       <c r="G10" s="107"/>
-      <c r="H10" s="155"/>
+      <c r="H10" s="140"/>
       <c r="I10" s="95"/>
     </row>
     <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="170" t="s">
+      <c r="B11" s="155" t="s">
         <v>125</v>
       </c>
       <c r="C11" s="119" t="s">
@@ -8518,11 +8535,11 @@
       </c>
       <c r="F11" s="116"/>
       <c r="G11" s="107"/>
-      <c r="H11" s="155"/>
+      <c r="H11" s="140"/>
       <c r="I11" s="95"/>
     </row>
     <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="170" t="s">
+      <c r="B12" s="155" t="s">
         <v>126</v>
       </c>
       <c r="C12" s="119" t="s">
@@ -8536,7 +8553,7 @@
       </c>
       <c r="F12" s="116"/>
       <c r="G12" s="107"/>
-      <c r="H12" s="155"/>
+      <c r="H12" s="140"/>
       <c r="I12" s="95"/>
     </row>
     <row r="13" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -8600,7 +8617,7 @@
       <c r="G15" s="135" t="s">
         <v>269</v>
       </c>
-      <c r="H15" s="154" t="s">
+      <c r="H15" s="139" t="s">
         <v>275</v>
       </c>
       <c r="I15" s="136" t="s">
@@ -8644,10 +8661,10 @@
       <c r="G17" s="131" t="s">
         <v>261</v>
       </c>
-      <c r="H17" s="154" t="s">
+      <c r="H17" s="139" t="s">
         <v>283</v>
       </c>
-      <c r="I17" s="153"/>
+      <c r="I17" s="138"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="133" t="s">
@@ -8662,17 +8679,17 @@
       <c r="E18" s="115"/>
       <c r="F18" s="116"/>
       <c r="G18" s="131"/>
-      <c r="H18" s="154"/>
-      <c r="I18" s="153"/>
+      <c r="H18" s="139"/>
+      <c r="I18" s="138"/>
     </row>
     <row r="19" spans="2:9" ht="108" x14ac:dyDescent="0.3">
-      <c r="B19" s="167" t="s">
+      <c r="B19" s="152" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="156" t="s">
+      <c r="C19" s="141" t="s">
         <v>287</v>
       </c>
-      <c r="D19" s="156" t="s">
+      <c r="D19" s="141" t="s">
         <v>179</v>
       </c>
       <c r="E19" s="93" t="s">
@@ -8685,24 +8702,24 @@
       <c r="I19" s="95"/>
     </row>
     <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="160" t="s">
+      <c r="B20" s="145" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="161" t="s">
+      <c r="C20" s="146" t="s">
         <v>291</v>
       </c>
-      <c r="D20" s="161" t="s">
+      <c r="D20" s="146" t="s">
         <v>179</v>
       </c>
-      <c r="E20" s="162" t="s">
+      <c r="E20" s="147" t="s">
         <v>262</v>
       </c>
-      <c r="F20" s="163"/>
-      <c r="G20" s="164" t="s">
+      <c r="F20" s="148"/>
+      <c r="G20" s="149" t="s">
         <v>267</v>
       </c>
-      <c r="H20" s="165"/>
-      <c r="I20" s="166"/>
+      <c r="H20" s="150"/>
+      <c r="I20" s="151"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Task\000_PJT\111_PTC\1.doc\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\일정\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1801,36 +1801,36 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>출도 (26/02/01)
+Proto (26/04/06)
+정확한 일정인지 확인 필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Proto (26/08/01)
+P1 (27/04/01)
+P2 (27/06/15)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Proto (진행 중)
+P1 (26/04/01)
+P2 (26/10/01)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>[임제훈 사원]
-- LHD ESIR
+- LHD ESIR 계획서 작성
 - R로직 튜닝</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[임제훈 사원]
-- ESIR 계획서 등록 (~10/21)
 - Core Temp 튜닝 결과 확인 (~10/21)
+- ESIR 계획서 등록 (~10/24)
 - 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/24)
 - R로직 튜닝 (~10/24)
 - 최신 승인도 확인</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>출도 (26/02/01)
-Proto (26/04/06)
-정확한 일정인지 확인 필요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Proto (26/08/01)
-P1 (27/04/01)
-P2 (27/06/15)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Proto (진행 중)
-P1 (26/04/01)
-P2 (26/10/01)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8056,7 +8056,7 @@
         <v>179</v>
       </c>
       <c r="E7" s="102" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F7" s="116"/>
       <c r="G7" s="107"/>
@@ -8074,7 +8074,7 @@
         <v>179</v>
       </c>
       <c r="E8" s="102" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F8" s="116"/>
       <c r="G8" s="106"/>
@@ -8211,7 +8211,7 @@
         <v>269</v>
       </c>
       <c r="H15" s="139" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="I15" s="136"/>
     </row>
@@ -8231,7 +8231,7 @@
       <c r="F16" s="116"/>
       <c r="G16" s="107"/>
       <c r="H16" s="135" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="I16" s="136"/>
     </row>
@@ -8268,7 +8268,7 @@
         <v>179</v>
       </c>
       <c r="E18" s="115" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F18" s="116"/>
       <c r="G18" s="131"/>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\일정\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\2.project\hkmc_ptc_heater\Doc\1. 일정\1. Weekly Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="305">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1831,6 +1831,17 @@
 - 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/24)
 - R로직 튜닝 (~10/24)
 - 최신 승인도 확인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">[우리산업]
+PM : 유정호, 기구 : 공준석, HW : 신지훈, 
+제조 : 전진호, 품질 : 박상철, 일렉스 : 남시온, 류상근, 박철수, 슬로박법인 : 김예현
+[공조설계팀]
+안성민 책임연구원 010-2207-9180
+freshair@hyundai.com
+[신차 품질팀]
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5469,14 +5480,16 @@
       <c r="BK14" s="31"/>
       <c r="BL14" s="10"/>
     </row>
-    <row r="15" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:64" ht="285.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="27" t="s">
         <v>65</v>
       </c>
       <c r="C15" s="59" t="s">
         <v>85</v>
       </c>
-      <c r="D15" s="33"/>
+      <c r="D15" s="34" t="s">
+        <v>304</v>
+      </c>
       <c r="E15" s="6"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\2.project\hkmc_ptc_heater\Doc\1. 일정\1. Weekly Plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\일정\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="309">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1819,21 +1819,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[임제훈 사원]
-- LHD ESIR 계획서 작성
-- R로직 튜닝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- Core Temp 튜닝 결과 확인 (~10/21)
-- ESIR 계획서 등록 (~10/24)
-- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/24)
-- R로직 튜닝 (~10/24)
-- 최신 승인도 확인</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">[우리산업]
 PM : 유정호, 기구 : 공준석, HW : 신지훈, 
 제조 : 전진호, 품질 : 박상철, 일렉스 : 남시온, 류상근, 박철수, 슬로박법인 : 김예현
@@ -1842,6 +1827,48 @@
 freshair@hyundai.com
 [신차 품질팀]
 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- LHD, RHD 사양 3D 모델링 수령 (10/21)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- LHD R로직 튜닝
+- RHD R로직 튜닝 (HVAC 미보유, 보류)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- LHD ESIR 계획서 작성
+- R로직 튜닝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 최소 작동 전압 범위 수정 후, EV HTR 개발팀 김민수 선임에게 전달 (~10/24)
+  : 0℃, -30℃ 환경에서 QV Air PTC와 160V, 170V 출력 비교 필요로 인한 요청</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 온도 정합성 테스트 (10/20)
+- 제어기 선행품질 검증 현황 작성 (10/21)
+- 제어기 선행품질 검증 현황 관련 기아 오토랜드 방문 (10/23)
+- 설계 변경 진행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- Core Temp 튜닝 결과 확인 (~10/22)
+- HVAC RPM 확인 (~10/22)
+- 공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (~10/22)
+- R로직 튜닝 (~10/22)
+- ESIR 계획서 등록 (~10/24)
+- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/24)
+- 최신 승인도 확인 (~10/31)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3188,7 +3215,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3704,6 +3731,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -5488,7 +5518,7 @@
         <v>85</v>
       </c>
       <c r="D15" s="34" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="7"/>
@@ -8127,7 +8157,7 @@
       </c>
       <c r="F10" s="116"/>
       <c r="G10" s="107"/>
-      <c r="H10" s="140"/>
+      <c r="H10" s="91"/>
       <c r="I10" s="95"/>
     </row>
     <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -8145,7 +8175,7 @@
       </c>
       <c r="F11" s="116"/>
       <c r="G11" s="107"/>
-      <c r="H11" s="140"/>
+      <c r="H11" s="91"/>
       <c r="I11" s="95"/>
     </row>
     <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -8182,7 +8212,7 @@
       <c r="F13" s="116"/>
       <c r="G13" s="107"/>
       <c r="H13" s="135" t="s">
-        <v>277</v>
+        <v>307</v>
       </c>
       <c r="I13" s="136"/>
     </row>
@@ -8202,7 +8232,7 @@
       <c r="F14" s="116"/>
       <c r="G14" s="107"/>
       <c r="H14" s="135" t="s">
-        <v>279</v>
+        <v>304</v>
       </c>
       <c r="I14" s="136"/>
     </row>
@@ -8224,11 +8254,11 @@
         <v>269</v>
       </c>
       <c r="H15" s="139" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="I15" s="136"/>
     </row>
-    <row r="16" spans="1:9" ht="81" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="108" x14ac:dyDescent="0.3">
       <c r="B16" s="133" t="s">
         <v>86</v>
       </c>
@@ -8244,7 +8274,7 @@
       <c r="F16" s="116"/>
       <c r="G16" s="107"/>
       <c r="H16" s="135" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="I16" s="136"/>
     </row>
@@ -8265,8 +8295,8 @@
       <c r="G17" s="131" t="s">
         <v>261</v>
       </c>
-      <c r="H17" s="139" t="s">
-        <v>283</v>
+      <c r="H17" s="172" t="s">
+        <v>303</v>
       </c>
       <c r="I17" s="138"/>
     </row>
@@ -8285,7 +8315,7 @@
       </c>
       <c r="F18" s="116"/>
       <c r="G18" s="131"/>
-      <c r="H18" s="139"/>
+      <c r="H18" s="135"/>
       <c r="I18" s="138"/>
     </row>
     <row r="19" spans="2:9" ht="108" x14ac:dyDescent="0.3">
@@ -8304,6 +8334,9 @@
       <c r="F19" s="116"/>
       <c r="G19" s="135" t="s">
         <v>268</v>
+      </c>
+      <c r="H19" s="135" t="s">
+        <v>306</v>
       </c>
       <c r="I19" s="95"/>
     </row>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -1842,14 +1842,25 @@
   </si>
   <si>
     <t>[임제훈 사원]
-- LHD ESIR 계획서 작성
-- R로직 튜닝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
 - 최소 작동 전압 범위 수정 후, EV HTR 개발팀 김민수 선임에게 전달 (~10/24)
   : 0℃, -30℃ 환경에서 QV Air PTC와 160V, 170V 출력 비교 필요로 인한 요청</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- LHD ESIR 계획서 작성 (~10/24)
+- R로직 튜닝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- Core Temp 튜닝 결과 확인 (~10/22)
+- HVAC RPM 확인 (~10/22)
+- R로직 튜닝 (~10/22)
+- 공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (~10/24)
+- ESIR 계획서 등록 (~10/24)
+- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/24)
+- 최신 승인도 확인 (~10/31)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1857,18 +1868,7 @@
 - 온도 정합성 테스트 (10/20)
 - 제어기 선행품질 검증 현황 작성 (10/21)
 - 제어기 선행품질 검증 현황 관련 기아 오토랜드 방문 (10/23)
-- 설계 변경 진행</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- Core Temp 튜닝 결과 확인 (~10/22)
-- HVAC RPM 확인 (~10/22)
-- 공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (~10/22)
-- R로직 튜닝 (~10/22)
-- ESIR 계획서 등록 (~10/24)
-- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/24)
-- 최신 승인도 확인 (~10/31)</t>
+- 설계 변경 진행 (~10/24)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3687,6 +3687,9 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3731,9 +3734,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -4356,90 +4356,90 @@
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="157" t="s">
+      <c r="B2" s="158" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="159" t="s">
+      <c r="C2" s="160" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="159" t="s">
+      <c r="D2" s="160" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="163">
+      <c r="E2" s="164">
         <v>23</v>
       </c>
-      <c r="F2" s="161"/>
-      <c r="G2" s="161"/>
-      <c r="H2" s="161"/>
-      <c r="I2" s="161"/>
-      <c r="J2" s="161"/>
-      <c r="K2" s="161"/>
-      <c r="L2" s="161"/>
-      <c r="M2" s="161"/>
-      <c r="N2" s="161"/>
-      <c r="O2" s="161"/>
-      <c r="P2" s="161"/>
-      <c r="Q2" s="161">
+      <c r="F2" s="162"/>
+      <c r="G2" s="162"/>
+      <c r="H2" s="162"/>
+      <c r="I2" s="162"/>
+      <c r="J2" s="162"/>
+      <c r="K2" s="162"/>
+      <c r="L2" s="162"/>
+      <c r="M2" s="162"/>
+      <c r="N2" s="162"/>
+      <c r="O2" s="162"/>
+      <c r="P2" s="162"/>
+      <c r="Q2" s="162">
         <v>24</v>
       </c>
-      <c r="R2" s="161"/>
-      <c r="S2" s="161"/>
-      <c r="T2" s="161"/>
-      <c r="U2" s="161"/>
-      <c r="V2" s="161"/>
-      <c r="W2" s="161"/>
-      <c r="X2" s="161"/>
-      <c r="Y2" s="161"/>
-      <c r="Z2" s="161"/>
-      <c r="AA2" s="161"/>
-      <c r="AB2" s="161"/>
-      <c r="AC2" s="161">
+      <c r="R2" s="162"/>
+      <c r="S2" s="162"/>
+      <c r="T2" s="162"/>
+      <c r="U2" s="162"/>
+      <c r="V2" s="162"/>
+      <c r="W2" s="162"/>
+      <c r="X2" s="162"/>
+      <c r="Y2" s="162"/>
+      <c r="Z2" s="162"/>
+      <c r="AA2" s="162"/>
+      <c r="AB2" s="162"/>
+      <c r="AC2" s="162">
         <v>25</v>
       </c>
-      <c r="AD2" s="161"/>
-      <c r="AE2" s="161"/>
-      <c r="AF2" s="161"/>
-      <c r="AG2" s="161"/>
-      <c r="AH2" s="161"/>
-      <c r="AI2" s="161"/>
-      <c r="AJ2" s="161"/>
-      <c r="AK2" s="161"/>
-      <c r="AL2" s="161"/>
-      <c r="AM2" s="161"/>
-      <c r="AN2" s="161"/>
-      <c r="AO2" s="161">
+      <c r="AD2" s="162"/>
+      <c r="AE2" s="162"/>
+      <c r="AF2" s="162"/>
+      <c r="AG2" s="162"/>
+      <c r="AH2" s="162"/>
+      <c r="AI2" s="162"/>
+      <c r="AJ2" s="162"/>
+      <c r="AK2" s="162"/>
+      <c r="AL2" s="162"/>
+      <c r="AM2" s="162"/>
+      <c r="AN2" s="162"/>
+      <c r="AO2" s="162">
         <v>26</v>
       </c>
-      <c r="AP2" s="161"/>
-      <c r="AQ2" s="161"/>
-      <c r="AR2" s="161"/>
-      <c r="AS2" s="161"/>
-      <c r="AT2" s="161"/>
-      <c r="AU2" s="161"/>
-      <c r="AV2" s="161"/>
-      <c r="AW2" s="161"/>
-      <c r="AX2" s="161"/>
-      <c r="AY2" s="161"/>
-      <c r="AZ2" s="162"/>
-      <c r="BA2" s="161">
+      <c r="AP2" s="162"/>
+      <c r="AQ2" s="162"/>
+      <c r="AR2" s="162"/>
+      <c r="AS2" s="162"/>
+      <c r="AT2" s="162"/>
+      <c r="AU2" s="162"/>
+      <c r="AV2" s="162"/>
+      <c r="AW2" s="162"/>
+      <c r="AX2" s="162"/>
+      <c r="AY2" s="162"/>
+      <c r="AZ2" s="163"/>
+      <c r="BA2" s="162">
         <v>27</v>
       </c>
-      <c r="BB2" s="161"/>
-      <c r="BC2" s="161"/>
-      <c r="BD2" s="161"/>
-      <c r="BE2" s="161"/>
-      <c r="BF2" s="161"/>
-      <c r="BG2" s="161"/>
-      <c r="BH2" s="161"/>
-      <c r="BI2" s="161"/>
-      <c r="BJ2" s="161"/>
-      <c r="BK2" s="161"/>
-      <c r="BL2" s="162"/>
+      <c r="BB2" s="162"/>
+      <c r="BC2" s="162"/>
+      <c r="BD2" s="162"/>
+      <c r="BE2" s="162"/>
+      <c r="BF2" s="162"/>
+      <c r="BG2" s="162"/>
+      <c r="BH2" s="162"/>
+      <c r="BI2" s="162"/>
+      <c r="BJ2" s="162"/>
+      <c r="BK2" s="162"/>
+      <c r="BL2" s="163"/>
     </row>
     <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="158"/>
-      <c r="C3" s="160"/>
-      <c r="D3" s="160"/>
+      <c r="B3" s="159"/>
+      <c r="C3" s="161"/>
+      <c r="D3" s="161"/>
       <c r="E3" s="22">
         <v>1</v>
       </c>
@@ -6410,39 +6410,39 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="166" t="s">
+      <c r="B2" s="167" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="170" t="s">
+      <c r="C2" s="171" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="170" t="s">
+      <c r="D2" s="171" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="168" t="s">
+      <c r="E2" s="169" t="s">
         <v>127</v>
       </c>
       <c r="F2" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="164" t="s">
+      <c r="G2" s="165" t="s">
         <v>114</v>
       </c>
-      <c r="H2" s="164"/>
-      <c r="I2" s="164"/>
-      <c r="J2" s="165"/>
-      <c r="K2" s="164" t="s">
+      <c r="H2" s="165"/>
+      <c r="I2" s="165"/>
+      <c r="J2" s="166"/>
+      <c r="K2" s="165" t="s">
         <v>183</v>
       </c>
-      <c r="L2" s="164"/>
-      <c r="M2" s="164"/>
-      <c r="N2" s="165"/>
+      <c r="L2" s="165"/>
+      <c r="M2" s="165"/>
+      <c r="N2" s="166"/>
     </row>
     <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="167"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="169"/>
+      <c r="B3" s="168"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="170"/>
       <c r="F3" s="99" t="s">
         <v>112</v>
       </c>
@@ -7185,30 +7185,30 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="166" t="s">
+      <c r="B2" s="167" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="170" t="s">
+      <c r="C2" s="171" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="170" t="s">
+      <c r="D2" s="171" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="168" t="s">
+      <c r="E2" s="169" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="164" t="s">
+      <c r="F2" s="165" t="s">
         <v>183</v>
       </c>
-      <c r="G2" s="164"/>
-      <c r="H2" s="164"/>
-      <c r="I2" s="165"/>
+      <c r="G2" s="165"/>
+      <c r="H2" s="165"/>
+      <c r="I2" s="166"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="167"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="169"/>
+      <c r="B3" s="168"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="170"/>
       <c r="F3" s="99" t="s">
         <v>115</v>
       </c>
@@ -7586,30 +7586,30 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="166" t="s">
+      <c r="B2" s="167" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="170" t="s">
+      <c r="C2" s="171" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="170" t="s">
+      <c r="D2" s="171" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="168" t="s">
+      <c r="E2" s="169" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="164" t="s">
+      <c r="F2" s="165" t="s">
         <v>228</v>
       </c>
-      <c r="G2" s="164"/>
-      <c r="H2" s="164"/>
-      <c r="I2" s="165"/>
+      <c r="G2" s="165"/>
+      <c r="H2" s="165"/>
+      <c r="I2" s="166"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="167"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="169"/>
+      <c r="B3" s="168"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="170"/>
       <c r="F3" s="99" t="s">
         <v>115</v>
       </c>
@@ -7993,30 +7993,30 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="166" t="s">
+      <c r="B2" s="167" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="170" t="s">
+      <c r="C2" s="171" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="170" t="s">
+      <c r="D2" s="171" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="168" t="s">
+      <c r="E2" s="169" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="164" t="s">
+      <c r="F2" s="165" t="s">
         <v>260</v>
       </c>
-      <c r="G2" s="164"/>
-      <c r="H2" s="164"/>
-      <c r="I2" s="165"/>
+      <c r="G2" s="165"/>
+      <c r="H2" s="165"/>
+      <c r="I2" s="166"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="167"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="169"/>
+      <c r="B3" s="168"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="170"/>
       <c r="F3" s="99" t="s">
         <v>295</v>
       </c>
@@ -8212,7 +8212,7 @@
       <c r="F13" s="116"/>
       <c r="G13" s="107"/>
       <c r="H13" s="135" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I13" s="136"/>
     </row>
@@ -8254,7 +8254,7 @@
         <v>269</v>
       </c>
       <c r="H15" s="139" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I15" s="136"/>
     </row>
@@ -8274,7 +8274,7 @@
       <c r="F16" s="116"/>
       <c r="G16" s="107"/>
       <c r="H16" s="135" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="I16" s="136"/>
     </row>
@@ -8295,7 +8295,7 @@
       <c r="G17" s="131" t="s">
         <v>261</v>
       </c>
-      <c r="H17" s="172" t="s">
+      <c r="H17" s="157" t="s">
         <v>303</v>
       </c>
       <c r="I17" s="138"/>
@@ -8336,7 +8336,7 @@
         <v>268</v>
       </c>
       <c r="H19" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I19" s="95"/>
     </row>
@@ -8370,6 +8370,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8399,30 +8400,30 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="166" t="s">
+      <c r="B2" s="167" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="170" t="s">
+      <c r="C2" s="171" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="170" t="s">
+      <c r="D2" s="171" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="168" t="s">
+      <c r="E2" s="169" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="164" t="s">
+      <c r="F2" s="165" t="s">
         <v>293</v>
       </c>
-      <c r="G2" s="164"/>
-      <c r="H2" s="164"/>
-      <c r="I2" s="165"/>
+      <c r="G2" s="165"/>
+      <c r="H2" s="165"/>
+      <c r="I2" s="166"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="167"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="169"/>
+      <c r="B3" s="168"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="170"/>
       <c r="F3" s="99" t="s">
         <v>294</v>
       </c>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -1868,6 +1868,14 @@
 - 온도 정합성 테스트 (10/20)
 - 제어기 선행품질 검증 현황 작성 (10/21)
 - 제어기 선행품질 검증 현황 관련 기아 오토랜드 방문 (10/23)
+  : 1. P2 단계 전까지 매 월 1회 제어기 검증 현황 관련 회의 진행 예정
+    2. 진행 단계 별로 이력 및 변경점 꾸준히 업데이트 해서 자료 회신 요청
+    3. Fail Safety 항목 공유 요청
+    4. 제어기 검증 프로세스 관련 자료 공유 요청
+    5. 컨버전 룰이 무엇인지에 대한 자료 공유 요청
+    6. S/W 검증 현황의 검증 항목별 LIST 자료 공유 요청
+    7. CPU / 메모리 부하율 관리 방안 재확인 요청
+    8. 고장 진단 로그 저장 가능 개수 재확인 요청
 - 설계 변경 진행 (~10/24)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8196,7 +8204,7 @@
       <c r="H12" s="140"/>
       <c r="I12" s="95"/>
     </row>
-    <row r="13" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="175.5" x14ac:dyDescent="0.3">
       <c r="B13" s="134" t="s">
         <v>63</v>
       </c>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="310">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1876,7 +1876,14 @@
     6. S/W 검증 현황의 검증 항목별 LIST 자료 공유 요청
     7. CPU / 메모리 부하율 관리 방안 재확인 요청
     8. 고장 진단 로그 저장 가능 개수 재확인 요청
-- 설계 변경 진행 (~10/24)</t>
+- 설계 변경 진행 (~10/24)
+- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- SWE.3 SDDS 후속 작업 (진행률 : 95%)
+- SPQA 프로세스 절차를 따라 ALM 등록 (~10/31)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8072,7 +8079,7 @@
       <c r="F5" s="116"/>
       <c r="G5" s="107"/>
       <c r="H5" s="125" t="s">
-        <v>281</v>
+        <v>309</v>
       </c>
       <c r="I5" s="137" t="s">
         <v>280</v>
@@ -8204,7 +8211,7 @@
       <c r="H12" s="140"/>
       <c r="I12" s="95"/>
     </row>
-    <row r="13" spans="1:9" ht="175.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="189" x14ac:dyDescent="0.3">
       <c r="B13" s="134" t="s">
         <v>63</v>
       </c>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="316">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1836,8 +1836,32 @@
   </si>
   <si>
     <t>[임제훈 사원]
+- SWE.3 SDDS 후속 작업 (진행률 : 95%)
+- SPQA 프로세스 절차를 따라 ALM 등록 (~10/31)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
 - LHD R로직 튜닝
 - RHD R로직 튜닝 (HVAC 미보유, 보류)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- LHD R로직 튜닝
+- RHD R로직 튜닝 (HVAC 미보유, 보류)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- LHD ESIR 계획서 작성 (~10/24)
+- R로직 튜닝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- LHD ESIR 계획서 작성 (~10/24)
+- R로직 튜닝</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1848,26 +1872,100 @@
   </si>
   <si>
     <t>[임제훈 사원]
-- LHD ESIR 계획서 작성 (~10/24)
-- R로직 튜닝</t>
+- 최소 작동 전압 범위 수정 후, EV HTR 개발팀 김민수 선임에게 전달 (~10/24)
+  : 0℃, -30℃ 환경에서 QV Air PTC와 160V, 170V 출력 비교 필요로 인한 요청</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[임제훈 사원]
-- Core Temp 튜닝 결과 확인 (~10/22)
-- HVAC RPM 확인 (~10/22)
-- R로직 튜닝 (~10/22)
-- 공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (~10/24)
-- ESIR 계획서 등록 (~10/24)
-- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/24)
-- 최신 승인도 확인 (~10/31)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- 온도 정합성 테스트 (10/20)
-- 제어기 선행품질 검증 현황 작성 (10/21)
-- 제어기 선행품질 검증 현황 관련 기아 오토랜드 방문 (10/23)
+- 설계 변경 진행 (~10/24)
+- 제어기 선행품질 검증 현황 관련 기아 오토랜드 방문 후 자료 회신 (~10/29)
+  : 1. P2 단계 전까지 매 월 1회 제어기 검증 현황 관련 회의 진행 예정
+    2. 진행 단계 별로 이력 및 변경점 꾸준히 업데이트 해서 자료 회신 요청
+    3. Fail Safety 항목 공유 요청
+    4. 제어기 검증 프로세스 관련 자료 공유 요청
+    5. 컨버전 룰이 무엇인지에 대한 자료 공유 요청
+    6. S/W 검증 현황의 검증 항목별 LIST 자료 공유 요청
+    7. CPU / 메모리 부하율 관리 방안 재확인 요청
+    8. 고장 진단 로그 저장 가능 개수 재확인 요청
+- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>온도 정합성 테스트 (10/20)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제어기 선행품질 검증 현황 작성 (10/21)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제어기 선행품질 검증 현황 관련 기아 오토랜드 방문 (10/23)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
   : 1. P2 단계 전까지 매 월 1회 제어기 검증 현황 관련 회의 진행 예정
     2. 진행 단계 별로 이력 및 변경점 꾸준히 업데이트 해서 자료 회신 요청
     3. Fail Safety 항목 공유 요청
@@ -1878,11 +1976,80 @@
     8. 고장 진단 로그 저장 가능 개수 재확인 요청
 - 설계 변경 진행 (~10/24)
 - 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Core Temp 튜닝 결과 확인 (~10/22)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HVAC RPM 확인 (~10/22)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- R로직 튜닝 (~10/22)
+- 공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (~10/24)
+- ESIR 계획서 등록 (~10/24)
+- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/24)
+- 최신 승인도 확인 (~10/31)</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[임제훈 사원]
-- SWE.3 SDDS 후속 작업 (진행률 : 95%)
+- 공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (~10/24)
+- R로직 튜닝 (~10/28)
+- ESIR 계획서 등록 (~10/28)
+- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/28)
+- 최신 승인도 확인 (~10/31)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- SWE.3 SDDS 후속 작업 (진행률 : 100%)
 - SPQA 프로세스 절차를 따라 ALM 등록 (~10/31)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8079,10 +8246,10 @@
       <c r="F5" s="116"/>
       <c r="G5" s="107"/>
       <c r="H5" s="125" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="I5" s="137" t="s">
-        <v>280</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -8227,9 +8394,11 @@
       <c r="F13" s="116"/>
       <c r="G13" s="107"/>
       <c r="H13" s="135" t="s">
-        <v>308</v>
-      </c>
-      <c r="I13" s="136"/>
+        <v>312</v>
+      </c>
+      <c r="I13" s="136" t="s">
+        <v>311</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="133" t="s">
@@ -8247,9 +8416,11 @@
       <c r="F14" s="116"/>
       <c r="G14" s="107"/>
       <c r="H14" s="135" t="s">
-        <v>304</v>
-      </c>
-      <c r="I14" s="136"/>
+        <v>305</v>
+      </c>
+      <c r="I14" s="136" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
       <c r="B15" s="133" t="s">
@@ -8269,9 +8440,11 @@
         <v>269</v>
       </c>
       <c r="H15" s="139" t="s">
-        <v>306</v>
-      </c>
-      <c r="I15" s="136"/>
+        <v>307</v>
+      </c>
+      <c r="I15" s="136" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="16" spans="1:9" ht="108" x14ac:dyDescent="0.3">
       <c r="B16" s="133" t="s">
@@ -8289,9 +8462,11 @@
       <c r="F16" s="116"/>
       <c r="G16" s="107"/>
       <c r="H16" s="135" t="s">
-        <v>307</v>
-      </c>
-      <c r="I16" s="136"/>
+        <v>313</v>
+      </c>
+      <c r="I16" s="136" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="132" t="s">
@@ -8351,9 +8526,11 @@
         <v>268</v>
       </c>
       <c r="H19" s="135" t="s">
-        <v>305</v>
-      </c>
-      <c r="I19" s="95"/>
+        <v>309</v>
+      </c>
+      <c r="I19" s="136" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="145" t="s">

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -2040,17 +2040,18 @@
   </si>
   <si>
     <t>[임제훈 사원]
-- 공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (~10/24)
+- SWE.3 SDDS 후속 작업 (진행률 : 100%)
+- SPQA 프로세스 절차를 따라 ALM 등록 (~10/31)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
 - R로직 튜닝 (~10/28)
 - ESIR 계획서 등록 (~10/28)
 - 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/28)
+- 공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (10/30)
+  : 휴가 중, 목요일 출근 예정, 이 때 메일로 다시 문의
 - 최신 승인도 확인 (~10/31)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- SWE.3 SDDS 후속 작업 (진행률 : 100%)
-- SPQA 프로세스 절차를 따라 ALM 등록 (~10/31)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8249,7 +8250,7 @@
         <v>304</v>
       </c>
       <c r="I5" s="137" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -8465,7 +8466,7 @@
         <v>313</v>
       </c>
       <c r="I16" s="136" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -1874,21 +1874,6 @@
     <t>[임제훈 사원]
 - 최소 작동 전압 범위 수정 후, EV HTR 개발팀 김민수 선임에게 전달 (~10/24)
   : 0℃, -30℃ 환경에서 QV Air PTC와 160V, 170V 출력 비교 필요로 인한 요청</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- 설계 변경 진행 (~10/24)
-- 제어기 선행품질 검증 현황 관련 기아 오토랜드 방문 후 자료 회신 (~10/29)
-  : 1. P2 단계 전까지 매 월 1회 제어기 검증 현황 관련 회의 진행 예정
-    2. 진행 단계 별로 이력 및 변경점 꾸준히 업데이트 해서 자료 회신 요청
-    3. Fail Safety 항목 공유 요청
-    4. 제어기 검증 프로세스 관련 자료 공유 요청
-    5. 컨버전 룰이 무엇인지에 대한 자료 공유 요청
-    6. S/W 검증 현황의 검증 항목별 LIST 자료 공유 요청
-    7. CPU / 메모리 부하율 관리 방안 재확인 요청
-    8. 고장 진단 로그 저장 가능 개수 재확인 요청
-- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2046,6 +2031,24 @@
   </si>
   <si>
     <t>[임제훈 사원]
+- 설계 변경 진행 (~10/24)
+- CPU 및 메모리 부하율 관리 대책 르네사스 문의 (~10/27)
+- 사이버 보안 항목 QV와 비교 및 리스트업 후 공조시스템설계팀 회신 (~10/27)
+- 제어기 선행품질 검증 현황 관련 기아 오토랜드 방문 후 자료 회신 (~10/29)
+  : 1. P2 단계 전까지 매 월 1회 제어기 검증 현황 관련 회의 진행 예정
+    2. 진행 단계 별로 이력 및 변경점 꾸준히 업데이트 해서 자료 회신 요청
+    3. Fail Safety 항목 공유 요청
+    4. 제어기 검증 프로세스 관련 자료 공유 요청
+    5. 컨버전 룰이 무엇인지에 대한 자료 공유 요청
+    6. S/W 검증 현황의 검증 항목별 LIST 자료 공유 요청
+    7. CPU / 메모리 부하율 관리 방안 재확인 요청
+    8. 고장 진단 로그 저장 가능 개수 재확인 요청
+- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- ESIR 일정에 맞춰서 5가지 항목 다 가능한지 파악하기 (~10/27)
 - R로직 튜닝 (~10/28)
 - ESIR 계획서 등록 (~10/28)
 - 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/28)
@@ -8250,7 +8253,7 @@
         <v>304</v>
       </c>
       <c r="I5" s="137" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -8395,10 +8398,10 @@
       <c r="F13" s="116"/>
       <c r="G13" s="107"/>
       <c r="H13" s="135" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I13" s="136" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -8463,7 +8466,7 @@
       <c r="F16" s="116"/>
       <c r="G16" s="107"/>
       <c r="H16" s="135" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I16" s="136" t="s">
         <v>315</v>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -1848,26 +1848,8 @@
   </si>
   <si>
     <t>[임제훈 사원]
-- LHD R로직 튜닝
-- RHD R로직 튜닝 (HVAC 미보유, 보류)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
 - LHD ESIR 계획서 작성 (~10/24)
 - R로직 튜닝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- LHD ESIR 계획서 작성 (~10/24)
-- R로직 튜닝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- 최소 작동 전압 범위 수정 후, EV HTR 개발팀 김민수 선임에게 전달 (~10/24)
-  : 0℃, -30℃ 환경에서 QV Air PTC와 160V, 170V 출력 비교 필요로 인한 요청</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1965,6 +1947,42 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>[임제훈 사원]
+- SWE.3 SDDS 후속 작업 (진행률 : 100%)
+- SPQA 프로세스 절차를 따라 ALM 등록 (~10/31)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- CPU 및 메모리 부하율 관리 대책 르네사스 문의 (~10/27)
+- 사이버 보안 항목 QV와 비교 및 리스트업 후 공조시스템설계팀 회신 (~10/29)
+- 제어기 선행품질 검증 현황 관련 기아 오토랜드 방문 후 자료 회신 (~10/29)
+  : 1. P2 단계 전까지 매 월 1회 제어기 검증 현황 관련 회의 진행 예정
+    2. 진행 단계 별로 이력 및 변경점 꾸준히 업데이트 해서 자료 회신 요청
+    3. Fail Safety 항목 공유 요청
+    4. 제어기 검증 프로세스 관련 자료 공유 요청
+    5. 컨버전 룰이 무엇인지에 대한 자료 공유 요청
+    6. S/W 검증 현황의 검증 항목별 LIST 자료 공유 요청
+    7. CPU / 메모리 부하율 관리 방안 재확인 요청
+    8. 고장 진단 로그 저장 가능 개수 재확인 요청
+- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)
+- 설계 변경 진행 (~11/10)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- LHD ESIR 계획서 (기구, HW 업로드 후, 행추가 예정) (~10/31)
+- R로직 튜닝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 최소 작동 전압 범위 수정 후, EV HTR 개발팀 김민수 선임에게 전달
+  : 0℃, -30℃ 환경에서 QV Air PTC와 160V, 170V 출력 비교 필요로 인한 요청
+  : 다른 작업 먼저 한다고 함, 추후 진행 예정이고 일정 미정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">[임제훈 사원]
 - </t>
@@ -2015,46 +2033,504 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-- R로직 튜닝 (~10/22)
-- 공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (~10/24)
-- ESIR 계획서 등록 (~10/24)
-- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/24)
-- 최신 승인도 확인 (~10/31)</t>
+</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>로직</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>튜닝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (~10/22)
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공조시스템설계팀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>김동환</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>연구원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사이버보안</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>일정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>재문의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (~10/24)
+- ESIR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>계획서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>등록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (~10/24)
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제어사양서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>고장진단</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사양</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>로직검증</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>체크리스트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>갱신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (~10/24)
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>최신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>승인도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (~10/31)</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[임제훈 사원]
-- SWE.3 SDDS 후속 작업 (진행률 : 100%)
-- SPQA 프로세스 절차를 따라 ALM 등록 (~10/31)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- 설계 변경 진행 (~10/24)
-- CPU 및 메모리 부하율 관리 대책 르네사스 문의 (~10/27)
-- 사이버 보안 항목 QV와 비교 및 리스트업 후 공조시스템설계팀 회신 (~10/27)
-- 제어기 선행품질 검증 현황 관련 기아 오토랜드 방문 후 자료 회신 (~10/29)
-  : 1. P2 단계 전까지 매 월 1회 제어기 검증 현황 관련 회의 진행 예정
-    2. 진행 단계 별로 이력 및 변경점 꾸준히 업데이트 해서 자료 회신 요청
-    3. Fail Safety 항목 공유 요청
-    4. 제어기 검증 프로세스 관련 자료 공유 요청
-    5. 컨버전 룰이 무엇인지에 대한 자료 공유 요청
-    6. S/W 검증 현황의 검증 항목별 LIST 자료 공유 요청
-    7. CPU / 메모리 부하율 관리 방안 재확인 요청
-    8. 고장 진단 로그 저장 가능 개수 재확인 요청
-- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- ESIR 일정에 맞춰서 5가지 항목 다 가능한지 파악하기 (~10/27)
-- R로직 튜닝 (~10/28)
-- ESIR 계획서 등록 (~10/28)
-- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/28)
+- R로직 튜닝 (~10/27)
+- ESIR 일정에 맞춰서 5가지 항목 다 가능한지 파악하기 (~10/29)
 - 공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (10/30)
   : 휴가 중, 목요일 출근 예정, 이 때 메일로 다시 문의
+- ESIR 계획서 등록 (~10/31)
+- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)
 - 최신 승인도 확인 (~10/31)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- BJ PTC HTR 벤치 시험 합동 평가 일정 (10/29 예정)
+  : SW 대응은 딱히 없을 것 같다고 했지만, 결과나 진행 사항 파악 필요
+- LHD R로직 튜닝
+- RHD R로직 튜닝 (HVAC 미보유, 보류)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2065,7 +2541,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2197,6 +2673,14 @@
     </font>
     <font>
       <strike/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
@@ -8253,7 +8737,7 @@
         <v>304</v>
       </c>
       <c r="I5" s="137" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -8398,13 +8882,13 @@
       <c r="F13" s="116"/>
       <c r="G13" s="107"/>
       <c r="H13" s="135" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="I13" s="136" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
       <c r="B14" s="133" t="s">
         <v>74</v>
       </c>
@@ -8423,7 +8907,7 @@
         <v>305</v>
       </c>
       <c r="I14" s="136" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -8444,10 +8928,10 @@
         <v>269</v>
       </c>
       <c r="H15" s="139" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I15" s="136" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="108" x14ac:dyDescent="0.3">
@@ -8466,10 +8950,10 @@
       <c r="F16" s="116"/>
       <c r="G16" s="107"/>
       <c r="H16" s="135" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I16" s="136" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -8530,10 +9014,10 @@
         <v>268</v>
       </c>
       <c r="H19" s="135" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="I19" s="136" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -2516,21 +2516,26 @@
   </si>
   <si>
     <t>[임제훈 사원]
+- BJ PTC HTR 벤치 시험 합동 평가 일정 (10/29 예정)
+  : SW 대응은 딱히 없을 것 같다고 했지만, 결과나 진행 사항 파악 필요
+- LHD R로직 튜닝
+- RHD R로직 튜닝 (HVAC 미보유, 보류)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
 - R로직 튜닝 (~10/27)
 - ESIR 일정에 맞춰서 5가지 항목 다 가능한지 파악하기 (~10/29)
 - 공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (10/30)
   : 휴가 중, 목요일 출근 예정, 이 때 메일로 다시 문의
+- ES 규격 대로 15초 내로 목표 전력 도달 SW로 변경 (~10/29)
+  : Softstart enable 0으로 변경
+  : Sofftstart 0일 때, R로직 확인, 전력 구간 별 칼로리와 CAN 출력 차이 비교
 - ESIR 계획서 등록 (~10/31)
 - 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)
-- 최신 승인도 확인 (~10/31)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- BJ PTC HTR 벤치 시험 합동 평가 일정 (10/29 예정)
-  : SW 대응은 딱히 없을 것 같다고 했지만, 결과나 진행 사항 파악 필요
-- LHD R로직 튜닝
-- RHD R로직 튜닝 (HVAC 미보유, 보류)</t>
+- 최신 승인도 확인 (~10/31)
+- 제작사양서 배포 준비 (~10/31)
+  : SW 파일, 제어사양서</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8907,7 +8912,7 @@
         <v>305</v>
       </c>
       <c r="I14" s="136" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -8934,7 +8939,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="108" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="175.5" x14ac:dyDescent="0.3">
       <c r="B16" s="133" t="s">
         <v>86</v>
       </c>
@@ -8953,7 +8958,7 @@
         <v>313</v>
       </c>
       <c r="I16" s="136" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\일정\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\PROJECT\Gitlab\HMC\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="317">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1950,29 +1950,6 @@
     <t>[임제훈 사원]
 - SWE.3 SDDS 후속 작업 (진행률 : 100%)
 - SPQA 프로세스 절차를 따라 ALM 등록 (~10/31)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- CPU 및 메모리 부하율 관리 대책 르네사스 문의 (~10/27)
-- 사이버 보안 항목 QV와 비교 및 리스트업 후 공조시스템설계팀 회신 (~10/29)
-- 제어기 선행품질 검증 현황 관련 기아 오토랜드 방문 후 자료 회신 (~10/29)
-  : 1. P2 단계 전까지 매 월 1회 제어기 검증 현황 관련 회의 진행 예정
-    2. 진행 단계 별로 이력 및 변경점 꾸준히 업데이트 해서 자료 회신 요청
-    3. Fail Safety 항목 공유 요청
-    4. 제어기 검증 프로세스 관련 자료 공유 요청
-    5. 컨버전 룰이 무엇인지에 대한 자료 공유 요청
-    6. S/W 검증 현황의 검증 항목별 LIST 자료 공유 요청
-    7. CPU / 메모리 부하율 관리 방안 재확인 요청
-    8. 고장 진단 로그 저장 가능 개수 재확인 요청
-- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)
-- 설계 변경 진행 (~11/10)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- LHD ESIR 계획서 (기구, HW 업로드 후, 행추가 예정) (~10/31)
-- R로직 튜닝</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2535,7 +2512,42 @@
 - 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)
 - 최신 승인도 확인 (~10/31)
 - 제작사양서 배포 준비 (~10/31)
-  : SW 파일, 제어사양서</t>
+  : SW 파일, 제어사양서
+[김진겸 사원]
+- R로직 튜닝 완료, Softstart 해제 이후 영향성 평가 진행(~10/30)
+- LV / HV 정합성 확인 완료, 전류 튜닝 진행 중(~10/30)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- CPU 및 메모리 부하율 관리 대책 르네사스 문의 (~10/27)
+- 사이버 보안 항목 QV와 비교 및 리스트업 후 공조시스템설계팀 회신 (~10/29)
+- 제어기 선행품질 검증 현황 관련 기아 오토랜드 방문 후 자료 회신 (~10/29)
+  : 1. P2 단계 전까지 매 월 1회 제어기 검증 현황 관련 회의 진행 예정
+    2. 진행 단계 별로 이력 및 변경점 꾸준히 업데이트 해서 자료 회신 요청
+    3. Fail Safety 항목 공유 요청
+    4. 제어기 검증 프로세스 관련 자료 공유 요청
+    5. 컨버전 룰이 무엇인지에 대한 자료 공유 요청
+    6. S/W 검증 현황의 검증 항목별 LIST 자료 공유 요청
+    7. CPU / 메모리 부하율 관리 방안 재확인 요청
+    8. 고장 진단 로그 저장 가능 개수 재확인 요청
+- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)
+- 설계 변경 진행 (~11/10)
+[김진겸 사원]
+- V01.02.00 기본 동작 점검(10/29 완료)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- LHD ESIR 계획서 (기구, HW 업로드 후, 행추가 예정) (~10/31)
+- R로직 튜닝
+[김진겸 사원]
+- LHD 사양 R로직 튜닝 예정(11월 중)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[김진겸 사원]
+- HVAC 요청 중(EV HTR 개발팀 김민수 선임)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8779,7 +8791,9 @@
       <c r="F7" s="116"/>
       <c r="G7" s="107"/>
       <c r="H7" s="91"/>
-      <c r="I7" s="95"/>
+      <c r="I7" s="136" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="8" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="154" t="s">
@@ -8871,7 +8885,7 @@
       <c r="H12" s="140"/>
       <c r="I12" s="95"/>
     </row>
-    <row r="13" spans="1:9" ht="189" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="256.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="134" t="s">
         <v>63</v>
       </c>
@@ -8890,10 +8904,10 @@
         <v>308</v>
       </c>
       <c r="I13" s="136" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="133" t="s">
         <v>74</v>
       </c>
@@ -8912,10 +8926,10 @@
         <v>305</v>
       </c>
       <c r="I14" s="136" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="133" t="s">
         <v>56</v>
       </c>
@@ -8936,10 +8950,10 @@
         <v>306</v>
       </c>
       <c r="I15" s="136" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="175.5" x14ac:dyDescent="0.3">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="270" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="133" t="s">
         <v>86</v>
       </c>
@@ -8955,10 +8969,10 @@
       <c r="F16" s="116"/>
       <c r="G16" s="107"/>
       <c r="H16" s="135" t="s">
+        <v>311</v>
+      </c>
+      <c r="I16" s="136" t="s">
         <v>313</v>
-      </c>
-      <c r="I16" s="136" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -9022,7 +9036,7 @@
         <v>307</v>
       </c>
       <c r="I19" s="136" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\일정\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Task\000_PJT\111_PTC\1.doc\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="318">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1832,12 +1832,6 @@
   <si>
     <t>[임제훈 사원]
 - LHD, RHD 사양 3D 모델링 수령 (10/21)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- SWE.3 SDDS 후속 작업 (진행률 : 95%)
-- SPQA 프로세스 절차를 따라 ALM 등록 (~10/31)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1944,12 +1938,6 @@
 - 설계 변경 진행 (~10/24)
 - 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- SWE.3 SDDS 후속 작업 (진행률 : 100%)
-- SPQA 프로세스 절차를 따라 ALM 등록 (~10/31)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2538,6 +2526,32 @@
   : SW 파일, 제어사양서</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>[임제훈 사원]
+- SWE.3 SDDS 후속 작업 (진행률 : 100%)
+- SPQA 프로세스 절차를 따라 ALM 등록 (~10/31)
+[조현진 전임]
+- SWE.1, 2, 3 등록에 맞추어 SWE. 4, 5, 6 ALM 등록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[조현진 전임]
+- 10월 31일 현대자동차 남양연구소 난방평가 요청(from. 김민수 선임)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[조현진 전임]
+- ESIR 대응 산출물 작성 및 전달 (진행률 : 100%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- SWE.3 SDDS 후속 작업 (진행률 : 95%)
+- SPQA 프로세스 절차를 따라 ALM 등록 (~10/31)
+[조현진 전임]
+- 조치사항에 맞추어 Software Test Plan 수정작업 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2770,7 +2784,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="80">
+  <borders count="81">
     <border>
       <left/>
       <right/>
@@ -3869,6 +3883,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3890,7 +3917,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="173">
+  <cellXfs count="174">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4409,6 +4436,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="80" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -8723,7 +8753,7 @@
       <c r="H4" s="90"/>
       <c r="I4" s="94"/>
     </row>
-    <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
       <c r="B5" s="156" t="s">
         <v>182</v>
       </c>
@@ -8739,10 +8769,10 @@
       <c r="F5" s="116"/>
       <c r="G5" s="107"/>
       <c r="H5" s="125" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="I5" s="137" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -8760,8 +8790,10 @@
       </c>
       <c r="F6" s="125"/>
       <c r="G6" s="125"/>
-      <c r="H6" s="125"/>
-      <c r="I6" s="137"/>
+      <c r="H6" s="135" t="s">
+        <v>316</v>
+      </c>
+      <c r="I6" s="173"/>
     </row>
     <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="154" t="s">
@@ -8779,7 +8811,9 @@
       <c r="F7" s="116"/>
       <c r="G7" s="107"/>
       <c r="H7" s="91"/>
-      <c r="I7" s="95"/>
+      <c r="I7" s="136" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="8" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="154" t="s">
@@ -8887,10 +8921,10 @@
       <c r="F13" s="116"/>
       <c r="G13" s="107"/>
       <c r="H13" s="135" t="s">
+        <v>307</v>
+      </c>
+      <c r="I13" s="136" t="s">
         <v>308</v>
-      </c>
-      <c r="I13" s="136" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -8909,10 +8943,10 @@
       <c r="F14" s="116"/>
       <c r="G14" s="107"/>
       <c r="H14" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I14" s="136" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -8933,10 +8967,10 @@
         <v>269</v>
       </c>
       <c r="H15" s="139" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I15" s="136" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="175.5" x14ac:dyDescent="0.3">
@@ -8955,10 +8989,10 @@
       <c r="F16" s="116"/>
       <c r="G16" s="107"/>
       <c r="H16" s="135" t="s">
+        <v>311</v>
+      </c>
+      <c r="I16" s="136" t="s">
         <v>313</v>
-      </c>
-      <c r="I16" s="136" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -9019,10 +9053,10 @@
         <v>268</v>
       </c>
       <c r="H19" s="135" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I19" s="136" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\PROJECT\Gitlab\HMC\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\일정\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="319">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1944,19 +1944,6 @@
 - 설계 변경 진행 (~10/24)
 - 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- SWE.3 SDDS 후속 작업 (진행률 : 100%)
-- SPQA 프로세스 절차를 따라 ALM 등록 (~10/31)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- 최소 작동 전압 범위 수정 후, EV HTR 개발팀 김민수 선임에게 전달
-  : 0℃, -30℃ 환경에서 QV Air PTC와 160V, 170V 출력 비교 필요로 인한 요청
-  : 다른 작업 먼저 한다고 함, 추후 진행 예정이고 일정 미정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2493,33 +2480,6 @@
   </si>
   <si>
     <t>[임제훈 사원]
-- BJ PTC HTR 벤치 시험 합동 평가 일정 (10/29 예정)
-  : SW 대응은 딱히 없을 것 같다고 했지만, 결과나 진행 사항 파악 필요
-- LHD R로직 튜닝
-- RHD R로직 튜닝 (HVAC 미보유, 보류)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- R로직 튜닝 (~10/27)
-- ESIR 일정에 맞춰서 5가지 항목 다 가능한지 파악하기 (~10/29)
-- 공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (10/30)
-  : 휴가 중, 목요일 출근 예정, 이 때 메일로 다시 문의
-- ES 규격 대로 15초 내로 목표 전력 도달 SW로 변경 (~10/29)
-  : Softstart enable 0으로 변경
-  : Sofftstart 0일 때, R로직 확인, 전력 구간 별 칼로리와 CAN 출력 차이 비교
-- ESIR 계획서 등록 (~10/31)
-- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)
-- 최신 승인도 확인 (~10/31)
-- 제작사양서 배포 준비 (~10/31)
-  : SW 파일, 제어사양서
-[김진겸 사원]
-- R로직 튜닝 완료, Softstart 해제 이후 영향성 평가 진행(~10/30)
-- LV / HV 정합성 확인 완료, 전류 튜닝 진행 중(~10/30)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
 - CPU 및 메모리 부하율 관리 대책 르네사스 문의 (~10/27)
 - 사이버 보안 항목 QV와 비교 및 리스트업 후 공조시스템설계팀 회신 (~10/29)
 - 제어기 선행품질 검증 현황 관련 기아 오토랜드 방문 후 자료 회신 (~10/29)
@@ -2538,16 +2498,73 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>[김진겸 사원]
+- HVAC 요청 중(EV HTR 개발팀 김민수 선임)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>[임제훈 사원]
-- LHD ESIR 계획서 (기구, HW 업로드 후, 행추가 예정) (~10/31)
+- BJ PTC HTR 벤치 시험 합동 평가 일정 (10/29 예정)
+  : SW 대응은 딱히 없을 것 같다고 했지만, 결과나 진행 사항 파악 필요
+  : 오늘 결과를 바탕으로 HKMC가 상위 보고 후 진행 방향 결정 후 진행 예정
+- LHD R로직 튜닝
+- RHD R로직 튜닝 (HVAC 미보유, 보류)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- LHD ESIR 계획서 (10/29)
+  : 90700-00, 95480-00 행추가 해서 ESIR 계획서 등록 완료
 - R로직 튜닝
 [김진겸 사원]
 - LHD 사양 R로직 튜닝 예정(11월 중)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[김진겸 사원]
-- HVAC 요청 중(EV HTR 개발팀 김민수 선임)</t>
+    <t>[임제훈 사원]
+- LV, HV 전압 값 확인 완료 (10/28)
+- ESIR 일정에 맞춰서 5가지 항목 다 가능한지 파악하기 (~10/29)
+- ES 규격 대로 15초 내로 목표 전력 도달 SW로 변경 (~10/29)
+  : Softstart enable 0으로 변경
+  : 정우헌 책임에게 softstart 미적용 SW로 배포 진행 메일 송신 후 확인 요청 완료
+- R로직 튜닝 (~10/29)
+  : Softsatrt enable 0으로 변경 후 재확인 및 튜닝
+- 전류 튜닝 (~10/29)
+  : CAN 데이터와 칼로리 상 전력 차이 확인
+  : 오차 많이 발생 시, 수석님 확인 후 전류 튜닝 진행
+- 공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (~10/30)
+  : 휴가 중, 목요일 출근 예정, 이 때 메일로 다시 문의
+- ESIR 계획서 등록 (~10/31)
+- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)
+- 최신 승인도 확인 (~10/31)
+- 제작사양서 배포 준비 (~10/31)
+  : SW 파일, 제어사양서
+[김진겸 사원]
+- R로직 튜닝 완료, Softstart 해제 이후 영향성 평가 진행(~10/30)
+- LV / HV 정합성 확인 완료, 전류 튜닝 진행 중(~10/30)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 이슈 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- AY LHD PCB 생산 후, SU2i 세팅으로 EOL 진행 시, NG 문의 (10/28)
+  : SU2i 버전 01.01, AY LHD 01.00으로 버전 다르다고 답변 완료
+- 최소 작동 전압 범위 수정 후, EV HTR 개발팀 김민수 선임에게 전달
+  : 0℃, -30℃ 환경에서 QV Air PTC와 160V, 170V 출력 비교 필요로 인한 요청
+  : 다른 작업 먼저 한다고 함, 추후 진행 예정이고 일정 미정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 이슈 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- SWE.3 SDDS 후속 작업 (진행률 : 97%)
+- SPQA 프로세스 절차를 따라 ALM 등록 (~11/06)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3902,7 +3919,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="173">
+  <cellXfs count="174">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4421,6 +4438,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="72" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -8754,7 +8774,7 @@
         <v>304</v>
       </c>
       <c r="I5" s="137" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -8792,7 +8812,7 @@
       <c r="G7" s="107"/>
       <c r="H7" s="91"/>
       <c r="I7" s="136" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8904,10 +8924,10 @@
         <v>308</v>
       </c>
       <c r="I13" s="136" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="81" x14ac:dyDescent="0.3">
       <c r="B14" s="133" t="s">
         <v>74</v>
       </c>
@@ -8950,10 +8970,10 @@
         <v>306</v>
       </c>
       <c r="I15" s="136" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="270" customHeight="1" x14ac:dyDescent="0.3">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="317.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="133" t="s">
         <v>86</v>
       </c>
@@ -8969,10 +8989,10 @@
       <c r="F16" s="116"/>
       <c r="G16" s="107"/>
       <c r="H16" s="135" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="I16" s="136" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -8995,7 +9015,9 @@
       <c r="H17" s="157" t="s">
         <v>303</v>
       </c>
-      <c r="I17" s="138"/>
+      <c r="I17" s="173" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="18" spans="2:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="133" t="s">
@@ -9036,7 +9058,7 @@
         <v>307</v>
       </c>
       <c r="I19" s="136" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -9057,7 +9079,9 @@
         <v>267</v>
       </c>
       <c r="H20" s="150"/>
-      <c r="I20" s="151"/>
+      <c r="I20" s="149" t="s">
+        <v>317</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="320">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2536,11 +2536,6 @@
   </si>
   <si>
     <t>[조현진 전임]
-- 10월 31일 현대자동차 남양연구소 난방평가 요청(from. 김민수 선임)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[조현진 전임]
 - ESIR 대응 산출물 작성 및 전달 (진행률 : 100%)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2550,6 +2545,32 @@
 - SPQA 프로세스 절차를 따라 ALM 등록 (~10/31)
 [조현진 전임]
 - 조치사항에 맞추어 Software Test Plan 수정작업 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[공조시스템설계팀] 
+김응영 책임 010-7635-0265
+key@hyundai.com
+이웅기 연구원 010-8427-8230
+lwg8230@hyundai.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[조현진 전임]
+- 10월 31일 현대자동차 남양연구소 난방평가 요청(from. 김민수 선임)
+  1) T-Car와 Proto 토출온 20도 차이(HVAC 문제로 파악됨)
+  2) 난방평가 목적
+    : 차량 실측 소비전력과 히터 피드백 소비전력 비교,
+      변경된 HVAC으로 인한 R-logic 영향성평가(오실레이션 여부 확인)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[조현진 전임]
+- 10월 29일 공조시스템 설계팀 김응영 책임, 이웅기 연구원 주관 회의 사항
+   1) SVm 대비 SX3 lod 길이 축소 -&gt; 성능 만족을 위해 rod 1개 추가
+      제어기 크기 증가 -&gt; 제어기가 차량 상 카울 크로스바 영역 침범
+      전체적인 히터 사이즈 축소 주기적으로 요청
+   2) 11월 6일 목요일까지 변경된 모델링 데이터 전달요청</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4392,6 +4413,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="80" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4436,9 +4460,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="80" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -4477,7 +4498,7 @@
       <xdr:rowOff>790452</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>404500</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>1442356</xdr:rowOff>
@@ -4509,16 +4530,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>229120</xdr:colOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>310763</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>204107</xdr:rowOff>
+      <xdr:rowOff>353786</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>259133</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>163285</xdr:rowOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>340776</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>108857</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -4527,8 +4548,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="24422620" y="204107"/>
-          <a:ext cx="30013" cy="19839214"/>
+          <a:off x="12502763" y="353786"/>
+          <a:ext cx="30013" cy="24696964"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -5045,7 +5066,8 @@
     <col min="2" max="2" width="18.875" customWidth="1"/>
     <col min="3" max="3" width="28.375" customWidth="1"/>
     <col min="4" max="4" width="30.75" customWidth="1"/>
-    <col min="5" max="34" width="8.375" customWidth="1"/>
+    <col min="5" max="28" width="8.375" hidden="1" customWidth="1"/>
+    <col min="29" max="34" width="8.375" customWidth="1"/>
     <col min="35" max="35" width="10.375" customWidth="1"/>
     <col min="36" max="64" width="8.375" customWidth="1"/>
   </cols>
@@ -5061,90 +5083,90 @@
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="158" t="s">
+      <c r="B2" s="159" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="160" t="s">
+      <c r="C2" s="161" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="160" t="s">
+      <c r="D2" s="161" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="164">
+      <c r="E2" s="165">
         <v>23</v>
       </c>
-      <c r="F2" s="162"/>
-      <c r="G2" s="162"/>
-      <c r="H2" s="162"/>
-      <c r="I2" s="162"/>
-      <c r="J2" s="162"/>
-      <c r="K2" s="162"/>
-      <c r="L2" s="162"/>
-      <c r="M2" s="162"/>
-      <c r="N2" s="162"/>
-      <c r="O2" s="162"/>
-      <c r="P2" s="162"/>
-      <c r="Q2" s="162">
+      <c r="F2" s="163"/>
+      <c r="G2" s="163"/>
+      <c r="H2" s="163"/>
+      <c r="I2" s="163"/>
+      <c r="J2" s="163"/>
+      <c r="K2" s="163"/>
+      <c r="L2" s="163"/>
+      <c r="M2" s="163"/>
+      <c r="N2" s="163"/>
+      <c r="O2" s="163"/>
+      <c r="P2" s="163"/>
+      <c r="Q2" s="163">
         <v>24</v>
       </c>
-      <c r="R2" s="162"/>
-      <c r="S2" s="162"/>
-      <c r="T2" s="162"/>
-      <c r="U2" s="162"/>
-      <c r="V2" s="162"/>
-      <c r="W2" s="162"/>
-      <c r="X2" s="162"/>
-      <c r="Y2" s="162"/>
-      <c r="Z2" s="162"/>
-      <c r="AA2" s="162"/>
-      <c r="AB2" s="162"/>
-      <c r="AC2" s="162">
+      <c r="R2" s="163"/>
+      <c r="S2" s="163"/>
+      <c r="T2" s="163"/>
+      <c r="U2" s="163"/>
+      <c r="V2" s="163"/>
+      <c r="W2" s="163"/>
+      <c r="X2" s="163"/>
+      <c r="Y2" s="163"/>
+      <c r="Z2" s="163"/>
+      <c r="AA2" s="163"/>
+      <c r="AB2" s="163"/>
+      <c r="AC2" s="163">
         <v>25</v>
       </c>
-      <c r="AD2" s="162"/>
-      <c r="AE2" s="162"/>
-      <c r="AF2" s="162"/>
-      <c r="AG2" s="162"/>
-      <c r="AH2" s="162"/>
-      <c r="AI2" s="162"/>
-      <c r="AJ2" s="162"/>
-      <c r="AK2" s="162"/>
-      <c r="AL2" s="162"/>
-      <c r="AM2" s="162"/>
-      <c r="AN2" s="162"/>
-      <c r="AO2" s="162">
+      <c r="AD2" s="163"/>
+      <c r="AE2" s="163"/>
+      <c r="AF2" s="163"/>
+      <c r="AG2" s="163"/>
+      <c r="AH2" s="163"/>
+      <c r="AI2" s="163"/>
+      <c r="AJ2" s="163"/>
+      <c r="AK2" s="163"/>
+      <c r="AL2" s="163"/>
+      <c r="AM2" s="163"/>
+      <c r="AN2" s="163"/>
+      <c r="AO2" s="163">
         <v>26</v>
       </c>
-      <c r="AP2" s="162"/>
-      <c r="AQ2" s="162"/>
-      <c r="AR2" s="162"/>
-      <c r="AS2" s="162"/>
-      <c r="AT2" s="162"/>
-      <c r="AU2" s="162"/>
-      <c r="AV2" s="162"/>
-      <c r="AW2" s="162"/>
-      <c r="AX2" s="162"/>
-      <c r="AY2" s="162"/>
-      <c r="AZ2" s="163"/>
-      <c r="BA2" s="162">
+      <c r="AP2" s="163"/>
+      <c r="AQ2" s="163"/>
+      <c r="AR2" s="163"/>
+      <c r="AS2" s="163"/>
+      <c r="AT2" s="163"/>
+      <c r="AU2" s="163"/>
+      <c r="AV2" s="163"/>
+      <c r="AW2" s="163"/>
+      <c r="AX2" s="163"/>
+      <c r="AY2" s="163"/>
+      <c r="AZ2" s="164"/>
+      <c r="BA2" s="163">
         <v>27</v>
       </c>
-      <c r="BB2" s="162"/>
-      <c r="BC2" s="162"/>
-      <c r="BD2" s="162"/>
-      <c r="BE2" s="162"/>
-      <c r="BF2" s="162"/>
-      <c r="BG2" s="162"/>
-      <c r="BH2" s="162"/>
-      <c r="BI2" s="162"/>
-      <c r="BJ2" s="162"/>
-      <c r="BK2" s="162"/>
-      <c r="BL2" s="163"/>
+      <c r="BB2" s="163"/>
+      <c r="BC2" s="163"/>
+      <c r="BD2" s="163"/>
+      <c r="BE2" s="163"/>
+      <c r="BF2" s="163"/>
+      <c r="BG2" s="163"/>
+      <c r="BH2" s="163"/>
+      <c r="BI2" s="163"/>
+      <c r="BJ2" s="163"/>
+      <c r="BK2" s="163"/>
+      <c r="BL2" s="164"/>
     </row>
     <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="159"/>
-      <c r="C3" s="161"/>
-      <c r="D3" s="161"/>
+      <c r="B3" s="160"/>
+      <c r="C3" s="162"/>
+      <c r="D3" s="162"/>
       <c r="E3" s="22">
         <v>1</v>
       </c>
@@ -6719,14 +6741,16 @@
       <c r="BK20" s="73"/>
       <c r="BL20" s="70"/>
     </row>
-    <row r="21" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:64" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="57" t="s">
         <v>110</v>
       </c>
       <c r="C21" s="82" t="s">
         <v>108</v>
       </c>
-      <c r="D21" s="39"/>
+      <c r="D21" s="34" t="s">
+        <v>317</v>
+      </c>
       <c r="E21" s="64"/>
       <c r="F21" s="65"/>
       <c r="G21" s="65"/>
@@ -7115,39 +7139,39 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="167" t="s">
+      <c r="B2" s="168" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="171" t="s">
+      <c r="C2" s="172" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="171" t="s">
+      <c r="D2" s="172" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="169" t="s">
+      <c r="E2" s="170" t="s">
         <v>127</v>
       </c>
       <c r="F2" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="165" t="s">
+      <c r="G2" s="166" t="s">
         <v>114</v>
       </c>
-      <c r="H2" s="165"/>
-      <c r="I2" s="165"/>
-      <c r="J2" s="166"/>
-      <c r="K2" s="165" t="s">
+      <c r="H2" s="166"/>
+      <c r="I2" s="166"/>
+      <c r="J2" s="167"/>
+      <c r="K2" s="166" t="s">
         <v>183</v>
       </c>
-      <c r="L2" s="165"/>
-      <c r="M2" s="165"/>
-      <c r="N2" s="166"/>
+      <c r="L2" s="166"/>
+      <c r="M2" s="166"/>
+      <c r="N2" s="167"/>
     </row>
     <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="168"/>
-      <c r="C3" s="172"/>
-      <c r="D3" s="172"/>
-      <c r="E3" s="170"/>
+      <c r="B3" s="169"/>
+      <c r="C3" s="173"/>
+      <c r="D3" s="173"/>
+      <c r="E3" s="171"/>
       <c r="F3" s="99" t="s">
         <v>112</v>
       </c>
@@ -7890,30 +7914,30 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="167" t="s">
+      <c r="B2" s="168" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="171" t="s">
+      <c r="C2" s="172" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="171" t="s">
+      <c r="D2" s="172" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="169" t="s">
+      <c r="E2" s="170" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="165" t="s">
+      <c r="F2" s="166" t="s">
         <v>183</v>
       </c>
-      <c r="G2" s="165"/>
-      <c r="H2" s="165"/>
-      <c r="I2" s="166"/>
+      <c r="G2" s="166"/>
+      <c r="H2" s="166"/>
+      <c r="I2" s="167"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="168"/>
-      <c r="C3" s="172"/>
-      <c r="D3" s="172"/>
-      <c r="E3" s="170"/>
+      <c r="B3" s="169"/>
+      <c r="C3" s="173"/>
+      <c r="D3" s="173"/>
+      <c r="E3" s="171"/>
       <c r="F3" s="99" t="s">
         <v>115</v>
       </c>
@@ -8291,30 +8315,30 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="167" t="s">
+      <c r="B2" s="168" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="171" t="s">
+      <c r="C2" s="172" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="171" t="s">
+      <c r="D2" s="172" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="169" t="s">
+      <c r="E2" s="170" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="165" t="s">
+      <c r="F2" s="166" t="s">
         <v>228</v>
       </c>
-      <c r="G2" s="165"/>
-      <c r="H2" s="165"/>
-      <c r="I2" s="166"/>
+      <c r="G2" s="166"/>
+      <c r="H2" s="166"/>
+      <c r="I2" s="167"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="168"/>
-      <c r="C3" s="172"/>
-      <c r="D3" s="172"/>
-      <c r="E3" s="170"/>
+      <c r="B3" s="169"/>
+      <c r="C3" s="173"/>
+      <c r="D3" s="173"/>
+      <c r="E3" s="171"/>
       <c r="F3" s="99" t="s">
         <v>115</v>
       </c>
@@ -8698,30 +8722,30 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="167" t="s">
+      <c r="B2" s="168" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="171" t="s">
+      <c r="C2" s="172" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="171" t="s">
+      <c r="D2" s="172" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="169" t="s">
+      <c r="E2" s="170" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="165" t="s">
+      <c r="F2" s="166" t="s">
         <v>260</v>
       </c>
-      <c r="G2" s="165"/>
-      <c r="H2" s="165"/>
-      <c r="I2" s="166"/>
+      <c r="G2" s="166"/>
+      <c r="H2" s="166"/>
+      <c r="I2" s="167"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="168"/>
-      <c r="C3" s="172"/>
-      <c r="D3" s="172"/>
-      <c r="E3" s="170"/>
+      <c r="B3" s="169"/>
+      <c r="C3" s="173"/>
+      <c r="D3" s="173"/>
+      <c r="E3" s="171"/>
       <c r="F3" s="99" t="s">
         <v>295</v>
       </c>
@@ -8769,7 +8793,7 @@
       <c r="F5" s="116"/>
       <c r="G5" s="107"/>
       <c r="H5" s="125" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I5" s="137" t="s">
         <v>314</v>
@@ -8791,11 +8815,11 @@
       <c r="F6" s="125"/>
       <c r="G6" s="125"/>
       <c r="H6" s="135" t="s">
-        <v>316</v>
-      </c>
-      <c r="I6" s="173"/>
-    </row>
-    <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+        <v>315</v>
+      </c>
+      <c r="I6" s="158"/>
+    </row>
+    <row r="7" spans="1:9" ht="93" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="154" t="s">
         <v>76</v>
       </c>
@@ -8812,10 +8836,10 @@
       <c r="G7" s="107"/>
       <c r="H7" s="91"/>
       <c r="I7" s="136" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="87.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="154" t="s">
         <v>110</v>
       </c>
@@ -8831,7 +8855,9 @@
       <c r="F8" s="116"/>
       <c r="G8" s="106"/>
       <c r="H8" s="91"/>
-      <c r="I8" s="95"/>
+      <c r="I8" s="136" t="s">
+        <v>319</v>
+      </c>
     </row>
     <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="155" t="s">
@@ -9119,30 +9145,30 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="167" t="s">
+      <c r="B2" s="168" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="171" t="s">
+      <c r="C2" s="172" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="171" t="s">
+      <c r="D2" s="172" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="169" t="s">
+      <c r="E2" s="170" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="165" t="s">
+      <c r="F2" s="166" t="s">
         <v>293</v>
       </c>
-      <c r="G2" s="165"/>
-      <c r="H2" s="165"/>
-      <c r="I2" s="166"/>
+      <c r="G2" s="166"/>
+      <c r="H2" s="166"/>
+      <c r="I2" s="167"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="168"/>
-      <c r="C3" s="172"/>
-      <c r="D3" s="172"/>
-      <c r="E3" s="170"/>
+      <c r="B3" s="169"/>
+      <c r="C3" s="173"/>
+      <c r="D3" s="173"/>
+      <c r="E3" s="171"/>
       <c r="F3" s="99" t="s">
         <v>294</v>
       </c>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Task\000_PJT\111_PTC\1.doc\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\일정\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1938,23 +1938,6 @@
 - 설계 변경 진행 (~10/24)
 - 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- CPU 및 메모리 부하율 관리 대책 르네사스 문의 (~10/27)
-- 사이버 보안 항목 QV와 비교 및 리스트업 후 공조시스템설계팀 회신 (~10/29)
-- 제어기 선행품질 검증 현황 관련 기아 오토랜드 방문 후 자료 회신 (~10/29)
-  : 1. P2 단계 전까지 매 월 1회 제어기 검증 현황 관련 회의 진행 예정
-    2. 진행 단계 별로 이력 및 변경점 꾸준히 업데이트 해서 자료 회신 요청
-    3. Fail Safety 항목 공유 요청
-    4. 제어기 검증 프로세스 관련 자료 공유 요청
-    5. 컨버전 룰이 무엇인지에 대한 자료 공유 요청
-    6. S/W 검증 현황의 검증 항목별 LIST 자료 공유 요청
-    7. CPU / 메모리 부하율 관리 방안 재확인 요청
-    8. 고장 진단 로그 저장 가능 개수 재확인 요청
-- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)
-- 설계 변경 진행 (~11/10)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2512,6 +2495,71 @@
   </si>
   <si>
     <t>[임제훈 사원]
+- SWE.3 SDDS 후속 작업 (진행률 : 100%)
+- SPQA 프로세스 절차를 따라 ALM 등록 (~10/31)
+[조현진 전임]
+- SWE.1, 2, 3 등록에 맞추어 SWE. 4, 5, 6 ALM 등록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[조현진 전임]
+- ESIR 대응 산출물 작성 및 전달 (진행률 : 100%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- SWE.3 SDDS 후속 작업 (진행률 : 95%)
+- SPQA 프로세스 절차를 따라 ALM 등록 (~10/31)
+[조현진 전임]
+- 조치사항에 맞추어 Software Test Plan 수정작업 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[공조시스템설계팀] 
+김응영 책임 010-7635-0265
+key@hyundai.com
+이웅기 연구원 010-8427-8230
+lwg8230@hyundai.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[조현진 전임]
+- 10월 31일 현대자동차 남양연구소 난방평가 요청(from. 김민수 선임)
+  1) T-Car와 Proto 토출온 20도 차이(HVAC 문제로 파악됨)
+  2) 난방평가 목적
+    : 차량 실측 소비전력과 히터 피드백 소비전력 비교,
+      변경된 HVAC으로 인한 R-logic 영향성평가(오실레이션 여부 확인)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[조현진 전임]
+- 10월 29일 공조시스템 설계팀 김응영 책임, 이웅기 연구원 주관 회의 사항
+   1) SVm 대비 SX3 lod 길이 축소 -&gt; 성능 만족을 위해 rod 1개 추가
+      제어기 크기 증가 -&gt; 제어기가 차량 상 카울 크로스바 영역 침범
+      전체적인 히터 사이즈 축소 주기적으로 요청
+   2) 11월 6일 목요일까지 변경된 모델링 데이터 전달요청</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- CPU 및 메모리 부하율 관리 대책 르네사스 문의 (~10/27)
+- 사이버 보안 항목 QV와 비교 및 리스트업 후 공조시스템설계팀 회신 (~10/29)
+- 제어기 선행품질 검증 현황 관련 기아 오토랜드 방문 후 자료 회신 (~10/29)
+  : 1. P2 단계 전까지 매 월 1회 제어기 검증 현황 관련 회의 진행 예정
+    2. 진행 단계 별로 이력 및 변경점 꾸준히 업데이트 해서 자료 회신 요청
+    3. Fail Safety 항목 공유 요청
+    4. 제어기 검증 프로세스 관련 자료 공유 요청
+    5. 컨버전 룰이 무엇인지에 대한 자료 공유 요청
+    6. S/W 검증 현황의 검증 항목별 LIST 자료 공유 요청
+    7. CPU / 메모리 부하율 관리 방안 재확인 요청
+    8. 고장 진단 로그 저장 가능 개수 재확인 요청
+- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)
+- 설계 변경 진행 (~11/10)
+  : 기구팀 문의 결과, QV, SVm, BJ 담당자 전부 똑같다고 함. 결재 라인 똑같이 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
 - R로직 튜닝 (~10/27)
 - ESIR 일정에 맞춰서 5가지 항목 다 가능한지 파악하기 (~10/29)
 - 공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (10/30)
@@ -2523,54 +2571,10 @@
 - 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)
 - 최신 승인도 확인 (~10/31)
 - 제작사양서 배포 준비 (~10/31)
-  : SW 파일, 제어사양서</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- SWE.3 SDDS 후속 작업 (진행률 : 100%)
-- SPQA 프로세스 절차를 따라 ALM 등록 (~10/31)
-[조현진 전임]
-- SWE.1, 2, 3 등록에 맞추어 SWE. 4, 5, 6 ALM 등록</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[조현진 전임]
-- ESIR 대응 산출물 작성 및 전달 (진행률 : 100%)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- SWE.3 SDDS 후속 작업 (진행률 : 95%)
-- SPQA 프로세스 절차를 따라 ALM 등록 (~10/31)
-[조현진 전임]
-- 조치사항에 맞추어 Software Test Plan 수정작업 완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[공조시스템설계팀] 
-김응영 책임 010-7635-0265
-key@hyundai.com
-이웅기 연구원 010-8427-8230
-lwg8230@hyundai.com</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[조현진 전임]
-- 10월 31일 현대자동차 남양연구소 난방평가 요청(from. 김민수 선임)
-  1) T-Car와 Proto 토출온 20도 차이(HVAC 문제로 파악됨)
-  2) 난방평가 목적
-    : 차량 실측 소비전력과 히터 피드백 소비전력 비교,
-      변경된 HVAC으로 인한 R-logic 영향성평가(오실레이션 여부 확인)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[조현진 전임]
-- 10월 29일 공조시스템 설계팀 김응영 책임, 이웅기 연구원 주관 회의 사항
-   1) SVm 대비 SX3 lod 길이 축소 -&gt; 성능 만족을 위해 rod 1개 추가
-      제어기 크기 증가 -&gt; 제어기가 차량 상 카울 크로스바 영역 침범
-      전체적인 히터 사이즈 축소 주기적으로 요청
-   2) 11월 6일 목요일까지 변경된 모델링 데이터 전달요청</t>
+  : SW 파일, 제어사양서
+  : 10월 14일부터 tc 160℃, 스톤 기울기 변경되었음
+  : 제작사양서 배포 기준, tc 160℃ 스톤 기울기 변경된 샘플 기준으로 튜닝 완료
+  : P1 때 tc 165℃ 변경 협의 중</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6749,7 +6753,7 @@
         <v>108</v>
       </c>
       <c r="D21" s="34" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E21" s="64"/>
       <c r="F21" s="65"/>
@@ -8793,10 +8797,10 @@
       <c r="F5" s="116"/>
       <c r="G5" s="107"/>
       <c r="H5" s="125" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="I5" s="137" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -8815,7 +8819,7 @@
       <c r="F6" s="125"/>
       <c r="G6" s="125"/>
       <c r="H6" s="135" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="I6" s="158"/>
     </row>
@@ -8836,7 +8840,7 @@
       <c r="G7" s="107"/>
       <c r="H7" s="91"/>
       <c r="I7" s="136" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="87.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8856,7 +8860,7 @@
       <c r="G8" s="106"/>
       <c r="H8" s="91"/>
       <c r="I8" s="136" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -8931,7 +8935,7 @@
       <c r="H12" s="140"/>
       <c r="I12" s="95"/>
     </row>
-    <row r="13" spans="1:9" ht="189" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="222" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="134" t="s">
         <v>63</v>
       </c>
@@ -8950,7 +8954,7 @@
         <v>307</v>
       </c>
       <c r="I13" s="136" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -8972,7 +8976,7 @@
         <v>304</v>
       </c>
       <c r="I14" s="136" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -8996,10 +9000,10 @@
         <v>305</v>
       </c>
       <c r="I15" s="136" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="175.5" x14ac:dyDescent="0.3">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="228.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="133" t="s">
         <v>86</v>
       </c>
@@ -9015,10 +9019,10 @@
       <c r="F16" s="116"/>
       <c r="G16" s="107"/>
       <c r="H16" s="135" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I16" s="136" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -9082,7 +9086,7 @@
         <v>306</v>
       </c>
       <c r="I19" s="136" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="대일정" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="316">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -259,17 +259,6 @@
 dong3082@kia.com
 [샤시부품개발2팀]
 김현우 책임 010-8493-6493</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[전자편의개발 2팀] 
-서상기 책임 010-9311-9821
-zsskz@hyundai.com
-[공조시스템설계팀] 
-김응영 책임 010-7635-0265
-key@hyundai.com
-안성민 책임연구원 
-freshair@hyundai.com</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1661,84 +1650,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2주차 (10/10 ~ 10/15)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3주차 (10/16 ~ 10/22)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4주차 (10/23 ~ 10/29)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- AY 회의 진행 (25/10/20)
-- LHD ESIR
-- R로직 튜닝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- AY 회의 진행 (25/10/20)
-- LHD ESIR
-- R로직 튜닝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- 온도 정합성 테스트 (10/20)
-- 제어기 선행품질 검증 현황 작성
-- 제어기 선행품질 검증 현황 관련 기아 오토랜드 방문 (10/23)
-- 설계 변경 진행</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- 온도 정합성 테스트 (10/20)
-- 제어기 선행품질 검증 현황 작성
-- 제어기 선행품질 검증 현황 관련 기아 오토랜드 방문 (10/23)
-- 설계 변경 진행</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- LHD R로직 튜닝
-- RHD R로직 튜닝 (HVAC 미보유, 보류)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- LHD R로직 튜닝
-- RHD R로직 튜닝 (HVAC 미보유, 보류)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- SWE.3 SDDS 후속 작업 (진행률 : 90%)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- SWE.3 SDDS 후속 작업 (진행률 : 90%)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- ESIR 계획서 등록
-- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신
-- Core Temp 튜닝 결과 확인
-- 최신 승인도 확인
-- R로직 튜닝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">[임제훈 사원]
-- </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>오세영
 조현진
 임제훈</t>
@@ -1781,23 +1692,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1주차 (10/30 ~ 11/05)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1주차 (10/02)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2주차 (11/06 ~ 11/12)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3주차 (11/13 ~ 11/19)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4주차 (11/20 ~ 11/26)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1938,12 +1833,6 @@
 - 설계 변경 진행 (~10/24)
 - 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- LHD ESIR 계획서 (기구, HW 업로드 후, 행추가 예정) (~10/31)
-- R로직 튜닝</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2487,14 +2376,6 @@
   </si>
   <si>
     <t>[임제훈 사원]
-- BJ PTC HTR 벤치 시험 합동 평가 일정 (10/29 예정)
-  : SW 대응은 딱히 없을 것 같다고 했지만, 결과나 진행 사항 파악 필요
-- LHD R로직 튜닝
-- RHD R로직 튜닝 (HVAC 미보유, 보류)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
 - SWE.3 SDDS 후속 작업 (진행률 : 100%)
 - SPQA 프로세스 절차를 따라 ALM 등록 (~10/31)
 [조현진 전임]
@@ -2559,22 +2440,325 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>4주차 (10/24 ~ 10/30)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3주차 (10/17 ~ 10/23)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2주차 (10/10 ~ 10/16)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1주차 (10/31 ~ 11/06)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2주차 (11/07 ~ 11/13)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3주차 (11/14 ~ 11/20)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4주차 (11/21 ~ 11/27)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>[임제훈 사원]
-- R로직 튜닝 (~10/27)
-- ESIR 일정에 맞춰서 5가지 항목 다 가능한지 파악하기 (~10/29)
+- SWE.3 SDDS 후속 작업 (진행률 : 100%)
+- SPQA 프로세스 절차를 따라 ALM 등록 (~11/06)
+[조현진 전임]
+- SWE.1, 2, 3 등록에 맞추어 SWE. 4, 5, 6 ALM 등록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BJ PTC HTR 벤치 시험 합동 평가 일정 (10/29 예정)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : SW 대응은 딱히 없을 것 같다고 했지만, 결과나 진행 사항 파악 필요
+- LHD R로직 튜닝
+- RHD R로직 튜닝 (HVAC 미보유, 보류)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R로직 튜닝 (~10/27)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ESIR 일정에 맞춰서 5가지 항목 다 가능한지 파악하기 (~10/29)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 - 공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (10/30)
   : 휴가 중, 목요일 출근 예정, 이 때 메일로 다시 문의
-- ES 규격 대로 15초 내로 목표 전력 도달 SW로 변경 (~10/29)
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ES 규격 대로 15초 내로 목표 전력 도달 SW로 변경 (~10/29)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
   : Softstart enable 0으로 변경
   : Sofftstart 0일 때, R로직 확인, 전력 구간 별 칼로리와 CAN 출력 차이 비교
 - ESIR 계획서 등록 (~10/31)
-- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 - 최신 승인도 확인 (~10/31)
-- 제작사양서 배포 준비 (~10/31)
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제작사양서 배포 준비 (~10/31)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
   : SW 파일, 제어사양서
   : 10월 14일부터 tc 160℃, 스톤 기울기 변경되었음
   : 제작사양서 배포 기준, tc 160℃ 스톤 기울기 변경된 샘플 기준으로 튜닝 완료
   : P1 때 tc 165℃ 변경 협의 중</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- LHD R로직 튜닝
+- RHD R로직 튜닝 (HVAC 미보유, 보류)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- R로직 튜닝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">LHD ESIR 계획서 (기구, HW 업로드 후, 행추가 예정) (~10/31)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  : 90700-00, 95480-00 계획서 등록 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- R로직 튜닝</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (~11/03)
+  : 10/30 문의 완료, 재회신 요청 예정
+- ESIR 계획서 등록 (~11/05)
+- 최신 승인도 확인 (~11/06)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[우리산업]
+PM : 유정호, 품질 : 박상철, 기구 : 김민수, 공준석, HW : 신지훈
+[전자편의개발 2팀] 
+서상기 책임 010-9311-9821
+zsskz@hyundai.com
+[공조시스템설계팀] 
+김응영 책임 010-7635-0265
+key@hyundai.com
+이웅기 연구원 010-8427-8230
+lwg8230@hyundai.com
+[기아샤시시스템품질팀]
+김제일 매니저
+J1@kia.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[우리산업]
+기구 : 정우헌, HW : 신지훈
+[공조시스템설계팀]
+정재근 책임 연구원 010-9402-3594
+wjdworms1357@hyundai.com
+김동환 연구원 010-4162-2776
+kdh2776@hyundai.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 사이버 보안 항목 QV와 비교 및 리스트업 후 공조시스템설계팀 회신 (~11/05)
+  : ES95489-21 빼는 것은 안됨. 업데이트에 해당하는 항목 N/A로 하자고 회신 받음
+- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~11/03)
+- 설계 변경 진행 (~11/10)
+  : 기구팀 문의 결과, QV, SVm, BJ 담당자 전부 똑같다고 함. 결재 라인 똑같이 예정
+  : 설계 변경 문서 작성</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2809,7 +2993,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="81">
+  <borders count="83">
     <border>
       <left/>
       <right/>
@@ -3921,6 +4105,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3942,7 +4148,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="179">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4464,6 +4670,21 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="81" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -5091,7 +5312,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="161" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D2" s="161" t="s">
         <v>39</v>
@@ -5354,10 +5575,10 @@
     </row>
     <row r="4" spans="1:64" ht="183" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="63" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C4" s="61" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D4" s="35" t="s">
         <v>42</v>
@@ -5435,10 +5656,10 @@
     </row>
     <row r="5" spans="1:64" ht="81" x14ac:dyDescent="0.3">
       <c r="B5" s="28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C5" s="62" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D5" s="35" t="s">
         <v>41</v>
@@ -5514,10 +5735,10 @@
     </row>
     <row r="6" spans="1:64" ht="67.5" x14ac:dyDescent="0.3">
       <c r="B6" s="28" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D6" s="34" t="s">
         <v>40</v>
@@ -5597,10 +5818,10 @@
     </row>
     <row r="7" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C7" s="58" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D7" s="33"/>
       <c r="E7" s="6"/>
@@ -5678,7 +5899,7 @@
     </row>
     <row r="8" spans="1:64" ht="81" x14ac:dyDescent="0.3">
       <c r="B8" s="28" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C8" s="58"/>
       <c r="D8" s="33"/>
@@ -5702,7 +5923,7 @@
       <c r="V8" s="30"/>
       <c r="W8" s="30"/>
       <c r="X8" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y8" s="31"/>
       <c r="Z8" s="30"/>
@@ -5712,22 +5933,22 @@
       <c r="AD8" s="31"/>
       <c r="AE8" s="31"/>
       <c r="AF8" s="15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG8" s="31"/>
       <c r="AH8" s="31"/>
       <c r="AI8" s="17" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AJ8" s="31"/>
       <c r="AK8" s="31"/>
       <c r="AL8" s="31"/>
       <c r="AM8" s="17" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AN8" s="123"/>
       <c r="AO8" s="29" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AP8" s="31"/>
       <c r="AQ8" s="31"/>
@@ -5758,7 +5979,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="59" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="6"/>
@@ -5783,11 +6004,11 @@
       <c r="X9" s="7"/>
       <c r="Y9" s="7"/>
       <c r="Z9" s="17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA9" s="7"/>
       <c r="AB9" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AC9" s="9"/>
       <c r="AD9" s="7"/>
@@ -5828,10 +6049,10 @@
     </row>
     <row r="10" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="6"/>
@@ -5854,11 +6075,11 @@
       <c r="V10" s="7"/>
       <c r="W10" s="7"/>
       <c r="X10" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Y10" s="7"/>
       <c r="Z10" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA10" s="7"/>
       <c r="AB10" s="8"/>
@@ -5871,7 +6092,7 @@
       </c>
       <c r="AH10" s="7"/>
       <c r="AI10" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AJ10" s="7"/>
       <c r="AK10" s="7"/>
@@ -5905,10 +6126,10 @@
     </row>
     <row r="11" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="28" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C11" s="58" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D11" s="33"/>
       <c r="E11" s="6"/>
@@ -5934,34 +6155,34 @@
       <c r="Y11" s="7"/>
       <c r="Z11" s="7"/>
       <c r="AA11" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AB11" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC11" s="9"/>
       <c r="AD11" s="30"/>
       <c r="AE11" s="31"/>
       <c r="AF11" s="31"/>
       <c r="AG11" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AH11" s="7"/>
       <c r="AI11" s="13"/>
       <c r="AJ11" s="7"/>
       <c r="AK11" s="17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AL11" s="7"/>
       <c r="AM11" s="7"/>
       <c r="AN11" s="8"/>
       <c r="AO11" s="9"/>
       <c r="AP11" s="17" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AQ11" s="7"/>
       <c r="AR11" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AS11" s="7"/>
       <c r="AT11" s="7"/>
@@ -5986,10 +6207,10 @@
     </row>
     <row r="12" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="28" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D12" s="33"/>
       <c r="E12" s="6"/>
@@ -6024,12 +6245,12 @@
       <c r="AH12" s="7"/>
       <c r="AI12" s="13"/>
       <c r="AJ12" s="101" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AK12" s="36"/>
       <c r="AL12" s="13"/>
       <c r="AM12" s="13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AN12" s="8"/>
       <c r="AO12" s="12"/>
@@ -6046,7 +6267,7 @@
       </c>
       <c r="AW12" s="7"/>
       <c r="AX12" s="13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AY12" s="7"/>
       <c r="AZ12" s="10"/>
@@ -6063,15 +6284,15 @@
       <c r="BK12" s="31"/>
       <c r="BL12" s="10"/>
     </row>
-    <row r="13" spans="1:64" ht="183.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:64" ht="228.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C13" s="59" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>43</v>
+        <v>313</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="7"/>
@@ -6094,7 +6315,7 @@
       <c r="U13" s="7"/>
       <c r="V13" s="7"/>
       <c r="W13" s="13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X13" s="7"/>
       <c r="Y13" s="7"/>
@@ -6107,11 +6328,11 @@
       <c r="AF13" s="7"/>
       <c r="AG13" s="7"/>
       <c r="AH13" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AI13" s="36"/>
       <c r="AJ13" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AK13" s="30"/>
       <c r="AL13" s="7"/>
@@ -6119,19 +6340,19 @@
         <v>4</v>
       </c>
       <c r="AN13" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AO13" s="9"/>
       <c r="AP13" s="7"/>
       <c r="AQ13" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AR13" s="7"/>
       <c r="AS13" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AT13" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AU13" s="7"/>
       <c r="AV13" s="7"/>
@@ -6154,13 +6375,13 @@
     </row>
     <row r="14" spans="1:64" ht="67.5" x14ac:dyDescent="0.3">
       <c r="B14" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="59" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" s="34" t="s">
         <v>74</v>
-      </c>
-      <c r="C14" s="59" t="s">
-        <v>84</v>
-      </c>
-      <c r="D14" s="34" t="s">
-        <v>75</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="7"/>
@@ -6200,13 +6421,13 @@
       <c r="AH14" s="7"/>
       <c r="AI14" s="7"/>
       <c r="AJ14" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AK14" s="13" t="s">
         <v>13</v>
       </c>
       <c r="AL14" s="17" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AM14" s="7"/>
       <c r="AN14" s="8"/>
@@ -6221,7 +6442,7 @@
         <v>15</v>
       </c>
       <c r="AU14" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AV14" s="7"/>
       <c r="AW14" s="7"/>
@@ -6243,13 +6464,13 @@
     </row>
     <row r="15" spans="1:64" ht="285.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C15" s="59" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D15" s="34" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="7"/>
@@ -6272,7 +6493,7 @@
       <c r="W15" s="7"/>
       <c r="X15" s="7"/>
       <c r="Y15" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Z15" s="13"/>
       <c r="AA15" s="7"/>
@@ -6280,26 +6501,26 @@
       <c r="AC15" s="12"/>
       <c r="AD15" s="7"/>
       <c r="AE15" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AF15" s="38"/>
       <c r="AG15" s="37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AH15" s="7"/>
       <c r="AI15" s="37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AJ15" s="30"/>
       <c r="AK15" s="7"/>
       <c r="AL15" s="13"/>
       <c r="AM15" s="13"/>
       <c r="AN15" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AO15" s="9"/>
       <c r="AP15" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ15" s="13"/>
       <c r="AR15" s="7"/>
@@ -6326,10 +6547,10 @@
     </row>
     <row r="16" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="27" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="6"/>
@@ -6374,25 +6595,25 @@
       <c r="AH16" s="7"/>
       <c r="AI16" s="13"/>
       <c r="AJ16" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AK16" s="37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AL16" s="7"/>
       <c r="AM16" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AN16" s="8"/>
       <c r="AO16" s="12"/>
       <c r="AP16" s="13"/>
       <c r="AQ16" s="13"/>
       <c r="AR16" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AS16" s="7"/>
       <c r="AT16" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AU16" s="7"/>
       <c r="AV16" s="7"/>
@@ -6415,13 +6636,13 @@
     </row>
     <row r="17" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="57" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C17" s="60" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D17" s="76" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E17" s="40"/>
       <c r="F17" s="41"/>
@@ -6432,13 +6653,13 @@
       <c r="K17" s="41"/>
       <c r="L17" s="41"/>
       <c r="M17" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N17" s="41"/>
       <c r="O17" s="41"/>
       <c r="P17" s="43"/>
       <c r="Q17" s="104" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="R17" s="103"/>
       <c r="S17" s="41"/>
@@ -6448,7 +6669,7 @@
       <c r="W17" s="42"/>
       <c r="X17" s="41"/>
       <c r="Y17" s="30" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Z17" s="41"/>
       <c r="AA17" s="41"/>
@@ -6461,7 +6682,7 @@
       <c r="AH17" s="41"/>
       <c r="AI17" s="37"/>
       <c r="AJ17" s="30" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AK17" s="46"/>
       <c r="AL17" s="41"/>
@@ -6469,11 +6690,11 @@
       <c r="AN17" s="8"/>
       <c r="AO17" s="47"/>
       <c r="AP17" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AQ17" s="42"/>
       <c r="AR17" s="37" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AS17" s="41"/>
       <c r="AT17" s="42"/>
@@ -6481,7 +6702,7 @@
       <c r="AV17" s="41"/>
       <c r="AW17" s="41"/>
       <c r="AX17" s="17" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AY17" s="41"/>
       <c r="AZ17" s="48"/>
@@ -6489,7 +6710,7 @@
       <c r="BB17" s="45"/>
       <c r="BC17" s="45"/>
       <c r="BD17" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="BE17" s="71"/>
       <c r="BF17" s="45"/>
@@ -6500,14 +6721,16 @@
       <c r="BK17" s="71"/>
       <c r="BL17" s="48"/>
     </row>
-    <row r="18" spans="2:64" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:64" ht="108" x14ac:dyDescent="0.3">
       <c r="B18" s="27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>259</v>
-      </c>
-      <c r="D18" s="33"/>
+        <v>258</v>
+      </c>
+      <c r="D18" s="178" t="s">
+        <v>314</v>
+      </c>
       <c r="E18" s="64"/>
       <c r="F18" s="65"/>
       <c r="G18" s="65"/>
@@ -6535,12 +6758,12 @@
       <c r="AC18" s="67"/>
       <c r="AD18" s="65"/>
       <c r="AE18" s="68" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AF18" s="65"/>
       <c r="AG18" s="68"/>
       <c r="AH18" s="56" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI18" s="69"/>
       <c r="AJ18" s="65"/>
@@ -6561,27 +6784,27 @@
       <c r="AU18" s="73"/>
       <c r="AV18" s="65"/>
       <c r="AW18" s="69" t="s">
+        <v>88</v>
+      </c>
+      <c r="AX18" s="69" t="s">
         <v>89</v>
       </c>
-      <c r="AX18" s="69" t="s">
+      <c r="AY18" s="69" t="s">
         <v>90</v>
       </c>
-      <c r="AY18" s="69" t="s">
+      <c r="AZ18" s="70" t="s">
         <v>91</v>
-      </c>
-      <c r="AZ18" s="70" t="s">
-        <v>92</v>
       </c>
       <c r="BA18" s="67"/>
       <c r="BB18" s="73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BC18" s="73"/>
       <c r="BD18" s="73" t="s">
+        <v>93</v>
+      </c>
+      <c r="BE18" s="73" t="s">
         <v>94</v>
-      </c>
-      <c r="BE18" s="73" t="s">
-        <v>95</v>
       </c>
       <c r="BF18" s="72"/>
       <c r="BG18" s="73"/>
@@ -6593,10 +6816,10 @@
     </row>
     <row r="19" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="77" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C19" s="78" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D19" s="33"/>
       <c r="E19" s="64"/>
@@ -6637,11 +6860,11 @@
       <c r="AN19" s="66"/>
       <c r="AO19" s="67"/>
       <c r="AP19" s="69" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AQ19" s="69"/>
       <c r="AR19" s="69" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AS19" s="65"/>
       <c r="AT19" s="65"/>
@@ -6651,7 +6874,7 @@
       <c r="AX19" s="65"/>
       <c r="AY19" s="69"/>
       <c r="AZ19" s="70" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BA19" s="67"/>
       <c r="BB19" s="72"/>
@@ -6659,29 +6882,29 @@
       <c r="BD19" s="72"/>
       <c r="BE19" s="72"/>
       <c r="BF19" s="73" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="BG19" s="73"/>
       <c r="BH19" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="BI19" s="73" t="s">
         <v>100</v>
       </c>
-      <c r="BI19" s="73" t="s">
+      <c r="BJ19" s="73" t="s">
         <v>101</v>
-      </c>
-      <c r="BJ19" s="73" t="s">
-        <v>102</v>
       </c>
       <c r="BK19" s="73"/>
       <c r="BL19" s="70" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="77" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C20" s="78" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D20" s="39"/>
       <c r="E20" s="64"/>
@@ -6747,13 +6970,13 @@
     </row>
     <row r="21" spans="2:64" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="57" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C21" s="82" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D21" s="34" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="E21" s="64"/>
       <c r="F21" s="65"/>
@@ -6794,14 +7017,14 @@
       <c r="AO21" s="67"/>
       <c r="AP21" s="69"/>
       <c r="AQ21" s="69" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AR21" s="69"/>
       <c r="AS21" s="65"/>
       <c r="AT21" s="65"/>
       <c r="AU21" s="69"/>
       <c r="AV21" s="13" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AW21" s="65"/>
       <c r="AX21" s="65"/>
@@ -6809,20 +7032,20 @@
       <c r="AZ21" s="70"/>
       <c r="BA21" s="67"/>
       <c r="BB21" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BC21" s="73"/>
       <c r="BD21" s="69" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="BE21" s="72"/>
       <c r="BF21" s="73"/>
       <c r="BG21" s="69" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="BH21" s="73"/>
       <c r="BI21" s="69" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="BJ21" s="73"/>
       <c r="BK21" s="73"/>
@@ -6830,10 +7053,10 @@
     </row>
     <row r="22" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="57" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C22" s="82" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D22" s="39"/>
       <c r="E22" s="64"/>
@@ -6899,10 +7122,10 @@
     </row>
     <row r="23" spans="2:64" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="79" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C23" s="80" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D23" s="81"/>
       <c r="E23" s="49"/>
@@ -6996,118 +7219,118 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C1" t="s">
         <v>239</v>
-      </c>
-      <c r="C1" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="126" t="s">
+        <v>240</v>
+      </c>
+      <c r="B2" t="s">
         <v>241</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="127" t="s">
         <v>242</v>
       </c>
-      <c r="C2" s="127" t="s">
+      <c r="D2" t="s">
         <v>243</v>
-      </c>
-      <c r="D2" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="126" t="s">
+        <v>244</v>
+      </c>
+      <c r="B3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C3" s="128" t="s">
         <v>245</v>
       </c>
-      <c r="B3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C3" s="128" t="s">
-        <v>246</v>
-      </c>
       <c r="D3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="126" t="s">
+        <v>246</v>
+      </c>
+      <c r="B4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C4" s="128" t="s">
         <v>247</v>
       </c>
-      <c r="B4" t="s">
-        <v>242</v>
-      </c>
-      <c r="C4" s="128" t="s">
-        <v>248</v>
-      </c>
       <c r="D4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="129" t="s">
+        <v>248</v>
+      </c>
+      <c r="B5" t="s">
+        <v>241</v>
+      </c>
+      <c r="C5" s="128" t="s">
         <v>249</v>
       </c>
-      <c r="B5" t="s">
-        <v>242</v>
-      </c>
-      <c r="C5" s="128" t="s">
-        <v>250</v>
-      </c>
       <c r="D5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="127" t="s">
+        <v>250</v>
+      </c>
+      <c r="B6" t="s">
+        <v>243</v>
+      </c>
+      <c r="C6" s="130" t="s">
         <v>251</v>
       </c>
-      <c r="B6" t="s">
-        <v>244</v>
-      </c>
-      <c r="C6" s="130" t="s">
-        <v>252</v>
-      </c>
       <c r="D6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="127" t="s">
+        <v>252</v>
+      </c>
+      <c r="B7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C7" s="130" t="s">
         <v>253</v>
       </c>
-      <c r="B7" t="s">
-        <v>244</v>
-      </c>
-      <c r="C7" s="130" t="s">
-        <v>254</v>
-      </c>
       <c r="D7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C8" s="126" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C9" s="126" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C10" s="130" t="s">
+        <v>256</v>
+      </c>
+      <c r="D10" t="s">
         <v>257</v>
-      </c>
-      <c r="D10" t="s">
-        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -7133,10 +7356,10 @@
   <sheetData>
     <row r="1" spans="1:14" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="110" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="111" t="s">
         <v>149</v>
-      </c>
-      <c r="B1" s="111" t="s">
-        <v>150</v>
       </c>
       <c r="C1" s="111"/>
       <c r="D1" s="111"/>
@@ -7147,25 +7370,25 @@
         <v>2</v>
       </c>
       <c r="C2" s="172" t="s">
+        <v>176</v>
+      </c>
+      <c r="D2" s="172" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="172" t="s">
-        <v>178</v>
-      </c>
       <c r="E2" s="170" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F2" s="98" t="s">
+        <v>112</v>
+      </c>
+      <c r="G2" s="166" t="s">
         <v>113</v>
-      </c>
-      <c r="G2" s="166" t="s">
-        <v>114</v>
       </c>
       <c r="H2" s="166"/>
       <c r="I2" s="166"/>
       <c r="J2" s="167"/>
       <c r="K2" s="166" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L2" s="166"/>
       <c r="M2" s="166"/>
@@ -7177,169 +7400,169 @@
       <c r="D3" s="173"/>
       <c r="E3" s="171"/>
       <c r="F3" s="99" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G3" s="99" t="s">
+        <v>114</v>
+      </c>
+      <c r="H3" s="99" t="s">
         <v>115</v>
       </c>
-      <c r="H3" s="99" t="s">
+      <c r="I3" s="99" t="s">
         <v>116</v>
       </c>
-      <c r="I3" s="99" t="s">
-        <v>117</v>
-      </c>
       <c r="J3" s="100" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K3" s="99" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L3" s="99" t="s">
+        <v>115</v>
+      </c>
+      <c r="M3" s="99" t="s">
         <v>116</v>
       </c>
-      <c r="M3" s="99" t="s">
-        <v>117</v>
-      </c>
       <c r="N3" s="100" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="108" x14ac:dyDescent="0.3">
       <c r="B4" s="84" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C4" s="118" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D4" s="118" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E4" s="92" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F4" s="107" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G4" s="116" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H4" s="107" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I4" s="107" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J4" s="94"/>
       <c r="K4" s="107" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L4" s="107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M4" s="107"/>
       <c r="N4" s="94"/>
     </row>
     <row r="5" spans="1:14" ht="108" x14ac:dyDescent="0.3">
       <c r="B5" s="85" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D5" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E5" s="93" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F5" s="107" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G5" s="116" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H5" s="107" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I5" s="107" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J5" s="95"/>
       <c r="K5" s="107" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L5" s="107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M5" s="107"/>
       <c r="N5" s="95"/>
     </row>
     <row r="6" spans="1:14" ht="108" x14ac:dyDescent="0.3">
       <c r="B6" s="85" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C6" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D6" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E6" s="93" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F6" s="107" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G6" s="116" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H6" s="107" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I6" s="107" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J6" s="95"/>
       <c r="K6" s="107" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L6" s="107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M6" s="107"/>
       <c r="N6" s="95"/>
     </row>
     <row r="7" spans="1:14" ht="108" x14ac:dyDescent="0.3">
       <c r="B7" s="85" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C7" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D7" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E7" s="93" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F7" s="107" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G7" s="116" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H7" s="107" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I7" s="107" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J7" s="95"/>
       <c r="K7" s="107" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L7" s="107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M7" s="107"/>
       <c r="N7" s="95"/>
@@ -7349,268 +7572,268 @@
         <v>3</v>
       </c>
       <c r="C8" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D8" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E8" s="93" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F8" s="107" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G8" s="116" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H8" s="107" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I8" s="107" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J8" s="95"/>
       <c r="K8" s="107" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L8" s="107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M8" s="107"/>
       <c r="N8" s="95"/>
     </row>
     <row r="9" spans="1:14" ht="175.5" x14ac:dyDescent="0.3">
       <c r="B9" s="86" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C9" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D9" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E9" s="102" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F9" s="107" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G9" s="116" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H9" s="107" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I9" s="107" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J9" s="95"/>
       <c r="K9" s="107" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="L9" s="107" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="M9" s="107"/>
       <c r="N9" s="95"/>
     </row>
     <row r="10" spans="1:14" ht="121.5" x14ac:dyDescent="0.3">
       <c r="B10" s="86" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C10" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D10" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E10" s="102" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F10" s="107" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G10" s="116" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H10" s="107" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I10" s="107" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J10" s="95"/>
       <c r="K10" s="107" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L10" s="107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M10" s="107"/>
       <c r="N10" s="95"/>
     </row>
     <row r="11" spans="1:14" ht="108" x14ac:dyDescent="0.3">
       <c r="B11" s="85" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C11" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D11" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E11" s="102" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F11" s="107" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G11" s="116" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H11" s="107" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I11" s="107" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J11" s="95"/>
       <c r="K11" s="107" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L11" s="107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M11" s="107"/>
       <c r="N11" s="95"/>
     </row>
     <row r="12" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="86" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C12" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D12" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E12" s="102" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F12" s="107" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G12" s="116" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H12" s="107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I12" s="107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J12" s="95"/>
       <c r="K12" s="107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L12" s="107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M12" s="107"/>
       <c r="N12" s="95"/>
     </row>
     <row r="13" spans="1:14" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="86" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C13" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D13" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E13" s="102" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F13" s="107" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G13" s="116" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H13" s="107" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I13" s="107" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J13" s="95"/>
       <c r="K13" s="107" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L13" s="107" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M13" s="107"/>
       <c r="N13" s="95"/>
     </row>
     <row r="14" spans="1:14" ht="175.5" x14ac:dyDescent="0.3">
       <c r="B14" s="87" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C14" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="D14" s="119" t="s">
         <v>180</v>
-      </c>
-      <c r="D14" s="119" t="s">
-        <v>181</v>
       </c>
       <c r="E14" s="102"/>
       <c r="F14" s="107"/>
       <c r="G14" s="116"/>
       <c r="H14" s="107" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I14" s="107" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J14" s="95"/>
       <c r="K14" s="107" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L14" s="107" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M14" s="107"/>
       <c r="N14" s="95"/>
     </row>
     <row r="15" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="87" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C15" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D15" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E15" s="102" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F15" s="107" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G15" s="116" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H15" s="107" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I15" s="107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J15" s="95"/>
       <c r="K15" s="107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L15" s="107"/>
       <c r="M15" s="107"/>
@@ -7618,32 +7841,32 @@
     </row>
     <row r="16" spans="1:14" ht="121.5" x14ac:dyDescent="0.3">
       <c r="B16" s="86" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C16" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D16" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E16" s="93" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F16" s="107" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G16" s="116" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H16" s="107" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I16" s="107" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J16" s="95"/>
       <c r="K16" s="107" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L16" s="107"/>
       <c r="M16" s="107"/>
@@ -7651,173 +7874,173 @@
     </row>
     <row r="17" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="88" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C17" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D17" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E17" s="93" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F17" s="91"/>
       <c r="G17" s="116" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H17" s="91" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I17" s="91" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J17" s="95"/>
       <c r="K17" s="91" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L17" s="91" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M17" s="91"/>
       <c r="N17" s="95"/>
     </row>
     <row r="18" spans="2:14" ht="162" x14ac:dyDescent="0.3">
       <c r="B18" s="88" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C18" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D18" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E18" s="102" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F18" s="107" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G18" s="116" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H18" s="107" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I18" s="107" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J18" s="95"/>
       <c r="K18" s="107" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="L18" s="107" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M18" s="107"/>
       <c r="N18" s="95"/>
     </row>
     <row r="19" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="87" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C19" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D19" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E19" s="93" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F19" s="106" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G19" s="116" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H19" s="107" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I19" s="107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J19" s="95"/>
       <c r="K19" s="107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L19" s="107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M19" s="107"/>
       <c r="N19" s="95"/>
     </row>
     <row r="20" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="87" t="s">
+        <v>168</v>
+      </c>
+      <c r="C20" s="119" t="s">
+        <v>175</v>
+      </c>
+      <c r="D20" s="119" t="s">
+        <v>178</v>
+      </c>
+      <c r="E20" s="115" t="s">
         <v>169</v>
       </c>
-      <c r="C20" s="119" t="s">
-        <v>176</v>
-      </c>
-      <c r="D20" s="119" t="s">
-        <v>179</v>
-      </c>
-      <c r="E20" s="115" t="s">
+      <c r="F20" s="112" t="s">
         <v>170</v>
       </c>
-      <c r="F20" s="112" t="s">
+      <c r="G20" s="116" t="s">
         <v>171</v>
       </c>
-      <c r="G20" s="116" t="s">
-        <v>172</v>
-      </c>
       <c r="H20" s="121" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I20" s="107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J20" s="114"/>
       <c r="K20" s="107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L20" s="107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M20" s="107"/>
       <c r="N20" s="114"/>
     </row>
     <row r="21" spans="2:14" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="89" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C21" s="120" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D21" s="120" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E21" s="105" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F21" s="108" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G21" s="117" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H21" s="122" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I21" s="122" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J21" s="97"/>
       <c r="K21" s="122" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L21" s="122" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M21" s="122"/>
       <c r="N21" s="97"/>
@@ -7911,7 +8134,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="111" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C1" s="111"/>
       <c r="D1" s="111"/>
@@ -7922,16 +8145,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="172" t="s">
+        <v>176</v>
+      </c>
+      <c r="D2" s="172" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="172" t="s">
-        <v>178</v>
-      </c>
       <c r="E2" s="170" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F2" s="166" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G2" s="166"/>
       <c r="H2" s="166"/>
@@ -7943,30 +8166,30 @@
       <c r="D3" s="173"/>
       <c r="E3" s="171"/>
       <c r="F3" s="99" t="s">
+        <v>114</v>
+      </c>
+      <c r="G3" s="99" t="s">
         <v>115</v>
       </c>
-      <c r="G3" s="99" t="s">
+      <c r="H3" s="99" t="s">
         <v>116</v>
       </c>
-      <c r="H3" s="99" t="s">
-        <v>117</v>
-      </c>
       <c r="I3" s="100" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="84" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C4" s="118" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D4" s="118" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E4" s="92" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F4" s="116"/>
       <c r="G4" s="107"/>
@@ -7975,16 +8198,16 @@
     </row>
     <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="85" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D5" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E5" s="93" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F5" s="116"/>
       <c r="G5" s="107"/>
@@ -7993,16 +8216,16 @@
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="85" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C6" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D6" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E6" s="93" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F6" s="116"/>
       <c r="G6" s="107"/>
@@ -8011,16 +8234,16 @@
     </row>
     <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="85" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C7" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D7" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E7" s="93" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F7" s="116"/>
       <c r="G7" s="107"/>
@@ -8032,13 +8255,13 @@
         <v>3</v>
       </c>
       <c r="C8" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D8" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E8" s="93" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F8" s="116"/>
       <c r="G8" s="107"/>
@@ -8047,16 +8270,16 @@
     </row>
     <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.3">
       <c r="B9" s="86" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C9" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D9" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E9" s="102" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F9" s="116"/>
       <c r="G9" s="107"/>
@@ -8065,16 +8288,16 @@
     </row>
     <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="86" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C10" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D10" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E10" s="102" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F10" s="116"/>
       <c r="G10" s="107"/>
@@ -8083,16 +8306,16 @@
     </row>
     <row r="11" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
       <c r="B11" s="85" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C11" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D11" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E11" s="102" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F11" s="116"/>
       <c r="G11" s="107"/>
@@ -8101,16 +8324,16 @@
     </row>
     <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="86" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C12" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D12" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E12" s="102" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F12" s="116"/>
       <c r="G12" s="107"/>
@@ -8119,16 +8342,16 @@
     </row>
     <row r="13" spans="1:9" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="86" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C13" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D13" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E13" s="102" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F13" s="116"/>
       <c r="G13" s="107"/>
@@ -8137,34 +8360,34 @@
     </row>
     <row r="14" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
       <c r="B14" s="87" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C14" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="D14" s="119" t="s">
         <v>180</v>
-      </c>
-      <c r="D14" s="119" t="s">
-        <v>181</v>
       </c>
       <c r="E14" s="102"/>
       <c r="F14" s="116"/>
       <c r="G14" s="107"/>
       <c r="H14" s="91"/>
       <c r="I14" s="124" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="87" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C15" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D15" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E15" s="102" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F15" s="116"/>
       <c r="G15" s="107"/>
@@ -8173,16 +8396,16 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" s="86" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C16" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D16" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E16" s="93" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F16" s="116"/>
       <c r="G16" s="107"/>
@@ -8191,16 +8414,16 @@
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="88" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C17" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D17" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E17" s="93" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F17" s="116"/>
       <c r="G17" s="91"/>
@@ -8209,16 +8432,16 @@
     </row>
     <row r="18" spans="2:9" ht="27" x14ac:dyDescent="0.3">
       <c r="B18" s="88" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C18" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D18" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E18" s="102" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F18" s="116"/>
       <c r="G18" s="107"/>
@@ -8227,16 +8450,16 @@
     </row>
     <row r="19" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="87" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C19" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D19" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E19" s="93" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F19" s="116"/>
       <c r="G19" s="106"/>
@@ -8245,16 +8468,16 @@
     </row>
     <row r="20" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="87" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C20" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D20" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E20" s="115" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F20" s="116"/>
       <c r="G20" s="112"/>
@@ -8263,16 +8486,16 @@
     </row>
     <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="89" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C21" s="120" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D21" s="120" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E21" s="105" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F21" s="117"/>
       <c r="G21" s="108"/>
@@ -8312,7 +8535,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="111" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C1" s="111"/>
       <c r="D1" s="111"/>
@@ -8323,16 +8546,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="172" t="s">
+        <v>176</v>
+      </c>
+      <c r="D2" s="172" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="172" t="s">
-        <v>178</v>
-      </c>
       <c r="E2" s="170" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F2" s="166" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G2" s="166"/>
       <c r="H2" s="166"/>
@@ -8344,30 +8567,30 @@
       <c r="D3" s="173"/>
       <c r="E3" s="171"/>
       <c r="F3" s="99" t="s">
+        <v>114</v>
+      </c>
+      <c r="G3" s="99" t="s">
         <v>115</v>
       </c>
-      <c r="G3" s="99" t="s">
+      <c r="H3" s="99" t="s">
         <v>116</v>
       </c>
-      <c r="H3" s="99" t="s">
-        <v>117</v>
-      </c>
       <c r="I3" s="100" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="84" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C4" s="118" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D4" s="118" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E4" s="92" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F4" s="116"/>
       <c r="G4" s="107"/>
@@ -8376,16 +8599,16 @@
     </row>
     <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="85" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D5" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E5" s="93" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F5" s="116"/>
       <c r="G5" s="107"/>
@@ -8394,16 +8617,16 @@
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="85" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C6" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D6" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E6" s="93" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F6" s="116"/>
       <c r="G6" s="107"/>
@@ -8412,16 +8635,16 @@
     </row>
     <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="85" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C7" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D7" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E7" s="93" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F7" s="116"/>
       <c r="G7" s="107"/>
@@ -8433,13 +8656,13 @@
         <v>3</v>
       </c>
       <c r="C8" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D8" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E8" s="93" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F8" s="116"/>
       <c r="G8" s="107"/>
@@ -8448,16 +8671,16 @@
     </row>
     <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.3">
       <c r="B9" s="86" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C9" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D9" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E9" s="102" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F9" s="116"/>
       <c r="G9" s="107"/>
@@ -8466,16 +8689,16 @@
     </row>
     <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="86" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C10" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D10" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E10" s="102" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F10" s="116"/>
       <c r="G10" s="107"/>
@@ -8484,16 +8707,16 @@
     </row>
     <row r="11" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
       <c r="B11" s="85" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C11" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D11" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E11" s="102" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F11" s="116"/>
       <c r="G11" s="107"/>
@@ -8502,16 +8725,16 @@
     </row>
     <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="86" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C12" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D12" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E12" s="102" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F12" s="116"/>
       <c r="G12" s="107"/>
@@ -8520,16 +8743,16 @@
     </row>
     <row r="13" spans="1:9" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="86" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C13" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D13" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E13" s="102" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F13" s="116"/>
       <c r="G13" s="107"/>
@@ -8538,40 +8761,40 @@
     </row>
     <row r="14" spans="1:9" ht="337.5" x14ac:dyDescent="0.3">
       <c r="B14" s="87" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C14" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="D14" s="119" t="s">
         <v>180</v>
-      </c>
-      <c r="D14" s="119" t="s">
-        <v>181</v>
       </c>
       <c r="E14" s="102"/>
       <c r="F14" s="125" t="s">
+        <v>229</v>
+      </c>
+      <c r="G14" s="125" t="s">
         <v>230</v>
       </c>
-      <c r="G14" s="125" t="s">
+      <c r="H14" s="125" t="s">
         <v>231</v>
       </c>
-      <c r="H14" s="125" t="s">
-        <v>232</v>
-      </c>
       <c r="I14" s="125" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="87" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C15" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D15" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E15" s="102" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F15" s="116"/>
       <c r="G15" s="107"/>
@@ -8580,16 +8803,16 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" s="86" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C16" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D16" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E16" s="93" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F16" s="116"/>
       <c r="G16" s="107"/>
@@ -8598,16 +8821,16 @@
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="88" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C17" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D17" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E17" s="93" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F17" s="116"/>
       <c r="G17" s="91"/>
@@ -8616,16 +8839,16 @@
     </row>
     <row r="18" spans="2:9" ht="27" x14ac:dyDescent="0.3">
       <c r="B18" s="88" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C18" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D18" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E18" s="102" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F18" s="116"/>
       <c r="G18" s="107"/>
@@ -8634,16 +8857,16 @@
     </row>
     <row r="19" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="87" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C19" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D19" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E19" s="93" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F19" s="116"/>
       <c r="G19" s="106"/>
@@ -8652,16 +8875,16 @@
     </row>
     <row r="20" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="87" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C20" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D20" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E20" s="115" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F20" s="116"/>
       <c r="G20" s="112"/>
@@ -8670,16 +8893,16 @@
     </row>
     <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="89" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C21" s="120" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D21" s="120" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E21" s="105" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F21" s="117"/>
       <c r="G21" s="108"/>
@@ -8719,7 +8942,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="111" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C1" s="111"/>
       <c r="D1" s="111"/>
@@ -8730,16 +8953,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="172" t="s">
+        <v>176</v>
+      </c>
+      <c r="D2" s="172" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="172" t="s">
-        <v>178</v>
-      </c>
       <c r="E2" s="170" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F2" s="166" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G2" s="166"/>
       <c r="H2" s="166"/>
@@ -8751,30 +8974,30 @@
       <c r="D3" s="173"/>
       <c r="E3" s="171"/>
       <c r="F3" s="99" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="G3" s="99" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="H3" s="99" t="s">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="I3" s="100" t="s">
-        <v>273</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="153" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C4" s="118" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D4" s="118" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E4" s="142" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F4" s="143"/>
       <c r="G4" s="144"/>
@@ -8783,98 +9006,98 @@
     </row>
     <row r="5" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
       <c r="B5" s="156" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C5" s="119" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="D5" s="119" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E5" s="102" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F5" s="116"/>
       <c r="G5" s="107"/>
       <c r="H5" s="125" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="I5" s="137" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="154" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="C6" s="119" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="D6" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E6" s="102" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F6" s="125"/>
       <c r="G6" s="125"/>
       <c r="H6" s="135" t="s">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="I6" s="158"/>
     </row>
     <row r="7" spans="1:9" ht="93" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="154" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C7" s="119" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="D7" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E7" s="102" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="F7" s="116"/>
       <c r="G7" s="107"/>
       <c r="H7" s="91"/>
       <c r="I7" s="136" t="s">
-        <v>316</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="87.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="154" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C8" s="119" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="D8" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E8" s="102" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="F8" s="116"/>
       <c r="G8" s="106"/>
       <c r="H8" s="91"/>
       <c r="I8" s="136" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="155" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C9" s="119" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="D9" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E9" s="93" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F9" s="116"/>
       <c r="G9" s="107"/>
@@ -8883,16 +9106,16 @@
     </row>
     <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="155" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C10" s="119" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="D10" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E10" s="93" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F10" s="116"/>
       <c r="G10" s="107"/>
@@ -8901,16 +9124,16 @@
     </row>
     <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="155" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C11" s="119" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="D11" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E11" s="93" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F11" s="116"/>
       <c r="G11" s="107"/>
@@ -8919,16 +9142,16 @@
     </row>
     <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="155" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C12" s="119" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="D12" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E12" s="93" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F12" s="116"/>
       <c r="G12" s="107"/>
@@ -8937,128 +9160,128 @@
     </row>
     <row r="13" spans="1:9" ht="222" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="134" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C13" s="119" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="D13" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E13" s="102" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F13" s="116"/>
       <c r="G13" s="107"/>
       <c r="H13" s="135" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="I13" s="136" t="s">
-        <v>318</v>
+        <v>298</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
       <c r="B14" s="133" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C14" s="119" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="D14" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E14" s="102" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F14" s="116"/>
       <c r="G14" s="107"/>
       <c r="H14" s="135" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="I14" s="136" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
       <c r="B15" s="133" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C15" s="119" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="D15" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E15" s="102" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F15" s="116"/>
       <c r="G15" s="135" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H15" s="139" t="s">
-        <v>305</v>
-      </c>
-      <c r="I15" s="136" t="s">
-        <v>308</v>
+        <v>287</v>
+      </c>
+      <c r="I15" s="177" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="228.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="133" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C16" s="119" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="D16" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E16" s="102" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F16" s="116"/>
       <c r="G16" s="107"/>
       <c r="H16" s="135" t="s">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="I16" s="136" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="132" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C17" s="119" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="D17" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E17" s="115" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F17" s="116"/>
       <c r="G17" s="131" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H17" s="157" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="I17" s="138"/>
     </row>
     <row r="18" spans="2:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="133" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C18" s="119" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="D18" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E18" s="115" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="F18" s="116"/>
       <c r="G18" s="131"/>
@@ -9070,41 +9293,41 @@
         <v>3</v>
       </c>
       <c r="C19" s="141" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="D19" s="141" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E19" s="93" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F19" s="116"/>
       <c r="G19" s="135" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H19" s="135" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="I19" s="136" t="s">
-        <v>309</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="145" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C20" s="146" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="D20" s="146" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E20" s="147" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F20" s="148"/>
       <c r="G20" s="149" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H20" s="150"/>
       <c r="I20" s="151"/>
@@ -9142,7 +9365,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="111" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C1" s="111"/>
       <c r="D1" s="111"/>
@@ -9153,16 +9376,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="172" t="s">
+        <v>176</v>
+      </c>
+      <c r="D2" s="172" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="172" t="s">
-        <v>178</v>
-      </c>
       <c r="E2" s="170" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F2" s="166" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="G2" s="166"/>
       <c r="H2" s="166"/>
@@ -9174,70 +9397,68 @@
       <c r="D3" s="173"/>
       <c r="E3" s="171"/>
       <c r="F3" s="99" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="G3" s="99" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="H3" s="99" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="I3" s="100" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="153" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C4" s="118" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D4" s="118" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E4" s="142" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F4" s="143"/>
       <c r="G4" s="144"/>
       <c r="H4" s="90"/>
       <c r="I4" s="94"/>
     </row>
-    <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
       <c r="B5" s="156" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C5" s="119" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="D5" s="119" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E5" s="102" t="s">
-        <v>162</v>
-      </c>
-      <c r="F5" s="116"/>
-      <c r="G5" s="107"/>
-      <c r="H5" s="125" t="s">
-        <v>281</v>
-      </c>
-      <c r="I5" s="137" t="s">
-        <v>280</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="F5" s="125" t="s">
+        <v>306</v>
+      </c>
+      <c r="G5" s="174"/>
+      <c r="H5" s="125"/>
+      <c r="I5" s="137"/>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="154" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="C6" s="119" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="D6" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E6" s="102" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F6" s="125"/>
       <c r="G6" s="125"/>
@@ -9246,16 +9467,16 @@
     </row>
     <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="154" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C7" s="119" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="D7" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E7" s="102" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F7" s="116"/>
       <c r="G7" s="107"/>
@@ -9264,16 +9485,16 @@
     </row>
     <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="154" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C8" s="119" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="D8" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E8" s="93" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F8" s="116"/>
       <c r="G8" s="106"/>
@@ -9282,16 +9503,16 @@
     </row>
     <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="155" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C9" s="119" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="D9" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E9" s="93" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F9" s="116"/>
       <c r="G9" s="107"/>
@@ -9300,16 +9521,16 @@
     </row>
     <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="155" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C10" s="119" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="D10" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E10" s="93" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F10" s="116"/>
       <c r="G10" s="107"/>
@@ -9318,16 +9539,16 @@
     </row>
     <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="155" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C11" s="119" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="D11" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E11" s="93" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F11" s="116"/>
       <c r="G11" s="107"/>
@@ -9336,184 +9557,170 @@
     </row>
     <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="155" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C12" s="119" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="D12" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E12" s="93" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F12" s="116"/>
       <c r="G12" s="107"/>
       <c r="H12" s="140"/>
       <c r="I12" s="95"/>
     </row>
-    <row r="13" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="94.5" x14ac:dyDescent="0.3">
       <c r="B13" s="134" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C13" s="119" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="D13" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E13" s="102" t="s">
+        <v>263</v>
+      </c>
+      <c r="F13" s="135" t="s">
+        <v>315</v>
+      </c>
+      <c r="G13" s="174"/>
+      <c r="H13" s="135"/>
+      <c r="I13" s="136"/>
+    </row>
+    <row r="14" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="B14" s="133" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="119" t="s">
+        <v>273</v>
+      </c>
+      <c r="D14" s="119" t="s">
+        <v>178</v>
+      </c>
+      <c r="E14" s="102" t="s">
         <v>264</v>
       </c>
-      <c r="F13" s="116"/>
-      <c r="G13" s="107"/>
-      <c r="H13" s="135" t="s">
-        <v>277</v>
-      </c>
-      <c r="I13" s="136" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="133" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" s="119" t="s">
-        <v>287</v>
-      </c>
-      <c r="D14" s="119" t="s">
-        <v>179</v>
-      </c>
-      <c r="E14" s="102" t="s">
-        <v>265</v>
-      </c>
-      <c r="F14" s="116"/>
-      <c r="G14" s="107"/>
-      <c r="H14" s="135" t="s">
-        <v>279</v>
-      </c>
-      <c r="I14" s="136" t="s">
-        <v>278</v>
-      </c>
+      <c r="F14" s="135" t="s">
+        <v>309</v>
+      </c>
+      <c r="G14" s="174"/>
+      <c r="H14" s="135"/>
+      <c r="I14" s="136"/>
     </row>
     <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
       <c r="B15" s="133" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C15" s="119" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="D15" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E15" s="102" t="s">
-        <v>263</v>
-      </c>
-      <c r="F15" s="116"/>
-      <c r="G15" s="135" t="s">
-        <v>269</v>
-      </c>
-      <c r="H15" s="139" t="s">
+        <v>262</v>
+      </c>
+      <c r="F15" s="135" t="s">
+        <v>310</v>
+      </c>
+      <c r="G15" s="175"/>
+      <c r="H15" s="139"/>
+      <c r="I15" s="136"/>
+    </row>
+    <row r="16" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
+      <c r="B16" s="133" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="119" t="s">
         <v>275</v>
       </c>
-      <c r="I15" s="136" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="81" x14ac:dyDescent="0.3">
-      <c r="B16" s="133" t="s">
-        <v>86</v>
-      </c>
-      <c r="C16" s="119" t="s">
-        <v>289</v>
-      </c>
       <c r="D16" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E16" s="102" t="s">
-        <v>266</v>
-      </c>
-      <c r="F16" s="116"/>
-      <c r="G16" s="107"/>
-      <c r="H16" s="135" t="s">
-        <v>282</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="F16" s="135" t="s">
+        <v>312</v>
+      </c>
+      <c r="G16" s="174"/>
+      <c r="H16" s="135"/>
       <c r="I16" s="136"/>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="132" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C17" s="119" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="D17" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E17" s="115" t="s">
-        <v>270</v>
-      </c>
-      <c r="F17" s="116"/>
-      <c r="G17" s="131" t="s">
-        <v>261</v>
-      </c>
-      <c r="H17" s="139" t="s">
-        <v>283</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="F17" s="157"/>
+      <c r="G17" s="176"/>
+      <c r="H17" s="139"/>
       <c r="I17" s="138"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="133" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C18" s="119" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="D18" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E18" s="115"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="131"/>
+      <c r="F18" s="157"/>
+      <c r="G18" s="176"/>
       <c r="H18" s="139"/>
       <c r="I18" s="138"/>
     </row>
-    <row r="19" spans="2:9" ht="108" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" ht="54" x14ac:dyDescent="0.3">
       <c r="B19" s="152" t="s">
         <v>3</v>
       </c>
       <c r="C19" s="141" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="D19" s="141" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E19" s="93" t="s">
-        <v>157</v>
-      </c>
-      <c r="F19" s="116"/>
-      <c r="G19" s="135" t="s">
-        <v>268</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="F19" s="135" t="s">
+        <v>290</v>
+      </c>
+      <c r="G19" s="175"/>
       <c r="I19" s="95"/>
     </row>
     <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="145" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C20" s="146" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="D20" s="146" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E20" s="147" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F20" s="148"/>
-      <c r="G20" s="149" t="s">
-        <v>267</v>
-      </c>
+      <c r="G20" s="149"/>
       <c r="H20" s="150"/>
       <c r="I20" s="151"/>
     </row>
@@ -9527,5 +9734,6 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="318">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2422,24 +2422,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[임제훈 사원]
-- CPU 및 메모리 부하율 관리 대책 르네사스 문의 (~10/27)
-- 사이버 보안 항목 QV와 비교 및 리스트업 후 공조시스템설계팀 회신 (~10/29)
-- 제어기 선행품질 검증 현황 관련 기아 오토랜드 방문 후 자료 회신 (~10/29)
-  : 1. P2 단계 전까지 매 월 1회 제어기 검증 현황 관련 회의 진행 예정
-    2. 진행 단계 별로 이력 및 변경점 꾸준히 업데이트 해서 자료 회신 요청
-    3. Fail Safety 항목 공유 요청
-    4. 제어기 검증 프로세스 관련 자료 공유 요청
-    5. 컨버전 룰이 무엇인지에 대한 자료 공유 요청
-    6. S/W 검증 현황의 검증 항목별 LIST 자료 공유 요청
-    7. CPU / 메모리 부하율 관리 방안 재확인 요청
-    8. 고장 진단 로그 저장 가능 개수 재확인 요청
-- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)
-- 설계 변경 진행 (~11/10)
-  : 기구팀 문의 결과, QV, SVm, BJ 담당자 전부 똑같다고 함. 결재 라인 똑같이 예정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>4주차 (10/24 ~ 10/30)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2505,142 +2487,6 @@
   : SW 대응은 딱히 없을 것 같다고 했지만, 결과나 진행 사항 파악 필요
 - LHD R로직 튜닝
 - RHD R로직 튜닝 (HVAC 미보유, 보류)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">[임제훈 사원]
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R로직 튜닝 (~10/27)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ESIR 일정에 맞춰서 5가지 항목 다 가능한지 파악하기 (~10/29)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- 공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (10/30)
-  : 휴가 중, 목요일 출근 예정, 이 때 메일로 다시 문의
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ES 규격 대로 15초 내로 목표 전력 도달 SW로 변경 (~10/29)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : Softstart enable 0으로 변경
-  : Sofftstart 0일 때, R로직 확인, 전력 구간 별 칼로리와 CAN 출력 차이 비교
-- ESIR 계획서 등록 (~10/31)
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- 최신 승인도 확인 (~10/31)
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>제작사양서 배포 준비 (~10/31)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : SW 파일, 제어사양서
-  : 10월 14일부터 tc 160℃, 스톤 기울기 변경되었음
-  : 제작사양서 배포 기준, tc 160℃ 스톤 기울기 변경된 샘플 기준으로 튜닝 완료
-  : P1 때 tc 165℃ 변경 협의 중</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2718,14 +2564,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[임제훈 사원]
-- 공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (~11/03)
-  : 10/30 문의 완료, 재회신 요청 예정
-- ESIR 계획서 등록 (~11/05)
-- 최신 승인도 확인 (~11/06)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[우리산업]
 PM : 유정호, 품질 : 박상철, 기구 : 김민수, 공준석, HW : 신지훈
 [전자편의개발 2팀] 
@@ -2755,10 +2593,267 @@
     <t>[임제훈 사원]
 - 사이버 보안 항목 QV와 비교 및 리스트업 후 공조시스템설계팀 회신 (~11/05)
   : ES95489-21 빼는 것은 안됨. 업데이트에 해당하는 항목 N/A로 하자고 회신 받음
-- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~11/03)
+- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~11/05)
 - 설계 변경 진행 (~11/10)
   : 기구팀 문의 결과, QV, SVm, BJ 담당자 전부 똑같다고 함. 결재 라인 똑같이 예정
   : 설계 변경 문서 작성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SU2i CARRY OVER
+Proto (진행 중)
+P1 (26/05/15)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R로직 튜닝 (~10/27)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ESIR 일정에 맞춰서 5가지 항목 다 가능한지 파악하기 (~10/29)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ES 규격 대로 15초 내로 목표 전력 도달 SW로 변경 (~10/29)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : Softstart enable 0으로 변경
+  : Sofftstart 0일 때, R로직 확인, 전력 구간 별 칼로리와 CAN 출력 차이 비교</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제작사양서 배포 준비 (~10/31)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : SW 파일, 제어사양서
+  : 10월 14일부터 tc 160℃, 스톤 기울기 변경되었음
+  : 제작사양서 배포 기준, tc 160℃ 스톤 기울기 변경된 샘플 기준으로 튜닝 완료
+  : P1 때 tc 165℃ 변경 협의 중
+- 공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (10/30)
+  : 휴가 중, 목요일 출근 예정, 이 때 메일로 다시 문의
+- ESIR 계획서 등록 (~10/31)
+- 최신 승인도 확인 (~10/31)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CPU 및 메모리 부하율 관리 대책 르네사스 문의 (~10/27)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사이버 보안 항목 QV와 비교 및 리스트업 후 공조시스템설계팀 회신 (~10/29)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제어기 선행품질 검증 현황 관련 기아 오토랜드 방문 후 자료 회신 (~10/29)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : 1. P2 단계 전까지 매 월 1회 제어기 검증 현황 관련 회의 진행 예정
+    2. 진행 단계 별로 이력 및 변경점 꾸준히 업데이트 해서 자료 회신 요청
+    3. Fail Safety 항목 공유 요청
+    4. 제어기 검증 프로세스 관련 자료 공유 요청
+    5. 컨버전 룰이 무엇인지에 대한 자료 공유 요청
+    6. S/W 검증 현황의 검증 항목별 LIST 자료 공유 요청
+    7. CPU / 메모리 부하율 관리 방안 재확인 요청
+    8. 고장 진단 로그 저장 가능 개수 재확인 요청
+- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~10/31)
+- 설계 변경 진행 (~11/10)
+  : 기구팀 문의 결과, QV, SVm, BJ 담당자 전부 똑같다고 함. 결재 라인 똑같이 예정</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- PTC 벤치 테스트 한온에서 진행 (11/12)
+  : BJ RHD HVAC 수령 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (11/03)
+  : 일정 조율에 대한 사유 작성하여 재회신 예정, 조건부 승인으로 가면 된다고 함
+  : 사이버 보안팀에 시료 제출하여 선 공정 검사 진행 여부는 확인 해본다고 함
+- ESIR 계획서 등록 (~11/05)
+- 최신 승인도 확인 (~11/06)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2993,7 +3088,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="83">
+  <borders count="82">
     <border>
       <left/>
       <right/>
@@ -4118,15 +4213,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="hair">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -4148,7 +4234,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4626,6 +4712,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="80" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="81" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4670,21 +4768,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="81" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -5308,90 +5391,90 @@
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="159" t="s">
+      <c r="B2" s="163" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="161" t="s">
+      <c r="C2" s="165" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="161" t="s">
+      <c r="D2" s="165" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="165">
+      <c r="E2" s="169">
         <v>23</v>
       </c>
-      <c r="F2" s="163"/>
-      <c r="G2" s="163"/>
-      <c r="H2" s="163"/>
-      <c r="I2" s="163"/>
-      <c r="J2" s="163"/>
-      <c r="K2" s="163"/>
-      <c r="L2" s="163"/>
-      <c r="M2" s="163"/>
-      <c r="N2" s="163"/>
-      <c r="O2" s="163"/>
-      <c r="P2" s="163"/>
-      <c r="Q2" s="163">
+      <c r="F2" s="167"/>
+      <c r="G2" s="167"/>
+      <c r="H2" s="167"/>
+      <c r="I2" s="167"/>
+      <c r="J2" s="167"/>
+      <c r="K2" s="167"/>
+      <c r="L2" s="167"/>
+      <c r="M2" s="167"/>
+      <c r="N2" s="167"/>
+      <c r="O2" s="167"/>
+      <c r="P2" s="167"/>
+      <c r="Q2" s="167">
         <v>24</v>
       </c>
-      <c r="R2" s="163"/>
-      <c r="S2" s="163"/>
-      <c r="T2" s="163"/>
-      <c r="U2" s="163"/>
-      <c r="V2" s="163"/>
-      <c r="W2" s="163"/>
-      <c r="X2" s="163"/>
-      <c r="Y2" s="163"/>
-      <c r="Z2" s="163"/>
-      <c r="AA2" s="163"/>
-      <c r="AB2" s="163"/>
-      <c r="AC2" s="163">
+      <c r="R2" s="167"/>
+      <c r="S2" s="167"/>
+      <c r="T2" s="167"/>
+      <c r="U2" s="167"/>
+      <c r="V2" s="167"/>
+      <c r="W2" s="167"/>
+      <c r="X2" s="167"/>
+      <c r="Y2" s="167"/>
+      <c r="Z2" s="167"/>
+      <c r="AA2" s="167"/>
+      <c r="AB2" s="167"/>
+      <c r="AC2" s="167">
         <v>25</v>
       </c>
-      <c r="AD2" s="163"/>
-      <c r="AE2" s="163"/>
-      <c r="AF2" s="163"/>
-      <c r="AG2" s="163"/>
-      <c r="AH2" s="163"/>
-      <c r="AI2" s="163"/>
-      <c r="AJ2" s="163"/>
-      <c r="AK2" s="163"/>
-      <c r="AL2" s="163"/>
-      <c r="AM2" s="163"/>
-      <c r="AN2" s="163"/>
-      <c r="AO2" s="163">
+      <c r="AD2" s="167"/>
+      <c r="AE2" s="167"/>
+      <c r="AF2" s="167"/>
+      <c r="AG2" s="167"/>
+      <c r="AH2" s="167"/>
+      <c r="AI2" s="167"/>
+      <c r="AJ2" s="167"/>
+      <c r="AK2" s="167"/>
+      <c r="AL2" s="167"/>
+      <c r="AM2" s="167"/>
+      <c r="AN2" s="167"/>
+      <c r="AO2" s="167">
         <v>26</v>
       </c>
-      <c r="AP2" s="163"/>
-      <c r="AQ2" s="163"/>
-      <c r="AR2" s="163"/>
-      <c r="AS2" s="163"/>
-      <c r="AT2" s="163"/>
-      <c r="AU2" s="163"/>
-      <c r="AV2" s="163"/>
-      <c r="AW2" s="163"/>
-      <c r="AX2" s="163"/>
-      <c r="AY2" s="163"/>
-      <c r="AZ2" s="164"/>
-      <c r="BA2" s="163">
+      <c r="AP2" s="167"/>
+      <c r="AQ2" s="167"/>
+      <c r="AR2" s="167"/>
+      <c r="AS2" s="167"/>
+      <c r="AT2" s="167"/>
+      <c r="AU2" s="167"/>
+      <c r="AV2" s="167"/>
+      <c r="AW2" s="167"/>
+      <c r="AX2" s="167"/>
+      <c r="AY2" s="167"/>
+      <c r="AZ2" s="168"/>
+      <c r="BA2" s="167">
         <v>27</v>
       </c>
-      <c r="BB2" s="163"/>
-      <c r="BC2" s="163"/>
-      <c r="BD2" s="163"/>
-      <c r="BE2" s="163"/>
-      <c r="BF2" s="163"/>
-      <c r="BG2" s="163"/>
-      <c r="BH2" s="163"/>
-      <c r="BI2" s="163"/>
-      <c r="BJ2" s="163"/>
-      <c r="BK2" s="163"/>
-      <c r="BL2" s="164"/>
+      <c r="BB2" s="167"/>
+      <c r="BC2" s="167"/>
+      <c r="BD2" s="167"/>
+      <c r="BE2" s="167"/>
+      <c r="BF2" s="167"/>
+      <c r="BG2" s="167"/>
+      <c r="BH2" s="167"/>
+      <c r="BI2" s="167"/>
+      <c r="BJ2" s="167"/>
+      <c r="BK2" s="167"/>
+      <c r="BL2" s="168"/>
     </row>
     <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="160"/>
-      <c r="C3" s="162"/>
-      <c r="D3" s="162"/>
+      <c r="B3" s="164"/>
+      <c r="C3" s="166"/>
+      <c r="D3" s="166"/>
       <c r="E3" s="22">
         <v>1</v>
       </c>
@@ -6292,7 +6375,7 @@
         <v>82</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="7"/>
@@ -6728,8 +6811,8 @@
       <c r="C18" s="59" t="s">
         <v>258</v>
       </c>
-      <c r="D18" s="178" t="s">
-        <v>314</v>
+      <c r="D18" s="162" t="s">
+        <v>311</v>
       </c>
       <c r="E18" s="64"/>
       <c r="F18" s="65"/>
@@ -7366,39 +7449,39 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="168" t="s">
+      <c r="B2" s="172" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="172" t="s">
+      <c r="C2" s="176" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="172" t="s">
+      <c r="D2" s="176" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="170" t="s">
+      <c r="E2" s="174" t="s">
         <v>126</v>
       </c>
       <c r="F2" s="98" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="166" t="s">
+      <c r="G2" s="170" t="s">
         <v>113</v>
       </c>
-      <c r="H2" s="166"/>
-      <c r="I2" s="166"/>
-      <c r="J2" s="167"/>
-      <c r="K2" s="166" t="s">
+      <c r="H2" s="170"/>
+      <c r="I2" s="170"/>
+      <c r="J2" s="171"/>
+      <c r="K2" s="170" t="s">
         <v>182</v>
       </c>
-      <c r="L2" s="166"/>
-      <c r="M2" s="166"/>
-      <c r="N2" s="167"/>
+      <c r="L2" s="170"/>
+      <c r="M2" s="170"/>
+      <c r="N2" s="171"/>
     </row>
     <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="169"/>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="171"/>
+      <c r="B3" s="173"/>
+      <c r="C3" s="177"/>
+      <c r="D3" s="177"/>
+      <c r="E3" s="175"/>
       <c r="F3" s="99" t="s">
         <v>111</v>
       </c>
@@ -8141,30 +8224,30 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="168" t="s">
+      <c r="B2" s="172" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="172" t="s">
+      <c r="C2" s="176" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="172" t="s">
+      <c r="D2" s="176" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="170" t="s">
+      <c r="E2" s="174" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="166" t="s">
+      <c r="F2" s="170" t="s">
         <v>182</v>
       </c>
-      <c r="G2" s="166"/>
-      <c r="H2" s="166"/>
-      <c r="I2" s="167"/>
+      <c r="G2" s="170"/>
+      <c r="H2" s="170"/>
+      <c r="I2" s="171"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="169"/>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="171"/>
+      <c r="B3" s="173"/>
+      <c r="C3" s="177"/>
+      <c r="D3" s="177"/>
+      <c r="E3" s="175"/>
       <c r="F3" s="99" t="s">
         <v>114</v>
       </c>
@@ -8542,30 +8625,30 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="168" t="s">
+      <c r="B2" s="172" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="172" t="s">
+      <c r="C2" s="176" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="172" t="s">
+      <c r="D2" s="176" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="170" t="s">
+      <c r="E2" s="174" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="166" t="s">
+      <c r="F2" s="170" t="s">
         <v>227</v>
       </c>
-      <c r="G2" s="166"/>
-      <c r="H2" s="166"/>
-      <c r="I2" s="167"/>
+      <c r="G2" s="170"/>
+      <c r="H2" s="170"/>
+      <c r="I2" s="171"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="169"/>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="171"/>
+      <c r="B3" s="173"/>
+      <c r="C3" s="177"/>
+      <c r="D3" s="177"/>
+      <c r="E3" s="175"/>
       <c r="F3" s="99" t="s">
         <v>114</v>
       </c>
@@ -8949,41 +9032,41 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="168" t="s">
+      <c r="B2" s="172" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="172" t="s">
+      <c r="C2" s="176" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="172" t="s">
+      <c r="D2" s="176" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="170" t="s">
+      <c r="E2" s="174" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="166" t="s">
+      <c r="F2" s="170" t="s">
         <v>259</v>
       </c>
-      <c r="G2" s="166"/>
-      <c r="H2" s="166"/>
-      <c r="I2" s="167"/>
+      <c r="G2" s="170"/>
+      <c r="H2" s="170"/>
+      <c r="I2" s="171"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="169"/>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="171"/>
+      <c r="B3" s="173"/>
+      <c r="C3" s="177"/>
+      <c r="D3" s="177"/>
+      <c r="E3" s="175"/>
       <c r="F3" s="99" t="s">
         <v>280</v>
       </c>
       <c r="G3" s="99" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H3" s="99" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="I3" s="100" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -9177,7 +9260,7 @@
         <v>289</v>
       </c>
       <c r="I13" s="136" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -9199,7 +9282,7 @@
         <v>286</v>
       </c>
       <c r="I14" s="136" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -9222,8 +9305,8 @@
       <c r="H15" s="139" t="s">
         <v>287</v>
       </c>
-      <c r="I15" s="177" t="s">
-        <v>311</v>
+      <c r="I15" s="161" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="228.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9245,7 +9328,7 @@
         <v>291</v>
       </c>
       <c r="I16" s="136" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -9372,41 +9455,41 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="168" t="s">
+      <c r="B2" s="172" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="172" t="s">
+      <c r="C2" s="176" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="172" t="s">
+      <c r="D2" s="176" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="170" t="s">
+      <c r="E2" s="174" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="166" t="s">
+      <c r="F2" s="170" t="s">
         <v>279</v>
       </c>
-      <c r="G2" s="166"/>
-      <c r="H2" s="166"/>
-      <c r="I2" s="167"/>
+      <c r="G2" s="170"/>
+      <c r="H2" s="170"/>
+      <c r="I2" s="171"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="169"/>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="171"/>
+      <c r="B3" s="173"/>
+      <c r="C3" s="177"/>
+      <c r="D3" s="177"/>
+      <c r="E3" s="175"/>
       <c r="F3" s="99" t="s">
+        <v>301</v>
+      </c>
+      <c r="G3" s="99" t="s">
         <v>302</v>
       </c>
-      <c r="G3" s="99" t="s">
+      <c r="H3" s="99" t="s">
         <v>303</v>
       </c>
-      <c r="H3" s="99" t="s">
+      <c r="I3" s="100" t="s">
         <v>304</v>
-      </c>
-      <c r="I3" s="100" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -9441,9 +9524,9 @@
         <v>161</v>
       </c>
       <c r="F5" s="125" t="s">
-        <v>306</v>
-      </c>
-      <c r="G5" s="174"/>
+        <v>305</v>
+      </c>
+      <c r="G5" s="159"/>
       <c r="H5" s="125"/>
       <c r="I5" s="137"/>
     </row>
@@ -9587,9 +9670,9 @@
         <v>263</v>
       </c>
       <c r="F13" s="135" t="s">
-        <v>315</v>
-      </c>
-      <c r="G13" s="174"/>
+        <v>312</v>
+      </c>
+      <c r="G13" s="159"/>
       <c r="H13" s="135"/>
       <c r="I13" s="136"/>
     </row>
@@ -9607,9 +9690,11 @@
         <v>264</v>
       </c>
       <c r="F14" s="135" t="s">
-        <v>309</v>
-      </c>
-      <c r="G14" s="174"/>
+        <v>307</v>
+      </c>
+      <c r="G14" s="159" t="s">
+        <v>316</v>
+      </c>
       <c r="H14" s="135"/>
       <c r="I14" s="136"/>
     </row>
@@ -9627,13 +9712,13 @@
         <v>262</v>
       </c>
       <c r="F15" s="135" t="s">
-        <v>310</v>
-      </c>
-      <c r="G15" s="175"/>
+        <v>308</v>
+      </c>
+      <c r="G15" s="160"/>
       <c r="H15" s="139"/>
       <c r="I15" s="136"/>
     </row>
-    <row r="16" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="81" x14ac:dyDescent="0.3">
       <c r="B16" s="133" t="s">
         <v>85</v>
       </c>
@@ -9647,9 +9732,9 @@
         <v>265</v>
       </c>
       <c r="F16" s="135" t="s">
-        <v>312</v>
-      </c>
-      <c r="G16" s="174"/>
+        <v>317</v>
+      </c>
+      <c r="G16" s="159"/>
       <c r="H16" s="135"/>
       <c r="I16" s="136"/>
     </row>
@@ -9664,10 +9749,10 @@
         <v>178</v>
       </c>
       <c r="E17" s="115" t="s">
-        <v>269</v>
+        <v>313</v>
       </c>
       <c r="F17" s="157"/>
-      <c r="G17" s="176"/>
+      <c r="G17" s="157"/>
       <c r="H17" s="139"/>
       <c r="I17" s="138"/>
     </row>
@@ -9683,7 +9768,7 @@
       </c>
       <c r="E18" s="115"/>
       <c r="F18" s="157"/>
-      <c r="G18" s="176"/>
+      <c r="G18" s="135"/>
       <c r="H18" s="139"/>
       <c r="I18" s="138"/>
     </row>
@@ -9703,7 +9788,7 @@
       <c r="F19" s="135" t="s">
         <v>290</v>
       </c>
-      <c r="G19" s="175"/>
+      <c r="G19" s="160"/>
       <c r="I19" s="95"/>
     </row>
     <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="321">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2854,6 +2854,25 @@
   : 사이버 보안팀에 시료 제출하여 선 공정 검사 진행 여부는 확인 해본다고 함
 - ESIR 계획서 등록 (~11/05)
 - 최신 승인도 확인 (~11/06)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">[임제훈 사원]
+- 공조 로컬 CAN 심의회 진행 (11/10)
+  : SVm, BJ, NX5e, MX5a, HE1i 대상
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 공조 로컬 CAN 심의회 진행 (11/10)
+  : SVm, BJ, NX5e, MX5a, HE1i 대상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 공조 로컬 CAN 심의회 진행 (11/10)
+  : SVm, BJ, NX5e, MX5a, HE1i 대상</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -9562,7 +9581,9 @@
         <v>162</v>
       </c>
       <c r="F7" s="116"/>
-      <c r="G7" s="107"/>
+      <c r="G7" s="107" t="s">
+        <v>320</v>
+      </c>
       <c r="H7" s="91"/>
       <c r="I7" s="95"/>
     </row>
@@ -9672,7 +9693,9 @@
       <c r="F13" s="135" t="s">
         <v>312</v>
       </c>
-      <c r="G13" s="159"/>
+      <c r="G13" s="159" t="s">
+        <v>320</v>
+      </c>
       <c r="H13" s="135"/>
       <c r="I13" s="136"/>
     </row>
@@ -9734,7 +9757,9 @@
       <c r="F16" s="135" t="s">
         <v>317</v>
       </c>
-      <c r="G16" s="159"/>
+      <c r="G16" s="159" t="s">
+        <v>318</v>
+      </c>
       <c r="H16" s="135"/>
       <c r="I16" s="136"/>
     </row>
@@ -9752,7 +9777,9 @@
         <v>313</v>
       </c>
       <c r="F17" s="157"/>
-      <c r="G17" s="157"/>
+      <c r="G17" s="121" t="s">
+        <v>319</v>
+      </c>
       <c r="H17" s="139"/>
       <c r="I17" s="138"/>
     </row>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\일정\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\PROJECT\Gitlab\HMC\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="323">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2492,12 +2492,6 @@
   </si>
   <si>
     <t>[임제훈 사원]
-- LHD R로직 튜닝
-- RHD R로직 튜닝 (HVAC 미보유, 보류)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
 - R로직 튜닝</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2587,16 +2581,6 @@
 wjdworms1357@hyundai.com
 김동환 연구원 010-4162-2776
 kdh2776@hyundai.com</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- 사이버 보안 항목 QV와 비교 및 리스트업 후 공조시스템설계팀 회신 (~11/05)
-  : ES95489-21 빼는 것은 안됨. 업데이트에 해당하는 항목 N/A로 하자고 회신 받음
-- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~11/05)
-- 설계 변경 진행 (~11/10)
-  : 기구팀 문의 결과, QV, SVm, BJ 담당자 전부 똑같다고 함. 결재 라인 똑같이 예정
-  : 설계 변경 문서 작성</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2843,12 +2827,6 @@
   </si>
   <si>
     <t>[임제훈 사원]
-- PTC 벤치 테스트 한온에서 진행 (11/12)
-  : BJ RHD HVAC 수령 예정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
 - 공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (11/03)
   : 일정 조율에 대한 사유 작성하여 재회신 예정, 조건부 승인으로 가면 된다고 함
   : 사이버 보안팀에 시료 제출하여 선 공정 검사 진행 여부는 확인 해본다고 함
@@ -2873,6 +2851,50 @@
     <t>[임제훈 사원]
 - 공조 로컬 CAN 심의회 진행 (11/10)
   : SVm, BJ, NX5e, MX5a, HE1i 대상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- LHD R로직 튜닝
+- RHD R로직 튜닝 (HVAC 미보유, 보류)
+[김진겸 사원]
+- RHD R 로직 튜닝을 위한 HVAC 수령 대기 중
+  (11/12 기구팀 한온 출장 시 수령 예정)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 사이버 보안 항목 QV와 비교 및 리스트업 후 공조시스템설계팀 회신 (~11/05)
+  : ES95489-21 빼는 것은 안됨. 업데이트에 해당하는 항목 N/A로 하자고 회신 받음
+- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~11/05)
+- 설계 변경 진행 (~11/10)
+  : 기구팀 문의 결과, QV, SVm, BJ 담당자 전부 똑같다고 함. 결재 라인 똑같이 예정
+  : 설계 변경 문서 작성
+[김진겸 사원]
+- 설계변경 시 ERP 등록 준비(~11/10)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 공조 로컬 CAN 심의회 진행 (11/10)
+  : SVm, BJ, NX5e, MX5a, HE1i 대상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[김진겸 사원]
+- PROTO 차량 난방 평가 진행(10/31, 현대 남양연구소)
+- 난방 성능 불만족으로, 고객사 측에서 성능 증대 요청 중
+  (기구 대응 중, 김민수 선임)
+- 11/05~11/07 한온에서 동일 차량으로 평가 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- PTC 벤치 테스트 한온에서 진행 (11/12)
+  : BJ RHD HVAC 수령 예정
+[김진겸 사원]
+- 열에너지차량시험팀 측에서 11/10(월) 챔버 확보
+  : 자동차 측에서 실차 튜닝 요청, 참석 인원 선정 필요</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5123,6 +5145,49 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2886076</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1009650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>4645520</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1619250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9353551" y="4581525"/>
+          <a:ext cx="1759444" cy="609600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
@@ -6394,7 +6459,7 @@
         <v>82</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="7"/>
@@ -6831,7 +6896,7 @@
         <v>258</v>
       </c>
       <c r="D18" s="162" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E18" s="64"/>
       <c r="F18" s="65"/>
@@ -9279,7 +9344,7 @@
         <v>289</v>
       </c>
       <c r="I13" s="136" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -9325,7 +9390,7 @@
         <v>287</v>
       </c>
       <c r="I15" s="161" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="228.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9347,7 +9412,7 @@
         <v>291</v>
       </c>
       <c r="I16" s="136" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -9567,7 +9632,7 @@
       <c r="H6" s="125"/>
       <c r="I6" s="137"/>
     </row>
-    <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="138" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="154" t="s">
         <v>75</v>
       </c>
@@ -9580,9 +9645,11 @@
       <c r="E7" s="102" t="s">
         <v>162</v>
       </c>
-      <c r="F7" s="116"/>
+      <c r="F7" s="125" t="s">
+        <v>321</v>
+      </c>
       <c r="G7" s="107" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H7" s="91"/>
       <c r="I7" s="95"/>
@@ -9677,7 +9744,7 @@
       <c r="H12" s="140"/>
       <c r="I12" s="95"/>
     </row>
-    <row r="13" spans="1:9" ht="94.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="135" x14ac:dyDescent="0.3">
       <c r="B13" s="134" t="s">
         <v>62</v>
       </c>
@@ -9691,7 +9758,7 @@
         <v>263</v>
       </c>
       <c r="F13" s="135" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="G13" s="159" t="s">
         <v>320</v>
@@ -9699,7 +9766,7 @@
       <c r="H13" s="135"/>
       <c r="I13" s="136"/>
     </row>
-    <row r="14" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="94.5" x14ac:dyDescent="0.3">
       <c r="B14" s="133" t="s">
         <v>73</v>
       </c>
@@ -9713,10 +9780,10 @@
         <v>264</v>
       </c>
       <c r="F14" s="135" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="G14" s="159" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="H14" s="135"/>
       <c r="I14" s="136"/>
@@ -9735,7 +9802,7 @@
         <v>262</v>
       </c>
       <c r="F15" s="135" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G15" s="160"/>
       <c r="H15" s="139"/>
@@ -9755,10 +9822,10 @@
         <v>265</v>
       </c>
       <c r="F16" s="135" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G16" s="159" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="H16" s="135"/>
       <c r="I16" s="136"/>
@@ -9774,11 +9841,11 @@
         <v>178</v>
       </c>
       <c r="E17" s="115" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F17" s="157"/>
       <c r="G17" s="121" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="H17" s="139"/>
       <c r="I17" s="138"/>
@@ -9847,5 +9914,6 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\PROJECT\Gitlab\HMC\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\일정\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="328">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1722,11 +1722,6 @@
 freshair@hyundai.com
 [신차 품질팀]
 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- LHD, RHD 사양 3D 모델링 수령 (10/21)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2826,15 +2821,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[임제훈 사원]
-- 공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (11/03)
-  : 일정 조율에 대한 사유 작성하여 재회신 예정, 조건부 승인으로 가면 된다고 함
-  : 사이버 보안팀에 시료 제출하여 선 공정 검사 진행 여부는 확인 해본다고 함
-- ESIR 계획서 등록 (~11/05)
-- 최신 승인도 확인 (~11/06)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">[임제훈 사원]
 - 공조 로컬 CAN 심의회 진행 (11/10)
   : SVm, BJ, NX5e, MX5a, HE1i 대상
@@ -2864,8 +2850,50 @@
   </si>
   <si>
     <t>[임제훈 사원]
-- 사이버 보안 항목 QV와 비교 및 리스트업 후 공조시스템설계팀 회신 (~11/05)
+- 공조 로컬 CAN 심의회 진행 (11/10)
+  : SVm, BJ, NX5e, MX5a, HE1i 대상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[김진겸 사원]
+- PROTO 차량 난방 평가 진행(10/31, 현대 남양연구소)
+- 난방 성능 불만족으로, 고객사 측에서 성능 증대 요청 중
+  (기구 대응 중, 김민수 선임)
+- 11/05~11/07 한온에서 동일 차량으로 평가 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- PTC 벤치 테스트 한온에서 진행 (11/12)
+  : BJ RHD HVAC 수령 예정
+- 열에너지차량시험 측 일정 최종 정리 공유
+  : 11/10(월) BJ Proto 20호차 실차 튜닝 요청
+  : 11/14(금) BJ AP2 차량 PTC 개선품 리워크 후 확인 (남양연구소 B1-7)
+  : 11/18(화) ~ 11/20(목) 리워크 완료 AP2 차량 국내 트립 진행
+  : 11/25(화) ~ 11/26(수) 실차 난방 평가 진행
+[김진겸 사원]
+- 열에너지차량시험팀 측에서 11/10(월) 챔버 확보
+  : 자동차 측에서 실차 튜닝 요청, 참석 인원 선정 필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 열에너지차량시험 측 일정 최종 정리 공유
+  : 11/14(금) BJ AP2 차량 PTC 개선품 리워크 후 확인 (남양연구소 B1-7)
+  : 11/18(화) ~ 11/20(목) 리워크 완료 AP2 차량 국내 트립 진행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 열에너지차량시험 측 일정 최종 정리 공유
+  : 11/25(화) ~ 11/26(수) 실차 난방 평가 진행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 사이버 보안 항목 QV와 비교 및 리스트업 후 공조시스템설계팀 회신 (11/04)
   : ES95489-21 빼는 것은 안됨. 업데이트에 해당하는 항목 N/A로 하자고 회신 받음
+  : 공조시스템설계팀 방침으로 인해 SVm 사이버 보안 적용 진행, 업데이트 불가능
 - 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~11/05)
 - 설계 변경 진행 (~11/10)
   : 기구팀 문의 결과, QV, SVm, BJ 담당자 전부 똑같다고 함. 결재 라인 똑같이 예정
@@ -2875,26 +2903,60 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LHD, RHD 사양 3D 모델링 수령 (10/21)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>기구팀에서 고객사에 ESIR 일정 문의 (10/29)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>[임제훈 사원]
-- 공조 로컬 CAN 심의회 진행 (11/10)
-  : SVm, BJ, NX5e, MX5a, HE1i 대상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[김진겸 사원]
-- PROTO 차량 난방 평가 진행(10/31, 현대 남양연구소)
-- 난방 성능 불만족으로, 고객사 측에서 성능 증대 요청 중
-  (기구 대응 중, 김민수 선임)
-- 11/05~11/07 한온에서 동일 차량으로 평가 예정</t>
+- NX5e PCB 제작사양서 배포 (~11/04)
+- 공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (~11/05)
+  : 일정 조율에 대한 사유 작성하여 재회신 예정, 조건부 승인으로 가면 된다고 함
+  : 사이버 보안팀에 시료 제출하여 선 공정 검사 진행 여부는 확인 해본다고 함
+- ESIR 계획서 등록 (~11/05)
+- 최신 승인도 확인 (~11/06)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 이슈 없음</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[임제훈 사원]
-- PTC 벤치 테스트 한온에서 진행 (11/12)
-  : BJ RHD HVAC 수령 예정
-[김진겸 사원]
-- 열에너지차량시험팀 측에서 11/10(월) 챔버 확보
-  : 자동차 측에서 실차 튜닝 요청, 참석 인원 선정 필요</t>
+- 기구팀 승인도 승인 요청 (11/03)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4275,7 +4337,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="178">
+  <cellXfs count="179">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4809,6 +4871,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -6459,7 +6524,7 @@
         <v>82</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="7"/>
@@ -6896,7 +6961,7 @@
         <v>258</v>
       </c>
       <c r="D18" s="162" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E18" s="64"/>
       <c r="F18" s="65"/>
@@ -7143,7 +7208,7 @@
         <v>107</v>
       </c>
       <c r="D21" s="34" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E21" s="64"/>
       <c r="F21" s="65"/>
@@ -9144,13 +9209,13 @@
         <v>280</v>
       </c>
       <c r="G3" s="99" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H3" s="99" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I3" s="100" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -9187,10 +9252,10 @@
       <c r="F5" s="116"/>
       <c r="G5" s="107"/>
       <c r="H5" s="125" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I5" s="137" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -9209,7 +9274,7 @@
       <c r="F6" s="125"/>
       <c r="G6" s="125"/>
       <c r="H6" s="135" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I6" s="158"/>
     </row>
@@ -9230,7 +9295,7 @@
       <c r="G7" s="107"/>
       <c r="H7" s="91"/>
       <c r="I7" s="136" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="87.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9250,7 +9315,7 @@
       <c r="G8" s="106"/>
       <c r="H8" s="91"/>
       <c r="I8" s="136" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -9341,10 +9406,10 @@
       <c r="F13" s="116"/>
       <c r="G13" s="107"/>
       <c r="H13" s="135" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I13" s="136" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -9363,10 +9428,10 @@
       <c r="F14" s="116"/>
       <c r="G14" s="107"/>
       <c r="H14" s="135" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I14" s="136" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -9387,10 +9452,10 @@
         <v>268</v>
       </c>
       <c r="H15" s="139" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I15" s="161" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="228.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9409,10 +9474,10 @@
       <c r="F16" s="116"/>
       <c r="G16" s="107"/>
       <c r="H16" s="135" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I16" s="136" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -9433,9 +9498,11 @@
         <v>260</v>
       </c>
       <c r="H17" s="157" t="s">
-        <v>285</v>
-      </c>
-      <c r="I17" s="138"/>
+        <v>323</v>
+      </c>
+      <c r="I17" s="138" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="18" spans="2:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="133" t="s">
@@ -9473,10 +9540,10 @@
         <v>267</v>
       </c>
       <c r="H19" s="135" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I19" s="136" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -9564,16 +9631,16 @@
       <c r="D3" s="177"/>
       <c r="E3" s="175"/>
       <c r="F3" s="99" t="s">
+        <v>300</v>
+      </c>
+      <c r="G3" s="99" t="s">
         <v>301</v>
       </c>
-      <c r="G3" s="99" t="s">
+      <c r="H3" s="99" t="s">
         <v>302</v>
       </c>
-      <c r="H3" s="99" t="s">
+      <c r="I3" s="100" t="s">
         <v>303</v>
-      </c>
-      <c r="I3" s="100" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -9608,7 +9675,7 @@
         <v>161</v>
       </c>
       <c r="F5" s="125" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G5" s="159"/>
       <c r="H5" s="125"/>
@@ -9646,10 +9713,10 @@
         <v>162</v>
       </c>
       <c r="F7" s="125" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G7" s="107" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H7" s="91"/>
       <c r="I7" s="95"/>
@@ -9744,7 +9811,7 @@
       <c r="H12" s="140"/>
       <c r="I12" s="95"/>
     </row>
-    <row r="13" spans="1:9" ht="135" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="148.5" x14ac:dyDescent="0.3">
       <c r="B13" s="134" t="s">
         <v>62</v>
       </c>
@@ -9758,15 +9825,15 @@
         <v>263</v>
       </c>
       <c r="F13" s="135" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G13" s="159" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H13" s="135"/>
       <c r="I13" s="136"/>
     </row>
-    <row r="14" spans="1:9" ht="94.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="162" x14ac:dyDescent="0.3">
       <c r="B14" s="133" t="s">
         <v>73</v>
       </c>
@@ -9780,13 +9847,17 @@
         <v>264</v>
       </c>
       <c r="F14" s="135" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G14" s="159" t="s">
-        <v>322</v>
-      </c>
-      <c r="H14" s="135"/>
-      <c r="I14" s="136"/>
+        <v>319</v>
+      </c>
+      <c r="H14" s="107" t="s">
+        <v>320</v>
+      </c>
+      <c r="I14" s="124" t="s">
+        <v>321</v>
+      </c>
     </row>
     <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
       <c r="B15" s="133" t="s">
@@ -9802,13 +9873,13 @@
         <v>262</v>
       </c>
       <c r="F15" s="135" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G15" s="160"/>
       <c r="H15" s="139"/>
       <c r="I15" s="136"/>
     </row>
-    <row r="16" spans="1:9" ht="81" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="94.5" x14ac:dyDescent="0.3">
       <c r="B16" s="133" t="s">
         <v>85</v>
       </c>
@@ -9822,10 +9893,10 @@
         <v>265</v>
       </c>
       <c r="F16" s="135" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="G16" s="159" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H16" s="135"/>
       <c r="I16" s="136"/>
@@ -9841,11 +9912,13 @@
         <v>178</v>
       </c>
       <c r="E17" s="115" t="s">
-        <v>311</v>
-      </c>
-      <c r="F17" s="157"/>
+        <v>310</v>
+      </c>
+      <c r="F17" s="157" t="s">
+        <v>327</v>
+      </c>
       <c r="G17" s="121" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H17" s="139"/>
       <c r="I17" s="138"/>
@@ -9880,7 +9953,7 @@
         <v>156</v>
       </c>
       <c r="F19" s="135" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G19" s="160"/>
       <c r="I19" s="95"/>
@@ -9898,7 +9971,9 @@
       <c r="E20" s="147" t="s">
         <v>261</v>
       </c>
-      <c r="F20" s="148"/>
+      <c r="F20" s="178" t="s">
+        <v>326</v>
+      </c>
       <c r="G20" s="149"/>
       <c r="H20" s="150"/>
       <c r="I20" s="151"/>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="329">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2821,13 +2821,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">[임제훈 사원]
-- 공조 로컬 CAN 심의회 진행 (11/10)
-  : SVm, BJ, NX5e, MX5a, HE1i 대상
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[임제훈 사원]
 - 공조 로컬 CAN 심의회 진행 (11/10)
   : SVm, BJ, NX5e, MX5a, HE1i 대상</t>
@@ -2846,12 +2839,6 @@
 [김진겸 사원]
 - RHD R 로직 튜닝을 위한 HVAC 수령 대기 중
   (11/12 기구팀 한온 출장 시 수령 예정)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- 공조 로컬 CAN 심의회 진행 (11/10)
-  : SVm, BJ, NX5e, MX5a, HE1i 대상</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2887,19 +2874,6 @@
     <t>[임제훈 사원]
 - 열에너지차량시험 측 일정 최종 정리 공유
   : 11/25(화) ~ 11/26(수) 실차 난방 평가 진행</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- 사이버 보안 항목 QV와 비교 및 리스트업 후 공조시스템설계팀 회신 (11/04)
-  : ES95489-21 빼는 것은 안됨. 업데이트에 해당하는 항목 N/A로 하자고 회신 받음
-  : 공조시스템설계팀 방침으로 인해 SVm 사이버 보안 적용 진행, 업데이트 불가능
-- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (~11/05)
-- 설계 변경 진행 (~11/10)
-  : 기구팀 문의 결과, QV, SVm, BJ 담당자 전부 똑같다고 함. 결재 라인 똑같이 예정
-  : 설계 변경 문서 작성
-[김진겸 사원]
-- 설계변경 시 ERP 등록 준비(~11/10)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2941,22 +2915,57 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>- 이슈 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 기구팀 승인도 승인 요청 (11/03)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>[임제훈 사원]
 - NX5e PCB 제작사양서 배포 (~11/04)
+  : Power 90% 3499 → 3543 변경 후 전달 완료, 체크썸 변경
 - 공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (~11/05)
   : 일정 조율에 대한 사유 작성하여 재회신 예정, 조건부 승인으로 가면 된다고 함
   : 사이버 보안팀에 시료 제출하여 선 공정 검사 진행 여부는 확인 해본다고 함
-- ESIR 계획서 등록 (~11/05)
+- ESIR 계획서 등록 완료 (11/05)
 - 최신 승인도 확인 (~11/06)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>- 이슈 없음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[임제훈 사원]
-- 기구팀 승인도 승인 요청 (11/03)</t>
+- 공조 로컬 CAN 심의회 진행 (11/10)
+  : SVm, BJ, NX5e, MX5a, HE1i 대상
+- ESIR 진행 (~11/15)
+  : ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- ESIR 진행 (~11/15)
+  : ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 사이버 보안 항목 QV와 비교 및 리스트업 후 공조시스템설계팀 회신 (11/04)
+  : ES95489-21 빼는 것은 안됨. 업데이트에 해당하는 항목 N/A로 하자고 회신 받음
+  : 공조시스템설계팀 방침으로 인해 SVm 사이버 보안 적용 진행, 업데이트 불가능
+[김진겸 사원]
+- 설계변경 시 ERP 등록 준비(11/06)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 설계 변경 진행 (11/07)
+  : 기구팀 문의 결과, QV, SVm, BJ 담당자 전부 똑같다고 함. 결재 라인 똑같이 예정
+  : 설계 변경 문서 작성 (제어사양서, SW 변경이력, 
+  : 사이버 보안 미적용 SW, 적용 SW 동작 확인 완료
+- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (11/07)
+- 공조 로컬 CAN 심의회 진행 (11/10)
+  : SVm, BJ, NX5e, MX5a, HE1i 대상</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4827,6 +4836,9 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4871,9 +4883,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -5540,90 +5549,90 @@
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="163" t="s">
+      <c r="B2" s="164" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="165" t="s">
+      <c r="C2" s="166" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="165" t="s">
+      <c r="D2" s="166" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="169">
+      <c r="E2" s="170">
         <v>23</v>
       </c>
-      <c r="F2" s="167"/>
-      <c r="G2" s="167"/>
-      <c r="H2" s="167"/>
-      <c r="I2" s="167"/>
-      <c r="J2" s="167"/>
-      <c r="K2" s="167"/>
-      <c r="L2" s="167"/>
-      <c r="M2" s="167"/>
-      <c r="N2" s="167"/>
-      <c r="O2" s="167"/>
-      <c r="P2" s="167"/>
-      <c r="Q2" s="167">
+      <c r="F2" s="168"/>
+      <c r="G2" s="168"/>
+      <c r="H2" s="168"/>
+      <c r="I2" s="168"/>
+      <c r="J2" s="168"/>
+      <c r="K2" s="168"/>
+      <c r="L2" s="168"/>
+      <c r="M2" s="168"/>
+      <c r="N2" s="168"/>
+      <c r="O2" s="168"/>
+      <c r="P2" s="168"/>
+      <c r="Q2" s="168">
         <v>24</v>
       </c>
-      <c r="R2" s="167"/>
-      <c r="S2" s="167"/>
-      <c r="T2" s="167"/>
-      <c r="U2" s="167"/>
-      <c r="V2" s="167"/>
-      <c r="W2" s="167"/>
-      <c r="X2" s="167"/>
-      <c r="Y2" s="167"/>
-      <c r="Z2" s="167"/>
-      <c r="AA2" s="167"/>
-      <c r="AB2" s="167"/>
-      <c r="AC2" s="167">
+      <c r="R2" s="168"/>
+      <c r="S2" s="168"/>
+      <c r="T2" s="168"/>
+      <c r="U2" s="168"/>
+      <c r="V2" s="168"/>
+      <c r="W2" s="168"/>
+      <c r="X2" s="168"/>
+      <c r="Y2" s="168"/>
+      <c r="Z2" s="168"/>
+      <c r="AA2" s="168"/>
+      <c r="AB2" s="168"/>
+      <c r="AC2" s="168">
         <v>25</v>
       </c>
-      <c r="AD2" s="167"/>
-      <c r="AE2" s="167"/>
-      <c r="AF2" s="167"/>
-      <c r="AG2" s="167"/>
-      <c r="AH2" s="167"/>
-      <c r="AI2" s="167"/>
-      <c r="AJ2" s="167"/>
-      <c r="AK2" s="167"/>
-      <c r="AL2" s="167"/>
-      <c r="AM2" s="167"/>
-      <c r="AN2" s="167"/>
-      <c r="AO2" s="167">
+      <c r="AD2" s="168"/>
+      <c r="AE2" s="168"/>
+      <c r="AF2" s="168"/>
+      <c r="AG2" s="168"/>
+      <c r="AH2" s="168"/>
+      <c r="AI2" s="168"/>
+      <c r="AJ2" s="168"/>
+      <c r="AK2" s="168"/>
+      <c r="AL2" s="168"/>
+      <c r="AM2" s="168"/>
+      <c r="AN2" s="168"/>
+      <c r="AO2" s="168">
         <v>26</v>
       </c>
-      <c r="AP2" s="167"/>
-      <c r="AQ2" s="167"/>
-      <c r="AR2" s="167"/>
-      <c r="AS2" s="167"/>
-      <c r="AT2" s="167"/>
-      <c r="AU2" s="167"/>
-      <c r="AV2" s="167"/>
-      <c r="AW2" s="167"/>
-      <c r="AX2" s="167"/>
-      <c r="AY2" s="167"/>
-      <c r="AZ2" s="168"/>
-      <c r="BA2" s="167">
+      <c r="AP2" s="168"/>
+      <c r="AQ2" s="168"/>
+      <c r="AR2" s="168"/>
+      <c r="AS2" s="168"/>
+      <c r="AT2" s="168"/>
+      <c r="AU2" s="168"/>
+      <c r="AV2" s="168"/>
+      <c r="AW2" s="168"/>
+      <c r="AX2" s="168"/>
+      <c r="AY2" s="168"/>
+      <c r="AZ2" s="169"/>
+      <c r="BA2" s="168">
         <v>27</v>
       </c>
-      <c r="BB2" s="167"/>
-      <c r="BC2" s="167"/>
-      <c r="BD2" s="167"/>
-      <c r="BE2" s="167"/>
-      <c r="BF2" s="167"/>
-      <c r="BG2" s="167"/>
-      <c r="BH2" s="167"/>
-      <c r="BI2" s="167"/>
-      <c r="BJ2" s="167"/>
-      <c r="BK2" s="167"/>
-      <c r="BL2" s="168"/>
+      <c r="BB2" s="168"/>
+      <c r="BC2" s="168"/>
+      <c r="BD2" s="168"/>
+      <c r="BE2" s="168"/>
+      <c r="BF2" s="168"/>
+      <c r="BG2" s="168"/>
+      <c r="BH2" s="168"/>
+      <c r="BI2" s="168"/>
+      <c r="BJ2" s="168"/>
+      <c r="BK2" s="168"/>
+      <c r="BL2" s="169"/>
     </row>
     <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="164"/>
-      <c r="C3" s="166"/>
-      <c r="D3" s="166"/>
+      <c r="B3" s="165"/>
+      <c r="C3" s="167"/>
+      <c r="D3" s="167"/>
       <c r="E3" s="22">
         <v>1</v>
       </c>
@@ -7598,39 +7607,39 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="172" t="s">
+      <c r="B2" s="173" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="176" t="s">
+      <c r="C2" s="177" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="176" t="s">
+      <c r="D2" s="177" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="174" t="s">
+      <c r="E2" s="175" t="s">
         <v>126</v>
       </c>
       <c r="F2" s="98" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="170" t="s">
+      <c r="G2" s="171" t="s">
         <v>113</v>
       </c>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="171"/>
-      <c r="K2" s="170" t="s">
+      <c r="H2" s="171"/>
+      <c r="I2" s="171"/>
+      <c r="J2" s="172"/>
+      <c r="K2" s="171" t="s">
         <v>182</v>
       </c>
-      <c r="L2" s="170"/>
-      <c r="M2" s="170"/>
-      <c r="N2" s="171"/>
+      <c r="L2" s="171"/>
+      <c r="M2" s="171"/>
+      <c r="N2" s="172"/>
     </row>
     <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="173"/>
-      <c r="C3" s="177"/>
-      <c r="D3" s="177"/>
-      <c r="E3" s="175"/>
+      <c r="B3" s="174"/>
+      <c r="C3" s="178"/>
+      <c r="D3" s="178"/>
+      <c r="E3" s="176"/>
       <c r="F3" s="99" t="s">
         <v>111</v>
       </c>
@@ -8373,30 +8382,30 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="172" t="s">
+      <c r="B2" s="173" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="176" t="s">
+      <c r="C2" s="177" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="176" t="s">
+      <c r="D2" s="177" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="174" t="s">
+      <c r="E2" s="175" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="170" t="s">
+      <c r="F2" s="171" t="s">
         <v>182</v>
       </c>
-      <c r="G2" s="170"/>
-      <c r="H2" s="170"/>
-      <c r="I2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="172"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="173"/>
-      <c r="C3" s="177"/>
-      <c r="D3" s="177"/>
-      <c r="E3" s="175"/>
+      <c r="B3" s="174"/>
+      <c r="C3" s="178"/>
+      <c r="D3" s="178"/>
+      <c r="E3" s="176"/>
       <c r="F3" s="99" t="s">
         <v>114</v>
       </c>
@@ -8774,30 +8783,30 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="172" t="s">
+      <c r="B2" s="173" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="176" t="s">
+      <c r="C2" s="177" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="176" t="s">
+      <c r="D2" s="177" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="174" t="s">
+      <c r="E2" s="175" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="170" t="s">
+      <c r="F2" s="171" t="s">
         <v>227</v>
       </c>
-      <c r="G2" s="170"/>
-      <c r="H2" s="170"/>
-      <c r="I2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="172"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="173"/>
-      <c r="C3" s="177"/>
-      <c r="D3" s="177"/>
-      <c r="E3" s="175"/>
+      <c r="B3" s="174"/>
+      <c r="C3" s="178"/>
+      <c r="D3" s="178"/>
+      <c r="E3" s="176"/>
       <c r="F3" s="99" t="s">
         <v>114</v>
       </c>
@@ -9181,30 +9190,30 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="172" t="s">
+      <c r="B2" s="173" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="176" t="s">
+      <c r="C2" s="177" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="176" t="s">
+      <c r="D2" s="177" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="174" t="s">
+      <c r="E2" s="175" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="170" t="s">
+      <c r="F2" s="171" t="s">
         <v>259</v>
       </c>
-      <c r="G2" s="170"/>
-      <c r="H2" s="170"/>
-      <c r="I2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="172"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="173"/>
-      <c r="C3" s="177"/>
-      <c r="D3" s="177"/>
-      <c r="E3" s="175"/>
+      <c r="B3" s="174"/>
+      <c r="C3" s="178"/>
+      <c r="D3" s="178"/>
+      <c r="E3" s="176"/>
       <c r="F3" s="99" t="s">
         <v>280</v>
       </c>
@@ -9498,10 +9507,10 @@
         <v>260</v>
       </c>
       <c r="H17" s="157" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="I17" s="138" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="18" spans="2:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -9606,30 +9615,30 @@
       <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="172" t="s">
+      <c r="B2" s="173" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="176" t="s">
+      <c r="C2" s="177" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="176" t="s">
+      <c r="D2" s="177" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="174" t="s">
+      <c r="E2" s="175" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="170" t="s">
+      <c r="F2" s="171" t="s">
         <v>279</v>
       </c>
-      <c r="G2" s="170"/>
-      <c r="H2" s="170"/>
-      <c r="I2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="172"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="173"/>
-      <c r="C3" s="177"/>
-      <c r="D3" s="177"/>
-      <c r="E3" s="175"/>
+      <c r="B3" s="174"/>
+      <c r="C3" s="178"/>
+      <c r="D3" s="178"/>
+      <c r="E3" s="176"/>
       <c r="F3" s="99" t="s">
         <v>300</v>
       </c>
@@ -9713,10 +9722,10 @@
         <v>162</v>
       </c>
       <c r="F7" s="125" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G7" s="107" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H7" s="91"/>
       <c r="I7" s="95"/>
@@ -9811,7 +9820,7 @@
       <c r="H12" s="140"/>
       <c r="I12" s="95"/>
     </row>
-    <row r="13" spans="1:9" ht="148.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="108" x14ac:dyDescent="0.3">
       <c r="B13" s="134" t="s">
         <v>62</v>
       </c>
@@ -9825,10 +9834,10 @@
         <v>263</v>
       </c>
       <c r="F13" s="135" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="G13" s="159" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="H13" s="135"/>
       <c r="I13" s="136"/>
@@ -9847,16 +9856,16 @@
         <v>264</v>
       </c>
       <c r="F14" s="135" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G14" s="159" t="s">
+        <v>317</v>
+      </c>
+      <c r="H14" s="107" t="s">
+        <v>318</v>
+      </c>
+      <c r="I14" s="124" t="s">
         <v>319</v>
-      </c>
-      <c r="H14" s="107" t="s">
-        <v>320</v>
-      </c>
-      <c r="I14" s="124" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -9879,7 +9888,7 @@
       <c r="H15" s="139"/>
       <c r="I15" s="136"/>
     </row>
-    <row r="16" spans="1:9" ht="94.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="108" x14ac:dyDescent="0.3">
       <c r="B16" s="133" t="s">
         <v>85</v>
       </c>
@@ -9893,12 +9902,14 @@
         <v>265</v>
       </c>
       <c r="F16" s="135" t="s">
+        <v>324</v>
+      </c>
+      <c r="G16" s="159" t="s">
         <v>325</v>
       </c>
-      <c r="G16" s="159" t="s">
-        <v>313</v>
-      </c>
-      <c r="H16" s="135"/>
+      <c r="H16" s="107" t="s">
+        <v>326</v>
+      </c>
       <c r="I16" s="136"/>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -9915,10 +9926,10 @@
         <v>310</v>
       </c>
       <c r="F17" s="157" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="G17" s="121" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H17" s="139"/>
       <c r="I17" s="138"/>
@@ -9971,8 +9982,8 @@
       <c r="E20" s="147" t="s">
         <v>261</v>
       </c>
-      <c r="F20" s="178" t="s">
-        <v>326</v>
+      <c r="F20" s="163" t="s">
+        <v>322</v>
       </c>
       <c r="G20" s="149"/>
       <c r="H20" s="150"/>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -2959,11 +2959,13 @@
   </si>
   <si>
     <t>[임제훈 사원]
+- 사이버 보안 M단계 적용으로 김응영 책임에게 유선 확인 완료 (11/07)
+  : 공정 감사 5EA 건에 대해서는 공정 감사 어디서 하는지 모른다고 함, 확인 필요
 - 설계 변경 진행 (11/07)
   : 기구팀 문의 결과, QV, SVm, BJ 담당자 전부 똑같다고 함. 결재 라인 똑같이 예정
-  : 설계 변경 문서 작성 (제어사양서, SW 변경이력, 
+  : 설계 변경 문서 작성 완료
   : 사이버 보안 미적용 SW, 적용 SW 동작 확인 완료
-- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 (11/07)
+- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 완료 (11/07)
 - 공조 로컬 CAN 심의회 진행 (11/10)
   : SVm, BJ, NX5e, MX5a, HE1i 대상</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -9820,7 +9822,7 @@
       <c r="H12" s="140"/>
       <c r="I12" s="95"/>
     </row>
-    <row r="13" spans="1:9" ht="108" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="135" x14ac:dyDescent="0.3">
       <c r="B13" s="134" t="s">
         <v>62</v>
       </c>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685"/>
   </bookViews>
   <sheets>
     <sheet name="대일정" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="331">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2553,32 +2553,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[우리산업]
-PM : 유정호, 품질 : 박상철, 기구 : 김민수, 공준석, HW : 신지훈
-[전자편의개발 2팀] 
-서상기 책임 010-9311-9821
-zsskz@hyundai.com
-[공조시스템설계팀] 
-김응영 책임 010-7635-0265
-key@hyundai.com
-이웅기 연구원 010-8427-8230
-lwg8230@hyundai.com
-[기아샤시시스템품질팀]
-김제일 매니저
-J1@kia.com</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[우리산업]
-기구 : 정우헌, HW : 신지훈
-[공조시스템설계팀]
-정재근 책임 연구원 010-9402-3594
-wjdworms1357@hyundai.com
-김동환 연구원 010-4162-2776
-kdh2776@hyundai.com</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SU2i CARRY OVER
 Proto (진행 중)
 P1 (26/05/15)</t>
@@ -2828,12 +2802,6 @@
   </si>
   <si>
     <t>[임제훈 사원]
-- 공조 로컬 CAN 심의회 진행 (11/10)
-  : SVm, BJ, NX5e, MX5a, HE1i 대상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
 - LHD R로직 튜닝
 - RHD R로직 튜닝 (HVAC 미보유, 보류)
 [김진겸 사원]
@@ -2847,20 +2815,6 @@
 - 난방 성능 불만족으로, 고객사 측에서 성능 증대 요청 중
   (기구 대응 중, 김민수 선임)
 - 11/05~11/07 한온에서 동일 차량으로 평가 예정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- PTC 벤치 테스트 한온에서 진행 (11/12)
-  : BJ RHD HVAC 수령 예정
-- 열에너지차량시험 측 일정 최종 정리 공유
-  : 11/10(월) BJ Proto 20호차 실차 튜닝 요청
-  : 11/14(금) BJ AP2 차량 PTC 개선품 리워크 후 확인 (남양연구소 B1-7)
-  : 11/18(화) ~ 11/20(목) 리워크 완료 AP2 차량 국내 트립 진행
-  : 11/25(화) ~ 11/26(수) 실차 난방 평가 진행
-[김진겸 사원]
-- 열에너지차량시험팀 측에서 11/10(월) 챔버 확보
-  : 자동차 측에서 실차 튜닝 요청, 참석 인원 선정 필요</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2936,14 +2890,6 @@
   </si>
   <si>
     <t>[임제훈 사원]
-- 공조 로컬 CAN 심의회 진행 (11/10)
-  : SVm, BJ, NX5e, MX5a, HE1i 대상
-- ESIR 진행 (~11/15)
-  : ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
 - ESIR 진행 (~11/15)
   : ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2961,13 +2907,91 @@
     <t>[임제훈 사원]
 - 사이버 보안 M단계 적용으로 김응영 책임에게 유선 확인 완료 (11/07)
   : 공정 감사 5EA 건에 대해서는 공정 감사 어디서 하는지 모른다고 함, 확인 필요
-- 설계 변경 진행 (11/07)
+- 기아샤시시스템품질팀 김제일 매니저 사이버보안 납품건 확인 완료 (11/10)
+  : QV와 동일하게 LP2 5EA 납품, M단계 전량 사이버 보안 적용 진행 요청 받음
+  : 사이버 보안으로 바뀐 이력 공유 완료
+- 설계 변경 결재 상신 완료 (11/10)
   : 기구팀 문의 결과, QV, SVm, BJ 담당자 전부 똑같다고 함. 결재 라인 똑같이 예정
   : 설계 변경 문서 작성 완료
   : 사이버 보안 미적용 SW, 적용 SW 동작 확인 완료
-- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 완료 (11/07)
-- 공조 로컬 CAN 심의회 진행 (11/10)
+- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 완료 (11/10)
+- 공조 로컬 CAN 심의회 진행 (11/13)
   : SVm, BJ, NX5e, MX5a, HE1i 대상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 열에너지차량시험팀 주관 BJ1 항속형 실차 검증 진행 (11/10)
+  : 최대난방평가 재현 결과 플로어 모드 첫 진입 시 좌우 온도 편차 최대 4.5℃
+  : 이후 모든 단계가 끝날 때 좌우 온도 편차 1℃ 내 수렴
+  : 온도 제어성 정합 평가 플로어 8단, 토출부 도어 Dr 4.65V, Ps 4.66V 강제 제어
+  : Duty 90% 강제 제어 결과 좌우 온도 편차 3.75℃
+  : Duty 50% ~ 80% 강제 제어 결과 60% 때 좌우 온도 편차 1.14℃, 그 외 1℃ 내
+- PTC 벤치 테스트 한온에서 진행 (11/12)
+  : BJ RHD HVAC 수령 예정
+- 열에너지차량시험 측 일정 최종 정리 공유
+  : 11/10(월) BJ Proto 20호차 실차 튜닝 요청
+  : 11/14(금) BJ AP2 차량 PTC 개선품 리워크 후 확인 (남양연구소 B1-7)
+  : 11/18(화) ~ 11/20(목) 리워크 완료 AP2 차량 국내 트립 진행
+  : 11/25(화) ~ 11/26(수) 실차 난방 평가 진행
+- 공조 로컬 CAN 심의회 진행 (11/13)
+  : SVm, BJ, NX5e, MX5a, HE1i 대상
+[김진겸 사원]
+- 열에너지차량시험팀 측에서 11/10(월) 챔버 확보
+  : 자동차 측에서 실차 튜닝 요청, 참석 인원 선정 필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 공조 로컬 CAN 심의회 진행 (11/13)
+  : SVm, BJ, NX5e, MX5a, HE1i 대상
+- ESIR 진행 (~11/15)
+  : ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 공조 로컬 CAN 심의회 진행 (11/13)
+  : SVm, BJ, NX5e, MX5a, HE1i 대상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[우리산업]
+PM : 유정호, 품질 : 박상철, 기구 : 김민수, 공준석, HW : 신지훈
+[전자편의개발 2팀] 
+서상기 책임 010-9311-9821
+zsskz@hyundai.com
+[공조시스템설계팀] 
+김응영 책임 010-7635-0265
+key@hyundai.com
+이웅기 연구원 010-8427-8230
+lwg8230@hyundai.com
+[기아샤시시스템품질팀]
+김제일 매니저 010-2718-1192
+J1@kia.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[우리산업]
+기구 : 정우헌, HW : 신지훈
+[공조시스템설계팀]
+정재근 책임 연구원 010-9402-3594
+wjdworms1357@hyundai.com
+김동환 연구원 010-4162-2776
+kdh2776@hyundai.com
+[한온시스템 열관리 소형 HVAC팀]
+이호 전임 연구원 010-9209-7136
+hlee17@hanonsystems.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[우리산업]
+기구 : 공준석, 강명준</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[우리산업]
+기구 : 공준석, HW : 하성빈</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4592,9 +4616,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4885,6 +4906,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -5551,90 +5575,90 @@
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="164" t="s">
+      <c r="B2" s="163" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="166" t="s">
+      <c r="C2" s="165" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="166" t="s">
+      <c r="D2" s="165" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="170">
+      <c r="E2" s="169">
         <v>23</v>
       </c>
-      <c r="F2" s="168"/>
-      <c r="G2" s="168"/>
-      <c r="H2" s="168"/>
-      <c r="I2" s="168"/>
-      <c r="J2" s="168"/>
-      <c r="K2" s="168"/>
-      <c r="L2" s="168"/>
-      <c r="M2" s="168"/>
-      <c r="N2" s="168"/>
-      <c r="O2" s="168"/>
-      <c r="P2" s="168"/>
-      <c r="Q2" s="168">
+      <c r="F2" s="167"/>
+      <c r="G2" s="167"/>
+      <c r="H2" s="167"/>
+      <c r="I2" s="167"/>
+      <c r="J2" s="167"/>
+      <c r="K2" s="167"/>
+      <c r="L2" s="167"/>
+      <c r="M2" s="167"/>
+      <c r="N2" s="167"/>
+      <c r="O2" s="167"/>
+      <c r="P2" s="167"/>
+      <c r="Q2" s="167">
         <v>24</v>
       </c>
-      <c r="R2" s="168"/>
-      <c r="S2" s="168"/>
-      <c r="T2" s="168"/>
-      <c r="U2" s="168"/>
-      <c r="V2" s="168"/>
-      <c r="W2" s="168"/>
-      <c r="X2" s="168"/>
-      <c r="Y2" s="168"/>
-      <c r="Z2" s="168"/>
-      <c r="AA2" s="168"/>
-      <c r="AB2" s="168"/>
-      <c r="AC2" s="168">
+      <c r="R2" s="167"/>
+      <c r="S2" s="167"/>
+      <c r="T2" s="167"/>
+      <c r="U2" s="167"/>
+      <c r="V2" s="167"/>
+      <c r="W2" s="167"/>
+      <c r="X2" s="167"/>
+      <c r="Y2" s="167"/>
+      <c r="Z2" s="167"/>
+      <c r="AA2" s="167"/>
+      <c r="AB2" s="167"/>
+      <c r="AC2" s="167">
         <v>25</v>
       </c>
-      <c r="AD2" s="168"/>
-      <c r="AE2" s="168"/>
-      <c r="AF2" s="168"/>
-      <c r="AG2" s="168"/>
-      <c r="AH2" s="168"/>
-      <c r="AI2" s="168"/>
-      <c r="AJ2" s="168"/>
-      <c r="AK2" s="168"/>
-      <c r="AL2" s="168"/>
-      <c r="AM2" s="168"/>
-      <c r="AN2" s="168"/>
-      <c r="AO2" s="168">
+      <c r="AD2" s="167"/>
+      <c r="AE2" s="167"/>
+      <c r="AF2" s="167"/>
+      <c r="AG2" s="167"/>
+      <c r="AH2" s="167"/>
+      <c r="AI2" s="167"/>
+      <c r="AJ2" s="167"/>
+      <c r="AK2" s="167"/>
+      <c r="AL2" s="167"/>
+      <c r="AM2" s="167"/>
+      <c r="AN2" s="167"/>
+      <c r="AO2" s="167">
         <v>26</v>
       </c>
-      <c r="AP2" s="168"/>
-      <c r="AQ2" s="168"/>
-      <c r="AR2" s="168"/>
-      <c r="AS2" s="168"/>
-      <c r="AT2" s="168"/>
-      <c r="AU2" s="168"/>
-      <c r="AV2" s="168"/>
-      <c r="AW2" s="168"/>
-      <c r="AX2" s="168"/>
-      <c r="AY2" s="168"/>
-      <c r="AZ2" s="169"/>
-      <c r="BA2" s="168">
+      <c r="AP2" s="167"/>
+      <c r="AQ2" s="167"/>
+      <c r="AR2" s="167"/>
+      <c r="AS2" s="167"/>
+      <c r="AT2" s="167"/>
+      <c r="AU2" s="167"/>
+      <c r="AV2" s="167"/>
+      <c r="AW2" s="167"/>
+      <c r="AX2" s="167"/>
+      <c r="AY2" s="167"/>
+      <c r="AZ2" s="168"/>
+      <c r="BA2" s="167">
         <v>27</v>
       </c>
-      <c r="BB2" s="168"/>
-      <c r="BC2" s="168"/>
-      <c r="BD2" s="168"/>
-      <c r="BE2" s="168"/>
-      <c r="BF2" s="168"/>
-      <c r="BG2" s="168"/>
-      <c r="BH2" s="168"/>
-      <c r="BI2" s="168"/>
-      <c r="BJ2" s="168"/>
-      <c r="BK2" s="168"/>
-      <c r="BL2" s="169"/>
+      <c r="BB2" s="167"/>
+      <c r="BC2" s="167"/>
+      <c r="BD2" s="167"/>
+      <c r="BE2" s="167"/>
+      <c r="BF2" s="167"/>
+      <c r="BG2" s="167"/>
+      <c r="BH2" s="167"/>
+      <c r="BI2" s="167"/>
+      <c r="BJ2" s="167"/>
+      <c r="BK2" s="167"/>
+      <c r="BL2" s="168"/>
     </row>
     <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="165"/>
-      <c r="C3" s="167"/>
-      <c r="D3" s="167"/>
+      <c r="B3" s="164"/>
+      <c r="C3" s="166"/>
+      <c r="D3" s="166"/>
       <c r="E3" s="22">
         <v>1</v>
       </c>
@@ -6171,7 +6195,7 @@
       <c r="Y8" s="31"/>
       <c r="Z8" s="30"/>
       <c r="AA8" s="30"/>
-      <c r="AB8" s="123"/>
+      <c r="AB8" s="122"/>
       <c r="AC8" s="29"/>
       <c r="AD8" s="31"/>
       <c r="AE8" s="31"/>
@@ -6189,7 +6213,7 @@
       <c r="AM8" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="AN8" s="123"/>
+      <c r="AN8" s="122"/>
       <c r="AO8" s="29" t="s">
         <v>226</v>
       </c>
@@ -6374,7 +6398,9 @@
       <c r="C11" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="33"/>
+      <c r="D11" s="161" t="s">
+        <v>330</v>
+      </c>
       <c r="E11" s="6"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -6455,7 +6481,9 @@
       <c r="C12" s="58" t="s">
         <v>105</v>
       </c>
-      <c r="D12" s="33"/>
+      <c r="D12" s="161" t="s">
+        <v>330</v>
+      </c>
       <c r="E12" s="6"/>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
@@ -6487,7 +6515,7 @@
       <c r="AG12" s="30"/>
       <c r="AH12" s="7"/>
       <c r="AI12" s="13"/>
-      <c r="AJ12" s="101" t="s">
+      <c r="AJ12" s="100" t="s">
         <v>129</v>
       </c>
       <c r="AK12" s="36"/>
@@ -6535,7 +6563,7 @@
         <v>82</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="7"/>
@@ -6901,10 +6929,10 @@
       <c r="N17" s="41"/>
       <c r="O17" s="41"/>
       <c r="P17" s="43"/>
-      <c r="Q17" s="104" t="s">
+      <c r="Q17" s="103" t="s">
         <v>137</v>
       </c>
-      <c r="R17" s="103"/>
+      <c r="R17" s="102"/>
       <c r="S17" s="41"/>
       <c r="T17" s="41"/>
       <c r="U17" s="41"/>
@@ -6964,15 +6992,15 @@
       <c r="BK17" s="71"/>
       <c r="BL17" s="48"/>
     </row>
-    <row r="18" spans="2:64" ht="108" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:64" ht="179.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="27" t="s">
         <v>85</v>
       </c>
       <c r="C18" s="59" t="s">
         <v>258</v>
       </c>
-      <c r="D18" s="162" t="s">
-        <v>309</v>
+      <c r="D18" s="161" t="s">
+        <v>328</v>
       </c>
       <c r="E18" s="64"/>
       <c r="F18" s="65"/>
@@ -7215,7 +7243,7 @@
       <c r="B21" s="57" t="s">
         <v>109</v>
       </c>
-      <c r="C21" s="82" t="s">
+      <c r="C21" s="81" t="s">
         <v>107</v>
       </c>
       <c r="D21" s="34" t="s">
@@ -7298,7 +7326,7 @@
       <c r="B22" s="57" t="s">
         <v>166</v>
       </c>
-      <c r="C22" s="82" t="s">
+      <c r="C22" s="81" t="s">
         <v>107</v>
       </c>
       <c r="D22" s="39"/>
@@ -7370,7 +7398,9 @@
       <c r="C23" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="D23" s="81"/>
+      <c r="D23" s="178" t="s">
+        <v>329</v>
+      </c>
       <c r="E23" s="49"/>
       <c r="F23" s="50"/>
       <c r="G23" s="50"/>
@@ -7469,13 +7499,13 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="126" t="s">
+      <c r="A2" s="125" t="s">
         <v>240</v>
       </c>
       <c r="B2" t="s">
         <v>241</v>
       </c>
-      <c r="C2" s="127" t="s">
+      <c r="C2" s="126" t="s">
         <v>242</v>
       </c>
       <c r="D2" t="s">
@@ -7483,13 +7513,13 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="126" t="s">
+      <c r="A3" s="125" t="s">
         <v>244</v>
       </c>
       <c r="B3" t="s">
         <v>241</v>
       </c>
-      <c r="C3" s="128" t="s">
+      <c r="C3" s="127" t="s">
         <v>245</v>
       </c>
       <c r="D3" t="s">
@@ -7497,13 +7527,13 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="126" t="s">
+      <c r="A4" s="125" t="s">
         <v>246</v>
       </c>
       <c r="B4" t="s">
         <v>241</v>
       </c>
-      <c r="C4" s="128" t="s">
+      <c r="C4" s="127" t="s">
         <v>247</v>
       </c>
       <c r="D4" t="s">
@@ -7511,13 +7541,13 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="129" t="s">
+      <c r="A5" s="128" t="s">
         <v>248</v>
       </c>
       <c r="B5" t="s">
         <v>241</v>
       </c>
-      <c r="C5" s="128" t="s">
+      <c r="C5" s="127" t="s">
         <v>249</v>
       </c>
       <c r="D5" t="s">
@@ -7525,13 +7555,13 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="127" t="s">
+      <c r="A6" s="126" t="s">
         <v>250</v>
       </c>
       <c r="B6" t="s">
         <v>243</v>
       </c>
-      <c r="C6" s="130" t="s">
+      <c r="C6" s="129" t="s">
         <v>251</v>
       </c>
       <c r="D6" t="s">
@@ -7539,13 +7569,13 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="127" t="s">
+      <c r="A7" s="126" t="s">
         <v>252</v>
       </c>
       <c r="B7" t="s">
         <v>243</v>
       </c>
-      <c r="C7" s="130" t="s">
+      <c r="C7" s="129" t="s">
         <v>253</v>
       </c>
       <c r="D7" t="s">
@@ -7553,7 +7583,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C8" s="126" t="s">
+      <c r="C8" s="125" t="s">
         <v>254</v>
       </c>
       <c r="D8" t="s">
@@ -7561,7 +7591,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C9" s="126" t="s">
+      <c r="C9" s="125" t="s">
         <v>255</v>
       </c>
       <c r="D9" t="s">
@@ -7569,7 +7599,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C10" s="130" t="s">
+      <c r="C10" s="129" t="s">
         <v>256</v>
       </c>
       <c r="D10" t="s">
@@ -7587,706 +7617,706 @@
   <dimension ref="A1:N22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="83" customWidth="1"/>
-    <col min="2" max="2" width="9" style="83"/>
-    <col min="3" max="4" width="14.75" style="83" customWidth="1"/>
-    <col min="5" max="5" width="43" style="83" customWidth="1"/>
-    <col min="6" max="6" width="62.125" style="83" customWidth="1"/>
-    <col min="7" max="7" width="61.875" style="83" customWidth="1"/>
-    <col min="8" max="14" width="62.125" style="83" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="83"/>
+    <col min="1" max="1" width="3.375" style="82" customWidth="1"/>
+    <col min="2" max="2" width="9" style="82"/>
+    <col min="3" max="4" width="14.75" style="82" customWidth="1"/>
+    <col min="5" max="5" width="43" style="82" customWidth="1"/>
+    <col min="6" max="6" width="62.125" style="82" customWidth="1"/>
+    <col min="7" max="7" width="61.875" style="82" customWidth="1"/>
+    <col min="8" max="14" width="62.125" style="82" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="82"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="109" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="111" t="s">
+      <c r="B1" s="110" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="111"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="109"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="108"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="173" t="s">
+      <c r="B2" s="172" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="177" t="s">
+      <c r="C2" s="176" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="177" t="s">
+      <c r="D2" s="176" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="175" t="s">
+      <c r="E2" s="174" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="98" t="s">
+      <c r="F2" s="97" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="171" t="s">
+      <c r="G2" s="170" t="s">
         <v>113</v>
       </c>
-      <c r="H2" s="171"/>
-      <c r="I2" s="171"/>
-      <c r="J2" s="172"/>
-      <c r="K2" s="171" t="s">
+      <c r="H2" s="170"/>
+      <c r="I2" s="170"/>
+      <c r="J2" s="171"/>
+      <c r="K2" s="170" t="s">
         <v>182</v>
       </c>
-      <c r="L2" s="171"/>
-      <c r="M2" s="171"/>
-      <c r="N2" s="172"/>
+      <c r="L2" s="170"/>
+      <c r="M2" s="170"/>
+      <c r="N2" s="171"/>
     </row>
     <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="174"/>
-      <c r="C3" s="178"/>
-      <c r="D3" s="178"/>
-      <c r="E3" s="176"/>
-      <c r="F3" s="99" t="s">
+      <c r="B3" s="173"/>
+      <c r="C3" s="177"/>
+      <c r="D3" s="177"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="98" t="s">
         <v>111</v>
       </c>
-      <c r="G3" s="99" t="s">
+      <c r="G3" s="98" t="s">
         <v>114</v>
       </c>
-      <c r="H3" s="99" t="s">
+      <c r="H3" s="98" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="99" t="s">
+      <c r="I3" s="98" t="s">
         <v>116</v>
       </c>
-      <c r="J3" s="100" t="s">
+      <c r="J3" s="99" t="s">
         <v>110</v>
       </c>
-      <c r="K3" s="99" t="s">
+      <c r="K3" s="98" t="s">
         <v>215</v>
       </c>
-      <c r="L3" s="99" t="s">
+      <c r="L3" s="98" t="s">
         <v>115</v>
       </c>
-      <c r="M3" s="99" t="s">
+      <c r="M3" s="98" t="s">
         <v>116</v>
       </c>
-      <c r="N3" s="100" t="s">
+      <c r="N3" s="99" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="108" x14ac:dyDescent="0.3">
-      <c r="B4" s="84" t="s">
+      <c r="B4" s="83" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="118" t="s">
+      <c r="D4" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="92" t="s">
+      <c r="E4" s="91" t="s">
         <v>152</v>
       </c>
-      <c r="F4" s="107" t="s">
+      <c r="F4" s="106" t="s">
         <v>143</v>
       </c>
-      <c r="G4" s="116" t="s">
+      <c r="G4" s="115" t="s">
         <v>171</v>
       </c>
-      <c r="H4" s="107" t="s">
+      <c r="H4" s="106" t="s">
         <v>184</v>
       </c>
-      <c r="I4" s="107" t="s">
+      <c r="I4" s="106" t="s">
         <v>201</v>
       </c>
-      <c r="J4" s="94"/>
-      <c r="K4" s="107" t="s">
+      <c r="J4" s="93"/>
+      <c r="K4" s="106" t="s">
         <v>208</v>
       </c>
-      <c r="L4" s="107" t="s">
+      <c r="L4" s="106" t="s">
         <v>174</v>
       </c>
-      <c r="M4" s="107"/>
-      <c r="N4" s="94"/>
+      <c r="M4" s="106"/>
+      <c r="N4" s="93"/>
     </row>
     <row r="5" spans="1:14" ht="108" x14ac:dyDescent="0.3">
-      <c r="B5" s="85" t="s">
+      <c r="B5" s="84" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="119" t="s">
+      <c r="C5" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="119" t="s">
+      <c r="D5" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="93" t="s">
+      <c r="E5" s="92" t="s">
         <v>153</v>
       </c>
-      <c r="F5" s="107" t="s">
+      <c r="F5" s="106" t="s">
         <v>143</v>
       </c>
-      <c r="G5" s="116" t="s">
+      <c r="G5" s="115" t="s">
         <v>171</v>
       </c>
-      <c r="H5" s="107" t="s">
+      <c r="H5" s="106" t="s">
         <v>184</v>
       </c>
-      <c r="I5" s="107" t="s">
+      <c r="I5" s="106" t="s">
         <v>201</v>
       </c>
-      <c r="J5" s="95"/>
-      <c r="K5" s="107" t="s">
+      <c r="J5" s="94"/>
+      <c r="K5" s="106" t="s">
         <v>208</v>
       </c>
-      <c r="L5" s="107" t="s">
+      <c r="L5" s="106" t="s">
         <v>174</v>
       </c>
-      <c r="M5" s="107"/>
-      <c r="N5" s="95"/>
+      <c r="M5" s="106"/>
+      <c r="N5" s="94"/>
     </row>
     <row r="6" spans="1:14" ht="108" x14ac:dyDescent="0.3">
-      <c r="B6" s="85" t="s">
+      <c r="B6" s="84" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="119" t="s">
+      <c r="C6" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D6" s="119" t="s">
+      <c r="D6" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E6" s="93" t="s">
+      <c r="E6" s="92" t="s">
         <v>154</v>
       </c>
-      <c r="F6" s="107" t="s">
+      <c r="F6" s="106" t="s">
         <v>143</v>
       </c>
-      <c r="G6" s="116" t="s">
+      <c r="G6" s="115" t="s">
         <v>171</v>
       </c>
-      <c r="H6" s="107" t="s">
+      <c r="H6" s="106" t="s">
         <v>184</v>
       </c>
-      <c r="I6" s="107" t="s">
+      <c r="I6" s="106" t="s">
         <v>201</v>
       </c>
-      <c r="J6" s="95"/>
-      <c r="K6" s="107" t="s">
+      <c r="J6" s="94"/>
+      <c r="K6" s="106" t="s">
         <v>208</v>
       </c>
-      <c r="L6" s="107" t="s">
+      <c r="L6" s="106" t="s">
         <v>174</v>
       </c>
-      <c r="M6" s="107"/>
-      <c r="N6" s="95"/>
+      <c r="M6" s="106"/>
+      <c r="N6" s="94"/>
     </row>
     <row r="7" spans="1:14" ht="108" x14ac:dyDescent="0.3">
-      <c r="B7" s="85" t="s">
+      <c r="B7" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="C7" s="119" t="s">
+      <c r="C7" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D7" s="119" t="s">
+      <c r="D7" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="93" t="s">
+      <c r="E7" s="92" t="s">
         <v>155</v>
       </c>
-      <c r="F7" s="107" t="s">
+      <c r="F7" s="106" t="s">
         <v>143</v>
       </c>
-      <c r="G7" s="116" t="s">
+      <c r="G7" s="115" t="s">
         <v>171</v>
       </c>
-      <c r="H7" s="107" t="s">
+      <c r="H7" s="106" t="s">
         <v>184</v>
       </c>
-      <c r="I7" s="107" t="s">
+      <c r="I7" s="106" t="s">
         <v>201</v>
       </c>
-      <c r="J7" s="95"/>
-      <c r="K7" s="107" t="s">
+      <c r="J7" s="94"/>
+      <c r="K7" s="106" t="s">
         <v>208</v>
       </c>
-      <c r="L7" s="107" t="s">
+      <c r="L7" s="106" t="s">
         <v>174</v>
       </c>
-      <c r="M7" s="107"/>
-      <c r="N7" s="95"/>
+      <c r="M7" s="106"/>
+      <c r="N7" s="94"/>
     </row>
     <row r="8" spans="1:14" ht="108" x14ac:dyDescent="0.3">
-      <c r="B8" s="86" t="s">
+      <c r="B8" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="119" t="s">
+      <c r="C8" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D8" s="119" t="s">
+      <c r="D8" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E8" s="93" t="s">
+      <c r="E8" s="92" t="s">
         <v>156</v>
       </c>
-      <c r="F8" s="107" t="s">
+      <c r="F8" s="106" t="s">
         <v>144</v>
       </c>
-      <c r="G8" s="116" t="s">
+      <c r="G8" s="115" t="s">
         <v>171</v>
       </c>
-      <c r="H8" s="107" t="s">
+      <c r="H8" s="106" t="s">
         <v>184</v>
       </c>
-      <c r="I8" s="107" t="s">
+      <c r="I8" s="106" t="s">
         <v>201</v>
       </c>
-      <c r="J8" s="95"/>
-      <c r="K8" s="107" t="s">
+      <c r="J8" s="94"/>
+      <c r="K8" s="106" t="s">
         <v>208</v>
       </c>
-      <c r="L8" s="107" t="s">
+      <c r="L8" s="106" t="s">
         <v>174</v>
       </c>
-      <c r="M8" s="107"/>
-      <c r="N8" s="95"/>
+      <c r="M8" s="106"/>
+      <c r="N8" s="94"/>
     </row>
     <row r="9" spans="1:14" ht="175.5" x14ac:dyDescent="0.3">
-      <c r="B9" s="86" t="s">
+      <c r="B9" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="119" t="s">
+      <c r="C9" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D9" s="119" t="s">
+      <c r="D9" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E9" s="102" t="s">
+      <c r="E9" s="101" t="s">
         <v>157</v>
       </c>
-      <c r="F9" s="107" t="s">
+      <c r="F9" s="106" t="s">
         <v>145</v>
       </c>
-      <c r="G9" s="116" t="s">
+      <c r="G9" s="115" t="s">
         <v>171</v>
       </c>
-      <c r="H9" s="107" t="s">
+      <c r="H9" s="106" t="s">
         <v>185</v>
       </c>
-      <c r="I9" s="107" t="s">
+      <c r="I9" s="106" t="s">
         <v>202</v>
       </c>
-      <c r="J9" s="95"/>
-      <c r="K9" s="107" t="s">
+      <c r="J9" s="94"/>
+      <c r="K9" s="106" t="s">
         <v>209</v>
       </c>
-      <c r="L9" s="107" t="s">
+      <c r="L9" s="106" t="s">
         <v>216</v>
       </c>
-      <c r="M9" s="107"/>
-      <c r="N9" s="95"/>
+      <c r="M9" s="106"/>
+      <c r="N9" s="94"/>
     </row>
     <row r="10" spans="1:14" ht="121.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="86" t="s">
+      <c r="B10" s="85" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="119" t="s">
+      <c r="C10" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D10" s="119" t="s">
+      <c r="D10" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E10" s="102" t="s">
+      <c r="E10" s="101" t="s">
         <v>158</v>
       </c>
-      <c r="F10" s="107" t="s">
+      <c r="F10" s="106" t="s">
         <v>144</v>
       </c>
-      <c r="G10" s="116" t="s">
+      <c r="G10" s="115" t="s">
         <v>171</v>
       </c>
-      <c r="H10" s="107" t="s">
+      <c r="H10" s="106" t="s">
         <v>184</v>
       </c>
-      <c r="I10" s="107" t="s">
+      <c r="I10" s="106" t="s">
         <v>203</v>
       </c>
-      <c r="J10" s="95"/>
-      <c r="K10" s="107" t="s">
+      <c r="J10" s="94"/>
+      <c r="K10" s="106" t="s">
         <v>208</v>
       </c>
-      <c r="L10" s="107" t="s">
+      <c r="L10" s="106" t="s">
         <v>174</v>
       </c>
-      <c r="M10" s="107"/>
-      <c r="N10" s="95"/>
+      <c r="M10" s="106"/>
+      <c r="N10" s="94"/>
     </row>
     <row r="11" spans="1:14" ht="108" x14ac:dyDescent="0.3">
-      <c r="B11" s="85" t="s">
+      <c r="B11" s="84" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="119" t="s">
+      <c r="C11" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D11" s="119" t="s">
+      <c r="D11" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E11" s="102" t="s">
+      <c r="E11" s="101" t="s">
         <v>159</v>
       </c>
-      <c r="F11" s="107" t="s">
+      <c r="F11" s="106" t="s">
         <v>142</v>
       </c>
-      <c r="G11" s="116" t="s">
+      <c r="G11" s="115" t="s">
         <v>171</v>
       </c>
-      <c r="H11" s="107" t="s">
+      <c r="H11" s="106" t="s">
         <v>183</v>
       </c>
-      <c r="I11" s="107" t="s">
+      <c r="I11" s="106" t="s">
         <v>197</v>
       </c>
-      <c r="J11" s="95"/>
-      <c r="K11" s="107" t="s">
+      <c r="J11" s="94"/>
+      <c r="K11" s="106" t="s">
         <v>210</v>
       </c>
-      <c r="L11" s="107" t="s">
+      <c r="L11" s="106" t="s">
         <v>174</v>
       </c>
-      <c r="M11" s="107"/>
-      <c r="N11" s="95"/>
+      <c r="M11" s="106"/>
+      <c r="N11" s="94"/>
     </row>
     <row r="12" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="86" t="s">
+      <c r="B12" s="85" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="119" t="s">
+      <c r="C12" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D12" s="119" t="s">
+      <c r="D12" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E12" s="102" t="s">
+      <c r="E12" s="101" t="s">
         <v>160</v>
       </c>
-      <c r="F12" s="107" t="s">
+      <c r="F12" s="106" t="s">
         <v>146</v>
       </c>
-      <c r="G12" s="116" t="s">
+      <c r="G12" s="115" t="s">
         <v>171</v>
       </c>
-      <c r="H12" s="107" t="s">
+      <c r="H12" s="106" t="s">
         <v>174</v>
       </c>
-      <c r="I12" s="107" t="s">
+      <c r="I12" s="106" t="s">
         <v>174</v>
       </c>
-      <c r="J12" s="95"/>
-      <c r="K12" s="107" t="s">
+      <c r="J12" s="94"/>
+      <c r="K12" s="106" t="s">
         <v>174</v>
       </c>
-      <c r="L12" s="107" t="s">
+      <c r="L12" s="106" t="s">
         <v>174</v>
       </c>
-      <c r="M12" s="107"/>
-      <c r="N12" s="95"/>
+      <c r="M12" s="106"/>
+      <c r="N12" s="94"/>
     </row>
     <row r="13" spans="1:14" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="86" t="s">
+      <c r="B13" s="85" t="s">
         <v>118</v>
       </c>
-      <c r="C13" s="119" t="s">
+      <c r="C13" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D13" s="119" t="s">
+      <c r="D13" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="102" t="s">
+      <c r="E13" s="101" t="s">
         <v>161</v>
       </c>
-      <c r="F13" s="107" t="s">
+      <c r="F13" s="106" t="s">
         <v>165</v>
       </c>
-      <c r="G13" s="116" t="s">
+      <c r="G13" s="115" t="s">
         <v>171</v>
       </c>
-      <c r="H13" s="107" t="s">
+      <c r="H13" s="106" t="s">
         <v>191</v>
       </c>
-      <c r="I13" s="107" t="s">
+      <c r="I13" s="106" t="s">
         <v>204</v>
       </c>
-      <c r="J13" s="95"/>
-      <c r="K13" s="107" t="s">
+      <c r="J13" s="94"/>
+      <c r="K13" s="106" t="s">
         <v>214</v>
       </c>
-      <c r="L13" s="107" t="s">
+      <c r="L13" s="106" t="s">
         <v>218</v>
       </c>
-      <c r="M13" s="107"/>
-      <c r="N13" s="95"/>
+      <c r="M13" s="106"/>
+      <c r="N13" s="94"/>
     </row>
     <row r="14" spans="1:14" ht="175.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="87" t="s">
+      <c r="B14" s="86" t="s">
         <v>181</v>
       </c>
-      <c r="C14" s="119" t="s">
+      <c r="C14" s="118" t="s">
         <v>179</v>
       </c>
-      <c r="D14" s="119" t="s">
+      <c r="D14" s="118" t="s">
         <v>180</v>
       </c>
-      <c r="E14" s="102"/>
-      <c r="F14" s="107"/>
-      <c r="G14" s="116"/>
-      <c r="H14" s="107" t="s">
+      <c r="E14" s="101"/>
+      <c r="F14" s="106"/>
+      <c r="G14" s="115"/>
+      <c r="H14" s="106" t="s">
         <v>200</v>
       </c>
-      <c r="I14" s="107" t="s">
+      <c r="I14" s="106" t="s">
         <v>207</v>
       </c>
-      <c r="J14" s="95"/>
-      <c r="K14" s="107" t="s">
+      <c r="J14" s="94"/>
+      <c r="K14" s="106" t="s">
         <v>211</v>
       </c>
-      <c r="L14" s="107" t="s">
+      <c r="L14" s="106" t="s">
         <v>217</v>
       </c>
-      <c r="M14" s="107"/>
-      <c r="N14" s="95"/>
+      <c r="M14" s="106"/>
+      <c r="N14" s="94"/>
     </row>
     <row r="15" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="87" t="s">
+      <c r="B15" s="86" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="119" t="s">
+      <c r="C15" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D15" s="119" t="s">
+      <c r="D15" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E15" s="102" t="s">
+      <c r="E15" s="101" t="s">
         <v>162</v>
       </c>
-      <c r="F15" s="107" t="s">
+      <c r="F15" s="106" t="s">
         <v>172</v>
       </c>
-      <c r="G15" s="116" t="s">
+      <c r="G15" s="115" t="s">
         <v>171</v>
       </c>
-      <c r="H15" s="107" t="s">
+      <c r="H15" s="106" t="s">
         <v>190</v>
       </c>
-      <c r="I15" s="107" t="s">
+      <c r="I15" s="106" t="s">
         <v>174</v>
       </c>
-      <c r="J15" s="95"/>
-      <c r="K15" s="107" t="s">
+      <c r="J15" s="94"/>
+      <c r="K15" s="106" t="s">
         <v>174</v>
       </c>
-      <c r="L15" s="107"/>
-      <c r="M15" s="107"/>
-      <c r="N15" s="95"/>
+      <c r="L15" s="106"/>
+      <c r="M15" s="106"/>
+      <c r="N15" s="94"/>
     </row>
     <row r="16" spans="1:14" ht="121.5" x14ac:dyDescent="0.3">
-      <c r="B16" s="86" t="s">
+      <c r="B16" s="85" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="119" t="s">
+      <c r="C16" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D16" s="119" t="s">
+      <c r="D16" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E16" s="93" t="s">
+      <c r="E16" s="92" t="s">
         <v>163</v>
       </c>
-      <c r="F16" s="107" t="s">
+      <c r="F16" s="106" t="s">
         <v>173</v>
       </c>
-      <c r="G16" s="116" t="s">
+      <c r="G16" s="115" t="s">
         <v>171</v>
       </c>
-      <c r="H16" s="107" t="s">
+      <c r="H16" s="106" t="s">
         <v>198</v>
       </c>
-      <c r="I16" s="107" t="s">
+      <c r="I16" s="106" t="s">
         <v>206</v>
       </c>
-      <c r="J16" s="95"/>
-      <c r="K16" s="107" t="s">
+      <c r="J16" s="94"/>
+      <c r="K16" s="106" t="s">
         <v>213</v>
       </c>
-      <c r="L16" s="107"/>
-      <c r="M16" s="107"/>
-      <c r="N16" s="95"/>
+      <c r="L16" s="106"/>
+      <c r="M16" s="106"/>
+      <c r="N16" s="94"/>
     </row>
     <row r="17" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="88" t="s">
+      <c r="B17" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C17" s="119" t="s">
+      <c r="C17" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D17" s="119" t="s">
+      <c r="D17" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E17" s="93" t="s">
+      <c r="E17" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="F17" s="91"/>
-      <c r="G17" s="116" t="s">
+      <c r="F17" s="90"/>
+      <c r="G17" s="115" t="s">
         <v>171</v>
       </c>
-      <c r="H17" s="91" t="s">
+      <c r="H17" s="90" t="s">
         <v>199</v>
       </c>
-      <c r="I17" s="91" t="s">
+      <c r="I17" s="90" t="s">
         <v>199</v>
       </c>
-      <c r="J17" s="95"/>
-      <c r="K17" s="91" t="s">
+      <c r="J17" s="94"/>
+      <c r="K17" s="90" t="s">
         <v>105</v>
       </c>
-      <c r="L17" s="91" t="s">
+      <c r="L17" s="90" t="s">
         <v>105</v>
       </c>
-      <c r="M17" s="91"/>
-      <c r="N17" s="95"/>
+      <c r="M17" s="90"/>
+      <c r="N17" s="94"/>
     </row>
     <row r="18" spans="2:14" ht="162" x14ac:dyDescent="0.3">
-      <c r="B18" s="88" t="s">
+      <c r="B18" s="87" t="s">
         <v>106</v>
       </c>
-      <c r="C18" s="119" t="s">
+      <c r="C18" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D18" s="119" t="s">
+      <c r="D18" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E18" s="102" t="s">
+      <c r="E18" s="101" t="s">
         <v>164</v>
       </c>
-      <c r="F18" s="107" t="s">
+      <c r="F18" s="106" t="s">
         <v>147</v>
       </c>
-      <c r="G18" s="116" t="s">
+      <c r="G18" s="115" t="s">
         <v>171</v>
       </c>
-      <c r="H18" s="107" t="s">
+      <c r="H18" s="106" t="s">
         <v>189</v>
       </c>
-      <c r="I18" s="107" t="s">
+      <c r="I18" s="106" t="s">
         <v>205</v>
       </c>
-      <c r="J18" s="95"/>
-      <c r="K18" s="107" t="s">
+      <c r="J18" s="94"/>
+      <c r="K18" s="106" t="s">
         <v>212</v>
       </c>
-      <c r="L18" s="107" t="s">
+      <c r="L18" s="106" t="s">
         <v>212</v>
       </c>
-      <c r="M18" s="107"/>
-      <c r="N18" s="95"/>
+      <c r="M18" s="106"/>
+      <c r="N18" s="94"/>
     </row>
     <row r="19" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="87" t="s">
+      <c r="B19" s="86" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="119" t="s">
+      <c r="C19" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D19" s="119" t="s">
+      <c r="D19" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E19" s="93" t="s">
+      <c r="E19" s="92" t="s">
         <v>139</v>
       </c>
-      <c r="F19" s="106" t="s">
+      <c r="F19" s="105" t="s">
         <v>150</v>
       </c>
-      <c r="G19" s="116" t="s">
+      <c r="G19" s="115" t="s">
         <v>171</v>
       </c>
-      <c r="H19" s="107" t="s">
+      <c r="H19" s="106" t="s">
         <v>188</v>
       </c>
-      <c r="I19" s="107" t="s">
+      <c r="I19" s="106" t="s">
         <v>174</v>
       </c>
-      <c r="J19" s="95"/>
-      <c r="K19" s="107" t="s">
+      <c r="J19" s="94"/>
+      <c r="K19" s="106" t="s">
         <v>174</v>
       </c>
-      <c r="L19" s="107" t="s">
+      <c r="L19" s="106" t="s">
         <v>174</v>
       </c>
-      <c r="M19" s="107"/>
-      <c r="N19" s="95"/>
+      <c r="M19" s="106"/>
+      <c r="N19" s="94"/>
     </row>
     <row r="20" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="87" t="s">
+      <c r="B20" s="86" t="s">
         <v>168</v>
       </c>
-      <c r="C20" s="119" t="s">
+      <c r="C20" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D20" s="119" t="s">
+      <c r="D20" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="115" t="s">
+      <c r="E20" s="114" t="s">
         <v>169</v>
       </c>
-      <c r="F20" s="112" t="s">
+      <c r="F20" s="111" t="s">
         <v>170</v>
       </c>
-      <c r="G20" s="116" t="s">
+      <c r="G20" s="115" t="s">
         <v>171</v>
       </c>
-      <c r="H20" s="121" t="s">
+      <c r="H20" s="120" t="s">
         <v>187</v>
       </c>
-      <c r="I20" s="107" t="s">
+      <c r="I20" s="106" t="s">
         <v>174</v>
       </c>
-      <c r="J20" s="114"/>
-      <c r="K20" s="107" t="s">
+      <c r="J20" s="113"/>
+      <c r="K20" s="106" t="s">
         <v>174</v>
       </c>
-      <c r="L20" s="107" t="s">
+      <c r="L20" s="106" t="s">
         <v>174</v>
       </c>
-      <c r="M20" s="107"/>
-      <c r="N20" s="114"/>
+      <c r="M20" s="106"/>
+      <c r="N20" s="113"/>
     </row>
     <row r="21" spans="2:14" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="89" t="s">
+      <c r="B21" s="88" t="s">
         <v>108</v>
       </c>
-      <c r="C21" s="120" t="s">
+      <c r="C21" s="119" t="s">
         <v>175</v>
       </c>
-      <c r="D21" s="120" t="s">
+      <c r="D21" s="119" t="s">
         <v>178</v>
       </c>
-      <c r="E21" s="105" t="s">
+      <c r="E21" s="104" t="s">
         <v>140</v>
       </c>
-      <c r="F21" s="108" t="s">
+      <c r="F21" s="107" t="s">
         <v>151</v>
       </c>
-      <c r="G21" s="117" t="s">
+      <c r="G21" s="116" t="s">
         <v>171</v>
       </c>
-      <c r="H21" s="122" t="s">
+      <c r="H21" s="121" t="s">
         <v>186</v>
       </c>
-      <c r="I21" s="122" t="s">
+      <c r="I21" s="121" t="s">
         <v>174</v>
       </c>
-      <c r="J21" s="97"/>
-      <c r="K21" s="122" t="s">
+      <c r="J21" s="96"/>
+      <c r="K21" s="121" t="s">
         <v>174</v>
       </c>
-      <c r="L21" s="122" t="s">
+      <c r="L21" s="121" t="s">
         <v>174</v>
       </c>
-      <c r="M21" s="122"/>
-      <c r="N21" s="97"/>
+      <c r="M21" s="121"/>
+      <c r="N21" s="96"/>
     </row>
     <row r="22" spans="2:14" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -8363,387 +8393,387 @@
   <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="83" customWidth="1"/>
-    <col min="2" max="2" width="9" style="83"/>
-    <col min="3" max="4" width="14.75" style="83" customWidth="1"/>
-    <col min="5" max="5" width="43" style="83" customWidth="1"/>
-    <col min="6" max="6" width="61.875" style="83" customWidth="1"/>
-    <col min="7" max="9" width="62.125" style="83" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="83"/>
+    <col min="1" max="1" width="3.375" style="82" customWidth="1"/>
+    <col min="2" max="2" width="9" style="82"/>
+    <col min="3" max="4" width="14.75" style="82" customWidth="1"/>
+    <col min="5" max="5" width="43" style="82" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="82" customWidth="1"/>
+    <col min="7" max="9" width="62.125" style="82" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="82"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="111" t="s">
+      <c r="B1" s="110" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="111"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="109"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="108"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="173" t="s">
+      <c r="B2" s="172" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="177" t="s">
+      <c r="C2" s="176" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="177" t="s">
+      <c r="D2" s="176" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="175" t="s">
+      <c r="E2" s="174" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="171" t="s">
+      <c r="F2" s="170" t="s">
         <v>182</v>
       </c>
-      <c r="G2" s="171"/>
-      <c r="H2" s="171"/>
-      <c r="I2" s="172"/>
+      <c r="G2" s="170"/>
+      <c r="H2" s="170"/>
+      <c r="I2" s="171"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="174"/>
-      <c r="C3" s="178"/>
-      <c r="D3" s="178"/>
-      <c r="E3" s="176"/>
-      <c r="F3" s="99" t="s">
+      <c r="B3" s="173"/>
+      <c r="C3" s="177"/>
+      <c r="D3" s="177"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="98" t="s">
         <v>114</v>
       </c>
-      <c r="G3" s="99" t="s">
+      <c r="G3" s="98" t="s">
         <v>115</v>
       </c>
-      <c r="H3" s="99" t="s">
+      <c r="H3" s="98" t="s">
         <v>116</v>
       </c>
-      <c r="I3" s="100" t="s">
+      <c r="I3" s="99" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="84" t="s">
+      <c r="B4" s="83" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="118" t="s">
+      <c r="D4" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="92" t="s">
+      <c r="E4" s="91" t="s">
         <v>152</v>
       </c>
-      <c r="F4" s="116"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="90"/>
-      <c r="I4" s="94"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="106"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="93"/>
     </row>
     <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="85" t="s">
+      <c r="B5" s="84" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="119" t="s">
+      <c r="C5" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="119" t="s">
+      <c r="D5" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="93" t="s">
+      <c r="E5" s="92" t="s">
         <v>153</v>
       </c>
-      <c r="F5" s="116"/>
-      <c r="G5" s="107"/>
-      <c r="H5" s="91"/>
-      <c r="I5" s="95"/>
+      <c r="F5" s="115"/>
+      <c r="G5" s="106"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="94"/>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="85" t="s">
+      <c r="B6" s="84" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="119" t="s">
+      <c r="C6" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D6" s="119" t="s">
+      <c r="D6" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E6" s="93" t="s">
+      <c r="E6" s="92" t="s">
         <v>154</v>
       </c>
-      <c r="F6" s="116"/>
-      <c r="G6" s="107"/>
-      <c r="H6" s="91"/>
-      <c r="I6" s="95"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="106"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="94"/>
     </row>
     <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="85" t="s">
+      <c r="B7" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="C7" s="119" t="s">
+      <c r="C7" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D7" s="119" t="s">
+      <c r="D7" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="93" t="s">
+      <c r="E7" s="92" t="s">
         <v>155</v>
       </c>
-      <c r="F7" s="116"/>
-      <c r="G7" s="107"/>
-      <c r="H7" s="91"/>
-      <c r="I7" s="95"/>
+      <c r="F7" s="115"/>
+      <c r="G7" s="106"/>
+      <c r="H7" s="90"/>
+      <c r="I7" s="94"/>
     </row>
     <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="86" t="s">
+      <c r="B8" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="119" t="s">
+      <c r="C8" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D8" s="119" t="s">
+      <c r="D8" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E8" s="93" t="s">
+      <c r="E8" s="92" t="s">
         <v>156</v>
       </c>
-      <c r="F8" s="116"/>
-      <c r="G8" s="107"/>
-      <c r="H8" s="91"/>
-      <c r="I8" s="95"/>
+      <c r="F8" s="115"/>
+      <c r="G8" s="106"/>
+      <c r="H8" s="90"/>
+      <c r="I8" s="94"/>
     </row>
     <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.3">
-      <c r="B9" s="86" t="s">
+      <c r="B9" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="119" t="s">
+      <c r="C9" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D9" s="119" t="s">
+      <c r="D9" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E9" s="102" t="s">
+      <c r="E9" s="101" t="s">
         <v>157</v>
       </c>
-      <c r="F9" s="116"/>
-      <c r="G9" s="107"/>
-      <c r="H9" s="91"/>
-      <c r="I9" s="95"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="106"/>
+      <c r="H9" s="90"/>
+      <c r="I9" s="94"/>
     </row>
     <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="86" t="s">
+      <c r="B10" s="85" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="119" t="s">
+      <c r="C10" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D10" s="119" t="s">
+      <c r="D10" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E10" s="102" t="s">
+      <c r="E10" s="101" t="s">
         <v>158</v>
       </c>
-      <c r="F10" s="116"/>
-      <c r="G10" s="107"/>
-      <c r="H10" s="91"/>
-      <c r="I10" s="95"/>
+      <c r="F10" s="115"/>
+      <c r="G10" s="106"/>
+      <c r="H10" s="90"/>
+      <c r="I10" s="94"/>
     </row>
     <row r="11" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="B11" s="85" t="s">
+      <c r="B11" s="84" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="119" t="s">
+      <c r="C11" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D11" s="119" t="s">
+      <c r="D11" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E11" s="102" t="s">
+      <c r="E11" s="101" t="s">
         <v>159</v>
       </c>
-      <c r="F11" s="116"/>
-      <c r="G11" s="107"/>
-      <c r="H11" s="91"/>
-      <c r="I11" s="95"/>
+      <c r="F11" s="115"/>
+      <c r="G11" s="106"/>
+      <c r="H11" s="90"/>
+      <c r="I11" s="94"/>
     </row>
     <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="86" t="s">
+      <c r="B12" s="85" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="119" t="s">
+      <c r="C12" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D12" s="119" t="s">
+      <c r="D12" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E12" s="102" t="s">
+      <c r="E12" s="101" t="s">
         <v>160</v>
       </c>
-      <c r="F12" s="116"/>
-      <c r="G12" s="107"/>
-      <c r="H12" s="91"/>
-      <c r="I12" s="95"/>
+      <c r="F12" s="115"/>
+      <c r="G12" s="106"/>
+      <c r="H12" s="90"/>
+      <c r="I12" s="94"/>
     </row>
     <row r="13" spans="1:9" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="86" t="s">
+      <c r="B13" s="85" t="s">
         <v>118</v>
       </c>
-      <c r="C13" s="119" t="s">
+      <c r="C13" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D13" s="119" t="s">
+      <c r="D13" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="102" t="s">
+      <c r="E13" s="101" t="s">
         <v>161</v>
       </c>
-      <c r="F13" s="116"/>
-      <c r="G13" s="107"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="95"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="106"/>
+      <c r="H13" s="90"/>
+      <c r="I13" s="94"/>
     </row>
     <row r="14" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="87" t="s">
+      <c r="B14" s="86" t="s">
         <v>181</v>
       </c>
-      <c r="C14" s="119" t="s">
+      <c r="C14" s="118" t="s">
         <v>179</v>
       </c>
-      <c r="D14" s="119" t="s">
+      <c r="D14" s="118" t="s">
         <v>180</v>
       </c>
-      <c r="E14" s="102"/>
-      <c r="F14" s="116"/>
-      <c r="G14" s="107"/>
-      <c r="H14" s="91"/>
-      <c r="I14" s="124" t="s">
+      <c r="E14" s="101"/>
+      <c r="F14" s="115"/>
+      <c r="G14" s="106"/>
+      <c r="H14" s="90"/>
+      <c r="I14" s="123" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="87" t="s">
+      <c r="B15" s="86" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="119" t="s">
+      <c r="C15" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D15" s="119" t="s">
+      <c r="D15" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E15" s="102" t="s">
+      <c r="E15" s="101" t="s">
         <v>162</v>
       </c>
-      <c r="F15" s="116"/>
-      <c r="G15" s="107"/>
-      <c r="H15" s="91"/>
-      <c r="I15" s="95"/>
+      <c r="F15" s="115"/>
+      <c r="G15" s="106"/>
+      <c r="H15" s="90"/>
+      <c r="I15" s="94"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="86" t="s">
+      <c r="B16" s="85" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="119" t="s">
+      <c r="C16" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D16" s="119" t="s">
+      <c r="D16" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E16" s="93" t="s">
+      <c r="E16" s="92" t="s">
         <v>163</v>
       </c>
-      <c r="F16" s="116"/>
-      <c r="G16" s="107"/>
-      <c r="H16" s="91"/>
-      <c r="I16" s="95"/>
+      <c r="F16" s="115"/>
+      <c r="G16" s="106"/>
+      <c r="H16" s="90"/>
+      <c r="I16" s="94"/>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="88" t="s">
+      <c r="B17" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C17" s="119" t="s">
+      <c r="C17" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D17" s="119" t="s">
+      <c r="D17" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E17" s="93" t="s">
+      <c r="E17" s="92" t="s">
         <v>105</v>
       </c>
-      <c r="F17" s="116"/>
-      <c r="G17" s="91"/>
-      <c r="H17" s="91"/>
-      <c r="I17" s="95"/>
+      <c r="F17" s="115"/>
+      <c r="G17" s="90"/>
+      <c r="H17" s="90"/>
+      <c r="I17" s="94"/>
     </row>
     <row r="18" spans="2:9" ht="27" x14ac:dyDescent="0.3">
-      <c r="B18" s="88" t="s">
+      <c r="B18" s="87" t="s">
         <v>106</v>
       </c>
-      <c r="C18" s="119" t="s">
+      <c r="C18" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D18" s="119" t="s">
+      <c r="D18" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E18" s="102" t="s">
+      <c r="E18" s="101" t="s">
         <v>164</v>
       </c>
-      <c r="F18" s="116"/>
-      <c r="G18" s="107"/>
-      <c r="H18" s="91"/>
-      <c r="I18" s="95"/>
+      <c r="F18" s="115"/>
+      <c r="G18" s="106"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="94"/>
     </row>
     <row r="19" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="87" t="s">
+      <c r="B19" s="86" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="119" t="s">
+      <c r="C19" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D19" s="119" t="s">
+      <c r="D19" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E19" s="93" t="s">
+      <c r="E19" s="92" t="s">
         <v>139</v>
       </c>
-      <c r="F19" s="116"/>
-      <c r="G19" s="106"/>
-      <c r="H19" s="91"/>
-      <c r="I19" s="95"/>
+      <c r="F19" s="115"/>
+      <c r="G19" s="105"/>
+      <c r="H19" s="90"/>
+      <c r="I19" s="94"/>
     </row>
     <row r="20" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="87" t="s">
+      <c r="B20" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="C20" s="119" t="s">
+      <c r="C20" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D20" s="119" t="s">
+      <c r="D20" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="115" t="s">
+      <c r="E20" s="114" t="s">
         <v>169</v>
       </c>
-      <c r="F20" s="116"/>
-      <c r="G20" s="112"/>
-      <c r="H20" s="113"/>
-      <c r="I20" s="114"/>
+      <c r="F20" s="115"/>
+      <c r="G20" s="111"/>
+      <c r="H20" s="112"/>
+      <c r="I20" s="113"/>
     </row>
     <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="89" t="s">
+      <c r="B21" s="88" t="s">
         <v>108</v>
       </c>
-      <c r="C21" s="120" t="s">
+      <c r="C21" s="119" t="s">
         <v>175</v>
       </c>
-      <c r="D21" s="120" t="s">
+      <c r="D21" s="119" t="s">
         <v>178</v>
       </c>
-      <c r="E21" s="105" t="s">
+      <c r="E21" s="104" t="s">
         <v>140</v>
       </c>
-      <c r="F21" s="117"/>
-      <c r="G21" s="108"/>
-      <c r="H21" s="96"/>
-      <c r="I21" s="97"/>
+      <c r="F21" s="116"/>
+      <c r="G21" s="107"/>
+      <c r="H21" s="95"/>
+      <c r="I21" s="96"/>
     </row>
     <row r="22" spans="2:9" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -8764,393 +8794,393 @@
   <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="83" customWidth="1"/>
-    <col min="2" max="2" width="9" style="83"/>
-    <col min="3" max="4" width="14.75" style="83" customWidth="1"/>
-    <col min="5" max="5" width="43" style="83" customWidth="1"/>
-    <col min="6" max="6" width="61.875" style="83" customWidth="1"/>
-    <col min="7" max="9" width="62.125" style="83" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="83"/>
+    <col min="1" max="1" width="3.375" style="82" customWidth="1"/>
+    <col min="2" max="2" width="9" style="82"/>
+    <col min="3" max="4" width="14.75" style="82" customWidth="1"/>
+    <col min="5" max="5" width="43" style="82" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="82" customWidth="1"/>
+    <col min="7" max="9" width="62.125" style="82" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="82"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="111" t="s">
+      <c r="B1" s="110" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="111"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="109"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="108"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="173" t="s">
+      <c r="B2" s="172" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="177" t="s">
+      <c r="C2" s="176" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="177" t="s">
+      <c r="D2" s="176" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="175" t="s">
+      <c r="E2" s="174" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="171" t="s">
+      <c r="F2" s="170" t="s">
         <v>227</v>
       </c>
-      <c r="G2" s="171"/>
-      <c r="H2" s="171"/>
-      <c r="I2" s="172"/>
+      <c r="G2" s="170"/>
+      <c r="H2" s="170"/>
+      <c r="I2" s="171"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="174"/>
-      <c r="C3" s="178"/>
-      <c r="D3" s="178"/>
-      <c r="E3" s="176"/>
-      <c r="F3" s="99" t="s">
+      <c r="B3" s="173"/>
+      <c r="C3" s="177"/>
+      <c r="D3" s="177"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="98" t="s">
         <v>114</v>
       </c>
-      <c r="G3" s="99" t="s">
+      <c r="G3" s="98" t="s">
         <v>115</v>
       </c>
-      <c r="H3" s="99" t="s">
+      <c r="H3" s="98" t="s">
         <v>116</v>
       </c>
-      <c r="I3" s="100" t="s">
+      <c r="I3" s="99" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="84" t="s">
+      <c r="B4" s="83" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="118" t="s">
+      <c r="D4" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="92" t="s">
+      <c r="E4" s="91" t="s">
         <v>152</v>
       </c>
-      <c r="F4" s="116"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="90"/>
-      <c r="I4" s="94"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="106"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="93"/>
     </row>
     <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="85" t="s">
+      <c r="B5" s="84" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="119" t="s">
+      <c r="C5" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="119" t="s">
+      <c r="D5" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="93" t="s">
+      <c r="E5" s="92" t="s">
         <v>153</v>
       </c>
-      <c r="F5" s="116"/>
-      <c r="G5" s="107"/>
-      <c r="H5" s="91"/>
-      <c r="I5" s="95"/>
+      <c r="F5" s="115"/>
+      <c r="G5" s="106"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="94"/>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="85" t="s">
+      <c r="B6" s="84" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="119" t="s">
+      <c r="C6" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D6" s="119" t="s">
+      <c r="D6" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E6" s="93" t="s">
+      <c r="E6" s="92" t="s">
         <v>154</v>
       </c>
-      <c r="F6" s="116"/>
-      <c r="G6" s="107"/>
-      <c r="H6" s="91"/>
-      <c r="I6" s="95"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="106"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="94"/>
     </row>
     <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="85" t="s">
+      <c r="B7" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="C7" s="119" t="s">
+      <c r="C7" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D7" s="119" t="s">
+      <c r="D7" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="93" t="s">
+      <c r="E7" s="92" t="s">
         <v>155</v>
       </c>
-      <c r="F7" s="116"/>
-      <c r="G7" s="107"/>
-      <c r="H7" s="91"/>
-      <c r="I7" s="95"/>
+      <c r="F7" s="115"/>
+      <c r="G7" s="106"/>
+      <c r="H7" s="90"/>
+      <c r="I7" s="94"/>
     </row>
     <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="86" t="s">
+      <c r="B8" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="119" t="s">
+      <c r="C8" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D8" s="119" t="s">
+      <c r="D8" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E8" s="93" t="s">
+      <c r="E8" s="92" t="s">
         <v>156</v>
       </c>
-      <c r="F8" s="116"/>
-      <c r="G8" s="107"/>
-      <c r="H8" s="91"/>
-      <c r="I8" s="95"/>
+      <c r="F8" s="115"/>
+      <c r="G8" s="106"/>
+      <c r="H8" s="90"/>
+      <c r="I8" s="94"/>
     </row>
     <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.3">
-      <c r="B9" s="86" t="s">
+      <c r="B9" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="119" t="s">
+      <c r="C9" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D9" s="119" t="s">
+      <c r="D9" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E9" s="102" t="s">
+      <c r="E9" s="101" t="s">
         <v>157</v>
       </c>
-      <c r="F9" s="116"/>
-      <c r="G9" s="107"/>
-      <c r="H9" s="91"/>
-      <c r="I9" s="95"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="106"/>
+      <c r="H9" s="90"/>
+      <c r="I9" s="94"/>
     </row>
     <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="86" t="s">
+      <c r="B10" s="85" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="119" t="s">
+      <c r="C10" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D10" s="119" t="s">
+      <c r="D10" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E10" s="102" t="s">
+      <c r="E10" s="101" t="s">
         <v>158</v>
       </c>
-      <c r="F10" s="116"/>
-      <c r="G10" s="107"/>
-      <c r="H10" s="91"/>
-      <c r="I10" s="95"/>
+      <c r="F10" s="115"/>
+      <c r="G10" s="106"/>
+      <c r="H10" s="90"/>
+      <c r="I10" s="94"/>
     </row>
     <row r="11" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="B11" s="85" t="s">
+      <c r="B11" s="84" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="119" t="s">
+      <c r="C11" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D11" s="119" t="s">
+      <c r="D11" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E11" s="102" t="s">
+      <c r="E11" s="101" t="s">
         <v>159</v>
       </c>
-      <c r="F11" s="116"/>
-      <c r="G11" s="107"/>
-      <c r="H11" s="91"/>
-      <c r="I11" s="95"/>
+      <c r="F11" s="115"/>
+      <c r="G11" s="106"/>
+      <c r="H11" s="90"/>
+      <c r="I11" s="94"/>
     </row>
     <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="86" t="s">
+      <c r="B12" s="85" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="119" t="s">
+      <c r="C12" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D12" s="119" t="s">
+      <c r="D12" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E12" s="102" t="s">
+      <c r="E12" s="101" t="s">
         <v>160</v>
       </c>
-      <c r="F12" s="116"/>
-      <c r="G12" s="107"/>
-      <c r="H12" s="91"/>
-      <c r="I12" s="95"/>
+      <c r="F12" s="115"/>
+      <c r="G12" s="106"/>
+      <c r="H12" s="90"/>
+      <c r="I12" s="94"/>
     </row>
     <row r="13" spans="1:9" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="86" t="s">
+      <c r="B13" s="85" t="s">
         <v>118</v>
       </c>
-      <c r="C13" s="119" t="s">
+      <c r="C13" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D13" s="119" t="s">
+      <c r="D13" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="102" t="s">
+      <c r="E13" s="101" t="s">
         <v>161</v>
       </c>
-      <c r="F13" s="116"/>
-      <c r="G13" s="107"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="95"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="106"/>
+      <c r="H13" s="90"/>
+      <c r="I13" s="94"/>
     </row>
     <row r="14" spans="1:9" ht="337.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="87" t="s">
+      <c r="B14" s="86" t="s">
         <v>181</v>
       </c>
-      <c r="C14" s="119" t="s">
+      <c r="C14" s="118" t="s">
         <v>179</v>
       </c>
-      <c r="D14" s="119" t="s">
+      <c r="D14" s="118" t="s">
         <v>180</v>
       </c>
-      <c r="E14" s="102"/>
-      <c r="F14" s="125" t="s">
+      <c r="E14" s="101"/>
+      <c r="F14" s="124" t="s">
         <v>229</v>
       </c>
-      <c r="G14" s="125" t="s">
+      <c r="G14" s="124" t="s">
         <v>230</v>
       </c>
-      <c r="H14" s="125" t="s">
+      <c r="H14" s="124" t="s">
         <v>231</v>
       </c>
-      <c r="I14" s="125" t="s">
+      <c r="I14" s="124" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="87" t="s">
+      <c r="B15" s="86" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="119" t="s">
+      <c r="C15" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D15" s="119" t="s">
+      <c r="D15" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E15" s="102" t="s">
+      <c r="E15" s="101" t="s">
         <v>162</v>
       </c>
-      <c r="F15" s="116"/>
-      <c r="G15" s="107"/>
-      <c r="H15" s="91"/>
-      <c r="I15" s="95"/>
+      <c r="F15" s="115"/>
+      <c r="G15" s="106"/>
+      <c r="H15" s="90"/>
+      <c r="I15" s="94"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="86" t="s">
+      <c r="B16" s="85" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="119" t="s">
+      <c r="C16" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D16" s="119" t="s">
+      <c r="D16" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E16" s="93" t="s">
+      <c r="E16" s="92" t="s">
         <v>163</v>
       </c>
-      <c r="F16" s="116"/>
-      <c r="G16" s="107"/>
-      <c r="H16" s="91"/>
-      <c r="I16" s="95"/>
+      <c r="F16" s="115"/>
+      <c r="G16" s="106"/>
+      <c r="H16" s="90"/>
+      <c r="I16" s="94"/>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="88" t="s">
+      <c r="B17" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C17" s="119" t="s">
+      <c r="C17" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D17" s="119" t="s">
+      <c r="D17" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E17" s="93" t="s">
+      <c r="E17" s="92" t="s">
         <v>105</v>
       </c>
-      <c r="F17" s="116"/>
-      <c r="G17" s="91"/>
-      <c r="H17" s="91"/>
-      <c r="I17" s="95"/>
+      <c r="F17" s="115"/>
+      <c r="G17" s="90"/>
+      <c r="H17" s="90"/>
+      <c r="I17" s="94"/>
     </row>
     <row r="18" spans="2:9" ht="27" x14ac:dyDescent="0.3">
-      <c r="B18" s="88" t="s">
+      <c r="B18" s="87" t="s">
         <v>106</v>
       </c>
-      <c r="C18" s="119" t="s">
+      <c r="C18" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D18" s="119" t="s">
+      <c r="D18" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E18" s="102" t="s">
+      <c r="E18" s="101" t="s">
         <v>164</v>
       </c>
-      <c r="F18" s="116"/>
-      <c r="G18" s="107"/>
-      <c r="H18" s="91"/>
-      <c r="I18" s="95"/>
+      <c r="F18" s="115"/>
+      <c r="G18" s="106"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="94"/>
     </row>
     <row r="19" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="87" t="s">
+      <c r="B19" s="86" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="119" t="s">
+      <c r="C19" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D19" s="119" t="s">
+      <c r="D19" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E19" s="93" t="s">
+      <c r="E19" s="92" t="s">
         <v>139</v>
       </c>
-      <c r="F19" s="116"/>
-      <c r="G19" s="106"/>
-      <c r="H19" s="91"/>
-      <c r="I19" s="95"/>
+      <c r="F19" s="115"/>
+      <c r="G19" s="105"/>
+      <c r="H19" s="90"/>
+      <c r="I19" s="94"/>
     </row>
     <row r="20" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="87" t="s">
+      <c r="B20" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="C20" s="119" t="s">
+      <c r="C20" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D20" s="119" t="s">
+      <c r="D20" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="115" t="s">
+      <c r="E20" s="114" t="s">
         <v>169</v>
       </c>
-      <c r="F20" s="116"/>
-      <c r="G20" s="112"/>
-      <c r="H20" s="113"/>
-      <c r="I20" s="114"/>
+      <c r="F20" s="115"/>
+      <c r="G20" s="111"/>
+      <c r="H20" s="112"/>
+      <c r="I20" s="113"/>
     </row>
     <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="89" t="s">
+      <c r="B21" s="88" t="s">
         <v>108</v>
       </c>
-      <c r="C21" s="120" t="s">
+      <c r="C21" s="119" t="s">
         <v>175</v>
       </c>
-      <c r="D21" s="120" t="s">
+      <c r="D21" s="119" t="s">
         <v>178</v>
       </c>
-      <c r="E21" s="105" t="s">
+      <c r="E21" s="104" t="s">
         <v>140</v>
       </c>
-      <c r="F21" s="117"/>
-      <c r="G21" s="108"/>
-      <c r="H21" s="96"/>
-      <c r="I21" s="97"/>
+      <c r="F21" s="116"/>
+      <c r="G21" s="107"/>
+      <c r="H21" s="95"/>
+      <c r="I21" s="96"/>
     </row>
     <row r="22" spans="2:9" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -9171,411 +9201,411 @@
   <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="83" customWidth="1"/>
-    <col min="2" max="2" width="9" style="83"/>
-    <col min="3" max="4" width="14.75" style="83" customWidth="1"/>
-    <col min="5" max="5" width="43" style="83" customWidth="1"/>
-    <col min="6" max="6" width="61.875" style="83" customWidth="1"/>
-    <col min="7" max="9" width="62.125" style="83" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="83"/>
+    <col min="1" max="1" width="3.375" style="82" customWidth="1"/>
+    <col min="2" max="2" width="9" style="82"/>
+    <col min="3" max="4" width="14.75" style="82" customWidth="1"/>
+    <col min="5" max="5" width="43" style="82" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="82" customWidth="1"/>
+    <col min="7" max="9" width="62.125" style="82" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="82"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="111" t="s">
+      <c r="B1" s="110" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="111"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="109"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="108"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="173" t="s">
+      <c r="B2" s="172" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="177" t="s">
+      <c r="C2" s="176" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="177" t="s">
+      <c r="D2" s="176" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="175" t="s">
+      <c r="E2" s="174" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="171" t="s">
+      <c r="F2" s="170" t="s">
         <v>259</v>
       </c>
-      <c r="G2" s="171"/>
-      <c r="H2" s="171"/>
-      <c r="I2" s="172"/>
+      <c r="G2" s="170"/>
+      <c r="H2" s="170"/>
+      <c r="I2" s="171"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="174"/>
-      <c r="C3" s="178"/>
-      <c r="D3" s="178"/>
-      <c r="E3" s="176"/>
-      <c r="F3" s="99" t="s">
+      <c r="B3" s="173"/>
+      <c r="C3" s="177"/>
+      <c r="D3" s="177"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="98" t="s">
         <v>280</v>
       </c>
-      <c r="G3" s="99" t="s">
+      <c r="G3" s="98" t="s">
         <v>299</v>
       </c>
-      <c r="H3" s="99" t="s">
+      <c r="H3" s="98" t="s">
         <v>298</v>
       </c>
-      <c r="I3" s="100" t="s">
+      <c r="I3" s="99" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="153" t="s">
+      <c r="B4" s="152" t="s">
         <v>108</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="118" t="s">
+      <c r="D4" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="142" t="s">
+      <c r="E4" s="141" t="s">
         <v>140</v>
       </c>
-      <c r="F4" s="143"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="90"/>
-      <c r="I4" s="94"/>
+      <c r="F4" s="142"/>
+      <c r="G4" s="143"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="93"/>
     </row>
     <row r="5" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="B5" s="156" t="s">
+      <c r="B5" s="155" t="s">
         <v>181</v>
       </c>
-      <c r="C5" s="119" t="s">
+      <c r="C5" s="118" t="s">
         <v>270</v>
       </c>
-      <c r="D5" s="119" t="s">
+      <c r="D5" s="118" t="s">
         <v>180</v>
       </c>
-      <c r="E5" s="102" t="s">
+      <c r="E5" s="101" t="s">
         <v>161</v>
       </c>
-      <c r="F5" s="116"/>
-      <c r="G5" s="107"/>
-      <c r="H5" s="125" t="s">
+      <c r="F5" s="115"/>
+      <c r="G5" s="106"/>
+      <c r="H5" s="124" t="s">
         <v>293</v>
       </c>
-      <c r="I5" s="137" t="s">
+      <c r="I5" s="136" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="154" t="s">
+      <c r="B6" s="153" t="s">
         <v>278</v>
       </c>
-      <c r="C6" s="119" t="s">
+      <c r="C6" s="118" t="s">
         <v>271</v>
       </c>
-      <c r="D6" s="119" t="s">
+      <c r="D6" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E6" s="102" t="s">
+      <c r="E6" s="101" t="s">
         <v>161</v>
       </c>
-      <c r="F6" s="125"/>
-      <c r="G6" s="125"/>
-      <c r="H6" s="135" t="s">
+      <c r="F6" s="124"/>
+      <c r="G6" s="124"/>
+      <c r="H6" s="134" t="s">
         <v>292</v>
       </c>
-      <c r="I6" s="158"/>
+      <c r="I6" s="157"/>
     </row>
     <row r="7" spans="1:9" ht="93" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="154" t="s">
+      <c r="B7" s="153" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="119" t="s">
+      <c r="C7" s="118" t="s">
         <v>272</v>
       </c>
-      <c r="D7" s="119" t="s">
+      <c r="D7" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="102" t="s">
+      <c r="E7" s="101" t="s">
         <v>283</v>
       </c>
-      <c r="F7" s="116"/>
-      <c r="G7" s="107"/>
-      <c r="H7" s="91"/>
-      <c r="I7" s="136" t="s">
+      <c r="F7" s="115"/>
+      <c r="G7" s="106"/>
+      <c r="H7" s="90"/>
+      <c r="I7" s="135" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="87.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="154" t="s">
+      <c r="B8" s="153" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="119" t="s">
+      <c r="C8" s="118" t="s">
         <v>271</v>
       </c>
-      <c r="D8" s="119" t="s">
+      <c r="D8" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E8" s="102" t="s">
+      <c r="E8" s="101" t="s">
         <v>282</v>
       </c>
-      <c r="F8" s="116"/>
-      <c r="G8" s="106"/>
-      <c r="H8" s="91"/>
-      <c r="I8" s="136" t="s">
+      <c r="F8" s="115"/>
+      <c r="G8" s="105"/>
+      <c r="H8" s="90"/>
+      <c r="I8" s="135" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="155" t="s">
+      <c r="B9" s="154" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="119" t="s">
+      <c r="C9" s="118" t="s">
         <v>271</v>
       </c>
-      <c r="D9" s="119" t="s">
+      <c r="D9" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E9" s="93" t="s">
+      <c r="E9" s="92" t="s">
         <v>152</v>
       </c>
-      <c r="F9" s="116"/>
-      <c r="G9" s="107"/>
-      <c r="H9" s="140"/>
-      <c r="I9" s="95"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="106"/>
+      <c r="H9" s="139"/>
+      <c r="I9" s="94"/>
     </row>
     <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="155" t="s">
+      <c r="B10" s="154" t="s">
         <v>123</v>
       </c>
-      <c r="C10" s="119" t="s">
+      <c r="C10" s="118" t="s">
         <v>271</v>
       </c>
-      <c r="D10" s="119" t="s">
+      <c r="D10" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E10" s="93" t="s">
+      <c r="E10" s="92" t="s">
         <v>153</v>
       </c>
-      <c r="F10" s="116"/>
-      <c r="G10" s="107"/>
-      <c r="H10" s="91"/>
-      <c r="I10" s="95"/>
+      <c r="F10" s="115"/>
+      <c r="G10" s="106"/>
+      <c r="H10" s="90"/>
+      <c r="I10" s="94"/>
     </row>
     <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="155" t="s">
+      <c r="B11" s="154" t="s">
         <v>124</v>
       </c>
-      <c r="C11" s="119" t="s">
+      <c r="C11" s="118" t="s">
         <v>271</v>
       </c>
-      <c r="D11" s="119" t="s">
+      <c r="D11" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E11" s="93" t="s">
+      <c r="E11" s="92" t="s">
         <v>154</v>
       </c>
-      <c r="F11" s="116"/>
-      <c r="G11" s="107"/>
-      <c r="H11" s="91"/>
-      <c r="I11" s="95"/>
+      <c r="F11" s="115"/>
+      <c r="G11" s="106"/>
+      <c r="H11" s="90"/>
+      <c r="I11" s="94"/>
     </row>
     <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="155" t="s">
+      <c r="B12" s="154" t="s">
         <v>125</v>
       </c>
-      <c r="C12" s="119" t="s">
+      <c r="C12" s="118" t="s">
         <v>271</v>
       </c>
-      <c r="D12" s="119" t="s">
+      <c r="D12" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E12" s="93" t="s">
+      <c r="E12" s="92" t="s">
         <v>155</v>
       </c>
-      <c r="F12" s="116"/>
-      <c r="G12" s="107"/>
-      <c r="H12" s="140"/>
-      <c r="I12" s="95"/>
+      <c r="F12" s="115"/>
+      <c r="G12" s="106"/>
+      <c r="H12" s="139"/>
+      <c r="I12" s="94"/>
     </row>
     <row r="13" spans="1:9" ht="222" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="134" t="s">
+      <c r="B13" s="133" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="119" t="s">
+      <c r="C13" s="118" t="s">
         <v>273</v>
       </c>
-      <c r="D13" s="119" t="s">
+      <c r="D13" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="102" t="s">
+      <c r="E13" s="101" t="s">
         <v>263</v>
       </c>
-      <c r="F13" s="116"/>
-      <c r="G13" s="107"/>
-      <c r="H13" s="135" t="s">
+      <c r="F13" s="115"/>
+      <c r="G13" s="106"/>
+      <c r="H13" s="134" t="s">
         <v>288</v>
       </c>
-      <c r="I13" s="136" t="s">
-        <v>312</v>
+      <c r="I13" s="135" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="133" t="s">
+      <c r="B14" s="132" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="119" t="s">
+      <c r="C14" s="118" t="s">
         <v>273</v>
       </c>
-      <c r="D14" s="119" t="s">
+      <c r="D14" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E14" s="102" t="s">
+      <c r="E14" s="101" t="s">
         <v>264</v>
       </c>
-      <c r="F14" s="116"/>
-      <c r="G14" s="107"/>
-      <c r="H14" s="135" t="s">
+      <c r="F14" s="115"/>
+      <c r="G14" s="106"/>
+      <c r="H14" s="134" t="s">
         <v>285</v>
       </c>
-      <c r="I14" s="136" t="s">
+      <c r="I14" s="135" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="B15" s="133" t="s">
+      <c r="B15" s="132" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="119" t="s">
+      <c r="C15" s="118" t="s">
         <v>274</v>
       </c>
-      <c r="D15" s="119" t="s">
+      <c r="D15" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E15" s="102" t="s">
+      <c r="E15" s="101" t="s">
         <v>262</v>
       </c>
-      <c r="F15" s="116"/>
-      <c r="G15" s="135" t="s">
+      <c r="F15" s="115"/>
+      <c r="G15" s="134" t="s">
         <v>268</v>
       </c>
-      <c r="H15" s="139" t="s">
+      <c r="H15" s="138" t="s">
         <v>286</v>
       </c>
-      <c r="I15" s="161" t="s">
+      <c r="I15" s="160" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="228.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="133" t="s">
+      <c r="B16" s="132" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="119" t="s">
+      <c r="C16" s="118" t="s">
         <v>275</v>
       </c>
-      <c r="D16" s="119" t="s">
+      <c r="D16" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E16" s="102" t="s">
+      <c r="E16" s="101" t="s">
         <v>265</v>
       </c>
-      <c r="F16" s="116"/>
-      <c r="G16" s="107"/>
-      <c r="H16" s="135" t="s">
+      <c r="F16" s="115"/>
+      <c r="G16" s="106"/>
+      <c r="H16" s="134" t="s">
         <v>290</v>
       </c>
-      <c r="I16" s="136" t="s">
-        <v>311</v>
+      <c r="I16" s="135" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="132" t="s">
+      <c r="B17" s="131" t="s">
         <v>167</v>
       </c>
-      <c r="C17" s="119" t="s">
+      <c r="C17" s="118" t="s">
         <v>273</v>
       </c>
-      <c r="D17" s="119" t="s">
+      <c r="D17" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E17" s="115" t="s">
+      <c r="E17" s="114" t="s">
         <v>269</v>
       </c>
-      <c r="F17" s="116"/>
-      <c r="G17" s="131" t="s">
+      <c r="F17" s="115"/>
+      <c r="G17" s="130" t="s">
         <v>260</v>
       </c>
-      <c r="H17" s="157" t="s">
-        <v>320</v>
-      </c>
-      <c r="I17" s="138" t="s">
-        <v>321</v>
+      <c r="H17" s="156" t="s">
+        <v>316</v>
+      </c>
+      <c r="I17" s="137" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="18" spans="2:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="133" t="s">
+      <c r="B18" s="132" t="s">
         <v>141</v>
       </c>
-      <c r="C18" s="119" t="s">
+      <c r="C18" s="118" t="s">
         <v>276</v>
       </c>
-      <c r="D18" s="119" t="s">
+      <c r="D18" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E18" s="115" t="s">
+      <c r="E18" s="114" t="s">
         <v>281</v>
       </c>
-      <c r="F18" s="116"/>
-      <c r="G18" s="131"/>
-      <c r="H18" s="135"/>
-      <c r="I18" s="138"/>
+      <c r="F18" s="115"/>
+      <c r="G18" s="130"/>
+      <c r="H18" s="134"/>
+      <c r="I18" s="137"/>
     </row>
     <row r="19" spans="2:9" ht="108" x14ac:dyDescent="0.3">
-      <c r="B19" s="152" t="s">
+      <c r="B19" s="151" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="141" t="s">
+      <c r="C19" s="140" t="s">
         <v>273</v>
       </c>
-      <c r="D19" s="141" t="s">
+      <c r="D19" s="140" t="s">
         <v>178</v>
       </c>
-      <c r="E19" s="93" t="s">
+      <c r="E19" s="92" t="s">
         <v>156</v>
       </c>
-      <c r="F19" s="116"/>
-      <c r="G19" s="135" t="s">
+      <c r="F19" s="115"/>
+      <c r="G19" s="134" t="s">
         <v>267</v>
       </c>
-      <c r="H19" s="135" t="s">
+      <c r="H19" s="134" t="s">
         <v>287</v>
       </c>
-      <c r="I19" s="136" t="s">
+      <c r="I19" s="135" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="145" t="s">
+      <c r="B20" s="144" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="146" t="s">
+      <c r="C20" s="145" t="s">
         <v>277</v>
       </c>
-      <c r="D20" s="146" t="s">
+      <c r="D20" s="145" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="147" t="s">
+      <c r="E20" s="146" t="s">
         <v>261</v>
       </c>
-      <c r="F20" s="148"/>
-      <c r="G20" s="149" t="s">
+      <c r="F20" s="147"/>
+      <c r="G20" s="148" t="s">
         <v>266</v>
       </c>
-      <c r="H20" s="150"/>
-      <c r="I20" s="151"/>
+      <c r="H20" s="149"/>
+      <c r="I20" s="150"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -9596,400 +9626,400 @@
   <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="83" customWidth="1"/>
-    <col min="2" max="2" width="9" style="83"/>
-    <col min="3" max="4" width="14.75" style="83" customWidth="1"/>
-    <col min="5" max="5" width="43" style="83" customWidth="1"/>
-    <col min="6" max="6" width="61.875" style="83" customWidth="1"/>
-    <col min="7" max="9" width="62.125" style="83" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="83"/>
+    <col min="1" max="1" width="3.375" style="82" customWidth="1"/>
+    <col min="2" max="2" width="9" style="82"/>
+    <col min="3" max="4" width="14.75" style="82" customWidth="1"/>
+    <col min="5" max="5" width="43" style="82" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="82" customWidth="1"/>
+    <col min="7" max="9" width="62.125" style="82" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="82"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="111" t="s">
+      <c r="B1" s="110" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="111"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="109"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="108"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="173" t="s">
+      <c r="B2" s="172" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="177" t="s">
+      <c r="C2" s="176" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="177" t="s">
+      <c r="D2" s="176" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="175" t="s">
+      <c r="E2" s="174" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="171" t="s">
+      <c r="F2" s="170" t="s">
         <v>279</v>
       </c>
-      <c r="G2" s="171"/>
-      <c r="H2" s="171"/>
-      <c r="I2" s="172"/>
+      <c r="G2" s="170"/>
+      <c r="H2" s="170"/>
+      <c r="I2" s="171"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="174"/>
-      <c r="C3" s="178"/>
-      <c r="D3" s="178"/>
-      <c r="E3" s="176"/>
-      <c r="F3" s="99" t="s">
+      <c r="B3" s="173"/>
+      <c r="C3" s="177"/>
+      <c r="D3" s="177"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="98" t="s">
         <v>300</v>
       </c>
-      <c r="G3" s="99" t="s">
+      <c r="G3" s="98" t="s">
         <v>301</v>
       </c>
-      <c r="H3" s="99" t="s">
+      <c r="H3" s="98" t="s">
         <v>302</v>
       </c>
-      <c r="I3" s="100" t="s">
+      <c r="I3" s="99" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="153" t="s">
+      <c r="B4" s="152" t="s">
         <v>108</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="118" t="s">
+      <c r="D4" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="142" t="s">
+      <c r="E4" s="141" t="s">
         <v>140</v>
       </c>
-      <c r="F4" s="143"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="90"/>
-      <c r="I4" s="94"/>
+      <c r="F4" s="142"/>
+      <c r="G4" s="143"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="93"/>
     </row>
     <row r="5" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="B5" s="156" t="s">
+      <c r="B5" s="155" t="s">
         <v>181</v>
       </c>
-      <c r="C5" s="119" t="s">
+      <c r="C5" s="118" t="s">
         <v>270</v>
       </c>
-      <c r="D5" s="119" t="s">
+      <c r="D5" s="118" t="s">
         <v>180</v>
       </c>
-      <c r="E5" s="102" t="s">
+      <c r="E5" s="101" t="s">
         <v>161</v>
       </c>
-      <c r="F5" s="125" t="s">
+      <c r="F5" s="124" t="s">
         <v>304</v>
       </c>
-      <c r="G5" s="159"/>
-      <c r="H5" s="125"/>
-      <c r="I5" s="137"/>
+      <c r="G5" s="158"/>
+      <c r="H5" s="124"/>
+      <c r="I5" s="136"/>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="154" t="s">
+      <c r="B6" s="153" t="s">
         <v>278</v>
       </c>
-      <c r="C6" s="119" t="s">
+      <c r="C6" s="118" t="s">
         <v>271</v>
       </c>
-      <c r="D6" s="119" t="s">
+      <c r="D6" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E6" s="102" t="s">
+      <c r="E6" s="101" t="s">
         <v>161</v>
       </c>
-      <c r="F6" s="125"/>
-      <c r="G6" s="125"/>
-      <c r="H6" s="125"/>
-      <c r="I6" s="137"/>
+      <c r="F6" s="124"/>
+      <c r="G6" s="124"/>
+      <c r="H6" s="124"/>
+      <c r="I6" s="136"/>
     </row>
     <row r="7" spans="1:9" ht="138" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="154" t="s">
+      <c r="B7" s="153" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="119" t="s">
+      <c r="C7" s="118" t="s">
         <v>272</v>
       </c>
-      <c r="D7" s="119" t="s">
+      <c r="D7" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="102" t="s">
+      <c r="E7" s="101" t="s">
         <v>162</v>
       </c>
-      <c r="F7" s="125" t="s">
-        <v>316</v>
-      </c>
-      <c r="G7" s="107" t="s">
+      <c r="F7" s="124" t="s">
+        <v>313</v>
+      </c>
+      <c r="G7" s="106" t="s">
+        <v>311</v>
+      </c>
+      <c r="H7" s="90"/>
+      <c r="I7" s="94"/>
+    </row>
+    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="153" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="118" t="s">
+        <v>271</v>
+      </c>
+      <c r="D8" s="118" t="s">
+        <v>178</v>
+      </c>
+      <c r="E8" s="92" t="s">
+        <v>139</v>
+      </c>
+      <c r="F8" s="115"/>
+      <c r="G8" s="105"/>
+      <c r="H8" s="90"/>
+      <c r="I8" s="94"/>
+    </row>
+    <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="154" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="118" t="s">
+        <v>271</v>
+      </c>
+      <c r="D9" s="118" t="s">
+        <v>178</v>
+      </c>
+      <c r="E9" s="92" t="s">
+        <v>152</v>
+      </c>
+      <c r="F9" s="115"/>
+      <c r="G9" s="106"/>
+      <c r="H9" s="139"/>
+      <c r="I9" s="94"/>
+    </row>
+    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="154" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" s="118" t="s">
+        <v>271</v>
+      </c>
+      <c r="D10" s="118" t="s">
+        <v>178</v>
+      </c>
+      <c r="E10" s="92" t="s">
+        <v>153</v>
+      </c>
+      <c r="F10" s="115"/>
+      <c r="G10" s="106"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="94"/>
+    </row>
+    <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="154" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" s="118" t="s">
+        <v>271</v>
+      </c>
+      <c r="D11" s="118" t="s">
+        <v>178</v>
+      </c>
+      <c r="E11" s="92" t="s">
+        <v>154</v>
+      </c>
+      <c r="F11" s="115"/>
+      <c r="G11" s="106"/>
+      <c r="H11" s="139"/>
+      <c r="I11" s="94"/>
+    </row>
+    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="154" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" s="118" t="s">
+        <v>271</v>
+      </c>
+      <c r="D12" s="118" t="s">
+        <v>178</v>
+      </c>
+      <c r="E12" s="92" t="s">
+        <v>155</v>
+      </c>
+      <c r="F12" s="115"/>
+      <c r="G12" s="106"/>
+      <c r="H12" s="139"/>
+      <c r="I12" s="94"/>
+    </row>
+    <row r="13" spans="1:9" ht="175.5" x14ac:dyDescent="0.3">
+      <c r="B13" s="133" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="118" t="s">
+        <v>273</v>
+      </c>
+      <c r="D13" s="118" t="s">
+        <v>178</v>
+      </c>
+      <c r="E13" s="101" t="s">
+        <v>263</v>
+      </c>
+      <c r="F13" s="134" t="s">
+        <v>322</v>
+      </c>
+      <c r="G13" s="158" t="s">
+        <v>323</v>
+      </c>
+      <c r="H13" s="134"/>
+      <c r="I13" s="135"/>
+    </row>
+    <row r="14" spans="1:9" ht="270" x14ac:dyDescent="0.3">
+      <c r="B14" s="132" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="118" t="s">
+        <v>273</v>
+      </c>
+      <c r="D14" s="118" t="s">
+        <v>178</v>
+      </c>
+      <c r="E14" s="101" t="s">
+        <v>264</v>
+      </c>
+      <c r="F14" s="134" t="s">
+        <v>312</v>
+      </c>
+      <c r="G14" s="158" t="s">
+        <v>324</v>
+      </c>
+      <c r="H14" s="106" t="s">
         <v>314</v>
       </c>
-      <c r="H7" s="91"/>
-      <c r="I7" s="95"/>
-    </row>
-    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="154" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8" s="119" t="s">
-        <v>271</v>
-      </c>
-      <c r="D8" s="119" t="s">
+      <c r="I14" s="123" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
+      <c r="B15" s="132" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="118" t="s">
+        <v>274</v>
+      </c>
+      <c r="D15" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E8" s="93" t="s">
-        <v>139</v>
-      </c>
-      <c r="F8" s="116"/>
-      <c r="G8" s="106"/>
-      <c r="H8" s="91"/>
-      <c r="I8" s="95"/>
-    </row>
-    <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="155" t="s">
-        <v>117</v>
-      </c>
-      <c r="C9" s="119" t="s">
-        <v>271</v>
-      </c>
-      <c r="D9" s="119" t="s">
+      <c r="E15" s="101" t="s">
+        <v>262</v>
+      </c>
+      <c r="F15" s="134" t="s">
+        <v>306</v>
+      </c>
+      <c r="G15" s="159"/>
+      <c r="H15" s="138"/>
+      <c r="I15" s="135"/>
+    </row>
+    <row r="16" spans="1:9" ht="108" x14ac:dyDescent="0.3">
+      <c r="B16" s="132" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="118" t="s">
+        <v>275</v>
+      </c>
+      <c r="D16" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E9" s="93" t="s">
-        <v>152</v>
-      </c>
-      <c r="F9" s="116"/>
-      <c r="G9" s="107"/>
-      <c r="H9" s="140"/>
-      <c r="I9" s="95"/>
-    </row>
-    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="155" t="s">
-        <v>123</v>
-      </c>
-      <c r="C10" s="119" t="s">
-        <v>271</v>
-      </c>
-      <c r="D10" s="119" t="s">
+      <c r="E16" s="101" t="s">
+        <v>265</v>
+      </c>
+      <c r="F16" s="134" t="s">
+        <v>320</v>
+      </c>
+      <c r="G16" s="158" t="s">
+        <v>325</v>
+      </c>
+      <c r="H16" s="106" t="s">
+        <v>321</v>
+      </c>
+      <c r="I16" s="135"/>
+    </row>
+    <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="131" t="s">
+        <v>167</v>
+      </c>
+      <c r="C17" s="118" t="s">
+        <v>273</v>
+      </c>
+      <c r="D17" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E10" s="93" t="s">
-        <v>153</v>
-      </c>
-      <c r="F10" s="116"/>
-      <c r="G10" s="107"/>
-      <c r="H10" s="140"/>
-      <c r="I10" s="95"/>
-    </row>
-    <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="155" t="s">
-        <v>124</v>
-      </c>
-      <c r="C11" s="119" t="s">
-        <v>271</v>
-      </c>
-      <c r="D11" s="119" t="s">
+      <c r="E17" s="114" t="s">
+        <v>308</v>
+      </c>
+      <c r="F17" s="156" t="s">
+        <v>319</v>
+      </c>
+      <c r="G17" s="120" t="s">
+        <v>326</v>
+      </c>
+      <c r="H17" s="138"/>
+      <c r="I17" s="137"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B18" s="132" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" s="118" t="s">
+        <v>276</v>
+      </c>
+      <c r="D18" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E11" s="93" t="s">
-        <v>154</v>
-      </c>
-      <c r="F11" s="116"/>
-      <c r="G11" s="107"/>
-      <c r="H11" s="140"/>
-      <c r="I11" s="95"/>
-    </row>
-    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="155" t="s">
-        <v>125</v>
-      </c>
-      <c r="C12" s="119" t="s">
-        <v>271</v>
-      </c>
-      <c r="D12" s="119" t="s">
+      <c r="E18" s="114"/>
+      <c r="F18" s="156"/>
+      <c r="G18" s="134"/>
+      <c r="H18" s="138"/>
+      <c r="I18" s="137"/>
+    </row>
+    <row r="19" spans="2:9" ht="54" x14ac:dyDescent="0.3">
+      <c r="B19" s="151" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="140" t="s">
+        <v>273</v>
+      </c>
+      <c r="D19" s="140" t="s">
         <v>178</v>
       </c>
-      <c r="E12" s="93" t="s">
-        <v>155</v>
-      </c>
-      <c r="F12" s="116"/>
-      <c r="G12" s="107"/>
-      <c r="H12" s="140"/>
-      <c r="I12" s="95"/>
-    </row>
-    <row r="13" spans="1:9" ht="135" x14ac:dyDescent="0.3">
-      <c r="B13" s="134" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" s="119" t="s">
-        <v>273</v>
-      </c>
-      <c r="D13" s="119" t="s">
+      <c r="E19" s="92" t="s">
+        <v>156</v>
+      </c>
+      <c r="F19" s="134" t="s">
+        <v>289</v>
+      </c>
+      <c r="G19" s="159"/>
+      <c r="I19" s="94"/>
+    </row>
+    <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="144" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="145" t="s">
+        <v>277</v>
+      </c>
+      <c r="D20" s="145" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="102" t="s">
-        <v>263</v>
-      </c>
-      <c r="F13" s="135" t="s">
-        <v>327</v>
-      </c>
-      <c r="G13" s="159" t="s">
-        <v>328</v>
-      </c>
-      <c r="H13" s="135"/>
-      <c r="I13" s="136"/>
-    </row>
-    <row r="14" spans="1:9" ht="162" x14ac:dyDescent="0.3">
-      <c r="B14" s="133" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="119" t="s">
-        <v>273</v>
-      </c>
-      <c r="D14" s="119" t="s">
-        <v>178</v>
-      </c>
-      <c r="E14" s="102" t="s">
-        <v>264</v>
-      </c>
-      <c r="F14" s="135" t="s">
-        <v>315</v>
-      </c>
-      <c r="G14" s="159" t="s">
-        <v>317</v>
-      </c>
-      <c r="H14" s="107" t="s">
+      <c r="E20" s="146" t="s">
+        <v>261</v>
+      </c>
+      <c r="F20" s="162" t="s">
         <v>318</v>
       </c>
-      <c r="I14" s="124" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="B15" s="133" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="119" t="s">
-        <v>274</v>
-      </c>
-      <c r="D15" s="119" t="s">
-        <v>178</v>
-      </c>
-      <c r="E15" s="102" t="s">
-        <v>262</v>
-      </c>
-      <c r="F15" s="135" t="s">
-        <v>306</v>
-      </c>
-      <c r="G15" s="160"/>
-      <c r="H15" s="139"/>
-      <c r="I15" s="136"/>
-    </row>
-    <row r="16" spans="1:9" ht="108" x14ac:dyDescent="0.3">
-      <c r="B16" s="133" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" s="119" t="s">
-        <v>275</v>
-      </c>
-      <c r="D16" s="119" t="s">
-        <v>178</v>
-      </c>
-      <c r="E16" s="102" t="s">
-        <v>265</v>
-      </c>
-      <c r="F16" s="135" t="s">
-        <v>324</v>
-      </c>
-      <c r="G16" s="159" t="s">
-        <v>325</v>
-      </c>
-      <c r="H16" s="107" t="s">
-        <v>326</v>
-      </c>
-      <c r="I16" s="136"/>
-    </row>
-    <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="132" t="s">
-        <v>167</v>
-      </c>
-      <c r="C17" s="119" t="s">
-        <v>273</v>
-      </c>
-      <c r="D17" s="119" t="s">
-        <v>178</v>
-      </c>
-      <c r="E17" s="115" t="s">
-        <v>310</v>
-      </c>
-      <c r="F17" s="157" t="s">
-        <v>323</v>
-      </c>
-      <c r="G17" s="121" t="s">
-        <v>313</v>
-      </c>
-      <c r="H17" s="139"/>
-      <c r="I17" s="138"/>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="133" t="s">
-        <v>141</v>
-      </c>
-      <c r="C18" s="119" t="s">
-        <v>276</v>
-      </c>
-      <c r="D18" s="119" t="s">
-        <v>178</v>
-      </c>
-      <c r="E18" s="115"/>
-      <c r="F18" s="157"/>
-      <c r="G18" s="135"/>
-      <c r="H18" s="139"/>
-      <c r="I18" s="138"/>
-    </row>
-    <row r="19" spans="2:9" ht="54" x14ac:dyDescent="0.3">
-      <c r="B19" s="152" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="141" t="s">
-        <v>273</v>
-      </c>
-      <c r="D19" s="141" t="s">
-        <v>178</v>
-      </c>
-      <c r="E19" s="93" t="s">
-        <v>156</v>
-      </c>
-      <c r="F19" s="135" t="s">
-        <v>289</v>
-      </c>
-      <c r="G19" s="160"/>
-      <c r="I19" s="95"/>
-    </row>
-    <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="145" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="146" t="s">
-        <v>277</v>
-      </c>
-      <c r="D20" s="146" t="s">
-        <v>178</v>
-      </c>
-      <c r="E20" s="147" t="s">
-        <v>261</v>
-      </c>
-      <c r="F20" s="163" t="s">
-        <v>322</v>
-      </c>
-      <c r="G20" s="149"/>
-      <c r="H20" s="150"/>
-      <c r="I20" s="151"/>
+      <c r="G20" s="148"/>
+      <c r="H20" s="149"/>
+      <c r="I20" s="150"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="대일정" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="333">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2820,13 +2820,6 @@
   <si>
     <t>[임제훈 사원]
 - 열에너지차량시험 측 일정 최종 정리 공유
-  : 11/14(금) BJ AP2 차량 PTC 개선품 리워크 후 확인 (남양연구소 B1-7)
-  : 11/18(화) ~ 11/20(목) 리워크 완료 AP2 차량 국내 트립 진행</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- 열에너지차량시험 측 일정 최종 정리 공유
   : 11/25(화) ~ 11/26(수) 실차 난방 평가 진행</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2890,33 +2883,11 @@
   </si>
   <si>
     <t>[임제훈 사원]
-- ESIR 진행 (~11/15)
-  : ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
 - 사이버 보안 항목 QV와 비교 및 리스트업 후 공조시스템설계팀 회신 (11/04)
   : ES95489-21 빼는 것은 안됨. 업데이트에 해당하는 항목 N/A로 하자고 회신 받음
   : 공조시스템설계팀 방침으로 인해 SVm 사이버 보안 적용 진행, 업데이트 불가능
 [김진겸 사원]
 - 설계변경 시 ERP 등록 준비(11/06)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- 사이버 보안 M단계 적용으로 김응영 책임에게 유선 확인 완료 (11/07)
-  : 공정 감사 5EA 건에 대해서는 공정 감사 어디서 하는지 모른다고 함, 확인 필요
-- 기아샤시시스템품질팀 김제일 매니저 사이버보안 납품건 확인 완료 (11/10)
-  : QV와 동일하게 LP2 5EA 납품, M단계 전량 사이버 보안 적용 진행 요청 받음
-  : 사이버 보안으로 바뀐 이력 공유 완료
-- 설계 변경 결재 상신 완료 (11/10)
-  : 기구팀 문의 결과, QV, SVm, BJ 담당자 전부 똑같다고 함. 결재 라인 똑같이 예정
-  : 설계 변경 문서 작성 완료
-  : 사이버 보안 미적용 SW, 적용 SW 동작 확인 완료
-- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 완료 (11/10)
-- 공조 로컬 CAN 심의회 진행 (11/13)
-  : SVm, BJ, NX5e, MX5a, HE1i 대상</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2944,14 +2915,6 @@
   <si>
     <t>[임제훈 사원]
 - 공조 로컬 CAN 심의회 진행 (11/13)
-  : SVm, BJ, NX5e, MX5a, HE1i 대상
-- ESIR 진행 (~11/15)
-  : ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- 공조 로컬 CAN 심의회 진행 (11/13)
   : SVm, BJ, NX5e, MX5a, HE1i 대상</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2992,6 +2955,70 @@
   <si>
     <t>[우리산업]
 기구 : 공준석, HW : 하성빈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 기아샤시시스템품질팀 평택 공장 방문 (11/14)
+  : 11월 정기 협의체 회의는 평택 공장 방문 점검으로 대체
+  : 정기 협의체 진행 후 요청 자료에 대한 리뷰 (12월 정기 방문시 설명으로 협의)
+  : 평택 PTC 인라인 공정 확인요청 (SVm 조립공정과 그나마 유사한 공정 선정)
+  : SV 대비 SVm 서지 내성 관련 강건화 설계컨셉 설명 요청 (H/W)
+  : SVm PCB 실물 2ea 준비요청</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 사이버 보안 적용 단계, 피지컬 ID, 사이버보안품질팀 담당자 문의 (11/11)
+  : 김동환 연구원 유선 문의 완료, 빠르게 파악 후 회신 한다고 함.
+  : 12일 오전 까지 회신 없으면 12일 오후 정재근 책임 연구원 연락 예정
+- 공조 로컬 CAN 심의회 진행 (11/13)
+  : SVm, BJ, NX5e, MX5a, HE1i 대상
+- ESIR 진행 (~11/15)
+  : ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24
+  : ES95411-00 Unit Test, Integration Test 파라소프트 결과서 필요
+  : ES90700-00 작성 완료, 결재본 첨부 필요
+  : ES95480-00 작성 완료, 결재본 첨부 필요
+  : ES95489-21 피지컬 ID 및 보안 키 생성 업무 연락 및 첨부 자료 필요
+  : ES95489-24 실제 수행 자료 필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 사이버 보안 M단계 적용으로 김응영 책임에게 유선 확인 완료 (11/07)
+  : 공정 감사 5EA 건에 대해서는 공정 감사 어디서 하는지 모른다고 함
+- 기아샤시시스템품질팀 김제일 매니저 사이버보안 납품건 확인 완료 (11/10)
+  : QV와 동일하게 LP2 5EA 납품, M단계 전량 사이버 보안 적용 진행 요청 받음
+  : 사이버 보안으로 바뀐 이력 김제일 매니저 공유 완료
+- 설계 변경 결재 상신 완료 (11/10)
+  : 기구팀 문의 결과, QV, SVm, BJ 담당자 전부 똑같다고 함. 결재 라인 똑같이 예정
+  : 설계 변경 문서 작성 완료
+  : 사이버 보안 미적용 SW, 적용 SW 동작 확인 완료
+- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 완료 (11/10)
+- 공조 로컬 CAN 심의회 진행 (11/13)
+  : SVm, BJ, NX5e, MX5a, HE1i 대상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- R로직 튜닝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 열에너지차량시험 측 일정 최종 정리 공유
+  : 11/14(금) BJ AP2 차량 PTC 개선품 리워크 후 확인 (남양연구소 B1-7)
+  : 11/18(화) ~ 11/20(목) 리워크 완료 AP2 차량 국내 트립 진행
+- LHD, RHD R로직 튜닝
+  : 11/17 ~ 11/21 야간 칼로리 사용 예약, 11/24 ~ 11/28 주간 칼로리 사용 예약
+  : 11/17 ~ 11/21 주간 사용은 이제창 사원에게 사용 여부 확인 필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- R로직 튜닝
+  : 11/17 ~ 11/21 야간 칼로리 사용 예약, 11/24 ~ 11/28 주간 칼로리 사용 예약
+  : 11/17 ~ 11/21 주간 사용은 이제창 사원에게 사용 여부 확인 필요</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4372,7 +4399,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="180">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4862,6 +4889,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4907,8 +4937,8 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -5575,90 +5605,90 @@
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="163" t="s">
+      <c r="B2" s="164" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="165" t="s">
+      <c r="C2" s="166" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="165" t="s">
+      <c r="D2" s="166" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="169">
+      <c r="E2" s="170">
         <v>23</v>
       </c>
-      <c r="F2" s="167"/>
-      <c r="G2" s="167"/>
-      <c r="H2" s="167"/>
-      <c r="I2" s="167"/>
-      <c r="J2" s="167"/>
-      <c r="K2" s="167"/>
-      <c r="L2" s="167"/>
-      <c r="M2" s="167"/>
-      <c r="N2" s="167"/>
-      <c r="O2" s="167"/>
-      <c r="P2" s="167"/>
-      <c r="Q2" s="167">
+      <c r="F2" s="168"/>
+      <c r="G2" s="168"/>
+      <c r="H2" s="168"/>
+      <c r="I2" s="168"/>
+      <c r="J2" s="168"/>
+      <c r="K2" s="168"/>
+      <c r="L2" s="168"/>
+      <c r="M2" s="168"/>
+      <c r="N2" s="168"/>
+      <c r="O2" s="168"/>
+      <c r="P2" s="168"/>
+      <c r="Q2" s="168">
         <v>24</v>
       </c>
-      <c r="R2" s="167"/>
-      <c r="S2" s="167"/>
-      <c r="T2" s="167"/>
-      <c r="U2" s="167"/>
-      <c r="V2" s="167"/>
-      <c r="W2" s="167"/>
-      <c r="X2" s="167"/>
-      <c r="Y2" s="167"/>
-      <c r="Z2" s="167"/>
-      <c r="AA2" s="167"/>
-      <c r="AB2" s="167"/>
-      <c r="AC2" s="167">
+      <c r="R2" s="168"/>
+      <c r="S2" s="168"/>
+      <c r="T2" s="168"/>
+      <c r="U2" s="168"/>
+      <c r="V2" s="168"/>
+      <c r="W2" s="168"/>
+      <c r="X2" s="168"/>
+      <c r="Y2" s="168"/>
+      <c r="Z2" s="168"/>
+      <c r="AA2" s="168"/>
+      <c r="AB2" s="168"/>
+      <c r="AC2" s="168">
         <v>25</v>
       </c>
-      <c r="AD2" s="167"/>
-      <c r="AE2" s="167"/>
-      <c r="AF2" s="167"/>
-      <c r="AG2" s="167"/>
-      <c r="AH2" s="167"/>
-      <c r="AI2" s="167"/>
-      <c r="AJ2" s="167"/>
-      <c r="AK2" s="167"/>
-      <c r="AL2" s="167"/>
-      <c r="AM2" s="167"/>
-      <c r="AN2" s="167"/>
-      <c r="AO2" s="167">
+      <c r="AD2" s="168"/>
+      <c r="AE2" s="168"/>
+      <c r="AF2" s="168"/>
+      <c r="AG2" s="168"/>
+      <c r="AH2" s="168"/>
+      <c r="AI2" s="168"/>
+      <c r="AJ2" s="168"/>
+      <c r="AK2" s="168"/>
+      <c r="AL2" s="168"/>
+      <c r="AM2" s="168"/>
+      <c r="AN2" s="168"/>
+      <c r="AO2" s="168">
         <v>26</v>
       </c>
-      <c r="AP2" s="167"/>
-      <c r="AQ2" s="167"/>
-      <c r="AR2" s="167"/>
-      <c r="AS2" s="167"/>
-      <c r="AT2" s="167"/>
-      <c r="AU2" s="167"/>
-      <c r="AV2" s="167"/>
-      <c r="AW2" s="167"/>
-      <c r="AX2" s="167"/>
-      <c r="AY2" s="167"/>
-      <c r="AZ2" s="168"/>
-      <c r="BA2" s="167">
+      <c r="AP2" s="168"/>
+      <c r="AQ2" s="168"/>
+      <c r="AR2" s="168"/>
+      <c r="AS2" s="168"/>
+      <c r="AT2" s="168"/>
+      <c r="AU2" s="168"/>
+      <c r="AV2" s="168"/>
+      <c r="AW2" s="168"/>
+      <c r="AX2" s="168"/>
+      <c r="AY2" s="168"/>
+      <c r="AZ2" s="169"/>
+      <c r="BA2" s="168">
         <v>27</v>
       </c>
-      <c r="BB2" s="167"/>
-      <c r="BC2" s="167"/>
-      <c r="BD2" s="167"/>
-      <c r="BE2" s="167"/>
-      <c r="BF2" s="167"/>
-      <c r="BG2" s="167"/>
-      <c r="BH2" s="167"/>
-      <c r="BI2" s="167"/>
-      <c r="BJ2" s="167"/>
-      <c r="BK2" s="167"/>
-      <c r="BL2" s="168"/>
+      <c r="BB2" s="168"/>
+      <c r="BC2" s="168"/>
+      <c r="BD2" s="168"/>
+      <c r="BE2" s="168"/>
+      <c r="BF2" s="168"/>
+      <c r="BG2" s="168"/>
+      <c r="BH2" s="168"/>
+      <c r="BI2" s="168"/>
+      <c r="BJ2" s="168"/>
+      <c r="BK2" s="168"/>
+      <c r="BL2" s="169"/>
     </row>
     <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="164"/>
-      <c r="C3" s="166"/>
-      <c r="D3" s="166"/>
+      <c r="B3" s="165"/>
+      <c r="C3" s="167"/>
+      <c r="D3" s="167"/>
       <c r="E3" s="22">
         <v>1</v>
       </c>
@@ -6399,7 +6429,7 @@
         <v>77</v>
       </c>
       <c r="D11" s="161" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="7"/>
@@ -6482,7 +6512,7 @@
         <v>105</v>
       </c>
       <c r="D12" s="161" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="7"/>
@@ -6563,7 +6593,7 @@
         <v>82</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="7"/>
@@ -7000,7 +7030,7 @@
         <v>258</v>
       </c>
       <c r="D18" s="161" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E18" s="64"/>
       <c r="F18" s="65"/>
@@ -7398,8 +7428,8 @@
       <c r="C23" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="D23" s="178" t="s">
-        <v>329</v>
+      <c r="D23" s="163" t="s">
+        <v>325</v>
       </c>
       <c r="E23" s="49"/>
       <c r="F23" s="50"/>
@@ -7639,39 +7669,39 @@
       <c r="E1" s="108"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="172" t="s">
+      <c r="B2" s="173" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="176" t="s">
+      <c r="C2" s="177" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="176" t="s">
+      <c r="D2" s="177" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="174" t="s">
+      <c r="E2" s="175" t="s">
         <v>126</v>
       </c>
       <c r="F2" s="97" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="170" t="s">
+      <c r="G2" s="171" t="s">
         <v>113</v>
       </c>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="171"/>
-      <c r="K2" s="170" t="s">
+      <c r="H2" s="171"/>
+      <c r="I2" s="171"/>
+      <c r="J2" s="172"/>
+      <c r="K2" s="171" t="s">
         <v>182</v>
       </c>
-      <c r="L2" s="170"/>
-      <c r="M2" s="170"/>
-      <c r="N2" s="171"/>
+      <c r="L2" s="171"/>
+      <c r="M2" s="171"/>
+      <c r="N2" s="172"/>
     </row>
     <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="173"/>
-      <c r="C3" s="177"/>
-      <c r="D3" s="177"/>
-      <c r="E3" s="175"/>
+      <c r="B3" s="174"/>
+      <c r="C3" s="178"/>
+      <c r="D3" s="178"/>
+      <c r="E3" s="176"/>
       <c r="F3" s="98" t="s">
         <v>111</v>
       </c>
@@ -8414,30 +8444,30 @@
       <c r="E1" s="108"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="172" t="s">
+      <c r="B2" s="173" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="176" t="s">
+      <c r="C2" s="177" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="176" t="s">
+      <c r="D2" s="177" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="174" t="s">
+      <c r="E2" s="175" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="170" t="s">
+      <c r="F2" s="171" t="s">
         <v>182</v>
       </c>
-      <c r="G2" s="170"/>
-      <c r="H2" s="170"/>
-      <c r="I2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="172"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="173"/>
-      <c r="C3" s="177"/>
-      <c r="D3" s="177"/>
-      <c r="E3" s="175"/>
+      <c r="B3" s="174"/>
+      <c r="C3" s="178"/>
+      <c r="D3" s="178"/>
+      <c r="E3" s="176"/>
       <c r="F3" s="98" t="s">
         <v>114</v>
       </c>
@@ -8815,30 +8845,30 @@
       <c r="E1" s="108"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="172" t="s">
+      <c r="B2" s="173" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="176" t="s">
+      <c r="C2" s="177" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="176" t="s">
+      <c r="D2" s="177" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="174" t="s">
+      <c r="E2" s="175" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="170" t="s">
+      <c r="F2" s="171" t="s">
         <v>227</v>
       </c>
-      <c r="G2" s="170"/>
-      <c r="H2" s="170"/>
-      <c r="I2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="172"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="173"/>
-      <c r="C3" s="177"/>
-      <c r="D3" s="177"/>
-      <c r="E3" s="175"/>
+      <c r="B3" s="174"/>
+      <c r="C3" s="178"/>
+      <c r="D3" s="178"/>
+      <c r="E3" s="176"/>
       <c r="F3" s="98" t="s">
         <v>114</v>
       </c>
@@ -9222,30 +9252,30 @@
       <c r="E1" s="108"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="172" t="s">
+      <c r="B2" s="173" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="176" t="s">
+      <c r="C2" s="177" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="176" t="s">
+      <c r="D2" s="177" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="174" t="s">
+      <c r="E2" s="175" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="170" t="s">
+      <c r="F2" s="171" t="s">
         <v>259</v>
       </c>
-      <c r="G2" s="170"/>
-      <c r="H2" s="170"/>
-      <c r="I2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="172"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="173"/>
-      <c r="C3" s="177"/>
-      <c r="D3" s="177"/>
-      <c r="E3" s="175"/>
+      <c r="B3" s="174"/>
+      <c r="C3" s="178"/>
+      <c r="D3" s="178"/>
+      <c r="E3" s="176"/>
       <c r="F3" s="98" t="s">
         <v>280</v>
       </c>
@@ -9539,10 +9569,10 @@
         <v>260</v>
       </c>
       <c r="H17" s="156" t="s">
+        <v>315</v>
+      </c>
+      <c r="I17" s="137" t="s">
         <v>316</v>
-      </c>
-      <c r="I17" s="137" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="18" spans="2:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -9647,30 +9677,30 @@
       <c r="E1" s="108"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="172" t="s">
+      <c r="B2" s="173" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="176" t="s">
+      <c r="C2" s="177" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="176" t="s">
+      <c r="D2" s="177" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="174" t="s">
+      <c r="E2" s="175" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="170" t="s">
+      <c r="F2" s="171" t="s">
         <v>279</v>
       </c>
-      <c r="G2" s="170"/>
-      <c r="H2" s="170"/>
-      <c r="I2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="172"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="173"/>
-      <c r="C3" s="177"/>
-      <c r="D3" s="177"/>
-      <c r="E3" s="175"/>
+      <c r="B3" s="174"/>
+      <c r="C3" s="178"/>
+      <c r="D3" s="178"/>
+      <c r="E3" s="176"/>
       <c r="F3" s="98" t="s">
         <v>300</v>
       </c>
@@ -9866,12 +9896,14 @@
         <v>263</v>
       </c>
       <c r="F13" s="134" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G13" s="158" t="s">
-        <v>323</v>
-      </c>
-      <c r="H13" s="134"/>
+        <v>329</v>
+      </c>
+      <c r="H13" s="106" t="s">
+        <v>327</v>
+      </c>
       <c r="I13" s="135"/>
     </row>
     <row r="14" spans="1:9" ht="270" x14ac:dyDescent="0.3">
@@ -9891,13 +9923,13 @@
         <v>312</v>
       </c>
       <c r="G14" s="158" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="H14" s="106" t="s">
+        <v>331</v>
+      </c>
+      <c r="I14" s="123" t="s">
         <v>314</v>
-      </c>
-      <c r="I14" s="123" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -9916,11 +9948,15 @@
       <c r="F15" s="134" t="s">
         <v>306</v>
       </c>
-      <c r="G15" s="159"/>
-      <c r="H15" s="138"/>
+      <c r="G15" s="159" t="s">
+        <v>330</v>
+      </c>
+      <c r="H15" s="179" t="s">
+        <v>332</v>
+      </c>
       <c r="I15" s="135"/>
     </row>
-    <row r="16" spans="1:9" ht="108" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="175.5" x14ac:dyDescent="0.3">
       <c r="B16" s="132" t="s">
         <v>85</v>
       </c>
@@ -9934,14 +9970,12 @@
         <v>265</v>
       </c>
       <c r="F16" s="134" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G16" s="158" t="s">
-        <v>325</v>
-      </c>
-      <c r="H16" s="106" t="s">
-        <v>321</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="H16" s="106"/>
       <c r="I16" s="135"/>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -9958,10 +9992,10 @@
         <v>308</v>
       </c>
       <c r="F17" s="156" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G17" s="120" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H17" s="138"/>
       <c r="I17" s="137"/>
@@ -10015,7 +10049,7 @@
         <v>261</v>
       </c>
       <c r="F20" s="162" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G20" s="148"/>
       <c r="H20" s="149"/>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="334">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2486,11 +2486,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[임제훈 사원]
-- R로직 튜닝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -2863,53 +2858,6 @@
   </si>
   <si>
     <t>- 이슈 없음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- 기구팀 승인도 승인 요청 (11/03)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- NX5e PCB 제작사양서 배포 (~11/04)
-  : Power 90% 3499 → 3543 변경 후 전달 완료, 체크썸 변경
-- 공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (~11/05)
-  : 일정 조율에 대한 사유 작성하여 재회신 예정, 조건부 승인으로 가면 된다고 함
-  : 사이버 보안팀에 시료 제출하여 선 공정 검사 진행 여부는 확인 해본다고 함
-- ESIR 계획서 등록 완료 (11/05)
-- 최신 승인도 확인 (~11/06)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- 사이버 보안 항목 QV와 비교 및 리스트업 후 공조시스템설계팀 회신 (11/04)
-  : ES95489-21 빼는 것은 안됨. 업데이트에 해당하는 항목 N/A로 하자고 회신 받음
-  : 공조시스템설계팀 방침으로 인해 SVm 사이버 보안 적용 진행, 업데이트 불가능
-[김진겸 사원]
-- 설계변경 시 ERP 등록 준비(11/06)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- 열에너지차량시험팀 주관 BJ1 항속형 실차 검증 진행 (11/10)
-  : 최대난방평가 재현 결과 플로어 모드 첫 진입 시 좌우 온도 편차 최대 4.5℃
-  : 이후 모든 단계가 끝날 때 좌우 온도 편차 1℃ 내 수렴
-  : 온도 제어성 정합 평가 플로어 8단, 토출부 도어 Dr 4.65V, Ps 4.66V 강제 제어
-  : Duty 90% 강제 제어 결과 좌우 온도 편차 3.75℃
-  : Duty 50% ~ 80% 강제 제어 결과 60% 때 좌우 온도 편차 1.14℃, 그 외 1℃ 내
-- PTC 벤치 테스트 한온에서 진행 (11/12)
-  : BJ RHD HVAC 수령 예정
-- 열에너지차량시험 측 일정 최종 정리 공유
-  : 11/10(월) BJ Proto 20호차 실차 튜닝 요청
-  : 11/14(금) BJ AP2 차량 PTC 개선품 리워크 후 확인 (남양연구소 B1-7)
-  : 11/18(화) ~ 11/20(목) 리워크 완료 AP2 차량 국내 트립 진행
-  : 11/25(화) ~ 11/26(수) 실차 난방 평가 진행
-- 공조 로컬 CAN 심의회 진행 (11/13)
-  : SVm, BJ, NX5e, MX5a, HE1i 대상
-[김진겸 사원]
-- 열에너지차량시험팀 측에서 11/10(월) 챔버 확보
-  : 자동차 측에서 실차 튜닝 요청, 참석 인원 선정 필요</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2969,8 +2917,783 @@
   </si>
   <si>
     <t>[임제훈 사원]
-- 사이버 보안 적용 단계, 피지컬 ID, 사이버보안품질팀 담당자 문의 (11/11)
-  : 김동환 연구원 유선 문의 완료, 빠르게 파악 후 회신 한다고 함.
+- R로직 튜닝
+  : 11/17 ~ 11/21 야간 칼로리 사용 예약, 11/24 ~ 11/28 주간 칼로리 사용 예약
+  : 11/17 ~ 11/21 주간 사용은 이제창 사원에게 사용 여부 확인 필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사이버 보안 항목 QV와 비교 및 리스트업 후 공조시스템설계팀 회신 (11/04)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ES95489-21 빼는 것은 안됨. 업데이트에 해당하는 항목 N/A로 하자고 회신 받음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공조시스템설계팀 방침으로 인해 SVm 사이버 보안 적용 진행, 업데이트 불가능</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+[김진겸 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>설계변경 시 ERP 등록 준비(11/06)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사이버 보안 M단계 적용으로 김응영 책임에게 유선 확인 완료 (11/07)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공정 감사 5EA 건에 대해서는 공정 감사 어디서 하는지 모른다고 함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>기아샤시시스템품질팀 김제일 매니저 사이버보안 납품건 확인 완료 (11/10)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>QV와 동일하게 LP2 5EA 납품, M단계 전량 사이버 보안 적용 진행 요청 받음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사이버 보안으로 바뀐 이력 김제일 매니저 공유 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>설계 변경 결재 상신 완료 (11/10)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>기구팀 문의 결과, QV, SVm, BJ 담당자 전부 똑같다고 함. 결재 라인 똑같이 예정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>설계 변경 문서 작성 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사이버 보안 미적용 SW, 적용 SW 동작 확인 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 완료 (11/10)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- 공조 로컬 CAN 심의회 진행 (11/13)
+  : SVm, BJ, NX5e, MX5a, HE1i 대상</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>열에너지차량시험팀 주관 BJ1 항속형 실차 검증 진행 (11/10)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>최대난방평가 재현 결과 플로어 모드 첫 진입 시 좌우 온도 편차 최대 4.5℃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이후 모든 단계가 끝날 때 좌우 온도 편차 1℃ 내 수렴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>온도 제어성 정합 평가 플로어 8단, 토출부 도어 Dr 4.65V, Ps 4.66V 강제 제어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Duty 90% 강제 제어 결과 좌우 온도 편차 3.75℃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Duty 50% ~ 80% 강제 제어 결과 60% 때 좌우 온도 편차 1.14℃, 그 외 1℃ 내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- PTC 벤치 테스트 한온에서 진행 (11/12)
+  : BJ RHD HVAC 수령 예정
+- 열에너지차량시험 측 일정 최종 정리 공유
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>11/10(월) BJ Proto 20호차 실차 튜닝 요청</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : 11/14(금) BJ AP2 차량 PTC 개선품 리워크 후 확인 (남양연구소 B1-7)
+  : 11/18(화) ~ 11/20(목) 리워크 완료 AP2 차량 국내 트립 진행
+  : 11/25(화) ~ 11/26(수) 실차 난방 평가 진행
+- 공조 로컬 CAN 심의회 진행 (11/13)
+  : SVm, BJ, NX5e, MX5a, HE1i 대상
+[김진겸 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>열에너지차량시험팀 측에서 11/10(월) 챔버 확보</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>자동차 측에서 실차 튜닝 요청, 참석 인원 선정 필요</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- LHD, RHD R로직 튜닝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NX5e PCB 제작사양서 배포 (~11/04)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Power 90% 3499 → 3543 변경 후 전달 완료, 체크썸 변경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (~11/05)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>일정 조율에 대한 사유 작성하여 재회신 예정, 조건부 승인으로 가면 된다고 함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사이버 보안팀에 시료 제출하여 선 공정 검사 진행 여부는 확인 해본다고 함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ESIR 계획서 등록 완료 (11/05)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- 최신 승인도 확인 (~11/06)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 최신 승인도 확인 (~11/20)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사이버 보안 적용 단계, 피지컬 ID, 사이버보안품질팀 담당자 문의 (11/11)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>김동환 연구원 유선 문의 완료, 빠르게 파악 후 회신 한다고 함.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
   : 12일 오전 까지 회신 없으면 12일 오후 정재근 책임 연구원 연락 예정
 - 공조 로컬 CAN 심의회 진행 (11/13)
   : SVm, BJ, NX5e, MX5a, HE1i 대상
@@ -2981,27 +3704,33 @@
   : ES95480-00 작성 완료, 결재본 첨부 필요
   : ES95489-21 피지컬 ID 및 보안 키 생성 업무 연락 및 첨부 자료 필요
   : ES95489-24 실제 수행 자료 필요</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>기구팀 승인도 승인 요청 (11/03)</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[임제훈 사원]
-- 사이버 보안 M단계 적용으로 김응영 책임에게 유선 확인 완료 (11/07)
-  : 공정 감사 5EA 건에 대해서는 공정 감사 어디서 하는지 모른다고 함
-- 기아샤시시스템품질팀 김제일 매니저 사이버보안 납품건 확인 완료 (11/10)
-  : QV와 동일하게 LP2 5EA 납품, M단계 전량 사이버 보안 적용 진행 요청 받음
-  : 사이버 보안으로 바뀐 이력 김제일 매니저 공유 완료
-- 설계 변경 결재 상신 완료 (11/10)
-  : 기구팀 문의 결과, QV, SVm, BJ 담당자 전부 똑같다고 함. 결재 라인 똑같이 예정
-  : 설계 변경 문서 작성 완료
-  : 사이버 보안 미적용 SW, 적용 SW 동작 확인 완료
-- 제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 완료 (11/10)
-- 공조 로컬 CAN 심의회 진행 (11/13)
-  : SVm, BJ, NX5e, MX5a, HE1i 대상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- R로직 튜닝</t>
+- 최소 작동 전압 범위 수정 후, EV HTR 개발팀 김민수 선임에게 전달
+  : 0℃, -30℃ 환경에서 QV Air PTC와 160V, 170V 출력 비교 필요로 인한 요청
+  : 다른 작업 먼저 한다고 함, 추후 진행 예정이고 일정 미정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3011,14 +3740,19 @@
   : 11/18(화) ~ 11/20(목) 리워크 완료 AP2 차량 국내 트립 진행
 - LHD, RHD R로직 튜닝
   : 11/17 ~ 11/21 야간 칼로리 사용 예약, 11/24 ~ 11/28 주간 칼로리 사용 예약
-  : 11/17 ~ 11/21 주간 사용은 이제창 사원에게 사용 여부 확인 필요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- R로직 튜닝
-  : 11/17 ~ 11/21 야간 칼로리 사용 예약, 11/24 ~ 11/28 주간 칼로리 사용 예약
-  : 11/17 ~ 11/21 주간 사용은 이제창 사원에게 사용 여부 확인 필요</t>
+  : 11/17 ~ 11/21 주간 사용은 이제창 사원에게 사용 여부 확인 필요
+- 한온 BJ LP#2 Event 대응 관련 E/O Cut 공유 요청 (~11/14)
+  : 한온 납품 요청일에 어떠한 일이 있어도 납품이 완료되어야 한다고 함
+  : 12/15까지 검사 완료 기준으로 납품이 되어야 함
+  : 검사 완료 요구일 12/15, 이후 납품건은 항공 발송 필요
+  : 너무 일찍 공급되면 분실 위험이 있어 12/5 ~ 12/15간 납품 요망
+  : PTC HTR LINEAR HV(EP2H0BJEAA02), Qty 100
+  : PTC HTR LINEAR HV(EP2H0BJELA01), Qty 50
+  : 강명준 사원 말로는 설계 변경 관련 이라고 함
+  : 기구 설계 변경 때 묻어가도 된다고는 했지만, 확인 필요, 일정 확인 필요
+  : Sample 생성 및 체크썸 생성 후 R로직 튜닝, 성능 및 기능 점검 필수
+  : SW 점검 관련 하여 일정 확인 필수, 칼로리 사용 예약 필수
+- BJ1 사이버 보안 적용 단계 및 납품건 확인 필요 (~11/20)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4892,6 +5626,9 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4936,9 +5673,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -5605,90 +6339,90 @@
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="164" t="s">
+      <c r="B2" s="165" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="166" t="s">
+      <c r="C2" s="167" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="166" t="s">
+      <c r="D2" s="167" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="170">
+      <c r="E2" s="171">
         <v>23</v>
       </c>
-      <c r="F2" s="168"/>
-      <c r="G2" s="168"/>
-      <c r="H2" s="168"/>
-      <c r="I2" s="168"/>
-      <c r="J2" s="168"/>
-      <c r="K2" s="168"/>
-      <c r="L2" s="168"/>
-      <c r="M2" s="168"/>
-      <c r="N2" s="168"/>
-      <c r="O2" s="168"/>
-      <c r="P2" s="168"/>
-      <c r="Q2" s="168">
+      <c r="F2" s="169"/>
+      <c r="G2" s="169"/>
+      <c r="H2" s="169"/>
+      <c r="I2" s="169"/>
+      <c r="J2" s="169"/>
+      <c r="K2" s="169"/>
+      <c r="L2" s="169"/>
+      <c r="M2" s="169"/>
+      <c r="N2" s="169"/>
+      <c r="O2" s="169"/>
+      <c r="P2" s="169"/>
+      <c r="Q2" s="169">
         <v>24</v>
       </c>
-      <c r="R2" s="168"/>
-      <c r="S2" s="168"/>
-      <c r="T2" s="168"/>
-      <c r="U2" s="168"/>
-      <c r="V2" s="168"/>
-      <c r="W2" s="168"/>
-      <c r="X2" s="168"/>
-      <c r="Y2" s="168"/>
-      <c r="Z2" s="168"/>
-      <c r="AA2" s="168"/>
-      <c r="AB2" s="168"/>
-      <c r="AC2" s="168">
+      <c r="R2" s="169"/>
+      <c r="S2" s="169"/>
+      <c r="T2" s="169"/>
+      <c r="U2" s="169"/>
+      <c r="V2" s="169"/>
+      <c r="W2" s="169"/>
+      <c r="X2" s="169"/>
+      <c r="Y2" s="169"/>
+      <c r="Z2" s="169"/>
+      <c r="AA2" s="169"/>
+      <c r="AB2" s="169"/>
+      <c r="AC2" s="169">
         <v>25</v>
       </c>
-      <c r="AD2" s="168"/>
-      <c r="AE2" s="168"/>
-      <c r="AF2" s="168"/>
-      <c r="AG2" s="168"/>
-      <c r="AH2" s="168"/>
-      <c r="AI2" s="168"/>
-      <c r="AJ2" s="168"/>
-      <c r="AK2" s="168"/>
-      <c r="AL2" s="168"/>
-      <c r="AM2" s="168"/>
-      <c r="AN2" s="168"/>
-      <c r="AO2" s="168">
+      <c r="AD2" s="169"/>
+      <c r="AE2" s="169"/>
+      <c r="AF2" s="169"/>
+      <c r="AG2" s="169"/>
+      <c r="AH2" s="169"/>
+      <c r="AI2" s="169"/>
+      <c r="AJ2" s="169"/>
+      <c r="AK2" s="169"/>
+      <c r="AL2" s="169"/>
+      <c r="AM2" s="169"/>
+      <c r="AN2" s="169"/>
+      <c r="AO2" s="169">
         <v>26</v>
       </c>
-      <c r="AP2" s="168"/>
-      <c r="AQ2" s="168"/>
-      <c r="AR2" s="168"/>
-      <c r="AS2" s="168"/>
-      <c r="AT2" s="168"/>
-      <c r="AU2" s="168"/>
-      <c r="AV2" s="168"/>
-      <c r="AW2" s="168"/>
-      <c r="AX2" s="168"/>
-      <c r="AY2" s="168"/>
-      <c r="AZ2" s="169"/>
-      <c r="BA2" s="168">
+      <c r="AP2" s="169"/>
+      <c r="AQ2" s="169"/>
+      <c r="AR2" s="169"/>
+      <c r="AS2" s="169"/>
+      <c r="AT2" s="169"/>
+      <c r="AU2" s="169"/>
+      <c r="AV2" s="169"/>
+      <c r="AW2" s="169"/>
+      <c r="AX2" s="169"/>
+      <c r="AY2" s="169"/>
+      <c r="AZ2" s="170"/>
+      <c r="BA2" s="169">
         <v>27</v>
       </c>
-      <c r="BB2" s="168"/>
-      <c r="BC2" s="168"/>
-      <c r="BD2" s="168"/>
-      <c r="BE2" s="168"/>
-      <c r="BF2" s="168"/>
-      <c r="BG2" s="168"/>
-      <c r="BH2" s="168"/>
-      <c r="BI2" s="168"/>
-      <c r="BJ2" s="168"/>
-      <c r="BK2" s="168"/>
-      <c r="BL2" s="169"/>
+      <c r="BB2" s="169"/>
+      <c r="BC2" s="169"/>
+      <c r="BD2" s="169"/>
+      <c r="BE2" s="169"/>
+      <c r="BF2" s="169"/>
+      <c r="BG2" s="169"/>
+      <c r="BH2" s="169"/>
+      <c r="BI2" s="169"/>
+      <c r="BJ2" s="169"/>
+      <c r="BK2" s="169"/>
+      <c r="BL2" s="170"/>
     </row>
     <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="165"/>
-      <c r="C3" s="167"/>
-      <c r="D3" s="167"/>
+      <c r="B3" s="166"/>
+      <c r="C3" s="168"/>
+      <c r="D3" s="168"/>
       <c r="E3" s="22">
         <v>1</v>
       </c>
@@ -6429,7 +7163,7 @@
         <v>77</v>
       </c>
       <c r="D11" s="161" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="7"/>
@@ -6512,7 +7246,7 @@
         <v>105</v>
       </c>
       <c r="D12" s="161" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="7"/>
@@ -6593,7 +7327,7 @@
         <v>82</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="7"/>
@@ -7030,7 +7764,7 @@
         <v>258</v>
       </c>
       <c r="D18" s="161" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E18" s="64"/>
       <c r="F18" s="65"/>
@@ -7429,7 +8163,7 @@
         <v>104</v>
       </c>
       <c r="D23" s="163" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E23" s="49"/>
       <c r="F23" s="50"/>
@@ -7669,39 +8403,39 @@
       <c r="E1" s="108"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="173" t="s">
+      <c r="B2" s="174" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="177" t="s">
+      <c r="C2" s="178" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="177" t="s">
+      <c r="D2" s="178" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="175" t="s">
+      <c r="E2" s="176" t="s">
         <v>126</v>
       </c>
       <c r="F2" s="97" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="171" t="s">
+      <c r="G2" s="172" t="s">
         <v>113</v>
       </c>
-      <c r="H2" s="171"/>
-      <c r="I2" s="171"/>
-      <c r="J2" s="172"/>
-      <c r="K2" s="171" t="s">
+      <c r="H2" s="172"/>
+      <c r="I2" s="172"/>
+      <c r="J2" s="173"/>
+      <c r="K2" s="172" t="s">
         <v>182</v>
       </c>
-      <c r="L2" s="171"/>
-      <c r="M2" s="171"/>
-      <c r="N2" s="172"/>
+      <c r="L2" s="172"/>
+      <c r="M2" s="172"/>
+      <c r="N2" s="173"/>
     </row>
     <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="174"/>
-      <c r="C3" s="178"/>
-      <c r="D3" s="178"/>
-      <c r="E3" s="176"/>
+      <c r="B3" s="175"/>
+      <c r="C3" s="179"/>
+      <c r="D3" s="179"/>
+      <c r="E3" s="177"/>
       <c r="F3" s="98" t="s">
         <v>111</v>
       </c>
@@ -8444,30 +9178,30 @@
       <c r="E1" s="108"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="173" t="s">
+      <c r="B2" s="174" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="177" t="s">
+      <c r="C2" s="178" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="177" t="s">
+      <c r="D2" s="178" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="175" t="s">
+      <c r="E2" s="176" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="171" t="s">
+      <c r="F2" s="172" t="s">
         <v>182</v>
       </c>
-      <c r="G2" s="171"/>
-      <c r="H2" s="171"/>
-      <c r="I2" s="172"/>
+      <c r="G2" s="172"/>
+      <c r="H2" s="172"/>
+      <c r="I2" s="173"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="174"/>
-      <c r="C3" s="178"/>
-      <c r="D3" s="178"/>
-      <c r="E3" s="176"/>
+      <c r="B3" s="175"/>
+      <c r="C3" s="179"/>
+      <c r="D3" s="179"/>
+      <c r="E3" s="177"/>
       <c r="F3" s="98" t="s">
         <v>114</v>
       </c>
@@ -8845,30 +9579,30 @@
       <c r="E1" s="108"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="173" t="s">
+      <c r="B2" s="174" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="177" t="s">
+      <c r="C2" s="178" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="177" t="s">
+      <c r="D2" s="178" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="175" t="s">
+      <c r="E2" s="176" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="171" t="s">
+      <c r="F2" s="172" t="s">
         <v>227</v>
       </c>
-      <c r="G2" s="171"/>
-      <c r="H2" s="171"/>
-      <c r="I2" s="172"/>
+      <c r="G2" s="172"/>
+      <c r="H2" s="172"/>
+      <c r="I2" s="173"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="174"/>
-      <c r="C3" s="178"/>
-      <c r="D3" s="178"/>
-      <c r="E3" s="176"/>
+      <c r="B3" s="175"/>
+      <c r="C3" s="179"/>
+      <c r="D3" s="179"/>
+      <c r="E3" s="177"/>
       <c r="F3" s="98" t="s">
         <v>114</v>
       </c>
@@ -9252,30 +9986,30 @@
       <c r="E1" s="108"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="173" t="s">
+      <c r="B2" s="174" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="177" t="s">
+      <c r="C2" s="178" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="177" t="s">
+      <c r="D2" s="178" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="175" t="s">
+      <c r="E2" s="176" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="171" t="s">
+      <c r="F2" s="172" t="s">
         <v>259</v>
       </c>
-      <c r="G2" s="171"/>
-      <c r="H2" s="171"/>
-      <c r="I2" s="172"/>
+      <c r="G2" s="172"/>
+      <c r="H2" s="172"/>
+      <c r="I2" s="173"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="174"/>
-      <c r="C3" s="178"/>
-      <c r="D3" s="178"/>
-      <c r="E3" s="176"/>
+      <c r="B3" s="175"/>
+      <c r="C3" s="179"/>
+      <c r="D3" s="179"/>
+      <c r="E3" s="177"/>
       <c r="F3" s="98" t="s">
         <v>280</v>
       </c>
@@ -9480,7 +10214,7 @@
         <v>288</v>
       </c>
       <c r="I13" s="135" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -9526,7 +10260,7 @@
         <v>286</v>
       </c>
       <c r="I15" s="160" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="228.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9548,7 +10282,7 @@
         <v>290</v>
       </c>
       <c r="I16" s="135" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -9569,10 +10303,10 @@
         <v>260</v>
       </c>
       <c r="H17" s="156" t="s">
+        <v>314</v>
+      </c>
+      <c r="I17" s="137" t="s">
         <v>315</v>
-      </c>
-      <c r="I17" s="137" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="18" spans="2:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -9677,30 +10411,30 @@
       <c r="E1" s="108"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="173" t="s">
+      <c r="B2" s="174" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="177" t="s">
+      <c r="C2" s="178" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="177" t="s">
+      <c r="D2" s="178" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="175" t="s">
+      <c r="E2" s="176" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="171" t="s">
+      <c r="F2" s="172" t="s">
         <v>279</v>
       </c>
-      <c r="G2" s="171"/>
-      <c r="H2" s="171"/>
-      <c r="I2" s="172"/>
+      <c r="G2" s="172"/>
+      <c r="H2" s="172"/>
+      <c r="I2" s="173"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="174"/>
-      <c r="C3" s="178"/>
-      <c r="D3" s="178"/>
-      <c r="E3" s="176"/>
+      <c r="B3" s="175"/>
+      <c r="C3" s="179"/>
+      <c r="D3" s="179"/>
+      <c r="E3" s="177"/>
       <c r="F3" s="98" t="s">
         <v>300</v>
       </c>
@@ -9784,10 +10518,10 @@
         <v>162</v>
       </c>
       <c r="F7" s="124" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G7" s="106" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H7" s="90"/>
       <c r="I7" s="94"/>
@@ -9896,13 +10630,13 @@
         <v>263</v>
       </c>
       <c r="F13" s="134" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="G13" s="158" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="H13" s="106" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="I13" s="135"/>
     </row>
@@ -9920,16 +10654,16 @@
         <v>264</v>
       </c>
       <c r="F14" s="134" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G14" s="158" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H14" s="106" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I14" s="123" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -9946,13 +10680,13 @@
         <v>262</v>
       </c>
       <c r="F15" s="134" t="s">
-        <v>306</v>
-      </c>
-      <c r="G15" s="159" t="s">
-        <v>330</v>
-      </c>
-      <c r="H15" s="179" t="s">
-        <v>332</v>
+        <v>327</v>
+      </c>
+      <c r="G15" s="134" t="s">
+        <v>327</v>
+      </c>
+      <c r="H15" s="164" t="s">
+        <v>323</v>
       </c>
       <c r="I15" s="135"/>
     </row>
@@ -9970,12 +10704,14 @@
         <v>265</v>
       </c>
       <c r="F16" s="134" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="G16" s="158" t="s">
-        <v>328</v>
-      </c>
-      <c r="H16" s="106"/>
+        <v>330</v>
+      </c>
+      <c r="H16" s="158" t="s">
+        <v>329</v>
+      </c>
       <c r="I16" s="135"/>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -9989,13 +10725,13 @@
         <v>178</v>
       </c>
       <c r="E17" s="114" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F17" s="156" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="G17" s="120" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="H17" s="138"/>
       <c r="I17" s="137"/>
@@ -10032,7 +10768,9 @@
       <c r="F19" s="134" t="s">
         <v>289</v>
       </c>
-      <c r="G19" s="159"/>
+      <c r="G19" s="159" t="s">
+        <v>332</v>
+      </c>
       <c r="I19" s="94"/>
     </row>
     <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -10049,7 +10787,7 @@
         <v>261</v>
       </c>
       <c r="F20" s="162" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G20" s="148"/>
       <c r="H20" s="149"/>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -2916,13 +2916,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[임제훈 사원]
-- R로직 튜닝
-  : 11/17 ~ 11/21 야간 칼로리 사용 예약, 11/24 ~ 11/28 주간 칼로리 사용 예약
-  : 11/17 ~ 11/21 주간 사용은 이제창 사원에게 사용 여부 확인 필요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">[임제훈 사원]
 - </t>
@@ -3636,11 +3629,6 @@
       <t xml:space="preserve">
 - 최신 승인도 확인 (~11/06)</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- 최신 승인도 확인 (~11/20)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3735,12 +3723,24 @@
   </si>
   <si>
     <t>[임제훈 사원]
+- TC 변경 관련 명확하게 확인 (~11/20)
+- 최신 승인도 확인 (~11/20)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- LHD, RHD R로직 튜닝
+  : 11/17 ~ 11/19 신뢰성팀 주간 사용, 11/20 ~ 11/21 기구 개발팀 주간 사용
+  : 11/17 ~ 11/21 야간 칼로리 사용 예약 완료
+  : 11/24 ~ 11/28 주,야 칼로리 사용 예약 완료
+  : 12/01 ~ 12/05 야간 칼로리 사용 예약 완료, 신뢰성팀 주간 사용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
 - 열에너지차량시험 측 일정 최종 정리 공유
   : 11/14(금) BJ AP2 차량 PTC 개선품 리워크 후 확인 (남양연구소 B1-7)
   : 11/18(화) ~ 11/20(목) 리워크 완료 AP2 차량 국내 트립 진행
-- LHD, RHD R로직 튜닝
-  : 11/17 ~ 11/21 야간 칼로리 사용 예약, 11/24 ~ 11/28 주간 칼로리 사용 예약
-  : 11/17 ~ 11/21 주간 사용은 이제창 사원에게 사용 여부 확인 필요
 - 한온 BJ LP#2 Event 대응 관련 E/O Cut 공유 요청 (~11/14)
   : 한온 납품 요청일에 어떠한 일이 있어도 납품이 완료되어야 한다고 함
   : 12/15까지 검사 완료 기준으로 납품이 되어야 함
@@ -3749,10 +3749,15 @@
   : PTC HTR LINEAR HV(EP2H0BJEAA02), Qty 100
   : PTC HTR LINEAR HV(EP2H0BJELA01), Qty 50
   : 강명준 사원 말로는 설계 변경 관련 이라고 함
-  : 기구 설계 변경 때 묻어가도 된다고는 했지만, 확인 필요, 일정 확인 필요
+  : 기구 설계 변경 때 묻어가도 된다고는 했지만, 확인 필요, 기구 일정 확인 필요
   : Sample 생성 및 체크썸 생성 후 R로직 튜닝, 성능 및 기능 점검 필수
-  : SW 점검 관련 하여 일정 확인 필수, 칼로리 사용 예약 필수
-- BJ1 사이버 보안 적용 단계 및 납품건 확인 필요 (~11/20)</t>
+  : SW 점검 관련 하여 납품 일정 확인 필수, 칼로리 사용 예약 필수
+- BJ1 사이버 보안 적용 단계 및 납품건 확인 필요 (~11/20)
+- LHD, RHD R로직 튜닝
+  : 11/17 ~ 11/19 신뢰성팀 주간 사용, 11/20 ~ 11/21 기구 개발팀 주간 사용
+  : 11/17 ~ 11/21 야간 칼로리 사용 예약 완료
+  : 11/24 ~ 11/28 주,야 칼로리 사용 예약 완료
+  : 12/01 ~ 12/05 야간 칼로리 사용 예약 완료, 신뢰성팀 주간 사용</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10630,17 +10635,17 @@
         <v>263</v>
       </c>
       <c r="F13" s="134" t="s">
+        <v>323</v>
+      </c>
+      <c r="G13" s="158" t="s">
         <v>324</v>
-      </c>
-      <c r="G13" s="158" t="s">
-        <v>325</v>
       </c>
       <c r="H13" s="106" t="s">
         <v>322</v>
       </c>
       <c r="I13" s="135"/>
     </row>
-    <row r="14" spans="1:9" ht="270" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="283.5" x14ac:dyDescent="0.3">
       <c r="B14" s="132" t="s">
         <v>73</v>
       </c>
@@ -10657,7 +10662,7 @@
         <v>311</v>
       </c>
       <c r="G14" s="158" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H14" s="106" t="s">
         <v>333</v>
@@ -10666,7 +10671,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="81" x14ac:dyDescent="0.3">
       <c r="B15" s="132" t="s">
         <v>55</v>
       </c>
@@ -10680,13 +10685,13 @@
         <v>262</v>
       </c>
       <c r="F15" s="134" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G15" s="134" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H15" s="164" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="I15" s="135"/>
     </row>
@@ -10704,13 +10709,13 @@
         <v>265</v>
       </c>
       <c r="F16" s="134" t="s">
+        <v>327</v>
+      </c>
+      <c r="G16" s="158" t="s">
         <v>328</v>
       </c>
-      <c r="G16" s="158" t="s">
-        <v>330</v>
-      </c>
       <c r="H16" s="158" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I16" s="135"/>
     </row>
@@ -10728,7 +10733,7 @@
         <v>307</v>
       </c>
       <c r="F17" s="156" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G17" s="120" t="s">
         <v>317</v>
@@ -10769,7 +10774,7 @@
         <v>289</v>
       </c>
       <c r="G19" s="159" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="I19" s="94"/>
     </row>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -2813,12 +2813,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[임제훈 사원]
-- 열에너지차량시험 측 일정 최종 정리 공유
-  : 11/25(화) ~ 11/26(수) 실차 난방 평가 진행</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">[임제훈 사원]
 - </t>
@@ -2906,16 +2900,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[임제훈 사원]
-- 기아샤시시스템품질팀 평택 공장 방문 (11/14)
-  : 11월 정기 협의체 회의는 평택 공장 방문 점검으로 대체
-  : 정기 협의체 진행 후 요청 자료에 대한 리뷰 (12월 정기 방문시 설명으로 협의)
-  : 평택 PTC 인라인 공정 확인요청 (SVm 조립공정과 그나마 유사한 공정 선정)
-  : SV 대비 SVm 서지 내성 관련 강건화 설계컨셉 설명 요청 (H/W)
-  : SVm PCB 실물 2ea 준비요청</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">[임제훈 사원]
 - </t>
@@ -3646,6 +3630,62 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
+      <t>기구팀 승인도 승인 요청 (11/03)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 최소 작동 전압 범위 수정 후, EV HTR 개발팀 김민수 선임에게 전달
+  : 0℃, -30℃ 환경에서 QV Air PTC와 160V, 170V 출력 비교 필요로 인한 요청
+  : 다른 작업 먼저 한다고 함, 추후 진행 예정이고 일정 미정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 기아샤시시스템품질팀 평택 공장 방문 (11/14)
+  : 11월 정기 협의체 회의는 평택 공장 방문 점검으로 대체
+  : 정기 협의체 진행 후 요청 자료에 대한 리뷰 (12월 정기 방문시 설명으로 협의)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 최대 난방 및 좌우 온도 편차 실차 검증
+  : 11/25(화) ~ 11/26(수) 실차 난방 평가 진행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. TC 160℃ → 165℃ 변경 확인 (11/19)
+  [ 안건 ]
+    - Stone TC 160℃ → 165℃ 변경
+  [ 진행 및 검토 ]
+    - 165℃ 변경 되었을 때 진행 일정
+     : R로직 튜닝
+     : 로직 및 기능 체크리스트 기반 검증 진행
+2. 승인도 수령 (11/19)
+  [ 안건 ]
+    - 변경점 업데이트된 승인도 수령
+  [ 진행 및 검토 ]
+    - RATED MAX, LINEAR MAX 성능 확인
+    - Core Temp 구간 변경 확인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>사이버 보안 적용 단계, 피지컬 ID, 사이버보안품질팀 담당자 문의 (11/11)</t>
     </r>
     <r>
@@ -3687,77 +3727,60 @@
   : SVm, BJ, NX5e, MX5a, HE1i 대상
 - ESIR 진행 (~11/15)
   : ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24
-  : ES95411-00 Unit Test, Integration Test 파라소프트 결과서 필요
-  : ES90700-00 작성 완료, 결재본 첨부 필요
-  : ES95480-00 작성 완료, 결재본 첨부 필요
-  : ES95489-21 피지컬 ID 및 보안 키 생성 업무 연락 및 첨부 자료 필요
-  : ES95489-24 실제 수행 자료 필요</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">[임제훈 사원]
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>기구팀 승인도 승인 요청 (11/03)</t>
+  : ES95411-00 (95%, ~11/21)
+  : ES90700-00 (50%, ~11/21)
+  : ES95480-00 (50%, ~11/21)
+  : ES95489-21 (95%, ~11/14)
+  : ES95489-24 (100%)</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[임제훈 사원]
-- 최소 작동 전압 범위 수정 후, EV HTR 개발팀 김민수 선임에게 전달
-  : 0℃, -30℃ 환경에서 QV Air PTC와 160V, 170V 출력 비교 필요로 인한 요청
-  : 다른 작업 먼저 한다고 함, 추후 진행 예정이고 일정 미정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- TC 변경 관련 명확하게 확인 (~11/20)
-- 최신 승인도 확인 (~11/20)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- LHD, RHD R로직 튜닝
-  : 11/17 ~ 11/19 신뢰성팀 주간 사용, 11/20 ~ 11/21 기구 개발팀 주간 사용
-  : 11/17 ~ 11/21 야간 칼로리 사용 예약 완료
-  : 11/24 ~ 11/28 주,야 칼로리 사용 예약 완료
-  : 12/01 ~ 12/05 야간 칼로리 사용 예약 완료, 신뢰성팀 주간 사용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- 열에너지차량시험 측 일정 최종 정리 공유
+1. 최대 난방 및 좌우 온도 편차 실차 검증
   : 11/14(금) BJ AP2 차량 PTC 개선품 리워크 후 확인 (남양연구소 B1-7)
   : 11/18(화) ~ 11/20(목) 리워크 완료 AP2 차량 국내 트립 진행
-- 한온 BJ LP#2 Event 대응 관련 E/O Cut 공유 요청 (~11/14)
-  : 한온 납품 요청일에 어떠한 일이 있어도 납품이 완료되어야 한다고 함
-  : 12/15까지 검사 완료 기준으로 납품이 되어야 함
-  : 검사 완료 요구일 12/15, 이후 납품건은 항공 발송 필요
-  : 너무 일찍 공급되면 분실 위험이 있어 12/5 ~ 12/15간 납품 요망
-  : PTC HTR LINEAR HV(EP2H0BJEAA02), Qty 100
-  : PTC HTR LINEAR HV(EP2H0BJELA01), Qty 50
-  : 강명준 사원 말로는 설계 변경 관련 이라고 함
-  : 기구 설계 변경 때 묻어가도 된다고는 했지만, 확인 필요, 기구 일정 확인 필요
-  : Sample 생성 및 체크썸 생성 후 R로직 튜닝, 성능 및 기능 점검 필수
-  : SW 점검 관련 하여 납품 일정 확인 필수, 칼로리 사용 예약 필수
-- BJ1 사이버 보안 적용 단계 및 납품건 확인 필요 (~11/20)
-- LHD, RHD R로직 튜닝
-  : 11/17 ~ 11/19 신뢰성팀 주간 사용, 11/20 ~ 11/21 기구 개발팀 주간 사용
-  : 11/17 ~ 11/21 야간 칼로리 사용 예약 완료
-  : 11/24 ~ 11/28 주,야 칼로리 사용 예약 완료
-  : 12/01 ~ 12/05 야간 칼로리 사용 예약 완료, 신뢰성팀 주간 사용</t>
+2. 한온 BJ LP#2 Event 대응 (11/14)
+  [ 안건 ]
+    - LP2 Event 대응
+  [ 요청사항 ]
+    - 12/15까지 대전 한온 BJ1 150대 납품 완료
+  [ 진행 및 검토]
+    - BJ1 LP2 현대자동차 대일정 26. 4. 15 → 26. 5. 1. 변경
+     : LP2 일정 여유가 있는데, 납품 시기 너무 빠름, 재확인 필요
+    - 12/15 납품을 해야하는 경우
+     : PCB 생산 일정 확인 후, SW 배포 가능 일자 확인
+     : LHD, RHD R로직 튜닝, 체크리스트 기반 기능 및 성능 시험
+     : SW 설계 변경 진행
+3. BJ1 사이버 보안 적용 단계 및 납품건 확인 (11/17)
+  [ 진행 및 검토 ]
+    - 공조시스템설계팀, 품질팀 문의
+4. LHD, RHD R로직 튜닝 및 기능 점검
+  [ 안건 ]
+    - 설계 변경 진행을 위한 SW 점검
+  [ 진행 및 검토 ]
+    - 칼로리 사용 예약
+     : 11/17 ~ 11/21 야간 칼로리 사용 예약 완료
+     : 11/24 ~ 11/28 주간, 야간 칼로리 사용 예약 완료
+     : 12/01 ~ 12/05 야간 칼로리 사용 예약 완료
+    - LHD, RHD R로직 튜닝
+     : 김진겸 사원 일정 협의 후 진행
+    - 로직 및 기능 체크리스트 기반 검증 진행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. LHD, RHD R로직 튜닝 및 기능 점검
+  [ 안건 ]
+    - SW 점검
+  [ 진행 및 검토 ]
+    - 칼로리 사용 예약
+     : 11/17 ~ 11/21 야간 칼로리 사용 예약 완료
+     : 11/24 ~ 11/28 주간, 야간 칼로리 사용 예약 완료
+     : 12/01 ~ 12/05 야간 칼로리 사용 예약 완료
+    - LHD, RHD R로직 튜닝
+     : 김진겸 사원 일정 협의 후 진행
+    - 로직 및 기능 체크리스트 기반 검증 진행</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7168,7 +7191,7 @@
         <v>77</v>
       </c>
       <c r="D11" s="161" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="7"/>
@@ -7251,7 +7274,7 @@
         <v>105</v>
       </c>
       <c r="D12" s="161" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="7"/>
@@ -7332,7 +7355,7 @@
         <v>82</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="7"/>
@@ -7769,7 +7792,7 @@
         <v>258</v>
       </c>
       <c r="D18" s="161" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E18" s="64"/>
       <c r="F18" s="65"/>
@@ -8168,7 +8191,7 @@
         <v>104</v>
       </c>
       <c r="D23" s="163" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E23" s="49"/>
       <c r="F23" s="50"/>
@@ -10308,10 +10331,10 @@
         <v>260</v>
       </c>
       <c r="H17" s="156" t="s">
+        <v>313</v>
+      </c>
+      <c r="I17" s="137" t="s">
         <v>314</v>
-      </c>
-      <c r="I17" s="137" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="18" spans="2:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10635,17 +10658,17 @@
         <v>263</v>
       </c>
       <c r="F13" s="134" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G13" s="158" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H13" s="106" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="I13" s="135"/>
     </row>
-    <row r="14" spans="1:9" ht="283.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="405" x14ac:dyDescent="0.3">
       <c r="B14" s="132" t="s">
         <v>73</v>
       </c>
@@ -10662,16 +10685,16 @@
         <v>311</v>
       </c>
       <c r="G14" s="158" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H14" s="106" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I14" s="123" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="81" x14ac:dyDescent="0.3">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="162" x14ac:dyDescent="0.3">
       <c r="B15" s="132" t="s">
         <v>55</v>
       </c>
@@ -10685,17 +10708,17 @@
         <v>262</v>
       </c>
       <c r="F15" s="134" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G15" s="134" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H15" s="164" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="I15" s="135"/>
     </row>
-    <row r="16" spans="1:9" ht="175.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="189" x14ac:dyDescent="0.3">
       <c r="B16" s="132" t="s">
         <v>85</v>
       </c>
@@ -10709,13 +10732,13 @@
         <v>265</v>
       </c>
       <c r="F16" s="134" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G16" s="158" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="H16" s="158" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I16" s="135"/>
     </row>
@@ -10733,10 +10756,10 @@
         <v>307</v>
       </c>
       <c r="F17" s="156" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="G17" s="120" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H17" s="138"/>
       <c r="I17" s="137"/>
@@ -10774,7 +10797,7 @@
         <v>289</v>
       </c>
       <c r="G19" s="159" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="I19" s="94"/>
     </row>
@@ -10792,7 +10815,7 @@
         <v>261</v>
       </c>
       <c r="F20" s="162" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G20" s="148"/>
       <c r="H20" s="149"/>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -3672,70 +3672,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">[임제훈 사원]
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>사이버 보안 적용 단계, 피지컬 ID, 사이버보안품질팀 담당자 문의 (11/11)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>김동환 연구원 유선 문의 완료, 빠르게 파악 후 회신 한다고 함.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : 12일 오전 까지 회신 없으면 12일 오후 정재근 책임 연구원 연락 예정
-- 공조 로컬 CAN 심의회 진행 (11/13)
-  : SVm, BJ, NX5e, MX5a, HE1i 대상
-- ESIR 진행 (~11/15)
-  : ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24
-  : ES95411-00 (95%, ~11/21)
-  : ES90700-00 (50%, ~11/21)
-  : ES95480-00 (50%, ~11/21)
-  : ES95489-21 (95%, ~11/14)
-  : ES95489-24 (100%)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[임제훈 사원]
 1. 최대 난방 및 좌우 온도 편차 실차 검증
   : 11/14(금) BJ AP2 차량 PTC 개선품 리워크 후 확인 (남양연구소 B1-7)
@@ -3781,6 +3717,70 @@
     - LHD, RHD R로직 튜닝
      : 김진겸 사원 일정 협의 후 진행
     - 로직 및 기능 체크리스트 기반 검증 진행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사이버 보안 적용 단계, 피지컬 ID, 사이버보안품질팀 담당자 문의 (11/11)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>김동환 연구원 유선 문의 완료, 빠르게 파악 후 회신 한다고 함.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : 12일 오전 까지 회신 없으면 12일 오후 정재근 책임 연구원 연락 예정
+- 공조 로컬 CAN 심의회 진행 (11/13)
+  : SVm, BJ, NX5e, MX5a, HE1i 대상
+- ESIR 진행 (~11/15)
+  : ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24
+  : ES95411-00 (95%, ~11/21)
+  : ES90700-00 (50%, ~11/21)
+  : ES95480-00 (50%, ~11/21)
+  : ES95489-21 (100%)
+  : ES95489-24 (100%)</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10688,7 +10688,7 @@
         <v>323</v>
       </c>
       <c r="H14" s="106" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I14" s="123" t="s">
         <v>329</v>
@@ -10714,7 +10714,7 @@
         <v>324</v>
       </c>
       <c r="H15" s="164" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I15" s="135"/>
     </row>
@@ -10735,7 +10735,7 @@
         <v>325</v>
       </c>
       <c r="G16" s="158" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H16" s="158" t="s">
         <v>330</v>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -3240,226 +3240,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">[임제훈 사원]
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>열에너지차량시험팀 주관 BJ1 항속형 실차 검증 진행 (11/10)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>최대난방평가 재현 결과 플로어 모드 첫 진입 시 좌우 온도 편차 최대 4.5℃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>이후 모든 단계가 끝날 때 좌우 온도 편차 1℃ 내 수렴</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>온도 제어성 정합 평가 플로어 8단, 토출부 도어 Dr 4.65V, Ps 4.66V 강제 제어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Duty 90% 강제 제어 결과 좌우 온도 편차 3.75℃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Duty 50% ~ 80% 강제 제어 결과 60% 때 좌우 온도 편차 1.14℃, 그 외 1℃ 내</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- PTC 벤치 테스트 한온에서 진행 (11/12)
-  : BJ RHD HVAC 수령 예정
-- 열에너지차량시험 측 일정 최종 정리 공유
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>11/10(월) BJ Proto 20호차 실차 튜닝 요청</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : 11/14(금) BJ AP2 차량 PTC 개선품 리워크 후 확인 (남양연구소 B1-7)
-  : 11/18(화) ~ 11/20(목) 리워크 완료 AP2 차량 국내 트립 진행
-  : 11/25(화) ~ 11/26(수) 실차 난방 평가 진행
-- 공조 로컬 CAN 심의회 진행 (11/13)
-  : SVm, BJ, NX5e, MX5a, HE1i 대상
-[김진겸 사원]
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>열에너지차량시험팀 측에서 11/10(월) 챔버 확보</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>자동차 측에서 실차 튜닝 요청, 참석 인원 선정 필요</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[임제훈 사원]
 - LHD, RHD R로직 튜닝</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3646,12 +3426,6 @@
 - 기아샤시시스템품질팀 평택 공장 방문 (11/14)
   : 11월 정기 협의체 회의는 평택 공장 방문 점검으로 대체
   : 정기 협의체 진행 후 요청 자료에 대한 리뷰 (12월 정기 방문시 설명으로 협의)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- 최대 난방 및 좌우 온도 편차 실차 검증
-  : 11/25(화) ~ 11/26(수) 실차 난방 평가 진행</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3781,6 +3555,232 @@
   : ES95489-21 (100%)
   : ES95489-24 (100%)</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>열에너지차량시험팀 주관 BJ1 항속형 실차 검증 진행 (11/10)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>최대난방평가 재현 결과 플로어 모드 첫 진입 시 좌우 온도 편차 최대 4.5℃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이후 모든 단계가 끝날 때 좌우 온도 편차 1℃ 내 수렴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>온도 제어성 정합 평가 플로어 8단, 토출부 도어 Dr 4.65V, Ps 4.66V 강제 제어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Duty 90% 강제 제어 결과 좌우 온도 편차 3.75℃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Duty 50% ~ 80% 강제 제어 결과 60% 때 좌우 온도 편차 1.14℃, 그 외 1℃ 내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- PTC 벤치 테스트 한온에서 진행 (11/12)
+  : BJ RHD HVAC 수령 예정
+- 열에너지차량시험 측 일정 최종 정리 공유
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>11/10(월) BJ Proto 20호차 실차 튜닝 요청</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : 11/14(금) BJ AP2 차량 PTC 개선품 리워크 후 확인 (남양연구소 B1-7)
+  : 11/18(화) ~ 11/20(목) 리워크 완료 AP2 차량 국내 트립 진행
+  : 11/24(월) ~ 11/25(화) 실차 난방 평가 진행
+- 공조 로컬 CAN 심의회 진행 (11/13)
+  : SVm, BJ, NX5e, MX5a, HE1i 대상
+[김진겸 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>열에너지차량시험팀 측에서 11/10(월) 챔버 확보</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>자동차 측에서 실차 튜닝 요청, 참석 인원 선정 필요</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 최대 난방 및 좌우 온도 편차 실차 검증
+  : 11/24(월) ~ 11/25(화) 실차 난방 평가 진행</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10664,7 +10664,7 @@
         <v>322</v>
       </c>
       <c r="H13" s="106" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I13" s="135"/>
     </row>
@@ -10685,13 +10685,13 @@
         <v>311</v>
       </c>
       <c r="G14" s="158" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="H14" s="106" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="I14" s="123" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="162" x14ac:dyDescent="0.3">
@@ -10708,13 +10708,13 @@
         <v>262</v>
       </c>
       <c r="F15" s="134" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G15" s="134" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H15" s="164" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="I15" s="135"/>
     </row>
@@ -10732,13 +10732,13 @@
         <v>265</v>
       </c>
       <c r="F16" s="134" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G16" s="158" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H16" s="158" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="I16" s="135"/>
     </row>
@@ -10756,7 +10756,7 @@
         <v>307</v>
       </c>
       <c r="F17" s="156" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G17" s="120" t="s">
         <v>316</v>
@@ -10797,7 +10797,7 @@
         <v>289</v>
       </c>
       <c r="G19" s="159" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I19" s="94"/>
     </row>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -3733,7 +3733,7 @@
       <t xml:space="preserve">
   : 11/14(금) BJ AP2 차량 PTC 개선품 리워크 후 확인 (남양연구소 B1-7)
   : 11/18(화) ~ 11/20(목) 리워크 완료 AP2 차량 국내 트립 진행
-  : 11/24(월) ~ 11/25(화) 실차 난방 평가 진행
+  : 11/25(화) ~ 11/26(수) 실차 난방 평가 진행
 - 공조 로컬 CAN 심의회 진행 (11/13)
   : SVm, BJ, NX5e, MX5a, HE1i 대상
 [김진겸 사원]
@@ -3780,7 +3780,7 @@
   <si>
     <t>[임제훈 사원]
 - 최대 난방 및 좌우 온도 편차 실차 검증
-  : 11/24(월) ~ 11/25(화) 실차 난방 평가 진행</t>
+  : 11/25(화) ~ 11/26(수) 실차 난방 평가 진행</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -3430,13 +3430,320 @@
   </si>
   <si>
     <t>[임제훈 사원]
-1. TC 160℃ → 165℃ 변경 확인 (11/19)
+1. LHD, RHD R로직 튜닝 및 기능 점검
   [ 안건 ]
-    - Stone TC 160℃ → 165℃ 변경
+    - SW 점검
   [ 진행 및 검토 ]
-    - 165℃ 변경 되었을 때 진행 일정
-     : R로직 튜닝
-     : 로직 및 기능 체크리스트 기반 검증 진행
+    - 칼로리 사용 예약
+     : 11/17 ~ 11/21 야간 칼로리 사용 예약 완료
+     : 11/24 ~ 11/28 주간, 야간 칼로리 사용 예약 완료
+     : 12/01 ~ 12/05 야간 칼로리 사용 예약 완료
+    - LHD, RHD R로직 튜닝
+     : 김진겸 사원 일정 협의 후 진행
+    - 로직 및 기능 체크리스트 기반 검증 진행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사이버 보안 적용 단계, 피지컬 ID, 사이버보안품질팀 담당자 문의 (11/11)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>김동환 연구원 유선 문의 완료, 빠르게 파악 후 회신 한다고 함.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : 12일 오전 까지 회신 없으면 12일 오후 정재근 책임 연구원 연락 예정
+- 공조 로컬 CAN 심의회 진행 (11/13)
+  : SVm, BJ, NX5e, MX5a, HE1i 대상
+- ESIR 진행 (~11/15)
+  : ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24
+  : ES95411-00 (95%, ~11/21)
+  : ES90700-00 (50%, ~11/21)
+  : ES95480-00 (50%, ~11/21)
+  : ES95489-21 (100%)
+  : ES95489-24 (100%)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>열에너지차량시험팀 주관 BJ1 항속형 실차 검증 진행 (11/10)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>최대난방평가 재현 결과 플로어 모드 첫 진입 시 좌우 온도 편차 최대 4.5℃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이후 모든 단계가 끝날 때 좌우 온도 편차 1℃ 내 수렴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>온도 제어성 정합 평가 플로어 8단, 토출부 도어 Dr 4.65V, Ps 4.66V 강제 제어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Duty 90% 강제 제어 결과 좌우 온도 편차 3.75℃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Duty 50% ~ 80% 강제 제어 결과 60% 때 좌우 온도 편차 1.14℃, 그 외 1℃ 내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- PTC 벤치 테스트 한온에서 진행 (11/12)
+  : BJ RHD HVAC 수령 예정
+- 열에너지차량시험 측 일정 최종 정리 공유
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>11/10(월) BJ Proto 20호차 실차 튜닝 요청</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : 11/14(금) BJ AP2 차량 PTC 개선품 리워크 후 확인 (남양연구소 B1-7)
+  : 11/18(화) ~ 11/20(목) 리워크 완료 AP2 차량 국내 트립 진행
+  : 11/25(화) ~ 11/26(수) 실차 난방 평가 진행
+- 공조 로컬 CAN 심의회 진행 (11/13)
+  : SVm, BJ, NX5e, MX5a, HE1i 대상
+[김진겸 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>열에너지차량시험팀 측에서 11/10(월) 챔버 확보</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>자동차 측에서 실차 튜닝 요청, 참석 인원 선정 필요</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 최대 난방 및 좌우 온도 편차 실차 검증
+  : 11/25(화) ~ 11/26(수) 실차 난방 평가 진행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. TC 160℃ → 165℃ 변경 건 (11/13)
+  [ 안건 ]
+    - Stone TC 160℃ → 165℃ 변경 확정
+  [ 진행 및 검토 ]
+    - 165℃ 적용된 마스터 샘플 2대 요청
+     : 12월 말 ~ 1월 초 입고 예상
+    - 26. 2. 15. P1인데, P1 S/W 언제까지 확정 되어야 하는지 확인 (김기환 수석)
+    - R로직 튜닝
+    - 로직 및 기능 체크리스트 기반 검증 진행
 2. 승인도 수령 (11/19)
   [ 안건 ]
     - 변경점 업데이트된 승인도 수령
@@ -3454,7 +3761,7 @@
   [ 안건 ]
     - LP2 Event 대응
   [ 요청사항 ]
-    - 12/15까지 대전 한온 BJ1 150대 납품 완료
+    - 슬로바키아 법인 ↔ 터키 한온 직거래
   [ 진행 및 검토]
     - BJ1 LP2 현대자동차 대일정 26. 4. 15 → 26. 5. 1. 변경
      : LP2 일정 여유가 있는데, 납품 시기 너무 빠름, 재확인 필요
@@ -3476,311 +3783,6 @@
     - LHD, RHD R로직 튜닝
      : 김진겸 사원 일정 협의 후 진행
     - 로직 및 기능 체크리스트 기반 검증 진행</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-1. LHD, RHD R로직 튜닝 및 기능 점검
-  [ 안건 ]
-    - SW 점검
-  [ 진행 및 검토 ]
-    - 칼로리 사용 예약
-     : 11/17 ~ 11/21 야간 칼로리 사용 예약 완료
-     : 11/24 ~ 11/28 주간, 야간 칼로리 사용 예약 완료
-     : 12/01 ~ 12/05 야간 칼로리 사용 예약 완료
-    - LHD, RHD R로직 튜닝
-     : 김진겸 사원 일정 협의 후 진행
-    - 로직 및 기능 체크리스트 기반 검증 진행</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">[임제훈 사원]
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>사이버 보안 적용 단계, 피지컬 ID, 사이버보안품질팀 담당자 문의 (11/11)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>김동환 연구원 유선 문의 완료, 빠르게 파악 후 회신 한다고 함.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : 12일 오전 까지 회신 없으면 12일 오후 정재근 책임 연구원 연락 예정
-- 공조 로컬 CAN 심의회 진행 (11/13)
-  : SVm, BJ, NX5e, MX5a, HE1i 대상
-- ESIR 진행 (~11/15)
-  : ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24
-  : ES95411-00 (95%, ~11/21)
-  : ES90700-00 (50%, ~11/21)
-  : ES95480-00 (50%, ~11/21)
-  : ES95489-21 (100%)
-  : ES95489-24 (100%)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">[임제훈 사원]
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>열에너지차량시험팀 주관 BJ1 항속형 실차 검증 진행 (11/10)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>최대난방평가 재현 결과 플로어 모드 첫 진입 시 좌우 온도 편차 최대 4.5℃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>이후 모든 단계가 끝날 때 좌우 온도 편차 1℃ 내 수렴</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>온도 제어성 정합 평가 플로어 8단, 토출부 도어 Dr 4.65V, Ps 4.66V 강제 제어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Duty 90% 강제 제어 결과 좌우 온도 편차 3.75℃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Duty 50% ~ 80% 강제 제어 결과 60% 때 좌우 온도 편차 1.14℃, 그 외 1℃ 내</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- PTC 벤치 테스트 한온에서 진행 (11/12)
-  : BJ RHD HVAC 수령 예정
-- 열에너지차량시험 측 일정 최종 정리 공유
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>11/10(월) BJ Proto 20호차 실차 튜닝 요청</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : 11/14(금) BJ AP2 차량 PTC 개선품 리워크 후 확인 (남양연구소 B1-7)
-  : 11/18(화) ~ 11/20(목) 리워크 완료 AP2 차량 국내 트립 진행
-  : 11/25(화) ~ 11/26(수) 실차 난방 평가 진행
-- 공조 로컬 CAN 심의회 진행 (11/13)
-  : SVm, BJ, NX5e, MX5a, HE1i 대상
-[김진겸 사원]
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>열에너지차량시험팀 측에서 11/10(월) 챔버 확보</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>자동차 측에서 실차 튜닝 요청, 참석 인원 선정 필요</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- 최대 난방 및 좌우 온도 편차 실차 검증
-  : 11/25(화) ~ 11/26(수) 실차 난방 평가 진행</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10685,13 +10687,13 @@
         <v>311</v>
       </c>
       <c r="G14" s="158" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H14" s="106" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="I14" s="123" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="162" x14ac:dyDescent="0.3">
@@ -10714,11 +10716,11 @@
         <v>323</v>
       </c>
       <c r="H15" s="164" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="I15" s="135"/>
     </row>
-    <row r="16" spans="1:9" ht="189" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="216" x14ac:dyDescent="0.3">
       <c r="B16" s="132" t="s">
         <v>85</v>
       </c>
@@ -10735,10 +10737,10 @@
         <v>324</v>
       </c>
       <c r="G16" s="158" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="H16" s="158" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I16" s="135"/>
     </row>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="334">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3415,99 +3415,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[임제훈 사원]
-- 최소 작동 전압 범위 수정 후, EV HTR 개발팀 김민수 선임에게 전달
-  : 0℃, -30℃ 환경에서 QV Air PTC와 160V, 170V 출력 비교 필요로 인한 요청
-  : 다른 작업 먼저 한다고 함, 추후 진행 예정이고 일정 미정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- 기아샤시시스템품질팀 평택 공장 방문 (11/14)
-  : 11월 정기 협의체 회의는 평택 공장 방문 점검으로 대체
-  : 정기 협의체 진행 후 요청 자료에 대한 리뷰 (12월 정기 방문시 설명으로 협의)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-1. LHD, RHD R로직 튜닝 및 기능 점검
-  [ 안건 ]
-    - SW 점검
-  [ 진행 및 검토 ]
-    - 칼로리 사용 예약
-     : 11/17 ~ 11/21 야간 칼로리 사용 예약 완료
-     : 11/24 ~ 11/28 주간, 야간 칼로리 사용 예약 완료
-     : 12/01 ~ 12/05 야간 칼로리 사용 예약 완료
-    - LHD, RHD R로직 튜닝
-     : 김진겸 사원 일정 협의 후 진행
-    - 로직 및 기능 체크리스트 기반 검증 진행</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">[임제훈 사원]
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>사이버 보안 적용 단계, 피지컬 ID, 사이버보안품질팀 담당자 문의 (11/11)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>김동환 연구원 유선 문의 완료, 빠르게 파악 후 회신 한다고 함.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : 12일 오전 까지 회신 없으면 12일 오후 정재근 책임 연구원 연락 예정
-- 공조 로컬 CAN 심의회 진행 (11/13)
-  : SVm, BJ, NX5e, MX5a, HE1i 대상
-- ESIR 진행 (~11/15)
-  : ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24
-  : ES95411-00 (95%, ~11/21)
-  : ES90700-00 (50%, ~11/21)
-  : ES95480-00 (50%, ~11/21)
-  : ES95489-21 (100%)
-  : ES95489-24 (100%)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">[임제훈 사원]
 - </t>
@@ -3735,21 +3642,9 @@
   </si>
   <si>
     <t>[임제훈 사원]
-1. TC 160℃ → 165℃ 변경 건 (11/13)
-  [ 안건 ]
-    - Stone TC 160℃ → 165℃ 변경 확정
-  [ 진행 및 검토 ]
-    - 165℃ 적용된 마스터 샘플 2대 요청
-     : 12월 말 ~ 1월 초 입고 예상
-    - 26. 2. 15. P1인데, P1 S/W 언제까지 확정 되어야 하는지 확인 (김기환 수석)
-    - R로직 튜닝
-    - 로직 및 기능 체크리스트 기반 검증 진행
-2. 승인도 수령 (11/19)
-  [ 안건 ]
-    - 변경점 업데이트된 승인도 수령
-  [ 진행 및 검토 ]
-    - RATED MAX, LINEAR MAX 성능 확인
-    - Core Temp 구간 변경 확인</t>
+- 기아샤시시스템품질팀 평택 공장 방문 (11/14)
+  : 11월 정기 협의체 회의는 평택 공장 방문 점검으로 대체
+  : 정기 협의체 진행 후 요청 자료에 대한 리뷰 (12월 정기 방문시 설명으로 협의)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3783,6 +3678,124 @@
     - LHD, RHD R로직 튜닝
      : 김진겸 사원 일정 협의 후 진행
     - 로직 및 기능 체크리스트 기반 검증 진행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. LHD, RHD R로직 튜닝 및 기능 점검
+  [ 안건 ]
+    - SW 점검
+  [ 진행 및 검토 ]
+    - 칼로리 사용 예약
+     : 11/17 ~ 11/21 야간 칼로리 사용 예약 완료
+     : 11/24 ~ 11/28 주간, 야간 칼로리 사용 예약 완료
+     : 12/01 ~ 12/05 야간 칼로리 사용 예약 완료
+    - LHD, RHD R로직 튜닝
+     : 김진겸 사원 일정 협의 후 진행
+    - 로직 및 기능 체크리스트 기반 검증 진행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">[임제훈 사원]
+1. 기구 변경 건 (11/14)
+  [ 안건 ]
+    - Stone TC 160℃ → 165℃ 변경
+    - 전압 범위 변경
+    - LINEAR MAX 성능 7000W 변경
+    - 제어 사양서, S/W 재배포 요청
+  [ 진행 및 검토 ]
+    - 165℃ 적용된 마스터 샘플 제작 완료까지 최소 2일 소요
+    - 26. 2. 15. P1 일정, P1 S/W 언제까지 확정 되어야 하는지 확인 (김기환 수석)
+    - R로직 튜닝
+    - 로직 및 기능 체크리스트 기반 검증 진행
+    - 설계 변경으로 진행해야 하는지 확인
+2. 승인도 수령 건 (11/14)
+  [ 안건 ]
+    - 변경점 업데이트된 승인도 HKMC 발송
+  [ 진행 및 검토 ]
+    - 전압 범위 변경점 확인
+    - RATED MAX, LINEAR MAX 성능 확인
+    - Core Temp 구간 변경 확인
+3. ESIR (~11/15)
+  [ 안건 ]
+    - ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24 ESIR 진행
+  [ 진행 및 검토 ]
+    - ES95489-21 (100%)
+    - ES95489-24 (100%)
+    - ES95411-00 (95%, ~11/21)
+    - ES90700-00 (50%, ~11/21)
+    - ES95480-00 (50%, ~11/21)
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. 변동점 현황 작성 (~11/19)
+  [ 안건 ]
+    - SU2i 대비 변동점 현황 파악
+  [ 진행 및 검토 ]
+    - 과거차 사례 반영 현황 작성
+      : 과거차 사례 5가지 작성
+    - SU2i 대비 변동 내용
+      : 보호 로직 (HV 저전압, 과전압)
+    - 변동내용 품질 RISK SW 항목 있는지 파악 필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사이버 보안 적용 단계, 피지컬 ID, 사이버보안품질팀 담당자 문의 (11/11)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>김동환 연구원 유선 문의 완료, 빠르게 파악 후 회신 한다고 함.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : 12일 오전 까지 회신 없으면 12일 오후 정재근 책임 연구원 연락 예정
+- 공조 로컬 CAN 심의회 진행 (11/13)
+  : SVm, BJ, NX5e, MX5a, HE1i 대상</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10666,7 +10679,7 @@
         <v>322</v>
       </c>
       <c r="H13" s="106" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I13" s="135"/>
     </row>
@@ -10687,13 +10700,13 @@
         <v>311</v>
       </c>
       <c r="G14" s="158" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="H14" s="106" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="I14" s="123" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="162" x14ac:dyDescent="0.3">
@@ -10716,11 +10729,11 @@
         <v>323</v>
       </c>
       <c r="H15" s="164" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="I15" s="135"/>
     </row>
-    <row r="16" spans="1:9" ht="216" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="405" x14ac:dyDescent="0.3">
       <c r="B16" s="132" t="s">
         <v>85</v>
       </c>
@@ -10737,14 +10750,14 @@
         <v>324</v>
       </c>
       <c r="G16" s="158" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H16" s="158" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I16" s="135"/>
     </row>
-    <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="135" x14ac:dyDescent="0.3">
       <c r="B17" s="131" t="s">
         <v>167</v>
       </c>
@@ -10763,7 +10776,9 @@
       <c r="G17" s="120" t="s">
         <v>316</v>
       </c>
-      <c r="H17" s="138"/>
+      <c r="H17" s="164" t="s">
+        <v>332</v>
+      </c>
       <c r="I17" s="137"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
@@ -10779,7 +10794,7 @@
       <c r="E18" s="114"/>
       <c r="F18" s="156"/>
       <c r="G18" s="134"/>
-      <c r="H18" s="138"/>
+      <c r="H18" s="134"/>
       <c r="I18" s="137"/>
     </row>
     <row r="19" spans="2:9" ht="54" x14ac:dyDescent="0.3">
@@ -10799,7 +10814,7 @@
         <v>289</v>
       </c>
       <c r="G19" s="159" t="s">
-        <v>326</v>
+        <v>289</v>
       </c>
       <c r="I19" s="94"/>
     </row>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -3642,13 +3642,6 @@
   </si>
   <si>
     <t>[임제훈 사원]
-- 기아샤시시스템품질팀 평택 공장 방문 (11/14)
-  : 11월 정기 협의체 회의는 평택 공장 방문 점검으로 대체
-  : 정기 협의체 진행 후 요청 자료에 대한 리뷰 (12월 정기 방문시 설명으로 협의)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
 1. 최대 난방 및 좌우 온도 편차 실차 검증
   : 11/14(금) BJ AP2 차량 PTC 개선품 리워크 후 확인 (남양연구소 B1-7)
   : 11/18(화) ~ 11/20(목) 리워크 완료 AP2 차량 국내 트립 진행
@@ -3796,6 +3789,27 @@
 - 공조 로컬 CAN 심의회 진행 (11/13)
   : SVm, BJ, NX5e, MX5a, HE1i 대상</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">[임제훈 사원]
+1. 기아샤시시스템품질팀 평택 공장 방문 건 (11/14)
+  [ 안건 ]
+    - 서지 내성 평가
+  [ 요청사항 ]
+    - 11월 정기 협의체 회의는 평택 공장 방문 점검으로 대체
+    - 정기 협의체 진행 후 요청 자료에 대한 리뷰 (12월 정기 방문시 설명으로 협의)
+  [ 진행 및 검토]
+    - 11/14 서지 내성 평가 Fail
+     : PCB 라이팅 정지
+     : LP2 생산 물품으로 11/24 재평가 실행
+    - 재평가 Fail일 경우
+     : LV, HV, 전력 센싱 값 확인 및 튜닝
+     : R로직 튜닝, 체크리스트 기반 기능 및 성능 시험
+     : SW 설계 변경 필요
+    - 재평가 Pass일 경우
+     :
+  </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10659,7 +10673,7 @@
       <c r="H12" s="139"/>
       <c r="I12" s="94"/>
     </row>
-    <row r="13" spans="1:9" ht="175.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="243" x14ac:dyDescent="0.3">
       <c r="B13" s="133" t="s">
         <v>62</v>
       </c>
@@ -10679,7 +10693,7 @@
         <v>322</v>
       </c>
       <c r="H13" s="106" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I13" s="135"/>
     </row>
@@ -10703,7 +10717,7 @@
         <v>326</v>
       </c>
       <c r="H14" s="106" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="I14" s="123" t="s">
         <v>327</v>
@@ -10729,7 +10743,7 @@
         <v>323</v>
       </c>
       <c r="H15" s="164" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I15" s="135"/>
     </row>
@@ -10750,10 +10764,10 @@
         <v>324</v>
       </c>
       <c r="G16" s="158" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H16" s="158" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I16" s="135"/>
     </row>
@@ -10777,7 +10791,7 @@
         <v>316</v>
       </c>
       <c r="H17" s="164" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I17" s="137"/>
     </row>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="348">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2791,12 +2791,6 @@
   </si>
   <si>
     <t>[임제훈 사원]
-- 공조 로컬 CAN 심의회 진행 (11/10)
-  : SVm, BJ, NX5e, MX5a, HE1i 대상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
 - LHD R로직 튜닝
 - RHD R로직 튜닝 (HVAC 미보유, 보류)
 [김진겸 사원]
@@ -2852,12 +2846,6 @@
   </si>
   <si>
     <t>- 이슈 없음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- 공조 로컬 CAN 심의회 진행 (11/13)
-  : SVm, BJ, NX5e, MX5a, HE1i 대상</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2891,11 +2879,6 @@
   </si>
   <si>
     <t>[우리산업]
-기구 : 공준석, 강명준</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[우리산업]
 기구 : 공준석, HW : 하성빈</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2992,6 +2975,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>[임제훈 사원]
+- LHD, RHD R로직 튜닝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">[임제훈 사원]
 - </t>
@@ -3006,7 +2994,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>사이버 보안 M단계 적용으로 김응영 책임에게 유선 확인 완료 (11/07)</t>
+      <t>NX5e PCB 제작사양서 배포 (~11/04)</t>
     </r>
     <r>
       <rPr>
@@ -3030,7 +3018,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>공정 감사 5EA 건에 대해서는 공정 감사 어디서 하는지 모른다고 함</t>
+      <t>Power 90% 3499 → 3543 변경 후 전달 완료, 체크썸 변경</t>
     </r>
     <r>
       <rPr>
@@ -3054,7 +3042,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>기아샤시시스템품질팀 김제일 매니저 사이버보안 납품건 확인 완료 (11/10)</t>
+      <t>공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (~11/05)</t>
     </r>
     <r>
       <rPr>
@@ -3078,7 +3066,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>QV와 동일하게 LP2 5EA 납품, M단계 전량 사이버 보안 적용 진행 요청 받음</t>
+      <t>일정 조율에 대한 사유 작성하여 재회신 예정, 조건부 승인으로 가면 된다고 함</t>
     </r>
     <r>
       <rPr>
@@ -3102,7 +3090,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>사이버 보안으로 바뀐 이력 김제일 매니저 공유 완료</t>
+      <t>사이버 보안팀에 시료 제출하여 선 공정 검사 진행 여부는 확인 해본다고 함</t>
     </r>
     <r>
       <rPr>
@@ -3126,7 +3114,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>설계 변경 결재 상신 완료 (11/10)</t>
+      <t>ESIR 계획서 등록 완료 (11/05)</t>
     </r>
     <r>
       <rPr>
@@ -3138,110 +3126,8 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>기구팀 문의 결과, QV, SVm, BJ 담당자 전부 똑같다고 함. 결재 라인 똑같이 예정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>설계 변경 문서 작성 완료</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>사이버 보안 미적용 SW, 적용 SW 동작 확인 완료</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 완료 (11/10)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- 공조 로컬 CAN 심의회 진행 (11/13)
-  : SVm, BJ, NX5e, MX5a, HE1i 대상</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- LHD, RHD R로직 튜닝</t>
+- 최신 승인도 확인 (~11/06)</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3259,378 +3145,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>NX5e PCB 제작사양서 배포 (~11/04)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Power 90% 3499 → 3543 변경 후 전달 완료, 체크썸 변경</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>공조시스템설계팀 김동환 연구원 사이버보안 일정 재문의 (~11/05)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>일정 조율에 대한 사유 작성하여 재회신 예정, 조건부 승인으로 가면 된다고 함</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>사이버 보안팀에 시료 제출하여 선 공정 검사 진행 여부는 확인 해본다고 함</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ESIR 계획서 등록 완료 (11/05)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- 최신 승인도 확인 (~11/06)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">[임제훈 사원]
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>기구팀 승인도 승인 요청 (11/03)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">[임제훈 사원]
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>열에너지차량시험팀 주관 BJ1 항속형 실차 검증 진행 (11/10)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>최대난방평가 재현 결과 플로어 모드 첫 진입 시 좌우 온도 편차 최대 4.5℃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>이후 모든 단계가 끝날 때 좌우 온도 편차 1℃ 내 수렴</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>온도 제어성 정합 평가 플로어 8단, 토출부 도어 Dr 4.65V, Ps 4.66V 강제 제어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Duty 90% 강제 제어 결과 좌우 온도 편차 3.75℃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Duty 50% ~ 80% 강제 제어 결과 60% 때 좌우 온도 편차 1.14℃, 그 외 1℃ 내</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- PTC 벤치 테스트 한온에서 진행 (11/12)
-  : BJ RHD HVAC 수령 예정
-- 열에너지차량시험 측 일정 최종 정리 공유
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>11/10(월) BJ Proto 20호차 실차 튜닝 요청</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : 11/14(금) BJ AP2 차량 PTC 개선품 리워크 후 확인 (남양연구소 B1-7)
-  : 11/18(화) ~ 11/20(목) 리워크 완료 AP2 차량 국내 트립 진행
-  : 11/25(화) ~ 11/26(수) 실차 난방 평가 진행
-- 공조 로컬 CAN 심의회 진행 (11/13)
-  : SVm, BJ, NX5e, MX5a, HE1i 대상
-[김진겸 사원]
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>열에너지차량시험팀 측에서 11/10(월) 챔버 확보</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>자동차 측에서 실차 튜닝 요청, 참석 인원 선정 필요</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3638,6 +3153,95 @@
     <t>[임제훈 사원]
 - 최대 난방 및 좌우 온도 편차 실차 검증
   : 11/25(화) ~ 11/26(수) 실차 난방 평가 진행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. LHD, RHD R로직 튜닝 및 기능 점검
+  [ 안건 ]
+    - SW 점검
+  [ 진행 및 검토 ]
+    - 칼로리 사용 예약
+     : 11/17 ~ 11/21 야간 칼로리 사용 예약 완료
+     : 11/24 ~ 11/28 주간, 야간 칼로리 사용 예약 완료
+     : 12/01 ~ 12/05 야간 칼로리 사용 예약 완료
+    - LHD, RHD R로직 튜닝
+     : 김진겸 사원 일정 협의 후 진행
+    - 로직 및 기능 체크리스트 기반 검증 진행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">[임제훈 사원]
+1. 기아샤시시스템품질팀 평택 공장 방문 건 (11/14)
+  [ 안건 ]
+    - 서지 내성 평가
+  [ 요청사항 ]
+    - 11월 정기 협의체 회의는 평택 공장 방문 점검으로 대체
+    - 정기 협의체 진행 후 요청 자료에 대한 리뷰 (12월 정기 방문시 설명으로 협의)
+  [ 진행 및 검토]
+    - 11/14 서지 내성 평가 Fail
+     : PCB 라이팅 정지
+     : LP2 생산 물품으로 11/24 재평가 실행
+    - 재평가 Fail일 경우
+     : LV, HV, 전력 센싱 값 확인 및 튜닝
+     : R로직 튜닝, 체크리스트 기반 기능 및 성능 시험
+     : SW 설계 변경 필요
+    - 재평가 Pass일 경우
+     :
+  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[우리산업]
+기구 : 공준석, 강명준</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[우리산업]
+기구 : 공준석, 강명준</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALL Drawing
+4/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Proto
+10/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LP2
+10/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOP
+1/2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALL Drawing
+6/30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HE1i LHD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HE1i RHD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SP1
+5/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M/CAR
+3/31</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3660,6 +3264,8 @@
 3. BJ1 사이버 보안 적용 단계 및 납품건 확인 (11/17)
   [ 진행 및 검토 ]
     - 공조시스템설계팀, 품질팀 문의
+     : QV와 동일하게 진행 요청
+     : LP2 사이버 보안 적용품 5EA 납품, M 단계 전량 사이버 보안 적용
 4. LHD, RHD R로직 튜닝 및 기능 점검
   [ 안건 ]
     - 설계 변경 진행을 위한 SW 점검
@@ -3674,22 +3280,22 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>SP1
+5/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LP2
+10/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOP
+1/2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>[임제훈 사원]
-1. LHD, RHD R로직 튜닝 및 기능 점검
-  [ 안건 ]
-    - SW 점검
-  [ 진행 및 검토 ]
-    - 칼로리 사용 예약
-     : 11/17 ~ 11/21 야간 칼로리 사용 예약 완료
-     : 11/24 ~ 11/28 주간, 야간 칼로리 사용 예약 완료
-     : 12/01 ~ 12/05 야간 칼로리 사용 예약 완료
-    - LHD, RHD R로직 튜닝
-     : 김진겸 사원 일정 협의 후 진행
-    - 로직 및 기능 체크리스트 기반 검증 진행</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">[임제훈 사원]
 1. 기구 변경 건 (11/14)
   [ 안건 ]
     - Stone TC 160℃ → 165℃ 변경
@@ -3697,8 +3303,8 @@
     - LINEAR MAX 성능 7000W 변경
     - 제어 사양서, S/W 재배포 요청
   [ 진행 및 검토 ]
-    - 165℃ 적용된 마스터 샘플 제작 완료까지 최소 2일 소요
-    - 26. 2. 15. P1 일정, P1 S/W 언제까지 확정 되어야 하는지 확인 (김기환 수석)
+    - 165℃ 적용된 마스터 샘플 재고 부족으로 제작 불가
+    - NX5e 11/21 PCB 생산 예정일에 맞추어 재배포 불가
     - R로직 튜닝
     - 로직 및 기능 체크리스트 기반 검증 진행
     - 설계 변경으로 진행해야 하는지 확인
@@ -3707,8 +3313,15 @@
     - 변경점 업데이트된 승인도 HKMC 발송
   [ 진행 및 검토 ]
     - 전압 범위 변경점 확인
+      : 정격 전압 360V → 351V 변경
+      : 최대 작동 전압 403.2V → 413V 변경
     - RATED MAX, LINEAR MAX 성능 확인
+      : LINEAR MAX 7200W → 7000W 변경
     - Core Temp 구간 변경 확인
+      : Cut 100℃ → 90℃ 변경
+      : Recovery 90℃ → 85℃ 변경
+      : Limit Start 90℃ → 85℃ 변경
+      : Limit Stop 100℃ → 90℃ 변경
 3. ESIR (~11/15)
   [ 안건 ]
     - ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24 ESIR 진행
@@ -3717,8 +3330,7 @@
     - ES95489-24 (100%)
     - ES95411-00 (95%, ~11/21)
     - ES90700-00 (50%, ~11/21)
-    - ES95480-00 (50%, ~11/21)
-</t>
+    - ES95480-00 (50%, ~11/21)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3731,7 +3343,9 @@
       : 과거차 사례 5가지 작성
     - SU2i 대비 변동 내용
       : 보호 로직 (HV 저전압, 과전압)
-    - 변동내용 품질 RISK SW 항목 있는지 파악 필요</t>
+    - 품질 RISK
+      : S/W 이원화로 인한 PCB 색상 변경 품질 RISK
+      : 작동 전압 범위 변경으로 인한 품질 RISK</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3749,7 +3363,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>사이버 보안 적용 단계, 피지컬 ID, 사이버보안품질팀 담당자 문의 (11/11)</t>
+      <t>공조 로컬 CAN 심의회 진행 (11/13)</t>
     </r>
     <r>
       <rPr>
@@ -3773,6 +3387,616 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
+      <t>SVm, BJ, NX5e, MX5a, HE1i 대상</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사이버 보안 M단계 적용으로 김응영 책임에게 유선 확인 완료 (11/07)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공정 감사 5EA 건에 대해서는 공정 감사 어디서 하는지 모른다고 함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>기아샤시시스템품질팀 김제일 매니저 사이버보안 납품건 확인 완료 (11/10)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>QV와 동일하게 LP2 5EA 납품, M단계 전량 사이버 보안 적용 진행 요청 받음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사이버 보안으로 바뀐 이력 김제일 매니저 공유 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>설계 변경 결재 상신 완료 (11/10)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>기구팀 문의 결과, QV, SVm, BJ 담당자 전부 똑같다고 함. 결재 라인 똑같이 예정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>설계 변경 문서 작성 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사이버 보안 미적용 SW, 적용 SW 동작 확인 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 완료 (11/10)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공조 로컬 CAN 심의회 진행 (11/13)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SVm, BJ, NX5e, MX5a, HE1i 대상</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>열에너지차량시험팀 주관 BJ1 항속형 실차 검증 진행 (11/10)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>최대난방평가 재현 결과 플로어 모드 첫 진입 시 좌우 온도 편차 최대 4.5℃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이후 모든 단계가 끝날 때 좌우 온도 편차 1℃ 내 수렴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>온도 제어성 정합 평가 플로어 8단, 토출부 도어 Dr 4.65V, Ps 4.66V 강제 제어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Duty 90% 강제 제어 결과 좌우 온도 편차 3.75℃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Duty 50% ~ 80% 강제 제어 결과 60% 때 좌우 온도 편차 1.14℃, 그 외 1℃ 내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PTC 벤치 테스트 한온에서 진행 (11/12)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BJ RHD HVAC 2대 수령</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공조 로컬 CAN 심의회 진행 (11/13)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SVm, BJ, NX5e, MX5a, HE1i 대상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+[김진겸 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>열에너지차량시험팀 측에서 11/10(월) 챔버 확보</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>자동차 측에서 실차 튜닝 요청, 참석 인원 선정 필요</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사이버 보안 적용 단계, 피지컬 ID, 사이버보안품질팀 담당자 문의 (11/11)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>김동환 연구원 유선 문의 완료, 빠르게 파악 후 회신 한다고 함.</t>
     </r>
     <r>
@@ -3785,31 +4009,118 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-  : 12일 오전 까지 회신 없으면 12일 오후 정재근 책임 연구원 연락 예정
-- 공조 로컬 CAN 심의회 진행 (11/13)
-  : SVm, BJ, NX5e, MX5a, HE1i 대상</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">[임제훈 사원]
-1. 기아샤시시스템품질팀 평택 공장 방문 건 (11/14)
-  [ 안건 ]
-    - 서지 내성 평가
-  [ 요청사항 ]
-    - 11월 정기 협의체 회의는 평택 공장 방문 점검으로 대체
-    - 정기 협의체 진행 후 요청 자료에 대한 리뷰 (12월 정기 방문시 설명으로 협의)
-  [ 진행 및 검토]
-    - 11/14 서지 내성 평가 Fail
-     : PCB 라이팅 정지
-     : LP2 생산 물품으로 11/24 재평가 실행
-    - 재평가 Fail일 경우
-     : LV, HV, 전력 센싱 값 확인 및 튜닝
-     : R로직 튜닝, 체크리스트 기반 기능 및 성능 시험
-     : SW 설계 변경 필요
-    - 재평가 Pass일 경우
-     :
-  </t>
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>12일 오전 까지 회신 없으면 12일 오후 정재근 책임 연구원 연락 예정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공조 로컬 CAN 심의회 진행 (11/13)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SVm, BJ, NX5e, MX5a, HE1i 대상</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공조 로컬 CAN 심의회 진행 (11/13)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SVm, BJ, NX5e, MX5a, HE1i 대상</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 최소 작동 전압 범위 수정 후, EV HTR 개발팀 김민수 선임에게 전달
+  : 0℃, -30℃ 환경에서 QV Air PTC와 160V, 170V 출력 비교 필요로 인한 요청
+  : 다른 작업 먼저 한다고 함, 추후 진행 예정이고 일정 미정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5190,7 +5501,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="180">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5431,9 +5742,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5686,6 +5994,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5730,6 +6047,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -5788,7 +6108,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6190013" y="10084131"/>
+          <a:off x="6190013" y="11118273"/>
           <a:ext cx="3059130" cy="651904"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5808,7 +6128,7 @@
     <xdr:to>
       <xdr:col>37</xdr:col>
       <xdr:colOff>340776</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>108857</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -5819,7 +6139,7 @@
       <xdr:spPr>
         <a:xfrm flipH="1">
           <a:off x="12502763" y="353786"/>
-          <a:ext cx="30013" cy="24696964"/>
+          <a:ext cx="30013" cy="27350357"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -6372,7 +6692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BL24"/>
+  <dimension ref="A1:BL25"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.375" customWidth="1"/>
@@ -6396,90 +6716,90 @@
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="165" t="s">
+      <c r="B2" s="167" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="167" t="s">
+      <c r="C2" s="169" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="167" t="s">
+      <c r="D2" s="169" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="171">
+      <c r="E2" s="173">
         <v>23</v>
       </c>
-      <c r="F2" s="169"/>
-      <c r="G2" s="169"/>
-      <c r="H2" s="169"/>
-      <c r="I2" s="169"/>
-      <c r="J2" s="169"/>
-      <c r="K2" s="169"/>
-      <c r="L2" s="169"/>
-      <c r="M2" s="169"/>
-      <c r="N2" s="169"/>
-      <c r="O2" s="169"/>
-      <c r="P2" s="169"/>
-      <c r="Q2" s="169">
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="171"/>
+      <c r="J2" s="171"/>
+      <c r="K2" s="171"/>
+      <c r="L2" s="171"/>
+      <c r="M2" s="171"/>
+      <c r="N2" s="171"/>
+      <c r="O2" s="171"/>
+      <c r="P2" s="171"/>
+      <c r="Q2" s="171">
         <v>24</v>
       </c>
-      <c r="R2" s="169"/>
-      <c r="S2" s="169"/>
-      <c r="T2" s="169"/>
-      <c r="U2" s="169"/>
-      <c r="V2" s="169"/>
-      <c r="W2" s="169"/>
-      <c r="X2" s="169"/>
-      <c r="Y2" s="169"/>
-      <c r="Z2" s="169"/>
-      <c r="AA2" s="169"/>
-      <c r="AB2" s="169"/>
-      <c r="AC2" s="169">
+      <c r="R2" s="171"/>
+      <c r="S2" s="171"/>
+      <c r="T2" s="171"/>
+      <c r="U2" s="171"/>
+      <c r="V2" s="171"/>
+      <c r="W2" s="171"/>
+      <c r="X2" s="171"/>
+      <c r="Y2" s="171"/>
+      <c r="Z2" s="171"/>
+      <c r="AA2" s="171"/>
+      <c r="AB2" s="171"/>
+      <c r="AC2" s="171">
         <v>25</v>
       </c>
-      <c r="AD2" s="169"/>
-      <c r="AE2" s="169"/>
-      <c r="AF2" s="169"/>
-      <c r="AG2" s="169"/>
-      <c r="AH2" s="169"/>
-      <c r="AI2" s="169"/>
-      <c r="AJ2" s="169"/>
-      <c r="AK2" s="169"/>
-      <c r="AL2" s="169"/>
-      <c r="AM2" s="169"/>
-      <c r="AN2" s="169"/>
-      <c r="AO2" s="169">
+      <c r="AD2" s="171"/>
+      <c r="AE2" s="171"/>
+      <c r="AF2" s="171"/>
+      <c r="AG2" s="171"/>
+      <c r="AH2" s="171"/>
+      <c r="AI2" s="171"/>
+      <c r="AJ2" s="171"/>
+      <c r="AK2" s="171"/>
+      <c r="AL2" s="171"/>
+      <c r="AM2" s="171"/>
+      <c r="AN2" s="171"/>
+      <c r="AO2" s="171">
         <v>26</v>
       </c>
-      <c r="AP2" s="169"/>
-      <c r="AQ2" s="169"/>
-      <c r="AR2" s="169"/>
-      <c r="AS2" s="169"/>
-      <c r="AT2" s="169"/>
-      <c r="AU2" s="169"/>
-      <c r="AV2" s="169"/>
-      <c r="AW2" s="169"/>
-      <c r="AX2" s="169"/>
-      <c r="AY2" s="169"/>
-      <c r="AZ2" s="170"/>
-      <c r="BA2" s="169">
+      <c r="AP2" s="171"/>
+      <c r="AQ2" s="171"/>
+      <c r="AR2" s="171"/>
+      <c r="AS2" s="171"/>
+      <c r="AT2" s="171"/>
+      <c r="AU2" s="171"/>
+      <c r="AV2" s="171"/>
+      <c r="AW2" s="171"/>
+      <c r="AX2" s="171"/>
+      <c r="AY2" s="171"/>
+      <c r="AZ2" s="172"/>
+      <c r="BA2" s="171">
         <v>27</v>
       </c>
-      <c r="BB2" s="169"/>
-      <c r="BC2" s="169"/>
-      <c r="BD2" s="169"/>
-      <c r="BE2" s="169"/>
-      <c r="BF2" s="169"/>
-      <c r="BG2" s="169"/>
-      <c r="BH2" s="169"/>
-      <c r="BI2" s="169"/>
-      <c r="BJ2" s="169"/>
-      <c r="BK2" s="169"/>
-      <c r="BL2" s="170"/>
+      <c r="BB2" s="171"/>
+      <c r="BC2" s="171"/>
+      <c r="BD2" s="171"/>
+      <c r="BE2" s="171"/>
+      <c r="BF2" s="171"/>
+      <c r="BG2" s="171"/>
+      <c r="BH2" s="171"/>
+      <c r="BI2" s="171"/>
+      <c r="BJ2" s="171"/>
+      <c r="BK2" s="171"/>
+      <c r="BL2" s="172"/>
     </row>
     <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="166"/>
-      <c r="C3" s="168"/>
-      <c r="D3" s="168"/>
+      <c r="B3" s="168"/>
+      <c r="C3" s="170"/>
+      <c r="D3" s="170"/>
       <c r="E3" s="22">
         <v>1</v>
       </c>
@@ -7016,7 +7336,7 @@
       <c r="Y8" s="31"/>
       <c r="Z8" s="30"/>
       <c r="AA8" s="30"/>
-      <c r="AB8" s="122"/>
+      <c r="AB8" s="121"/>
       <c r="AC8" s="29"/>
       <c r="AD8" s="31"/>
       <c r="AE8" s="31"/>
@@ -7034,7 +7354,7 @@
       <c r="AM8" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="AN8" s="122"/>
+      <c r="AN8" s="121"/>
       <c r="AO8" s="29" t="s">
         <v>226</v>
       </c>
@@ -7219,8 +7539,8 @@
       <c r="C11" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="161" t="s">
-        <v>320</v>
+      <c r="D11" s="160" t="s">
+        <v>317</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="7"/>
@@ -7302,8 +7622,8 @@
       <c r="C12" s="58" t="s">
         <v>105</v>
       </c>
-      <c r="D12" s="161" t="s">
-        <v>320</v>
+      <c r="D12" s="160" t="s">
+        <v>317</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="7"/>
@@ -7336,7 +7656,7 @@
       <c r="AG12" s="30"/>
       <c r="AH12" s="7"/>
       <c r="AI12" s="13"/>
-      <c r="AJ12" s="100" t="s">
+      <c r="AJ12" s="99" t="s">
         <v>129</v>
       </c>
       <c r="AK12" s="36"/>
@@ -7384,7 +7704,7 @@
         <v>82</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="7"/>
@@ -7750,10 +8070,10 @@
       <c r="N17" s="41"/>
       <c r="O17" s="41"/>
       <c r="P17" s="43"/>
-      <c r="Q17" s="103" t="s">
+      <c r="Q17" s="102" t="s">
         <v>137</v>
       </c>
-      <c r="R17" s="102"/>
+      <c r="R17" s="101"/>
       <c r="S17" s="41"/>
       <c r="T17" s="41"/>
       <c r="U17" s="41"/>
@@ -7820,8 +8140,8 @@
       <c r="C18" s="59" t="s">
         <v>258</v>
       </c>
-      <c r="D18" s="161" t="s">
-        <v>318</v>
+      <c r="D18" s="160" t="s">
+        <v>316</v>
       </c>
       <c r="E18" s="64"/>
       <c r="F18" s="65"/>
@@ -8064,7 +8384,7 @@
       <c r="B21" s="57" t="s">
         <v>109</v>
       </c>
-      <c r="C21" s="81" t="s">
+      <c r="C21" s="80" t="s">
         <v>107</v>
       </c>
       <c r="D21" s="34" t="s">
@@ -8147,7 +8467,7 @@
       <c r="B22" s="57" t="s">
         <v>166</v>
       </c>
-      <c r="C22" s="81" t="s">
+      <c r="C22" s="80" t="s">
         <v>107</v>
       </c>
       <c r="D22" s="39"/>
@@ -8212,78 +8532,165 @@
       <c r="BK22" s="73"/>
       <c r="BL22" s="70"/>
     </row>
-    <row r="23" spans="2:64" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="79" t="s">
-        <v>167</v>
-      </c>
-      <c r="C23" s="80" t="s">
-        <v>104</v>
-      </c>
-      <c r="D23" s="163" t="s">
-        <v>319</v>
-      </c>
-      <c r="E23" s="49"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="50"/>
-      <c r="H23" s="50"/>
-      <c r="I23" s="50"/>
-      <c r="J23" s="50"/>
-      <c r="K23" s="50"/>
-      <c r="L23" s="50"/>
-      <c r="M23" s="50"/>
-      <c r="N23" s="50"/>
-      <c r="O23" s="50"/>
-      <c r="P23" s="51"/>
-      <c r="Q23" s="52"/>
-      <c r="R23" s="50"/>
-      <c r="S23" s="50"/>
-      <c r="T23" s="50"/>
-      <c r="U23" s="50"/>
-      <c r="V23" s="50"/>
-      <c r="W23" s="50"/>
-      <c r="X23" s="50"/>
-      <c r="Y23" s="50"/>
-      <c r="Z23" s="50"/>
-      <c r="AA23" s="50"/>
-      <c r="AB23" s="51"/>
-      <c r="AC23" s="52"/>
-      <c r="AD23" s="50"/>
-      <c r="AE23" s="50"/>
-      <c r="AF23" s="50"/>
-      <c r="AG23" s="53"/>
-      <c r="AH23" s="50"/>
-      <c r="AI23" s="54"/>
-      <c r="AJ23" s="50"/>
-      <c r="AK23" s="50"/>
-      <c r="AL23" s="50"/>
-      <c r="AM23" s="50"/>
-      <c r="AN23" s="51"/>
-      <c r="AO23" s="52"/>
-      <c r="AP23" s="54"/>
-      <c r="AQ23" s="54"/>
-      <c r="AR23" s="54"/>
-      <c r="AS23" s="50"/>
-      <c r="AT23" s="50"/>
-      <c r="AU23" s="54"/>
-      <c r="AV23" s="50"/>
-      <c r="AW23" s="50"/>
-      <c r="AX23" s="50"/>
-      <c r="AY23" s="54"/>
-      <c r="AZ23" s="55"/>
-      <c r="BA23" s="52"/>
-      <c r="BB23" s="74"/>
-      <c r="BC23" s="75"/>
-      <c r="BD23" s="74"/>
-      <c r="BE23" s="74"/>
-      <c r="BF23" s="75"/>
-      <c r="BG23" s="75"/>
-      <c r="BH23" s="75"/>
-      <c r="BI23" s="75"/>
-      <c r="BJ23" s="75"/>
-      <c r="BK23" s="75"/>
-      <c r="BL23" s="55"/>
-    </row>
-    <row r="24" spans="2:64" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="57" t="s">
+        <v>333</v>
+      </c>
+      <c r="C23" s="80"/>
+      <c r="D23" s="165" t="s">
+        <v>326</v>
+      </c>
+      <c r="E23" s="64"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="65"/>
+      <c r="K23" s="65"/>
+      <c r="L23" s="65"/>
+      <c r="M23" s="65"/>
+      <c r="N23" s="65"/>
+      <c r="O23" s="65"/>
+      <c r="P23" s="66"/>
+      <c r="Q23" s="67"/>
+      <c r="R23" s="65"/>
+      <c r="S23" s="65"/>
+      <c r="T23" s="65"/>
+      <c r="U23" s="65"/>
+      <c r="V23" s="65"/>
+      <c r="W23" s="65"/>
+      <c r="X23" s="65"/>
+      <c r="Y23" s="65"/>
+      <c r="Z23" s="65"/>
+      <c r="AA23" s="65"/>
+      <c r="AB23" s="66"/>
+      <c r="AC23" s="67"/>
+      <c r="AD23" s="65"/>
+      <c r="AE23" s="65"/>
+      <c r="AF23" s="69" t="s">
+        <v>327</v>
+      </c>
+      <c r="AG23" s="68"/>
+      <c r="AH23" s="65"/>
+      <c r="AI23" s="69"/>
+      <c r="AJ23" s="65"/>
+      <c r="AK23" s="65"/>
+      <c r="AL23" s="69" t="s">
+        <v>328</v>
+      </c>
+      <c r="AM23" s="65"/>
+      <c r="AN23" s="66"/>
+      <c r="AO23" s="67"/>
+      <c r="AP23" s="69"/>
+      <c r="AQ23" s="69" t="s">
+        <v>335</v>
+      </c>
+      <c r="AR23" s="69"/>
+      <c r="AS23" s="65"/>
+      <c r="AT23" s="69" t="s">
+        <v>334</v>
+      </c>
+      <c r="AU23" s="69"/>
+      <c r="AV23" s="65"/>
+      <c r="AW23" s="65"/>
+      <c r="AX23" s="69" t="s">
+        <v>329</v>
+      </c>
+      <c r="AY23" s="69"/>
+      <c r="AZ23" s="70"/>
+      <c r="BA23" s="166" t="s">
+        <v>330</v>
+      </c>
+      <c r="BB23" s="72"/>
+      <c r="BC23" s="73"/>
+      <c r="BD23" s="72"/>
+      <c r="BE23" s="72"/>
+      <c r="BF23" s="73"/>
+      <c r="BG23" s="73"/>
+      <c r="BH23" s="73"/>
+      <c r="BI23" s="73"/>
+      <c r="BJ23" s="73"/>
+      <c r="BK23" s="73"/>
+      <c r="BL23" s="70"/>
+    </row>
+    <row r="24" spans="2:64" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="79" t="s">
+        <v>332</v>
+      </c>
+      <c r="C24" s="164"/>
+      <c r="D24" s="162" t="s">
+        <v>325</v>
+      </c>
+      <c r="E24" s="49"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="50"/>
+      <c r="K24" s="50"/>
+      <c r="L24" s="50"/>
+      <c r="M24" s="50"/>
+      <c r="N24" s="50"/>
+      <c r="O24" s="50"/>
+      <c r="P24" s="51"/>
+      <c r="Q24" s="52"/>
+      <c r="R24" s="50"/>
+      <c r="S24" s="50"/>
+      <c r="T24" s="50"/>
+      <c r="U24" s="50"/>
+      <c r="V24" s="50"/>
+      <c r="W24" s="50"/>
+      <c r="X24" s="50"/>
+      <c r="Y24" s="50"/>
+      <c r="Z24" s="50"/>
+      <c r="AA24" s="50"/>
+      <c r="AB24" s="51"/>
+      <c r="AC24" s="52"/>
+      <c r="AD24" s="50"/>
+      <c r="AE24" s="50"/>
+      <c r="AF24" s="50"/>
+      <c r="AG24" s="53"/>
+      <c r="AH24" s="54" t="s">
+        <v>331</v>
+      </c>
+      <c r="AI24" s="54"/>
+      <c r="AJ24" s="50"/>
+      <c r="AK24" s="50"/>
+      <c r="AL24" s="50"/>
+      <c r="AM24" s="50"/>
+      <c r="AN24" s="51"/>
+      <c r="AO24" s="52"/>
+      <c r="AP24" s="54"/>
+      <c r="AQ24" s="54"/>
+      <c r="AR24" s="54"/>
+      <c r="AS24" s="50"/>
+      <c r="AT24" s="54" t="s">
+        <v>337</v>
+      </c>
+      <c r="AU24" s="54"/>
+      <c r="AV24" s="50"/>
+      <c r="AW24" s="50"/>
+      <c r="AX24" s="54" t="s">
+        <v>338</v>
+      </c>
+      <c r="AY24" s="54"/>
+      <c r="AZ24" s="55"/>
+      <c r="BA24" s="182" t="s">
+        <v>339</v>
+      </c>
+      <c r="BB24" s="74"/>
+      <c r="BC24" s="75"/>
+      <c r="BD24" s="74"/>
+      <c r="BE24" s="74"/>
+      <c r="BF24" s="75"/>
+      <c r="BG24" s="75"/>
+      <c r="BH24" s="75"/>
+      <c r="BI24" s="75"/>
+      <c r="BJ24" s="75"/>
+      <c r="BK24" s="75"/>
+      <c r="BL24" s="55"/>
+    </row>
+    <row r="25" spans="2:64" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B2:B3"/>
@@ -8320,13 +8727,13 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="125" t="s">
+      <c r="A2" s="124" t="s">
         <v>240</v>
       </c>
       <c r="B2" t="s">
         <v>241</v>
       </c>
-      <c r="C2" s="126" t="s">
+      <c r="C2" s="125" t="s">
         <v>242</v>
       </c>
       <c r="D2" t="s">
@@ -8334,13 +8741,13 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="125" t="s">
+      <c r="A3" s="124" t="s">
         <v>244</v>
       </c>
       <c r="B3" t="s">
         <v>241</v>
       </c>
-      <c r="C3" s="127" t="s">
+      <c r="C3" s="126" t="s">
         <v>245</v>
       </c>
       <c r="D3" t="s">
@@ -8348,13 +8755,13 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="125" t="s">
+      <c r="A4" s="124" t="s">
         <v>246</v>
       </c>
       <c r="B4" t="s">
         <v>241</v>
       </c>
-      <c r="C4" s="127" t="s">
+      <c r="C4" s="126" t="s">
         <v>247</v>
       </c>
       <c r="D4" t="s">
@@ -8362,13 +8769,13 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="128" t="s">
+      <c r="A5" s="127" t="s">
         <v>248</v>
       </c>
       <c r="B5" t="s">
         <v>241</v>
       </c>
-      <c r="C5" s="127" t="s">
+      <c r="C5" s="126" t="s">
         <v>249</v>
       </c>
       <c r="D5" t="s">
@@ -8376,13 +8783,13 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="126" t="s">
+      <c r="A6" s="125" t="s">
         <v>250</v>
       </c>
       <c r="B6" t="s">
         <v>243</v>
       </c>
-      <c r="C6" s="129" t="s">
+      <c r="C6" s="128" t="s">
         <v>251</v>
       </c>
       <c r="D6" t="s">
@@ -8390,13 +8797,13 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="125" t="s">
         <v>252</v>
       </c>
       <c r="B7" t="s">
         <v>243</v>
       </c>
-      <c r="C7" s="129" t="s">
+      <c r="C7" s="128" t="s">
         <v>253</v>
       </c>
       <c r="D7" t="s">
@@ -8404,7 +8811,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C8" s="125" t="s">
+      <c r="C8" s="124" t="s">
         <v>254</v>
       </c>
       <c r="D8" t="s">
@@ -8412,7 +8819,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C9" s="125" t="s">
+      <c r="C9" s="124" t="s">
         <v>255</v>
       </c>
       <c r="D9" t="s">
@@ -8420,7 +8827,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C10" s="129" t="s">
+      <c r="C10" s="128" t="s">
         <v>256</v>
       </c>
       <c r="D10" t="s">
@@ -8438,706 +8845,706 @@
   <dimension ref="A1:N22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="82" customWidth="1"/>
-    <col min="2" max="2" width="9" style="82"/>
-    <col min="3" max="4" width="14.75" style="82" customWidth="1"/>
-    <col min="5" max="5" width="43" style="82" customWidth="1"/>
-    <col min="6" max="6" width="62.125" style="82" customWidth="1"/>
-    <col min="7" max="7" width="61.875" style="82" customWidth="1"/>
-    <col min="8" max="14" width="62.125" style="82" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="82"/>
+    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
+    <col min="2" max="2" width="9" style="81"/>
+    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
+    <col min="5" max="5" width="43" style="81" customWidth="1"/>
+    <col min="6" max="6" width="62.125" style="81" customWidth="1"/>
+    <col min="7" max="7" width="61.875" style="81" customWidth="1"/>
+    <col min="8" max="14" width="62.125" style="81" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="81"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="108" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="110" t="s">
+      <c r="B1" s="109" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="108"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="174" t="s">
+      <c r="B2" s="176" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="178" t="s">
+      <c r="C2" s="180" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="178" t="s">
+      <c r="D2" s="180" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="176" t="s">
+      <c r="E2" s="178" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="97" t="s">
+      <c r="F2" s="96" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="172" t="s">
+      <c r="G2" s="174" t="s">
         <v>113</v>
       </c>
-      <c r="H2" s="172"/>
-      <c r="I2" s="172"/>
-      <c r="J2" s="173"/>
-      <c r="K2" s="172" t="s">
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
+      <c r="J2" s="175"/>
+      <c r="K2" s="174" t="s">
         <v>182</v>
       </c>
-      <c r="L2" s="172"/>
-      <c r="M2" s="172"/>
-      <c r="N2" s="173"/>
+      <c r="L2" s="174"/>
+      <c r="M2" s="174"/>
+      <c r="N2" s="175"/>
     </row>
     <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="175"/>
-      <c r="C3" s="179"/>
-      <c r="D3" s="179"/>
-      <c r="E3" s="177"/>
-      <c r="F3" s="98" t="s">
+      <c r="B3" s="177"/>
+      <c r="C3" s="181"/>
+      <c r="D3" s="181"/>
+      <c r="E3" s="179"/>
+      <c r="F3" s="97" t="s">
         <v>111</v>
       </c>
-      <c r="G3" s="98" t="s">
+      <c r="G3" s="97" t="s">
         <v>114</v>
       </c>
-      <c r="H3" s="98" t="s">
+      <c r="H3" s="97" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="98" t="s">
+      <c r="I3" s="97" t="s">
         <v>116</v>
       </c>
-      <c r="J3" s="99" t="s">
+      <c r="J3" s="98" t="s">
         <v>110</v>
       </c>
-      <c r="K3" s="98" t="s">
+      <c r="K3" s="97" t="s">
         <v>215</v>
       </c>
-      <c r="L3" s="98" t="s">
+      <c r="L3" s="97" t="s">
         <v>115</v>
       </c>
-      <c r="M3" s="98" t="s">
+      <c r="M3" s="97" t="s">
         <v>116</v>
       </c>
-      <c r="N3" s="99" t="s">
+      <c r="N3" s="98" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="108" x14ac:dyDescent="0.3">
-      <c r="B4" s="83" t="s">
+      <c r="B4" s="82" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="116" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="117" t="s">
+      <c r="D4" s="116" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="91" t="s">
+      <c r="E4" s="90" t="s">
         <v>152</v>
       </c>
-      <c r="F4" s="106" t="s">
+      <c r="F4" s="105" t="s">
         <v>143</v>
       </c>
-      <c r="G4" s="115" t="s">
+      <c r="G4" s="114" t="s">
         <v>171</v>
       </c>
-      <c r="H4" s="106" t="s">
+      <c r="H4" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="I4" s="106" t="s">
+      <c r="I4" s="105" t="s">
         <v>201</v>
       </c>
-      <c r="J4" s="93"/>
-      <c r="K4" s="106" t="s">
+      <c r="J4" s="92"/>
+      <c r="K4" s="105" t="s">
         <v>208</v>
       </c>
-      <c r="L4" s="106" t="s">
+      <c r="L4" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="M4" s="106"/>
-      <c r="N4" s="93"/>
+      <c r="M4" s="105"/>
+      <c r="N4" s="92"/>
     </row>
     <row r="5" spans="1:14" ht="108" x14ac:dyDescent="0.3">
-      <c r="B5" s="84" t="s">
+      <c r="B5" s="83" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="118" t="s">
+      <c r="C5" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="118" t="s">
+      <c r="D5" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="92" t="s">
+      <c r="E5" s="91" t="s">
         <v>153</v>
       </c>
-      <c r="F5" s="106" t="s">
+      <c r="F5" s="105" t="s">
         <v>143</v>
       </c>
-      <c r="G5" s="115" t="s">
+      <c r="G5" s="114" t="s">
         <v>171</v>
       </c>
-      <c r="H5" s="106" t="s">
+      <c r="H5" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="I5" s="106" t="s">
+      <c r="I5" s="105" t="s">
         <v>201</v>
       </c>
-      <c r="J5" s="94"/>
-      <c r="K5" s="106" t="s">
+      <c r="J5" s="93"/>
+      <c r="K5" s="105" t="s">
         <v>208</v>
       </c>
-      <c r="L5" s="106" t="s">
+      <c r="L5" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="M5" s="106"/>
-      <c r="N5" s="94"/>
+      <c r="M5" s="105"/>
+      <c r="N5" s="93"/>
     </row>
     <row r="6" spans="1:14" ht="108" x14ac:dyDescent="0.3">
-      <c r="B6" s="84" t="s">
+      <c r="B6" s="83" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="118" t="s">
+      <c r="C6" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D6" s="118" t="s">
+      <c r="D6" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E6" s="92" t="s">
+      <c r="E6" s="91" t="s">
         <v>154</v>
       </c>
-      <c r="F6" s="106" t="s">
+      <c r="F6" s="105" t="s">
         <v>143</v>
       </c>
-      <c r="G6" s="115" t="s">
+      <c r="G6" s="114" t="s">
         <v>171</v>
       </c>
-      <c r="H6" s="106" t="s">
+      <c r="H6" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="I6" s="106" t="s">
+      <c r="I6" s="105" t="s">
         <v>201</v>
       </c>
-      <c r="J6" s="94"/>
-      <c r="K6" s="106" t="s">
+      <c r="J6" s="93"/>
+      <c r="K6" s="105" t="s">
         <v>208</v>
       </c>
-      <c r="L6" s="106" t="s">
+      <c r="L6" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="M6" s="106"/>
-      <c r="N6" s="94"/>
+      <c r="M6" s="105"/>
+      <c r="N6" s="93"/>
     </row>
     <row r="7" spans="1:14" ht="108" x14ac:dyDescent="0.3">
-      <c r="B7" s="84" t="s">
+      <c r="B7" s="83" t="s">
         <v>125</v>
       </c>
-      <c r="C7" s="118" t="s">
+      <c r="C7" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D7" s="118" t="s">
+      <c r="D7" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="92" t="s">
+      <c r="E7" s="91" t="s">
         <v>155</v>
       </c>
-      <c r="F7" s="106" t="s">
+      <c r="F7" s="105" t="s">
         <v>143</v>
       </c>
-      <c r="G7" s="115" t="s">
+      <c r="G7" s="114" t="s">
         <v>171</v>
       </c>
-      <c r="H7" s="106" t="s">
+      <c r="H7" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="I7" s="106" t="s">
+      <c r="I7" s="105" t="s">
         <v>201</v>
       </c>
-      <c r="J7" s="94"/>
-      <c r="K7" s="106" t="s">
+      <c r="J7" s="93"/>
+      <c r="K7" s="105" t="s">
         <v>208</v>
       </c>
-      <c r="L7" s="106" t="s">
+      <c r="L7" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="M7" s="106"/>
-      <c r="N7" s="94"/>
+      <c r="M7" s="105"/>
+      <c r="N7" s="93"/>
     </row>
     <row r="8" spans="1:14" ht="108" x14ac:dyDescent="0.3">
-      <c r="B8" s="85" t="s">
+      <c r="B8" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="118" t="s">
+      <c r="C8" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D8" s="118" t="s">
+      <c r="D8" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E8" s="92" t="s">
+      <c r="E8" s="91" t="s">
         <v>156</v>
       </c>
-      <c r="F8" s="106" t="s">
+      <c r="F8" s="105" t="s">
         <v>144</v>
       </c>
-      <c r="G8" s="115" t="s">
+      <c r="G8" s="114" t="s">
         <v>171</v>
       </c>
-      <c r="H8" s="106" t="s">
+      <c r="H8" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="I8" s="106" t="s">
+      <c r="I8" s="105" t="s">
         <v>201</v>
       </c>
-      <c r="J8" s="94"/>
-      <c r="K8" s="106" t="s">
+      <c r="J8" s="93"/>
+      <c r="K8" s="105" t="s">
         <v>208</v>
       </c>
-      <c r="L8" s="106" t="s">
+      <c r="L8" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="M8" s="106"/>
-      <c r="N8" s="94"/>
+      <c r="M8" s="105"/>
+      <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:14" ht="175.5" x14ac:dyDescent="0.3">
-      <c r="B9" s="85" t="s">
+      <c r="B9" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="118" t="s">
+      <c r="C9" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D9" s="118" t="s">
+      <c r="D9" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E9" s="101" t="s">
+      <c r="E9" s="100" t="s">
         <v>157</v>
       </c>
-      <c r="F9" s="106" t="s">
+      <c r="F9" s="105" t="s">
         <v>145</v>
       </c>
-      <c r="G9" s="115" t="s">
+      <c r="G9" s="114" t="s">
         <v>171</v>
       </c>
-      <c r="H9" s="106" t="s">
+      <c r="H9" s="105" t="s">
         <v>185</v>
       </c>
-      <c r="I9" s="106" t="s">
+      <c r="I9" s="105" t="s">
         <v>202</v>
       </c>
-      <c r="J9" s="94"/>
-      <c r="K9" s="106" t="s">
+      <c r="J9" s="93"/>
+      <c r="K9" s="105" t="s">
         <v>209</v>
       </c>
-      <c r="L9" s="106" t="s">
+      <c r="L9" s="105" t="s">
         <v>216</v>
       </c>
-      <c r="M9" s="106"/>
-      <c r="N9" s="94"/>
+      <c r="M9" s="105"/>
+      <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" ht="121.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="85" t="s">
+      <c r="B10" s="84" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="118" t="s">
+      <c r="C10" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D10" s="118" t="s">
+      <c r="D10" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E10" s="101" t="s">
+      <c r="E10" s="100" t="s">
         <v>158</v>
       </c>
-      <c r="F10" s="106" t="s">
+      <c r="F10" s="105" t="s">
         <v>144</v>
       </c>
-      <c r="G10" s="115" t="s">
+      <c r="G10" s="114" t="s">
         <v>171</v>
       </c>
-      <c r="H10" s="106" t="s">
+      <c r="H10" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="I10" s="106" t="s">
+      <c r="I10" s="105" t="s">
         <v>203</v>
       </c>
-      <c r="J10" s="94"/>
-      <c r="K10" s="106" t="s">
+      <c r="J10" s="93"/>
+      <c r="K10" s="105" t="s">
         <v>208</v>
       </c>
-      <c r="L10" s="106" t="s">
+      <c r="L10" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="M10" s="106"/>
-      <c r="N10" s="94"/>
+      <c r="M10" s="105"/>
+      <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:14" ht="108" x14ac:dyDescent="0.3">
-      <c r="B11" s="84" t="s">
+      <c r="B11" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="118" t="s">
+      <c r="C11" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D11" s="118" t="s">
+      <c r="D11" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E11" s="101" t="s">
+      <c r="E11" s="100" t="s">
         <v>159</v>
       </c>
-      <c r="F11" s="106" t="s">
+      <c r="F11" s="105" t="s">
         <v>142</v>
       </c>
-      <c r="G11" s="115" t="s">
+      <c r="G11" s="114" t="s">
         <v>171</v>
       </c>
-      <c r="H11" s="106" t="s">
+      <c r="H11" s="105" t="s">
         <v>183</v>
       </c>
-      <c r="I11" s="106" t="s">
+      <c r="I11" s="105" t="s">
         <v>197</v>
       </c>
-      <c r="J11" s="94"/>
-      <c r="K11" s="106" t="s">
+      <c r="J11" s="93"/>
+      <c r="K11" s="105" t="s">
         <v>210</v>
       </c>
-      <c r="L11" s="106" t="s">
+      <c r="L11" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="M11" s="106"/>
-      <c r="N11" s="94"/>
+      <c r="M11" s="105"/>
+      <c r="N11" s="93"/>
     </row>
     <row r="12" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="85" t="s">
+      <c r="B12" s="84" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="118" t="s">
+      <c r="C12" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D12" s="118" t="s">
+      <c r="D12" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E12" s="101" t="s">
+      <c r="E12" s="100" t="s">
         <v>160</v>
       </c>
-      <c r="F12" s="106" t="s">
+      <c r="F12" s="105" t="s">
         <v>146</v>
       </c>
-      <c r="G12" s="115" t="s">
+      <c r="G12" s="114" t="s">
         <v>171</v>
       </c>
-      <c r="H12" s="106" t="s">
+      <c r="H12" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="I12" s="106" t="s">
+      <c r="I12" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="J12" s="94"/>
-      <c r="K12" s="106" t="s">
+      <c r="J12" s="93"/>
+      <c r="K12" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="L12" s="106" t="s">
+      <c r="L12" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="M12" s="106"/>
-      <c r="N12" s="94"/>
+      <c r="M12" s="105"/>
+      <c r="N12" s="93"/>
     </row>
     <row r="13" spans="1:14" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="85" t="s">
+      <c r="B13" s="84" t="s">
         <v>118</v>
       </c>
-      <c r="C13" s="118" t="s">
+      <c r="C13" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D13" s="118" t="s">
+      <c r="D13" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="101" t="s">
+      <c r="E13" s="100" t="s">
         <v>161</v>
       </c>
-      <c r="F13" s="106" t="s">
+      <c r="F13" s="105" t="s">
         <v>165</v>
       </c>
-      <c r="G13" s="115" t="s">
+      <c r="G13" s="114" t="s">
         <v>171</v>
       </c>
-      <c r="H13" s="106" t="s">
+      <c r="H13" s="105" t="s">
         <v>191</v>
       </c>
-      <c r="I13" s="106" t="s">
+      <c r="I13" s="105" t="s">
         <v>204</v>
       </c>
-      <c r="J13" s="94"/>
-      <c r="K13" s="106" t="s">
+      <c r="J13" s="93"/>
+      <c r="K13" s="105" t="s">
         <v>214</v>
       </c>
-      <c r="L13" s="106" t="s">
+      <c r="L13" s="105" t="s">
         <v>218</v>
       </c>
-      <c r="M13" s="106"/>
-      <c r="N13" s="94"/>
+      <c r="M13" s="105"/>
+      <c r="N13" s="93"/>
     </row>
     <row r="14" spans="1:14" ht="175.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="86" t="s">
+      <c r="B14" s="85" t="s">
         <v>181</v>
       </c>
-      <c r="C14" s="118" t="s">
+      <c r="C14" s="117" t="s">
         <v>179</v>
       </c>
-      <c r="D14" s="118" t="s">
+      <c r="D14" s="117" t="s">
         <v>180</v>
       </c>
-      <c r="E14" s="101"/>
-      <c r="F14" s="106"/>
-      <c r="G14" s="115"/>
-      <c r="H14" s="106" t="s">
+      <c r="E14" s="100"/>
+      <c r="F14" s="105"/>
+      <c r="G14" s="114"/>
+      <c r="H14" s="105" t="s">
         <v>200</v>
       </c>
-      <c r="I14" s="106" t="s">
+      <c r="I14" s="105" t="s">
         <v>207</v>
       </c>
-      <c r="J14" s="94"/>
-      <c r="K14" s="106" t="s">
+      <c r="J14" s="93"/>
+      <c r="K14" s="105" t="s">
         <v>211</v>
       </c>
-      <c r="L14" s="106" t="s">
+      <c r="L14" s="105" t="s">
         <v>217</v>
       </c>
-      <c r="M14" s="106"/>
-      <c r="N14" s="94"/>
+      <c r="M14" s="105"/>
+      <c r="N14" s="93"/>
     </row>
     <row r="15" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="86" t="s">
+      <c r="B15" s="85" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="118" t="s">
+      <c r="C15" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D15" s="118" t="s">
+      <c r="D15" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E15" s="101" t="s">
+      <c r="E15" s="100" t="s">
         <v>162</v>
       </c>
-      <c r="F15" s="106" t="s">
+      <c r="F15" s="105" t="s">
         <v>172</v>
       </c>
-      <c r="G15" s="115" t="s">
+      <c r="G15" s="114" t="s">
         <v>171</v>
       </c>
-      <c r="H15" s="106" t="s">
+      <c r="H15" s="105" t="s">
         <v>190</v>
       </c>
-      <c r="I15" s="106" t="s">
+      <c r="I15" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="J15" s="94"/>
-      <c r="K15" s="106" t="s">
+      <c r="J15" s="93"/>
+      <c r="K15" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="L15" s="106"/>
-      <c r="M15" s="106"/>
-      <c r="N15" s="94"/>
+      <c r="L15" s="105"/>
+      <c r="M15" s="105"/>
+      <c r="N15" s="93"/>
     </row>
     <row r="16" spans="1:14" ht="121.5" x14ac:dyDescent="0.3">
-      <c r="B16" s="85" t="s">
+      <c r="B16" s="84" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="118" t="s">
+      <c r="C16" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D16" s="118" t="s">
+      <c r="D16" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E16" s="92" t="s">
+      <c r="E16" s="91" t="s">
         <v>163</v>
       </c>
-      <c r="F16" s="106" t="s">
+      <c r="F16" s="105" t="s">
         <v>173</v>
       </c>
-      <c r="G16" s="115" t="s">
+      <c r="G16" s="114" t="s">
         <v>171</v>
       </c>
-      <c r="H16" s="106" t="s">
+      <c r="H16" s="105" t="s">
         <v>198</v>
       </c>
-      <c r="I16" s="106" t="s">
+      <c r="I16" s="105" t="s">
         <v>206</v>
       </c>
-      <c r="J16" s="94"/>
-      <c r="K16" s="106" t="s">
+      <c r="J16" s="93"/>
+      <c r="K16" s="105" t="s">
         <v>213</v>
       </c>
-      <c r="L16" s="106"/>
-      <c r="M16" s="106"/>
-      <c r="N16" s="94"/>
+      <c r="L16" s="105"/>
+      <c r="M16" s="105"/>
+      <c r="N16" s="93"/>
     </row>
     <row r="17" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="87" t="s">
+      <c r="B17" s="86" t="s">
         <v>141</v>
       </c>
-      <c r="C17" s="118" t="s">
+      <c r="C17" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D17" s="118" t="s">
+      <c r="D17" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E17" s="92" t="s">
+      <c r="E17" s="91" t="s">
         <v>138</v>
       </c>
-      <c r="F17" s="90"/>
-      <c r="G17" s="115" t="s">
+      <c r="F17" s="89"/>
+      <c r="G17" s="114" t="s">
         <v>171</v>
       </c>
-      <c r="H17" s="90" t="s">
+      <c r="H17" s="89" t="s">
         <v>199</v>
       </c>
-      <c r="I17" s="90" t="s">
+      <c r="I17" s="89" t="s">
         <v>199</v>
       </c>
-      <c r="J17" s="94"/>
-      <c r="K17" s="90" t="s">
+      <c r="J17" s="93"/>
+      <c r="K17" s="89" t="s">
         <v>105</v>
       </c>
-      <c r="L17" s="90" t="s">
+      <c r="L17" s="89" t="s">
         <v>105</v>
       </c>
-      <c r="M17" s="90"/>
-      <c r="N17" s="94"/>
+      <c r="M17" s="89"/>
+      <c r="N17" s="93"/>
     </row>
     <row r="18" spans="2:14" ht="162" x14ac:dyDescent="0.3">
-      <c r="B18" s="87" t="s">
+      <c r="B18" s="86" t="s">
         <v>106</v>
       </c>
-      <c r="C18" s="118" t="s">
+      <c r="C18" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D18" s="118" t="s">
+      <c r="D18" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E18" s="101" t="s">
+      <c r="E18" s="100" t="s">
         <v>164</v>
       </c>
-      <c r="F18" s="106" t="s">
+      <c r="F18" s="105" t="s">
         <v>147</v>
       </c>
-      <c r="G18" s="115" t="s">
+      <c r="G18" s="114" t="s">
         <v>171</v>
       </c>
-      <c r="H18" s="106" t="s">
+      <c r="H18" s="105" t="s">
         <v>189</v>
       </c>
-      <c r="I18" s="106" t="s">
+      <c r="I18" s="105" t="s">
         <v>205</v>
       </c>
-      <c r="J18" s="94"/>
-      <c r="K18" s="106" t="s">
+      <c r="J18" s="93"/>
+      <c r="K18" s="105" t="s">
         <v>212</v>
       </c>
-      <c r="L18" s="106" t="s">
+      <c r="L18" s="105" t="s">
         <v>212</v>
       </c>
-      <c r="M18" s="106"/>
-      <c r="N18" s="94"/>
+      <c r="M18" s="105"/>
+      <c r="N18" s="93"/>
     </row>
     <row r="19" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="86" t="s">
+      <c r="B19" s="85" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="118" t="s">
+      <c r="C19" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D19" s="118" t="s">
+      <c r="D19" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E19" s="92" t="s">
+      <c r="E19" s="91" t="s">
         <v>139</v>
       </c>
-      <c r="F19" s="105" t="s">
+      <c r="F19" s="104" t="s">
         <v>150</v>
       </c>
-      <c r="G19" s="115" t="s">
+      <c r="G19" s="114" t="s">
         <v>171</v>
       </c>
-      <c r="H19" s="106" t="s">
+      <c r="H19" s="105" t="s">
         <v>188</v>
       </c>
-      <c r="I19" s="106" t="s">
+      <c r="I19" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="J19" s="94"/>
-      <c r="K19" s="106" t="s">
+      <c r="J19" s="93"/>
+      <c r="K19" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="L19" s="106" t="s">
+      <c r="L19" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="M19" s="106"/>
-      <c r="N19" s="94"/>
+      <c r="M19" s="105"/>
+      <c r="N19" s="93"/>
     </row>
     <row r="20" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="86" t="s">
+      <c r="B20" s="85" t="s">
         <v>168</v>
       </c>
-      <c r="C20" s="118" t="s">
+      <c r="C20" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D20" s="118" t="s">
+      <c r="D20" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="114" t="s">
+      <c r="E20" s="113" t="s">
         <v>169</v>
       </c>
-      <c r="F20" s="111" t="s">
+      <c r="F20" s="110" t="s">
         <v>170</v>
       </c>
-      <c r="G20" s="115" t="s">
+      <c r="G20" s="114" t="s">
         <v>171</v>
       </c>
-      <c r="H20" s="120" t="s">
+      <c r="H20" s="119" t="s">
         <v>187</v>
       </c>
-      <c r="I20" s="106" t="s">
+      <c r="I20" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="J20" s="113"/>
-      <c r="K20" s="106" t="s">
+      <c r="J20" s="112"/>
+      <c r="K20" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="L20" s="106" t="s">
+      <c r="L20" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="M20" s="106"/>
-      <c r="N20" s="113"/>
+      <c r="M20" s="105"/>
+      <c r="N20" s="112"/>
     </row>
     <row r="21" spans="2:14" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="88" t="s">
+      <c r="B21" s="87" t="s">
         <v>108</v>
       </c>
-      <c r="C21" s="119" t="s">
+      <c r="C21" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D21" s="119" t="s">
+      <c r="D21" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E21" s="104" t="s">
+      <c r="E21" s="103" t="s">
         <v>140</v>
       </c>
-      <c r="F21" s="107" t="s">
+      <c r="F21" s="106" t="s">
         <v>151</v>
       </c>
-      <c r="G21" s="116" t="s">
+      <c r="G21" s="115" t="s">
         <v>171</v>
       </c>
-      <c r="H21" s="121" t="s">
+      <c r="H21" s="120" t="s">
         <v>186</v>
       </c>
-      <c r="I21" s="121" t="s">
+      <c r="I21" s="120" t="s">
         <v>174</v>
       </c>
-      <c r="J21" s="96"/>
-      <c r="K21" s="121" t="s">
+      <c r="J21" s="95"/>
+      <c r="K21" s="120" t="s">
         <v>174</v>
       </c>
-      <c r="L21" s="121" t="s">
+      <c r="L21" s="120" t="s">
         <v>174</v>
       </c>
-      <c r="M21" s="121"/>
-      <c r="N21" s="96"/>
+      <c r="M21" s="120"/>
+      <c r="N21" s="95"/>
     </row>
     <row r="22" spans="2:14" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -9214,387 +9621,387 @@
   <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="82" customWidth="1"/>
-    <col min="2" max="2" width="9" style="82"/>
-    <col min="3" max="4" width="14.75" style="82" customWidth="1"/>
-    <col min="5" max="5" width="43" style="82" customWidth="1"/>
-    <col min="6" max="6" width="61.875" style="82" customWidth="1"/>
-    <col min="7" max="9" width="62.125" style="82" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="82"/>
+    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
+    <col min="2" max="2" width="9" style="81"/>
+    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
+    <col min="5" max="5" width="43" style="81" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
+    <col min="7" max="9" width="62.125" style="81" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="81"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="110" t="s">
+      <c r="B1" s="109" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="108"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="174" t="s">
+      <c r="B2" s="176" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="178" t="s">
+      <c r="C2" s="180" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="178" t="s">
+      <c r="D2" s="180" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="176" t="s">
+      <c r="E2" s="178" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="172" t="s">
+      <c r="F2" s="174" t="s">
         <v>182</v>
       </c>
-      <c r="G2" s="172"/>
-      <c r="H2" s="172"/>
-      <c r="I2" s="173"/>
+      <c r="G2" s="174"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="175"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="175"/>
-      <c r="C3" s="179"/>
-      <c r="D3" s="179"/>
-      <c r="E3" s="177"/>
-      <c r="F3" s="98" t="s">
+      <c r="B3" s="177"/>
+      <c r="C3" s="181"/>
+      <c r="D3" s="181"/>
+      <c r="E3" s="179"/>
+      <c r="F3" s="97" t="s">
         <v>114</v>
       </c>
-      <c r="G3" s="98" t="s">
+      <c r="G3" s="97" t="s">
         <v>115</v>
       </c>
-      <c r="H3" s="98" t="s">
+      <c r="H3" s="97" t="s">
         <v>116</v>
       </c>
-      <c r="I3" s="99" t="s">
+      <c r="I3" s="98" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="83" t="s">
+      <c r="B4" s="82" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="116" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="117" t="s">
+      <c r="D4" s="116" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="91" t="s">
+      <c r="E4" s="90" t="s">
         <v>152</v>
       </c>
-      <c r="F4" s="115"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="93"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="92"/>
     </row>
     <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="84" t="s">
+      <c r="B5" s="83" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="118" t="s">
+      <c r="C5" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="118" t="s">
+      <c r="D5" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="92" t="s">
+      <c r="E5" s="91" t="s">
         <v>153</v>
       </c>
-      <c r="F5" s="115"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="90"/>
-      <c r="I5" s="94"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="93"/>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="84" t="s">
+      <c r="B6" s="83" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="118" t="s">
+      <c r="C6" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D6" s="118" t="s">
+      <c r="D6" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E6" s="92" t="s">
+      <c r="E6" s="91" t="s">
         <v>154</v>
       </c>
-      <c r="F6" s="115"/>
-      <c r="G6" s="106"/>
-      <c r="H6" s="90"/>
-      <c r="I6" s="94"/>
+      <c r="F6" s="114"/>
+      <c r="G6" s="105"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="93"/>
     </row>
     <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="84" t="s">
+      <c r="B7" s="83" t="s">
         <v>125</v>
       </c>
-      <c r="C7" s="118" t="s">
+      <c r="C7" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D7" s="118" t="s">
+      <c r="D7" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="92" t="s">
+      <c r="E7" s="91" t="s">
         <v>155</v>
       </c>
-      <c r="F7" s="115"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="90"/>
-      <c r="I7" s="94"/>
+      <c r="F7" s="114"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="89"/>
+      <c r="I7" s="93"/>
     </row>
     <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="85" t="s">
+      <c r="B8" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="118" t="s">
+      <c r="C8" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D8" s="118" t="s">
+      <c r="D8" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E8" s="92" t="s">
+      <c r="E8" s="91" t="s">
         <v>156</v>
       </c>
-      <c r="F8" s="115"/>
-      <c r="G8" s="106"/>
-      <c r="H8" s="90"/>
-      <c r="I8" s="94"/>
+      <c r="F8" s="114"/>
+      <c r="G8" s="105"/>
+      <c r="H8" s="89"/>
+      <c r="I8" s="93"/>
     </row>
     <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.3">
-      <c r="B9" s="85" t="s">
+      <c r="B9" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="118" t="s">
+      <c r="C9" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D9" s="118" t="s">
+      <c r="D9" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E9" s="101" t="s">
+      <c r="E9" s="100" t="s">
         <v>157</v>
       </c>
-      <c r="F9" s="115"/>
-      <c r="G9" s="106"/>
-      <c r="H9" s="90"/>
-      <c r="I9" s="94"/>
+      <c r="F9" s="114"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="89"/>
+      <c r="I9" s="93"/>
     </row>
     <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="85" t="s">
+      <c r="B10" s="84" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="118" t="s">
+      <c r="C10" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D10" s="118" t="s">
+      <c r="D10" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E10" s="101" t="s">
+      <c r="E10" s="100" t="s">
         <v>158</v>
       </c>
-      <c r="F10" s="115"/>
-      <c r="G10" s="106"/>
-      <c r="H10" s="90"/>
-      <c r="I10" s="94"/>
+      <c r="F10" s="114"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="89"/>
+      <c r="I10" s="93"/>
     </row>
     <row r="11" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="B11" s="84" t="s">
+      <c r="B11" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="118" t="s">
+      <c r="C11" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D11" s="118" t="s">
+      <c r="D11" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E11" s="101" t="s">
+      <c r="E11" s="100" t="s">
         <v>159</v>
       </c>
-      <c r="F11" s="115"/>
-      <c r="G11" s="106"/>
-      <c r="H11" s="90"/>
-      <c r="I11" s="94"/>
+      <c r="F11" s="114"/>
+      <c r="G11" s="105"/>
+      <c r="H11" s="89"/>
+      <c r="I11" s="93"/>
     </row>
     <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="85" t="s">
+      <c r="B12" s="84" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="118" t="s">
+      <c r="C12" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D12" s="118" t="s">
+      <c r="D12" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E12" s="101" t="s">
+      <c r="E12" s="100" t="s">
         <v>160</v>
       </c>
-      <c r="F12" s="115"/>
-      <c r="G12" s="106"/>
-      <c r="H12" s="90"/>
-      <c r="I12" s="94"/>
+      <c r="F12" s="114"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="89"/>
+      <c r="I12" s="93"/>
     </row>
     <row r="13" spans="1:9" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="85" t="s">
+      <c r="B13" s="84" t="s">
         <v>118</v>
       </c>
-      <c r="C13" s="118" t="s">
+      <c r="C13" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D13" s="118" t="s">
+      <c r="D13" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="101" t="s">
+      <c r="E13" s="100" t="s">
         <v>161</v>
       </c>
-      <c r="F13" s="115"/>
-      <c r="G13" s="106"/>
-      <c r="H13" s="90"/>
-      <c r="I13" s="94"/>
+      <c r="F13" s="114"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="89"/>
+      <c r="I13" s="93"/>
     </row>
     <row r="14" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="86" t="s">
+      <c r="B14" s="85" t="s">
         <v>181</v>
       </c>
-      <c r="C14" s="118" t="s">
+      <c r="C14" s="117" t="s">
         <v>179</v>
       </c>
-      <c r="D14" s="118" t="s">
+      <c r="D14" s="117" t="s">
         <v>180</v>
       </c>
-      <c r="E14" s="101"/>
-      <c r="F14" s="115"/>
-      <c r="G14" s="106"/>
-      <c r="H14" s="90"/>
-      <c r="I14" s="123" t="s">
+      <c r="E14" s="100"/>
+      <c r="F14" s="114"/>
+      <c r="G14" s="105"/>
+      <c r="H14" s="89"/>
+      <c r="I14" s="122" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="86" t="s">
+      <c r="B15" s="85" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="118" t="s">
+      <c r="C15" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D15" s="118" t="s">
+      <c r="D15" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E15" s="101" t="s">
+      <c r="E15" s="100" t="s">
         <v>162</v>
       </c>
-      <c r="F15" s="115"/>
-      <c r="G15" s="106"/>
-      <c r="H15" s="90"/>
-      <c r="I15" s="94"/>
+      <c r="F15" s="114"/>
+      <c r="G15" s="105"/>
+      <c r="H15" s="89"/>
+      <c r="I15" s="93"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="85" t="s">
+      <c r="B16" s="84" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="118" t="s">
+      <c r="C16" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D16" s="118" t="s">
+      <c r="D16" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E16" s="92" t="s">
+      <c r="E16" s="91" t="s">
         <v>163</v>
       </c>
-      <c r="F16" s="115"/>
-      <c r="G16" s="106"/>
-      <c r="H16" s="90"/>
-      <c r="I16" s="94"/>
+      <c r="F16" s="114"/>
+      <c r="G16" s="105"/>
+      <c r="H16" s="89"/>
+      <c r="I16" s="93"/>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="87" t="s">
+      <c r="B17" s="86" t="s">
         <v>141</v>
       </c>
-      <c r="C17" s="118" t="s">
+      <c r="C17" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D17" s="118" t="s">
+      <c r="D17" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E17" s="92" t="s">
+      <c r="E17" s="91" t="s">
         <v>105</v>
       </c>
-      <c r="F17" s="115"/>
-      <c r="G17" s="90"/>
-      <c r="H17" s="90"/>
-      <c r="I17" s="94"/>
+      <c r="F17" s="114"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="93"/>
     </row>
     <row r="18" spans="2:9" ht="27" x14ac:dyDescent="0.3">
-      <c r="B18" s="87" t="s">
+      <c r="B18" s="86" t="s">
         <v>106</v>
       </c>
-      <c r="C18" s="118" t="s">
+      <c r="C18" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D18" s="118" t="s">
+      <c r="D18" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E18" s="101" t="s">
+      <c r="E18" s="100" t="s">
         <v>164</v>
       </c>
-      <c r="F18" s="115"/>
-      <c r="G18" s="106"/>
-      <c r="H18" s="90"/>
-      <c r="I18" s="94"/>
+      <c r="F18" s="114"/>
+      <c r="G18" s="105"/>
+      <c r="H18" s="89"/>
+      <c r="I18" s="93"/>
     </row>
     <row r="19" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="86" t="s">
+      <c r="B19" s="85" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="118" t="s">
+      <c r="C19" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D19" s="118" t="s">
+      <c r="D19" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E19" s="92" t="s">
+      <c r="E19" s="91" t="s">
         <v>139</v>
       </c>
-      <c r="F19" s="115"/>
-      <c r="G19" s="105"/>
-      <c r="H19" s="90"/>
-      <c r="I19" s="94"/>
+      <c r="F19" s="114"/>
+      <c r="G19" s="104"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="93"/>
     </row>
     <row r="20" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="86" t="s">
+      <c r="B20" s="85" t="s">
         <v>167</v>
       </c>
-      <c r="C20" s="118" t="s">
+      <c r="C20" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D20" s="118" t="s">
+      <c r="D20" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="114" t="s">
+      <c r="E20" s="113" t="s">
         <v>169</v>
       </c>
-      <c r="F20" s="115"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="112"/>
-      <c r="I20" s="113"/>
+      <c r="F20" s="114"/>
+      <c r="G20" s="110"/>
+      <c r="H20" s="111"/>
+      <c r="I20" s="112"/>
     </row>
     <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="88" t="s">
+      <c r="B21" s="87" t="s">
         <v>108</v>
       </c>
-      <c r="C21" s="119" t="s">
+      <c r="C21" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D21" s="119" t="s">
+      <c r="D21" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E21" s="104" t="s">
+      <c r="E21" s="103" t="s">
         <v>140</v>
       </c>
-      <c r="F21" s="116"/>
-      <c r="G21" s="107"/>
-      <c r="H21" s="95"/>
-      <c r="I21" s="96"/>
+      <c r="F21" s="115"/>
+      <c r="G21" s="106"/>
+      <c r="H21" s="94"/>
+      <c r="I21" s="95"/>
     </row>
     <row r="22" spans="2:9" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -9615,393 +10022,393 @@
   <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="82" customWidth="1"/>
-    <col min="2" max="2" width="9" style="82"/>
-    <col min="3" max="4" width="14.75" style="82" customWidth="1"/>
-    <col min="5" max="5" width="43" style="82" customWidth="1"/>
-    <col min="6" max="6" width="61.875" style="82" customWidth="1"/>
-    <col min="7" max="9" width="62.125" style="82" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="82"/>
+    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
+    <col min="2" max="2" width="9" style="81"/>
+    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
+    <col min="5" max="5" width="43" style="81" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
+    <col min="7" max="9" width="62.125" style="81" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="81"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="110" t="s">
+      <c r="B1" s="109" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="108"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="174" t="s">
+      <c r="B2" s="176" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="178" t="s">
+      <c r="C2" s="180" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="178" t="s">
+      <c r="D2" s="180" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="176" t="s">
+      <c r="E2" s="178" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="172" t="s">
+      <c r="F2" s="174" t="s">
         <v>227</v>
       </c>
-      <c r="G2" s="172"/>
-      <c r="H2" s="172"/>
-      <c r="I2" s="173"/>
+      <c r="G2" s="174"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="175"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="175"/>
-      <c r="C3" s="179"/>
-      <c r="D3" s="179"/>
-      <c r="E3" s="177"/>
-      <c r="F3" s="98" t="s">
+      <c r="B3" s="177"/>
+      <c r="C3" s="181"/>
+      <c r="D3" s="181"/>
+      <c r="E3" s="179"/>
+      <c r="F3" s="97" t="s">
         <v>114</v>
       </c>
-      <c r="G3" s="98" t="s">
+      <c r="G3" s="97" t="s">
         <v>115</v>
       </c>
-      <c r="H3" s="98" t="s">
+      <c r="H3" s="97" t="s">
         <v>116</v>
       </c>
-      <c r="I3" s="99" t="s">
+      <c r="I3" s="98" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="83" t="s">
+      <c r="B4" s="82" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="116" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="117" t="s">
+      <c r="D4" s="116" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="91" t="s">
+      <c r="E4" s="90" t="s">
         <v>152</v>
       </c>
-      <c r="F4" s="115"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="93"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="92"/>
     </row>
     <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="84" t="s">
+      <c r="B5" s="83" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="118" t="s">
+      <c r="C5" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="118" t="s">
+      <c r="D5" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="92" t="s">
+      <c r="E5" s="91" t="s">
         <v>153</v>
       </c>
-      <c r="F5" s="115"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="90"/>
-      <c r="I5" s="94"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="93"/>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="84" t="s">
+      <c r="B6" s="83" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="118" t="s">
+      <c r="C6" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D6" s="118" t="s">
+      <c r="D6" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E6" s="92" t="s">
+      <c r="E6" s="91" t="s">
         <v>154</v>
       </c>
-      <c r="F6" s="115"/>
-      <c r="G6" s="106"/>
-      <c r="H6" s="90"/>
-      <c r="I6" s="94"/>
+      <c r="F6" s="114"/>
+      <c r="G6" s="105"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="93"/>
     </row>
     <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="84" t="s">
+      <c r="B7" s="83" t="s">
         <v>125</v>
       </c>
-      <c r="C7" s="118" t="s">
+      <c r="C7" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D7" s="118" t="s">
+      <c r="D7" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="92" t="s">
+      <c r="E7" s="91" t="s">
         <v>155</v>
       </c>
-      <c r="F7" s="115"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="90"/>
-      <c r="I7" s="94"/>
+      <c r="F7" s="114"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="89"/>
+      <c r="I7" s="93"/>
     </row>
     <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="85" t="s">
+      <c r="B8" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="118" t="s">
+      <c r="C8" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D8" s="118" t="s">
+      <c r="D8" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E8" s="92" t="s">
+      <c r="E8" s="91" t="s">
         <v>156</v>
       </c>
-      <c r="F8" s="115"/>
-      <c r="G8" s="106"/>
-      <c r="H8" s="90"/>
-      <c r="I8" s="94"/>
+      <c r="F8" s="114"/>
+      <c r="G8" s="105"/>
+      <c r="H8" s="89"/>
+      <c r="I8" s="93"/>
     </row>
     <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.3">
-      <c r="B9" s="85" t="s">
+      <c r="B9" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="118" t="s">
+      <c r="C9" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D9" s="118" t="s">
+      <c r="D9" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E9" s="101" t="s">
+      <c r="E9" s="100" t="s">
         <v>157</v>
       </c>
-      <c r="F9" s="115"/>
-      <c r="G9" s="106"/>
-      <c r="H9" s="90"/>
-      <c r="I9" s="94"/>
+      <c r="F9" s="114"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="89"/>
+      <c r="I9" s="93"/>
     </row>
     <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="85" t="s">
+      <c r="B10" s="84" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="118" t="s">
+      <c r="C10" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D10" s="118" t="s">
+      <c r="D10" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E10" s="101" t="s">
+      <c r="E10" s="100" t="s">
         <v>158</v>
       </c>
-      <c r="F10" s="115"/>
-      <c r="G10" s="106"/>
-      <c r="H10" s="90"/>
-      <c r="I10" s="94"/>
+      <c r="F10" s="114"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="89"/>
+      <c r="I10" s="93"/>
     </row>
     <row r="11" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="B11" s="84" t="s">
+      <c r="B11" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="118" t="s">
+      <c r="C11" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D11" s="118" t="s">
+      <c r="D11" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E11" s="101" t="s">
+      <c r="E11" s="100" t="s">
         <v>159</v>
       </c>
-      <c r="F11" s="115"/>
-      <c r="G11" s="106"/>
-      <c r="H11" s="90"/>
-      <c r="I11" s="94"/>
+      <c r="F11" s="114"/>
+      <c r="G11" s="105"/>
+      <c r="H11" s="89"/>
+      <c r="I11" s="93"/>
     </row>
     <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="85" t="s">
+      <c r="B12" s="84" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="118" t="s">
+      <c r="C12" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D12" s="118" t="s">
+      <c r="D12" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E12" s="101" t="s">
+      <c r="E12" s="100" t="s">
         <v>160</v>
       </c>
-      <c r="F12" s="115"/>
-      <c r="G12" s="106"/>
-      <c r="H12" s="90"/>
-      <c r="I12" s="94"/>
+      <c r="F12" s="114"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="89"/>
+      <c r="I12" s="93"/>
     </row>
     <row r="13" spans="1:9" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="85" t="s">
+      <c r="B13" s="84" t="s">
         <v>118</v>
       </c>
-      <c r="C13" s="118" t="s">
+      <c r="C13" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D13" s="118" t="s">
+      <c r="D13" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="101" t="s">
+      <c r="E13" s="100" t="s">
         <v>161</v>
       </c>
-      <c r="F13" s="115"/>
-      <c r="G13" s="106"/>
-      <c r="H13" s="90"/>
-      <c r="I13" s="94"/>
+      <c r="F13" s="114"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="89"/>
+      <c r="I13" s="93"/>
     </row>
     <row r="14" spans="1:9" ht="337.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="86" t="s">
+      <c r="B14" s="85" t="s">
         <v>181</v>
       </c>
-      <c r="C14" s="118" t="s">
+      <c r="C14" s="117" t="s">
         <v>179</v>
       </c>
-      <c r="D14" s="118" t="s">
+      <c r="D14" s="117" t="s">
         <v>180</v>
       </c>
-      <c r="E14" s="101"/>
-      <c r="F14" s="124" t="s">
+      <c r="E14" s="100"/>
+      <c r="F14" s="123" t="s">
         <v>229</v>
       </c>
-      <c r="G14" s="124" t="s">
+      <c r="G14" s="123" t="s">
         <v>230</v>
       </c>
-      <c r="H14" s="124" t="s">
+      <c r="H14" s="123" t="s">
         <v>231</v>
       </c>
-      <c r="I14" s="124" t="s">
+      <c r="I14" s="123" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="86" t="s">
+      <c r="B15" s="85" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="118" t="s">
+      <c r="C15" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D15" s="118" t="s">
+      <c r="D15" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E15" s="101" t="s">
+      <c r="E15" s="100" t="s">
         <v>162</v>
       </c>
-      <c r="F15" s="115"/>
-      <c r="G15" s="106"/>
-      <c r="H15" s="90"/>
-      <c r="I15" s="94"/>
+      <c r="F15" s="114"/>
+      <c r="G15" s="105"/>
+      <c r="H15" s="89"/>
+      <c r="I15" s="93"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="85" t="s">
+      <c r="B16" s="84" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="118" t="s">
+      <c r="C16" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D16" s="118" t="s">
+      <c r="D16" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E16" s="92" t="s">
+      <c r="E16" s="91" t="s">
         <v>163</v>
       </c>
-      <c r="F16" s="115"/>
-      <c r="G16" s="106"/>
-      <c r="H16" s="90"/>
-      <c r="I16" s="94"/>
+      <c r="F16" s="114"/>
+      <c r="G16" s="105"/>
+      <c r="H16" s="89"/>
+      <c r="I16" s="93"/>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="87" t="s">
+      <c r="B17" s="86" t="s">
         <v>141</v>
       </c>
-      <c r="C17" s="118" t="s">
+      <c r="C17" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D17" s="118" t="s">
+      <c r="D17" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E17" s="92" t="s">
+      <c r="E17" s="91" t="s">
         <v>105</v>
       </c>
-      <c r="F17" s="115"/>
-      <c r="G17" s="90"/>
-      <c r="H17" s="90"/>
-      <c r="I17" s="94"/>
+      <c r="F17" s="114"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="93"/>
     </row>
     <row r="18" spans="2:9" ht="27" x14ac:dyDescent="0.3">
-      <c r="B18" s="87" t="s">
+      <c r="B18" s="86" t="s">
         <v>106</v>
       </c>
-      <c r="C18" s="118" t="s">
+      <c r="C18" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D18" s="118" t="s">
+      <c r="D18" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E18" s="101" t="s">
+      <c r="E18" s="100" t="s">
         <v>164</v>
       </c>
-      <c r="F18" s="115"/>
-      <c r="G18" s="106"/>
-      <c r="H18" s="90"/>
-      <c r="I18" s="94"/>
+      <c r="F18" s="114"/>
+      <c r="G18" s="105"/>
+      <c r="H18" s="89"/>
+      <c r="I18" s="93"/>
     </row>
     <row r="19" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="86" t="s">
+      <c r="B19" s="85" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="118" t="s">
+      <c r="C19" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D19" s="118" t="s">
+      <c r="D19" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E19" s="92" t="s">
+      <c r="E19" s="91" t="s">
         <v>139</v>
       </c>
-      <c r="F19" s="115"/>
-      <c r="G19" s="105"/>
-      <c r="H19" s="90"/>
-      <c r="I19" s="94"/>
+      <c r="F19" s="114"/>
+      <c r="G19" s="104"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="93"/>
     </row>
     <row r="20" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="86" t="s">
+      <c r="B20" s="85" t="s">
         <v>167</v>
       </c>
-      <c r="C20" s="118" t="s">
+      <c r="C20" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="D20" s="118" t="s">
+      <c r="D20" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="114" t="s">
+      <c r="E20" s="113" t="s">
         <v>169</v>
       </c>
-      <c r="F20" s="115"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="112"/>
-      <c r="I20" s="113"/>
+      <c r="F20" s="114"/>
+      <c r="G20" s="110"/>
+      <c r="H20" s="111"/>
+      <c r="I20" s="112"/>
     </row>
     <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="88" t="s">
+      <c r="B21" s="87" t="s">
         <v>108</v>
       </c>
-      <c r="C21" s="119" t="s">
+      <c r="C21" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="D21" s="119" t="s">
+      <c r="D21" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E21" s="104" t="s">
+      <c r="E21" s="103" t="s">
         <v>140</v>
       </c>
-      <c r="F21" s="116"/>
-      <c r="G21" s="107"/>
-      <c r="H21" s="95"/>
-      <c r="I21" s="96"/>
+      <c r="F21" s="115"/>
+      <c r="G21" s="106"/>
+      <c r="H21" s="94"/>
+      <c r="I21" s="95"/>
     </row>
     <row r="22" spans="2:9" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -10022,411 +10429,411 @@
   <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="82" customWidth="1"/>
-    <col min="2" max="2" width="9" style="82"/>
-    <col min="3" max="4" width="14.75" style="82" customWidth="1"/>
-    <col min="5" max="5" width="43" style="82" customWidth="1"/>
-    <col min="6" max="6" width="61.875" style="82" customWidth="1"/>
-    <col min="7" max="9" width="62.125" style="82" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="82"/>
+    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
+    <col min="2" max="2" width="9" style="81"/>
+    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
+    <col min="5" max="5" width="43" style="81" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
+    <col min="7" max="9" width="62.125" style="81" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="81"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="110" t="s">
+      <c r="B1" s="109" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="108"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="174" t="s">
+      <c r="B2" s="176" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="178" t="s">
+      <c r="C2" s="180" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="178" t="s">
+      <c r="D2" s="180" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="176" t="s">
+      <c r="E2" s="178" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="172" t="s">
+      <c r="F2" s="174" t="s">
         <v>259</v>
       </c>
-      <c r="G2" s="172"/>
-      <c r="H2" s="172"/>
-      <c r="I2" s="173"/>
+      <c r="G2" s="174"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="175"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="175"/>
-      <c r="C3" s="179"/>
-      <c r="D3" s="179"/>
-      <c r="E3" s="177"/>
-      <c r="F3" s="98" t="s">
+      <c r="B3" s="177"/>
+      <c r="C3" s="181"/>
+      <c r="D3" s="181"/>
+      <c r="E3" s="179"/>
+      <c r="F3" s="97" t="s">
         <v>280</v>
       </c>
-      <c r="G3" s="98" t="s">
+      <c r="G3" s="97" t="s">
         <v>299</v>
       </c>
-      <c r="H3" s="98" t="s">
+      <c r="H3" s="97" t="s">
         <v>298</v>
       </c>
-      <c r="I3" s="99" t="s">
+      <c r="I3" s="98" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="152" t="s">
+      <c r="B4" s="151" t="s">
         <v>108</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="116" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="117" t="s">
+      <c r="D4" s="116" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="141" t="s">
+      <c r="E4" s="140" t="s">
         <v>140</v>
       </c>
-      <c r="F4" s="142"/>
-      <c r="G4" s="143"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="93"/>
+      <c r="F4" s="141"/>
+      <c r="G4" s="142"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="92"/>
     </row>
     <row r="5" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="B5" s="155" t="s">
+      <c r="B5" s="154" t="s">
         <v>181</v>
       </c>
-      <c r="C5" s="118" t="s">
+      <c r="C5" s="117" t="s">
         <v>270</v>
       </c>
-      <c r="D5" s="118" t="s">
+      <c r="D5" s="117" t="s">
         <v>180</v>
       </c>
-      <c r="E5" s="101" t="s">
+      <c r="E5" s="100" t="s">
         <v>161</v>
       </c>
-      <c r="F5" s="115"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="124" t="s">
+      <c r="F5" s="114"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="123" t="s">
         <v>293</v>
       </c>
-      <c r="I5" s="136" t="s">
+      <c r="I5" s="135" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="153" t="s">
+      <c r="B6" s="152" t="s">
         <v>278</v>
       </c>
-      <c r="C6" s="118" t="s">
+      <c r="C6" s="117" t="s">
         <v>271</v>
       </c>
-      <c r="D6" s="118" t="s">
+      <c r="D6" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E6" s="101" t="s">
+      <c r="E6" s="100" t="s">
         <v>161</v>
       </c>
-      <c r="F6" s="124"/>
-      <c r="G6" s="124"/>
-      <c r="H6" s="134" t="s">
+      <c r="F6" s="123"/>
+      <c r="G6" s="123"/>
+      <c r="H6" s="133" t="s">
         <v>292</v>
       </c>
-      <c r="I6" s="157"/>
+      <c r="I6" s="156"/>
     </row>
     <row r="7" spans="1:9" ht="93" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="153" t="s">
+      <c r="B7" s="152" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="118" t="s">
+      <c r="C7" s="117" t="s">
         <v>272</v>
       </c>
-      <c r="D7" s="118" t="s">
+      <c r="D7" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="101" t="s">
+      <c r="E7" s="100" t="s">
         <v>283</v>
       </c>
-      <c r="F7" s="115"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="90"/>
-      <c r="I7" s="135" t="s">
+      <c r="F7" s="114"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="89"/>
+      <c r="I7" s="134" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="87.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="153" t="s">
+      <c r="B8" s="152" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="118" t="s">
+      <c r="C8" s="117" t="s">
         <v>271</v>
       </c>
-      <c r="D8" s="118" t="s">
+      <c r="D8" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E8" s="101" t="s">
+      <c r="E8" s="100" t="s">
         <v>282</v>
       </c>
-      <c r="F8" s="115"/>
-      <c r="G8" s="105"/>
-      <c r="H8" s="90"/>
-      <c r="I8" s="135" t="s">
+      <c r="F8" s="114"/>
+      <c r="G8" s="104"/>
+      <c r="H8" s="89"/>
+      <c r="I8" s="134" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="154" t="s">
+      <c r="B9" s="153" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="118" t="s">
+      <c r="C9" s="117" t="s">
         <v>271</v>
       </c>
-      <c r="D9" s="118" t="s">
+      <c r="D9" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E9" s="92" t="s">
+      <c r="E9" s="91" t="s">
         <v>152</v>
       </c>
-      <c r="F9" s="115"/>
-      <c r="G9" s="106"/>
-      <c r="H9" s="139"/>
-      <c r="I9" s="94"/>
+      <c r="F9" s="114"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="138"/>
+      <c r="I9" s="93"/>
     </row>
     <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="154" t="s">
+      <c r="B10" s="153" t="s">
         <v>123</v>
       </c>
-      <c r="C10" s="118" t="s">
+      <c r="C10" s="117" t="s">
         <v>271</v>
       </c>
-      <c r="D10" s="118" t="s">
+      <c r="D10" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E10" s="92" t="s">
+      <c r="E10" s="91" t="s">
         <v>153</v>
       </c>
-      <c r="F10" s="115"/>
-      <c r="G10" s="106"/>
-      <c r="H10" s="90"/>
-      <c r="I10" s="94"/>
+      <c r="F10" s="114"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="89"/>
+      <c r="I10" s="93"/>
     </row>
     <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="154" t="s">
+      <c r="B11" s="153" t="s">
         <v>124</v>
       </c>
-      <c r="C11" s="118" t="s">
+      <c r="C11" s="117" t="s">
         <v>271</v>
       </c>
-      <c r="D11" s="118" t="s">
+      <c r="D11" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E11" s="92" t="s">
+      <c r="E11" s="91" t="s">
         <v>154</v>
       </c>
-      <c r="F11" s="115"/>
-      <c r="G11" s="106"/>
-      <c r="H11" s="90"/>
-      <c r="I11" s="94"/>
+      <c r="F11" s="114"/>
+      <c r="G11" s="105"/>
+      <c r="H11" s="89"/>
+      <c r="I11" s="93"/>
     </row>
     <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="154" t="s">
+      <c r="B12" s="153" t="s">
         <v>125</v>
       </c>
-      <c r="C12" s="118" t="s">
+      <c r="C12" s="117" t="s">
         <v>271</v>
       </c>
-      <c r="D12" s="118" t="s">
+      <c r="D12" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E12" s="92" t="s">
+      <c r="E12" s="91" t="s">
         <v>155</v>
       </c>
-      <c r="F12" s="115"/>
-      <c r="G12" s="106"/>
-      <c r="H12" s="139"/>
-      <c r="I12" s="94"/>
+      <c r="F12" s="114"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="138"/>
+      <c r="I12" s="93"/>
     </row>
     <row r="13" spans="1:9" ht="222" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="133" t="s">
+      <c r="B13" s="132" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="118" t="s">
+      <c r="C13" s="117" t="s">
         <v>273</v>
       </c>
-      <c r="D13" s="118" t="s">
+      <c r="D13" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="101" t="s">
+      <c r="E13" s="100" t="s">
         <v>263</v>
       </c>
-      <c r="F13" s="115"/>
-      <c r="G13" s="106"/>
-      <c r="H13" s="134" t="s">
+      <c r="F13" s="114"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="133" t="s">
         <v>288</v>
       </c>
-      <c r="I13" s="135" t="s">
+      <c r="I13" s="134" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="132" t="s">
+      <c r="B14" s="131" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="118" t="s">
+      <c r="C14" s="117" t="s">
         <v>273</v>
       </c>
-      <c r="D14" s="118" t="s">
+      <c r="D14" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E14" s="101" t="s">
+      <c r="E14" s="100" t="s">
         <v>264</v>
       </c>
-      <c r="F14" s="115"/>
-      <c r="G14" s="106"/>
-      <c r="H14" s="134" t="s">
+      <c r="F14" s="114"/>
+      <c r="G14" s="105"/>
+      <c r="H14" s="133" t="s">
         <v>285</v>
       </c>
-      <c r="I14" s="135" t="s">
+      <c r="I14" s="134" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="B15" s="132" t="s">
+      <c r="B15" s="131" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="118" t="s">
+      <c r="C15" s="117" t="s">
         <v>274</v>
       </c>
-      <c r="D15" s="118" t="s">
+      <c r="D15" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E15" s="101" t="s">
+      <c r="E15" s="100" t="s">
         <v>262</v>
       </c>
-      <c r="F15" s="115"/>
-      <c r="G15" s="134" t="s">
+      <c r="F15" s="114"/>
+      <c r="G15" s="133" t="s">
         <v>268</v>
       </c>
-      <c r="H15" s="138" t="s">
+      <c r="H15" s="137" t="s">
         <v>286</v>
       </c>
-      <c r="I15" s="160" t="s">
+      <c r="I15" s="159" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="228.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="132" t="s">
+      <c r="B16" s="131" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="118" t="s">
+      <c r="C16" s="117" t="s">
         <v>275</v>
       </c>
-      <c r="D16" s="118" t="s">
+      <c r="D16" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E16" s="101" t="s">
+      <c r="E16" s="100" t="s">
         <v>265</v>
       </c>
-      <c r="F16" s="115"/>
-      <c r="G16" s="106"/>
-      <c r="H16" s="134" t="s">
+      <c r="F16" s="114"/>
+      <c r="G16" s="105"/>
+      <c r="H16" s="133" t="s">
         <v>290</v>
       </c>
-      <c r="I16" s="135" t="s">
+      <c r="I16" s="134" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="131" t="s">
+      <c r="B17" s="130" t="s">
         <v>167</v>
       </c>
-      <c r="C17" s="118" t="s">
+      <c r="C17" s="117" t="s">
         <v>273</v>
       </c>
-      <c r="D17" s="118" t="s">
+      <c r="D17" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E17" s="114" t="s">
+      <c r="E17" s="113" t="s">
         <v>269</v>
       </c>
-      <c r="F17" s="115"/>
-      <c r="G17" s="130" t="s">
+      <c r="F17" s="114"/>
+      <c r="G17" s="129" t="s">
         <v>260</v>
       </c>
-      <c r="H17" s="156" t="s">
+      <c r="H17" s="155" t="s">
+        <v>312</v>
+      </c>
+      <c r="I17" s="136" t="s">
         <v>313</v>
       </c>
-      <c r="I17" s="137" t="s">
-        <v>314</v>
-      </c>
     </row>
     <row r="18" spans="2:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="132" t="s">
+      <c r="B18" s="131" t="s">
         <v>141</v>
       </c>
-      <c r="C18" s="118" t="s">
+      <c r="C18" s="117" t="s">
         <v>276</v>
       </c>
-      <c r="D18" s="118" t="s">
+      <c r="D18" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E18" s="114" t="s">
+      <c r="E18" s="113" t="s">
         <v>281</v>
       </c>
-      <c r="F18" s="115"/>
-      <c r="G18" s="130"/>
-      <c r="H18" s="134"/>
-      <c r="I18" s="137"/>
+      <c r="F18" s="114"/>
+      <c r="G18" s="129"/>
+      <c r="H18" s="133"/>
+      <c r="I18" s="136"/>
     </row>
     <row r="19" spans="2:9" ht="108" x14ac:dyDescent="0.3">
-      <c r="B19" s="151" t="s">
+      <c r="B19" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="140" t="s">
+      <c r="C19" s="139" t="s">
         <v>273</v>
       </c>
-      <c r="D19" s="140" t="s">
+      <c r="D19" s="139" t="s">
         <v>178</v>
       </c>
-      <c r="E19" s="92" t="s">
+      <c r="E19" s="91" t="s">
         <v>156</v>
       </c>
-      <c r="F19" s="115"/>
-      <c r="G19" s="134" t="s">
+      <c r="F19" s="114"/>
+      <c r="G19" s="133" t="s">
         <v>267</v>
       </c>
-      <c r="H19" s="134" t="s">
+      <c r="H19" s="133" t="s">
         <v>287</v>
       </c>
-      <c r="I19" s="135" t="s">
+      <c r="I19" s="134" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="144" t="s">
+      <c r="B20" s="143" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="145" t="s">
+      <c r="C20" s="144" t="s">
         <v>277</v>
       </c>
-      <c r="D20" s="145" t="s">
+      <c r="D20" s="144" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="146" t="s">
+      <c r="E20" s="145" t="s">
         <v>261</v>
       </c>
-      <c r="F20" s="147"/>
-      <c r="G20" s="148" t="s">
+      <c r="F20" s="146"/>
+      <c r="G20" s="147" t="s">
         <v>266</v>
       </c>
-      <c r="H20" s="149"/>
-      <c r="I20" s="150"/>
+      <c r="H20" s="148"/>
+      <c r="I20" s="149"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -10447,410 +10854,413 @@
   <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="82" customWidth="1"/>
-    <col min="2" max="2" width="9" style="82"/>
-    <col min="3" max="4" width="14.75" style="82" customWidth="1"/>
-    <col min="5" max="5" width="43" style="82" customWidth="1"/>
-    <col min="6" max="6" width="61.875" style="82" customWidth="1"/>
-    <col min="7" max="9" width="62.125" style="82" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="82"/>
+    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
+    <col min="2" max="2" width="9" style="81"/>
+    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
+    <col min="5" max="5" width="43" style="81" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
+    <col min="7" max="9" width="62.125" style="81" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="81"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="110" t="s">
+      <c r="B1" s="109" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="108"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="174" t="s">
+      <c r="B2" s="176" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="178" t="s">
+      <c r="C2" s="180" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="178" t="s">
+      <c r="D2" s="180" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="176" t="s">
+      <c r="E2" s="178" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="172" t="s">
+      <c r="F2" s="174" t="s">
         <v>279</v>
       </c>
-      <c r="G2" s="172"/>
-      <c r="H2" s="172"/>
-      <c r="I2" s="173"/>
+      <c r="G2" s="174"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="175"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="175"/>
-      <c r="C3" s="179"/>
-      <c r="D3" s="179"/>
-      <c r="E3" s="177"/>
-      <c r="F3" s="98" t="s">
+      <c r="B3" s="177"/>
+      <c r="C3" s="181"/>
+      <c r="D3" s="181"/>
+      <c r="E3" s="179"/>
+      <c r="F3" s="97" t="s">
         <v>300</v>
       </c>
-      <c r="G3" s="98" t="s">
+      <c r="G3" s="97" t="s">
         <v>301</v>
       </c>
-      <c r="H3" s="98" t="s">
+      <c r="H3" s="97" t="s">
         <v>302</v>
       </c>
-      <c r="I3" s="99" t="s">
+      <c r="I3" s="98" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="152" t="s">
+      <c r="B4" s="151" t="s">
         <v>108</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="116" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="117" t="s">
+      <c r="D4" s="116" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="141" t="s">
+      <c r="E4" s="140" t="s">
         <v>140</v>
       </c>
-      <c r="F4" s="142"/>
-      <c r="G4" s="143"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="93"/>
+      <c r="F4" s="141"/>
+      <c r="G4" s="142"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="92"/>
     </row>
     <row r="5" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="B5" s="155" t="s">
+      <c r="B5" s="154" t="s">
         <v>181</v>
       </c>
-      <c r="C5" s="118" t="s">
+      <c r="C5" s="117" t="s">
         <v>270</v>
       </c>
-      <c r="D5" s="118" t="s">
+      <c r="D5" s="117" t="s">
         <v>180</v>
       </c>
-      <c r="E5" s="101" t="s">
+      <c r="E5" s="100" t="s">
         <v>161</v>
       </c>
-      <c r="F5" s="124" t="s">
+      <c r="F5" s="123" t="s">
         <v>304</v>
       </c>
-      <c r="G5" s="158"/>
-      <c r="H5" s="124"/>
-      <c r="I5" s="136"/>
+      <c r="G5" s="157"/>
+      <c r="H5" s="123"/>
+      <c r="I5" s="135"/>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="153" t="s">
+      <c r="B6" s="152" t="s">
         <v>278</v>
       </c>
-      <c r="C6" s="118" t="s">
+      <c r="C6" s="117" t="s">
         <v>271</v>
       </c>
-      <c r="D6" s="118" t="s">
+      <c r="D6" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E6" s="101" t="s">
+      <c r="E6" s="100" t="s">
         <v>161</v>
       </c>
-      <c r="F6" s="124"/>
-      <c r="G6" s="124"/>
-      <c r="H6" s="124"/>
-      <c r="I6" s="136"/>
+      <c r="F6" s="123"/>
+      <c r="G6" s="123"/>
+      <c r="H6" s="123"/>
+      <c r="I6" s="135"/>
     </row>
     <row r="7" spans="1:9" ht="138" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="153" t="s">
+      <c r="B7" s="152" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="118" t="s">
+      <c r="C7" s="117" t="s">
         <v>272</v>
       </c>
-      <c r="D7" s="118" t="s">
+      <c r="D7" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="101" t="s">
+      <c r="E7" s="100" t="s">
         <v>162</v>
       </c>
-      <c r="F7" s="124" t="s">
-        <v>312</v>
-      </c>
-      <c r="G7" s="106" t="s">
+      <c r="F7" s="123" t="s">
+        <v>311</v>
+      </c>
+      <c r="G7" s="105" t="s">
+        <v>342</v>
+      </c>
+      <c r="H7" s="89"/>
+      <c r="I7" s="93"/>
+    </row>
+    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="152" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="117" t="s">
+        <v>271</v>
+      </c>
+      <c r="D8" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E8" s="91" t="s">
+        <v>139</v>
+      </c>
+      <c r="F8" s="114"/>
+      <c r="G8" s="104"/>
+      <c r="H8" s="89"/>
+      <c r="I8" s="93"/>
+    </row>
+    <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="153" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="117" t="s">
+        <v>271</v>
+      </c>
+      <c r="D9" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E9" s="91" t="s">
+        <v>152</v>
+      </c>
+      <c r="F9" s="114"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="138"/>
+      <c r="I9" s="93"/>
+    </row>
+    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="153" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" s="117" t="s">
+        <v>271</v>
+      </c>
+      <c r="D10" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E10" s="91" t="s">
+        <v>153</v>
+      </c>
+      <c r="F10" s="114"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="138"/>
+      <c r="I10" s="93"/>
+    </row>
+    <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="153" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" s="117" t="s">
+        <v>271</v>
+      </c>
+      <c r="D11" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E11" s="91" t="s">
+        <v>154</v>
+      </c>
+      <c r="F11" s="114"/>
+      <c r="G11" s="105"/>
+      <c r="H11" s="138"/>
+      <c r="I11" s="93"/>
+    </row>
+    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="153" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" s="117" t="s">
+        <v>271</v>
+      </c>
+      <c r="D12" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E12" s="91" t="s">
+        <v>155</v>
+      </c>
+      <c r="F12" s="114"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="138"/>
+      <c r="I12" s="93"/>
+    </row>
+    <row r="13" spans="1:9" ht="243" x14ac:dyDescent="0.3">
+      <c r="B13" s="132" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="117" t="s">
+        <v>273</v>
+      </c>
+      <c r="D13" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E13" s="100" t="s">
+        <v>263</v>
+      </c>
+      <c r="F13" s="133" t="s">
+        <v>318</v>
+      </c>
+      <c r="G13" s="157" t="s">
+        <v>343</v>
+      </c>
+      <c r="H13" s="105" t="s">
+        <v>324</v>
+      </c>
+      <c r="I13" s="134"/>
+    </row>
+    <row r="14" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="B14" s="131" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="117" t="s">
+        <v>273</v>
+      </c>
+      <c r="D14" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E14" s="100" t="s">
+        <v>264</v>
+      </c>
+      <c r="F14" s="133" t="s">
         <v>310</v>
       </c>
-      <c r="H7" s="90"/>
-      <c r="I7" s="94"/>
-    </row>
-    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="153" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8" s="118" t="s">
-        <v>271</v>
-      </c>
-      <c r="D8" s="118" t="s">
+      <c r="G14" s="157" t="s">
+        <v>344</v>
+      </c>
+      <c r="H14" s="105" t="s">
+        <v>336</v>
+      </c>
+      <c r="I14" s="122" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="162" x14ac:dyDescent="0.3">
+      <c r="B15" s="131" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="117" t="s">
+        <v>274</v>
+      </c>
+      <c r="D15" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E8" s="92" t="s">
-        <v>139</v>
-      </c>
-      <c r="F8" s="115"/>
-      <c r="G8" s="105"/>
-      <c r="H8" s="90"/>
-      <c r="I8" s="94"/>
-    </row>
-    <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="154" t="s">
-        <v>117</v>
-      </c>
-      <c r="C9" s="118" t="s">
-        <v>271</v>
-      </c>
-      <c r="D9" s="118" t="s">
+      <c r="E15" s="100" t="s">
+        <v>262</v>
+      </c>
+      <c r="F15" s="133" t="s">
+        <v>319</v>
+      </c>
+      <c r="G15" s="133" t="s">
+        <v>319</v>
+      </c>
+      <c r="H15" s="163" t="s">
+        <v>323</v>
+      </c>
+      <c r="I15" s="134"/>
+    </row>
+    <row r="16" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="B16" s="131" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="117" t="s">
+        <v>275</v>
+      </c>
+      <c r="D16" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E9" s="92" t="s">
-        <v>152</v>
-      </c>
-      <c r="F9" s="115"/>
-      <c r="G9" s="106"/>
-      <c r="H9" s="139"/>
-      <c r="I9" s="94"/>
-    </row>
-    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="154" t="s">
-        <v>123</v>
-      </c>
-      <c r="C10" s="118" t="s">
-        <v>271</v>
-      </c>
-      <c r="D10" s="118" t="s">
+      <c r="E16" s="100" t="s">
+        <v>265</v>
+      </c>
+      <c r="F16" s="133" t="s">
+        <v>320</v>
+      </c>
+      <c r="G16" s="157" t="s">
+        <v>345</v>
+      </c>
+      <c r="H16" s="157" t="s">
+        <v>340</v>
+      </c>
+      <c r="I16" s="134"/>
+    </row>
+    <row r="17" spans="2:9" ht="162" x14ac:dyDescent="0.3">
+      <c r="B17" s="130" t="s">
+        <v>167</v>
+      </c>
+      <c r="C17" s="117" t="s">
+        <v>273</v>
+      </c>
+      <c r="D17" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E10" s="92" t="s">
-        <v>153</v>
-      </c>
-      <c r="F10" s="115"/>
-      <c r="G10" s="106"/>
-      <c r="H10" s="139"/>
-      <c r="I10" s="94"/>
-    </row>
-    <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="154" t="s">
-        <v>124</v>
-      </c>
-      <c r="C11" s="118" t="s">
-        <v>271</v>
-      </c>
-      <c r="D11" s="118" t="s">
+      <c r="E17" s="113" t="s">
+        <v>307</v>
+      </c>
+      <c r="F17" s="155" t="s">
+        <v>321</v>
+      </c>
+      <c r="G17" s="119" t="s">
+        <v>346</v>
+      </c>
+      <c r="H17" s="163" t="s">
+        <v>341</v>
+      </c>
+      <c r="I17" s="136"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B18" s="131" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" s="117" t="s">
+        <v>276</v>
+      </c>
+      <c r="D18" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E11" s="92" t="s">
-        <v>154</v>
-      </c>
-      <c r="F11" s="115"/>
-      <c r="G11" s="106"/>
-      <c r="H11" s="139"/>
-      <c r="I11" s="94"/>
-    </row>
-    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="154" t="s">
-        <v>125</v>
-      </c>
-      <c r="C12" s="118" t="s">
-        <v>271</v>
-      </c>
-      <c r="D12" s="118" t="s">
+      <c r="E18" s="113"/>
+      <c r="F18" s="155"/>
+      <c r="G18" s="133"/>
+      <c r="H18" s="133"/>
+      <c r="I18" s="136"/>
+    </row>
+    <row r="19" spans="2:9" ht="54" x14ac:dyDescent="0.3">
+      <c r="B19" s="150" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="139" t="s">
+        <v>273</v>
+      </c>
+      <c r="D19" s="139" t="s">
         <v>178</v>
       </c>
-      <c r="E12" s="92" t="s">
-        <v>155</v>
-      </c>
-      <c r="F12" s="115"/>
-      <c r="G12" s="106"/>
-      <c r="H12" s="139"/>
-      <c r="I12" s="94"/>
-    </row>
-    <row r="13" spans="1:9" ht="243" x14ac:dyDescent="0.3">
-      <c r="B13" s="133" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" s="118" t="s">
-        <v>273</v>
-      </c>
-      <c r="D13" s="118" t="s">
+      <c r="E19" s="91" t="s">
+        <v>156</v>
+      </c>
+      <c r="F19" s="133" t="s">
+        <v>289</v>
+      </c>
+      <c r="G19" s="158" t="s">
+        <v>289</v>
+      </c>
+      <c r="H19" s="137" t="s">
+        <v>347</v>
+      </c>
+      <c r="I19" s="93"/>
+    </row>
+    <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="143" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="144" t="s">
+        <v>277</v>
+      </c>
+      <c r="D20" s="144" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="101" t="s">
-        <v>263</v>
-      </c>
-      <c r="F13" s="134" t="s">
-        <v>321</v>
-      </c>
-      <c r="G13" s="158" t="s">
-        <v>322</v>
-      </c>
-      <c r="H13" s="106" t="s">
-        <v>333</v>
-      </c>
-      <c r="I13" s="135"/>
-    </row>
-    <row r="14" spans="1:9" ht="405" x14ac:dyDescent="0.3">
-      <c r="B14" s="132" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="118" t="s">
-        <v>273</v>
-      </c>
-      <c r="D14" s="118" t="s">
-        <v>178</v>
-      </c>
-      <c r="E14" s="101" t="s">
-        <v>264</v>
-      </c>
-      <c r="F14" s="134" t="s">
-        <v>311</v>
-      </c>
-      <c r="G14" s="158" t="s">
-        <v>326</v>
-      </c>
-      <c r="H14" s="106" t="s">
-        <v>328</v>
-      </c>
-      <c r="I14" s="123" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="162" x14ac:dyDescent="0.3">
-      <c r="B15" s="132" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="118" t="s">
-        <v>274</v>
-      </c>
-      <c r="D15" s="118" t="s">
-        <v>178</v>
-      </c>
-      <c r="E15" s="101" t="s">
-        <v>262</v>
-      </c>
-      <c r="F15" s="134" t="s">
-        <v>323</v>
-      </c>
-      <c r="G15" s="134" t="s">
-        <v>323</v>
-      </c>
-      <c r="H15" s="164" t="s">
-        <v>329</v>
-      </c>
-      <c r="I15" s="135"/>
-    </row>
-    <row r="16" spans="1:9" ht="405" x14ac:dyDescent="0.3">
-      <c r="B16" s="132" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" s="118" t="s">
-        <v>275</v>
-      </c>
-      <c r="D16" s="118" t="s">
-        <v>178</v>
-      </c>
-      <c r="E16" s="101" t="s">
-        <v>265</v>
-      </c>
-      <c r="F16" s="134" t="s">
-        <v>324</v>
-      </c>
-      <c r="G16" s="158" t="s">
-        <v>332</v>
-      </c>
-      <c r="H16" s="158" t="s">
-        <v>330</v>
-      </c>
-      <c r="I16" s="135"/>
-    </row>
-    <row r="17" spans="2:9" ht="135" x14ac:dyDescent="0.3">
-      <c r="B17" s="131" t="s">
-        <v>167</v>
-      </c>
-      <c r="C17" s="118" t="s">
-        <v>273</v>
-      </c>
-      <c r="D17" s="118" t="s">
-        <v>178</v>
-      </c>
-      <c r="E17" s="114" t="s">
-        <v>307</v>
-      </c>
-      <c r="F17" s="156" t="s">
-        <v>325</v>
-      </c>
-      <c r="G17" s="120" t="s">
-        <v>316</v>
-      </c>
-      <c r="H17" s="164" t="s">
-        <v>331</v>
-      </c>
-      <c r="I17" s="137"/>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="132" t="s">
-        <v>141</v>
-      </c>
-      <c r="C18" s="118" t="s">
-        <v>276</v>
-      </c>
-      <c r="D18" s="118" t="s">
-        <v>178</v>
-      </c>
-      <c r="E18" s="114"/>
-      <c r="F18" s="156"/>
-      <c r="G18" s="134"/>
-      <c r="H18" s="134"/>
-      <c r="I18" s="137"/>
-    </row>
-    <row r="19" spans="2:9" ht="54" x14ac:dyDescent="0.3">
-      <c r="B19" s="151" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="140" t="s">
-        <v>273</v>
-      </c>
-      <c r="D19" s="140" t="s">
-        <v>178</v>
-      </c>
-      <c r="E19" s="92" t="s">
-        <v>156</v>
-      </c>
-      <c r="F19" s="134" t="s">
-        <v>289</v>
-      </c>
-      <c r="G19" s="159" t="s">
-        <v>289</v>
-      </c>
-      <c r="I19" s="94"/>
-    </row>
-    <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="144" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="145" t="s">
-        <v>277</v>
-      </c>
-      <c r="D20" s="145" t="s">
-        <v>178</v>
-      </c>
-      <c r="E20" s="146" t="s">
+      <c r="E20" s="145" t="s">
         <v>261</v>
       </c>
-      <c r="F20" s="162" t="s">
-        <v>315</v>
-      </c>
-      <c r="G20" s="148"/>
-      <c r="H20" s="149"/>
-      <c r="I20" s="150"/>
+      <c r="F20" s="161" t="s">
+        <v>314</v>
+      </c>
+      <c r="G20" s="147"/>
+      <c r="H20" s="148"/>
+      <c r="I20" s="149"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -3156,11 +3156,870 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>[우리산업]
+기구 : 공준석, 강명준</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[우리산업]
+기구 : 공준석, 강명준</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALL Drawing
+4/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Proto
+10/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LP2
+10/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOP
+1/2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALL Drawing
+6/30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HE1i LHD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HE1i RHD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SP1
+5/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M/CAR
+3/31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SP1
+5/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LP2
+10/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOP
+1/2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. 변동점 현황 작성 (~11/19)
+  [ 안건 ]
+    - SU2i 대비 변동점 현황 파악
+  [ 진행 및 검토 ]
+    - 과거차 사례 반영 현황 작성
+      : 과거차 사례 5가지 작성
+    - SU2i 대비 변동 내용
+      : 보호 로직 (HV 저전압, 과전압)
+    - 품질 RISK
+      : S/W 이원화로 인한 PCB 색상 변경 품질 RISK
+      : 작동 전압 범위 변경으로 인한 품질 RISK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공조 로컬 CAN 심의회 진행 (11/13)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SVm, BJ, NX5e, MX5a, HE1i 대상</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사이버 보안 M단계 적용으로 김응영 책임에게 유선 확인 완료 (11/07)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공정 감사 5EA 건에 대해서는 공정 감사 어디서 하는지 모른다고 함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>기아샤시시스템품질팀 김제일 매니저 사이버보안 납품건 확인 완료 (11/10)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>QV와 동일하게 LP2 5EA 납품, M단계 전량 사이버 보안 적용 진행 요청 받음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사이버 보안으로 바뀐 이력 김제일 매니저 공유 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>설계 변경 결재 상신 완료 (11/10)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>기구팀 문의 결과, QV, SVm, BJ 담당자 전부 똑같다고 함. 결재 라인 똑같이 예정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>설계 변경 문서 작성 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사이버 보안 미적용 SW, 적용 SW 동작 확인 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 완료 (11/10)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공조 로컬 CAN 심의회 진행 (11/13)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SVm, BJ, NX5e, MX5a, HE1i 대상</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>열에너지차량시험팀 주관 BJ1 항속형 실차 검증 진행 (11/10)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>최대난방평가 재현 결과 플로어 모드 첫 진입 시 좌우 온도 편차 최대 4.5℃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이후 모든 단계가 끝날 때 좌우 온도 편차 1℃ 내 수렴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>온도 제어성 정합 평가 플로어 8단, 토출부 도어 Dr 4.65V, Ps 4.66V 강제 제어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Duty 90% 강제 제어 결과 좌우 온도 편차 3.75℃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Duty 50% ~ 80% 강제 제어 결과 60% 때 좌우 온도 편차 1.14℃, 그 외 1℃ 내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PTC 벤치 테스트 한온에서 진행 (11/12)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BJ RHD HVAC 2대 수령</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공조 로컬 CAN 심의회 진행 (11/13)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SVm, BJ, NX5e, MX5a, HE1i 대상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+[김진겸 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>열에너지차량시험팀 측에서 11/10(월) 챔버 확보</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>자동차 측에서 실차 튜닝 요청, 참석 인원 선정 필요</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사이버 보안 적용 단계, 피지컬 ID, 사이버보안품질팀 담당자 문의 (11/11)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>김동환 연구원 유선 문의 완료, 빠르게 파악 후 회신 한다고 함.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>12일 오전 까지 회신 없으면 12일 오후 정재근 책임 연구원 연락 예정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공조 로컬 CAN 심의회 진행 (11/13)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SVm, BJ, NX5e, MX5a, HE1i 대상</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공조 로컬 CAN 심의회 진행 (11/13)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SVm, BJ, NX5e, MX5a, HE1i 대상</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 최소 작동 전압 범위 수정 후, EV HTR 개발팀 김민수 선임에게 전달
+  : 0℃, -30℃ 환경에서 QV Air PTC와 160V, 170V 출력 비교 필요로 인한 요청
+  : 다른 작업 먼저 한다고 함, 추후 진행 예정이고 일정 미정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>[임제훈 사원]
 1. LHD, RHD R로직 튜닝 및 기능 점검
   [ 안건 ]
     - SW 점검
   [ 진행 및 검토 ]
+    - AY LHD 2EA, RHD 2EA 수령 (11/18)
     - 칼로리 사용 예약
      : 11/17 ~ 11/21 야간 칼로리 사용 예약 완료
      : 11/24 ~ 11/28 주간, 야간 칼로리 사용 예약 완료
@@ -3168,130 +4027,6 @@
     - LHD, RHD R로직 튜닝
      : 김진겸 사원 일정 협의 후 진행
     - 로직 및 기능 체크리스트 기반 검증 진행</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">[임제훈 사원]
-1. 기아샤시시스템품질팀 평택 공장 방문 건 (11/14)
-  [ 안건 ]
-    - 서지 내성 평가
-  [ 요청사항 ]
-    - 11월 정기 협의체 회의는 평택 공장 방문 점검으로 대체
-    - 정기 협의체 진행 후 요청 자료에 대한 리뷰 (12월 정기 방문시 설명으로 협의)
-  [ 진행 및 검토]
-    - 11/14 서지 내성 평가 Fail
-     : PCB 라이팅 정지
-     : LP2 생산 물품으로 11/24 재평가 실행
-    - 재평가 Fail일 경우
-     : LV, HV, 전력 센싱 값 확인 및 튜닝
-     : R로직 튜닝, 체크리스트 기반 기능 및 성능 시험
-     : SW 설계 변경 필요
-    - 재평가 Pass일 경우
-     :
-  </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[우리산업]
-기구 : 공준석, 강명준</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[우리산업]
-기구 : 공준석, 강명준</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALL Drawing
-4/15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Proto
-10/15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LP2
-10/15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SOP
-1/2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALL Drawing
-6/30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HE1i LHD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HE1i RHD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SP1
-5/15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M/CAR
-3/31</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-1. 최대 난방 및 좌우 온도 편차 실차 검증
-  : 11/14(금) BJ AP2 차량 PTC 개선품 리워크 후 확인 (남양연구소 B1-7)
-  : 11/18(화) ~ 11/20(목) 리워크 완료 AP2 차량 국내 트립 진행
-2. 한온 BJ LP#2 Event 대응 (11/14)
-  [ 안건 ]
-    - LP2 Event 대응
-  [ 요청사항 ]
-    - 슬로바키아 법인 ↔ 터키 한온 직거래
-  [ 진행 및 검토]
-    - BJ1 LP2 현대자동차 대일정 26. 4. 15 → 26. 5. 1. 변경
-     : LP2 일정 여유가 있는데, 납품 시기 너무 빠름, 재확인 필요
-    - 12/15 납품을 해야하는 경우
-     : PCB 생산 일정 확인 후, SW 배포 가능 일자 확인
-     : LHD, RHD R로직 튜닝, 체크리스트 기반 기능 및 성능 시험
-     : SW 설계 변경 진행
-3. BJ1 사이버 보안 적용 단계 및 납품건 확인 (11/17)
-  [ 진행 및 검토 ]
-    - 공조시스템설계팀, 품질팀 문의
-     : QV와 동일하게 진행 요청
-     : LP2 사이버 보안 적용품 5EA 납품, M 단계 전량 사이버 보안 적용
-4. LHD, RHD R로직 튜닝 및 기능 점검
-  [ 안건 ]
-    - 설계 변경 진행을 위한 SW 점검
-  [ 진행 및 검토 ]
-    - 칼로리 사용 예약
-     : 11/17 ~ 11/21 야간 칼로리 사용 예약 완료
-     : 11/24 ~ 11/28 주간, 야간 칼로리 사용 예약 완료
-     : 12/01 ~ 12/05 야간 칼로리 사용 예약 완료
-    - LHD, RHD R로직 튜닝
-     : 김진겸 사원 일정 협의 후 진행
-    - 로직 및 기능 체크리스트 기반 검증 진행</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SP1
-5/15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LP2
-10/15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SOP
-1/2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3305,6 +4040,7 @@
   [ 진행 및 검토 ]
     - 165℃ 적용된 마스터 샘플 재고 부족으로 제작 불가
     - NX5e 11/21 PCB 생산 예정일에 맞추어 재배포 불가
+     : P1 최종 사양 반영된 샘플 12/5 ~ 12/12 수령 예정
     - R로직 튜닝
     - 로직 및 기능 체크리스트 기반 검증 진행
     - 설계 변경으로 진행해야 하는지 확인
@@ -3329,798 +4065,71 @@
     - ES95489-21 (100%)
     - ES95489-24 (100%)
     - ES95411-00 (95%, ~11/21)
-    - ES90700-00 (50%, ~11/21)
-    - ES95480-00 (50%, ~11/21)</t>
+    - ES90700-00 (55%, ~11/21)
+    - ES95480-00 (55%, ~11/21)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[임제훈 사원]
-1. 변동점 현황 작성 (~11/19)
+1. 최대 난방 및 좌우 온도 편차 실차 검증
+  : 11/14(금) BJ AP2 차량 PTC 개선품 리워크 후 확인 (남양연구소 B1-7)
+  : 11/18(화) ~ 11/20(목) 리워크 완료 AP2 차량 국내 트립 진행
+2. 한온 BJ LP#2 Event 대응 (11/14)
   [ 안건 ]
-    - SU2i 대비 변동점 현황 파악
+    - LP2 Event 대응
+  [ 요청사항 ]
+    - 슬로바키아 법인 ↔ 터키 한온 직거래
+  [ 진행 및 검토]
+    - BJ1 LP2 현대자동차 대일정 26. 4. 15 → 26. 5. 1. 변경
+     : LP2 일정 여유가 있는데, 납품 시기 너무 빠름, 재확인 필요
+    - 12/15 납품을 해야하는 경우
+     : PCB 생산 일정 확인 후, SW 배포 가능 일자 확인
+     : LHD, RHD R로직 튜닝, 체크리스트 기반 기능 및 성능 시험
+     : SW 설계 변경 진행
+3. BJ1 사이버 보안 적용 단계 및 납품건 확인 (11/17)
   [ 진행 및 검토 ]
-    - 과거차 사례 반영 현황 작성
-      : 과거차 사례 5가지 작성
-    - SU2i 대비 변동 내용
-      : 보호 로직 (HV 저전압, 과전압)
-    - 품질 RISK
-      : S/W 이원화로 인한 PCB 색상 변경 품질 RISK
-      : 작동 전압 범위 변경으로 인한 품질 RISK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">[임제훈 사원]
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>공조 로컬 CAN 심의회 진행 (11/13)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SVm, BJ, NX5e, MX5a, HE1i 대상</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">[임제훈 사원]
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>사이버 보안 M단계 적용으로 김응영 책임에게 유선 확인 완료 (11/07)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>공정 감사 5EA 건에 대해서는 공정 감사 어디서 하는지 모른다고 함</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>기아샤시시스템품질팀 김제일 매니저 사이버보안 납품건 확인 완료 (11/10)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>QV와 동일하게 LP2 5EA 납품, M단계 전량 사이버 보안 적용 진행 요청 받음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>사이버 보안으로 바뀐 이력 김제일 매니저 공유 완료</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>설계 변경 결재 상신 완료 (11/10)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>기구팀 문의 결과, QV, SVm, BJ 담당자 전부 똑같다고 함. 결재 라인 똑같이 예정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>설계 변경 문서 작성 완료</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>사이버 보안 미적용 SW, 적용 SW 동작 확인 완료</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>제어사양서, 고장진단 사양, 로직검증 체크리스트 확인 및 갱신 완료 (11/10)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>공조 로컬 CAN 심의회 진행 (11/13)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SVm, BJ, NX5e, MX5a, HE1i 대상</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">[임제훈 사원]
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>열에너지차량시험팀 주관 BJ1 항속형 실차 검증 진행 (11/10)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>최대난방평가 재현 결과 플로어 모드 첫 진입 시 좌우 온도 편차 최대 4.5℃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>이후 모든 단계가 끝날 때 좌우 온도 편차 1℃ 내 수렴</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>온도 제어성 정합 평가 플로어 8단, 토출부 도어 Dr 4.65V, Ps 4.66V 강제 제어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Duty 90% 강제 제어 결과 좌우 온도 편차 3.75℃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Duty 50% ~ 80% 강제 제어 결과 60% 때 좌우 온도 편차 1.14℃, 그 외 1℃ 내</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PTC 벤치 테스트 한온에서 진행 (11/12)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>BJ RHD HVAC 2대 수령</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>공조 로컬 CAN 심의회 진행 (11/13)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SVm, BJ, NX5e, MX5a, HE1i 대상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-[김진겸 사원]
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>열에너지차량시험팀 측에서 11/10(월) 챔버 확보</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>자동차 측에서 실차 튜닝 요청, 참석 인원 선정 필요</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">[임제훈 사원]
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>사이버 보안 적용 단계, 피지컬 ID, 사이버보안품질팀 담당자 문의 (11/11)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>김동환 연구원 유선 문의 완료, 빠르게 파악 후 회신 한다고 함.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>12일 오전 까지 회신 없으면 12일 오후 정재근 책임 연구원 연락 예정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>공조 로컬 CAN 심의회 진행 (11/13)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SVm, BJ, NX5e, MX5a, HE1i 대상</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">[임제훈 사원]
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>공조 로컬 CAN 심의회 진행 (11/13)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SVm, BJ, NX5e, MX5a, HE1i 대상</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- 최소 작동 전압 범위 수정 후, EV HTR 개발팀 김민수 선임에게 전달
-  : 0℃, -30℃ 환경에서 QV Air PTC와 160V, 170V 출력 비교 필요로 인한 요청
-  : 다른 작업 먼저 한다고 함, 추후 진행 예정이고 일정 미정</t>
+    - 공조시스템설계팀, 품질팀 문의
+     : QV와 동일하게 진행 요청
+     : LP2 사이버 보안 적용품 5EA 납품, M 단계 전량 사이버 보안 적용
+4. BJ1 P1 차량 PTC 불량 방문 교체 및 분석 대응 (11/19)
+  [ 안건 ]
+    - BJ1 P1 차량 PTC 불량 방문 교체 및 분석 대응
+  [ 진행 및 검토 ]
+    - 남양연구소 방문 (11/19)
+5. LHD, RHD R로직 튜닝 및 기능 점검
+  [ 안건 ]
+    - 설계 변경 진행을 위한 SW 점검
+  [ 진행 및 검토 ]
+    - BJ1 변경점 반영된 최종 사양 샘플 11/21 수령 예정
+     : BJ1 PCB 재고 없음, P2 이전 PCB 재활용 예정
+    - 칼로리 사용 예약
+     : 11/17 ~ 11/21 야간 칼로리 사용 예약 완료
+     : 11/24 ~ 11/28 주간, 야간 칼로리 사용 예약 완료
+     : 12/01 ~ 12/05 야간 칼로리 사용 예약 완료
+    - LHD, RHD R로직 튜닝
+     : 김진겸 사원 일정 협의 후 진행
+    - 로직 및 기능 체크리스트 기반 검증 진행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">[임제훈 사원]
+1. 기아샤시시스템품질팀 평택 공장 방문 건 (11/14)
+  [ 안건 ]
+    - 서지 내성 평가
+  [ 요청사항 ]
+    - 11월 정기 협의체 회의는 평택 공장 방문 점검으로 대체
+    - 정기 협의체 진행 후 요청 자료에 대한 리뷰 (12월 정기 방문시 설명으로 협의)
+  [ 진행 및 검토]
+    - 11/14 서지 내성 평가 Fail
+     : LP2 생산 물품으로 11/28 재평가 실행
+    - 재평가 Fail일 경우
+     : LV, HV, 전력 센싱 값 확인 및 튜닝
+     : R로직 튜닝, 체크리스트 기반 기능 및 성능 시험
+     : SW 설계 변경 필요
+     : S/W 검증 소요 시간 4주 요청
+    - 재평가 Pass일 경우
+     : S/W 변경사항 없음
+  </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6003,6 +6012,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6047,9 +6059,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -6716,90 +6725,90 @@
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="167" t="s">
+      <c r="B2" s="168" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="169" t="s">
+      <c r="C2" s="170" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="169" t="s">
+      <c r="D2" s="170" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="173">
+      <c r="E2" s="174">
         <v>23</v>
       </c>
-      <c r="F2" s="171"/>
-      <c r="G2" s="171"/>
-      <c r="H2" s="171"/>
-      <c r="I2" s="171"/>
-      <c r="J2" s="171"/>
-      <c r="K2" s="171"/>
-      <c r="L2" s="171"/>
-      <c r="M2" s="171"/>
-      <c r="N2" s="171"/>
-      <c r="O2" s="171"/>
-      <c r="P2" s="171"/>
-      <c r="Q2" s="171">
+      <c r="F2" s="172"/>
+      <c r="G2" s="172"/>
+      <c r="H2" s="172"/>
+      <c r="I2" s="172"/>
+      <c r="J2" s="172"/>
+      <c r="K2" s="172"/>
+      <c r="L2" s="172"/>
+      <c r="M2" s="172"/>
+      <c r="N2" s="172"/>
+      <c r="O2" s="172"/>
+      <c r="P2" s="172"/>
+      <c r="Q2" s="172">
         <v>24</v>
       </c>
-      <c r="R2" s="171"/>
-      <c r="S2" s="171"/>
-      <c r="T2" s="171"/>
-      <c r="U2" s="171"/>
-      <c r="V2" s="171"/>
-      <c r="W2" s="171"/>
-      <c r="X2" s="171"/>
-      <c r="Y2" s="171"/>
-      <c r="Z2" s="171"/>
-      <c r="AA2" s="171"/>
-      <c r="AB2" s="171"/>
-      <c r="AC2" s="171">
+      <c r="R2" s="172"/>
+      <c r="S2" s="172"/>
+      <c r="T2" s="172"/>
+      <c r="U2" s="172"/>
+      <c r="V2" s="172"/>
+      <c r="W2" s="172"/>
+      <c r="X2" s="172"/>
+      <c r="Y2" s="172"/>
+      <c r="Z2" s="172"/>
+      <c r="AA2" s="172"/>
+      <c r="AB2" s="172"/>
+      <c r="AC2" s="172">
         <v>25</v>
       </c>
-      <c r="AD2" s="171"/>
-      <c r="AE2" s="171"/>
-      <c r="AF2" s="171"/>
-      <c r="AG2" s="171"/>
-      <c r="AH2" s="171"/>
-      <c r="AI2" s="171"/>
-      <c r="AJ2" s="171"/>
-      <c r="AK2" s="171"/>
-      <c r="AL2" s="171"/>
-      <c r="AM2" s="171"/>
-      <c r="AN2" s="171"/>
-      <c r="AO2" s="171">
+      <c r="AD2" s="172"/>
+      <c r="AE2" s="172"/>
+      <c r="AF2" s="172"/>
+      <c r="AG2" s="172"/>
+      <c r="AH2" s="172"/>
+      <c r="AI2" s="172"/>
+      <c r="AJ2" s="172"/>
+      <c r="AK2" s="172"/>
+      <c r="AL2" s="172"/>
+      <c r="AM2" s="172"/>
+      <c r="AN2" s="172"/>
+      <c r="AO2" s="172">
         <v>26</v>
       </c>
-      <c r="AP2" s="171"/>
-      <c r="AQ2" s="171"/>
-      <c r="AR2" s="171"/>
-      <c r="AS2" s="171"/>
-      <c r="AT2" s="171"/>
-      <c r="AU2" s="171"/>
-      <c r="AV2" s="171"/>
-      <c r="AW2" s="171"/>
-      <c r="AX2" s="171"/>
-      <c r="AY2" s="171"/>
-      <c r="AZ2" s="172"/>
-      <c r="BA2" s="171">
+      <c r="AP2" s="172"/>
+      <c r="AQ2" s="172"/>
+      <c r="AR2" s="172"/>
+      <c r="AS2" s="172"/>
+      <c r="AT2" s="172"/>
+      <c r="AU2" s="172"/>
+      <c r="AV2" s="172"/>
+      <c r="AW2" s="172"/>
+      <c r="AX2" s="172"/>
+      <c r="AY2" s="172"/>
+      <c r="AZ2" s="173"/>
+      <c r="BA2" s="172">
         <v>27</v>
       </c>
-      <c r="BB2" s="171"/>
-      <c r="BC2" s="171"/>
-      <c r="BD2" s="171"/>
-      <c r="BE2" s="171"/>
-      <c r="BF2" s="171"/>
-      <c r="BG2" s="171"/>
-      <c r="BH2" s="171"/>
-      <c r="BI2" s="171"/>
-      <c r="BJ2" s="171"/>
-      <c r="BK2" s="171"/>
-      <c r="BL2" s="172"/>
+      <c r="BB2" s="172"/>
+      <c r="BC2" s="172"/>
+      <c r="BD2" s="172"/>
+      <c r="BE2" s="172"/>
+      <c r="BF2" s="172"/>
+      <c r="BG2" s="172"/>
+      <c r="BH2" s="172"/>
+      <c r="BI2" s="172"/>
+      <c r="BJ2" s="172"/>
+      <c r="BK2" s="172"/>
+      <c r="BL2" s="173"/>
     </row>
     <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="168"/>
-      <c r="C3" s="170"/>
-      <c r="D3" s="170"/>
+      <c r="B3" s="169"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
       <c r="E3" s="22">
         <v>1</v>
       </c>
@@ -8534,11 +8543,11 @@
     </row>
     <row r="23" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="57" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C23" s="80"/>
       <c r="D23" s="165" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E23" s="64"/>
       <c r="F23" s="65"/>
@@ -8568,7 +8577,7 @@
       <c r="AD23" s="65"/>
       <c r="AE23" s="65"/>
       <c r="AF23" s="69" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="AG23" s="68"/>
       <c r="AH23" s="65"/>
@@ -8576,30 +8585,30 @@
       <c r="AJ23" s="65"/>
       <c r="AK23" s="65"/>
       <c r="AL23" s="69" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AM23" s="65"/>
       <c r="AN23" s="66"/>
       <c r="AO23" s="67"/>
       <c r="AP23" s="69"/>
       <c r="AQ23" s="69" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="AR23" s="69"/>
       <c r="AS23" s="65"/>
       <c r="AT23" s="69" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AU23" s="69"/>
       <c r="AV23" s="65"/>
       <c r="AW23" s="65"/>
       <c r="AX23" s="69" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AY23" s="69"/>
       <c r="AZ23" s="70"/>
       <c r="BA23" s="166" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="BB23" s="72"/>
       <c r="BC23" s="73"/>
@@ -8615,11 +8624,11 @@
     </row>
     <row r="24" spans="2:64" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="79" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C24" s="164"/>
       <c r="D24" s="162" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E24" s="49"/>
       <c r="F24" s="50"/>
@@ -8651,7 +8660,7 @@
       <c r="AF24" s="50"/>
       <c r="AG24" s="53"/>
       <c r="AH24" s="54" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AI24" s="54"/>
       <c r="AJ24" s="50"/>
@@ -8665,18 +8674,18 @@
       <c r="AR24" s="54"/>
       <c r="AS24" s="50"/>
       <c r="AT24" s="54" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="AU24" s="54"/>
       <c r="AV24" s="50"/>
       <c r="AW24" s="50"/>
       <c r="AX24" s="54" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="AY24" s="54"/>
       <c r="AZ24" s="55"/>
-      <c r="BA24" s="182" t="s">
-        <v>339</v>
+      <c r="BA24" s="167" t="s">
+        <v>336</v>
       </c>
       <c r="BB24" s="74"/>
       <c r="BC24" s="75"/>
@@ -8867,39 +8876,39 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="176" t="s">
+      <c r="B2" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="180" t="s">
+      <c r="C2" s="181" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="180" t="s">
+      <c r="D2" s="181" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="178" t="s">
+      <c r="E2" s="179" t="s">
         <v>126</v>
       </c>
       <c r="F2" s="96" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="174" t="s">
+      <c r="G2" s="175" t="s">
         <v>113</v>
       </c>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
-      <c r="J2" s="175"/>
-      <c r="K2" s="174" t="s">
+      <c r="H2" s="175"/>
+      <c r="I2" s="175"/>
+      <c r="J2" s="176"/>
+      <c r="K2" s="175" t="s">
         <v>182</v>
       </c>
-      <c r="L2" s="174"/>
-      <c r="M2" s="174"/>
-      <c r="N2" s="175"/>
+      <c r="L2" s="175"/>
+      <c r="M2" s="175"/>
+      <c r="N2" s="176"/>
     </row>
     <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="177"/>
-      <c r="C3" s="181"/>
-      <c r="D3" s="181"/>
-      <c r="E3" s="179"/>
+      <c r="B3" s="178"/>
+      <c r="C3" s="182"/>
+      <c r="D3" s="182"/>
+      <c r="E3" s="180"/>
       <c r="F3" s="97" t="s">
         <v>111</v>
       </c>
@@ -9642,30 +9651,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="176" t="s">
+      <c r="B2" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="180" t="s">
+      <c r="C2" s="181" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="180" t="s">
+      <c r="D2" s="181" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="178" t="s">
+      <c r="E2" s="179" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="174" t="s">
+      <c r="F2" s="175" t="s">
         <v>182</v>
       </c>
-      <c r="G2" s="174"/>
-      <c r="H2" s="174"/>
-      <c r="I2" s="175"/>
+      <c r="G2" s="175"/>
+      <c r="H2" s="175"/>
+      <c r="I2" s="176"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="177"/>
-      <c r="C3" s="181"/>
-      <c r="D3" s="181"/>
-      <c r="E3" s="179"/>
+      <c r="B3" s="178"/>
+      <c r="C3" s="182"/>
+      <c r="D3" s="182"/>
+      <c r="E3" s="180"/>
       <c r="F3" s="97" t="s">
         <v>114</v>
       </c>
@@ -10043,30 +10052,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="176" t="s">
+      <c r="B2" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="180" t="s">
+      <c r="C2" s="181" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="180" t="s">
+      <c r="D2" s="181" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="178" t="s">
+      <c r="E2" s="179" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="174" t="s">
+      <c r="F2" s="175" t="s">
         <v>227</v>
       </c>
-      <c r="G2" s="174"/>
-      <c r="H2" s="174"/>
-      <c r="I2" s="175"/>
+      <c r="G2" s="175"/>
+      <c r="H2" s="175"/>
+      <c r="I2" s="176"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="177"/>
-      <c r="C3" s="181"/>
-      <c r="D3" s="181"/>
-      <c r="E3" s="179"/>
+      <c r="B3" s="178"/>
+      <c r="C3" s="182"/>
+      <c r="D3" s="182"/>
+      <c r="E3" s="180"/>
       <c r="F3" s="97" t="s">
         <v>114</v>
       </c>
@@ -10450,30 +10459,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="176" t="s">
+      <c r="B2" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="180" t="s">
+      <c r="C2" s="181" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="180" t="s">
+      <c r="D2" s="181" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="178" t="s">
+      <c r="E2" s="179" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="174" t="s">
+      <c r="F2" s="175" t="s">
         <v>259</v>
       </c>
-      <c r="G2" s="174"/>
-      <c r="H2" s="174"/>
-      <c r="I2" s="175"/>
+      <c r="G2" s="175"/>
+      <c r="H2" s="175"/>
+      <c r="I2" s="176"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="177"/>
-      <c r="C3" s="181"/>
-      <c r="D3" s="181"/>
-      <c r="E3" s="179"/>
+      <c r="B3" s="178"/>
+      <c r="C3" s="182"/>
+      <c r="D3" s="182"/>
+      <c r="E3" s="180"/>
       <c r="F3" s="97" t="s">
         <v>280</v>
       </c>
@@ -10875,30 +10884,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="176" t="s">
+      <c r="B2" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="180" t="s">
+      <c r="C2" s="181" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="180" t="s">
+      <c r="D2" s="181" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="178" t="s">
+      <c r="E2" s="179" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="174" t="s">
+      <c r="F2" s="175" t="s">
         <v>279</v>
       </c>
-      <c r="G2" s="174"/>
-      <c r="H2" s="174"/>
-      <c r="I2" s="175"/>
+      <c r="G2" s="175"/>
+      <c r="H2" s="175"/>
+      <c r="I2" s="176"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="177"/>
-      <c r="C3" s="181"/>
-      <c r="D3" s="181"/>
-      <c r="E3" s="179"/>
+      <c r="B3" s="178"/>
+      <c r="C3" s="182"/>
+      <c r="D3" s="182"/>
+      <c r="E3" s="180"/>
       <c r="F3" s="97" t="s">
         <v>300</v>
       </c>
@@ -10985,7 +10994,7 @@
         <v>311</v>
       </c>
       <c r="G7" s="105" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="H7" s="89"/>
       <c r="I7" s="93"/>
@@ -11097,10 +11106,10 @@
         <v>318</v>
       </c>
       <c r="G13" s="157" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="H13" s="105" t="s">
-        <v>324</v>
+        <v>347</v>
       </c>
       <c r="I13" s="134"/>
     </row>
@@ -11121,16 +11130,16 @@
         <v>310</v>
       </c>
       <c r="G14" s="157" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="H14" s="105" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="I14" s="122" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="162" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="175.5" x14ac:dyDescent="0.3">
       <c r="B15" s="131" t="s">
         <v>55</v>
       </c>
@@ -11150,7 +11159,7 @@
         <v>319</v>
       </c>
       <c r="H15" s="163" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="I15" s="134"/>
     </row>
@@ -11171,10 +11180,10 @@
         <v>320</v>
       </c>
       <c r="G16" s="157" t="s">
+        <v>341</v>
+      </c>
+      <c r="H16" s="157" t="s">
         <v>345</v>
-      </c>
-      <c r="H16" s="157" t="s">
-        <v>340</v>
       </c>
       <c r="I16" s="134"/>
     </row>
@@ -11195,10 +11204,10 @@
         <v>321</v>
       </c>
       <c r="G17" s="119" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="H17" s="163" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="I17" s="136"/>
     </row>
@@ -11238,7 +11247,7 @@
         <v>289</v>
       </c>
       <c r="H19" s="137" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="I19" s="93"/>
     </row>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -4096,6 +4096,8 @@
     - BJ1 P1 차량 PTC 불량 방문 교체 및 분석 대응
   [ 진행 및 검토 ]
     - 남양연구소 방문 (11/19)
+     : PTC 교체 전 Test 진행, 상위 제어 통신 &amp; PTC 통신 IGBT Fail Fault 확인 완료
+     : PTC 교체 후 Test 진행, 상위 제어 통신 정상 동작 확인, PTC 통신 확인 X
 5. LHD, RHD R로직 튜닝 및 기능 점검
   [ 안건 ]
     - 설계 변경 진행을 위한 SW 점검
@@ -4112,24 +4114,24 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">[임제훈 사원]
+    <t>[임제훈 사원]
 1. 기아샤시시스템품질팀 평택 공장 방문 건 (11/14)
   [ 안건 ]
-    - 서지 내성 평가
+    - 서지 내성 평가 (H/W 진행)
   [ 요청사항 ]
     - 11월 정기 협의체 회의는 평택 공장 방문 점검으로 대체
     - 정기 협의체 진행 후 요청 자료에 대한 리뷰 (12월 정기 방문시 설명으로 협의)
   [ 진행 및 검토]
-    - 11/14 서지 내성 평가 Fail
-     : LP2 생산 물품으로 11/28 재평가 실행
+    - 11/14 서지 내성 평가 Fail (H/W 진행)
+     : LP2 생산 물품으로 11/28 재평가 실행 (H/W 진행)
     - 재평가 Fail일 경우
-     : LV, HV, 전력 센싱 값 확인 및 튜닝
-     : R로직 튜닝, 체크리스트 기반 기능 및 성능 시험
-     : SW 설계 변경 필요
-     : S/W 검증 소요 시간 4주 요청
+     : LV, HV, 전력 센싱 값 확인 및 튜닝 (S/W)
+     : R로직 튜닝, 체크리스트 기반 기능 및 성능 시험 (S/W)
+     : SW 설계 변경 필요 (S/W)
+     : 변경점 반영된 샘플 수령 후, S/W 검증 소요 시간 4주 요청 (S/W)
     - 재평가 Pass일 경우
      : S/W 변경사항 없음
-  </t>
+    - 11/28 결과 발표 전, 현재 설계 변경 진행된 S/W V01.02로 M단계 양산 시작</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -19,6 +19,7 @@
     <sheet name="2025.7" sheetId="4" r:id="rId5"/>
     <sheet name="2025.10" sheetId="6" r:id="rId6"/>
     <sheet name="2025.11" sheetId="8" r:id="rId7"/>
+    <sheet name="2025.12" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="362">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3150,12 +3151,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[임제훈 사원]
-- 최대 난방 및 좌우 온도 편차 실차 검증
-  : 11/25(화) ~ 11/26(수) 실차 난방 평가 진행</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[우리산업]
 기구 : 공준석, 강명준</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3221,21 +3216,6 @@
   <si>
     <t>SOP
 1/2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-1. 변동점 현황 작성 (~11/19)
-  [ 안건 ]
-    - SU2i 대비 변동점 현황 파악
-  [ 진행 및 검토 ]
-    - 과거차 사례 반영 현황 작성
-      : 과거차 사례 5가지 작성
-    - SU2i 대비 변동 내용
-      : 보호 로직 (HV 저전압, 과전압)
-    - 품질 RISK
-      : S/W 이원화로 인한 PCB 색상 변경 품질 RISK
-      : 작동 전압 범위 변경으로 인한 품질 RISK</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4011,106 +3991,6 @@
 - 최소 작동 전압 범위 수정 후, EV HTR 개발팀 김민수 선임에게 전달
   : 0℃, -30℃ 환경에서 QV Air PTC와 160V, 170V 출력 비교 필요로 인한 요청
   : 다른 작업 먼저 한다고 함, 추후 진행 예정이고 일정 미정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-1. LHD, RHD R로직 튜닝 및 기능 점검
-  [ 안건 ]
-    - SW 점검
-  [ 진행 및 검토 ]
-    - AY LHD 2EA, RHD 2EA 수령 (11/18)
-    - 칼로리 사용 예약
-     : 11/17 ~ 11/21 야간 칼로리 사용 예약 완료
-     : 11/24 ~ 11/28 주간, 야간 칼로리 사용 예약 완료
-     : 12/01 ~ 12/05 야간 칼로리 사용 예약 완료
-    - LHD, RHD R로직 튜닝
-     : 김진겸 사원 일정 협의 후 진행
-    - 로직 및 기능 체크리스트 기반 검증 진행</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-1. 기구 변경 건 (11/14)
-  [ 안건 ]
-    - Stone TC 160℃ → 165℃ 변경
-    - 전압 범위 변경
-    - LINEAR MAX 성능 7000W 변경
-    - 제어 사양서, S/W 재배포 요청
-  [ 진행 및 검토 ]
-    - 165℃ 적용된 마스터 샘플 재고 부족으로 제작 불가
-    - NX5e 11/21 PCB 생산 예정일에 맞추어 재배포 불가
-     : P1 최종 사양 반영된 샘플 12/5 ~ 12/12 수령 예정
-    - R로직 튜닝
-    - 로직 및 기능 체크리스트 기반 검증 진행
-    - 설계 변경으로 진행해야 하는지 확인
-2. 승인도 수령 건 (11/14)
-  [ 안건 ]
-    - 변경점 업데이트된 승인도 HKMC 발송
-  [ 진행 및 검토 ]
-    - 전압 범위 변경점 확인
-      : 정격 전압 360V → 351V 변경
-      : 최대 작동 전압 403.2V → 413V 변경
-    - RATED MAX, LINEAR MAX 성능 확인
-      : LINEAR MAX 7200W → 7000W 변경
-    - Core Temp 구간 변경 확인
-      : Cut 100℃ → 90℃ 변경
-      : Recovery 90℃ → 85℃ 변경
-      : Limit Start 90℃ → 85℃ 변경
-      : Limit Stop 100℃ → 90℃ 변경
-3. ESIR (~11/15)
-  [ 안건 ]
-    - ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24 ESIR 진행
-  [ 진행 및 검토 ]
-    - ES95489-21 (100%)
-    - ES95489-24 (100%)
-    - ES95411-00 (95%, ~11/21)
-    - ES90700-00 (55%, ~11/21)
-    - ES95480-00 (55%, ~11/21)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-1. 최대 난방 및 좌우 온도 편차 실차 검증
-  : 11/14(금) BJ AP2 차량 PTC 개선품 리워크 후 확인 (남양연구소 B1-7)
-  : 11/18(화) ~ 11/20(목) 리워크 완료 AP2 차량 국내 트립 진행
-2. 한온 BJ LP#2 Event 대응 (11/14)
-  [ 안건 ]
-    - LP2 Event 대응
-  [ 요청사항 ]
-    - 슬로바키아 법인 ↔ 터키 한온 직거래
-  [ 진행 및 검토]
-    - BJ1 LP2 현대자동차 대일정 26. 4. 15 → 26. 5. 1. 변경
-     : LP2 일정 여유가 있는데, 납품 시기 너무 빠름, 재확인 필요
-    - 12/15 납품을 해야하는 경우
-     : PCB 생산 일정 확인 후, SW 배포 가능 일자 확인
-     : LHD, RHD R로직 튜닝, 체크리스트 기반 기능 및 성능 시험
-     : SW 설계 변경 진행
-3. BJ1 사이버 보안 적용 단계 및 납품건 확인 (11/17)
-  [ 진행 및 검토 ]
-    - 공조시스템설계팀, 품질팀 문의
-     : QV와 동일하게 진행 요청
-     : LP2 사이버 보안 적용품 5EA 납품, M 단계 전량 사이버 보안 적용
-4. BJ1 P1 차량 PTC 불량 방문 교체 및 분석 대응 (11/19)
-  [ 안건 ]
-    - BJ1 P1 차량 PTC 불량 방문 교체 및 분석 대응
-  [ 진행 및 검토 ]
-    - 남양연구소 방문 (11/19)
-     : PTC 교체 전 Test 진행, 상위 제어 통신 &amp; PTC 통신 IGBT Fail Fault 확인 완료
-     : PTC 교체 후 Test 진행, 상위 제어 통신 정상 동작 확인, PTC 통신 확인 X
-5. LHD, RHD R로직 튜닝 및 기능 점검
-  [ 안건 ]
-    - 설계 변경 진행을 위한 SW 점검
-  [ 진행 및 검토 ]
-    - BJ1 변경점 반영된 최종 사양 샘플 11/21 수령 예정
-     : BJ1 PCB 재고 없음, P2 이전 PCB 재활용 예정
-    - 칼로리 사용 예약
-     : 11/17 ~ 11/21 야간 칼로리 사용 예약 완료
-     : 11/24 ~ 11/28 주간, 야간 칼로리 사용 예약 완료
-     : 12/01 ~ 12/05 야간 칼로리 사용 예약 완료
-    - LHD, RHD R로직 튜닝
-     : 김진겸 사원 일정 협의 후 진행
-    - 로직 및 기능 체크리스트 기반 검증 진행</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4132,6 +4012,1325 @@
     - 재평가 Pass일 경우
      : S/W 변경사항 없음
     - 11/28 결과 발표 전, 현재 설계 변경 진행된 S/W V01.02로 M단계 양산 시작</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. AP2 PTC 개선품 리워크 차량 최대 난방 및 좌우 온도 편차 실차 검증 (11/26)
+  [ 안건 ]
+    - 최대 난방 평가 및 좌우 온도 편차 실차 검증
+  [ 진행 및 검토 ]
+    - 최대 난방 평가
+      : 첫 플로어 모드 종료 시, 실내 온도 19℃ 이상 요구
+      : 19.2℃로 난방 성능 만족 (Pass)
+    - 좌우 온도 편차 검증
+      : 디프 모드 토출부 좌우 온도 편차 3.6℃ (Pass)
+      : 플로어 모드 1열 토출부 좌우 온도 편차 1.9℃ ~ 3℃ 내 수렴 (Pass)
+      : 플로어 모드 2열 토출부 좌우 온도 편차 0.4℃ ~ 1.5℃ 내 수렴 (Pass)
+2. 한온 BJ LP#2 Event 일정 확인
+  [ 안건 ]
+    - LP2 Event 대응
+  [ 요청사항 ]
+    - 슬로바키아 법인 ↔ 터키 한온 직거래
+  [ 진행 및 검토 ]
+    - LP2 Event 관련 생산 일정 확인 및 S/W 배포 일자 확인
+    - S/W R로직 QV와 동일하게 진행
+    - S/W 성능 및 기능 점검
+    - S/W 설계 변경 진행
+3. 사이버 보안 관련 자료 회신 요청
+  [ 요청사항 ]
+    - 사이버 보안 QV와 동일한 이력으로 진행 요청 (공조시스템설계팀)
+    - BJ1 ES95489-21 성적서 회신
+    - 사이버보안관련성평가 작성 후 회신
+  [ 진행 및 검토 ]
+    - BJ1 ES95489-21, ESIR 때 성적서 없음
+      : QV 사이버 보안 협의 및 일정 지연으로 BJ1 ESIR때 진행 불가
+      : BJ1 ES95489-21 검증 진행
+    - 사이버보안관련성평가 작성 후 검토 요청</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>기구 변경 건 (11/14)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 안건 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Stone TC 160℃ → 165℃ 변경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>전압 범위 변경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LINEAR MAX 성능 7000W 변경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - 제어 사양서, S/W 재배포 요청
+  [ 진행 및 검토 ]
+    - 165℃ 적용된 마스터 샘플 재고 부족으로 제작 불가
+    - NX5e 11/21 PCB 생산 예정일에 맞추어 재배포 불가
+     : P1 최종 사양 반영된 샘플 12/5 ~ 12/12 수령 예정
+    - R로직 튜닝
+    - 로직 및 기능 체크리스트 기반 검증 진행
+    - 설계 변경으로 진행해야 하는지 확인
+2. 승인도 수령 건 (11/14)
+  [ 안건 ]
+    - 변경점 업데이트된 승인도 HKMC 발송
+  [ 진행 및 검토 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>전압 범위 변경점 확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>정격 전압 360V → 351V 변경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>최대 작동 전압 403.2V → 413V 변경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RATED MAX, LINEAR MAX 성능 확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LINEAR MAX 7200W → 7000W 변경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Core Temp 구간 변경 확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cut 100℃ → 90℃ 변경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Recovery 90℃ → 85℃ 변경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Limit Start 90℃ → 85℃ 변경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Limit Stop 100℃ → 90℃ 변경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+3. ESIR (~11/15)
+  [ 안건 ]
+    - ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24 ESIR 진행
+  [ 진행 및 검토 ]
+    - ES95489-21 (100%)
+    - ES95489-24 (100%)
+    - ES95411-00 (95%, ~11/21)
+    - ES90700-00 (55%, ~11/21)
+    - ES95480-00 (55%, ~11/21)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>변동점 현황 작성 (~11/19)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 안건 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SU2i 대비 변동점 현황 파악</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 진행 및 검토 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>과거차 사례 반영 현황 작성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>과거차 사례 5가지 작성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SU2i 대비 변동 내용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>보호 로직 (HV 저전압, 과전압)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>품질 RISK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S/W 이원화로 인한 PCB 색상 변경 품질 RISK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>작동 전압 범위 변경으로 인한 품질 RISK</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. 제어사양서 작성, 로직점검 체크리스트 작성, 고장진단 사양 검토 후 갱신</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- 최소 작동 전압 범위 수정 후, EV HTR 개발팀 김민수 선임에게 전달
+  : 0℃, -30℃ 환경에서 QV Air PTC와 160V, 170V 출력 비교 필요로 인한 요청
+  : 다른 작업 먼저 한다고 함, 추후 진행 예정이고 일정 미정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. 기구 변경 건 (11/14)
+  [ 안건 ]
+    - Stone TC 160℃ → 165℃ 변경
+    - 전압 범위 변경
+    - LINEAR MAX 성능 7000W 변경
+    - 제어 사양서, S/W 재배포 요청
+  [ 진행 및 검토 ]
+    - 165℃ 적용된 마스터 샘플 재고 부족으로 제작 불가
+    - NX5e 11/21 PCB 생산 예정일에 맞추어 재배포 불가
+     : P1 최종 사양 반영된 샘플 12/5 ~ 12/12 수령 예정
+    - R로직 튜닝
+     : 12/01 ~ 12/12 야간 칼로리 사용 예약 완료
+     : 12/18 ~ 01/02 주간, 야간 칼로리 사용 예약 완료
+    - 로직 및 기능 체크리스트 기반 검증 진행
+    - 설계 변경으로 진행해야 하는지 확인
+2. ESIR (~12/05)
+  [ 안건 ]
+    - ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24 ESIR 진행
+  [ 진행 및 검토 ]
+    - ES95489-21 (100%)
+    - ES95489-24 (100%)
+    - ES95411-00 (95%, ~12/05)
+    - ES90700-00 (55%, ~12/05)
+    - ES95480-00 (55%, ~12/05)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. LHD, RHD R로직 튜닝 및 기능 점검
+  [ 안건 ]
+    - SW 점검
+  [ 진행 및 검토 ]
+    - AY LHD 2EA, RHD 2EA PTC 수령 (11/18)
+    - 칼로리 사용 예약
+     : 11/17 ~ 11/21 야간 칼로리 사용 예약 완료
+     : 11/24 ~ 11/28 주간, 야간 칼로리 사용 예약 완료
+     : 12/01 ~ 12/05 야간 칼로리 사용 예약 완료
+    - LHD, RHD R로직 튜닝
+     : 김진겸 사원 일정 협의 후 진행
+    - 로직 및 기능 체크리스트 기반 검증 진행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. LHD, RHD R로직 튜닝 및 기능 점검
+  [ 안건 ]
+    - SW 점검
+  [ 진행 및 검토 ]
+    - AY LHD 2EA, RHD 2EA PTC 수령 (11/18)
+    - 칼로리 사용 예약
+     : 12/01 ~ 12/12 야간 칼로리 사용 예약 완료
+     : 12/18 ~ 01/02 주간, 야간 칼로리 사용 예약 완료
+    - LHD, RHD R로직 튜닝
+     : 김진겸 사원 일정 협의 후 진행
+    - 로직 및 기능 체크리스트 기반 검증 진행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1주차 (11/28 ~ 12/04)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2주차 (12/05 ~ 12/11)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3주차 (12/12 ~ 12/18)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4주차 (12/19 ~ 12/25)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5주차 (12/26 ~ 01/01)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- SWE.3 SDDS 후속 작업 (진행률 : 97%)
+- SRS, SADS, SDDS ALM 등록 (~12/05)
+[조현진 전임]
+- SWE.1, 2, 3 등록에 맞추어 SWE. 4, 5, 6 ALM 등록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- SWE.3 SDDS 후속 작업 (진행률 : 97%)
+- SRS, SADS, SDDS ALM 등록 (~12/05)
+[조현진 전임]
+- SWE.1, 2, 3 등록에 맞추어 SWE. 4, 5, 6 ALM 등록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. 기아샤시시스템품질팀 평택 공장 방문 건 (11/14)
+  [ 안건 ]
+    - 서지 내성 평가 (H/W 진행)
+  [ 요청사항 ]
+    - 11월 정기 협의체 회의는 평택 공장 방문 점검으로 대체
+    - 정기 협의체 진행 후 요청 자료에 대한 리뷰 (12월 정기 방문시 설명으로 협의)
+  [ 진행 및 검토]
+    - 11/14 서지 내성 평가 Fail (H/W 진행)
+     : LP2 생산 물품으로 11/28 재평가 실행 (H/W 진행)
+    - 재평가 Fail일 경우 (H/W 결과)
+     : S/W LV, HV, 전력 센싱 값 확인 및 튜닝
+     : R로직 튜닝, 체크리스트 기반 기능 및 성능 시험
+     : S/W 설계 변경 필요
+     : 변경점 반영된 샘플 수령 후, S/W 검증 소요 시간 4주 요청
+    - 재평가 Pass일 경우 (H/W 결과)
+     : S/W 변경사항 없음
+    - 11/28 결과 발표 전, 현재 설계 변경 진행된 S/W V01.02로 M단계 양산 시작
+    - 칼로리 사용 예약
+     : 12/01 ~ 12/12 야간 칼로리 사용 예약 완료
+     : 12/18 ~ 01/02 주간, 야간 칼로리 사용 예약 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. 기아샤시시스템품질팀 평택 공장 방문 건 (11/14)
+  [ 안건 ]
+    - 서지 내성 평가 (H/W 진행)
+  [ 요청사항 ]
+    - 11월 정기 협의체 회의는 평택 공장 방문 점검으로 대체
+    - 정기 협의체 진행 후 요청 자료에 대한 리뷰 (12월 정기 방문시 설명으로 협의)
+  [ 진행 및 검토]
+    - 11/14 서지 내성 평가 Fail (H/W 진행)
+     : LP2 생산 물품으로 11/28 재평가 실행 (H/W 진행)
+    - 재평가 Fail일 경우 (H/W 결과)
+     : S/W LV, HV, 전력 센싱 값 확인 및 튜닝
+     : R로직 튜닝, 체크리스트 기반 기능 및 성능 시험
+     : S/W 설계 변경 필요
+     : 변경점 반영된 샘플 수령 후, S/W 검증 소요 시간 4주 요청
+    - 재평가 Pass일 경우 (H/W 결과)
+     : S/W 변경사항 없음
+    - 11/28 결과 발표 전, 현재 설계 변경 진행된 S/W V01.02로 M단계 양산 시작
+    - 칼로리 사용 예약
+     : 12/01 ~ 12/12 야간 칼로리 사용 예약 완료
+     : 12/18 ~ 01/02 주간, 야간 칼로리 사용 예약 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>최대 난방 및 좌우 온도 편차 실차 검증</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>11/14(금) BJ AP2 차량 PTC 개선품 리워크 후 확인 (남양연구소 B1-7)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>11/18(화) ~ 11/20(목) 리워크 완료 AP2 차량 국내 트립 진행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. 한온 BJ LP#2 Event 대응 (11/14)
+  [ 안건 ]
+    - LP2 Event 대응
+  [ 요청사항 ]
+    - 슬로바키아 법인 ↔ 터키 한온 직거래
+  [ 진행 및 검토]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BJ1 LP2 현대자동차 대일정 26. 4. 15 → 26. 5. 1. 변경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : LP2 일정 여유가 있는데, 납품 시기 너무 빠름, 재확인 필요
+    - 12/15 납품을 해야하는 경우
+     : PCB 생산 일정 확인 후, SW 배포 가능 일자 확인
+     : LHD, RHD R로직 튜닝, 체크리스트 기반 기능 및 성능 시험
+     : SW 설계 변경 진행
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BJ1 사이버 보안 적용 단계 및 납품건 확인 (11/17)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 진행 및 검토 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공조시스템설계팀, 품질팀 문의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>QV와 동일하게 진행 요청</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LP2 사이버 보안 적용품 5EA 납품, M 단계 전량 사이버 보안 적용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BJ1 P1 차량 PTC 불량 방문 교체 및 분석 대응 (11/19)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 안건 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BJ1 P1 차량 PTC 불량 방문 교체 및 분석 대응</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 진행 및 검토 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>남양연구소 방문 (11/19)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PTC 교체 전 Test 진행, 상위 제어 통신 &amp; PTC 통신 IGBT Fail Fault 확인 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PTC 교체 후 Test 진행, 상위 제어 통신 정상 동작 확인, PTC 통신 확인 X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+5. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LHD, RHD R로직 튜닝 및 기능 점검</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 안건 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>설계 변경 진행을 위한 SW 점검</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 진행 및 검토 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BJ1 변경점 반영된 최종 사양 샘플 11/21 수령 예정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BJ1 PCB 재고 없음, P2 이전 PCB 재활용 예정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>칼로리 사용 예약</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>11/17 ~ 11/21 야간 칼로리 사용 예약 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>11/24 ~ 11/28 주간, 야간 칼로리 사용 예약 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : 12/01 ~ 12/05 야간 칼로리 사용 예약 완료
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LHD, RHD R로직 튜닝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>김진겸 사원 일정 협의 후 진행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - 로직 및 기능 체크리스트 기반 검증 진행</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4366,7 +5565,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="82">
+  <borders count="88">
     <border>
       <left/>
       <right/>
@@ -5491,6 +6690,80 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -5512,7 +6785,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="194">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6061,6 +7334,39 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="72" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="82" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="86" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="86" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="87" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -8545,11 +9851,11 @@
     </row>
     <row r="23" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="57" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C23" s="80"/>
       <c r="D23" s="165" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E23" s="64"/>
       <c r="F23" s="65"/>
@@ -8579,7 +9885,7 @@
       <c r="AD23" s="65"/>
       <c r="AE23" s="65"/>
       <c r="AF23" s="69" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG23" s="68"/>
       <c r="AH23" s="65"/>
@@ -8587,30 +9893,30 @@
       <c r="AJ23" s="65"/>
       <c r="AK23" s="65"/>
       <c r="AL23" s="69" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AM23" s="65"/>
       <c r="AN23" s="66"/>
       <c r="AO23" s="67"/>
       <c r="AP23" s="69"/>
       <c r="AQ23" s="69" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AR23" s="69"/>
       <c r="AS23" s="65"/>
       <c r="AT23" s="69" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AU23" s="69"/>
       <c r="AV23" s="65"/>
       <c r="AW23" s="65"/>
       <c r="AX23" s="69" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AY23" s="69"/>
       <c r="AZ23" s="70"/>
       <c r="BA23" s="166" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="BB23" s="72"/>
       <c r="BC23" s="73"/>
@@ -8626,11 +9932,11 @@
     </row>
     <row r="24" spans="2:64" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="79" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C24" s="164"/>
       <c r="D24" s="162" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E24" s="49"/>
       <c r="F24" s="50"/>
@@ -8662,7 +9968,7 @@
       <c r="AF24" s="50"/>
       <c r="AG24" s="53"/>
       <c r="AH24" s="54" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AI24" s="54"/>
       <c r="AJ24" s="50"/>
@@ -8676,18 +9982,18 @@
       <c r="AR24" s="54"/>
       <c r="AS24" s="50"/>
       <c r="AT24" s="54" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AU24" s="54"/>
       <c r="AV24" s="50"/>
       <c r="AW24" s="50"/>
       <c r="AX24" s="54" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AY24" s="54"/>
       <c r="AZ24" s="55"/>
       <c r="BA24" s="167" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="BB24" s="74"/>
       <c r="BC24" s="75"/>
@@ -10959,7 +12265,9 @@
       </c>
       <c r="G5" s="157"/>
       <c r="H5" s="123"/>
-      <c r="I5" s="135"/>
+      <c r="I5" s="135" t="s">
+        <v>357</v>
+      </c>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="152" t="s">
@@ -10996,7 +12304,7 @@
         <v>311</v>
       </c>
       <c r="G7" s="105" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H7" s="89"/>
       <c r="I7" s="93"/>
@@ -11052,7 +12360,7 @@
       </c>
       <c r="F10" s="114"/>
       <c r="G10" s="105"/>
-      <c r="H10" s="138"/>
+      <c r="H10" s="89"/>
       <c r="I10" s="93"/>
     </row>
     <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -11070,7 +12378,7 @@
       </c>
       <c r="F11" s="114"/>
       <c r="G11" s="105"/>
-      <c r="H11" s="138"/>
+      <c r="H11" s="89"/>
       <c r="I11" s="93"/>
     </row>
     <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -11091,7 +12399,7 @@
       <c r="H12" s="138"/>
       <c r="I12" s="93"/>
     </row>
-    <row r="13" spans="1:9" ht="243" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="283.5" x14ac:dyDescent="0.3">
       <c r="B13" s="132" t="s">
         <v>62</v>
       </c>
@@ -11108,12 +12416,14 @@
         <v>318</v>
       </c>
       <c r="G13" s="157" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H13" s="105" t="s">
-        <v>347</v>
-      </c>
-      <c r="I13" s="134"/>
+        <v>342</v>
+      </c>
+      <c r="I13" s="122" t="s">
+        <v>360</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
       <c r="B14" s="131" t="s">
@@ -11132,13 +12442,13 @@
         <v>310</v>
       </c>
       <c r="G14" s="157" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H14" s="105" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="I14" s="122" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="175.5" x14ac:dyDescent="0.3">
@@ -11161,9 +12471,11 @@
         <v>319</v>
       </c>
       <c r="H15" s="163" t="s">
-        <v>344</v>
-      </c>
-      <c r="I15" s="134"/>
+        <v>349</v>
+      </c>
+      <c r="I15" s="122" t="s">
+        <v>350</v>
+      </c>
     </row>
     <row r="16" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
       <c r="B16" s="131" t="s">
@@ -11182,12 +12494,14 @@
         <v>320</v>
       </c>
       <c r="G16" s="157" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="H16" s="157" t="s">
-        <v>345</v>
-      </c>
-      <c r="I16" s="134"/>
+        <v>344</v>
+      </c>
+      <c r="I16" s="122" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="17" spans="2:9" ht="162" x14ac:dyDescent="0.3">
       <c r="B17" s="130" t="s">
@@ -11206,12 +12520,14 @@
         <v>321</v>
       </c>
       <c r="G17" s="119" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="H17" s="163" t="s">
-        <v>337</v>
-      </c>
-      <c r="I17" s="136"/>
+        <v>345</v>
+      </c>
+      <c r="I17" s="183" t="s">
+        <v>346</v>
+      </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="131" t="s">
@@ -11248,10 +12564,12 @@
       <c r="G19" s="158" t="s">
         <v>289</v>
       </c>
-      <c r="H19" s="137" t="s">
-        <v>343</v>
-      </c>
-      <c r="I19" s="93"/>
+      <c r="H19" s="133" t="s">
+        <v>341</v>
+      </c>
+      <c r="I19" s="134" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="143" t="s">
@@ -11286,4 +12604,422 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
+    <col min="2" max="2" width="9" style="81"/>
+    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
+    <col min="5" max="5" width="43" style="81" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
+    <col min="7" max="10" width="62.125" style="81" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="81"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="109" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="107"/>
+    </row>
+    <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="177" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="181" t="s">
+        <v>176</v>
+      </c>
+      <c r="D2" s="181" t="s">
+        <v>177</v>
+      </c>
+      <c r="E2" s="179" t="s">
+        <v>126</v>
+      </c>
+      <c r="F2" s="175" t="s">
+        <v>352</v>
+      </c>
+      <c r="G2" s="175"/>
+      <c r="H2" s="175"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="176"/>
+    </row>
+    <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="178"/>
+      <c r="C3" s="182"/>
+      <c r="D3" s="182"/>
+      <c r="E3" s="180"/>
+      <c r="F3" s="97" t="s">
+        <v>351</v>
+      </c>
+      <c r="G3" s="97" t="s">
+        <v>353</v>
+      </c>
+      <c r="H3" s="97" t="s">
+        <v>354</v>
+      </c>
+      <c r="I3" s="186" t="s">
+        <v>355</v>
+      </c>
+      <c r="J3" s="98" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="151" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="116" t="s">
+        <v>175</v>
+      </c>
+      <c r="D4" s="116" t="s">
+        <v>178</v>
+      </c>
+      <c r="E4" s="140" t="s">
+        <v>140</v>
+      </c>
+      <c r="F4" s="141"/>
+      <c r="G4" s="142"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="187"/>
+      <c r="J4" s="92"/>
+    </row>
+    <row r="5" spans="1:10" ht="67.5" x14ac:dyDescent="0.3">
+      <c r="B5" s="154" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" s="117" t="s">
+        <v>270</v>
+      </c>
+      <c r="D5" s="117" t="s">
+        <v>180</v>
+      </c>
+      <c r="E5" s="100" t="s">
+        <v>161</v>
+      </c>
+      <c r="F5" s="123" t="s">
+        <v>358</v>
+      </c>
+      <c r="G5" s="157"/>
+      <c r="H5" s="123"/>
+      <c r="I5" s="188"/>
+      <c r="J5" s="135"/>
+    </row>
+    <row r="6" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="152" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="117" t="s">
+        <v>271</v>
+      </c>
+      <c r="D6" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E6" s="100" t="s">
+        <v>161</v>
+      </c>
+      <c r="F6" s="123"/>
+      <c r="G6" s="123"/>
+      <c r="H6" s="123"/>
+      <c r="I6" s="188"/>
+      <c r="J6" s="135"/>
+    </row>
+    <row r="7" spans="1:10" ht="138" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="152" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="117" t="s">
+        <v>271</v>
+      </c>
+      <c r="D7" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E7" s="100" t="s">
+        <v>162</v>
+      </c>
+      <c r="F7" s="123"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="89"/>
+      <c r="I7" s="189"/>
+      <c r="J7" s="93"/>
+    </row>
+    <row r="8" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="152" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="117" t="s">
+        <v>271</v>
+      </c>
+      <c r="D8" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E8" s="91" t="s">
+        <v>139</v>
+      </c>
+      <c r="F8" s="114"/>
+      <c r="G8" s="104"/>
+      <c r="H8" s="89"/>
+      <c r="I8" s="189"/>
+      <c r="J8" s="93"/>
+    </row>
+    <row r="9" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="153" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="117" t="s">
+        <v>271</v>
+      </c>
+      <c r="D9" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E9" s="91" t="s">
+        <v>152</v>
+      </c>
+      <c r="F9" s="114"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="138"/>
+      <c r="I9" s="89"/>
+      <c r="J9" s="93"/>
+    </row>
+    <row r="10" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="153" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" s="117" t="s">
+        <v>271</v>
+      </c>
+      <c r="D10" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E10" s="91" t="s">
+        <v>153</v>
+      </c>
+      <c r="F10" s="114"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="89"/>
+      <c r="I10" s="189"/>
+      <c r="J10" s="93"/>
+    </row>
+    <row r="11" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="153" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" s="117" t="s">
+        <v>271</v>
+      </c>
+      <c r="D11" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E11" s="91" t="s">
+        <v>154</v>
+      </c>
+      <c r="F11" s="114"/>
+      <c r="G11" s="105"/>
+      <c r="H11" s="89"/>
+      <c r="I11" s="189"/>
+      <c r="J11" s="93"/>
+    </row>
+    <row r="12" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="153" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" s="117" t="s">
+        <v>271</v>
+      </c>
+      <c r="D12" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E12" s="91" t="s">
+        <v>155</v>
+      </c>
+      <c r="F12" s="114"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="138"/>
+      <c r="I12" s="89"/>
+      <c r="J12" s="93"/>
+    </row>
+    <row r="13" spans="1:10" ht="283.5" x14ac:dyDescent="0.3">
+      <c r="B13" s="132" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="117" t="s">
+        <v>273</v>
+      </c>
+      <c r="D13" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E13" s="100" t="s">
+        <v>263</v>
+      </c>
+      <c r="F13" s="105" t="s">
+        <v>359</v>
+      </c>
+      <c r="G13" s="157"/>
+      <c r="H13" s="105"/>
+      <c r="I13" s="190"/>
+      <c r="J13" s="122"/>
+    </row>
+    <row r="14" spans="1:10" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="B14" s="131" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="117" t="s">
+        <v>273</v>
+      </c>
+      <c r="D14" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E14" s="100" t="s">
+        <v>264</v>
+      </c>
+      <c r="F14" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="G14" s="157"/>
+      <c r="H14" s="105"/>
+      <c r="I14" s="190"/>
+      <c r="J14" s="122"/>
+    </row>
+    <row r="15" spans="1:10" ht="162" x14ac:dyDescent="0.3">
+      <c r="B15" s="131" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="117" t="s">
+        <v>273</v>
+      </c>
+      <c r="D15" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E15" s="100" t="s">
+        <v>262</v>
+      </c>
+      <c r="F15" s="105" t="s">
+        <v>350</v>
+      </c>
+      <c r="G15" s="158"/>
+      <c r="H15" s="163"/>
+      <c r="I15" s="105"/>
+      <c r="J15" s="122"/>
+    </row>
+    <row r="16" spans="1:10" ht="337.5" x14ac:dyDescent="0.3">
+      <c r="B16" s="131" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="117" t="s">
+        <v>273</v>
+      </c>
+      <c r="D16" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E16" s="100" t="s">
+        <v>265</v>
+      </c>
+      <c r="F16" s="105" t="s">
+        <v>348</v>
+      </c>
+      <c r="G16" s="157"/>
+      <c r="H16" s="157"/>
+      <c r="I16" s="191"/>
+      <c r="J16" s="122"/>
+    </row>
+    <row r="17" spans="2:10" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="B17" s="130" t="s">
+        <v>167</v>
+      </c>
+      <c r="C17" s="117" t="s">
+        <v>273</v>
+      </c>
+      <c r="D17" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E17" s="113" t="s">
+        <v>307</v>
+      </c>
+      <c r="F17" s="119" t="s">
+        <v>346</v>
+      </c>
+      <c r="G17" s="184"/>
+      <c r="H17" s="163"/>
+      <c r="I17" s="105"/>
+      <c r="J17" s="183"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B18" s="131" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" s="117" t="s">
+        <v>273</v>
+      </c>
+      <c r="D18" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E18" s="113"/>
+      <c r="F18" s="155"/>
+      <c r="G18" s="158"/>
+      <c r="H18" s="133"/>
+      <c r="I18" s="129"/>
+      <c r="J18" s="136"/>
+    </row>
+    <row r="19" spans="2:10" ht="54" x14ac:dyDescent="0.3">
+      <c r="B19" s="150" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="139" t="s">
+        <v>273</v>
+      </c>
+      <c r="D19" s="139" t="s">
+        <v>178</v>
+      </c>
+      <c r="E19" s="91" t="s">
+        <v>156</v>
+      </c>
+      <c r="F19" s="133" t="s">
+        <v>347</v>
+      </c>
+      <c r="G19" s="158"/>
+      <c r="H19" s="133"/>
+      <c r="I19" s="192"/>
+      <c r="J19" s="134"/>
+    </row>
+    <row r="20" spans="2:10" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="143" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="144" t="s">
+        <v>273</v>
+      </c>
+      <c r="D20" s="144" t="s">
+        <v>178</v>
+      </c>
+      <c r="E20" s="145" t="s">
+        <v>261</v>
+      </c>
+      <c r="F20" s="161" t="s">
+        <v>266</v>
+      </c>
+      <c r="G20" s="147"/>
+      <c r="H20" s="148"/>
+      <c r="I20" s="193"/>
+      <c r="J20" s="149"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:J2"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="대일정" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="363">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4758,6 +4758,579 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>최대 난방 및 좌우 온도 편차 실차 검증</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>11/14(금) BJ AP2 차량 PTC 개선품 리워크 후 확인 (남양연구소 B1-7)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>11/18(화) ~ 11/20(목) 리워크 완료 AP2 차량 국내 트립 진행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. 한온 BJ LP#2 Event 대응 (11/14)
+  [ 안건 ]
+    - LP2 Event 대응
+  [ 요청사항 ]
+    - 슬로바키아 법인 ↔ 터키 한온 직거래
+  [ 진행 및 검토]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BJ1 LP2 현대자동차 대일정 26. 4. 15 → 26. 5. 1. 변경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : LP2 일정 여유가 있는데, 납품 시기 너무 빠름, 재확인 필요
+    - 12/15 납품을 해야하는 경우
+     : PCB 생산 일정 확인 후, SW 배포 가능 일자 확인
+     : LHD, RHD R로직 튜닝, 체크리스트 기반 기능 및 성능 시험
+     : SW 설계 변경 진행
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BJ1 사이버 보안 적용 단계 및 납품건 확인 (11/17)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 진행 및 검토 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공조시스템설계팀, 품질팀 문의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>QV와 동일하게 진행 요청</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LP2 사이버 보안 적용품 5EA 납품, M 단계 전량 사이버 보안 적용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BJ1 P1 차량 PTC 불량 방문 교체 및 분석 대응 (11/19)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 안건 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BJ1 P1 차량 PTC 불량 방문 교체 및 분석 대응</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 진행 및 검토 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>남양연구소 방문 (11/19)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PTC 교체 전 Test 진행, 상위 제어 통신 &amp; PTC 통신 IGBT Fail Fault 확인 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PTC 교체 후 Test 진행, 상위 제어 통신 정상 동작 확인, PTC 통신 확인 X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+5. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LHD, RHD R로직 튜닝 및 기능 점검</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 안건 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>설계 변경 진행을 위한 SW 점검</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 진행 및 검토 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BJ1 변경점 반영된 최종 사양 샘플 11/21 수령 예정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BJ1 PCB 재고 없음, P2 이전 PCB 재활용 예정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>칼로리 사용 예약</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>11/17 ~ 11/21 야간 칼로리 사용 예약 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>11/24 ~ 11/28 주간, 야간 칼로리 사용 예약 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : 12/01 ~ 12/05 야간 칼로리 사용 예약 완료
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LHD, RHD R로직 튜닝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>김진겸 사원 일정 협의 후 진행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - 로직 및 기능 체크리스트 기반 검증 진행</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. LHD, RHD R로직 튜닝 및 기능 점검
+  [ 안건 ]
+    - SW 점검
+  [ 진행 및 검토 ]
+    - AY LHD 2EA, RHD 2EA PTC 수령 (11/18)
+    - 칼로리 사용 예약
+     : 12/01 ~ 12/12 야간 칼로리 사용 예약 완료
+     : 12/18 ~ 01/02 주간, 야간 칼로리 사용 예약 완료
+    - LHD, RHD R로직 튜닝
+     : 김진겸 사원 일정 협의 후 진행
+    - 로직 및 기능 체크리스트 기반 검증 진행
+2. LHD ESIR
+  [ 안건 ]
+    - AY LHD ESIR 성적서 제출
+  [ 진행 및 검토 ]
+    - LHD ESIR 마감 일정 점검
+    - ES90700-00, ES95480-00 진행 및 성적서 작성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>[임제훈 사원]
 1. 기아샤시시스템품질팀 평택 공장 방문 건 (11/14)
   [ 안건 ]
@@ -4765,7 +5338,7 @@
   [ 요청사항 ]
     - 11월 정기 협의체 회의는 평택 공장 방문 점검으로 대체
     - 정기 협의체 진행 후 요청 자료에 대한 리뷰 (12월 정기 방문시 설명으로 협의)
-  [ 진행 및 검토]
+  [ 진행 및 검토 ]
     - 11/14 서지 내성 평가 Fail (H/W 진행)
      : LP2 생산 물품으로 11/28 재평가 실행 (H/W 진행)
     - 재평가 Fail일 경우 (H/W 결과)
@@ -4778,559 +5351,20 @@
     - 11/28 결과 발표 전, 현재 설계 변경 진행된 S/W V01.02로 M단계 양산 시작
     - 칼로리 사용 예약
      : 12/01 ~ 12/12 야간 칼로리 사용 예약 완료
-     : 12/18 ~ 01/02 주간, 야간 칼로리 사용 예약 완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">[임제훈 사원]
-1. </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>최대 난방 및 좌우 온도 편차 실차 검증</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>11/14(금) BJ AP2 차량 PTC 개선품 리워크 후 확인 (남양연구소 B1-7)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>11/18(화) ~ 11/20(목) 리워크 완료 AP2 차량 국내 트립 진행</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-2. 한온 BJ LP#2 Event 대응 (11/14)
+     : 12/18 ~ 01/02 주간, 야간 칼로리 사용 예약 완료
+2. SVm 향후 진행 방안 협의 (12/02)
   [ 안건 ]
-    - LP2 Event 대응
+    - SVm 서지 평가 결과에 대한 향후 진행 방안 협의
   [ 요청사항 ]
-    - 슬로바키아 법인 ↔ 터키 한온 직거래
-  [ 진행 및 검토]
-    - </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>BJ1 LP2 현대자동차 대일정 26. 4. 15 → 26. 5. 1. 변경</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-     : LP2 일정 여유가 있는데, 납품 시기 너무 빠름, 재확인 필요
-    - 12/15 납품을 해야하는 경우
-     : PCB 생산 일정 확인 후, SW 배포 가능 일자 확인
-     : LHD, RHD R로직 튜닝, 체크리스트 기반 기능 및 성능 시험
-     : SW 설계 변경 진행
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>BJ1 사이버 보안 적용 단계 및 납품건 확인 (11/17)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
+    - 12/02 (화) 14:00 회의 진행
   [ 진행 및 검토 ]
-    - </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>공조시스템설계팀, 품질팀 문의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-     : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>QV와 동일하게 진행 요청</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-     : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>LP2 사이버 보안 적용품 5EA 납품, M 단계 전량 사이버 보안 적용</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-4. </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>BJ1 P1 차량 PTC 불량 방문 교체 및 분석 대응 (11/19)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
+3. SVm LP2용 제어기 별 시그널 점검
   [ 안건 ]
-    - </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>BJ1 P1 차량 PTC 불량 방문 교체 및 분석 대응</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
+    - 각 제어기(공조제어기, 히터컨트롤, 고전압PTC) 간 시그널 체크
+  [ 요청사항 ]
+    - LP2용 고전압 PTC 로컬 CAN 전체 신호 적용 정보 송부 (공조시스템설계팀)
   [ 진행 및 검토 ]
-    - </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>남양연구소 방문 (11/19)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-     : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PTC 교체 전 Test 진행, 상위 제어 통신 &amp; PTC 통신 IGBT Fail Fault 확인 완료</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-     : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PTC 교체 후 Test 진행, 상위 제어 통신 정상 동작 확인, PTC 통신 확인 X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-5. </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>LHD, RHD R로직 튜닝 및 기능 점검</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  [ 안건 ]
-    - </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>설계 변경 진행을 위한 SW 점검</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  [ 진행 및 검토 ]
-    - </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>BJ1 변경점 반영된 최종 사양 샘플 11/21 수령 예정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-     : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>BJ1 PCB 재고 없음, P2 이전 PCB 재활용 예정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-    - </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>칼로리 사용 예약</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-     : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>11/17 ~ 11/21 야간 칼로리 사용 예약 완료</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-     : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>11/24 ~ 11/28 주간, 야간 칼로리 사용 예약 완료</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-     : 12/01 ~ 12/05 야간 칼로리 사용 예약 완료
-    - </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>LHD, RHD R로직 튜닝</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-     : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>김진겸 사원 일정 협의 후 진행</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-    - 로직 및 기능 체크리스트 기반 검증 진행</t>
-    </r>
+    - 로컬 CAN DB 확인 및 송부 자료 작성</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7290,6 +7324,36 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="72" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="82" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="86" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="86" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="87" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7335,38 +7399,8 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="72" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="82" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="86" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="86" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="87" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -8033,90 +8067,90 @@
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="168" t="s">
+      <c r="B2" s="178" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="170" t="s">
+      <c r="C2" s="180" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="170" t="s">
+      <c r="D2" s="180" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="174">
+      <c r="E2" s="184">
         <v>23</v>
       </c>
-      <c r="F2" s="172"/>
-      <c r="G2" s="172"/>
-      <c r="H2" s="172"/>
-      <c r="I2" s="172"/>
-      <c r="J2" s="172"/>
-      <c r="K2" s="172"/>
-      <c r="L2" s="172"/>
-      <c r="M2" s="172"/>
-      <c r="N2" s="172"/>
-      <c r="O2" s="172"/>
-      <c r="P2" s="172"/>
-      <c r="Q2" s="172">
+      <c r="F2" s="182"/>
+      <c r="G2" s="182"/>
+      <c r="H2" s="182"/>
+      <c r="I2" s="182"/>
+      <c r="J2" s="182"/>
+      <c r="K2" s="182"/>
+      <c r="L2" s="182"/>
+      <c r="M2" s="182"/>
+      <c r="N2" s="182"/>
+      <c r="O2" s="182"/>
+      <c r="P2" s="182"/>
+      <c r="Q2" s="182">
         <v>24</v>
       </c>
-      <c r="R2" s="172"/>
-      <c r="S2" s="172"/>
-      <c r="T2" s="172"/>
-      <c r="U2" s="172"/>
-      <c r="V2" s="172"/>
-      <c r="W2" s="172"/>
-      <c r="X2" s="172"/>
-      <c r="Y2" s="172"/>
-      <c r="Z2" s="172"/>
-      <c r="AA2" s="172"/>
-      <c r="AB2" s="172"/>
-      <c r="AC2" s="172">
+      <c r="R2" s="182"/>
+      <c r="S2" s="182"/>
+      <c r="T2" s="182"/>
+      <c r="U2" s="182"/>
+      <c r="V2" s="182"/>
+      <c r="W2" s="182"/>
+      <c r="X2" s="182"/>
+      <c r="Y2" s="182"/>
+      <c r="Z2" s="182"/>
+      <c r="AA2" s="182"/>
+      <c r="AB2" s="182"/>
+      <c r="AC2" s="182">
         <v>25</v>
       </c>
-      <c r="AD2" s="172"/>
-      <c r="AE2" s="172"/>
-      <c r="AF2" s="172"/>
-      <c r="AG2" s="172"/>
-      <c r="AH2" s="172"/>
-      <c r="AI2" s="172"/>
-      <c r="AJ2" s="172"/>
-      <c r="AK2" s="172"/>
-      <c r="AL2" s="172"/>
-      <c r="AM2" s="172"/>
-      <c r="AN2" s="172"/>
-      <c r="AO2" s="172">
+      <c r="AD2" s="182"/>
+      <c r="AE2" s="182"/>
+      <c r="AF2" s="182"/>
+      <c r="AG2" s="182"/>
+      <c r="AH2" s="182"/>
+      <c r="AI2" s="182"/>
+      <c r="AJ2" s="182"/>
+      <c r="AK2" s="182"/>
+      <c r="AL2" s="182"/>
+      <c r="AM2" s="182"/>
+      <c r="AN2" s="182"/>
+      <c r="AO2" s="182">
         <v>26</v>
       </c>
-      <c r="AP2" s="172"/>
-      <c r="AQ2" s="172"/>
-      <c r="AR2" s="172"/>
-      <c r="AS2" s="172"/>
-      <c r="AT2" s="172"/>
-      <c r="AU2" s="172"/>
-      <c r="AV2" s="172"/>
-      <c r="AW2" s="172"/>
-      <c r="AX2" s="172"/>
-      <c r="AY2" s="172"/>
-      <c r="AZ2" s="173"/>
-      <c r="BA2" s="172">
+      <c r="AP2" s="182"/>
+      <c r="AQ2" s="182"/>
+      <c r="AR2" s="182"/>
+      <c r="AS2" s="182"/>
+      <c r="AT2" s="182"/>
+      <c r="AU2" s="182"/>
+      <c r="AV2" s="182"/>
+      <c r="AW2" s="182"/>
+      <c r="AX2" s="182"/>
+      <c r="AY2" s="182"/>
+      <c r="AZ2" s="183"/>
+      <c r="BA2" s="182">
         <v>27</v>
       </c>
-      <c r="BB2" s="172"/>
-      <c r="BC2" s="172"/>
-      <c r="BD2" s="172"/>
-      <c r="BE2" s="172"/>
-      <c r="BF2" s="172"/>
-      <c r="BG2" s="172"/>
-      <c r="BH2" s="172"/>
-      <c r="BI2" s="172"/>
-      <c r="BJ2" s="172"/>
-      <c r="BK2" s="172"/>
-      <c r="BL2" s="173"/>
+      <c r="BB2" s="182"/>
+      <c r="BC2" s="182"/>
+      <c r="BD2" s="182"/>
+      <c r="BE2" s="182"/>
+      <c r="BF2" s="182"/>
+      <c r="BG2" s="182"/>
+      <c r="BH2" s="182"/>
+      <c r="BI2" s="182"/>
+      <c r="BJ2" s="182"/>
+      <c r="BK2" s="182"/>
+      <c r="BL2" s="183"/>
     </row>
     <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="169"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
+      <c r="B3" s="179"/>
+      <c r="C3" s="181"/>
+      <c r="D3" s="181"/>
       <c r="E3" s="22">
         <v>1</v>
       </c>
@@ -10184,39 +10218,39 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="177" t="s">
+      <c r="B2" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="181" t="s">
+      <c r="C2" s="191" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="181" t="s">
+      <c r="D2" s="191" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="179" t="s">
+      <c r="E2" s="189" t="s">
         <v>126</v>
       </c>
       <c r="F2" s="96" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="175" t="s">
+      <c r="G2" s="185" t="s">
         <v>113</v>
       </c>
-      <c r="H2" s="175"/>
-      <c r="I2" s="175"/>
-      <c r="J2" s="176"/>
-      <c r="K2" s="175" t="s">
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="186"/>
+      <c r="K2" s="185" t="s">
         <v>182</v>
       </c>
-      <c r="L2" s="175"/>
-      <c r="M2" s="175"/>
-      <c r="N2" s="176"/>
+      <c r="L2" s="185"/>
+      <c r="M2" s="185"/>
+      <c r="N2" s="186"/>
     </row>
     <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="178"/>
-      <c r="C3" s="182"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="180"/>
+      <c r="B3" s="188"/>
+      <c r="C3" s="192"/>
+      <c r="D3" s="192"/>
+      <c r="E3" s="190"/>
       <c r="F3" s="97" t="s">
         <v>111</v>
       </c>
@@ -10959,30 +10993,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="177" t="s">
+      <c r="B2" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="181" t="s">
+      <c r="C2" s="191" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="181" t="s">
+      <c r="D2" s="191" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="179" t="s">
+      <c r="E2" s="189" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="175" t="s">
+      <c r="F2" s="185" t="s">
         <v>182</v>
       </c>
-      <c r="G2" s="175"/>
-      <c r="H2" s="175"/>
-      <c r="I2" s="176"/>
+      <c r="G2" s="185"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="186"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="178"/>
-      <c r="C3" s="182"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="180"/>
+      <c r="B3" s="188"/>
+      <c r="C3" s="192"/>
+      <c r="D3" s="192"/>
+      <c r="E3" s="190"/>
       <c r="F3" s="97" t="s">
         <v>114</v>
       </c>
@@ -11360,30 +11394,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="177" t="s">
+      <c r="B2" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="181" t="s">
+      <c r="C2" s="191" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="181" t="s">
+      <c r="D2" s="191" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="179" t="s">
+      <c r="E2" s="189" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="175" t="s">
+      <c r="F2" s="185" t="s">
         <v>227</v>
       </c>
-      <c r="G2" s="175"/>
-      <c r="H2" s="175"/>
-      <c r="I2" s="176"/>
+      <c r="G2" s="185"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="186"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="178"/>
-      <c r="C3" s="182"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="180"/>
+      <c r="B3" s="188"/>
+      <c r="C3" s="192"/>
+      <c r="D3" s="192"/>
+      <c r="E3" s="190"/>
       <c r="F3" s="97" t="s">
         <v>114</v>
       </c>
@@ -11767,30 +11801,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="177" t="s">
+      <c r="B2" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="181" t="s">
+      <c r="C2" s="191" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="181" t="s">
+      <c r="D2" s="191" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="179" t="s">
+      <c r="E2" s="189" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="175" t="s">
+      <c r="F2" s="185" t="s">
         <v>259</v>
       </c>
-      <c r="G2" s="175"/>
-      <c r="H2" s="175"/>
-      <c r="I2" s="176"/>
+      <c r="G2" s="185"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="186"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="178"/>
-      <c r="C3" s="182"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="180"/>
+      <c r="B3" s="188"/>
+      <c r="C3" s="192"/>
+      <c r="D3" s="192"/>
+      <c r="E3" s="190"/>
       <c r="F3" s="97" t="s">
         <v>280</v>
       </c>
@@ -12192,30 +12226,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="177" t="s">
+      <c r="B2" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="181" t="s">
+      <c r="C2" s="191" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="181" t="s">
+      <c r="D2" s="191" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="179" t="s">
+      <c r="E2" s="189" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="175" t="s">
+      <c r="F2" s="185" t="s">
         <v>279</v>
       </c>
-      <c r="G2" s="175"/>
-      <c r="H2" s="175"/>
-      <c r="I2" s="176"/>
+      <c r="G2" s="185"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="186"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="178"/>
-      <c r="C3" s="182"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="180"/>
+      <c r="B3" s="188"/>
+      <c r="C3" s="192"/>
+      <c r="D3" s="192"/>
+      <c r="E3" s="190"/>
       <c r="F3" s="97" t="s">
         <v>300</v>
       </c>
@@ -12422,7 +12456,7 @@
         <v>342</v>
       </c>
       <c r="I13" s="122" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
@@ -12445,7 +12479,7 @@
         <v>338</v>
       </c>
       <c r="H14" s="105" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I14" s="122" t="s">
         <v>343</v>
@@ -12525,7 +12559,7 @@
       <c r="H17" s="163" t="s">
         <v>345</v>
       </c>
-      <c r="I17" s="183" t="s">
+      <c r="I17" s="168" t="s">
         <v>346</v>
       </c>
     </row>
@@ -12632,31 +12666,31 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="177" t="s">
+      <c r="B2" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="181" t="s">
+      <c r="C2" s="191" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="181" t="s">
+      <c r="D2" s="191" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="179" t="s">
+      <c r="E2" s="189" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="175" t="s">
+      <c r="F2" s="185" t="s">
         <v>352</v>
       </c>
-      <c r="G2" s="175"/>
-      <c r="H2" s="175"/>
-      <c r="I2" s="185"/>
-      <c r="J2" s="176"/>
+      <c r="G2" s="185"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="193"/>
+      <c r="J2" s="186"/>
     </row>
     <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="178"/>
-      <c r="C3" s="182"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="180"/>
+      <c r="B3" s="188"/>
+      <c r="C3" s="192"/>
+      <c r="D3" s="192"/>
+      <c r="E3" s="190"/>
       <c r="F3" s="97" t="s">
         <v>351</v>
       </c>
@@ -12666,7 +12700,7 @@
       <c r="H3" s="97" t="s">
         <v>354</v>
       </c>
-      <c r="I3" s="186" t="s">
+      <c r="I3" s="170" t="s">
         <v>355</v>
       </c>
       <c r="J3" s="98" t="s">
@@ -12689,7 +12723,7 @@
       <c r="F4" s="141"/>
       <c r="G4" s="142"/>
       <c r="H4" s="88"/>
-      <c r="I4" s="187"/>
+      <c r="I4" s="171"/>
       <c r="J4" s="92"/>
     </row>
     <row r="5" spans="1:10" ht="67.5" x14ac:dyDescent="0.3">
@@ -12710,7 +12744,7 @@
       </c>
       <c r="G5" s="157"/>
       <c r="H5" s="123"/>
-      <c r="I5" s="188"/>
+      <c r="I5" s="172"/>
       <c r="J5" s="135"/>
     </row>
     <row r="6" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -12729,7 +12763,7 @@
       <c r="F6" s="123"/>
       <c r="G6" s="123"/>
       <c r="H6" s="123"/>
-      <c r="I6" s="188"/>
+      <c r="I6" s="172"/>
       <c r="J6" s="135"/>
     </row>
     <row r="7" spans="1:10" ht="138" customHeight="1" x14ac:dyDescent="0.3">
@@ -12748,7 +12782,7 @@
       <c r="F7" s="123"/>
       <c r="G7" s="105"/>
       <c r="H7" s="89"/>
-      <c r="I7" s="189"/>
+      <c r="I7" s="173"/>
       <c r="J7" s="93"/>
     </row>
     <row r="8" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -12767,7 +12801,7 @@
       <c r="F8" s="114"/>
       <c r="G8" s="104"/>
       <c r="H8" s="89"/>
-      <c r="I8" s="189"/>
+      <c r="I8" s="173"/>
       <c r="J8" s="93"/>
     </row>
     <row r="9" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -12805,7 +12839,7 @@
       <c r="F10" s="114"/>
       <c r="G10" s="105"/>
       <c r="H10" s="89"/>
-      <c r="I10" s="189"/>
+      <c r="I10" s="173"/>
       <c r="J10" s="93"/>
     </row>
     <row r="11" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -12824,7 +12858,7 @@
       <c r="F11" s="114"/>
       <c r="G11" s="105"/>
       <c r="H11" s="89"/>
-      <c r="I11" s="189"/>
+      <c r="I11" s="173"/>
       <c r="J11" s="93"/>
     </row>
     <row r="12" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -12846,7 +12880,7 @@
       <c r="I12" s="89"/>
       <c r="J12" s="93"/>
     </row>
-    <row r="13" spans="1:10" ht="283.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="409.5" x14ac:dyDescent="0.3">
       <c r="B13" s="132" t="s">
         <v>62</v>
       </c>
@@ -12860,11 +12894,11 @@
         <v>263</v>
       </c>
       <c r="F13" s="105" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="G13" s="157"/>
       <c r="H13" s="105"/>
-      <c r="I13" s="190"/>
+      <c r="I13" s="174"/>
       <c r="J13" s="122"/>
     </row>
     <row r="14" spans="1:10" ht="409.5" x14ac:dyDescent="0.3">
@@ -12885,10 +12919,10 @@
       </c>
       <c r="G14" s="157"/>
       <c r="H14" s="105"/>
-      <c r="I14" s="190"/>
+      <c r="I14" s="174"/>
       <c r="J14" s="122"/>
     </row>
-    <row r="15" spans="1:10" ht="162" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="243" x14ac:dyDescent="0.3">
       <c r="B15" s="131" t="s">
         <v>55</v>
       </c>
@@ -12902,7 +12936,7 @@
         <v>262</v>
       </c>
       <c r="F15" s="105" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="G15" s="158"/>
       <c r="H15" s="163"/>
@@ -12927,7 +12961,7 @@
       </c>
       <c r="G16" s="157"/>
       <c r="H16" s="157"/>
-      <c r="I16" s="191"/>
+      <c r="I16" s="175"/>
       <c r="J16" s="122"/>
     </row>
     <row r="17" spans="2:10" ht="40.5" x14ac:dyDescent="0.3">
@@ -12946,10 +12980,10 @@
       <c r="F17" s="119" t="s">
         <v>346</v>
       </c>
-      <c r="G17" s="184"/>
+      <c r="G17" s="169"/>
       <c r="H17" s="163"/>
       <c r="I17" s="105"/>
-      <c r="J17" s="183"/>
+      <c r="J17" s="168"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="131" t="s">
@@ -12986,7 +13020,7 @@
       </c>
       <c r="G19" s="158"/>
       <c r="H19" s="133"/>
-      <c r="I19" s="192"/>
+      <c r="I19" s="176"/>
       <c r="J19" s="134"/>
     </row>
     <row r="20" spans="2:10" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -13007,7 +13041,7 @@
       </c>
       <c r="G20" s="147"/>
       <c r="H20" s="148"/>
-      <c r="I20" s="193"/>
+      <c r="I20" s="177"/>
       <c r="J20" s="149"/>
     </row>
   </sheetData>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="364">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4015,41 +4015,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[임제훈 사원]
-1. AP2 PTC 개선품 리워크 차량 최대 난방 및 좌우 온도 편차 실차 검증 (11/26)
-  [ 안건 ]
-    - 최대 난방 평가 및 좌우 온도 편차 실차 검증
-  [ 진행 및 검토 ]
-    - 최대 난방 평가
-      : 첫 플로어 모드 종료 시, 실내 온도 19℃ 이상 요구
-      : 19.2℃로 난방 성능 만족 (Pass)
-    - 좌우 온도 편차 검증
-      : 디프 모드 토출부 좌우 온도 편차 3.6℃ (Pass)
-      : 플로어 모드 1열 토출부 좌우 온도 편차 1.9℃ ~ 3℃ 내 수렴 (Pass)
-      : 플로어 모드 2열 토출부 좌우 온도 편차 0.4℃ ~ 1.5℃ 내 수렴 (Pass)
-2. 한온 BJ LP#2 Event 일정 확인
-  [ 안건 ]
-    - LP2 Event 대응
-  [ 요청사항 ]
-    - 슬로바키아 법인 ↔ 터키 한온 직거래
-  [ 진행 및 검토 ]
-    - LP2 Event 관련 생산 일정 확인 및 S/W 배포 일자 확인
-    - S/W R로직 QV와 동일하게 진행
-    - S/W 성능 및 기능 점검
-    - S/W 설계 변경 진행
-3. 사이버 보안 관련 자료 회신 요청
-  [ 요청사항 ]
-    - 사이버 보안 QV와 동일한 이력으로 진행 요청 (공조시스템설계팀)
-    - BJ1 ES95489-21 성적서 회신
-    - 사이버보안관련성평가 작성 후 회신
-  [ 진행 및 검토 ]
-    - BJ1 ES95489-21, ESIR 때 성적서 없음
-      : QV 사이버 보안 협의 및 일정 지연으로 BJ1 ESIR때 진행 불가
-      : BJ1 ES95489-21 검증 진행
-    - 사이버보안관련성평가 작성 후 검토 요청</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">[임제훈 사원]
 1. </t>
@@ -4727,14 +4692,6 @@
   </si>
   <si>
     <t>[임제훈 사원]
-- SWE.3 SDDS 후속 작업 (진행률 : 97%)
-- SRS, SADS, SDDS ALM 등록 (~12/05)
-[조현진 전임]
-- SWE.1, 2, 3 등록에 맞추어 SWE. 4, 5, 6 ALM 등록</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
 1. 기아샤시시스템품질팀 평택 공장 방문 건 (11/14)
   [ 안건 ]
     - 서지 내성 평가 (H/W 진행)
@@ -5331,40 +5288,308 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AP2 PTC 개선품 리워크 차량 최대 난방 및 좌우 온도 편차 실차 검증 (11/26)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 안건 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>최대 난방 평가 및 좌우 온도 편차 실차 검증</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 진행 및 검토 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>최대 난방 평가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>첫 플로어 모드 종료 시, 실내 온도 19℃ 이상 요구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>19.2℃로 난방 성능 만족 (Pass)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>좌우 온도 편차 검증</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>디프 모드 토출부 좌우 온도 편차 3.6℃ (Pass)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>플로어 모드 1열 토출부 좌우 온도 편차 1.9℃ ~ 3℃ 내 수렴 (Pass)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>플로어 모드 2열 토출부 좌우 온도 편차 0.4℃ ~ 1.5℃ 내 수렴 (Pass)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. 한온 BJ LP#2 Event 일정 확인
+  [ 안건 ]
+    - LP2 Event 대응
+  [ 요청사항 ]
+    - 슬로바키아 법인 ↔ 터키 한온 직거래
+  [ 진행 및 검토 ]
+    - LP2 Event 관련 생산 일정 확인 및 S/W 배포 일자 확인
+    - S/W R로직 QV와 동일하게 진행
+    - S/W 성능 및 기능 점검
+    - S/W 설계 변경 진행
+3. 사이버 보안 관련 자료 회신 요청
+  [ 요청사항 ]
+    - 사이버 보안 QV와 동일한 이력으로 진행 요청 (공조시스템설계팀)
+    - BJ1 ES95489-21 성적서 회신
+    - 사이버보안관련성평가 작성 후 회신
+  [ 진행 및 검토 ]
+    - BJ1 ES95489-21, ESIR 때 성적서 없음
+      : QV 사이버 보안 협의 및 일정 지연으로 BJ1 ESIR때 진행 불가
+      : BJ1 ES95489-21 검증 진행
+    - 사이버보안관련성평가 작성 후 검토 요청</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>[임제훈 사원]
-1. 기아샤시시스템품질팀 평택 공장 방문 건 (11/14)
-  [ 안건 ]
-    - 서지 내성 평가 (H/W 진행)
-  [ 요청사항 ]
-    - 11월 정기 협의체 회의는 평택 공장 방문 점검으로 대체
-    - 정기 협의체 진행 후 요청 자료에 대한 리뷰 (12월 정기 방문시 설명으로 협의)
-  [ 진행 및 검토 ]
-    - 11/14 서지 내성 평가 Fail (H/W 진행)
-     : LP2 생산 물품으로 11/28 재평가 실행 (H/W 진행)
-    - 재평가 Fail일 경우 (H/W 결과)
-     : S/W LV, HV, 전력 센싱 값 확인 및 튜닝
-     : R로직 튜닝, 체크리스트 기반 기능 및 성능 시험
-     : S/W 설계 변경 필요
-     : 변경점 반영된 샘플 수령 후, S/W 검증 소요 시간 4주 요청
-    - 재평가 Pass일 경우 (H/W 결과)
-     : S/W 변경사항 없음
-    - 11/28 결과 발표 전, 현재 설계 변경 진행된 S/W V01.02로 M단계 양산 시작
-    - 칼로리 사용 예약
-     : 12/01 ~ 12/12 야간 칼로리 사용 예약 완료
-     : 12/18 ~ 01/02 주간, 야간 칼로리 사용 예약 완료
-2. SVm 향후 진행 방안 협의 (12/02)
-  [ 안건 ]
-    - SVm 서지 평가 결과에 대한 향후 진행 방안 협의
-  [ 요청사항 ]
-    - 12/02 (화) 14:00 회의 진행
-  [ 진행 및 검토 ]
-3. SVm LP2용 제어기 별 시그널 점검
+- SWE.3 SDDS 후속 작업 (진행률 : 97%)
+[조현진 전임]
+- SWE.1, 2, 3 등록에 맞추어 SWE. 4, 5, 6 ALM 등록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. SVm LP2용 제어기 별 시그널 점검 (12/02)
   [ 안건 ]
     - 각 제어기(공조제어기, 히터컨트롤, 고전압PTC) 간 시그널 체크
   [ 요청사항 ]
     - LP2용 고전압 PTC 로컬 CAN 전체 신호 적용 정보 송부 (공조시스템설계팀)
   [ 진행 및 검토 ]
-    - 로컬 CAN DB 확인 및 송부 자료 작성</t>
+    - 로컬 CAN DB 확인 및 사용 Signal 회신
+     : 25년 3분기 로컬 CAN 최종본 기준, SVm PTC 사용 중인 Signal 회신 완료
+2. SVm 서지 내성 향후 진행 사항 회의 (12/02)
+  [ 안건 ]
+    - 서지 내성 평가 결과 발표 (H/W)
+  [ 요청사항 ]
+    - BJ1에 비해 SVm이 서지 내성에 열세인 이유 설명 요청 (H/W)
+    - SVm 4EA, QV 3EA, BJ1 3EA 서지 내성 재평가 (H/W)
+     : 12/11 회의 예정
+  [ 진행 및 검토 ]
+    - 재평가 Fail일 경우 (H/W 결과)
+     : S/W 설계 변경 필요
+     : S/W LV, HV, 전력 센싱 값 확인 및 튜닝
+     : R로직 튜닝, 체크리스트 기반 기능 및 성능 시험
+     : 변경점 반영된 샘플 수령 후, S/W 검증 소요 시간 4주 요청 완료
+    - 재평가 Pass일 경우 (H/W 결과)
+     : S/W 변경사항 없음
+    - 칼로리 사용 예약
+     : 12/01 ~ 12/12 야간 칼로리 사용 예약 완료
+     : 12/18 ~ 01/02 주간, 야간 칼로리 사용 예약 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. S/W 설계 변경 (~12/05)
+  [ 안건 ]
+    - S/W 설계 변경
+  [ 요청사항 ]
+    - LP2 납품 슬로바키아 법인 ↔ 터키 한온 직거래
+  [ 진행 및 검토 ]
+    - LP2 정확한 납품 일정 없음
+    - S/W 설계 변경 진행
+     : S/W R로직 QV와 동일하게 진행
+     : S/W 성능 및 기능 점검
+2. 사이버 보안 관련 자료 회신 요청 (~12/05)
+  [ 요청사항 ]
+    - 사이버 보안 QV와 동일한 이력으로 진행 요청 (공조시스템설계팀)
+    - BJ1 ES95489-21 성적서 회신
+    - 사이버보안관련성평가 작성 후 회신
+  [ 진행 및 검토 ]
+    - BJ1 ES95489-21, ESIR 때 성적서 없음
+      : QV 사이버 보안 협의 및 일정 지연으로 BJ1 ESIR때 진행 불가
+      : BJ1 ES95489-21 검증 진행
+    - 사이버보안관련성평가 작성 후 검토 요청</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -12300,7 +12525,7 @@
       <c r="G5" s="157"/>
       <c r="H5" s="123"/>
       <c r="I5" s="135" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -12456,7 +12681,7 @@
         <v>342</v>
       </c>
       <c r="I13" s="122" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
@@ -12479,10 +12704,10 @@
         <v>338</v>
       </c>
       <c r="H14" s="105" t="s">
+        <v>358</v>
+      </c>
+      <c r="I14" s="122" t="s">
         <v>360</v>
-      </c>
-      <c r="I14" s="122" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="175.5" x14ac:dyDescent="0.3">
@@ -12505,10 +12730,10 @@
         <v>319</v>
       </c>
       <c r="H15" s="163" t="s">
+        <v>348</v>
+      </c>
+      <c r="I15" s="122" t="s">
         <v>349</v>
-      </c>
-      <c r="I15" s="122" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
@@ -12531,10 +12756,10 @@
         <v>339</v>
       </c>
       <c r="H16" s="157" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I16" s="122" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="162" x14ac:dyDescent="0.3">
@@ -12557,10 +12782,10 @@
         <v>340</v>
       </c>
       <c r="H17" s="163" t="s">
+        <v>344</v>
+      </c>
+      <c r="I17" s="168" t="s">
         <v>345</v>
-      </c>
-      <c r="I17" s="168" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
@@ -12602,7 +12827,7 @@
         <v>341</v>
       </c>
       <c r="I19" s="134" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -12679,7 +12904,7 @@
         <v>126</v>
       </c>
       <c r="F2" s="185" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G2" s="185"/>
       <c r="H2" s="185"/>
@@ -12692,19 +12917,19 @@
       <c r="D3" s="192"/>
       <c r="E3" s="190"/>
       <c r="F3" s="97" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G3" s="97" t="s">
+        <v>352</v>
+      </c>
+      <c r="H3" s="97" t="s">
         <v>353</v>
       </c>
-      <c r="H3" s="97" t="s">
+      <c r="I3" s="170" t="s">
         <v>354</v>
       </c>
-      <c r="I3" s="170" t="s">
+      <c r="J3" s="98" t="s">
         <v>355</v>
-      </c>
-      <c r="J3" s="98" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -12726,7 +12951,7 @@
       <c r="I4" s="171"/>
       <c r="J4" s="92"/>
     </row>
-    <row r="5" spans="1:10" ht="67.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="54" x14ac:dyDescent="0.3">
       <c r="B5" s="154" t="s">
         <v>181</v>
       </c>
@@ -12740,7 +12965,7 @@
         <v>161</v>
       </c>
       <c r="F5" s="123" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G5" s="157"/>
       <c r="H5" s="123"/>
@@ -12880,7 +13105,7 @@
       <c r="I12" s="89"/>
       <c r="J12" s="93"/>
     </row>
-    <row r="13" spans="1:10" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="364.5" x14ac:dyDescent="0.3">
       <c r="B13" s="132" t="s">
         <v>62</v>
       </c>
@@ -12901,7 +13126,7 @@
       <c r="I13" s="174"/>
       <c r="J13" s="122"/>
     </row>
-    <row r="14" spans="1:10" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="283.5" x14ac:dyDescent="0.3">
       <c r="B14" s="131" t="s">
         <v>73</v>
       </c>
@@ -12915,7 +13140,7 @@
         <v>264</v>
       </c>
       <c r="F14" s="105" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="G14" s="157"/>
       <c r="H14" s="105"/>
@@ -12936,7 +13161,7 @@
         <v>262</v>
       </c>
       <c r="F15" s="105" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G15" s="158"/>
       <c r="H15" s="163"/>
@@ -12957,7 +13182,7 @@
         <v>265</v>
       </c>
       <c r="F16" s="105" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G16" s="157"/>
       <c r="H16" s="157"/>
@@ -12978,7 +13203,7 @@
         <v>307</v>
       </c>
       <c r="F17" s="119" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G17" s="169"/>
       <c r="H17" s="163"/>
@@ -13016,7 +13241,7 @@
         <v>156</v>
       </c>
       <c r="F19" s="133" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G19" s="158"/>
       <c r="H19" s="133"/>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="371">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5540,14 +5540,276 @@
   </si>
   <si>
     <t>[임제훈 사원]
-1. SVm LP2용 제어기 별 시그널 점검 (12/02)
+1. LHD, RHD R로직 튜닝 및 기능 점검
   [ 안건 ]
-    - 각 제어기(공조제어기, 히터컨트롤, 고전압PTC) 간 시그널 체크
-  [ 요청사항 ]
-    - LP2용 고전압 PTC 로컬 CAN 전체 신호 적용 정보 송부 (공조시스템설계팀)
+    - SW 점검
   [ 진행 및 검토 ]
-    - 로컬 CAN DB 확인 및 사용 Signal 회신
-     : 25년 3분기 로컬 CAN 최종본 기준, SVm PTC 사용 중인 Signal 회신 완료
+    - AY LHD 2EA, RHD 2EA PTC 수령 (11/18)
+    - 칼로리 사용 예약
+     : 12/01 ~ 12/12 야간 칼로리 사용 예약 완료
+     : 12/18 ~ 01/02 주간, 야간 칼로리 사용 예약 완료
+    - LHD, RHD R로직 튜닝
+     : 김진겸 사원 일정 협의 후 진행
+    - 로직 및 기능 체크리스트 기반 검증 진행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. 기구 변경 건 (11/14)
+  [ 안건 ]
+    - Stone TC 160℃ → 165℃ 변경
+    - 전압 범위 변경
+     : 정격 전압 360V → 351V
+     : 최대 동작 전압 403.2V → 413V
+    - LINEAR MAX 성능 7000W 변경
+    - 제어 사양서, S/W 재배포 요청
+  [ 진행 및 검토 ]
+    - 165℃ 적용된 마스터 샘플 재고 부족으로 제작 불가
+    - NX5e 11/21 LHD, RHD PCB 생산 예정일에 맞추어 S/W 재배포 불가
+     : P1 최종 사양 반영된 샘플 12/5 ~ 12/12 수령 예정
+     : 1월 ALL TOOL 예정, 변경된 S/W 라이팅
+    - R로직 튜닝
+     : 12/01 ~ 12/12 야간 칼로리 사용 예약 완료
+     : 12/18 ~ 01/02 주간, 야간 칼로리 사용 예약 완료
+    - 로직 및 기능 체크리스트 기반 검증 진행
+    - 설계 변경으로 진행해야 하는지 확인
+2. ESIR (~12/05)
+  [ 안건 ]
+    - ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24 ESIR 진행
+  [ 진행 및 검토 ]
+    - ES95489-21 (100%)
+    - ES95489-24 (100%)
+    - ES95411-00 (95%, ~12/05)
+    - ES90700-00 (55%, ~12/05)
+    - ES95480-00 (55%, ~12/05)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. 기구 변경 건 (11/14)
+  [ 안건 ]
+    - Stone TC 160℃ → 165℃ 변경
+    - 전압 범위 변경
+     : 정격 전압 360V → 351V
+     : 최대 동작 전압 403.2V → 413V
+    - LINEAR MAX 성능 7000W 변경
+    - 제어 사양서, S/W 재배포 요청
+  [ 진행 및 검토 ]
+    - 165℃ 적용된 마스터 샘플 재고 부족으로 제작 불가
+    - NX5e 11/21 LHD, RHD PCB 생산 예정일에 맞추어 S/W 재배포 불가
+     : P1 최종 사양 반영된 샘플 12/5 ~ 12/12 수령 예정
+     : 1월 ALL TOOL 예정, 변경된 S/W 라이팅
+    - R로직 튜닝
+     : 12/01 ~ 12/12 야간 칼로리 사용 예약 완료
+     : 12/18 ~ 01/02 주간, 야간 칼로리 사용 예약 완료
+    - 로직 및 기능 체크리스트 기반 검증 진행
+    - 설계 변경으로 진행해야 하는지 확인
+2. ESIR (~12/05)
+  [ 안건 ]
+    - ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24 ESIR 진행
+  [ 진행 및 검토 ]
+    - ES95489-21 (100%)
+    - ES95489-24 (100%)
+    - ES95411-00 (95%, ~12/05)
+    - ES90700-00 (55%, ~12/05)
+    - ES95480-00 (55%, ~12/05)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SVm LP2용 제어기 별 시그널 점검 (12/02)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ 안건 ]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>각 제어기(공조제어기, 히터컨트롤, 고전압PTC) 간 시그널 체크</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ 요청사항 ]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LP2용 고전압 PTC 로컬 CAN 전체 신호 적용 정보 송부 (공조시스템설계팀)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ 진행 및 검토 ]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>로컬 CAN DB 확인 및 사용 Signal 회신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>25년 3분기 로컬 CAN 최종본 기준, SVm PTC 사용 중인 Signal 회신 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 2. SVm 서지 내성 향후 진행 사항 회의 (12/02)
   [ 안건 ]
     - 서지 내성 평가 결과 발표 (H/W)
@@ -5566,20 +5828,252 @@
     - 칼로리 사용 예약
      : 12/01 ~ 12/12 야간 칼로리 사용 예약 완료
      : 12/18 ~ 01/02 주간, 야간 칼로리 사용 예약 완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-1. S/W 설계 변경 (~12/05)
-  [ 안건 ]
-    - S/W 설계 변경
-  [ 요청사항 ]
-    - LP2 납품 슬로바키아 법인 ↔ 터키 한온 직거래
-  [ 진행 및 검토 ]
-    - LP2 정확한 납품 일정 없음
-    - S/W 설계 변경 진행
-     : S/W R로직 QV와 동일하게 진행
-     : S/W 성능 및 기능 점검
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S/W 설계 변경 (~12/05)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">[ 안건 ]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S/W 설계 변경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ 요청사항 ]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LP2 납품 슬로바키아 법인 ↔ 터키 한온 직거래</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ 진행 및 검토 ]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LP2 정확한 납품 일정 없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S/W 설계 변경 진행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S/W R로직 QV와 동일하게 진행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S/W 성능 및 기능 점검</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 2. 사이버 보안 관련 자료 회신 요청 (~12/05)
   [ 요청사항 ]
     - 사이버 보안 QV와 동일한 이력으로 진행 요청 (공조시스템설계팀)
@@ -5590,6 +6084,70 @@
       : QV 사이버 보안 협의 및 일정 지연으로 BJ1 ESIR때 진행 불가
       : BJ1 ES95489-21 검증 진행
     - 사이버보안관련성평가 작성 후 검토 요청</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. S/W 설계 변경 (12/05)
+  [ 안건 ]
+    - S/W 설계 변경
+  [ 진행 및 검토 ]
+    - 전자 결재 상신
+2. 사이버 보안 관련 자료 회신 요청 (~12/05)
+  [ 요청사항 ]
+    - 사이버 보안 QV와 동일한 이력으로 진행 요청 (공조시스템설계팀)
+    - BJ1 ES95489-21 성적서 회신
+    - 사이버보안관련성평가 작성 후 회신
+  [ 진행 및 검토 ]
+    - BJ1 ES95489-21, ESIR 때 성적서 없음
+      : QV 사이버 보안 협의 및 일정 지연으로 BJ1 ESIR때 진행 불가
+      : BJ1 ES95489-21 검증 진행
+    - 사이버보안관련성평가 작성 후 검토 요청
+3. BJ1 PTC 리워크 (12/09)
+  [ 안건 ]
+    - AP2 차량 PTC 제거 후, SP 차량에 리워크
+  [ 요청사항 ]
+    - 한온시스템 방문 후 리워크
+  [ 진행 및 검토 ]
+    - 차량 리워크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. SVm 서지 내성 향후 진행 사항 회의 (12/02)
+  [ 안건 ]
+    - 서지 내성 평가 결과 발표 (H/W)
+  [ 요청사항 ]
+    - BJ1에 비해 SVm이 서지 내성에 열세인 이유 설명 요청 (H/W)
+    - SVm 4EA, QV 3EA, BJ1 3EA 서지 내성 재평가 (H/W 12/08)
+     : 12/11 회의 예정
+  [ 진행 및 검토 ]
+    - 재평가 Fail일 경우 (H/W 결과)
+     : S/W 설계 변경 필요
+     : S/W LV, HV, 전력 센싱 값 확인 및 튜닝
+     : R로직 튜닝, 체크리스트 기반 기능 및 성능 시험
+     : 변경점 반영된 샘플 수령 후, S/W 검증 소요 시간 4주 요청 완료
+    - 재평가 Pass일 경우 (H/W 결과)
+     : S/W 변경사항 없음
+    - 칼로리 사용 예약
+     : 12/01 ~ 12/12 야간 칼로리 사용 예약 완료
+     : 12/18 ~ 01/02 주간, 야간 칼로리 사용 예약 완료
+2. SVm 설계 변경 기안 대결자 진행 (12/08)
+  [ 안건 ]
+    - 전자결재 대결자 선정
+  [ 진행 및 검토 ]
+    - 퇴사자 부서의 대결할 인원이 작업의뢰서_정보팀 작성해야 함.
+     : 남시온 선임</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. 제어사양서 작성, 로직점검 체크리스트 작성, 고장진단 사양 검토 후 갱신</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 이슈 없음</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -12967,7 +13525,9 @@
       <c r="F5" s="123" t="s">
         <v>361</v>
       </c>
-      <c r="G5" s="157"/>
+      <c r="G5" s="123" t="s">
+        <v>361</v>
+      </c>
       <c r="H5" s="123"/>
       <c r="I5" s="172"/>
       <c r="J5" s="135"/>
@@ -13119,14 +13679,16 @@
         <v>263</v>
       </c>
       <c r="F13" s="105" t="s">
-        <v>362</v>
-      </c>
-      <c r="G13" s="157"/>
+        <v>365</v>
+      </c>
+      <c r="G13" s="157" t="s">
+        <v>368</v>
+      </c>
       <c r="H13" s="105"/>
       <c r="I13" s="174"/>
       <c r="J13" s="122"/>
     </row>
-    <row r="14" spans="1:10" ht="283.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="310.5" x14ac:dyDescent="0.3">
       <c r="B14" s="131" t="s">
         <v>73</v>
       </c>
@@ -13140,9 +13702,11 @@
         <v>264</v>
       </c>
       <c r="F14" s="105" t="s">
-        <v>363</v>
-      </c>
-      <c r="G14" s="157"/>
+        <v>366</v>
+      </c>
+      <c r="G14" s="157" t="s">
+        <v>367</v>
+      </c>
       <c r="H14" s="105"/>
       <c r="I14" s="174"/>
       <c r="J14" s="122"/>
@@ -13163,12 +13727,14 @@
       <c r="F15" s="105" t="s">
         <v>359</v>
       </c>
-      <c r="G15" s="158"/>
+      <c r="G15" s="157" t="s">
+        <v>362</v>
+      </c>
       <c r="H15" s="163"/>
       <c r="I15" s="105"/>
       <c r="J15" s="122"/>
     </row>
-    <row r="16" spans="1:10" ht="337.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="378" x14ac:dyDescent="0.3">
       <c r="B16" s="131" t="s">
         <v>85</v>
       </c>
@@ -13182,9 +13748,11 @@
         <v>265</v>
       </c>
       <c r="F16" s="105" t="s">
-        <v>347</v>
-      </c>
-      <c r="G16" s="157"/>
+        <v>363</v>
+      </c>
+      <c r="G16" s="157" t="s">
+        <v>364</v>
+      </c>
       <c r="H16" s="157"/>
       <c r="I16" s="175"/>
       <c r="J16" s="122"/>
@@ -13205,7 +13773,9 @@
       <c r="F17" s="119" t="s">
         <v>345</v>
       </c>
-      <c r="G17" s="169"/>
+      <c r="G17" s="169" t="s">
+        <v>369</v>
+      </c>
       <c r="H17" s="163"/>
       <c r="I17" s="105"/>
       <c r="J17" s="168"/>
@@ -13227,7 +13797,7 @@
       <c r="I18" s="129"/>
       <c r="J18" s="136"/>
     </row>
-    <row r="19" spans="2:10" ht="54" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="150" t="s">
         <v>3</v>
       </c>
@@ -13240,8 +13810,8 @@
       <c r="E19" s="91" t="s">
         <v>156</v>
       </c>
-      <c r="F19" s="133" t="s">
-        <v>346</v>
+      <c r="F19" s="105" t="s">
+        <v>370</v>
       </c>
       <c r="G19" s="158"/>
       <c r="H19" s="133"/>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\일정\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Task\000_PJT\000_Heater\111_PTC\1.doc\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685"/>
   </bookViews>
   <sheets>
     <sheet name="대일정" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="372">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2392,14 +2392,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[공조시스템설계팀] 
-김응영 책임 010-7635-0265
-key@hyundai.com
-이웅기 연구원 010-8427-8230
-lwg8230@hyundai.com</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[조현진 전임]
 - 10월 31일 현대자동차 남양연구소 난방평가 요청(from. 김민수 선임)
   1) T-Car와 Proto 토출온 20도 차이(HVAC 문제로 파악됨)
@@ -6148,6 +6140,27 @@
   </si>
   <si>
     <t>- 이슈 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M
+8/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+[우리산업]
+PM : 유정호, 오민석
+부품개발 : 김기환, 장영수
+제조기술 : 김국진, 제품관리 : 백성진
+품질 : 조재길
+기구 : 김승면, 서동권, HW : 신지훈
+[공조시스템설계팀] 
+김응영 책임 010-7635-0265
+key@hyundai.com
+이웅기 연구원 010-8427-8230
+lwg8230@hyundai.com
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8254,16 +8267,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>310763</xdr:colOff>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>283550</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>353786</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>340776</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>108857</xdr:rowOff>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>313563</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>176893</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -8272,7 +8285,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="12502763" y="353786"/>
+          <a:off x="13754621" y="0"/>
           <a:ext cx="30013" cy="27350357"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -9674,7 +9687,7 @@
         <v>77</v>
       </c>
       <c r="D11" s="160" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="7"/>
@@ -9757,7 +9770,7 @@
         <v>105</v>
       </c>
       <c r="D12" s="160" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="7"/>
@@ -9838,7 +9851,7 @@
         <v>82</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="7"/>
@@ -10275,7 +10288,7 @@
         <v>258</v>
       </c>
       <c r="D18" s="160" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E18" s="64"/>
       <c r="F18" s="65"/>
@@ -10514,7 +10527,7 @@
       <c r="BK20" s="73"/>
       <c r="BL20" s="70"/>
     </row>
-    <row r="21" spans="2:64" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:64" ht="189" x14ac:dyDescent="0.3">
       <c r="B21" s="57" t="s">
         <v>109</v>
       </c>
@@ -10522,7 +10535,7 @@
         <v>107</v>
       </c>
       <c r="D21" s="34" t="s">
-        <v>294</v>
+        <v>371</v>
       </c>
       <c r="E21" s="64"/>
       <c r="F21" s="65"/>
@@ -10577,9 +10590,7 @@
       <c r="AY21" s="69"/>
       <c r="AZ21" s="70"/>
       <c r="BA21" s="67"/>
-      <c r="BB21" s="13" t="s">
-        <v>195</v>
-      </c>
+      <c r="BB21" s="13"/>
       <c r="BC21" s="73"/>
       <c r="BD21" s="69" t="s">
         <v>233</v>
@@ -10589,7 +10600,9 @@
       <c r="BG21" s="69" t="s">
         <v>234</v>
       </c>
-      <c r="BH21" s="73"/>
+      <c r="BH21" s="73" t="s">
+        <v>370</v>
+      </c>
       <c r="BI21" s="69" t="s">
         <v>235</v>
       </c>
@@ -10668,11 +10681,11 @@
     </row>
     <row r="23" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="57" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C23" s="80"/>
       <c r="D23" s="165" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E23" s="64"/>
       <c r="F23" s="65"/>
@@ -10702,7 +10715,7 @@
       <c r="AD23" s="65"/>
       <c r="AE23" s="65"/>
       <c r="AF23" s="69" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG23" s="68"/>
       <c r="AH23" s="65"/>
@@ -10710,30 +10723,30 @@
       <c r="AJ23" s="65"/>
       <c r="AK23" s="65"/>
       <c r="AL23" s="69" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AM23" s="65"/>
       <c r="AN23" s="66"/>
       <c r="AO23" s="67"/>
       <c r="AP23" s="69"/>
       <c r="AQ23" s="69" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AR23" s="69"/>
       <c r="AS23" s="65"/>
       <c r="AT23" s="69" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AU23" s="69"/>
       <c r="AV23" s="65"/>
       <c r="AW23" s="65"/>
       <c r="AX23" s="69" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AY23" s="69"/>
       <c r="AZ23" s="70"/>
       <c r="BA23" s="166" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="BB23" s="72"/>
       <c r="BC23" s="73"/>
@@ -10749,11 +10762,11 @@
     </row>
     <row r="24" spans="2:64" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="79" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C24" s="164"/>
       <c r="D24" s="162" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E24" s="49"/>
       <c r="F24" s="50"/>
@@ -10785,7 +10798,7 @@
       <c r="AF24" s="50"/>
       <c r="AG24" s="53"/>
       <c r="AH24" s="54" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AI24" s="54"/>
       <c r="AJ24" s="50"/>
@@ -10799,18 +10812,18 @@
       <c r="AR24" s="54"/>
       <c r="AS24" s="50"/>
       <c r="AT24" s="54" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AU24" s="54"/>
       <c r="AV24" s="50"/>
       <c r="AW24" s="50"/>
       <c r="AX24" s="54" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AY24" s="54"/>
       <c r="AZ24" s="55"/>
       <c r="BA24" s="167" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="BB24" s="74"/>
       <c r="BC24" s="75"/>
@@ -12612,13 +12625,13 @@
         <v>280</v>
       </c>
       <c r="G3" s="97" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H3" s="97" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I3" s="98" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -12698,7 +12711,7 @@
       <c r="G7" s="105"/>
       <c r="H7" s="89"/>
       <c r="I7" s="134" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="87.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -12718,7 +12731,7 @@
       <c r="G8" s="104"/>
       <c r="H8" s="89"/>
       <c r="I8" s="134" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -12812,7 +12825,7 @@
         <v>288</v>
       </c>
       <c r="I13" s="134" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -12834,7 +12847,7 @@
         <v>285</v>
       </c>
       <c r="I14" s="134" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -12858,7 +12871,7 @@
         <v>286</v>
       </c>
       <c r="I15" s="159" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="228.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -12880,7 +12893,7 @@
         <v>290</v>
       </c>
       <c r="I16" s="134" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -12901,10 +12914,10 @@
         <v>260</v>
       </c>
       <c r="H17" s="155" t="s">
+        <v>311</v>
+      </c>
+      <c r="I17" s="136" t="s">
         <v>312</v>
-      </c>
-      <c r="I17" s="136" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="18" spans="2:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13034,16 +13047,16 @@
       <c r="D3" s="192"/>
       <c r="E3" s="190"/>
       <c r="F3" s="97" t="s">
+        <v>299</v>
+      </c>
+      <c r="G3" s="97" t="s">
         <v>300</v>
       </c>
-      <c r="G3" s="97" t="s">
+      <c r="H3" s="97" t="s">
         <v>301</v>
       </c>
-      <c r="H3" s="97" t="s">
+      <c r="I3" s="98" t="s">
         <v>302</v>
-      </c>
-      <c r="I3" s="98" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -13078,12 +13091,12 @@
         <v>161</v>
       </c>
       <c r="F5" s="123" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G5" s="157"/>
       <c r="H5" s="123"/>
       <c r="I5" s="135" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -13118,10 +13131,10 @@
         <v>162</v>
       </c>
       <c r="F7" s="123" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G7" s="105" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H7" s="89"/>
       <c r="I7" s="93"/>
@@ -13230,16 +13243,16 @@
         <v>263</v>
       </c>
       <c r="F13" s="133" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G13" s="157" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H13" s="105" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I13" s="122" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
@@ -13256,16 +13269,16 @@
         <v>264</v>
       </c>
       <c r="F14" s="133" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G14" s="157" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H14" s="105" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="I14" s="122" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="175.5" x14ac:dyDescent="0.3">
@@ -13282,16 +13295,16 @@
         <v>262</v>
       </c>
       <c r="F15" s="133" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G15" s="133" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H15" s="163" t="s">
+        <v>347</v>
+      </c>
+      <c r="I15" s="122" t="s">
         <v>348</v>
-      </c>
-      <c r="I15" s="122" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
@@ -13308,16 +13321,16 @@
         <v>265</v>
       </c>
       <c r="F16" s="133" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G16" s="157" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H16" s="157" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I16" s="122" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="162" x14ac:dyDescent="0.3">
@@ -13331,19 +13344,19 @@
         <v>178</v>
       </c>
       <c r="E17" s="113" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F17" s="155" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G17" s="119" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H17" s="163" t="s">
+        <v>343</v>
+      </c>
+      <c r="I17" s="168" t="s">
         <v>344</v>
-      </c>
-      <c r="I17" s="168" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
@@ -13382,10 +13395,10 @@
         <v>289</v>
       </c>
       <c r="H19" s="133" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I19" s="134" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -13402,7 +13415,7 @@
         <v>261</v>
       </c>
       <c r="F20" s="161" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G20" s="147"/>
       <c r="H20" s="148"/>
@@ -13462,7 +13475,7 @@
         <v>126</v>
       </c>
       <c r="F2" s="185" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G2" s="185"/>
       <c r="H2" s="185"/>
@@ -13475,19 +13488,19 @@
       <c r="D3" s="192"/>
       <c r="E3" s="190"/>
       <c r="F3" s="97" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G3" s="97" t="s">
+        <v>351</v>
+      </c>
+      <c r="H3" s="97" t="s">
         <v>352</v>
       </c>
-      <c r="H3" s="97" t="s">
+      <c r="I3" s="170" t="s">
         <v>353</v>
       </c>
-      <c r="I3" s="170" t="s">
+      <c r="J3" s="98" t="s">
         <v>354</v>
-      </c>
-      <c r="J3" s="98" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -13523,10 +13536,10 @@
         <v>161</v>
       </c>
       <c r="F5" s="123" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G5" s="123" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H5" s="123"/>
       <c r="I5" s="172"/>
@@ -13679,10 +13692,10 @@
         <v>263</v>
       </c>
       <c r="F13" s="105" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G13" s="157" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H13" s="105"/>
       <c r="I13" s="174"/>
@@ -13702,10 +13715,10 @@
         <v>264</v>
       </c>
       <c r="F14" s="105" t="s">
+        <v>365</v>
+      </c>
+      <c r="G14" s="157" t="s">
         <v>366</v>
-      </c>
-      <c r="G14" s="157" t="s">
-        <v>367</v>
       </c>
       <c r="H14" s="105"/>
       <c r="I14" s="174"/>
@@ -13725,10 +13738,10 @@
         <v>262</v>
       </c>
       <c r="F15" s="105" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G15" s="157" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H15" s="163"/>
       <c r="I15" s="105"/>
@@ -13748,10 +13761,10 @@
         <v>265</v>
       </c>
       <c r="F16" s="105" t="s">
+        <v>362</v>
+      </c>
+      <c r="G16" s="157" t="s">
         <v>363</v>
-      </c>
-      <c r="G16" s="157" t="s">
-        <v>364</v>
       </c>
       <c r="H16" s="157"/>
       <c r="I16" s="175"/>
@@ -13768,13 +13781,13 @@
         <v>178</v>
       </c>
       <c r="E17" s="113" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F17" s="119" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G17" s="169" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H17" s="163"/>
       <c r="I17" s="105"/>
@@ -13811,7 +13824,7 @@
         <v>156</v>
       </c>
       <c r="F19" s="105" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G19" s="158"/>
       <c r="H19" s="133"/>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Task\000_PJT\000_Heater\111_PTC\1.doc\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\일정\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="대일정" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="376">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5622,222 +5622,6 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>SVm LP2용 제어기 별 시그널 점검 (12/02)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[ 안건 ]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-    - </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>각 제어기(공조제어기, 히터컨트롤, 고전압PTC) 간 시그널 체크</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[ 요청사항 ]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-    - </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>LP2용 고전압 PTC 로컬 CAN 전체 신호 적용 정보 송부 (공조시스템설계팀)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[ 진행 및 검토 ]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-    - </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>로컬 CAN DB 확인 및 사용 Signal 회신</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-     : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>25년 3분기 로컬 CAN 최종본 기준, SVm PTC 사용 중인 Signal 회신 완료</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-2. SVm 서지 내성 향후 진행 사항 회의 (12/02)
-  [ 안건 ]
-    - 서지 내성 평가 결과 발표 (H/W)
-  [ 요청사항 ]
-    - BJ1에 비해 SVm이 서지 내성에 열세인 이유 설명 요청 (H/W)
-    - SVm 4EA, QV 3EA, BJ1 3EA 서지 내성 재평가 (H/W)
-     : 12/11 회의 예정
-  [ 진행 및 검토 ]
-    - 재평가 Fail일 경우 (H/W 결과)
-     : S/W 설계 변경 필요
-     : S/W LV, HV, 전력 센싱 값 확인 및 튜닝
-     : R로직 튜닝, 체크리스트 기반 기능 및 성능 시험
-     : 변경점 반영된 샘플 수령 후, S/W 검증 소요 시간 4주 요청 완료
-    - 재평가 Pass일 경우 (H/W 결과)
-     : S/W 변경사항 없음
-    - 칼로리 사용 예약
-     : 12/01 ~ 12/12 야간 칼로리 사용 예약 완료
-     : 12/18 ~ 01/02 주간, 야간 칼로리 사용 예약 완료</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">[임제훈 사원]
-1. </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>S/W 설계 변경 (~12/05)</t>
     </r>
     <r>
@@ -6077,60 +5861,6 @@
       : BJ1 ES95489-21 검증 진행
     - 사이버보안관련성평가 작성 후 검토 요청</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-1. S/W 설계 변경 (12/05)
-  [ 안건 ]
-    - S/W 설계 변경
-  [ 진행 및 검토 ]
-    - 전자 결재 상신
-2. 사이버 보안 관련 자료 회신 요청 (~12/05)
-  [ 요청사항 ]
-    - 사이버 보안 QV와 동일한 이력으로 진행 요청 (공조시스템설계팀)
-    - BJ1 ES95489-21 성적서 회신
-    - 사이버보안관련성평가 작성 후 회신
-  [ 진행 및 검토 ]
-    - BJ1 ES95489-21, ESIR 때 성적서 없음
-      : QV 사이버 보안 협의 및 일정 지연으로 BJ1 ESIR때 진행 불가
-      : BJ1 ES95489-21 검증 진행
-    - 사이버보안관련성평가 작성 후 검토 요청
-3. BJ1 PTC 리워크 (12/09)
-  [ 안건 ]
-    - AP2 차량 PTC 제거 후, SP 차량에 리워크
-  [ 요청사항 ]
-    - 한온시스템 방문 후 리워크
-  [ 진행 및 검토 ]
-    - 차량 리워크</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-1. SVm 서지 내성 향후 진행 사항 회의 (12/02)
-  [ 안건 ]
-    - 서지 내성 평가 결과 발표 (H/W)
-  [ 요청사항 ]
-    - BJ1에 비해 SVm이 서지 내성에 열세인 이유 설명 요청 (H/W)
-    - SVm 4EA, QV 3EA, BJ1 3EA 서지 내성 재평가 (H/W 12/08)
-     : 12/11 회의 예정
-  [ 진행 및 검토 ]
-    - 재평가 Fail일 경우 (H/W 결과)
-     : S/W 설계 변경 필요
-     : S/W LV, HV, 전력 센싱 값 확인 및 튜닝
-     : R로직 튜닝, 체크리스트 기반 기능 및 성능 시험
-     : 변경점 반영된 샘플 수령 후, S/W 검증 소요 시간 4주 요청 완료
-    - 재평가 Pass일 경우 (H/W 결과)
-     : S/W 변경사항 없음
-    - 칼로리 사용 예약
-     : 12/01 ~ 12/12 야간 칼로리 사용 예약 완료
-     : 12/18 ~ 01/02 주간, 야간 칼로리 사용 예약 완료
-2. SVm 설계 변경 기안 대결자 진행 (12/08)
-  [ 안건 ]
-    - 전자결재 대결자 선정
-  [ 진행 및 검토 ]
-    - 퇴사자 부서의 대결할 인원이 작업의뢰서_정보팀 작성해야 함.
-     : 남시온 선임</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -6163,6 +5893,1453 @@
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SVm LP2용 제어기 별 시그널 점검 (12/02)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ 안건 ]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>각 제어기(공조제어기, 히터컨트롤, 고전압PTC) 간 시그널 체크</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ 요청사항 ]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LP2용 고전압 PTC 로컬 CAN 전체 신호 적용 정보 송부 (공조시스템설계팀)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ 진행 및 검토 ]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>로컬 CAN DB 확인 및 사용 Signal 회신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>25년 3분기 로컬 CAN 최종본 기준, SVm PTC 사용 중인 Signal 회신 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SVm 서지 내성 향후 진행 사항 회의 (12/02)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ 안건 ]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>서지 내성 평가 결과 발표 (H/W)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ 요청사항 ]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BJ1에 비해 SVm이 서지 내성에 열세인 이유 설명 요청 (H/W)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SVm 4EA, QV 3EA, BJ1 3EA 서지 내성 재평가 (H/W)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>12/11 회의 예정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ 진행 및 검토 ]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>재평가 Fail일 경우 (H/W 결과)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S/W 설계 변경 필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S/W LV, HV, 전력 센싱 값 확인 및 튜닝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R로직 튜닝, 체크리스트 기반 기능 및 성능 시험</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>변경점 반영된 샘플 수령 후, S/W 검증 소요 시간 4주 요청 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>재평가 Pass일 경우 (H/W 결과)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S/W 변경사항 없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>칼로리 사용 예약</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>12/01 ~ 12/12 야간 칼로리 사용 예약 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>12/18 ~ 01/02 주간, 야간 칼로리 사용 예약 완료</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SVm 서지 내성 향후 진행 사항 회의 (12/02)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ 안건 ]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>서지 내성 평가 결과 발표 (H/W)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ 요청사항 ]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BJ1에 비해 SVm이 서지 내성에 열세인 이유 설명 요청 (H/W)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SVm 4EA, QV 3EA, BJ1 3EA 서지 내성 재평가 (H/W 12/08)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>12/11 회의 예정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ 진행 및 검토 ]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>재평가 Fail일 경우 (H/W 결과)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S/W 설계 변경 필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S/W LV, HV, 전력 센싱 값 확인 및 튜닝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R로직 튜닝, 체크리스트 기반 기능 및 성능 시험</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>변경점 반영된 샘플 수령 후, S/W 검증 소요 시간 4주 요청 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>재평가 Pass일 경우 (H/W 결과)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S/W 변경사항 없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>칼로리 사용 예약</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>12/01 ~ 12/12 야간 칼로리 사용 예약 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>12/18 ~ 01/02 주간, 야간 칼로리 사용 예약 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SVm 설계 변경 기안 대결자 진행 (12/08)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 안건 ]
+    - 전자결재 대결자 선정
+  [ 진행 및 검토 ]
+    - 퇴사자 부서의 대결할 인원이 작업의뢰서_정보팀 작성해야 함.
+     : 남시온 선임</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. SVm 설계 변경 기안 대결자 진행
+  [ 안건 ]
+    - 전자결재 대결자 선정
+  [ 진행 및 검토 ]
+    - 퇴사자 부서의 대결할 인원이 작업의뢰서_정보팀 작성해야 함.
+     : 김명규 선임</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S/W 설계 변경 (12/05)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ 안건 ]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S/W 설계 변경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ 진행 및 검토 ]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>전자 결재 상신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. 사이버 보안 관련 자료 회신 요청 (~12/05)
+  [ 요청사항 ]
+    - 사이버 보안 QV와 동일한 이력으로 진행 요청 (공조시스템설계팀)
+    - BJ1 ES95489-21 성적서 회신
+    - 사이버보안관련성평가 작성 후 회신
+  [ 진행 및 검토 ]
+    - BJ1 ES95489-21, ESIR 때 성적서 없음
+      : QV 사이버 보안 협의 및 일정 지연으로 BJ1 ESIR때 진행 불가
+      : BJ1 ES95489-21 검증 진행
+    - 사이버보안관련성평가 작성 후 검토 요청
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BJ1 PTC 리워크 (12/09)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ 안건 ]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AP2 차량 PTC 제거 후, SP 차량에 리워크</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ 요청사항 ]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>한온시스템 방문 후 리워크</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ 진행 및 검토 ]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>차량 리워크</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. 사이버 보안 관련 자료 회신 요청
+  [ 요청사항 ]
+    - 사이버 보안 QV와 동일한 이력으로 진행 요청 (공조시스템설계팀)
+    - BJ1 ES95489-21 성적서 회신
+    - 사이버보안관련성평가 작성 후 회신
+  [ 진행 및 검토 ]
+    - BJ1 ES95489-21, ESIR 때 성적서 없음
+      : QV 사이버 보안 협의 및 일정 지연으로 BJ1 ESIR때 진행 불가
+      : BJ1 ES95489-21 검증 진행
+    - 사이버보안관련성평가 작성 후 검토 요청</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. 사이버 보안 관련 자료 회신 요청
+  [ 요청사항 ]
+    - 사이버 보안 QV와 동일한 이력으로 진행 요청 (공조시스템설계팀)
+    - BJ1 ES95489-21 성적서 회신
+    - 사이버보안관련성평가 작성 후 회신
+  [ 진행 및 검토 ]
+    - BJ1 ES95489-21, ESIR 때 성적서 없음
+      : QV 사이버 보안 협의 및 일정 지연으로 BJ1 ESIR때 진행 불가
+      : BJ1 ES95489-21 검증 진행
+    - 사이버보안관련성평가 작성 후 검토 요청</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. 기구 변경 건 (11/14)
+  [ 안건 ]
+    - Stone TC 160℃ → 165℃ 변경
+    - 전압 범위 변경
+     : 정격 전압 360V → 351V
+     : 최대 동작 전압 403.2V → 413V
+    - LINEAR MAX 성능 7000W 변경
+    - 제어 사양서, S/W 재배포 요청
+  [ 진행 및 검토 ]
+    - 165℃ 적용된 마스터 샘플 재고 부족으로 제작 불가
+    - NX5e 11/21 LHD, RHD PCB 생산 예정일에 맞추어 S/W 재배포 불가
+     : P1 최종 사양 반영된 샘플 12/5 ~ 12/12 수령 예정
+     : 1월 ALL TOOL 예정, 변경된 S/W 라이팅
+    - R로직 튜닝
+     : 12/01 ~ 12/12 야간 칼로리 사용 예약 완료
+     : 12/18 ~ 01/02 주간, 야간 칼로리 사용 예약 완료
+    - 로직 및 기능 체크리스트 기반 검증 진행
+    - 설계 변경으로 진행해야 하는지 확인
+2. ESIR (12/23)
+  [ 안건 ]
+    - ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24 ESIR 진행
+  [ 진행 및 검토 ]
+    - ES95489-21 (100%)
+    - ES95489-24 (100%)
+    - ES95411-00 (100%)
+    - ES90700-00 (100%)
+    - ES95480-00 (100%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -6171,7 +7348,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6318,6 +7495,15 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -6395,7 +7581,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="88">
+  <borders count="87">
     <border>
       <left/>
       <right/>
@@ -7583,17 +8769,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="hair">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -7615,7 +8790,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="194">
+  <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -8137,12 +9312,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="86" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="87" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -8863,90 +10032,90 @@
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="178" t="s">
+      <c r="B2" s="176" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="180" t="s">
+      <c r="C2" s="178" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="180" t="s">
+      <c r="D2" s="178" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="184">
+      <c r="E2" s="182">
         <v>23</v>
       </c>
-      <c r="F2" s="182"/>
-      <c r="G2" s="182"/>
-      <c r="H2" s="182"/>
-      <c r="I2" s="182"/>
-      <c r="J2" s="182"/>
-      <c r="K2" s="182"/>
-      <c r="L2" s="182"/>
-      <c r="M2" s="182"/>
-      <c r="N2" s="182"/>
-      <c r="O2" s="182"/>
-      <c r="P2" s="182"/>
-      <c r="Q2" s="182">
+      <c r="F2" s="180"/>
+      <c r="G2" s="180"/>
+      <c r="H2" s="180"/>
+      <c r="I2" s="180"/>
+      <c r="J2" s="180"/>
+      <c r="K2" s="180"/>
+      <c r="L2" s="180"/>
+      <c r="M2" s="180"/>
+      <c r="N2" s="180"/>
+      <c r="O2" s="180"/>
+      <c r="P2" s="180"/>
+      <c r="Q2" s="180">
         <v>24</v>
       </c>
-      <c r="R2" s="182"/>
-      <c r="S2" s="182"/>
-      <c r="T2" s="182"/>
-      <c r="U2" s="182"/>
-      <c r="V2" s="182"/>
-      <c r="W2" s="182"/>
-      <c r="X2" s="182"/>
-      <c r="Y2" s="182"/>
-      <c r="Z2" s="182"/>
-      <c r="AA2" s="182"/>
-      <c r="AB2" s="182"/>
-      <c r="AC2" s="182">
+      <c r="R2" s="180"/>
+      <c r="S2" s="180"/>
+      <c r="T2" s="180"/>
+      <c r="U2" s="180"/>
+      <c r="V2" s="180"/>
+      <c r="W2" s="180"/>
+      <c r="X2" s="180"/>
+      <c r="Y2" s="180"/>
+      <c r="Z2" s="180"/>
+      <c r="AA2" s="180"/>
+      <c r="AB2" s="180"/>
+      <c r="AC2" s="180">
         <v>25</v>
       </c>
-      <c r="AD2" s="182"/>
-      <c r="AE2" s="182"/>
-      <c r="AF2" s="182"/>
-      <c r="AG2" s="182"/>
-      <c r="AH2" s="182"/>
-      <c r="AI2" s="182"/>
-      <c r="AJ2" s="182"/>
-      <c r="AK2" s="182"/>
-      <c r="AL2" s="182"/>
-      <c r="AM2" s="182"/>
-      <c r="AN2" s="182"/>
-      <c r="AO2" s="182">
+      <c r="AD2" s="180"/>
+      <c r="AE2" s="180"/>
+      <c r="AF2" s="180"/>
+      <c r="AG2" s="180"/>
+      <c r="AH2" s="180"/>
+      <c r="AI2" s="180"/>
+      <c r="AJ2" s="180"/>
+      <c r="AK2" s="180"/>
+      <c r="AL2" s="180"/>
+      <c r="AM2" s="180"/>
+      <c r="AN2" s="180"/>
+      <c r="AO2" s="180">
         <v>26</v>
       </c>
-      <c r="AP2" s="182"/>
-      <c r="AQ2" s="182"/>
-      <c r="AR2" s="182"/>
-      <c r="AS2" s="182"/>
-      <c r="AT2" s="182"/>
-      <c r="AU2" s="182"/>
-      <c r="AV2" s="182"/>
-      <c r="AW2" s="182"/>
-      <c r="AX2" s="182"/>
-      <c r="AY2" s="182"/>
-      <c r="AZ2" s="183"/>
-      <c r="BA2" s="182">
+      <c r="AP2" s="180"/>
+      <c r="AQ2" s="180"/>
+      <c r="AR2" s="180"/>
+      <c r="AS2" s="180"/>
+      <c r="AT2" s="180"/>
+      <c r="AU2" s="180"/>
+      <c r="AV2" s="180"/>
+      <c r="AW2" s="180"/>
+      <c r="AX2" s="180"/>
+      <c r="AY2" s="180"/>
+      <c r="AZ2" s="181"/>
+      <c r="BA2" s="180">
         <v>27</v>
       </c>
-      <c r="BB2" s="182"/>
-      <c r="BC2" s="182"/>
-      <c r="BD2" s="182"/>
-      <c r="BE2" s="182"/>
-      <c r="BF2" s="182"/>
-      <c r="BG2" s="182"/>
-      <c r="BH2" s="182"/>
-      <c r="BI2" s="182"/>
-      <c r="BJ2" s="182"/>
-      <c r="BK2" s="182"/>
-      <c r="BL2" s="183"/>
+      <c r="BB2" s="180"/>
+      <c r="BC2" s="180"/>
+      <c r="BD2" s="180"/>
+      <c r="BE2" s="180"/>
+      <c r="BF2" s="180"/>
+      <c r="BG2" s="180"/>
+      <c r="BH2" s="180"/>
+      <c r="BI2" s="180"/>
+      <c r="BJ2" s="180"/>
+      <c r="BK2" s="180"/>
+      <c r="BL2" s="181"/>
     </row>
     <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="179"/>
-      <c r="C3" s="181"/>
-      <c r="D3" s="181"/>
+      <c r="B3" s="177"/>
+      <c r="C3" s="179"/>
+      <c r="D3" s="179"/>
       <c r="E3" s="22">
         <v>1</v>
       </c>
@@ -10535,7 +11704,7 @@
         <v>107</v>
       </c>
       <c r="D21" s="34" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E21" s="64"/>
       <c r="F21" s="65"/>
@@ -10601,7 +11770,7 @@
         <v>234</v>
       </c>
       <c r="BH21" s="73" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="BI21" s="69" t="s">
         <v>235</v>
@@ -11014,39 +12183,39 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="187" t="s">
+      <c r="B2" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="191" t="s">
+      <c r="C2" s="189" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="191" t="s">
+      <c r="D2" s="189" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="189" t="s">
+      <c r="E2" s="187" t="s">
         <v>126</v>
       </c>
       <c r="F2" s="96" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="185" t="s">
+      <c r="G2" s="183" t="s">
         <v>113</v>
       </c>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
-      <c r="J2" s="186"/>
-      <c r="K2" s="185" t="s">
+      <c r="H2" s="183"/>
+      <c r="I2" s="183"/>
+      <c r="J2" s="184"/>
+      <c r="K2" s="183" t="s">
         <v>182</v>
       </c>
-      <c r="L2" s="185"/>
-      <c r="M2" s="185"/>
-      <c r="N2" s="186"/>
+      <c r="L2" s="183"/>
+      <c r="M2" s="183"/>
+      <c r="N2" s="184"/>
     </row>
     <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="188"/>
-      <c r="C3" s="192"/>
-      <c r="D3" s="192"/>
-      <c r="E3" s="190"/>
+      <c r="B3" s="186"/>
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="188"/>
       <c r="F3" s="97" t="s">
         <v>111</v>
       </c>
@@ -11789,30 +12958,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="187" t="s">
+      <c r="B2" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="191" t="s">
+      <c r="C2" s="189" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="191" t="s">
+      <c r="D2" s="189" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="189" t="s">
+      <c r="E2" s="187" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="185" t="s">
+      <c r="F2" s="183" t="s">
         <v>182</v>
       </c>
-      <c r="G2" s="185"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="186"/>
+      <c r="G2" s="183"/>
+      <c r="H2" s="183"/>
+      <c r="I2" s="184"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="188"/>
-      <c r="C3" s="192"/>
-      <c r="D3" s="192"/>
-      <c r="E3" s="190"/>
+      <c r="B3" s="186"/>
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="188"/>
       <c r="F3" s="97" t="s">
         <v>114</v>
       </c>
@@ -12190,30 +13359,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="187" t="s">
+      <c r="B2" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="191" t="s">
+      <c r="C2" s="189" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="191" t="s">
+      <c r="D2" s="189" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="189" t="s">
+      <c r="E2" s="187" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="185" t="s">
+      <c r="F2" s="183" t="s">
         <v>227</v>
       </c>
-      <c r="G2" s="185"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="186"/>
+      <c r="G2" s="183"/>
+      <c r="H2" s="183"/>
+      <c r="I2" s="184"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="188"/>
-      <c r="C3" s="192"/>
-      <c r="D3" s="192"/>
-      <c r="E3" s="190"/>
+      <c r="B3" s="186"/>
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="188"/>
       <c r="F3" s="97" t="s">
         <v>114</v>
       </c>
@@ -12597,30 +13766,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="187" t="s">
+      <c r="B2" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="191" t="s">
+      <c r="C2" s="189" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="191" t="s">
+      <c r="D2" s="189" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="189" t="s">
+      <c r="E2" s="187" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="185" t="s">
+      <c r="F2" s="183" t="s">
         <v>259</v>
       </c>
-      <c r="G2" s="185"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="186"/>
+      <c r="G2" s="183"/>
+      <c r="H2" s="183"/>
+      <c r="I2" s="184"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="188"/>
-      <c r="C3" s="192"/>
-      <c r="D3" s="192"/>
-      <c r="E3" s="190"/>
+      <c r="B3" s="186"/>
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="188"/>
       <c r="F3" s="97" t="s">
         <v>280</v>
       </c>
@@ -13022,30 +14191,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="187" t="s">
+      <c r="B2" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="191" t="s">
+      <c r="C2" s="189" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="191" t="s">
+      <c r="D2" s="189" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="189" t="s">
+      <c r="E2" s="187" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="185" t="s">
+      <c r="F2" s="183" t="s">
         <v>279</v>
       </c>
-      <c r="G2" s="185"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="186"/>
+      <c r="G2" s="183"/>
+      <c r="H2" s="183"/>
+      <c r="I2" s="184"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="188"/>
-      <c r="C3" s="192"/>
-      <c r="D3" s="192"/>
-      <c r="E3" s="190"/>
+      <c r="B3" s="186"/>
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="188"/>
       <c r="F3" s="97" t="s">
         <v>299</v>
       </c>
@@ -13462,31 +14631,31 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="187" t="s">
+      <c r="B2" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="191" t="s">
+      <c r="C2" s="189" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="191" t="s">
+      <c r="D2" s="189" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="189" t="s">
+      <c r="E2" s="187" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="185" t="s">
+      <c r="F2" s="183" t="s">
         <v>350</v>
       </c>
-      <c r="G2" s="185"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="193"/>
-      <c r="J2" s="186"/>
+      <c r="G2" s="183"/>
+      <c r="H2" s="183"/>
+      <c r="I2" s="191"/>
+      <c r="J2" s="184"/>
     </row>
     <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="188"/>
-      <c r="C3" s="192"/>
-      <c r="D3" s="192"/>
-      <c r="E3" s="190"/>
+      <c r="B3" s="186"/>
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="188"/>
       <c r="F3" s="97" t="s">
         <v>349</v>
       </c>
@@ -13692,13 +14861,17 @@
         <v>263</v>
       </c>
       <c r="F13" s="105" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="G13" s="157" t="s">
-        <v>367</v>
-      </c>
-      <c r="H13" s="105"/>
-      <c r="I13" s="174"/>
+        <v>370</v>
+      </c>
+      <c r="H13" s="105" t="s">
+        <v>371</v>
+      </c>
+      <c r="I13" s="105" t="s">
+        <v>371</v>
+      </c>
       <c r="J13" s="122"/>
     </row>
     <row r="14" spans="1:10" ht="310.5" x14ac:dyDescent="0.3">
@@ -13715,13 +14888,17 @@
         <v>264</v>
       </c>
       <c r="F14" s="105" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G14" s="157" t="s">
-        <v>366</v>
-      </c>
-      <c r="H14" s="105"/>
-      <c r="I14" s="174"/>
+        <v>372</v>
+      </c>
+      <c r="H14" s="105" t="s">
+        <v>373</v>
+      </c>
+      <c r="I14" s="105" t="s">
+        <v>374</v>
+      </c>
       <c r="J14" s="122"/>
     </row>
     <row r="15" spans="1:10" ht="243" x14ac:dyDescent="0.3">
@@ -13743,8 +14920,12 @@
       <c r="G15" s="157" t="s">
         <v>361</v>
       </c>
-      <c r="H15" s="163"/>
-      <c r="I15" s="105"/>
+      <c r="H15" s="157" t="s">
+        <v>361</v>
+      </c>
+      <c r="I15" s="157" t="s">
+        <v>361</v>
+      </c>
       <c r="J15" s="122"/>
     </row>
     <row r="16" spans="1:10" ht="378" x14ac:dyDescent="0.3">
@@ -13766,8 +14947,12 @@
       <c r="G16" s="157" t="s">
         <v>363</v>
       </c>
-      <c r="H16" s="157"/>
-      <c r="I16" s="175"/>
+      <c r="H16" s="157" t="s">
+        <v>362</v>
+      </c>
+      <c r="I16" s="157" t="s">
+        <v>375</v>
+      </c>
       <c r="J16" s="122"/>
     </row>
     <row r="17" spans="2:10" ht="40.5" x14ac:dyDescent="0.3">
@@ -13787,10 +14972,14 @@
         <v>344</v>
       </c>
       <c r="G17" s="169" t="s">
-        <v>368</v>
-      </c>
-      <c r="H17" s="163"/>
-      <c r="I17" s="105"/>
+        <v>365</v>
+      </c>
+      <c r="H17" s="169" t="s">
+        <v>365</v>
+      </c>
+      <c r="I17" s="169" t="s">
+        <v>365</v>
+      </c>
       <c r="J17" s="168"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
@@ -13824,11 +15013,11 @@
         <v>156</v>
       </c>
       <c r="F19" s="105" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G19" s="158"/>
       <c r="H19" s="133"/>
-      <c r="I19" s="176"/>
+      <c r="I19" s="174"/>
       <c r="J19" s="134"/>
     </row>
     <row r="20" spans="2:10" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -13849,7 +15038,7 @@
       </c>
       <c r="G20" s="147"/>
       <c r="H20" s="148"/>
-      <c r="I20" s="177"/>
+      <c r="I20" s="175"/>
       <c r="J20" s="149"/>
     </row>
   </sheetData>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="대일정" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,8 @@
     <sheet name="2025.10" sheetId="6" r:id="rId6"/>
     <sheet name="2025.11" sheetId="8" r:id="rId7"/>
     <sheet name="2025.12" sheetId="9" r:id="rId8"/>
+    <sheet name="2026.1" sheetId="10" r:id="rId9"/>
+    <sheet name="2026.2" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="390">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1016,28 +1018,13 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>LP2
-10/1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SOP
 4/15</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SP1
-4/1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>M/Car
 2/15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Proto
-8/14</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -7338,6 +7325,339 @@
     - ES95411-00 (100%)
     - ES90700-00 (100%)
     - ES95480-00 (100%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1주차 (01/02 ~ 01/08)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2주차 (01/09 ~ 01/15)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3주차 (01/16 ~ 01/22)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4주차 (01/23 ~ 01/29)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1주차 (01/30 ~ 02/05)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SP1
+4/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LP2
+12/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T2
+9/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M
+3/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Proto
+8/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MX5a
+EREV
+(싼타페)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. 최대 난방 평가 성능 미달로 인한 성능 증대 계획
+  [ 요청사항 ]
+    - SP1 적용 S/W 튜닝
+  [ 진행 및 검토 ]
+    - HVAC 미수령
+      : 수령 일자 미정
+    - MX5a 샘플 미수령
+      : 수령 일자 미정
+    - S/W 튜닝 소요 기간 3주 요청
+      : TC 변경건으로 인한 R로직 재튜닝
+      : 전압 범위 변경</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LHD, RHD R로직 점검 및 기능 점검 (12/30)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 안건 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SW 점검</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 진행 및 검토 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LHD, RHD R로직 점검</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>로직 및 기능 체크리스트 기반 검증 진행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S/W 이상 없음</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. 기구 변경점 반영 및 S/W 적용 (~01/09)
+  [ 안건 ]
+    - Stone TC 160℃ → 165℃ 변경
+    - 전압 범위 변경
+     : 정격 전압 360V → 351V
+     : 최대 동작 전압 403.2V → 413V
+    - LINEAR MAX 성능 7000W 변경
+    - 제어 사양서, S/W 재배포 요청
+  [ 진행 및 검토 ]
+    - 최종 사양 반영된 샘플 수령 (01/06)
+    - 기구 변경점 S/W 반영
+    - R로직 튜닝
+    - 로직 및 기능 체크리스트 기반 검증 진행
+2. 사이버 보안 기능 품확 활동 (~01/09)
+  [ 안건 ]
+    - 첨부파일 작성
+     : NX5_(제어기명)_공정보안_체크리스트(설계팀,협력사용)
+  [ 진행 및 검토 ]
+    - QV 작성자료 참고
+    - 사이버보안품질연구팀에 보낼 샘플 준비
+     : PCB 2EA, Signal Connector 1EA, E2 Pin Connector 1EA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R로직 점검 및 기능 점검 (12/30)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 안건 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SW 점검</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 진행 및 검토 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R로직 점검</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>로직 및 기능 체크리스트 기반 검증 진행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S/W 이상 없음</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7581,7 +7901,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="87">
+  <borders count="89">
     <border>
       <left/>
       <right/>
@@ -8769,6 +9089,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -8790,7 +9132,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="192">
+  <cellXfs count="198">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -9366,6 +9708,24 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="80" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="87" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -10623,7 +10983,7 @@
     </row>
     <row r="8" spans="1:64" ht="81" x14ac:dyDescent="0.3">
       <c r="B8" s="28" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C8" s="58"/>
       <c r="D8" s="33"/>
@@ -10647,7 +11007,7 @@
       <c r="V8" s="30"/>
       <c r="W8" s="30"/>
       <c r="X8" s="15" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="Y8" s="31"/>
       <c r="Z8" s="30"/>
@@ -10657,22 +11017,22 @@
       <c r="AD8" s="31"/>
       <c r="AE8" s="31"/>
       <c r="AF8" s="15" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="AG8" s="31"/>
       <c r="AH8" s="31"/>
       <c r="AI8" s="17" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="AJ8" s="31"/>
       <c r="AK8" s="31"/>
       <c r="AL8" s="31"/>
       <c r="AM8" s="17" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AN8" s="121"/>
       <c r="AO8" s="29" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AP8" s="31"/>
       <c r="AQ8" s="31"/>
@@ -10856,7 +11216,7 @@
         <v>77</v>
       </c>
       <c r="D11" s="160" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="7"/>
@@ -10939,7 +11299,7 @@
         <v>105</v>
       </c>
       <c r="D12" s="160" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="7"/>
@@ -10995,7 +11355,7 @@
       </c>
       <c r="AW12" s="7"/>
       <c r="AX12" s="13" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AY12" s="7"/>
       <c r="AZ12" s="10"/>
@@ -11020,7 +11380,7 @@
         <v>82</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="7"/>
@@ -11149,13 +11509,13 @@
       <c r="AH14" s="7"/>
       <c r="AI14" s="7"/>
       <c r="AJ14" s="13" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="AK14" s="13" t="s">
         <v>13</v>
       </c>
       <c r="AL14" s="17" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="AM14" s="7"/>
       <c r="AN14" s="8"/>
@@ -11198,7 +11558,7 @@
         <v>84</v>
       </c>
       <c r="D15" s="34" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="7"/>
@@ -11364,7 +11724,7 @@
     </row>
     <row r="17" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="57" t="s">
-        <v>75</v>
+        <v>385</v>
       </c>
       <c r="C17" s="60" t="s">
         <v>104</v>
@@ -11410,7 +11770,7 @@
       <c r="AH17" s="41"/>
       <c r="AI17" s="37"/>
       <c r="AJ17" s="30" t="s">
-        <v>196</v>
+        <v>384</v>
       </c>
       <c r="AK17" s="46"/>
       <c r="AL17" s="41"/>
@@ -11418,27 +11778,31 @@
       <c r="AN17" s="8"/>
       <c r="AO17" s="47"/>
       <c r="AP17" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AQ17" s="42"/>
       <c r="AR17" s="37" t="s">
-        <v>194</v>
+        <v>380</v>
       </c>
       <c r="AS17" s="41"/>
       <c r="AT17" s="42"/>
       <c r="AU17" s="41"/>
       <c r="AV17" s="41"/>
-      <c r="AW17" s="41"/>
-      <c r="AX17" s="17" t="s">
-        <v>192</v>
-      </c>
+      <c r="AW17" s="42" t="s">
+        <v>382</v>
+      </c>
+      <c r="AX17" s="30"/>
       <c r="AY17" s="41"/>
-      <c r="AZ17" s="48"/>
+      <c r="AZ17" s="197" t="s">
+        <v>381</v>
+      </c>
       <c r="BA17" s="47"/>
       <c r="BB17" s="45"/>
-      <c r="BC17" s="45"/>
+      <c r="BC17" s="45" t="s">
+        <v>383</v>
+      </c>
       <c r="BD17" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BE17" s="71"/>
       <c r="BF17" s="45"/>
@@ -11454,10 +11818,10 @@
         <v>85</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D18" s="160" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E18" s="64"/>
       <c r="F18" s="65"/>
@@ -11704,7 +12068,7 @@
         <v>107</v>
       </c>
       <c r="D21" s="34" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E21" s="64"/>
       <c r="F21" s="65"/>
@@ -11745,14 +12109,14 @@
       <c r="AO21" s="67"/>
       <c r="AP21" s="69"/>
       <c r="AQ21" s="69" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AR21" s="69"/>
       <c r="AS21" s="65"/>
       <c r="AT21" s="65"/>
       <c r="AU21" s="69"/>
       <c r="AV21" s="13" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AW21" s="65"/>
       <c r="AX21" s="65"/>
@@ -11762,18 +12126,18 @@
       <c r="BB21" s="13"/>
       <c r="BC21" s="73"/>
       <c r="BD21" s="69" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="BE21" s="72"/>
       <c r="BF21" s="73"/>
       <c r="BG21" s="69" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="BH21" s="73" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="BI21" s="69" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="BJ21" s="73"/>
       <c r="BK21" s="73"/>
@@ -11850,11 +12214,11 @@
     </row>
     <row r="23" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="57" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C23" s="80"/>
       <c r="D23" s="165" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E23" s="64"/>
       <c r="F23" s="65"/>
@@ -11884,7 +12248,7 @@
       <c r="AD23" s="65"/>
       <c r="AE23" s="65"/>
       <c r="AF23" s="69" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="AG23" s="68"/>
       <c r="AH23" s="65"/>
@@ -11892,30 +12256,30 @@
       <c r="AJ23" s="65"/>
       <c r="AK23" s="65"/>
       <c r="AL23" s="69" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="AM23" s="65"/>
       <c r="AN23" s="66"/>
       <c r="AO23" s="67"/>
       <c r="AP23" s="69"/>
       <c r="AQ23" s="69" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="AR23" s="69"/>
       <c r="AS23" s="65"/>
       <c r="AT23" s="69" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="AU23" s="69"/>
       <c r="AV23" s="65"/>
       <c r="AW23" s="65"/>
       <c r="AX23" s="69" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="AY23" s="69"/>
       <c r="AZ23" s="70"/>
       <c r="BA23" s="166" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="BB23" s="72"/>
       <c r="BC23" s="73"/>
@@ -11931,11 +12295,11 @@
     </row>
     <row r="24" spans="2:64" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="79" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C24" s="164"/>
       <c r="D24" s="162" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E24" s="49"/>
       <c r="F24" s="50"/>
@@ -11967,7 +12331,7 @@
       <c r="AF24" s="50"/>
       <c r="AG24" s="53"/>
       <c r="AH24" s="54" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="AI24" s="54"/>
       <c r="AJ24" s="50"/>
@@ -11981,18 +12345,18 @@
       <c r="AR24" s="54"/>
       <c r="AS24" s="50"/>
       <c r="AT24" s="54" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="AU24" s="54"/>
       <c r="AV24" s="50"/>
       <c r="AW24" s="50"/>
       <c r="AX24" s="54" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="AY24" s="54"/>
       <c r="AZ24" s="55"/>
       <c r="BA24" s="167" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="BB24" s="74"/>
       <c r="BC24" s="75"/>
@@ -12025,6 +12389,404 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
+    <col min="2" max="2" width="9" style="81"/>
+    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
+    <col min="5" max="5" width="43" style="81" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
+    <col min="7" max="10" width="62.125" style="81" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="81"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="109" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="107"/>
+    </row>
+    <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="185" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="189" t="s">
+        <v>176</v>
+      </c>
+      <c r="D2" s="189" t="s">
+        <v>177</v>
+      </c>
+      <c r="E2" s="187" t="s">
+        <v>126</v>
+      </c>
+      <c r="F2" s="183" t="s">
+        <v>378</v>
+      </c>
+      <c r="G2" s="183"/>
+      <c r="H2" s="183"/>
+      <c r="I2" s="191"/>
+      <c r="J2" s="184"/>
+    </row>
+    <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="186"/>
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="188"/>
+      <c r="F3" s="97" t="s">
+        <v>379</v>
+      </c>
+      <c r="G3" s="97"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="170"/>
+      <c r="J3" s="98"/>
+    </row>
+    <row r="4" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="151" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="116" t="s">
+        <v>175</v>
+      </c>
+      <c r="D4" s="116" t="s">
+        <v>178</v>
+      </c>
+      <c r="E4" s="140" t="s">
+        <v>140</v>
+      </c>
+      <c r="F4" s="141"/>
+      <c r="G4" s="142"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="171"/>
+      <c r="J4" s="92"/>
+    </row>
+    <row r="5" spans="1:10" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="B5" s="154" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" s="117" t="s">
+        <v>267</v>
+      </c>
+      <c r="D5" s="117" t="s">
+        <v>180</v>
+      </c>
+      <c r="E5" s="100" t="s">
+        <v>161</v>
+      </c>
+      <c r="F5" s="123"/>
+      <c r="G5" s="123"/>
+      <c r="H5" s="123"/>
+      <c r="I5" s="172"/>
+      <c r="J5" s="135"/>
+    </row>
+    <row r="6" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="152" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="117" t="s">
+        <v>268</v>
+      </c>
+      <c r="D6" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E6" s="100" t="s">
+        <v>161</v>
+      </c>
+      <c r="F6" s="123"/>
+      <c r="G6" s="123"/>
+      <c r="H6" s="123"/>
+      <c r="I6" s="172"/>
+      <c r="J6" s="135"/>
+    </row>
+    <row r="7" spans="1:10" ht="138" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="152" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="117" t="s">
+        <v>268</v>
+      </c>
+      <c r="D7" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E7" s="100" t="s">
+        <v>162</v>
+      </c>
+      <c r="F7" s="123"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="89"/>
+      <c r="I7" s="173"/>
+      <c r="J7" s="93"/>
+    </row>
+    <row r="8" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="152" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="117" t="s">
+        <v>268</v>
+      </c>
+      <c r="D8" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E8" s="91" t="s">
+        <v>139</v>
+      </c>
+      <c r="F8" s="114"/>
+      <c r="G8" s="104"/>
+      <c r="H8" s="89"/>
+      <c r="I8" s="173"/>
+      <c r="J8" s="93"/>
+    </row>
+    <row r="9" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="153" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="117" t="s">
+        <v>268</v>
+      </c>
+      <c r="D9" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E9" s="91" t="s">
+        <v>152</v>
+      </c>
+      <c r="F9" s="114"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="138"/>
+      <c r="I9" s="89"/>
+      <c r="J9" s="93"/>
+    </row>
+    <row r="10" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="153" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" s="117" t="s">
+        <v>268</v>
+      </c>
+      <c r="D10" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E10" s="91" t="s">
+        <v>153</v>
+      </c>
+      <c r="F10" s="114"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="89"/>
+      <c r="I10" s="173"/>
+      <c r="J10" s="93"/>
+    </row>
+    <row r="11" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="153" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" s="117" t="s">
+        <v>268</v>
+      </c>
+      <c r="D11" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E11" s="91" t="s">
+        <v>154</v>
+      </c>
+      <c r="F11" s="114"/>
+      <c r="G11" s="105"/>
+      <c r="H11" s="89"/>
+      <c r="I11" s="173"/>
+      <c r="J11" s="93"/>
+    </row>
+    <row r="12" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="153" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" s="117" t="s">
+        <v>268</v>
+      </c>
+      <c r="D12" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E12" s="91" t="s">
+        <v>155</v>
+      </c>
+      <c r="F12" s="114"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="138"/>
+      <c r="I12" s="89"/>
+      <c r="J12" s="93"/>
+    </row>
+    <row r="13" spans="1:10" ht="27" x14ac:dyDescent="0.3">
+      <c r="B13" s="132" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="117" t="s">
+        <v>270</v>
+      </c>
+      <c r="D13" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E13" s="100" t="s">
+        <v>260</v>
+      </c>
+      <c r="F13" s="105"/>
+      <c r="G13" s="157"/>
+      <c r="H13" s="105"/>
+      <c r="I13" s="105"/>
+      <c r="J13" s="122"/>
+    </row>
+    <row r="14" spans="1:10" ht="27" x14ac:dyDescent="0.3">
+      <c r="B14" s="131" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="117" t="s">
+        <v>270</v>
+      </c>
+      <c r="D14" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E14" s="100" t="s">
+        <v>261</v>
+      </c>
+      <c r="F14" s="105"/>
+      <c r="G14" s="157"/>
+      <c r="H14" s="105"/>
+      <c r="I14" s="105"/>
+      <c r="J14" s="122"/>
+    </row>
+    <row r="15" spans="1:10" ht="67.5" x14ac:dyDescent="0.3">
+      <c r="B15" s="131" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="117" t="s">
+        <v>270</v>
+      </c>
+      <c r="D15" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E15" s="100" t="s">
+        <v>259</v>
+      </c>
+      <c r="F15" s="105"/>
+      <c r="G15" s="157"/>
+      <c r="H15" s="157"/>
+      <c r="I15" s="157"/>
+      <c r="J15" s="122"/>
+    </row>
+    <row r="16" spans="1:10" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="B16" s="131" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="117" t="s">
+        <v>270</v>
+      </c>
+      <c r="D16" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E16" s="100" t="s">
+        <v>262</v>
+      </c>
+      <c r="F16" s="105"/>
+      <c r="G16" s="157"/>
+      <c r="H16" s="157"/>
+      <c r="I16" s="157"/>
+      <c r="J16" s="122"/>
+    </row>
+    <row r="17" spans="2:10" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="B17" s="130" t="s">
+        <v>167</v>
+      </c>
+      <c r="C17" s="117" t="s">
+        <v>270</v>
+      </c>
+      <c r="D17" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E17" s="113" t="s">
+        <v>303</v>
+      </c>
+      <c r="F17" s="119"/>
+      <c r="G17" s="169"/>
+      <c r="H17" s="169"/>
+      <c r="I17" s="169"/>
+      <c r="J17" s="168"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B18" s="131" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" s="117" t="s">
+        <v>270</v>
+      </c>
+      <c r="D18" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E18" s="113"/>
+      <c r="F18" s="155"/>
+      <c r="G18" s="158"/>
+      <c r="H18" s="133"/>
+      <c r="I18" s="129"/>
+      <c r="J18" s="136"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B19" s="150" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="139" t="s">
+        <v>270</v>
+      </c>
+      <c r="D19" s="139" t="s">
+        <v>178</v>
+      </c>
+      <c r="E19" s="91" t="s">
+        <v>156</v>
+      </c>
+      <c r="F19" s="105" t="s">
+        <v>263</v>
+      </c>
+      <c r="G19" s="158"/>
+      <c r="H19" s="133"/>
+      <c r="I19" s="174"/>
+      <c r="J19" s="134"/>
+    </row>
+    <row r="20" spans="2:10" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="143" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="144" t="s">
+        <v>270</v>
+      </c>
+      <c r="D20" s="144" t="s">
+        <v>178</v>
+      </c>
+      <c r="E20" s="145" t="s">
+        <v>258</v>
+      </c>
+      <c r="F20" s="161" t="s">
+        <v>263</v>
+      </c>
+      <c r="G20" s="147"/>
+      <c r="H20" s="148"/>
+      <c r="I20" s="175"/>
+      <c r="J20" s="149"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:J2"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D10"/>
@@ -12036,118 +12798,118 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="124" t="s">
+        <v>237</v>
+      </c>
+      <c r="B2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C2" s="125" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2" t="s">
         <v>240</v>
-      </c>
-      <c r="B2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C2" s="125" t="s">
-        <v>242</v>
-      </c>
-      <c r="D2" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="124" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C3" s="126" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="124" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B4" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C4" s="126" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D4" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="127" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B5" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C5" s="126" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D5" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="125" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C6" s="128" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="125" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B7" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C7" s="128" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D7" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C8" s="124" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D8" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C9" s="124" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D9" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C10" s="128" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D10" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -12232,7 +12994,7 @@
         <v>110</v>
       </c>
       <c r="K3" s="97" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L3" s="97" t="s">
         <v>115</v>
@@ -12267,11 +13029,11 @@
         <v>184</v>
       </c>
       <c r="I4" s="105" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="J4" s="92"/>
       <c r="K4" s="105" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="L4" s="105" t="s">
         <v>174</v>
@@ -12302,11 +13064,11 @@
         <v>184</v>
       </c>
       <c r="I5" s="105" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="J5" s="93"/>
       <c r="K5" s="105" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="L5" s="105" t="s">
         <v>174</v>
@@ -12337,11 +13099,11 @@
         <v>184</v>
       </c>
       <c r="I6" s="105" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="J6" s="93"/>
       <c r="K6" s="105" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="L6" s="105" t="s">
         <v>174</v>
@@ -12372,11 +13134,11 @@
         <v>184</v>
       </c>
       <c r="I7" s="105" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="J7" s="93"/>
       <c r="K7" s="105" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="L7" s="105" t="s">
         <v>174</v>
@@ -12407,11 +13169,11 @@
         <v>184</v>
       </c>
       <c r="I8" s="105" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="J8" s="93"/>
       <c r="K8" s="105" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="L8" s="105" t="s">
         <v>174</v>
@@ -12442,14 +13204,14 @@
         <v>185</v>
       </c>
       <c r="I9" s="105" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="J9" s="93"/>
       <c r="K9" s="105" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="L9" s="105" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="M9" s="105"/>
       <c r="N9" s="93"/>
@@ -12477,11 +13239,11 @@
         <v>184</v>
       </c>
       <c r="I10" s="105" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="J10" s="93"/>
       <c r="K10" s="105" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="L10" s="105" t="s">
         <v>174</v>
@@ -12512,11 +13274,11 @@
         <v>183</v>
       </c>
       <c r="I11" s="105" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="J11" s="93"/>
       <c r="K11" s="105" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L11" s="105" t="s">
         <v>174</v>
@@ -12582,14 +13344,14 @@
         <v>191</v>
       </c>
       <c r="I13" s="105" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="J13" s="93"/>
       <c r="K13" s="105" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="L13" s="105" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="M13" s="105"/>
       <c r="N13" s="93"/>
@@ -12608,17 +13370,17 @@
       <c r="F14" s="105"/>
       <c r="G14" s="114"/>
       <c r="H14" s="105" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I14" s="105" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="J14" s="93"/>
       <c r="K14" s="105" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="L14" s="105" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="M14" s="105"/>
       <c r="N14" s="93"/>
@@ -12676,14 +13438,14 @@
         <v>171</v>
       </c>
       <c r="H16" s="105" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I16" s="105" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="J16" s="93"/>
       <c r="K16" s="105" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="L16" s="105"/>
       <c r="M16" s="105"/>
@@ -12707,10 +13469,10 @@
         <v>171</v>
       </c>
       <c r="H17" s="89" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I17" s="89" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="J17" s="93"/>
       <c r="K17" s="89" t="s">
@@ -12745,14 +13507,14 @@
         <v>189</v>
       </c>
       <c r="I18" s="105" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J18" s="93"/>
       <c r="K18" s="105" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="L18" s="105" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="M18" s="105"/>
       <c r="N18" s="93"/>
@@ -13190,7 +13952,7 @@
       <c r="G14" s="105"/>
       <c r="H14" s="89"/>
       <c r="I14" s="122" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -13372,7 +14134,7 @@
         <v>126</v>
       </c>
       <c r="F2" s="183" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G2" s="183"/>
       <c r="H2" s="183"/>
@@ -13588,16 +14350,16 @@
       </c>
       <c r="E14" s="100"/>
       <c r="F14" s="123" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="G14" s="123" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H14" s="123" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I14" s="123" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -13779,7 +14541,7 @@
         <v>126</v>
       </c>
       <c r="F2" s="183" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="G2" s="183"/>
       <c r="H2" s="183"/>
@@ -13791,16 +14553,16 @@
       <c r="D3" s="190"/>
       <c r="E3" s="188"/>
       <c r="F3" s="97" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="G3" s="97" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H3" s="97" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="I3" s="98" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -13826,7 +14588,7 @@
         <v>181</v>
       </c>
       <c r="C5" s="117" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D5" s="117" t="s">
         <v>180</v>
@@ -13837,18 +14599,18 @@
       <c r="F5" s="114"/>
       <c r="G5" s="105"/>
       <c r="H5" s="123" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="I5" s="135" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="152" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C6" s="117" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D6" s="117" t="s">
         <v>178</v>
@@ -13859,7 +14621,7 @@
       <c r="F6" s="123"/>
       <c r="G6" s="123"/>
       <c r="H6" s="133" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I6" s="156"/>
     </row>
@@ -13868,19 +14630,19 @@
         <v>75</v>
       </c>
       <c r="C7" s="117" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D7" s="117" t="s">
         <v>178</v>
       </c>
       <c r="E7" s="100" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F7" s="114"/>
       <c r="G7" s="105"/>
       <c r="H7" s="89"/>
       <c r="I7" s="134" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="87.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -13888,19 +14650,19 @@
         <v>109</v>
       </c>
       <c r="C8" s="117" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D8" s="117" t="s">
         <v>178</v>
       </c>
       <c r="E8" s="100" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F8" s="114"/>
       <c r="G8" s="104"/>
       <c r="H8" s="89"/>
       <c r="I8" s="134" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -13908,7 +14670,7 @@
         <v>117</v>
       </c>
       <c r="C9" s="117" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D9" s="117" t="s">
         <v>178</v>
@@ -13926,7 +14688,7 @@
         <v>123</v>
       </c>
       <c r="C10" s="117" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D10" s="117" t="s">
         <v>178</v>
@@ -13944,7 +14706,7 @@
         <v>124</v>
       </c>
       <c r="C11" s="117" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D11" s="117" t="s">
         <v>178</v>
@@ -13962,7 +14724,7 @@
         <v>125</v>
       </c>
       <c r="C12" s="117" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D12" s="117" t="s">
         <v>178</v>
@@ -13980,21 +14742,21 @@
         <v>62</v>
       </c>
       <c r="C13" s="117" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D13" s="117" t="s">
         <v>178</v>
       </c>
       <c r="E13" s="100" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F13" s="114"/>
       <c r="G13" s="105"/>
       <c r="H13" s="133" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="I13" s="134" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -14002,21 +14764,21 @@
         <v>73</v>
       </c>
       <c r="C14" s="117" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D14" s="117" t="s">
         <v>178</v>
       </c>
       <c r="E14" s="100" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F14" s="114"/>
       <c r="G14" s="105"/>
       <c r="H14" s="133" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="I14" s="134" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -14024,23 +14786,23 @@
         <v>55</v>
       </c>
       <c r="C15" s="117" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D15" s="117" t="s">
         <v>178</v>
       </c>
       <c r="E15" s="100" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F15" s="114"/>
       <c r="G15" s="133" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H15" s="137" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I15" s="159" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="228.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -14048,21 +14810,21 @@
         <v>85</v>
       </c>
       <c r="C16" s="117" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D16" s="117" t="s">
         <v>178</v>
       </c>
       <c r="E16" s="100" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F16" s="114"/>
       <c r="G16" s="105"/>
       <c r="H16" s="133" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I16" s="134" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -14070,23 +14832,23 @@
         <v>167</v>
       </c>
       <c r="C17" s="117" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D17" s="117" t="s">
         <v>178</v>
       </c>
       <c r="E17" s="113" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F17" s="114"/>
       <c r="G17" s="129" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="H17" s="155" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="I17" s="136" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="18" spans="2:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14094,13 +14856,13 @@
         <v>141</v>
       </c>
       <c r="C18" s="117" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D18" s="117" t="s">
         <v>178</v>
       </c>
       <c r="E18" s="113" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F18" s="114"/>
       <c r="G18" s="129"/>
@@ -14112,7 +14874,7 @@
         <v>3</v>
       </c>
       <c r="C19" s="139" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D19" s="139" t="s">
         <v>178</v>
@@ -14122,13 +14884,13 @@
       </c>
       <c r="F19" s="114"/>
       <c r="G19" s="133" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H19" s="133" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I19" s="134" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -14136,17 +14898,17 @@
         <v>45</v>
       </c>
       <c r="C20" s="144" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D20" s="144" t="s">
         <v>178</v>
       </c>
       <c r="E20" s="145" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F20" s="146"/>
       <c r="G20" s="147" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="H20" s="148"/>
       <c r="I20" s="149"/>
@@ -14204,7 +14966,7 @@
         <v>126</v>
       </c>
       <c r="F2" s="183" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="G2" s="183"/>
       <c r="H2" s="183"/>
@@ -14216,16 +14978,16 @@
       <c r="D3" s="190"/>
       <c r="E3" s="188"/>
       <c r="F3" s="97" t="s">
+        <v>296</v>
+      </c>
+      <c r="G3" s="97" t="s">
+        <v>297</v>
+      </c>
+      <c r="H3" s="97" t="s">
+        <v>298</v>
+      </c>
+      <c r="I3" s="98" t="s">
         <v>299</v>
-      </c>
-      <c r="G3" s="97" t="s">
-        <v>300</v>
-      </c>
-      <c r="H3" s="97" t="s">
-        <v>301</v>
-      </c>
-      <c r="I3" s="98" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -14251,7 +15013,7 @@
         <v>181</v>
       </c>
       <c r="C5" s="117" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D5" s="117" t="s">
         <v>180</v>
@@ -14260,20 +15022,20 @@
         <v>161</v>
       </c>
       <c r="F5" s="123" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G5" s="157"/>
       <c r="H5" s="123"/>
       <c r="I5" s="135" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="152" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C6" s="117" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D6" s="117" t="s">
         <v>178</v>
@@ -14291,7 +15053,7 @@
         <v>75</v>
       </c>
       <c r="C7" s="117" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D7" s="117" t="s">
         <v>178</v>
@@ -14300,10 +15062,10 @@
         <v>162</v>
       </c>
       <c r="F7" s="123" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G7" s="105" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="H7" s="89"/>
       <c r="I7" s="93"/>
@@ -14313,7 +15075,7 @@
         <v>109</v>
       </c>
       <c r="C8" s="117" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D8" s="117" t="s">
         <v>178</v>
@@ -14331,7 +15093,7 @@
         <v>117</v>
       </c>
       <c r="C9" s="117" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D9" s="117" t="s">
         <v>178</v>
@@ -14349,7 +15111,7 @@
         <v>123</v>
       </c>
       <c r="C10" s="117" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D10" s="117" t="s">
         <v>178</v>
@@ -14367,7 +15129,7 @@
         <v>124</v>
       </c>
       <c r="C11" s="117" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D11" s="117" t="s">
         <v>178</v>
@@ -14385,7 +15147,7 @@
         <v>125</v>
       </c>
       <c r="C12" s="117" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D12" s="117" t="s">
         <v>178</v>
@@ -14403,25 +15165,25 @@
         <v>62</v>
       </c>
       <c r="C13" s="117" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D13" s="117" t="s">
         <v>178</v>
       </c>
       <c r="E13" s="100" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F13" s="133" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G13" s="157" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H13" s="105" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I13" s="122" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
@@ -14429,25 +15191,25 @@
         <v>73</v>
       </c>
       <c r="C14" s="117" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D14" s="117" t="s">
         <v>178</v>
       </c>
       <c r="E14" s="100" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F14" s="133" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G14" s="157" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H14" s="105" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I14" s="122" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="175.5" x14ac:dyDescent="0.3">
@@ -14455,25 +15217,25 @@
         <v>55</v>
       </c>
       <c r="C15" s="117" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D15" s="117" t="s">
         <v>178</v>
       </c>
       <c r="E15" s="100" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F15" s="133" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="G15" s="133" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="H15" s="163" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="I15" s="122" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
@@ -14481,25 +15243,25 @@
         <v>85</v>
       </c>
       <c r="C16" s="117" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D16" s="117" t="s">
         <v>178</v>
       </c>
       <c r="E16" s="100" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F16" s="133" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G16" s="157" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="H16" s="157" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="I16" s="122" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="162" x14ac:dyDescent="0.3">
@@ -14507,25 +15269,25 @@
         <v>167</v>
       </c>
       <c r="C17" s="117" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D17" s="117" t="s">
         <v>178</v>
       </c>
       <c r="E17" s="113" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F17" s="155" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G17" s="119" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H17" s="163" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="I17" s="168" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
@@ -14533,7 +15295,7 @@
         <v>141</v>
       </c>
       <c r="C18" s="117" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D18" s="117" t="s">
         <v>178</v>
@@ -14549,7 +15311,7 @@
         <v>3</v>
       </c>
       <c r="C19" s="139" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D19" s="139" t="s">
         <v>178</v>
@@ -14558,16 +15320,16 @@
         <v>156</v>
       </c>
       <c r="F19" s="133" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="G19" s="158" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H19" s="133" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="I19" s="134" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -14575,16 +15337,16 @@
         <v>45</v>
       </c>
       <c r="C20" s="144" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D20" s="144" t="s">
         <v>178</v>
       </c>
       <c r="E20" s="145" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F20" s="161" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G20" s="147"/>
       <c r="H20" s="148"/>
@@ -14644,7 +15406,7 @@
         <v>126</v>
       </c>
       <c r="F2" s="183" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="G2" s="183"/>
       <c r="H2" s="183"/>
@@ -14657,19 +15419,19 @@
       <c r="D3" s="190"/>
       <c r="E3" s="188"/>
       <c r="F3" s="97" t="s">
+        <v>346</v>
+      </c>
+      <c r="G3" s="97" t="s">
+        <v>348</v>
+      </c>
+      <c r="H3" s="97" t="s">
         <v>349</v>
       </c>
-      <c r="G3" s="97" t="s">
+      <c r="I3" s="170" t="s">
+        <v>350</v>
+      </c>
+      <c r="J3" s="98" t="s">
         <v>351</v>
-      </c>
-      <c r="H3" s="97" t="s">
-        <v>352</v>
-      </c>
-      <c r="I3" s="170" t="s">
-        <v>353</v>
-      </c>
-      <c r="J3" s="98" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -14696,7 +15458,7 @@
         <v>181</v>
       </c>
       <c r="C5" s="117" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D5" s="117" t="s">
         <v>180</v>
@@ -14705,10 +15467,10 @@
         <v>161</v>
       </c>
       <c r="F5" s="123" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="G5" s="123" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="H5" s="123"/>
       <c r="I5" s="172"/>
@@ -14719,7 +15481,7 @@
         <v>118</v>
       </c>
       <c r="C6" s="117" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D6" s="117" t="s">
         <v>178</v>
@@ -14738,7 +15500,7 @@
         <v>75</v>
       </c>
       <c r="C7" s="117" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D7" s="117" t="s">
         <v>178</v>
@@ -14757,7 +15519,7 @@
         <v>109</v>
       </c>
       <c r="C8" s="117" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D8" s="117" t="s">
         <v>178</v>
@@ -14776,7 +15538,7 @@
         <v>117</v>
       </c>
       <c r="C9" s="117" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D9" s="117" t="s">
         <v>178</v>
@@ -14795,7 +15557,7 @@
         <v>123</v>
       </c>
       <c r="C10" s="117" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D10" s="117" t="s">
         <v>178</v>
@@ -14814,7 +15576,7 @@
         <v>124</v>
       </c>
       <c r="C11" s="117" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D11" s="117" t="s">
         <v>178</v>
@@ -14833,7 +15595,7 @@
         <v>125</v>
       </c>
       <c r="C12" s="117" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D12" s="117" t="s">
         <v>178</v>
@@ -14852,25 +15614,25 @@
         <v>62</v>
       </c>
       <c r="C13" s="117" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D13" s="117" t="s">
         <v>178</v>
       </c>
       <c r="E13" s="100" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F13" s="105" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G13" s="157" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H13" s="105" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="I13" s="105" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="J13" s="122"/>
     </row>
@@ -14879,25 +15641,25 @@
         <v>73</v>
       </c>
       <c r="C14" s="117" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D14" s="117" t="s">
         <v>178</v>
       </c>
       <c r="E14" s="100" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F14" s="105" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G14" s="157" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H14" s="105" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I14" s="105" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="J14" s="122"/>
     </row>
@@ -14906,25 +15668,25 @@
         <v>55</v>
       </c>
       <c r="C15" s="117" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D15" s="117" t="s">
         <v>178</v>
       </c>
       <c r="E15" s="100" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F15" s="105" t="s">
+        <v>355</v>
+      </c>
+      <c r="G15" s="157" t="s">
         <v>358</v>
       </c>
-      <c r="G15" s="157" t="s">
-        <v>361</v>
-      </c>
       <c r="H15" s="157" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="I15" s="157" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="J15" s="122"/>
     </row>
@@ -14933,25 +15695,25 @@
         <v>85</v>
       </c>
       <c r="C16" s="117" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D16" s="117" t="s">
         <v>178</v>
       </c>
       <c r="E16" s="100" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F16" s="105" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="G16" s="157" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="H16" s="157" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="I16" s="157" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="J16" s="122"/>
     </row>
@@ -14960,25 +15722,25 @@
         <v>167</v>
       </c>
       <c r="C17" s="117" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D17" s="117" t="s">
         <v>178</v>
       </c>
       <c r="E17" s="113" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F17" s="119" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G17" s="169" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="H17" s="169" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="I17" s="169" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="J17" s="168"/>
     </row>
@@ -14987,7 +15749,7 @@
         <v>141</v>
       </c>
       <c r="C18" s="117" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D18" s="117" t="s">
         <v>178</v>
@@ -15004,7 +15766,7 @@
         <v>3</v>
       </c>
       <c r="C19" s="139" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D19" s="139" t="s">
         <v>178</v>
@@ -15013,7 +15775,7 @@
         <v>156</v>
       </c>
       <c r="F19" s="105" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="G19" s="158"/>
       <c r="H19" s="133"/>
@@ -15025,16 +15787,16 @@
         <v>45</v>
       </c>
       <c r="C20" s="144" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D20" s="144" t="s">
         <v>178</v>
       </c>
       <c r="E20" s="145" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F20" s="161" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="G20" s="147"/>
       <c r="H20" s="148"/>
@@ -15053,4 +15815,402 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
+    <col min="2" max="2" width="9" style="81"/>
+    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
+    <col min="5" max="5" width="43" style="81" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
+    <col min="7" max="9" width="62.125" style="81" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="81"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="109" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="107"/>
+    </row>
+    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="185" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="189" t="s">
+        <v>176</v>
+      </c>
+      <c r="D2" s="189" t="s">
+        <v>177</v>
+      </c>
+      <c r="E2" s="187" t="s">
+        <v>126</v>
+      </c>
+      <c r="F2" s="183" t="s">
+        <v>373</v>
+      </c>
+      <c r="G2" s="183"/>
+      <c r="H2" s="183"/>
+      <c r="I2" s="184"/>
+    </row>
+    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="186"/>
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="188"/>
+      <c r="F3" s="97" t="s">
+        <v>374</v>
+      </c>
+      <c r="G3" s="97" t="s">
+        <v>375</v>
+      </c>
+      <c r="H3" s="97" t="s">
+        <v>376</v>
+      </c>
+      <c r="I3" s="98" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="151" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="116" t="s">
+        <v>175</v>
+      </c>
+      <c r="D4" s="116" t="s">
+        <v>178</v>
+      </c>
+      <c r="E4" s="140" t="s">
+        <v>140</v>
+      </c>
+      <c r="F4" s="141"/>
+      <c r="G4" s="142"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="92"/>
+    </row>
+    <row r="5" spans="1:9" ht="54" x14ac:dyDescent="0.3">
+      <c r="B5" s="154" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" s="117" t="s">
+        <v>267</v>
+      </c>
+      <c r="D5" s="117" t="s">
+        <v>180</v>
+      </c>
+      <c r="E5" s="100" t="s">
+        <v>161</v>
+      </c>
+      <c r="F5" s="123" t="s">
+        <v>357</v>
+      </c>
+      <c r="G5" s="123"/>
+      <c r="H5" s="123"/>
+      <c r="I5" s="135"/>
+    </row>
+    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="152" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="117" t="s">
+        <v>268</v>
+      </c>
+      <c r="D6" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E6" s="100" t="s">
+        <v>161</v>
+      </c>
+      <c r="F6" s="123"/>
+      <c r="G6" s="123"/>
+      <c r="H6" s="123"/>
+      <c r="I6" s="135"/>
+    </row>
+    <row r="7" spans="1:9" ht="162" x14ac:dyDescent="0.3">
+      <c r="B7" s="152" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="117" t="s">
+        <v>268</v>
+      </c>
+      <c r="D7" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E7" s="100" t="s">
+        <v>162</v>
+      </c>
+      <c r="F7" s="123" t="s">
+        <v>386</v>
+      </c>
+      <c r="G7" s="105"/>
+      <c r="H7" s="89"/>
+      <c r="I7" s="93"/>
+    </row>
+    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="152" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="117" t="s">
+        <v>268</v>
+      </c>
+      <c r="D8" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E8" s="91" t="s">
+        <v>139</v>
+      </c>
+      <c r="F8" s="114"/>
+      <c r="G8" s="104"/>
+      <c r="H8" s="89"/>
+      <c r="I8" s="93"/>
+    </row>
+    <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="153" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="117" t="s">
+        <v>268</v>
+      </c>
+      <c r="D9" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E9" s="91" t="s">
+        <v>152</v>
+      </c>
+      <c r="F9" s="114"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="138"/>
+      <c r="I9" s="93"/>
+    </row>
+    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="153" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" s="117" t="s">
+        <v>268</v>
+      </c>
+      <c r="D10" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E10" s="91" t="s">
+        <v>153</v>
+      </c>
+      <c r="F10" s="114"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="89"/>
+      <c r="I10" s="93"/>
+    </row>
+    <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="153" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" s="117" t="s">
+        <v>268</v>
+      </c>
+      <c r="D11" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E11" s="91" t="s">
+        <v>154</v>
+      </c>
+      <c r="F11" s="114"/>
+      <c r="G11" s="105"/>
+      <c r="H11" s="89"/>
+      <c r="I11" s="93"/>
+    </row>
+    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="153" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" s="117" t="s">
+        <v>268</v>
+      </c>
+      <c r="D12" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E12" s="91" t="s">
+        <v>155</v>
+      </c>
+      <c r="F12" s="114"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="138"/>
+      <c r="I12" s="93"/>
+    </row>
+    <row r="13" spans="1:9" ht="27" x14ac:dyDescent="0.3">
+      <c r="B13" s="132" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="117" t="s">
+        <v>270</v>
+      </c>
+      <c r="D13" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E13" s="100" t="s">
+        <v>260</v>
+      </c>
+      <c r="F13" s="105"/>
+      <c r="G13" s="157"/>
+      <c r="H13" s="105"/>
+      <c r="I13" s="122"/>
+    </row>
+    <row r="14" spans="1:9" ht="148.5" x14ac:dyDescent="0.3">
+      <c r="B14" s="131" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="117" t="s">
+        <v>270</v>
+      </c>
+      <c r="D14" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E14" s="100" t="s">
+        <v>261</v>
+      </c>
+      <c r="F14" s="105" t="s">
+        <v>370</v>
+      </c>
+      <c r="G14" s="157"/>
+      <c r="H14" s="105"/>
+      <c r="I14" s="122"/>
+    </row>
+    <row r="15" spans="1:9" ht="108" x14ac:dyDescent="0.3">
+      <c r="B15" s="131" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="117" t="s">
+        <v>270</v>
+      </c>
+      <c r="D15" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E15" s="100" t="s">
+        <v>259</v>
+      </c>
+      <c r="F15" s="105" t="s">
+        <v>387</v>
+      </c>
+      <c r="G15" s="157"/>
+      <c r="H15" s="157"/>
+      <c r="I15" s="192"/>
+    </row>
+    <row r="16" spans="1:9" ht="297" x14ac:dyDescent="0.3">
+      <c r="B16" s="131" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="117" t="s">
+        <v>270</v>
+      </c>
+      <c r="D16" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E16" s="100" t="s">
+        <v>262</v>
+      </c>
+      <c r="F16" s="105" t="s">
+        <v>388</v>
+      </c>
+      <c r="G16" s="157"/>
+      <c r="H16" s="157"/>
+      <c r="I16" s="192"/>
+    </row>
+    <row r="17" spans="2:9" ht="108" x14ac:dyDescent="0.3">
+      <c r="B17" s="130" t="s">
+        <v>167</v>
+      </c>
+      <c r="C17" s="117" t="s">
+        <v>270</v>
+      </c>
+      <c r="D17" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E17" s="113" t="s">
+        <v>303</v>
+      </c>
+      <c r="F17" s="119" t="s">
+        <v>389</v>
+      </c>
+      <c r="G17" s="169"/>
+      <c r="H17" s="169"/>
+      <c r="I17" s="193"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B18" s="131" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" s="117" t="s">
+        <v>270</v>
+      </c>
+      <c r="D18" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E18" s="113"/>
+      <c r="F18" s="155"/>
+      <c r="G18" s="158"/>
+      <c r="H18" s="133"/>
+      <c r="I18" s="136"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B19" s="150" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="139" t="s">
+        <v>270</v>
+      </c>
+      <c r="D19" s="139" t="s">
+        <v>178</v>
+      </c>
+      <c r="E19" s="91" t="s">
+        <v>156</v>
+      </c>
+      <c r="F19" s="105" t="s">
+        <v>263</v>
+      </c>
+      <c r="G19" s="158"/>
+      <c r="H19" s="133"/>
+      <c r="I19" s="134"/>
+    </row>
+    <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="194" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="118" t="s">
+        <v>270</v>
+      </c>
+      <c r="D20" s="118" t="s">
+        <v>178</v>
+      </c>
+      <c r="E20" s="103" t="s">
+        <v>258</v>
+      </c>
+      <c r="F20" s="195" t="s">
+        <v>263</v>
+      </c>
+      <c r="G20" s="106"/>
+      <c r="H20" s="196"/>
+      <c r="I20" s="95"/>
+    </row>
+    <row r="21" spans="2:9" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:I2"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -7519,8 +7519,136 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R로직 점검 및 기능 점검 (12/30)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 안건 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SW 점검</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 진행 및 검토 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R로직 점검</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>로직 및 기능 체크리스트 기반 검증 진행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S/W 이상 없음</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>[임제훈 사원]
-1. 기구 변경점 반영 및 S/W 적용 (~01/09)
+1. 실차 점검으로 인한 남양연구소 방문 (01/06)
+  [ 안건 ]
+    - 고객사 및 한온에서 차량 평가 중, Fault 발생으로 인한 실차 점검 요청
+  [ 진행 및 검토 ]
+    - 차량 평가 당시 상황 재현 시도
+    - Fault 발생 원인 및 분석
+  [ 결과 ]
+    - 엔진 열 + PTC 발열로 인한 열 중첩 현상으로 Fault 발생 추정됨
+    - 고객사에서는 과열로 인해 Fault 발생한 것은 정상적인 로직이라고 판단함.
+    - 차주 13일 (화) 혹은 14일 (수)에 챔버 일정 확정 후 테스트 진행
+     : 우리산업 테스트 참석 요청
+2. 기구 변경점 반영 및 S/W 적용 (~01/09)
   [ 안건 ]
     - Stone TC 160℃ → 165℃ 변경
     - 전압 범위 변경
@@ -7533,7 +7661,7 @@
     - 기구 변경점 S/W 반영
     - R로직 튜닝
     - 로직 및 기능 체크리스트 기반 검증 진행
-2. 사이버 보안 기능 품확 활동 (~01/09)
+3. 사이버 보안 기능 품확 활동 (~01/09)
   [ 안건 ]
     - 첨부파일 작성
      : NX5_(제어기명)_공정보안_체크리스트(설계팀,협력사용)
@@ -7541,123 +7669,6 @@
     - QV 작성자료 참고
     - 사이버보안품질연구팀에 보낼 샘플 준비
      : PCB 2EA, Signal Connector 1EA, E2 Pin Connector 1EA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">[임제훈 사원]
-1. </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R로직 점검 및 기능 점검 (12/30)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  [ 안건 ]
-    - </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SW 점검</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  [ 진행 및 검토 ]
-    - </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R로직 점검</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-    - </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>로직 및 기능 체크리스트 기반 검증 진행</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-      : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S/W 이상 없음</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -9661,6 +9672,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="80" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="87" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -9708,24 +9737,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="80" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="87" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -10392,90 +10403,90 @@
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="176" t="s">
+      <c r="B2" s="182" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="178" t="s">
+      <c r="C2" s="184" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="178" t="s">
+      <c r="D2" s="184" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="182">
+      <c r="E2" s="188">
         <v>23</v>
       </c>
-      <c r="F2" s="180"/>
-      <c r="G2" s="180"/>
-      <c r="H2" s="180"/>
-      <c r="I2" s="180"/>
-      <c r="J2" s="180"/>
-      <c r="K2" s="180"/>
-      <c r="L2" s="180"/>
-      <c r="M2" s="180"/>
-      <c r="N2" s="180"/>
-      <c r="O2" s="180"/>
-      <c r="P2" s="180"/>
-      <c r="Q2" s="180">
+      <c r="F2" s="186"/>
+      <c r="G2" s="186"/>
+      <c r="H2" s="186"/>
+      <c r="I2" s="186"/>
+      <c r="J2" s="186"/>
+      <c r="K2" s="186"/>
+      <c r="L2" s="186"/>
+      <c r="M2" s="186"/>
+      <c r="N2" s="186"/>
+      <c r="O2" s="186"/>
+      <c r="P2" s="186"/>
+      <c r="Q2" s="186">
         <v>24</v>
       </c>
-      <c r="R2" s="180"/>
-      <c r="S2" s="180"/>
-      <c r="T2" s="180"/>
-      <c r="U2" s="180"/>
-      <c r="V2" s="180"/>
-      <c r="W2" s="180"/>
-      <c r="X2" s="180"/>
-      <c r="Y2" s="180"/>
-      <c r="Z2" s="180"/>
-      <c r="AA2" s="180"/>
-      <c r="AB2" s="180"/>
-      <c r="AC2" s="180">
+      <c r="R2" s="186"/>
+      <c r="S2" s="186"/>
+      <c r="T2" s="186"/>
+      <c r="U2" s="186"/>
+      <c r="V2" s="186"/>
+      <c r="W2" s="186"/>
+      <c r="X2" s="186"/>
+      <c r="Y2" s="186"/>
+      <c r="Z2" s="186"/>
+      <c r="AA2" s="186"/>
+      <c r="AB2" s="186"/>
+      <c r="AC2" s="186">
         <v>25</v>
       </c>
-      <c r="AD2" s="180"/>
-      <c r="AE2" s="180"/>
-      <c r="AF2" s="180"/>
-      <c r="AG2" s="180"/>
-      <c r="AH2" s="180"/>
-      <c r="AI2" s="180"/>
-      <c r="AJ2" s="180"/>
-      <c r="AK2" s="180"/>
-      <c r="AL2" s="180"/>
-      <c r="AM2" s="180"/>
-      <c r="AN2" s="180"/>
-      <c r="AO2" s="180">
+      <c r="AD2" s="186"/>
+      <c r="AE2" s="186"/>
+      <c r="AF2" s="186"/>
+      <c r="AG2" s="186"/>
+      <c r="AH2" s="186"/>
+      <c r="AI2" s="186"/>
+      <c r="AJ2" s="186"/>
+      <c r="AK2" s="186"/>
+      <c r="AL2" s="186"/>
+      <c r="AM2" s="186"/>
+      <c r="AN2" s="186"/>
+      <c r="AO2" s="186">
         <v>26</v>
       </c>
-      <c r="AP2" s="180"/>
-      <c r="AQ2" s="180"/>
-      <c r="AR2" s="180"/>
-      <c r="AS2" s="180"/>
-      <c r="AT2" s="180"/>
-      <c r="AU2" s="180"/>
-      <c r="AV2" s="180"/>
-      <c r="AW2" s="180"/>
-      <c r="AX2" s="180"/>
-      <c r="AY2" s="180"/>
-      <c r="AZ2" s="181"/>
-      <c r="BA2" s="180">
+      <c r="AP2" s="186"/>
+      <c r="AQ2" s="186"/>
+      <c r="AR2" s="186"/>
+      <c r="AS2" s="186"/>
+      <c r="AT2" s="186"/>
+      <c r="AU2" s="186"/>
+      <c r="AV2" s="186"/>
+      <c r="AW2" s="186"/>
+      <c r="AX2" s="186"/>
+      <c r="AY2" s="186"/>
+      <c r="AZ2" s="187"/>
+      <c r="BA2" s="186">
         <v>27</v>
       </c>
-      <c r="BB2" s="180"/>
-      <c r="BC2" s="180"/>
-      <c r="BD2" s="180"/>
-      <c r="BE2" s="180"/>
-      <c r="BF2" s="180"/>
-      <c r="BG2" s="180"/>
-      <c r="BH2" s="180"/>
-      <c r="BI2" s="180"/>
-      <c r="BJ2" s="180"/>
-      <c r="BK2" s="180"/>
-      <c r="BL2" s="181"/>
+      <c r="BB2" s="186"/>
+      <c r="BC2" s="186"/>
+      <c r="BD2" s="186"/>
+      <c r="BE2" s="186"/>
+      <c r="BF2" s="186"/>
+      <c r="BG2" s="186"/>
+      <c r="BH2" s="186"/>
+      <c r="BI2" s="186"/>
+      <c r="BJ2" s="186"/>
+      <c r="BK2" s="186"/>
+      <c r="BL2" s="187"/>
     </row>
     <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="177"/>
-      <c r="C3" s="179"/>
-      <c r="D3" s="179"/>
+      <c r="B3" s="183"/>
+      <c r="C3" s="185"/>
+      <c r="D3" s="185"/>
       <c r="E3" s="22">
         <v>1</v>
       </c>
@@ -11793,7 +11804,7 @@
       </c>
       <c r="AX17" s="30"/>
       <c r="AY17" s="41"/>
-      <c r="AZ17" s="197" t="s">
+      <c r="AZ17" s="181" t="s">
         <v>381</v>
       </c>
       <c r="BA17" s="47"/>
@@ -12415,31 +12426,31 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="185" t="s">
+      <c r="B2" s="191" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="189" t="s">
+      <c r="C2" s="195" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="189" t="s">
+      <c r="D2" s="195" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="187" t="s">
+      <c r="E2" s="193" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="183" t="s">
+      <c r="F2" s="189" t="s">
         <v>378</v>
       </c>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="191"/>
-      <c r="J2" s="184"/>
+      <c r="G2" s="189"/>
+      <c r="H2" s="189"/>
+      <c r="I2" s="197"/>
+      <c r="J2" s="190"/>
     </row>
     <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="186"/>
-      <c r="C3" s="190"/>
-      <c r="D3" s="190"/>
-      <c r="E3" s="188"/>
+      <c r="B3" s="192"/>
+      <c r="C3" s="196"/>
+      <c r="D3" s="196"/>
+      <c r="E3" s="194"/>
       <c r="F3" s="97" t="s">
         <v>379</v>
       </c>
@@ -12945,39 +12956,39 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="185" t="s">
+      <c r="B2" s="191" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="189" t="s">
+      <c r="C2" s="195" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="189" t="s">
+      <c r="D2" s="195" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="187" t="s">
+      <c r="E2" s="193" t="s">
         <v>126</v>
       </c>
       <c r="F2" s="96" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="183" t="s">
+      <c r="G2" s="189" t="s">
         <v>113</v>
       </c>
-      <c r="H2" s="183"/>
-      <c r="I2" s="183"/>
-      <c r="J2" s="184"/>
-      <c r="K2" s="183" t="s">
+      <c r="H2" s="189"/>
+      <c r="I2" s="189"/>
+      <c r="J2" s="190"/>
+      <c r="K2" s="189" t="s">
         <v>182</v>
       </c>
-      <c r="L2" s="183"/>
-      <c r="M2" s="183"/>
-      <c r="N2" s="184"/>
+      <c r="L2" s="189"/>
+      <c r="M2" s="189"/>
+      <c r="N2" s="190"/>
     </row>
     <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="186"/>
-      <c r="C3" s="190"/>
-      <c r="D3" s="190"/>
-      <c r="E3" s="188"/>
+      <c r="B3" s="192"/>
+      <c r="C3" s="196"/>
+      <c r="D3" s="196"/>
+      <c r="E3" s="194"/>
       <c r="F3" s="97" t="s">
         <v>111</v>
       </c>
@@ -13720,30 +13731,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="185" t="s">
+      <c r="B2" s="191" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="189" t="s">
+      <c r="C2" s="195" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="189" t="s">
+      <c r="D2" s="195" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="187" t="s">
+      <c r="E2" s="193" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="183" t="s">
+      <c r="F2" s="189" t="s">
         <v>182</v>
       </c>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="184"/>
+      <c r="G2" s="189"/>
+      <c r="H2" s="189"/>
+      <c r="I2" s="190"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="186"/>
-      <c r="C3" s="190"/>
-      <c r="D3" s="190"/>
-      <c r="E3" s="188"/>
+      <c r="B3" s="192"/>
+      <c r="C3" s="196"/>
+      <c r="D3" s="196"/>
+      <c r="E3" s="194"/>
       <c r="F3" s="97" t="s">
         <v>114</v>
       </c>
@@ -14121,30 +14132,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="185" t="s">
+      <c r="B2" s="191" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="189" t="s">
+      <c r="C2" s="195" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="189" t="s">
+      <c r="D2" s="195" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="187" t="s">
+      <c r="E2" s="193" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="183" t="s">
+      <c r="F2" s="189" t="s">
         <v>224</v>
       </c>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="184"/>
+      <c r="G2" s="189"/>
+      <c r="H2" s="189"/>
+      <c r="I2" s="190"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="186"/>
-      <c r="C3" s="190"/>
-      <c r="D3" s="190"/>
-      <c r="E3" s="188"/>
+      <c r="B3" s="192"/>
+      <c r="C3" s="196"/>
+      <c r="D3" s="196"/>
+      <c r="E3" s="194"/>
       <c r="F3" s="97" t="s">
         <v>114</v>
       </c>
@@ -14528,30 +14539,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="185" t="s">
+      <c r="B2" s="191" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="189" t="s">
+      <c r="C2" s="195" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="189" t="s">
+      <c r="D2" s="195" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="187" t="s">
+      <c r="E2" s="193" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="183" t="s">
+      <c r="F2" s="189" t="s">
         <v>256</v>
       </c>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="184"/>
+      <c r="G2" s="189"/>
+      <c r="H2" s="189"/>
+      <c r="I2" s="190"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="186"/>
-      <c r="C3" s="190"/>
-      <c r="D3" s="190"/>
-      <c r="E3" s="188"/>
+      <c r="B3" s="192"/>
+      <c r="C3" s="196"/>
+      <c r="D3" s="196"/>
+      <c r="E3" s="194"/>
       <c r="F3" s="97" t="s">
         <v>277</v>
       </c>
@@ -14953,30 +14964,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="185" t="s">
+      <c r="B2" s="191" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="189" t="s">
+      <c r="C2" s="195" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="189" t="s">
+      <c r="D2" s="195" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="187" t="s">
+      <c r="E2" s="193" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="183" t="s">
+      <c r="F2" s="189" t="s">
         <v>276</v>
       </c>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="184"/>
+      <c r="G2" s="189"/>
+      <c r="H2" s="189"/>
+      <c r="I2" s="190"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="186"/>
-      <c r="C3" s="190"/>
-      <c r="D3" s="190"/>
-      <c r="E3" s="188"/>
+      <c r="B3" s="192"/>
+      <c r="C3" s="196"/>
+      <c r="D3" s="196"/>
+      <c r="E3" s="194"/>
       <c r="F3" s="97" t="s">
         <v>296</v>
       </c>
@@ -15393,31 +15404,31 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="185" t="s">
+      <c r="B2" s="191" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="189" t="s">
+      <c r="C2" s="195" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="189" t="s">
+      <c r="D2" s="195" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="187" t="s">
+      <c r="E2" s="193" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="183" t="s">
+      <c r="F2" s="189" t="s">
         <v>347</v>
       </c>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="191"/>
-      <c r="J2" s="184"/>
+      <c r="G2" s="189"/>
+      <c r="H2" s="189"/>
+      <c r="I2" s="197"/>
+      <c r="J2" s="190"/>
     </row>
     <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="186"/>
-      <c r="C3" s="190"/>
-      <c r="D3" s="190"/>
-      <c r="E3" s="188"/>
+      <c r="B3" s="192"/>
+      <c r="C3" s="196"/>
+      <c r="D3" s="196"/>
+      <c r="E3" s="194"/>
       <c r="F3" s="97" t="s">
         <v>346</v>
       </c>
@@ -15843,30 +15854,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="185" t="s">
+      <c r="B2" s="191" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="189" t="s">
+      <c r="C2" s="195" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="189" t="s">
+      <c r="D2" s="195" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="187" t="s">
+      <c r="E2" s="193" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="183" t="s">
+      <c r="F2" s="189" t="s">
         <v>373</v>
       </c>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="184"/>
+      <c r="G2" s="189"/>
+      <c r="H2" s="189"/>
+      <c r="I2" s="190"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="186"/>
-      <c r="C3" s="190"/>
-      <c r="D3" s="190"/>
-      <c r="E3" s="188"/>
+      <c r="B3" s="192"/>
+      <c r="C3" s="196"/>
+      <c r="D3" s="196"/>
+      <c r="E3" s="194"/>
       <c r="F3" s="97" t="s">
         <v>374</v>
       </c>
@@ -16102,9 +16113,9 @@
       </c>
       <c r="G15" s="157"/>
       <c r="H15" s="157"/>
-      <c r="I15" s="192"/>
-    </row>
-    <row r="16" spans="1:9" ht="297" x14ac:dyDescent="0.3">
+      <c r="I15" s="176"/>
+    </row>
+    <row r="16" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
       <c r="B16" s="131" t="s">
         <v>85</v>
       </c>
@@ -16118,11 +16129,11 @@
         <v>262</v>
       </c>
       <c r="F16" s="105" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G16" s="157"/>
       <c r="H16" s="157"/>
-      <c r="I16" s="192"/>
+      <c r="I16" s="176"/>
     </row>
     <row r="17" spans="2:9" ht="108" x14ac:dyDescent="0.3">
       <c r="B17" s="130" t="s">
@@ -16138,11 +16149,11 @@
         <v>303</v>
       </c>
       <c r="F17" s="119" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G17" s="169"/>
       <c r="H17" s="169"/>
-      <c r="I17" s="193"/>
+      <c r="I17" s="177"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="131" t="s">
@@ -16181,7 +16192,7 @@
       <c r="I19" s="134"/>
     </row>
     <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="194" t="s">
+      <c r="B20" s="178" t="s">
         <v>45</v>
       </c>
       <c r="C20" s="118" t="s">
@@ -16193,11 +16204,11 @@
       <c r="E20" s="103" t="s">
         <v>258</v>
       </c>
-      <c r="F20" s="195" t="s">
+      <c r="F20" s="179" t="s">
         <v>263</v>
       </c>
       <c r="G20" s="106"/>
-      <c r="H20" s="196"/>
+      <c r="H20" s="180"/>
       <c r="I20" s="95"/>
     </row>
     <row r="21" spans="2:9" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17688" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="대일정" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="392">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -7669,6 +7669,29 @@
     - QV 작성자료 참고
     - 사이버보안품질연구팀에 보낼 샘플 준비
      : PCB 2EA, Signal Connector 1EA, E2 Pin Connector 1EA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. 사이버 보안 관련 자료 회신 요청
+  [ 요청사항 ]
+    - 사이버 보안 QV와 동일한 이력으로 진행 요청 (공조시스템설계팀)
+    - BJ1 ES95489-21 성적서 회신
+    - 사이버보안관련성평가 작성 후 회신
+  [ 진행 및 검토 ]
+    - BJ1 ES95489-21, ESIR 때 성적서 없음
+      : QV 사이버 보안 협의 및 일정 지연으로 BJ1 ESIR때 진행 불가
+      : BJ1 ES95489-21 검증 진행
+    - 사이버보안관련성평가 작성 후 검토 요청</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. 국내 윈터 트립 (01/12 ~ 01/13)
+  [ 요청사항 ]
+    - 국내 윈터 트립 참석
+  [ 진행 및 검토 ]
+    - SVm P1(77호차) PTC 제어</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -9866,15 +9889,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>5</xdr:col>
-          <xdr:colOff>2733675</xdr:colOff>
+          <xdr:colOff>2735580</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>104775</xdr:rowOff>
+          <xdr:rowOff>106680</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>5</xdr:col>
           <xdr:colOff>3505200</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>504825</xdr:rowOff>
+          <xdr:rowOff>502920</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -9925,7 +9948,7 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>5</xdr:col>
-          <xdr:colOff>3286125</xdr:colOff>
+          <xdr:colOff>3284220</xdr:colOff>
           <xdr:row>12</xdr:row>
           <xdr:rowOff>342900</xdr:rowOff>
         </xdr:from>
@@ -10380,19 +10403,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BL25"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="18.875" customWidth="1"/>
-    <col min="3" max="3" width="28.375" customWidth="1"/>
-    <col min="4" max="4" width="30.75" customWidth="1"/>
-    <col min="5" max="28" width="8.375" hidden="1" customWidth="1"/>
-    <col min="29" max="34" width="8.375" customWidth="1"/>
-    <col min="35" max="35" width="10.375" customWidth="1"/>
-    <col min="36" max="64" width="8.375" customWidth="1"/>
+    <col min="1" max="1" width="4.3984375" customWidth="1"/>
+    <col min="2" max="2" width="18.8984375" customWidth="1"/>
+    <col min="3" max="3" width="28.3984375" customWidth="1"/>
+    <col min="4" max="4" width="30.69921875" customWidth="1"/>
+    <col min="5" max="28" width="8.3984375" hidden="1" customWidth="1"/>
+    <col min="29" max="34" width="8.3984375" customWidth="1"/>
+    <col min="35" max="35" width="10.3984375" customWidth="1"/>
+    <col min="36" max="64" width="8.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" s="20" customFormat="1" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:64" s="20" customFormat="1" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -10402,7 +10425,7 @@
       <c r="C1" s="21"/>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B2" s="182" t="s">
         <v>2</v>
       </c>
@@ -10483,7 +10506,7 @@
       <c r="BK2" s="186"/>
       <c r="BL2" s="187"/>
     </row>
-    <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="183"/>
       <c r="C3" s="185"/>
       <c r="D3" s="185"/>
@@ -10668,7 +10691,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:64" ht="183" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:64" ht="183" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="63" t="s">
         <v>119</v>
       </c>
@@ -10749,7 +10772,7 @@
       <c r="BK4" s="2"/>
       <c r="BL4" s="5"/>
     </row>
-    <row r="5" spans="1:64" ht="81" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:64" ht="93.6" x14ac:dyDescent="0.4">
       <c r="B5" s="28" t="s">
         <v>120</v>
       </c>
@@ -10828,7 +10851,7 @@
       <c r="BK5" s="31"/>
       <c r="BL5" s="10"/>
     </row>
-    <row r="6" spans="1:64" ht="67.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:64" ht="78" x14ac:dyDescent="0.4">
       <c r="B6" s="28" t="s">
         <v>121</v>
       </c>
@@ -10911,7 +10934,7 @@
       <c r="BK6" s="31"/>
       <c r="BL6" s="10"/>
     </row>
-    <row r="7" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="28" t="s">
         <v>122</v>
       </c>
@@ -10992,7 +11015,7 @@
       <c r="BK7" s="31"/>
       <c r="BL7" s="10"/>
     </row>
-    <row r="8" spans="1:64" ht="81" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:64" ht="93.6" x14ac:dyDescent="0.4">
       <c r="B8" s="28" t="s">
         <v>218</v>
       </c>
@@ -11069,7 +11092,7 @@
       <c r="BK8" s="31"/>
       <c r="BL8" s="10"/>
     </row>
-    <row r="9" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="27" t="s">
         <v>3</v>
       </c>
@@ -11142,7 +11165,7 @@
       <c r="BK9" s="31"/>
       <c r="BL9" s="10"/>
     </row>
-    <row r="10" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="27" t="s">
         <v>45</v>
       </c>
@@ -11219,7 +11242,7 @@
       <c r="BK10" s="31"/>
       <c r="BL10" s="10"/>
     </row>
-    <row r="11" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="28" t="s">
         <v>127</v>
       </c>
@@ -11302,7 +11325,7 @@
       <c r="BK11" s="31"/>
       <c r="BL11" s="10"/>
     </row>
-    <row r="12" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="28" t="s">
         <v>128</v>
       </c>
@@ -11383,7 +11406,7 @@
       <c r="BK12" s="31"/>
       <c r="BL12" s="10"/>
     </row>
-    <row r="13" spans="1:64" ht="228.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:64" ht="228.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="28" t="s">
         <v>62</v>
       </c>
@@ -11472,7 +11495,7 @@
       <c r="BK13" s="31"/>
       <c r="BL13" s="10"/>
     </row>
-    <row r="14" spans="1:64" ht="67.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:64" ht="93.6" x14ac:dyDescent="0.4">
       <c r="B14" s="27" t="s">
         <v>73</v>
       </c>
@@ -11561,7 +11584,7 @@
       <c r="BK14" s="31"/>
       <c r="BL14" s="10"/>
     </row>
-    <row r="15" spans="1:64" ht="285.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:64" ht="285.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="27" t="s">
         <v>64</v>
       </c>
@@ -11644,7 +11667,7 @@
       <c r="BK15" s="31"/>
       <c r="BL15" s="10"/>
     </row>
-    <row r="16" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="27" t="s">
         <v>65</v>
       </c>
@@ -11733,7 +11756,7 @@
       <c r="BK16" s="31"/>
       <c r="BL16" s="10"/>
     </row>
-    <row r="17" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="57" t="s">
         <v>385</v>
       </c>
@@ -11824,7 +11847,7 @@
       <c r="BK17" s="71"/>
       <c r="BL17" s="48"/>
     </row>
-    <row r="18" spans="2:64" ht="179.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:64" ht="179.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="27" t="s">
         <v>85</v>
       </c>
@@ -11917,7 +11940,7 @@
       <c r="BK18" s="73"/>
       <c r="BL18" s="70"/>
     </row>
-    <row r="19" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="77" t="s">
         <v>141</v>
       </c>
@@ -12002,7 +12025,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="77" t="s">
         <v>106</v>
       </c>
@@ -12071,7 +12094,7 @@
       <c r="BK20" s="73"/>
       <c r="BL20" s="70"/>
     </row>
-    <row r="21" spans="2:64" ht="189" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:64" ht="218.4" x14ac:dyDescent="0.4">
       <c r="B21" s="57" t="s">
         <v>109</v>
       </c>
@@ -12154,7 +12177,7 @@
       <c r="BK21" s="73"/>
       <c r="BL21" s="70"/>
     </row>
-    <row r="22" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="57" t="s">
         <v>166</v>
       </c>
@@ -12223,7 +12246,7 @@
       <c r="BK22" s="73"/>
       <c r="BL22" s="70"/>
     </row>
-    <row r="23" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="57" t="s">
         <v>326</v>
       </c>
@@ -12304,7 +12327,7 @@
       <c r="BK23" s="73"/>
       <c r="BL23" s="70"/>
     </row>
-    <row r="24" spans="2:64" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:64" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B24" s="79" t="s">
         <v>325</v>
       </c>
@@ -12381,7 +12404,7 @@
       <c r="BK24" s="75"/>
       <c r="BL24" s="55"/>
     </row>
-    <row r="25" spans="2:64" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="2:64" ht="18" thickTop="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B2:B3"/>
@@ -12403,18 +12426,18 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
+    <col min="1" max="1" width="3.3984375" style="81" customWidth="1"/>
     <col min="2" max="2" width="9" style="81"/>
-    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
+    <col min="3" max="4" width="14.69921875" style="81" customWidth="1"/>
     <col min="5" max="5" width="43" style="81" customWidth="1"/>
-    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
-    <col min="7" max="10" width="62.125" style="81" customWidth="1"/>
+    <col min="6" max="6" width="61.8984375" style="81" customWidth="1"/>
+    <col min="7" max="10" width="62.09765625" style="81" customWidth="1"/>
     <col min="11" max="16384" width="9" style="81"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="108" t="s">
         <v>0</v>
       </c>
@@ -12425,7 +12448,7 @@
       <c r="D1" s="109"/>
       <c r="E1" s="107"/>
     </row>
-    <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B2" s="191" t="s">
         <v>2</v>
       </c>
@@ -12446,7 +12469,7 @@
       <c r="I2" s="197"/>
       <c r="J2" s="190"/>
     </row>
-    <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="192"/>
       <c r="C3" s="196"/>
       <c r="D3" s="196"/>
@@ -12459,7 +12482,7 @@
       <c r="I3" s="170"/>
       <c r="J3" s="98"/>
     </row>
-    <row r="4" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="151" t="s">
         <v>108</v>
       </c>
@@ -12478,7 +12501,7 @@
       <c r="I4" s="171"/>
       <c r="J4" s="92"/>
     </row>
-    <row r="5" spans="1:10" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="46.8" x14ac:dyDescent="0.4">
       <c r="B5" s="154" t="s">
         <v>181</v>
       </c>
@@ -12497,7 +12520,7 @@
       <c r="I5" s="172"/>
       <c r="J5" s="135"/>
     </row>
-    <row r="6" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="152" t="s">
         <v>118</v>
       </c>
@@ -12516,7 +12539,7 @@
       <c r="I6" s="172"/>
       <c r="J6" s="135"/>
     </row>
-    <row r="7" spans="1:10" ht="138" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="138" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="152" t="s">
         <v>75</v>
       </c>
@@ -12535,7 +12558,7 @@
       <c r="I7" s="173"/>
       <c r="J7" s="93"/>
     </row>
-    <row r="8" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="152" t="s">
         <v>109</v>
       </c>
@@ -12554,7 +12577,7 @@
       <c r="I8" s="173"/>
       <c r="J8" s="93"/>
     </row>
-    <row r="9" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="153" t="s">
         <v>117</v>
       </c>
@@ -12573,7 +12596,7 @@
       <c r="I9" s="89"/>
       <c r="J9" s="93"/>
     </row>
-    <row r="10" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="153" t="s">
         <v>123</v>
       </c>
@@ -12592,7 +12615,7 @@
       <c r="I10" s="173"/>
       <c r="J10" s="93"/>
     </row>
-    <row r="11" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="153" t="s">
         <v>124</v>
       </c>
@@ -12611,7 +12634,7 @@
       <c r="I11" s="173"/>
       <c r="J11" s="93"/>
     </row>
-    <row r="12" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="153" t="s">
         <v>125</v>
       </c>
@@ -12630,7 +12653,7 @@
       <c r="I12" s="89"/>
       <c r="J12" s="93"/>
     </row>
-    <row r="13" spans="1:10" ht="27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="31.2" x14ac:dyDescent="0.4">
       <c r="B13" s="132" t="s">
         <v>62</v>
       </c>
@@ -12649,7 +12672,7 @@
       <c r="I13" s="105"/>
       <c r="J13" s="122"/>
     </row>
-    <row r="14" spans="1:10" ht="27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="31.2" x14ac:dyDescent="0.4">
       <c r="B14" s="131" t="s">
         <v>73</v>
       </c>
@@ -12668,7 +12691,7 @@
       <c r="I14" s="105"/>
       <c r="J14" s="122"/>
     </row>
-    <row r="15" spans="1:10" ht="67.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="78" x14ac:dyDescent="0.4">
       <c r="B15" s="131" t="s">
         <v>55</v>
       </c>
@@ -12687,7 +12710,7 @@
       <c r="I15" s="157"/>
       <c r="J15" s="122"/>
     </row>
-    <row r="16" spans="1:10" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="46.8" x14ac:dyDescent="0.4">
       <c r="B16" s="131" t="s">
         <v>85</v>
       </c>
@@ -12706,7 +12729,7 @@
       <c r="I16" s="157"/>
       <c r="J16" s="122"/>
     </row>
-    <row r="17" spans="2:10" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" ht="46.8" x14ac:dyDescent="0.4">
       <c r="B17" s="130" t="s">
         <v>167</v>
       </c>
@@ -12725,7 +12748,7 @@
       <c r="I17" s="169"/>
       <c r="J17" s="168"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B18" s="131" t="s">
         <v>141</v>
       </c>
@@ -12742,7 +12765,7 @@
       <c r="I18" s="129"/>
       <c r="J18" s="136"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B19" s="150" t="s">
         <v>3</v>
       </c>
@@ -12763,7 +12786,7 @@
       <c r="I19" s="174"/>
       <c r="J19" s="134"/>
     </row>
-    <row r="20" spans="2:10" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B20" s="143" t="s">
         <v>45</v>
       </c>
@@ -12801,13 +12824,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>235</v>
       </c>
@@ -12815,7 +12838,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="124" t="s">
         <v>237</v>
       </c>
@@ -12829,7 +12852,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="124" t="s">
         <v>241</v>
       </c>
@@ -12843,7 +12866,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" s="124" t="s">
         <v>243</v>
       </c>
@@ -12857,7 +12880,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" s="127" t="s">
         <v>245</v>
       </c>
@@ -12871,7 +12894,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" s="125" t="s">
         <v>247</v>
       </c>
@@ -12885,7 +12908,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" s="125" t="s">
         <v>249</v>
       </c>
@@ -12899,7 +12922,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C8" s="124" t="s">
         <v>251</v>
       </c>
@@ -12907,7 +12930,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C9" s="124" t="s">
         <v>252</v>
       </c>
@@ -12915,7 +12938,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C10" s="128" t="s">
         <v>253</v>
       </c>
@@ -12932,19 +12955,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
+    <col min="1" max="1" width="3.3984375" style="81" customWidth="1"/>
     <col min="2" max="2" width="9" style="81"/>
-    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
+    <col min="3" max="4" width="14.69921875" style="81" customWidth="1"/>
     <col min="5" max="5" width="43" style="81" customWidth="1"/>
-    <col min="6" max="6" width="62.125" style="81" customWidth="1"/>
-    <col min="7" max="7" width="61.875" style="81" customWidth="1"/>
-    <col min="8" max="14" width="62.125" style="81" customWidth="1"/>
+    <col min="6" max="6" width="62.09765625" style="81" customWidth="1"/>
+    <col min="7" max="7" width="61.8984375" style="81" customWidth="1"/>
+    <col min="8" max="14" width="62.09765625" style="81" customWidth="1"/>
     <col min="15" max="16384" width="9" style="81"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="108" t="s">
         <v>148</v>
       </c>
@@ -12955,7 +12978,7 @@
       <c r="D1" s="109"/>
       <c r="E1" s="107"/>
     </row>
-    <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B2" s="191" t="s">
         <v>2</v>
       </c>
@@ -12984,7 +13007,7 @@
       <c r="M2" s="189"/>
       <c r="N2" s="190"/>
     </row>
-    <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="192"/>
       <c r="C3" s="196"/>
       <c r="D3" s="196"/>
@@ -13017,7 +13040,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="108" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="124.8" x14ac:dyDescent="0.4">
       <c r="B4" s="82" t="s">
         <v>117</v>
       </c>
@@ -13052,7 +13075,7 @@
       <c r="M4" s="105"/>
       <c r="N4" s="92"/>
     </row>
-    <row r="5" spans="1:14" ht="108" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="124.8" x14ac:dyDescent="0.4">
       <c r="B5" s="83" t="s">
         <v>123</v>
       </c>
@@ -13087,7 +13110,7 @@
       <c r="M5" s="105"/>
       <c r="N5" s="93"/>
     </row>
-    <row r="6" spans="1:14" ht="108" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="124.8" x14ac:dyDescent="0.4">
       <c r="B6" s="83" t="s">
         <v>124</v>
       </c>
@@ -13122,7 +13145,7 @@
       <c r="M6" s="105"/>
       <c r="N6" s="93"/>
     </row>
-    <row r="7" spans="1:14" ht="108" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="124.8" x14ac:dyDescent="0.4">
       <c r="B7" s="83" t="s">
         <v>125</v>
       </c>
@@ -13157,7 +13180,7 @@
       <c r="M7" s="105"/>
       <c r="N7" s="93"/>
     </row>
-    <row r="8" spans="1:14" ht="108" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="124.8" x14ac:dyDescent="0.4">
       <c r="B8" s="84" t="s">
         <v>3</v>
       </c>
@@ -13192,7 +13215,7 @@
       <c r="M8" s="105"/>
       <c r="N8" s="93"/>
     </row>
-    <row r="9" spans="1:14" ht="175.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="202.8" x14ac:dyDescent="0.4">
       <c r="B9" s="84" t="s">
         <v>45</v>
       </c>
@@ -13227,7 +13250,7 @@
       <c r="M9" s="105"/>
       <c r="N9" s="93"/>
     </row>
-    <row r="10" spans="1:14" ht="121.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="140.4" x14ac:dyDescent="0.4">
       <c r="B10" s="84" t="s">
         <v>55</v>
       </c>
@@ -13262,7 +13285,7 @@
       <c r="M10" s="105"/>
       <c r="N10" s="93"/>
     </row>
-    <row r="11" spans="1:14" ht="108" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="124.8" x14ac:dyDescent="0.4">
       <c r="B11" s="83" t="s">
         <v>62</v>
       </c>
@@ -13297,7 +13320,7 @@
       <c r="M11" s="105"/>
       <c r="N11" s="93"/>
     </row>
-    <row r="12" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="84" t="s">
         <v>73</v>
       </c>
@@ -13332,7 +13355,7 @@
       <c r="M12" s="105"/>
       <c r="N12" s="93"/>
     </row>
-    <row r="13" spans="1:14" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="347.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="84" t="s">
         <v>118</v>
       </c>
@@ -13367,7 +13390,7 @@
       <c r="M13" s="105"/>
       <c r="N13" s="93"/>
     </row>
-    <row r="14" spans="1:14" ht="175.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="202.8" x14ac:dyDescent="0.4">
       <c r="B14" s="85" t="s">
         <v>181</v>
       </c>
@@ -13396,7 +13419,7 @@
       <c r="M14" s="105"/>
       <c r="N14" s="93"/>
     </row>
-    <row r="15" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="85" t="s">
         <v>75</v>
       </c>
@@ -13429,7 +13452,7 @@
       <c r="M15" s="105"/>
       <c r="N15" s="93"/>
     </row>
-    <row r="16" spans="1:14" ht="121.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="140.4" x14ac:dyDescent="0.4">
       <c r="B16" s="84" t="s">
         <v>85</v>
       </c>
@@ -13462,7 +13485,7 @@
       <c r="M16" s="105"/>
       <c r="N16" s="93"/>
     </row>
-    <row r="17" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="86" t="s">
         <v>141</v>
       </c>
@@ -13495,7 +13518,7 @@
       <c r="M17" s="89"/>
       <c r="N17" s="93"/>
     </row>
-    <row r="18" spans="2:14" ht="162" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:14" ht="187.2" x14ac:dyDescent="0.4">
       <c r="B18" s="86" t="s">
         <v>106</v>
       </c>
@@ -13530,7 +13553,7 @@
       <c r="M18" s="105"/>
       <c r="N18" s="93"/>
     </row>
-    <row r="19" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="85" t="s">
         <v>109</v>
       </c>
@@ -13565,7 +13588,7 @@
       <c r="M19" s="105"/>
       <c r="N19" s="93"/>
     </row>
-    <row r="20" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="85" t="s">
         <v>168</v>
       </c>
@@ -13600,7 +13623,7 @@
       <c r="M20" s="105"/>
       <c r="N20" s="112"/>
     </row>
-    <row r="21" spans="2:14" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:14" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B21" s="87" t="s">
         <v>108</v>
       </c>
@@ -13635,7 +13658,7 @@
       <c r="M21" s="120"/>
       <c r="N21" s="95"/>
     </row>
-    <row r="22" spans="2:14" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="2:14" ht="16.2" thickTop="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="K2:N2"/>
@@ -13658,15 +13681,15 @@
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>5</xdr:col>
-                <xdr:colOff>2733675</xdr:colOff>
+                <xdr:colOff>2735580</xdr:colOff>
                 <xdr:row>17</xdr:row>
-                <xdr:rowOff>104775</xdr:rowOff>
+                <xdr:rowOff>106680</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>5</xdr:col>
                 <xdr:colOff>3505200</xdr:colOff>
                 <xdr:row>17</xdr:row>
-                <xdr:rowOff>504825</xdr:rowOff>
+                <xdr:rowOff>502920</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -13683,7 +13706,7 @@
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>5</xdr:col>
-                <xdr:colOff>3286125</xdr:colOff>
+                <xdr:colOff>3284220</xdr:colOff>
                 <xdr:row>12</xdr:row>
                 <xdr:rowOff>342900</xdr:rowOff>
               </from>
@@ -13708,18 +13731,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
+    <col min="1" max="1" width="3.3984375" style="81" customWidth="1"/>
     <col min="2" max="2" width="9" style="81"/>
-    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
+    <col min="3" max="4" width="14.69921875" style="81" customWidth="1"/>
     <col min="5" max="5" width="43" style="81" customWidth="1"/>
-    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
-    <col min="7" max="9" width="62.125" style="81" customWidth="1"/>
+    <col min="6" max="6" width="61.8984375" style="81" customWidth="1"/>
+    <col min="7" max="9" width="62.09765625" style="81" customWidth="1"/>
     <col min="10" max="16384" width="9" style="81"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="108" t="s">
         <v>0</v>
       </c>
@@ -13730,7 +13753,7 @@
       <c r="D1" s="109"/>
       <c r="E1" s="107"/>
     </row>
-    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B2" s="191" t="s">
         <v>2</v>
       </c>
@@ -13750,7 +13773,7 @@
       <c r="H2" s="189"/>
       <c r="I2" s="190"/>
     </row>
-    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="192"/>
       <c r="C3" s="196"/>
       <c r="D3" s="196"/>
@@ -13768,7 +13791,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="82" t="s">
         <v>117</v>
       </c>
@@ -13786,7 +13809,7 @@
       <c r="H4" s="88"/>
       <c r="I4" s="92"/>
     </row>
-    <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="83" t="s">
         <v>123</v>
       </c>
@@ -13804,7 +13827,7 @@
       <c r="H5" s="89"/>
       <c r="I5" s="93"/>
     </row>
-    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="83" t="s">
         <v>124</v>
       </c>
@@ -13822,7 +13845,7 @@
       <c r="H6" s="89"/>
       <c r="I6" s="93"/>
     </row>
-    <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="83" t="s">
         <v>125</v>
       </c>
@@ -13840,7 +13863,7 @@
       <c r="H7" s="89"/>
       <c r="I7" s="93"/>
     </row>
-    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="84" t="s">
         <v>3</v>
       </c>
@@ -13858,7 +13881,7 @@
       <c r="H8" s="89"/>
       <c r="I8" s="93"/>
     </row>
-    <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="31.2" x14ac:dyDescent="0.4">
       <c r="B9" s="84" t="s">
         <v>45</v>
       </c>
@@ -13876,7 +13899,7 @@
       <c r="H9" s="89"/>
       <c r="I9" s="93"/>
     </row>
-    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="84" t="s">
         <v>55</v>
       </c>
@@ -13894,7 +13917,7 @@
       <c r="H10" s="89"/>
       <c r="I10" s="93"/>
     </row>
-    <row r="11" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="46.8" x14ac:dyDescent="0.4">
       <c r="B11" s="83" t="s">
         <v>62</v>
       </c>
@@ -13912,7 +13935,7 @@
       <c r="H11" s="89"/>
       <c r="I11" s="93"/>
     </row>
-    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="84" t="s">
         <v>73</v>
       </c>
@@ -13930,7 +13953,7 @@
       <c r="H12" s="89"/>
       <c r="I12" s="93"/>
     </row>
-    <row r="13" spans="1:9" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="347.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="84" t="s">
         <v>118</v>
       </c>
@@ -13948,7 +13971,7 @@
       <c r="H13" s="89"/>
       <c r="I13" s="93"/>
     </row>
-    <row r="14" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="409.6" x14ac:dyDescent="0.4">
       <c r="B14" s="85" t="s">
         <v>181</v>
       </c>
@@ -13966,7 +13989,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="85" t="s">
         <v>75</v>
       </c>
@@ -13984,7 +14007,7 @@
       <c r="H15" s="89"/>
       <c r="I15" s="93"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B16" s="84" t="s">
         <v>85</v>
       </c>
@@ -14002,7 +14025,7 @@
       <c r="H16" s="89"/>
       <c r="I16" s="93"/>
     </row>
-    <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="86" t="s">
         <v>141</v>
       </c>
@@ -14020,7 +14043,7 @@
       <c r="H17" s="89"/>
       <c r="I17" s="93"/>
     </row>
-    <row r="18" spans="2:9" ht="27" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" ht="31.2" x14ac:dyDescent="0.4">
       <c r="B18" s="86" t="s">
         <v>106</v>
       </c>
@@ -14038,7 +14061,7 @@
       <c r="H18" s="89"/>
       <c r="I18" s="93"/>
     </row>
-    <row r="19" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="85" t="s">
         <v>109</v>
       </c>
@@ -14056,7 +14079,7 @@
       <c r="H19" s="89"/>
       <c r="I19" s="93"/>
     </row>
-    <row r="20" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="85" t="s">
         <v>167</v>
       </c>
@@ -14074,7 +14097,7 @@
       <c r="H20" s="111"/>
       <c r="I20" s="112"/>
     </row>
-    <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B21" s="87" t="s">
         <v>108</v>
       </c>
@@ -14092,7 +14115,7 @@
       <c r="H21" s="94"/>
       <c r="I21" s="95"/>
     </row>
-    <row r="22" spans="2:9" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="2:9" ht="16.2" thickTop="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:B3"/>
@@ -14109,18 +14132,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
+    <col min="1" max="1" width="3.3984375" style="81" customWidth="1"/>
     <col min="2" max="2" width="9" style="81"/>
-    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
+    <col min="3" max="4" width="14.69921875" style="81" customWidth="1"/>
     <col min="5" max="5" width="43" style="81" customWidth="1"/>
-    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
-    <col min="7" max="9" width="62.125" style="81" customWidth="1"/>
+    <col min="6" max="6" width="61.8984375" style="81" customWidth="1"/>
+    <col min="7" max="9" width="62.09765625" style="81" customWidth="1"/>
     <col min="10" max="16384" width="9" style="81"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="108" t="s">
         <v>0</v>
       </c>
@@ -14131,7 +14154,7 @@
       <c r="D1" s="109"/>
       <c r="E1" s="107"/>
     </row>
-    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B2" s="191" t="s">
         <v>2</v>
       </c>
@@ -14151,7 +14174,7 @@
       <c r="H2" s="189"/>
       <c r="I2" s="190"/>
     </row>
-    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="192"/>
       <c r="C3" s="196"/>
       <c r="D3" s="196"/>
@@ -14169,7 +14192,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="82" t="s">
         <v>117</v>
       </c>
@@ -14187,7 +14210,7 @@
       <c r="H4" s="88"/>
       <c r="I4" s="92"/>
     </row>
-    <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="83" t="s">
         <v>123</v>
       </c>
@@ -14205,7 +14228,7 @@
       <c r="H5" s="89"/>
       <c r="I5" s="93"/>
     </row>
-    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="83" t="s">
         <v>124</v>
       </c>
@@ -14223,7 +14246,7 @@
       <c r="H6" s="89"/>
       <c r="I6" s="93"/>
     </row>
-    <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="83" t="s">
         <v>125</v>
       </c>
@@ -14241,7 +14264,7 @@
       <c r="H7" s="89"/>
       <c r="I7" s="93"/>
     </row>
-    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="84" t="s">
         <v>3</v>
       </c>
@@ -14259,7 +14282,7 @@
       <c r="H8" s="89"/>
       <c r="I8" s="93"/>
     </row>
-    <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="31.2" x14ac:dyDescent="0.4">
       <c r="B9" s="84" t="s">
         <v>45</v>
       </c>
@@ -14277,7 +14300,7 @@
       <c r="H9" s="89"/>
       <c r="I9" s="93"/>
     </row>
-    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="84" t="s">
         <v>55</v>
       </c>
@@ -14295,7 +14318,7 @@
       <c r="H10" s="89"/>
       <c r="I10" s="93"/>
     </row>
-    <row r="11" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="46.8" x14ac:dyDescent="0.4">
       <c r="B11" s="83" t="s">
         <v>62</v>
       </c>
@@ -14313,7 +14336,7 @@
       <c r="H11" s="89"/>
       <c r="I11" s="93"/>
     </row>
-    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="84" t="s">
         <v>73</v>
       </c>
@@ -14331,7 +14354,7 @@
       <c r="H12" s="89"/>
       <c r="I12" s="93"/>
     </row>
-    <row r="13" spans="1:9" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="347.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="84" t="s">
         <v>118</v>
       </c>
@@ -14349,7 +14372,7 @@
       <c r="H13" s="89"/>
       <c r="I13" s="93"/>
     </row>
-    <row r="14" spans="1:9" ht="337.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="390" x14ac:dyDescent="0.4">
       <c r="B14" s="85" t="s">
         <v>181</v>
       </c>
@@ -14373,7 +14396,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="85" t="s">
         <v>75</v>
       </c>
@@ -14391,7 +14414,7 @@
       <c r="H15" s="89"/>
       <c r="I15" s="93"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B16" s="84" t="s">
         <v>85</v>
       </c>
@@ -14409,7 +14432,7 @@
       <c r="H16" s="89"/>
       <c r="I16" s="93"/>
     </row>
-    <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="86" t="s">
         <v>141</v>
       </c>
@@ -14427,7 +14450,7 @@
       <c r="H17" s="89"/>
       <c r="I17" s="93"/>
     </row>
-    <row r="18" spans="2:9" ht="27" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" ht="31.2" x14ac:dyDescent="0.4">
       <c r="B18" s="86" t="s">
         <v>106</v>
       </c>
@@ -14445,7 +14468,7 @@
       <c r="H18" s="89"/>
       <c r="I18" s="93"/>
     </row>
-    <row r="19" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="85" t="s">
         <v>109</v>
       </c>
@@ -14463,7 +14486,7 @@
       <c r="H19" s="89"/>
       <c r="I19" s="93"/>
     </row>
-    <row r="20" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="85" t="s">
         <v>167</v>
       </c>
@@ -14481,7 +14504,7 @@
       <c r="H20" s="111"/>
       <c r="I20" s="112"/>
     </row>
-    <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B21" s="87" t="s">
         <v>108</v>
       </c>
@@ -14499,7 +14522,7 @@
       <c r="H21" s="94"/>
       <c r="I21" s="95"/>
     </row>
-    <row r="22" spans="2:9" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="2:9" ht="16.2" thickTop="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:B3"/>
@@ -14516,18 +14539,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
+    <col min="1" max="1" width="3.3984375" style="81" customWidth="1"/>
     <col min="2" max="2" width="9" style="81"/>
-    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
+    <col min="3" max="4" width="14.69921875" style="81" customWidth="1"/>
     <col min="5" max="5" width="43" style="81" customWidth="1"/>
-    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
-    <col min="7" max="9" width="62.125" style="81" customWidth="1"/>
+    <col min="6" max="6" width="61.8984375" style="81" customWidth="1"/>
+    <col min="7" max="9" width="62.09765625" style="81" customWidth="1"/>
     <col min="10" max="16384" width="9" style="81"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="108" t="s">
         <v>0</v>
       </c>
@@ -14538,7 +14561,7 @@
       <c r="D1" s="109"/>
       <c r="E1" s="107"/>
     </row>
-    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B2" s="191" t="s">
         <v>2</v>
       </c>
@@ -14558,7 +14581,7 @@
       <c r="H2" s="189"/>
       <c r="I2" s="190"/>
     </row>
-    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="192"/>
       <c r="C3" s="196"/>
       <c r="D3" s="196"/>
@@ -14576,7 +14599,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="151" t="s">
         <v>108</v>
       </c>
@@ -14594,7 +14617,7 @@
       <c r="H4" s="88"/>
       <c r="I4" s="92"/>
     </row>
-    <row r="5" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="78" x14ac:dyDescent="0.4">
       <c r="B5" s="154" t="s">
         <v>181</v>
       </c>
@@ -14616,7 +14639,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="152" t="s">
         <v>275</v>
       </c>
@@ -14636,7 +14659,7 @@
       </c>
       <c r="I6" s="156"/>
     </row>
-    <row r="7" spans="1:9" ht="93" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="93" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="152" t="s">
         <v>75</v>
       </c>
@@ -14656,7 +14679,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="87.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="87.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="152" t="s">
         <v>109</v>
       </c>
@@ -14676,7 +14699,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="153" t="s">
         <v>117</v>
       </c>
@@ -14694,7 +14717,7 @@
       <c r="H9" s="138"/>
       <c r="I9" s="93"/>
     </row>
-    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="153" t="s">
         <v>123</v>
       </c>
@@ -14712,7 +14735,7 @@
       <c r="H10" s="89"/>
       <c r="I10" s="93"/>
     </row>
-    <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="153" t="s">
         <v>124</v>
       </c>
@@ -14730,7 +14753,7 @@
       <c r="H11" s="89"/>
       <c r="I11" s="93"/>
     </row>
-    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="153" t="s">
         <v>125</v>
       </c>
@@ -14748,7 +14771,7 @@
       <c r="H12" s="138"/>
       <c r="I12" s="93"/>
     </row>
-    <row r="13" spans="1:9" ht="222" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="222" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="132" t="s">
         <v>62</v>
       </c>
@@ -14770,7 +14793,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="78" x14ac:dyDescent="0.4">
       <c r="B14" s="131" t="s">
         <v>73</v>
       </c>
@@ -14792,7 +14815,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="78" x14ac:dyDescent="0.4">
       <c r="B15" s="131" t="s">
         <v>55</v>
       </c>
@@ -14816,7 +14839,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="228.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="228.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="131" t="s">
         <v>85</v>
       </c>
@@ -14838,7 +14861,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="130" t="s">
         <v>167</v>
       </c>
@@ -14862,7 +14885,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="131" t="s">
         <v>141</v>
       </c>
@@ -14880,7 +14903,7 @@
       <c r="H18" s="133"/>
       <c r="I18" s="136"/>
     </row>
-    <row r="19" spans="2:9" ht="108" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" ht="124.8" x14ac:dyDescent="0.4">
       <c r="B19" s="150" t="s">
         <v>3</v>
       </c>
@@ -14904,7 +14927,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B20" s="143" t="s">
         <v>45</v>
       </c>
@@ -14941,18 +14964,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
+    <col min="1" max="1" width="3.3984375" style="81" customWidth="1"/>
     <col min="2" max="2" width="9" style="81"/>
-    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
+    <col min="3" max="4" width="14.69921875" style="81" customWidth="1"/>
     <col min="5" max="5" width="43" style="81" customWidth="1"/>
-    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
-    <col min="7" max="9" width="62.125" style="81" customWidth="1"/>
+    <col min="6" max="6" width="61.8984375" style="81" customWidth="1"/>
+    <col min="7" max="9" width="62.09765625" style="81" customWidth="1"/>
     <col min="10" max="16384" width="9" style="81"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="108" t="s">
         <v>0</v>
       </c>
@@ -14963,7 +14986,7 @@
       <c r="D1" s="109"/>
       <c r="E1" s="107"/>
     </row>
-    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B2" s="191" t="s">
         <v>2</v>
       </c>
@@ -14983,7 +15006,7 @@
       <c r="H2" s="189"/>
       <c r="I2" s="190"/>
     </row>
-    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="192"/>
       <c r="C3" s="196"/>
       <c r="D3" s="196"/>
@@ -15001,7 +15024,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="151" t="s">
         <v>108</v>
       </c>
@@ -15019,7 +15042,7 @@
       <c r="H4" s="88"/>
       <c r="I4" s="92"/>
     </row>
-    <row r="5" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="78" x14ac:dyDescent="0.4">
       <c r="B5" s="154" t="s">
         <v>181</v>
       </c>
@@ -15041,7 +15064,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="152" t="s">
         <v>275</v>
       </c>
@@ -15059,7 +15082,7 @@
       <c r="H6" s="123"/>
       <c r="I6" s="135"/>
     </row>
-    <row r="7" spans="1:9" ht="138" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="138" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="152" t="s">
         <v>75</v>
       </c>
@@ -15081,7 +15104,7 @@
       <c r="H7" s="89"/>
       <c r="I7" s="93"/>
     </row>
-    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="152" t="s">
         <v>109</v>
       </c>
@@ -15099,7 +15122,7 @@
       <c r="H8" s="89"/>
       <c r="I8" s="93"/>
     </row>
-    <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="153" t="s">
         <v>117</v>
       </c>
@@ -15117,7 +15140,7 @@
       <c r="H9" s="138"/>
       <c r="I9" s="93"/>
     </row>
-    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="153" t="s">
         <v>123</v>
       </c>
@@ -15135,7 +15158,7 @@
       <c r="H10" s="89"/>
       <c r="I10" s="93"/>
     </row>
-    <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="153" t="s">
         <v>124</v>
       </c>
@@ -15153,7 +15176,7 @@
       <c r="H11" s="89"/>
       <c r="I11" s="93"/>
     </row>
-    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="153" t="s">
         <v>125</v>
       </c>
@@ -15171,7 +15194,7 @@
       <c r="H12" s="138"/>
       <c r="I12" s="93"/>
     </row>
-    <row r="13" spans="1:9" ht="283.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="343.2" x14ac:dyDescent="0.4">
       <c r="B13" s="132" t="s">
         <v>62</v>
       </c>
@@ -15197,7 +15220,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="409.6" x14ac:dyDescent="0.4">
       <c r="B14" s="131" t="s">
         <v>73</v>
       </c>
@@ -15223,7 +15246,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="175.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="202.8" x14ac:dyDescent="0.4">
       <c r="B15" s="131" t="s">
         <v>55</v>
       </c>
@@ -15249,7 +15272,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="409.6" x14ac:dyDescent="0.4">
       <c r="B16" s="131" t="s">
         <v>85</v>
       </c>
@@ -15275,7 +15298,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="162" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="187.2" x14ac:dyDescent="0.4">
       <c r="B17" s="130" t="s">
         <v>167</v>
       </c>
@@ -15301,7 +15324,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B18" s="131" t="s">
         <v>141</v>
       </c>
@@ -15317,7 +15340,7 @@
       <c r="H18" s="133"/>
       <c r="I18" s="136"/>
     </row>
-    <row r="19" spans="2:9" ht="54" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" ht="62.4" x14ac:dyDescent="0.4">
       <c r="B19" s="150" t="s">
         <v>3</v>
       </c>
@@ -15343,7 +15366,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B20" s="143" t="s">
         <v>45</v>
       </c>
@@ -15381,18 +15404,18 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
+    <col min="1" max="1" width="3.3984375" style="81" customWidth="1"/>
     <col min="2" max="2" width="9" style="81"/>
-    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
+    <col min="3" max="4" width="14.69921875" style="81" customWidth="1"/>
     <col min="5" max="5" width="43" style="81" customWidth="1"/>
-    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
-    <col min="7" max="10" width="62.125" style="81" customWidth="1"/>
+    <col min="6" max="6" width="61.8984375" style="81" customWidth="1"/>
+    <col min="7" max="10" width="62.09765625" style="81" customWidth="1"/>
     <col min="11" max="16384" width="9" style="81"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="108" t="s">
         <v>0</v>
       </c>
@@ -15403,7 +15426,7 @@
       <c r="D1" s="109"/>
       <c r="E1" s="107"/>
     </row>
-    <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B2" s="191" t="s">
         <v>2</v>
       </c>
@@ -15424,7 +15447,7 @@
       <c r="I2" s="197"/>
       <c r="J2" s="190"/>
     </row>
-    <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="192"/>
       <c r="C3" s="196"/>
       <c r="D3" s="196"/>
@@ -15445,7 +15468,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="151" t="s">
         <v>108</v>
       </c>
@@ -15464,7 +15487,7 @@
       <c r="I4" s="171"/>
       <c r="J4" s="92"/>
     </row>
-    <row r="5" spans="1:10" ht="54" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="62.4" x14ac:dyDescent="0.4">
       <c r="B5" s="154" t="s">
         <v>181</v>
       </c>
@@ -15487,7 +15510,7 @@
       <c r="I5" s="172"/>
       <c r="J5" s="135"/>
     </row>
-    <row r="6" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="152" t="s">
         <v>118</v>
       </c>
@@ -15506,7 +15529,7 @@
       <c r="I6" s="172"/>
       <c r="J6" s="135"/>
     </row>
-    <row r="7" spans="1:10" ht="138" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="138" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="152" t="s">
         <v>75</v>
       </c>
@@ -15525,7 +15548,7 @@
       <c r="I7" s="173"/>
       <c r="J7" s="93"/>
     </row>
-    <row r="8" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="152" t="s">
         <v>109</v>
       </c>
@@ -15544,7 +15567,7 @@
       <c r="I8" s="173"/>
       <c r="J8" s="93"/>
     </row>
-    <row r="9" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="153" t="s">
         <v>117</v>
       </c>
@@ -15563,7 +15586,7 @@
       <c r="I9" s="89"/>
       <c r="J9" s="93"/>
     </row>
-    <row r="10" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="153" t="s">
         <v>123</v>
       </c>
@@ -15582,7 +15605,7 @@
       <c r="I10" s="173"/>
       <c r="J10" s="93"/>
     </row>
-    <row r="11" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="153" t="s">
         <v>124</v>
       </c>
@@ -15601,7 +15624,7 @@
       <c r="I11" s="173"/>
       <c r="J11" s="93"/>
     </row>
-    <row r="12" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="153" t="s">
         <v>125</v>
       </c>
@@ -15620,7 +15643,7 @@
       <c r="I12" s="89"/>
       <c r="J12" s="93"/>
     </row>
-    <row r="13" spans="1:10" ht="364.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="409.6" x14ac:dyDescent="0.4">
       <c r="B13" s="132" t="s">
         <v>62</v>
       </c>
@@ -15647,7 +15670,7 @@
       </c>
       <c r="J13" s="122"/>
     </row>
-    <row r="14" spans="1:10" ht="310.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="358.8" x14ac:dyDescent="0.4">
       <c r="B14" s="131" t="s">
         <v>73</v>
       </c>
@@ -15674,7 +15697,7 @@
       </c>
       <c r="J14" s="122"/>
     </row>
-    <row r="15" spans="1:10" ht="243" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="280.8" x14ac:dyDescent="0.4">
       <c r="B15" s="131" t="s">
         <v>55</v>
       </c>
@@ -15701,7 +15724,7 @@
       </c>
       <c r="J15" s="122"/>
     </row>
-    <row r="16" spans="1:10" ht="378" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="409.6" x14ac:dyDescent="0.4">
       <c r="B16" s="131" t="s">
         <v>85</v>
       </c>
@@ -15728,7 +15751,7 @@
       </c>
       <c r="J16" s="122"/>
     </row>
-    <row r="17" spans="2:10" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" ht="46.8" x14ac:dyDescent="0.4">
       <c r="B17" s="130" t="s">
         <v>167</v>
       </c>
@@ -15755,7 +15778,7 @@
       </c>
       <c r="J17" s="168"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B18" s="131" t="s">
         <v>141</v>
       </c>
@@ -15772,7 +15795,7 @@
       <c r="I18" s="129"/>
       <c r="J18" s="136"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B19" s="150" t="s">
         <v>3</v>
       </c>
@@ -15793,7 +15816,7 @@
       <c r="I19" s="174"/>
       <c r="J19" s="134"/>
     </row>
-    <row r="20" spans="2:10" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B20" s="143" t="s">
         <v>45</v>
       </c>
@@ -15831,18 +15854,18 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
+    <col min="1" max="1" width="3.3984375" style="81" customWidth="1"/>
     <col min="2" max="2" width="9" style="81"/>
-    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
+    <col min="3" max="4" width="14.69921875" style="81" customWidth="1"/>
     <col min="5" max="5" width="43" style="81" customWidth="1"/>
-    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
-    <col min="7" max="9" width="62.125" style="81" customWidth="1"/>
+    <col min="6" max="6" width="61.8984375" style="81" customWidth="1"/>
+    <col min="7" max="9" width="62.09765625" style="81" customWidth="1"/>
     <col min="10" max="16384" width="9" style="81"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="108" t="s">
         <v>0</v>
       </c>
@@ -15853,7 +15876,7 @@
       <c r="D1" s="109"/>
       <c r="E1" s="107"/>
     </row>
-    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B2" s="191" t="s">
         <v>2</v>
       </c>
@@ -15873,7 +15896,7 @@
       <c r="H2" s="189"/>
       <c r="I2" s="190"/>
     </row>
-    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="192"/>
       <c r="C3" s="196"/>
       <c r="D3" s="196"/>
@@ -15891,7 +15914,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="151" t="s">
         <v>108</v>
       </c>
@@ -15909,7 +15932,7 @@
       <c r="H4" s="88"/>
       <c r="I4" s="92"/>
     </row>
-    <row r="5" spans="1:9" ht="54" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="62.4" x14ac:dyDescent="0.4">
       <c r="B5" s="154" t="s">
         <v>181</v>
       </c>
@@ -15929,7 +15952,7 @@
       <c r="H5" s="123"/>
       <c r="I5" s="135"/>
     </row>
-    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="152" t="s">
         <v>118</v>
       </c>
@@ -15947,7 +15970,7 @@
       <c r="H6" s="123"/>
       <c r="I6" s="135"/>
     </row>
-    <row r="7" spans="1:9" ht="162" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="187.2" x14ac:dyDescent="0.4">
       <c r="B7" s="152" t="s">
         <v>75</v>
       </c>
@@ -15967,7 +15990,7 @@
       <c r="H7" s="89"/>
       <c r="I7" s="93"/>
     </row>
-    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="152" t="s">
         <v>109</v>
       </c>
@@ -15985,7 +16008,7 @@
       <c r="H8" s="89"/>
       <c r="I8" s="93"/>
     </row>
-    <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="153" t="s">
         <v>117</v>
       </c>
@@ -16003,7 +16026,7 @@
       <c r="H9" s="138"/>
       <c r="I9" s="93"/>
     </row>
-    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="153" t="s">
         <v>123</v>
       </c>
@@ -16021,7 +16044,7 @@
       <c r="H10" s="89"/>
       <c r="I10" s="93"/>
     </row>
-    <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="153" t="s">
         <v>124</v>
       </c>
@@ -16039,7 +16062,7 @@
       <c r="H11" s="89"/>
       <c r="I11" s="93"/>
     </row>
-    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="153" t="s">
         <v>125</v>
       </c>
@@ -16057,7 +16080,7 @@
       <c r="H12" s="138"/>
       <c r="I12" s="93"/>
     </row>
-    <row r="13" spans="1:9" ht="27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="93.6" x14ac:dyDescent="0.4">
       <c r="B13" s="132" t="s">
         <v>62</v>
       </c>
@@ -16071,11 +16094,13 @@
         <v>260</v>
       </c>
       <c r="F13" s="105"/>
-      <c r="G13" s="157"/>
+      <c r="G13" s="157" t="s">
+        <v>391</v>
+      </c>
       <c r="H13" s="105"/>
       <c r="I13" s="122"/>
     </row>
-    <row r="14" spans="1:9" ht="148.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="171.6" x14ac:dyDescent="0.4">
       <c r="B14" s="131" t="s">
         <v>73</v>
       </c>
@@ -16089,13 +16114,13 @@
         <v>261</v>
       </c>
       <c r="F14" s="105" t="s">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="G14" s="157"/>
       <c r="H14" s="105"/>
       <c r="I14" s="122"/>
     </row>
-    <row r="15" spans="1:9" ht="108" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="124.8" x14ac:dyDescent="0.4">
       <c r="B15" s="131" t="s">
         <v>55</v>
       </c>
@@ -16115,7 +16140,7 @@
       <c r="H15" s="157"/>
       <c r="I15" s="176"/>
     </row>
-    <row r="16" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="409.6" x14ac:dyDescent="0.4">
       <c r="B16" s="131" t="s">
         <v>85</v>
       </c>
@@ -16135,7 +16160,7 @@
       <c r="H16" s="157"/>
       <c r="I16" s="176"/>
     </row>
-    <row r="17" spans="2:9" ht="108" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="124.8" x14ac:dyDescent="0.4">
       <c r="B17" s="130" t="s">
         <v>167</v>
       </c>
@@ -16155,7 +16180,7 @@
       <c r="H17" s="169"/>
       <c r="I17" s="177"/>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B18" s="131" t="s">
         <v>141</v>
       </c>
@@ -16171,7 +16196,7 @@
       <c r="H18" s="133"/>
       <c r="I18" s="136"/>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B19" s="150" t="s">
         <v>3</v>
       </c>
@@ -16191,7 +16216,7 @@
       <c r="H19" s="133"/>
       <c r="I19" s="134"/>
     </row>
-    <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B20" s="178" t="s">
         <v>45</v>
       </c>
@@ -16211,7 +16236,7 @@
       <c r="H20" s="180"/>
       <c r="I20" s="95"/>
     </row>
-    <row r="21" spans="2:9" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="2:9" ht="16.2" thickTop="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:B3"/>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17688" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="대일정" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="406">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -7637,42 +7637,6 @@
   </si>
   <si>
     <t>[임제훈 사원]
-1. 실차 점검으로 인한 남양연구소 방문 (01/06)
-  [ 안건 ]
-    - 고객사 및 한온에서 차량 평가 중, Fault 발생으로 인한 실차 점검 요청
-  [ 진행 및 검토 ]
-    - 차량 평가 당시 상황 재현 시도
-    - Fault 발생 원인 및 분석
-  [ 결과 ]
-    - 엔진 열 + PTC 발열로 인한 열 중첩 현상으로 Fault 발생 추정됨
-    - 고객사에서는 과열로 인해 Fault 발생한 것은 정상적인 로직이라고 판단함.
-    - 차주 13일 (화) 혹은 14일 (수)에 챔버 일정 확정 후 테스트 진행
-     : 우리산업 테스트 참석 요청
-2. 기구 변경점 반영 및 S/W 적용 (~01/09)
-  [ 안건 ]
-    - Stone TC 160℃ → 165℃ 변경
-    - 전압 범위 변경
-     : 정격 전압 360V → 351V
-     : 최대 동작 전압 403.2V → 413V
-    - LINEAR MAX 성능 7000W 변경
-    - 제어 사양서, S/W 재배포 요청
-  [ 진행 및 검토 ]
-    - 최종 사양 반영된 샘플 수령 (01/06)
-    - 기구 변경점 S/W 반영
-    - R로직 튜닝
-    - 로직 및 기능 체크리스트 기반 검증 진행
-3. 사이버 보안 기능 품확 활동 (~01/09)
-  [ 안건 ]
-    - 첨부파일 작성
-     : NX5_(제어기명)_공정보안_체크리스트(설계팀,협력사용)
-  [ 진행 및 검토 ]
-    - QV 작성자료 참고
-    - 사이버보안품질연구팀에 보낼 샘플 준비
-     : PCB 2EA, Signal Connector 1EA, E2 Pin Connector 1EA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
 1. 사이버 보안 관련 자료 회신 요청
   [ 요청사항 ]
     - 사이버 보안 QV와 동일한 이력으로 진행 요청 (공조시스템설계팀)
@@ -7686,12 +7650,702 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[임제훈 사원]
+    <t>[김진겸 사원]
 1. 국내 윈터 트립 (01/12 ~ 01/13)
   [ 요청사항 ]
     - 국내 윈터 트립 참석
   [ 진행 및 검토 ]
-    - SVm P1(77호차) PTC 제어</t>
+    - SVm P1(77호차) PTC 제어
+[임제훈 사원]
+1. ISIR 성적서 작성 (~02/12)
+  [ 요청사항 ]
+    - ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24 성적서
+  [ 진행 및 검토 ]
+    - 2월 중순까지 성적서 작성 완료
+    - ES90700-00 (100%)
+    - ES95411-00 (90%)
+    - ES95480-00 (100%)
+    - ES95489-21 (90%)
+    - ES95489-24 (90%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>실차 점검으로 인한 남양연구소 방문 (01/06)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 안건 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>고객사 및 한온에서 차량 평가 중, Fault 발생으로 인한 실차 점검 요청</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 진행 및 검토 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>차량 평가 당시 상황 재현 시도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Fault 발생 원인 및 분석</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 결과 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>엔진 열 + PTC 발열로 인한 열 중첩 현상으로 Fault 발생 추정됨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>고객사에서는 과열로 인해 Fault 발생한 것은 정상적인 로직이라고 판단함.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>차주 13일 (화) 혹은 14일 (수)에 챔버 일정 확정 후 테스트 진행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>우리산업 테스트 참석 요청</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>기구 변경점 반영 및 S/W 적용 (~01/09)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 안건 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Stone TC 160℃ → 165℃ 변경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>전압 범위 변경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>정격 전압 360V → 351V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>최대 동작 전압 403.2V → 413V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LINEAR MAX 성능 7000W 변경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제어 사양서, S/W 재배포 요청</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 진행 및 검토 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>최종 사양 반영된 샘플 수령 (01/06)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>기구 변경점 S/W 반영</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R로직 튜닝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>로직 및 기능 체크리스트 기반 검증 진행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+3. 사이버 보안 기능 품확 활동 (~01/09)
+  [ 안건 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>첨부파일 작성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NX5_(제어기명)_공정보안_체크리스트(설계팀,협력사용)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 진행 및 검토 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>QV 작성자료 참고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - 사이버보안품질연구팀에 보낼 샘플 준비
+     : PCB 2EA, Signal Connector 1EA, E2 Pin Connector 1EA</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- SWE.3 SDDS 후속 작업 (진행률 : 97%)
+[조현진 전임]
+- SWE.1, 2, 3 등록에 맞추어 SWE. 4, 5, 6 ALM 등록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. 최대 난방 평가 성능 미달로 인한 성능 증대 계획
+  [ 요청사항 ]
+    - SP1 적용 S/W 튜닝
+  [ 진행 및 검토 ]
+    - HVAC 미수령
+      : 수령 일자 미정
+    - MX5a 샘플 미수령
+      : 수령 일자 미정
+    - S/W 튜닝 소요 기간 3주 요청
+      : TC 변경건으로 인한 R로직 재튜닝
+      : 전압 범위 변경</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`[임제훈 사원]
+1. FAIL-SAFETY 로직 검증 (01/13)
+  [ 요청사항 ]
+    - 타 차종에서 문제 발생, BJ1 PTC FAIL-SAFETY 검증 및 결과 요청
+  [ 진행 및 검토 ]
+    - FAIL-SAFETY 로직 검증 완료
+     : S/W 문제 없음
+    - 검증 결과 회신 완료
+2. ISIR 성적서 작성 (~02/12)
+  [ 요청사항 ]
+    - ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24 성적서
+  [ 진행 및 검토 ]
+    - 2월 중순까지 성적서 작성 완료
+    - ES90700-00 (100%)
+    - ES95411-00 (90%)
+    - ES95480-00 (100%)
+    - ES95489-21 (90%)
+    - ES95489-24 (90%)
+3. 사이버 보안 관련 자료 회신 요청
+  [ 요청사항 ]
+    - 사이버 보안 QV와 동일한 이력으로 진행 요청 (공조시스템설계팀)
+    - BJ1 ES95489-21 성적서 회신
+    - 사이버보안관련성평가 작성 후 회신
+  [ 진행 및 검토 ]
+    - BJ1 ES95489-21, ESIR 때 성적서 없음
+      : QV 사이버 보안 협의 및 일정 지연으로 BJ1 ESIR때 진행 불가
+      : BJ1 ES95489-21 검증 진행
+    - 사이버보안관련성평가 작성 후 검토 요청</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. NX5e C518 차량 PTC 리워크 (01/12)
+  [ 요청사항 ]
+    - 국내 트립에서 문제 발생
+     : PTC 교체 요청
+  [ 진행 및 검토 ]
+    - Proto 사양 PTC로 교체 완료
+    - 고품으로 나온 PTC 칼로리미터 검증 완료
+     : 차량에서 Core Temp가 내려가지 않던 현상 없음
+     : PTC 단품 정상 상태 및 동작 확인
+2. S/W 설계 변경 (01/13)
+  [ 안건 ]
+    - 변경점 반영된 최종 S/W 설계 변경
+  [ 진행 및 검토 ]
+    - S/W 로직 검증 완료
+     : S/W 문제 없음
+    - 설계변경 완료
+3. NX5e FATC 테스트 진행 (01/15)
+  [ 안건 ]
+    - 열에너지차량시험팀, 한온시스템 1월 15일 (목) FATC 테스트 진행
+  [ 진행 및 검토 ]
+    - 우리산업 참석 예정
+     : 동행자 EV HTR 개발팀 강상용 책임
+    - 외부 환경으로 인해 PTC 영향이 있는지 분석
+     : 엔진 열 영향 확인
+     : HVAC 덕트 구조 확인
+     : HVAC 풍량이 PTC에 영향을 끼치는지 확인
+4. 고객사 사이버 보안 기능 품확 활동 (~01/30)
+  [ 요청사항 ]
+    - 품확 진행 샘플
+  [ 진행 및 검토 ]
+    - 사이버보안품질연구팀에 보낼 샘플 준비
+     : PCB 1EA, Signal Connector 1EA, E2 Pin Connector 1EA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 이슈 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 이슈 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 이슈 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 이슈 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고객사 요청</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 이슈 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. PTC 제어 방향 문의 (~01/16)
+  [ 요청 사항 ]
+    - PTC Target Duty 수신 시 로직 (공조시스템설계팀 한별 책임 연구원)
+  [ 진행 및 검토 ]
+    - 급격한 Target Duty 변화 수신 (예시 80% → 40%)
+    - 급격한 Target Duty OFF 수신 (예시 80% → 0% (OFF))</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -9166,7 +9820,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="198">
+  <cellXfs count="201">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -9760,6 +10414,15 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="81" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -9889,15 +10552,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>5</xdr:col>
-          <xdr:colOff>2735580</xdr:colOff>
+          <xdr:colOff>2733675</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>106680</xdr:rowOff>
+          <xdr:rowOff>104775</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>5</xdr:col>
           <xdr:colOff>3505200</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>502920</xdr:rowOff>
+          <xdr:rowOff>504825</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -9948,7 +10611,7 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>5</xdr:col>
-          <xdr:colOff>3284220</xdr:colOff>
+          <xdr:colOff>3286125</xdr:colOff>
           <xdr:row>12</xdr:row>
           <xdr:rowOff>342900</xdr:rowOff>
         </xdr:from>
@@ -10403,19 +11066,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BL25"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.3984375" customWidth="1"/>
-    <col min="2" max="2" width="18.8984375" customWidth="1"/>
-    <col min="3" max="3" width="28.3984375" customWidth="1"/>
-    <col min="4" max="4" width="30.69921875" customWidth="1"/>
-    <col min="5" max="28" width="8.3984375" hidden="1" customWidth="1"/>
-    <col min="29" max="34" width="8.3984375" customWidth="1"/>
-    <col min="35" max="35" width="10.3984375" customWidth="1"/>
-    <col min="36" max="64" width="8.3984375" customWidth="1"/>
+    <col min="1" max="1" width="4.375" customWidth="1"/>
+    <col min="2" max="2" width="18.875" customWidth="1"/>
+    <col min="3" max="3" width="28.375" customWidth="1"/>
+    <col min="4" max="4" width="30.75" customWidth="1"/>
+    <col min="5" max="28" width="8.375" hidden="1" customWidth="1"/>
+    <col min="29" max="34" width="8.375" customWidth="1"/>
+    <col min="35" max="35" width="10.375" customWidth="1"/>
+    <col min="36" max="64" width="8.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" s="20" customFormat="1" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:64" s="20" customFormat="1" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -10425,7 +11088,7 @@
       <c r="C1" s="21"/>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B2" s="182" t="s">
         <v>2</v>
       </c>
@@ -10506,7 +11169,7 @@
       <c r="BK2" s="186"/>
       <c r="BL2" s="187"/>
     </row>
-    <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="183"/>
       <c r="C3" s="185"/>
       <c r="D3" s="185"/>
@@ -10691,7 +11354,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:64" ht="183" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:64" ht="183" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="63" t="s">
         <v>119</v>
       </c>
@@ -10772,7 +11435,7 @@
       <c r="BK4" s="2"/>
       <c r="BL4" s="5"/>
     </row>
-    <row r="5" spans="1:64" ht="93.6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:64" ht="81" x14ac:dyDescent="0.3">
       <c r="B5" s="28" t="s">
         <v>120</v>
       </c>
@@ -10851,7 +11514,7 @@
       <c r="BK5" s="31"/>
       <c r="BL5" s="10"/>
     </row>
-    <row r="6" spans="1:64" ht="78" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:64" ht="67.5" x14ac:dyDescent="0.3">
       <c r="B6" s="28" t="s">
         <v>121</v>
       </c>
@@ -10934,7 +11597,7 @@
       <c r="BK6" s="31"/>
       <c r="BL6" s="10"/>
     </row>
-    <row r="7" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="28" t="s">
         <v>122</v>
       </c>
@@ -11015,7 +11678,7 @@
       <c r="BK7" s="31"/>
       <c r="BL7" s="10"/>
     </row>
-    <row r="8" spans="1:64" ht="93.6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:64" ht="81" x14ac:dyDescent="0.3">
       <c r="B8" s="28" t="s">
         <v>218</v>
       </c>
@@ -11092,7 +11755,7 @@
       <c r="BK8" s="31"/>
       <c r="BL8" s="10"/>
     </row>
-    <row r="9" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="27" t="s">
         <v>3</v>
       </c>
@@ -11165,7 +11828,7 @@
       <c r="BK9" s="31"/>
       <c r="BL9" s="10"/>
     </row>
-    <row r="10" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="27" t="s">
         <v>45</v>
       </c>
@@ -11242,7 +11905,7 @@
       <c r="BK10" s="31"/>
       <c r="BL10" s="10"/>
     </row>
-    <row r="11" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="28" t="s">
         <v>127</v>
       </c>
@@ -11325,7 +11988,7 @@
       <c r="BK11" s="31"/>
       <c r="BL11" s="10"/>
     </row>
-    <row r="12" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="28" t="s">
         <v>128</v>
       </c>
@@ -11406,7 +12069,7 @@
       <c r="BK12" s="31"/>
       <c r="BL12" s="10"/>
     </row>
-    <row r="13" spans="1:64" ht="228.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:64" ht="228.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="28" t="s">
         <v>62</v>
       </c>
@@ -11495,7 +12158,7 @@
       <c r="BK13" s="31"/>
       <c r="BL13" s="10"/>
     </row>
-    <row r="14" spans="1:64" ht="93.6" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:64" ht="67.5" x14ac:dyDescent="0.3">
       <c r="B14" s="27" t="s">
         <v>73</v>
       </c>
@@ -11584,7 +12247,7 @@
       <c r="BK14" s="31"/>
       <c r="BL14" s="10"/>
     </row>
-    <row r="15" spans="1:64" ht="285.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:64" ht="285.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="27" t="s">
         <v>64</v>
       </c>
@@ -11667,7 +12330,7 @@
       <c r="BK15" s="31"/>
       <c r="BL15" s="10"/>
     </row>
-    <row r="16" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="27" t="s">
         <v>65</v>
       </c>
@@ -11756,7 +12419,7 @@
       <c r="BK16" s="31"/>
       <c r="BL16" s="10"/>
     </row>
-    <row r="17" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="57" t="s">
         <v>385</v>
       </c>
@@ -11847,7 +12510,7 @@
       <c r="BK17" s="71"/>
       <c r="BL17" s="48"/>
     </row>
-    <row r="18" spans="2:64" ht="179.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:64" ht="179.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="27" t="s">
         <v>85</v>
       </c>
@@ -11940,7 +12603,7 @@
       <c r="BK18" s="73"/>
       <c r="BL18" s="70"/>
     </row>
-    <row r="19" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="77" t="s">
         <v>141</v>
       </c>
@@ -12025,7 +12688,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="77" t="s">
         <v>106</v>
       </c>
@@ -12094,7 +12757,7 @@
       <c r="BK20" s="73"/>
       <c r="BL20" s="70"/>
     </row>
-    <row r="21" spans="2:64" ht="218.4" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:64" ht="189" x14ac:dyDescent="0.3">
       <c r="B21" s="57" t="s">
         <v>109</v>
       </c>
@@ -12177,7 +12840,7 @@
       <c r="BK21" s="73"/>
       <c r="BL21" s="70"/>
     </row>
-    <row r="22" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="57" t="s">
         <v>166</v>
       </c>
@@ -12246,7 +12909,7 @@
       <c r="BK22" s="73"/>
       <c r="BL22" s="70"/>
     </row>
-    <row r="23" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="57" t="s">
         <v>326</v>
       </c>
@@ -12327,7 +12990,7 @@
       <c r="BK23" s="73"/>
       <c r="BL23" s="70"/>
     </row>
-    <row r="24" spans="2:64" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:64" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="79" t="s">
         <v>325</v>
       </c>
@@ -12404,7 +13067,7 @@
       <c r="BK24" s="75"/>
       <c r="BL24" s="55"/>
     </row>
-    <row r="25" spans="2:64" ht="18" thickTop="1" x14ac:dyDescent="0.4"/>
+    <row r="25" spans="2:64" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B2:B3"/>
@@ -12426,18 +13089,18 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.3984375" style="81" customWidth="1"/>
+    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
     <col min="2" max="2" width="9" style="81"/>
-    <col min="3" max="4" width="14.69921875" style="81" customWidth="1"/>
+    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
     <col min="5" max="5" width="43" style="81" customWidth="1"/>
-    <col min="6" max="6" width="61.8984375" style="81" customWidth="1"/>
-    <col min="7" max="10" width="62.09765625" style="81" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
+    <col min="7" max="10" width="62.125" style="81" customWidth="1"/>
     <col min="11" max="16384" width="9" style="81"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="108" t="s">
         <v>0</v>
       </c>
@@ -12448,7 +13111,7 @@
       <c r="D1" s="109"/>
       <c r="E1" s="107"/>
     </row>
-    <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B2" s="191" t="s">
         <v>2</v>
       </c>
@@ -12469,7 +13132,7 @@
       <c r="I2" s="197"/>
       <c r="J2" s="190"/>
     </row>
-    <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="192"/>
       <c r="C3" s="196"/>
       <c r="D3" s="196"/>
@@ -12482,7 +13145,7 @@
       <c r="I3" s="170"/>
       <c r="J3" s="98"/>
     </row>
-    <row r="4" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="151" t="s">
         <v>108</v>
       </c>
@@ -12501,7 +13164,7 @@
       <c r="I4" s="171"/>
       <c r="J4" s="92"/>
     </row>
-    <row r="5" spans="1:10" ht="46.8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="40.5" x14ac:dyDescent="0.3">
       <c r="B5" s="154" t="s">
         <v>181</v>
       </c>
@@ -12520,7 +13183,7 @@
       <c r="I5" s="172"/>
       <c r="J5" s="135"/>
     </row>
-    <row r="6" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="152" t="s">
         <v>118</v>
       </c>
@@ -12539,7 +13202,7 @@
       <c r="I6" s="172"/>
       <c r="J6" s="135"/>
     </row>
-    <row r="7" spans="1:10" ht="138" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" ht="138" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="152" t="s">
         <v>75</v>
       </c>
@@ -12558,7 +13221,7 @@
       <c r="I7" s="173"/>
       <c r="J7" s="93"/>
     </row>
-    <row r="8" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="152" t="s">
         <v>109</v>
       </c>
@@ -12577,7 +13240,7 @@
       <c r="I8" s="173"/>
       <c r="J8" s="93"/>
     </row>
-    <row r="9" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="153" t="s">
         <v>117</v>
       </c>
@@ -12596,7 +13259,7 @@
       <c r="I9" s="89"/>
       <c r="J9" s="93"/>
     </row>
-    <row r="10" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="153" t="s">
         <v>123</v>
       </c>
@@ -12615,7 +13278,7 @@
       <c r="I10" s="173"/>
       <c r="J10" s="93"/>
     </row>
-    <row r="11" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="153" t="s">
         <v>124</v>
       </c>
@@ -12634,7 +13297,7 @@
       <c r="I11" s="173"/>
       <c r="J11" s="93"/>
     </row>
-    <row r="12" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="153" t="s">
         <v>125</v>
       </c>
@@ -12653,7 +13316,7 @@
       <c r="I12" s="89"/>
       <c r="J12" s="93"/>
     </row>
-    <row r="13" spans="1:10" ht="31.2" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="B13" s="132" t="s">
         <v>62</v>
       </c>
@@ -12672,7 +13335,7 @@
       <c r="I13" s="105"/>
       <c r="J13" s="122"/>
     </row>
-    <row r="14" spans="1:10" ht="31.2" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="B14" s="131" t="s">
         <v>73</v>
       </c>
@@ -12691,7 +13354,7 @@
       <c r="I14" s="105"/>
       <c r="J14" s="122"/>
     </row>
-    <row r="15" spans="1:10" ht="78" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" ht="67.5" x14ac:dyDescent="0.3">
       <c r="B15" s="131" t="s">
         <v>55</v>
       </c>
@@ -12710,7 +13373,7 @@
       <c r="I15" s="157"/>
       <c r="J15" s="122"/>
     </row>
-    <row r="16" spans="1:10" ht="46.8" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" ht="40.5" x14ac:dyDescent="0.3">
       <c r="B16" s="131" t="s">
         <v>85</v>
       </c>
@@ -12729,7 +13392,7 @@
       <c r="I16" s="157"/>
       <c r="J16" s="122"/>
     </row>
-    <row r="17" spans="2:10" ht="46.8" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:10" ht="40.5" x14ac:dyDescent="0.3">
       <c r="B17" s="130" t="s">
         <v>167</v>
       </c>
@@ -12748,7 +13411,7 @@
       <c r="I17" s="169"/>
       <c r="J17" s="168"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="131" t="s">
         <v>141</v>
       </c>
@@ -12765,7 +13428,7 @@
       <c r="I18" s="129"/>
       <c r="J18" s="136"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="150" t="s">
         <v>3</v>
       </c>
@@ -12786,7 +13449,7 @@
       <c r="I19" s="174"/>
       <c r="J19" s="134"/>
     </row>
-    <row r="20" spans="2:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="143" t="s">
         <v>45</v>
       </c>
@@ -12824,13 +13487,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>235</v>
       </c>
@@ -12838,7 +13501,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="124" t="s">
         <v>237</v>
       </c>
@@ -12852,7 +13515,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="124" t="s">
         <v>241</v>
       </c>
@@ -12866,7 +13529,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="124" t="s">
         <v>243</v>
       </c>
@@ -12880,7 +13543,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="127" t="s">
         <v>245</v>
       </c>
@@ -12894,7 +13557,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="125" t="s">
         <v>247</v>
       </c>
@@ -12908,7 +13571,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="125" t="s">
         <v>249</v>
       </c>
@@ -12922,7 +13585,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C8" s="124" t="s">
         <v>251</v>
       </c>
@@ -12930,7 +13593,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C9" s="124" t="s">
         <v>252</v>
       </c>
@@ -12938,7 +13601,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C10" s="128" t="s">
         <v>253</v>
       </c>
@@ -12955,19 +13618,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.3984375" style="81" customWidth="1"/>
+    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
     <col min="2" max="2" width="9" style="81"/>
-    <col min="3" max="4" width="14.69921875" style="81" customWidth="1"/>
+    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
     <col min="5" max="5" width="43" style="81" customWidth="1"/>
-    <col min="6" max="6" width="62.09765625" style="81" customWidth="1"/>
-    <col min="7" max="7" width="61.8984375" style="81" customWidth="1"/>
-    <col min="8" max="14" width="62.09765625" style="81" customWidth="1"/>
+    <col min="6" max="6" width="62.125" style="81" customWidth="1"/>
+    <col min="7" max="7" width="61.875" style="81" customWidth="1"/>
+    <col min="8" max="14" width="62.125" style="81" customWidth="1"/>
     <col min="15" max="16384" width="9" style="81"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="108" t="s">
         <v>148</v>
       </c>
@@ -12978,7 +13641,7 @@
       <c r="D1" s="109"/>
       <c r="E1" s="107"/>
     </row>
-    <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B2" s="191" t="s">
         <v>2</v>
       </c>
@@ -13007,7 +13670,7 @@
       <c r="M2" s="189"/>
       <c r="N2" s="190"/>
     </row>
-    <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="192"/>
       <c r="C3" s="196"/>
       <c r="D3" s="196"/>
@@ -13040,7 +13703,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="124.8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:14" ht="108" x14ac:dyDescent="0.3">
       <c r="B4" s="82" t="s">
         <v>117</v>
       </c>
@@ -13075,7 +13738,7 @@
       <c r="M4" s="105"/>
       <c r="N4" s="92"/>
     </row>
-    <row r="5" spans="1:14" ht="124.8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:14" ht="108" x14ac:dyDescent="0.3">
       <c r="B5" s="83" t="s">
         <v>123</v>
       </c>
@@ -13110,7 +13773,7 @@
       <c r="M5" s="105"/>
       <c r="N5" s="93"/>
     </row>
-    <row r="6" spans="1:14" ht="124.8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:14" ht="108" x14ac:dyDescent="0.3">
       <c r="B6" s="83" t="s">
         <v>124</v>
       </c>
@@ -13145,7 +13808,7 @@
       <c r="M6" s="105"/>
       <c r="N6" s="93"/>
     </row>
-    <row r="7" spans="1:14" ht="124.8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:14" ht="108" x14ac:dyDescent="0.3">
       <c r="B7" s="83" t="s">
         <v>125</v>
       </c>
@@ -13180,7 +13843,7 @@
       <c r="M7" s="105"/>
       <c r="N7" s="93"/>
     </row>
-    <row r="8" spans="1:14" ht="124.8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:14" ht="108" x14ac:dyDescent="0.3">
       <c r="B8" s="84" t="s">
         <v>3</v>
       </c>
@@ -13215,7 +13878,7 @@
       <c r="M8" s="105"/>
       <c r="N8" s="93"/>
     </row>
-    <row r="9" spans="1:14" ht="202.8" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:14" ht="175.5" x14ac:dyDescent="0.3">
       <c r="B9" s="84" t="s">
         <v>45</v>
       </c>
@@ -13250,7 +13913,7 @@
       <c r="M9" s="105"/>
       <c r="N9" s="93"/>
     </row>
-    <row r="10" spans="1:14" ht="140.4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:14" ht="121.5" x14ac:dyDescent="0.3">
       <c r="B10" s="84" t="s">
         <v>55</v>
       </c>
@@ -13285,7 +13948,7 @@
       <c r="M10" s="105"/>
       <c r="N10" s="93"/>
     </row>
-    <row r="11" spans="1:14" ht="124.8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:14" ht="108" x14ac:dyDescent="0.3">
       <c r="B11" s="83" t="s">
         <v>62</v>
       </c>
@@ -13320,7 +13983,7 @@
       <c r="M11" s="105"/>
       <c r="N11" s="93"/>
     </row>
-    <row r="12" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="84" t="s">
         <v>73</v>
       </c>
@@ -13355,7 +14018,7 @@
       <c r="M12" s="105"/>
       <c r="N12" s="93"/>
     </row>
-    <row r="13" spans="1:14" ht="347.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:14" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="84" t="s">
         <v>118</v>
       </c>
@@ -13390,7 +14053,7 @@
       <c r="M13" s="105"/>
       <c r="N13" s="93"/>
     </row>
-    <row r="14" spans="1:14" ht="202.8" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:14" ht="175.5" x14ac:dyDescent="0.3">
       <c r="B14" s="85" t="s">
         <v>181</v>
       </c>
@@ -13419,7 +14082,7 @@
       <c r="M14" s="105"/>
       <c r="N14" s="93"/>
     </row>
-    <row r="15" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="85" t="s">
         <v>75</v>
       </c>
@@ -13452,7 +14115,7 @@
       <c r="M15" s="105"/>
       <c r="N15" s="93"/>
     </row>
-    <row r="16" spans="1:14" ht="140.4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:14" ht="121.5" x14ac:dyDescent="0.3">
       <c r="B16" s="84" t="s">
         <v>85</v>
       </c>
@@ -13485,7 +14148,7 @@
       <c r="M16" s="105"/>
       <c r="N16" s="93"/>
     </row>
-    <row r="17" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="86" t="s">
         <v>141</v>
       </c>
@@ -13518,7 +14181,7 @@
       <c r="M17" s="89"/>
       <c r="N17" s="93"/>
     </row>
-    <row r="18" spans="2:14" ht="187.2" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:14" ht="162" x14ac:dyDescent="0.3">
       <c r="B18" s="86" t="s">
         <v>106</v>
       </c>
@@ -13553,7 +14216,7 @@
       <c r="M18" s="105"/>
       <c r="N18" s="93"/>
     </row>
-    <row r="19" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="85" t="s">
         <v>109</v>
       </c>
@@ -13588,7 +14251,7 @@
       <c r="M19" s="105"/>
       <c r="N19" s="93"/>
     </row>
-    <row r="20" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="85" t="s">
         <v>168</v>
       </c>
@@ -13623,7 +14286,7 @@
       <c r="M20" s="105"/>
       <c r="N20" s="112"/>
     </row>
-    <row r="21" spans="2:14" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:14" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="87" t="s">
         <v>108</v>
       </c>
@@ -13658,7 +14321,7 @@
       <c r="M21" s="120"/>
       <c r="N21" s="95"/>
     </row>
-    <row r="22" spans="2:14" ht="16.2" thickTop="1" x14ac:dyDescent="0.4"/>
+    <row r="22" spans="2:14" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="K2:N2"/>
@@ -13681,15 +14344,15 @@
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>5</xdr:col>
-                <xdr:colOff>2735580</xdr:colOff>
+                <xdr:colOff>2733675</xdr:colOff>
                 <xdr:row>17</xdr:row>
-                <xdr:rowOff>106680</xdr:rowOff>
+                <xdr:rowOff>104775</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>5</xdr:col>
                 <xdr:colOff>3505200</xdr:colOff>
                 <xdr:row>17</xdr:row>
-                <xdr:rowOff>502920</xdr:rowOff>
+                <xdr:rowOff>504825</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -13706,7 +14369,7 @@
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>5</xdr:col>
-                <xdr:colOff>3284220</xdr:colOff>
+                <xdr:colOff>3286125</xdr:colOff>
                 <xdr:row>12</xdr:row>
                 <xdr:rowOff>342900</xdr:rowOff>
               </from>
@@ -13731,18 +14394,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.3984375" style="81" customWidth="1"/>
+    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
     <col min="2" max="2" width="9" style="81"/>
-    <col min="3" max="4" width="14.69921875" style="81" customWidth="1"/>
+    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
     <col min="5" max="5" width="43" style="81" customWidth="1"/>
-    <col min="6" max="6" width="61.8984375" style="81" customWidth="1"/>
-    <col min="7" max="9" width="62.09765625" style="81" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
+    <col min="7" max="9" width="62.125" style="81" customWidth="1"/>
     <col min="10" max="16384" width="9" style="81"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="108" t="s">
         <v>0</v>
       </c>
@@ -13753,7 +14416,7 @@
       <c r="D1" s="109"/>
       <c r="E1" s="107"/>
     </row>
-    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B2" s="191" t="s">
         <v>2</v>
       </c>
@@ -13773,7 +14436,7 @@
       <c r="H2" s="189"/>
       <c r="I2" s="190"/>
     </row>
-    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="192"/>
       <c r="C3" s="196"/>
       <c r="D3" s="196"/>
@@ -13791,7 +14454,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="82" t="s">
         <v>117</v>
       </c>
@@ -13809,7 +14472,7 @@
       <c r="H4" s="88"/>
       <c r="I4" s="92"/>
     </row>
-    <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="83" t="s">
         <v>123</v>
       </c>
@@ -13827,7 +14490,7 @@
       <c r="H5" s="89"/>
       <c r="I5" s="93"/>
     </row>
-    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="83" t="s">
         <v>124</v>
       </c>
@@ -13845,7 +14508,7 @@
       <c r="H6" s="89"/>
       <c r="I6" s="93"/>
     </row>
-    <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="83" t="s">
         <v>125</v>
       </c>
@@ -13863,7 +14526,7 @@
       <c r="H7" s="89"/>
       <c r="I7" s="93"/>
     </row>
-    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="84" t="s">
         <v>3</v>
       </c>
@@ -13881,7 +14544,7 @@
       <c r="H8" s="89"/>
       <c r="I8" s="93"/>
     </row>
-    <row r="9" spans="1:9" ht="31.2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.3">
       <c r="B9" s="84" t="s">
         <v>45</v>
       </c>
@@ -13899,7 +14562,7 @@
       <c r="H9" s="89"/>
       <c r="I9" s="93"/>
     </row>
-    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="84" t="s">
         <v>55</v>
       </c>
@@ -13917,7 +14580,7 @@
       <c r="H10" s="89"/>
       <c r="I10" s="93"/>
     </row>
-    <row r="11" spans="1:9" ht="46.8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
       <c r="B11" s="83" t="s">
         <v>62</v>
       </c>
@@ -13935,7 +14598,7 @@
       <c r="H11" s="89"/>
       <c r="I11" s="93"/>
     </row>
-    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="84" t="s">
         <v>73</v>
       </c>
@@ -13953,7 +14616,7 @@
       <c r="H12" s="89"/>
       <c r="I12" s="93"/>
     </row>
-    <row r="13" spans="1:9" ht="347.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:9" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="84" t="s">
         <v>118</v>
       </c>
@@ -13971,7 +14634,7 @@
       <c r="H13" s="89"/>
       <c r="I13" s="93"/>
     </row>
-    <row r="14" spans="1:9" ht="409.6" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
       <c r="B14" s="85" t="s">
         <v>181</v>
       </c>
@@ -13989,7 +14652,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="85" t="s">
         <v>75</v>
       </c>
@@ -14007,7 +14670,7 @@
       <c r="H15" s="89"/>
       <c r="I15" s="93"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" s="84" t="s">
         <v>85</v>
       </c>
@@ -14025,7 +14688,7 @@
       <c r="H16" s="89"/>
       <c r="I16" s="93"/>
     </row>
-    <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="86" t="s">
         <v>141</v>
       </c>
@@ -14043,7 +14706,7 @@
       <c r="H17" s="89"/>
       <c r="I17" s="93"/>
     </row>
-    <row r="18" spans="2:9" ht="31.2" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:9" ht="27" x14ac:dyDescent="0.3">
       <c r="B18" s="86" t="s">
         <v>106</v>
       </c>
@@ -14061,7 +14724,7 @@
       <c r="H18" s="89"/>
       <c r="I18" s="93"/>
     </row>
-    <row r="19" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="85" t="s">
         <v>109</v>
       </c>
@@ -14079,7 +14742,7 @@
       <c r="H19" s="89"/>
       <c r="I19" s="93"/>
     </row>
-    <row r="20" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="85" t="s">
         <v>167</v>
       </c>
@@ -14097,7 +14760,7 @@
       <c r="H20" s="111"/>
       <c r="I20" s="112"/>
     </row>
-    <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="87" t="s">
         <v>108</v>
       </c>
@@ -14115,7 +14778,7 @@
       <c r="H21" s="94"/>
       <c r="I21" s="95"/>
     </row>
-    <row r="22" spans="2:9" ht="16.2" thickTop="1" x14ac:dyDescent="0.4"/>
+    <row r="22" spans="2:9" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:B3"/>
@@ -14132,18 +14795,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.3984375" style="81" customWidth="1"/>
+    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
     <col min="2" max="2" width="9" style="81"/>
-    <col min="3" max="4" width="14.69921875" style="81" customWidth="1"/>
+    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
     <col min="5" max="5" width="43" style="81" customWidth="1"/>
-    <col min="6" max="6" width="61.8984375" style="81" customWidth="1"/>
-    <col min="7" max="9" width="62.09765625" style="81" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
+    <col min="7" max="9" width="62.125" style="81" customWidth="1"/>
     <col min="10" max="16384" width="9" style="81"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="108" t="s">
         <v>0</v>
       </c>
@@ -14154,7 +14817,7 @@
       <c r="D1" s="109"/>
       <c r="E1" s="107"/>
     </row>
-    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B2" s="191" t="s">
         <v>2</v>
       </c>
@@ -14174,7 +14837,7 @@
       <c r="H2" s="189"/>
       <c r="I2" s="190"/>
     </row>
-    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="192"/>
       <c r="C3" s="196"/>
       <c r="D3" s="196"/>
@@ -14192,7 +14855,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="82" t="s">
         <v>117</v>
       </c>
@@ -14210,7 +14873,7 @@
       <c r="H4" s="88"/>
       <c r="I4" s="92"/>
     </row>
-    <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="83" t="s">
         <v>123</v>
       </c>
@@ -14228,7 +14891,7 @@
       <c r="H5" s="89"/>
       <c r="I5" s="93"/>
     </row>
-    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="83" t="s">
         <v>124</v>
       </c>
@@ -14246,7 +14909,7 @@
       <c r="H6" s="89"/>
       <c r="I6" s="93"/>
     </row>
-    <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="83" t="s">
         <v>125</v>
       </c>
@@ -14264,7 +14927,7 @@
       <c r="H7" s="89"/>
       <c r="I7" s="93"/>
     </row>
-    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="84" t="s">
         <v>3</v>
       </c>
@@ -14282,7 +14945,7 @@
       <c r="H8" s="89"/>
       <c r="I8" s="93"/>
     </row>
-    <row r="9" spans="1:9" ht="31.2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.3">
       <c r="B9" s="84" t="s">
         <v>45</v>
       </c>
@@ -14300,7 +14963,7 @@
       <c r="H9" s="89"/>
       <c r="I9" s="93"/>
     </row>
-    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="84" t="s">
         <v>55</v>
       </c>
@@ -14318,7 +14981,7 @@
       <c r="H10" s="89"/>
       <c r="I10" s="93"/>
     </row>
-    <row r="11" spans="1:9" ht="46.8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
       <c r="B11" s="83" t="s">
         <v>62</v>
       </c>
@@ -14336,7 +14999,7 @@
       <c r="H11" s="89"/>
       <c r="I11" s="93"/>
     </row>
-    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="84" t="s">
         <v>73</v>
       </c>
@@ -14354,7 +15017,7 @@
       <c r="H12" s="89"/>
       <c r="I12" s="93"/>
     </row>
-    <row r="13" spans="1:9" ht="347.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:9" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="84" t="s">
         <v>118</v>
       </c>
@@ -14372,7 +15035,7 @@
       <c r="H13" s="89"/>
       <c r="I13" s="93"/>
     </row>
-    <row r="14" spans="1:9" ht="390" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:9" ht="337.5" x14ac:dyDescent="0.3">
       <c r="B14" s="85" t="s">
         <v>181</v>
       </c>
@@ -14396,7 +15059,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="85" t="s">
         <v>75</v>
       </c>
@@ -14414,7 +15077,7 @@
       <c r="H15" s="89"/>
       <c r="I15" s="93"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" s="84" t="s">
         <v>85</v>
       </c>
@@ -14432,7 +15095,7 @@
       <c r="H16" s="89"/>
       <c r="I16" s="93"/>
     </row>
-    <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="86" t="s">
         <v>141</v>
       </c>
@@ -14450,7 +15113,7 @@
       <c r="H17" s="89"/>
       <c r="I17" s="93"/>
     </row>
-    <row r="18" spans="2:9" ht="31.2" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:9" ht="27" x14ac:dyDescent="0.3">
       <c r="B18" s="86" t="s">
         <v>106</v>
       </c>
@@ -14468,7 +15131,7 @@
       <c r="H18" s="89"/>
       <c r="I18" s="93"/>
     </row>
-    <row r="19" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="85" t="s">
         <v>109</v>
       </c>
@@ -14486,7 +15149,7 @@
       <c r="H19" s="89"/>
       <c r="I19" s="93"/>
     </row>
-    <row r="20" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="85" t="s">
         <v>167</v>
       </c>
@@ -14504,7 +15167,7 @@
       <c r="H20" s="111"/>
       <c r="I20" s="112"/>
     </row>
-    <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="87" t="s">
         <v>108</v>
       </c>
@@ -14522,7 +15185,7 @@
       <c r="H21" s="94"/>
       <c r="I21" s="95"/>
     </row>
-    <row r="22" spans="2:9" ht="16.2" thickTop="1" x14ac:dyDescent="0.4"/>
+    <row r="22" spans="2:9" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:B3"/>
@@ -14539,18 +15202,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.3984375" style="81" customWidth="1"/>
+    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
     <col min="2" max="2" width="9" style="81"/>
-    <col min="3" max="4" width="14.69921875" style="81" customWidth="1"/>
+    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
     <col min="5" max="5" width="43" style="81" customWidth="1"/>
-    <col min="6" max="6" width="61.8984375" style="81" customWidth="1"/>
-    <col min="7" max="9" width="62.09765625" style="81" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
+    <col min="7" max="9" width="62.125" style="81" customWidth="1"/>
     <col min="10" max="16384" width="9" style="81"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="108" t="s">
         <v>0</v>
       </c>
@@ -14561,7 +15224,7 @@
       <c r="D1" s="109"/>
       <c r="E1" s="107"/>
     </row>
-    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B2" s="191" t="s">
         <v>2</v>
       </c>
@@ -14581,7 +15244,7 @@
       <c r="H2" s="189"/>
       <c r="I2" s="190"/>
     </row>
-    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="192"/>
       <c r="C3" s="196"/>
       <c r="D3" s="196"/>
@@ -14599,7 +15262,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="151" t="s">
         <v>108</v>
       </c>
@@ -14617,7 +15280,7 @@
       <c r="H4" s="88"/>
       <c r="I4" s="92"/>
     </row>
-    <row r="5" spans="1:9" ht="78" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
       <c r="B5" s="154" t="s">
         <v>181</v>
       </c>
@@ -14639,7 +15302,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="152" t="s">
         <v>275</v>
       </c>
@@ -14659,7 +15322,7 @@
       </c>
       <c r="I6" s="156"/>
     </row>
-    <row r="7" spans="1:9" ht="93" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9" ht="93" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="152" t="s">
         <v>75</v>
       </c>
@@ -14679,7 +15342,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="87.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" ht="87.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="152" t="s">
         <v>109</v>
       </c>
@@ -14699,7 +15362,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="153" t="s">
         <v>117</v>
       </c>
@@ -14717,7 +15380,7 @@
       <c r="H9" s="138"/>
       <c r="I9" s="93"/>
     </row>
-    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="153" t="s">
         <v>123</v>
       </c>
@@ -14735,7 +15398,7 @@
       <c r="H10" s="89"/>
       <c r="I10" s="93"/>
     </row>
-    <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="153" t="s">
         <v>124</v>
       </c>
@@ -14753,7 +15416,7 @@
       <c r="H11" s="89"/>
       <c r="I11" s="93"/>
     </row>
-    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="153" t="s">
         <v>125</v>
       </c>
@@ -14771,7 +15434,7 @@
       <c r="H12" s="138"/>
       <c r="I12" s="93"/>
     </row>
-    <row r="13" spans="1:9" ht="222" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:9" ht="222" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="132" t="s">
         <v>62</v>
       </c>
@@ -14793,7 +15456,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="78" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
       <c r="B14" s="131" t="s">
         <v>73</v>
       </c>
@@ -14815,7 +15478,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="78" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
       <c r="B15" s="131" t="s">
         <v>55</v>
       </c>
@@ -14839,7 +15502,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="228.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:9" ht="228.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="131" t="s">
         <v>85</v>
       </c>
@@ -14861,7 +15524,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="130" t="s">
         <v>167</v>
       </c>
@@ -14885,7 +15548,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="131" t="s">
         <v>141</v>
       </c>
@@ -14903,7 +15566,7 @@
       <c r="H18" s="133"/>
       <c r="I18" s="136"/>
     </row>
-    <row r="19" spans="2:9" ht="124.8" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:9" ht="108" x14ac:dyDescent="0.3">
       <c r="B19" s="150" t="s">
         <v>3</v>
       </c>
@@ -14927,7 +15590,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="143" t="s">
         <v>45</v>
       </c>
@@ -14964,18 +15627,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.3984375" style="81" customWidth="1"/>
+    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
     <col min="2" max="2" width="9" style="81"/>
-    <col min="3" max="4" width="14.69921875" style="81" customWidth="1"/>
+    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
     <col min="5" max="5" width="43" style="81" customWidth="1"/>
-    <col min="6" max="6" width="61.8984375" style="81" customWidth="1"/>
-    <col min="7" max="9" width="62.09765625" style="81" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
+    <col min="7" max="9" width="62.125" style="81" customWidth="1"/>
     <col min="10" max="16384" width="9" style="81"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="108" t="s">
         <v>0</v>
       </c>
@@ -14986,7 +15649,7 @@
       <c r="D1" s="109"/>
       <c r="E1" s="107"/>
     </row>
-    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B2" s="191" t="s">
         <v>2</v>
       </c>
@@ -15006,7 +15669,7 @@
       <c r="H2" s="189"/>
       <c r="I2" s="190"/>
     </row>
-    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="192"/>
       <c r="C3" s="196"/>
       <c r="D3" s="196"/>
@@ -15024,7 +15687,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="151" t="s">
         <v>108</v>
       </c>
@@ -15042,7 +15705,7 @@
       <c r="H4" s="88"/>
       <c r="I4" s="92"/>
     </row>
-    <row r="5" spans="1:9" ht="78" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
       <c r="B5" s="154" t="s">
         <v>181</v>
       </c>
@@ -15064,7 +15727,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="152" t="s">
         <v>275</v>
       </c>
@@ -15082,7 +15745,7 @@
       <c r="H6" s="123"/>
       <c r="I6" s="135"/>
     </row>
-    <row r="7" spans="1:9" ht="138" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9" ht="138" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="152" t="s">
         <v>75</v>
       </c>
@@ -15104,7 +15767,7 @@
       <c r="H7" s="89"/>
       <c r="I7" s="93"/>
     </row>
-    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="152" t="s">
         <v>109</v>
       </c>
@@ -15122,7 +15785,7 @@
       <c r="H8" s="89"/>
       <c r="I8" s="93"/>
     </row>
-    <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="153" t="s">
         <v>117</v>
       </c>
@@ -15140,7 +15803,7 @@
       <c r="H9" s="138"/>
       <c r="I9" s="93"/>
     </row>
-    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="153" t="s">
         <v>123</v>
       </c>
@@ -15158,7 +15821,7 @@
       <c r="H10" s="89"/>
       <c r="I10" s="93"/>
     </row>
-    <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="153" t="s">
         <v>124</v>
       </c>
@@ -15176,7 +15839,7 @@
       <c r="H11" s="89"/>
       <c r="I11" s="93"/>
     </row>
-    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="153" t="s">
         <v>125</v>
       </c>
@@ -15194,7 +15857,7 @@
       <c r="H12" s="138"/>
       <c r="I12" s="93"/>
     </row>
-    <row r="13" spans="1:9" ht="343.2" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:9" ht="283.5" x14ac:dyDescent="0.3">
       <c r="B13" s="132" t="s">
         <v>62</v>
       </c>
@@ -15220,7 +15883,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="409.6" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
       <c r="B14" s="131" t="s">
         <v>73</v>
       </c>
@@ -15246,7 +15909,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="202.8" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:9" ht="175.5" x14ac:dyDescent="0.3">
       <c r="B15" s="131" t="s">
         <v>55</v>
       </c>
@@ -15272,7 +15935,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="409.6" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
       <c r="B16" s="131" t="s">
         <v>85</v>
       </c>
@@ -15298,7 +15961,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="187.2" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:9" ht="162" x14ac:dyDescent="0.3">
       <c r="B17" s="130" t="s">
         <v>167</v>
       </c>
@@ -15324,7 +15987,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="131" t="s">
         <v>141</v>
       </c>
@@ -15340,7 +16003,7 @@
       <c r="H18" s="133"/>
       <c r="I18" s="136"/>
     </row>
-    <row r="19" spans="2:9" ht="62.4" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:9" ht="54" x14ac:dyDescent="0.3">
       <c r="B19" s="150" t="s">
         <v>3</v>
       </c>
@@ -15366,7 +16029,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="143" t="s">
         <v>45</v>
       </c>
@@ -15404,18 +16067,18 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.3984375" style="81" customWidth="1"/>
+    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
     <col min="2" max="2" width="9" style="81"/>
-    <col min="3" max="4" width="14.69921875" style="81" customWidth="1"/>
+    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
     <col min="5" max="5" width="43" style="81" customWidth="1"/>
-    <col min="6" max="6" width="61.8984375" style="81" customWidth="1"/>
-    <col min="7" max="10" width="62.09765625" style="81" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
+    <col min="7" max="10" width="62.125" style="81" customWidth="1"/>
     <col min="11" max="16384" width="9" style="81"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="108" t="s">
         <v>0</v>
       </c>
@@ -15426,7 +16089,7 @@
       <c r="D1" s="109"/>
       <c r="E1" s="107"/>
     </row>
-    <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B2" s="191" t="s">
         <v>2</v>
       </c>
@@ -15447,7 +16110,7 @@
       <c r="I2" s="197"/>
       <c r="J2" s="190"/>
     </row>
-    <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="192"/>
       <c r="C3" s="196"/>
       <c r="D3" s="196"/>
@@ -15468,7 +16131,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="151" t="s">
         <v>108</v>
       </c>
@@ -15487,7 +16150,7 @@
       <c r="I4" s="171"/>
       <c r="J4" s="92"/>
     </row>
-    <row r="5" spans="1:10" ht="62.4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="54" x14ac:dyDescent="0.3">
       <c r="B5" s="154" t="s">
         <v>181</v>
       </c>
@@ -15510,7 +16173,7 @@
       <c r="I5" s="172"/>
       <c r="J5" s="135"/>
     </row>
-    <row r="6" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="152" t="s">
         <v>118</v>
       </c>
@@ -15529,7 +16192,7 @@
       <c r="I6" s="172"/>
       <c r="J6" s="135"/>
     </row>
-    <row r="7" spans="1:10" ht="138" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" ht="138" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="152" t="s">
         <v>75</v>
       </c>
@@ -15548,7 +16211,7 @@
       <c r="I7" s="173"/>
       <c r="J7" s="93"/>
     </row>
-    <row r="8" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="152" t="s">
         <v>109</v>
       </c>
@@ -15567,7 +16230,7 @@
       <c r="I8" s="173"/>
       <c r="J8" s="93"/>
     </row>
-    <row r="9" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="153" t="s">
         <v>117</v>
       </c>
@@ -15586,7 +16249,7 @@
       <c r="I9" s="89"/>
       <c r="J9" s="93"/>
     </row>
-    <row r="10" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="153" t="s">
         <v>123</v>
       </c>
@@ -15605,7 +16268,7 @@
       <c r="I10" s="173"/>
       <c r="J10" s="93"/>
     </row>
-    <row r="11" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="153" t="s">
         <v>124</v>
       </c>
@@ -15624,7 +16287,7 @@
       <c r="I11" s="173"/>
       <c r="J11" s="93"/>
     </row>
-    <row r="12" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="153" t="s">
         <v>125</v>
       </c>
@@ -15643,7 +16306,7 @@
       <c r="I12" s="89"/>
       <c r="J12" s="93"/>
     </row>
-    <row r="13" spans="1:10" ht="409.6" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" ht="364.5" x14ac:dyDescent="0.3">
       <c r="B13" s="132" t="s">
         <v>62</v>
       </c>
@@ -15670,7 +16333,7 @@
       </c>
       <c r="J13" s="122"/>
     </row>
-    <row r="14" spans="1:10" ht="358.8" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" ht="310.5" x14ac:dyDescent="0.3">
       <c r="B14" s="131" t="s">
         <v>73</v>
       </c>
@@ -15697,7 +16360,7 @@
       </c>
       <c r="J14" s="122"/>
     </row>
-    <row r="15" spans="1:10" ht="280.8" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" ht="243" x14ac:dyDescent="0.3">
       <c r="B15" s="131" t="s">
         <v>55</v>
       </c>
@@ -15724,7 +16387,7 @@
       </c>
       <c r="J15" s="122"/>
     </row>
-    <row r="16" spans="1:10" ht="409.6" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" ht="378" x14ac:dyDescent="0.3">
       <c r="B16" s="131" t="s">
         <v>85</v>
       </c>
@@ -15751,7 +16414,7 @@
       </c>
       <c r="J16" s="122"/>
     </row>
-    <row r="17" spans="2:10" ht="46.8" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:10" ht="40.5" x14ac:dyDescent="0.3">
       <c r="B17" s="130" t="s">
         <v>167</v>
       </c>
@@ -15778,7 +16441,7 @@
       </c>
       <c r="J17" s="168"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="131" t="s">
         <v>141</v>
       </c>
@@ -15795,7 +16458,7 @@
       <c r="I18" s="129"/>
       <c r="J18" s="136"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="150" t="s">
         <v>3</v>
       </c>
@@ -15816,7 +16479,7 @@
       <c r="I19" s="174"/>
       <c r="J19" s="134"/>
     </row>
-    <row r="20" spans="2:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="143" t="s">
         <v>45</v>
       </c>
@@ -15853,19 +16516,19 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.3984375" style="81" customWidth="1"/>
-    <col min="2" max="2" width="9" style="81"/>
-    <col min="3" max="4" width="14.69921875" style="81" customWidth="1"/>
+    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
+    <col min="2" max="2" width="10.125" style="81" customWidth="1"/>
+    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
     <col min="5" max="5" width="43" style="81" customWidth="1"/>
-    <col min="6" max="6" width="61.8984375" style="81" customWidth="1"/>
-    <col min="7" max="9" width="62.09765625" style="81" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
+    <col min="7" max="9" width="62.125" style="81" customWidth="1"/>
     <col min="10" max="16384" width="9" style="81"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="108" t="s">
         <v>0</v>
       </c>
@@ -15876,7 +16539,7 @@
       <c r="D1" s="109"/>
       <c r="E1" s="107"/>
     </row>
-    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B2" s="191" t="s">
         <v>2</v>
       </c>
@@ -15896,7 +16559,7 @@
       <c r="H2" s="189"/>
       <c r="I2" s="190"/>
     </row>
-    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="192"/>
       <c r="C3" s="196"/>
       <c r="D3" s="196"/>
@@ -15914,7 +16577,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="151" t="s">
         <v>108</v>
       </c>
@@ -15932,7 +16595,7 @@
       <c r="H4" s="88"/>
       <c r="I4" s="92"/>
     </row>
-    <row r="5" spans="1:9" ht="62.4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" ht="54" x14ac:dyDescent="0.3">
       <c r="B5" s="154" t="s">
         <v>181</v>
       </c>
@@ -15948,11 +16611,13 @@
       <c r="F5" s="123" t="s">
         <v>357</v>
       </c>
-      <c r="G5" s="123"/>
+      <c r="G5" s="123" t="s">
+        <v>392</v>
+      </c>
       <c r="H5" s="123"/>
       <c r="I5" s="135"/>
     </row>
-    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="152" t="s">
         <v>118</v>
       </c>
@@ -15965,12 +16630,16 @@
       <c r="E6" s="100" t="s">
         <v>161</v>
       </c>
-      <c r="F6" s="123"/>
-      <c r="G6" s="123"/>
+      <c r="F6" s="123" t="s">
+        <v>398</v>
+      </c>
+      <c r="G6" s="123" t="s">
+        <v>399</v>
+      </c>
       <c r="H6" s="123"/>
       <c r="I6" s="135"/>
     </row>
-    <row r="7" spans="1:9" ht="187.2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9" ht="162" x14ac:dyDescent="0.3">
       <c r="B7" s="152" t="s">
         <v>75</v>
       </c>
@@ -15986,11 +16655,13 @@
       <c r="F7" s="123" t="s">
         <v>386</v>
       </c>
-      <c r="G7" s="105"/>
+      <c r="G7" s="105" t="s">
+        <v>393</v>
+      </c>
       <c r="H7" s="89"/>
       <c r="I7" s="93"/>
     </row>
-    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="152" t="s">
         <v>109</v>
       </c>
@@ -16008,7 +16679,7 @@
       <c r="H8" s="89"/>
       <c r="I8" s="93"/>
     </row>
-    <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="153" t="s">
         <v>117</v>
       </c>
@@ -16026,7 +16697,7 @@
       <c r="H9" s="138"/>
       <c r="I9" s="93"/>
     </row>
-    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="153" t="s">
         <v>123</v>
       </c>
@@ -16044,7 +16715,7 @@
       <c r="H10" s="89"/>
       <c r="I10" s="93"/>
     </row>
-    <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="153" t="s">
         <v>124</v>
       </c>
@@ -16062,7 +16733,7 @@
       <c r="H11" s="89"/>
       <c r="I11" s="93"/>
     </row>
-    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="153" t="s">
         <v>125</v>
       </c>
@@ -16080,29 +16751,31 @@
       <c r="H12" s="138"/>
       <c r="I12" s="93"/>
     </row>
-    <row r="13" spans="1:9" ht="93.6" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:9" ht="94.5" x14ac:dyDescent="0.3">
       <c r="B13" s="132" t="s">
+        <v>400</v>
+      </c>
+      <c r="C13" s="117" t="s">
+        <v>403</v>
+      </c>
+      <c r="D13" s="117" t="s">
+        <v>404</v>
+      </c>
+      <c r="E13" s="91" t="s">
+        <v>401</v>
+      </c>
+      <c r="F13" s="123" t="s">
+        <v>402</v>
+      </c>
+      <c r="G13" s="198" t="s">
+        <v>405</v>
+      </c>
+      <c r="H13" s="199"/>
+      <c r="I13" s="200"/>
+    </row>
+    <row r="14" spans="1:9" ht="243" x14ac:dyDescent="0.3">
+      <c r="B14" s="132" t="s">
         <v>62</v>
-      </c>
-      <c r="C13" s="117" t="s">
-        <v>270</v>
-      </c>
-      <c r="D13" s="117" t="s">
-        <v>178</v>
-      </c>
-      <c r="E13" s="100" t="s">
-        <v>260</v>
-      </c>
-      <c r="F13" s="105"/>
-      <c r="G13" s="157" t="s">
-        <v>391</v>
-      </c>
-      <c r="H13" s="105"/>
-      <c r="I13" s="122"/>
-    </row>
-    <row r="14" spans="1:9" ht="171.6" x14ac:dyDescent="0.4">
-      <c r="B14" s="131" t="s">
-        <v>73</v>
       </c>
       <c r="C14" s="117" t="s">
         <v>270</v>
@@ -16111,18 +16784,18 @@
         <v>178</v>
       </c>
       <c r="E14" s="100" t="s">
-        <v>261</v>
-      </c>
-      <c r="F14" s="105" t="s">
+        <v>260</v>
+      </c>
+      <c r="F14" s="105"/>
+      <c r="G14" s="157" t="s">
         <v>390</v>
       </c>
-      <c r="G14" s="157"/>
       <c r="H14" s="105"/>
       <c r="I14" s="122"/>
     </row>
-    <row r="15" spans="1:9" ht="124.8" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:9" ht="378" x14ac:dyDescent="0.3">
       <c r="B15" s="131" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="C15" s="117" t="s">
         <v>270</v>
@@ -16131,18 +16804,20 @@
         <v>178</v>
       </c>
       <c r="E15" s="100" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F15" s="105" t="s">
-        <v>387</v>
-      </c>
-      <c r="G15" s="157"/>
-      <c r="H15" s="157"/>
-      <c r="I15" s="176"/>
-    </row>
-    <row r="16" spans="1:9" ht="409.6" x14ac:dyDescent="0.4">
+        <v>389</v>
+      </c>
+      <c r="G15" s="157" t="s">
+        <v>394</v>
+      </c>
+      <c r="H15" s="105"/>
+      <c r="I15" s="122"/>
+    </row>
+    <row r="16" spans="1:9" ht="108" x14ac:dyDescent="0.3">
       <c r="B16" s="131" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="C16" s="117" t="s">
         <v>270</v>
@@ -16151,18 +16826,20 @@
         <v>178</v>
       </c>
       <c r="E16" s="100" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F16" s="105" t="s">
-        <v>389</v>
-      </c>
-      <c r="G16" s="157"/>
+        <v>387</v>
+      </c>
+      <c r="G16" s="157" t="s">
+        <v>398</v>
+      </c>
       <c r="H16" s="157"/>
       <c r="I16" s="176"/>
     </row>
-    <row r="17" spans="2:9" ht="124.8" x14ac:dyDescent="0.4">
-      <c r="B17" s="130" t="s">
-        <v>167</v>
+    <row r="17" spans="2:9" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="B17" s="131" t="s">
+        <v>85</v>
       </c>
       <c r="C17" s="117" t="s">
         <v>270</v>
@@ -16170,19 +16847,21 @@
       <c r="D17" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E17" s="113" t="s">
-        <v>303</v>
-      </c>
-      <c r="F17" s="119" t="s">
-        <v>388</v>
-      </c>
-      <c r="G17" s="169"/>
-      <c r="H17" s="169"/>
-      <c r="I17" s="177"/>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B18" s="131" t="s">
-        <v>141</v>
+      <c r="E17" s="100" t="s">
+        <v>262</v>
+      </c>
+      <c r="F17" s="105" t="s">
+        <v>391</v>
+      </c>
+      <c r="G17" s="157" t="s">
+        <v>395</v>
+      </c>
+      <c r="H17" s="157"/>
+      <c r="I17" s="176"/>
+    </row>
+    <row r="18" spans="2:9" ht="108" x14ac:dyDescent="0.3">
+      <c r="B18" s="130" t="s">
+        <v>167</v>
       </c>
       <c r="C18" s="117" t="s">
         <v>270</v>
@@ -16190,53 +16869,79 @@
       <c r="D18" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E18" s="113"/>
-      <c r="F18" s="155"/>
-      <c r="G18" s="158"/>
-      <c r="H18" s="133"/>
-      <c r="I18" s="136"/>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B19" s="150" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="139" t="s">
+      <c r="E18" s="113" t="s">
+        <v>303</v>
+      </c>
+      <c r="F18" s="119" t="s">
+        <v>388</v>
+      </c>
+      <c r="G18" s="169" t="s">
+        <v>398</v>
+      </c>
+      <c r="H18" s="169"/>
+      <c r="I18" s="177"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B19" s="131" t="s">
+        <v>141</v>
+      </c>
+      <c r="C19" s="117" t="s">
         <v>270</v>
       </c>
-      <c r="D19" s="139" t="s">
+      <c r="D19" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="E19" s="91" t="s">
-        <v>156</v>
-      </c>
-      <c r="F19" s="105" t="s">
-        <v>263</v>
-      </c>
+      <c r="E19" s="113"/>
+      <c r="F19" s="155"/>
       <c r="G19" s="158"/>
       <c r="H19" s="133"/>
-      <c r="I19" s="134"/>
-    </row>
-    <row r="20" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B20" s="178" t="s">
+      <c r="I19" s="136"/>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B20" s="150" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="139" t="s">
+        <v>270</v>
+      </c>
+      <c r="D20" s="139" t="s">
+        <v>178</v>
+      </c>
+      <c r="E20" s="91" t="s">
+        <v>156</v>
+      </c>
+      <c r="F20" s="105" t="s">
+        <v>263</v>
+      </c>
+      <c r="G20" s="157" t="s">
+        <v>396</v>
+      </c>
+      <c r="H20" s="133"/>
+      <c r="I20" s="134"/>
+    </row>
+    <row r="21" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="178" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="118" t="s">
+      <c r="C21" s="118" t="s">
         <v>270</v>
       </c>
-      <c r="D20" s="118" t="s">
+      <c r="D21" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="103" t="s">
+      <c r="E21" s="103" t="s">
         <v>258</v>
       </c>
-      <c r="F20" s="179" t="s">
+      <c r="F21" s="179" t="s">
         <v>263</v>
       </c>
-      <c r="G20" s="106"/>
-      <c r="H20" s="180"/>
-      <c r="I20" s="95"/>
-    </row>
-    <row r="21" spans="2:9" ht="16.2" thickTop="1" x14ac:dyDescent="0.4"/>
+      <c r="G21" s="106" t="s">
+        <v>397</v>
+      </c>
+      <c r="H21" s="180"/>
+      <c r="I21" s="95"/>
+    </row>
+    <row r="22" spans="2:9" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:B3"/>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\일정\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Task\000_PJT\000_Heater\111_PTC\1.doc\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="413">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -8211,13 +8211,6 @@
     - 사이버보안품질연구팀에 보낼 샘플 준비
      : PCB 2EA, Signal Connector 1EA, E2 Pin Connector 1EA</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- SWE.3 SDDS 후속 작업 (진행률 : 97%)
-[조현진 전임]
-- SWE.1, 2, 3 등록에 맞추어 SWE. 4, 5, 6 ALM 등록</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -8346,6 +8339,46 @@
   [ 진행 및 검토 ]
     - 급격한 Target Duty 변화 수신 (예시 80% → 40%)
     - 급격한 Target Duty OFF 수신 (예시 80% → 0% (OFF))</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- SWE.3 SDDS 후속 작업 (진행률 : 97%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- SWE.3 SDDS 후속 작업 (진행률 : 97%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Proto (진행 중)
+P1 (25/07/30)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">[조현진 전임]
+- LIN CheckList Application 작성 (진행률 : 70%)
+  : 번역 간 오역이나 스펙상 명확하지 않은 부분 TOA 통해 고객사와 협의
+- Heating Logic 수정
+  : 정격전압 동작범위(190~470)대로 동작하도록 변경완료(01/13)   </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[조현진 전임]
+- LIN CheckList Application 작성 (진행률 : 60%)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -9820,7 +9853,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="201">
+  <cellXfs count="202">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -10367,6 +10400,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="81" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -10415,14 +10457,8 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="81" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -11089,90 +11125,90 @@
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="182" t="s">
+      <c r="B2" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="184" t="s">
+      <c r="C2" s="187" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="184" t="s">
+      <c r="D2" s="187" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="188">
+      <c r="E2" s="191">
         <v>23</v>
       </c>
-      <c r="F2" s="186"/>
-      <c r="G2" s="186"/>
-      <c r="H2" s="186"/>
-      <c r="I2" s="186"/>
-      <c r="J2" s="186"/>
-      <c r="K2" s="186"/>
-      <c r="L2" s="186"/>
-      <c r="M2" s="186"/>
-      <c r="N2" s="186"/>
-      <c r="O2" s="186"/>
-      <c r="P2" s="186"/>
-      <c r="Q2" s="186">
+      <c r="F2" s="189"/>
+      <c r="G2" s="189"/>
+      <c r="H2" s="189"/>
+      <c r="I2" s="189"/>
+      <c r="J2" s="189"/>
+      <c r="K2" s="189"/>
+      <c r="L2" s="189"/>
+      <c r="M2" s="189"/>
+      <c r="N2" s="189"/>
+      <c r="O2" s="189"/>
+      <c r="P2" s="189"/>
+      <c r="Q2" s="189">
         <v>24</v>
       </c>
-      <c r="R2" s="186"/>
-      <c r="S2" s="186"/>
-      <c r="T2" s="186"/>
-      <c r="U2" s="186"/>
-      <c r="V2" s="186"/>
-      <c r="W2" s="186"/>
-      <c r="X2" s="186"/>
-      <c r="Y2" s="186"/>
-      <c r="Z2" s="186"/>
-      <c r="AA2" s="186"/>
-      <c r="AB2" s="186"/>
-      <c r="AC2" s="186">
+      <c r="R2" s="189"/>
+      <c r="S2" s="189"/>
+      <c r="T2" s="189"/>
+      <c r="U2" s="189"/>
+      <c r="V2" s="189"/>
+      <c r="W2" s="189"/>
+      <c r="X2" s="189"/>
+      <c r="Y2" s="189"/>
+      <c r="Z2" s="189"/>
+      <c r="AA2" s="189"/>
+      <c r="AB2" s="189"/>
+      <c r="AC2" s="189">
         <v>25</v>
       </c>
-      <c r="AD2" s="186"/>
-      <c r="AE2" s="186"/>
-      <c r="AF2" s="186"/>
-      <c r="AG2" s="186"/>
-      <c r="AH2" s="186"/>
-      <c r="AI2" s="186"/>
-      <c r="AJ2" s="186"/>
-      <c r="AK2" s="186"/>
-      <c r="AL2" s="186"/>
-      <c r="AM2" s="186"/>
-      <c r="AN2" s="186"/>
-      <c r="AO2" s="186">
+      <c r="AD2" s="189"/>
+      <c r="AE2" s="189"/>
+      <c r="AF2" s="189"/>
+      <c r="AG2" s="189"/>
+      <c r="AH2" s="189"/>
+      <c r="AI2" s="189"/>
+      <c r="AJ2" s="189"/>
+      <c r="AK2" s="189"/>
+      <c r="AL2" s="189"/>
+      <c r="AM2" s="189"/>
+      <c r="AN2" s="189"/>
+      <c r="AO2" s="189">
         <v>26</v>
       </c>
-      <c r="AP2" s="186"/>
-      <c r="AQ2" s="186"/>
-      <c r="AR2" s="186"/>
-      <c r="AS2" s="186"/>
-      <c r="AT2" s="186"/>
-      <c r="AU2" s="186"/>
-      <c r="AV2" s="186"/>
-      <c r="AW2" s="186"/>
-      <c r="AX2" s="186"/>
-      <c r="AY2" s="186"/>
-      <c r="AZ2" s="187"/>
-      <c r="BA2" s="186">
+      <c r="AP2" s="189"/>
+      <c r="AQ2" s="189"/>
+      <c r="AR2" s="189"/>
+      <c r="AS2" s="189"/>
+      <c r="AT2" s="189"/>
+      <c r="AU2" s="189"/>
+      <c r="AV2" s="189"/>
+      <c r="AW2" s="189"/>
+      <c r="AX2" s="189"/>
+      <c r="AY2" s="189"/>
+      <c r="AZ2" s="190"/>
+      <c r="BA2" s="189">
         <v>27</v>
       </c>
-      <c r="BB2" s="186"/>
-      <c r="BC2" s="186"/>
-      <c r="BD2" s="186"/>
-      <c r="BE2" s="186"/>
-      <c r="BF2" s="186"/>
-      <c r="BG2" s="186"/>
-      <c r="BH2" s="186"/>
-      <c r="BI2" s="186"/>
-      <c r="BJ2" s="186"/>
-      <c r="BK2" s="186"/>
-      <c r="BL2" s="187"/>
+      <c r="BB2" s="189"/>
+      <c r="BC2" s="189"/>
+      <c r="BD2" s="189"/>
+      <c r="BE2" s="189"/>
+      <c r="BF2" s="189"/>
+      <c r="BG2" s="189"/>
+      <c r="BH2" s="189"/>
+      <c r="BI2" s="189"/>
+      <c r="BJ2" s="189"/>
+      <c r="BK2" s="189"/>
+      <c r="BL2" s="190"/>
     </row>
     <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="183"/>
-      <c r="C3" s="185"/>
-      <c r="D3" s="185"/>
+      <c r="B3" s="186"/>
+      <c r="C3" s="188"/>
+      <c r="D3" s="188"/>
       <c r="E3" s="22">
         <v>1</v>
       </c>
@@ -13112,31 +13148,31 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="191" t="s">
+      <c r="B2" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="195" t="s">
+      <c r="C2" s="198" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="195" t="s">
+      <c r="D2" s="198" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="193" t="s">
+      <c r="E2" s="196" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="189" t="s">
+      <c r="F2" s="192" t="s">
         <v>378</v>
       </c>
-      <c r="G2" s="189"/>
-      <c r="H2" s="189"/>
-      <c r="I2" s="197"/>
-      <c r="J2" s="190"/>
+      <c r="G2" s="192"/>
+      <c r="H2" s="192"/>
+      <c r="I2" s="200"/>
+      <c r="J2" s="193"/>
     </row>
     <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="192"/>
-      <c r="C3" s="196"/>
-      <c r="D3" s="196"/>
-      <c r="E3" s="194"/>
+      <c r="B3" s="195"/>
+      <c r="C3" s="199"/>
+      <c r="D3" s="199"/>
+      <c r="E3" s="197"/>
       <c r="F3" s="97" t="s">
         <v>379</v>
       </c>
@@ -13642,39 +13678,39 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="191" t="s">
+      <c r="B2" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="195" t="s">
+      <c r="C2" s="198" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="195" t="s">
+      <c r="D2" s="198" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="193" t="s">
+      <c r="E2" s="196" t="s">
         <v>126</v>
       </c>
       <c r="F2" s="96" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="189" t="s">
+      <c r="G2" s="192" t="s">
         <v>113</v>
       </c>
-      <c r="H2" s="189"/>
-      <c r="I2" s="189"/>
-      <c r="J2" s="190"/>
-      <c r="K2" s="189" t="s">
+      <c r="H2" s="192"/>
+      <c r="I2" s="192"/>
+      <c r="J2" s="193"/>
+      <c r="K2" s="192" t="s">
         <v>182</v>
       </c>
-      <c r="L2" s="189"/>
-      <c r="M2" s="189"/>
-      <c r="N2" s="190"/>
+      <c r="L2" s="192"/>
+      <c r="M2" s="192"/>
+      <c r="N2" s="193"/>
     </row>
     <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="192"/>
-      <c r="C3" s="196"/>
-      <c r="D3" s="196"/>
-      <c r="E3" s="194"/>
+      <c r="B3" s="195"/>
+      <c r="C3" s="199"/>
+      <c r="D3" s="199"/>
+      <c r="E3" s="197"/>
       <c r="F3" s="97" t="s">
         <v>111</v>
       </c>
@@ -14417,30 +14453,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="191" t="s">
+      <c r="B2" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="195" t="s">
+      <c r="C2" s="198" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="195" t="s">
+      <c r="D2" s="198" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="193" t="s">
+      <c r="E2" s="196" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="189" t="s">
+      <c r="F2" s="192" t="s">
         <v>182</v>
       </c>
-      <c r="G2" s="189"/>
-      <c r="H2" s="189"/>
-      <c r="I2" s="190"/>
+      <c r="G2" s="192"/>
+      <c r="H2" s="192"/>
+      <c r="I2" s="193"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="192"/>
-      <c r="C3" s="196"/>
-      <c r="D3" s="196"/>
-      <c r="E3" s="194"/>
+      <c r="B3" s="195"/>
+      <c r="C3" s="199"/>
+      <c r="D3" s="199"/>
+      <c r="E3" s="197"/>
       <c r="F3" s="97" t="s">
         <v>114</v>
       </c>
@@ -14818,30 +14854,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="191" t="s">
+      <c r="B2" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="195" t="s">
+      <c r="C2" s="198" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="195" t="s">
+      <c r="D2" s="198" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="193" t="s">
+      <c r="E2" s="196" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="189" t="s">
+      <c r="F2" s="192" t="s">
         <v>224</v>
       </c>
-      <c r="G2" s="189"/>
-      <c r="H2" s="189"/>
-      <c r="I2" s="190"/>
+      <c r="G2" s="192"/>
+      <c r="H2" s="192"/>
+      <c r="I2" s="193"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="192"/>
-      <c r="C3" s="196"/>
-      <c r="D3" s="196"/>
-      <c r="E3" s="194"/>
+      <c r="B3" s="195"/>
+      <c r="C3" s="199"/>
+      <c r="D3" s="199"/>
+      <c r="E3" s="197"/>
       <c r="F3" s="97" t="s">
         <v>114</v>
       </c>
@@ -15225,30 +15261,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="191" t="s">
+      <c r="B2" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="195" t="s">
+      <c r="C2" s="198" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="195" t="s">
+      <c r="D2" s="198" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="193" t="s">
+      <c r="E2" s="196" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="189" t="s">
+      <c r="F2" s="192" t="s">
         <v>256</v>
       </c>
-      <c r="G2" s="189"/>
-      <c r="H2" s="189"/>
-      <c r="I2" s="190"/>
+      <c r="G2" s="192"/>
+      <c r="H2" s="192"/>
+      <c r="I2" s="193"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="192"/>
-      <c r="C3" s="196"/>
-      <c r="D3" s="196"/>
-      <c r="E3" s="194"/>
+      <c r="B3" s="195"/>
+      <c r="C3" s="199"/>
+      <c r="D3" s="199"/>
+      <c r="E3" s="197"/>
       <c r="F3" s="97" t="s">
         <v>277</v>
       </c>
@@ -15650,30 +15686,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="191" t="s">
+      <c r="B2" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="195" t="s">
+      <c r="C2" s="198" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="195" t="s">
+      <c r="D2" s="198" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="193" t="s">
+      <c r="E2" s="196" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="189" t="s">
+      <c r="F2" s="192" t="s">
         <v>276</v>
       </c>
-      <c r="G2" s="189"/>
-      <c r="H2" s="189"/>
-      <c r="I2" s="190"/>
+      <c r="G2" s="192"/>
+      <c r="H2" s="192"/>
+      <c r="I2" s="193"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="192"/>
-      <c r="C3" s="196"/>
-      <c r="D3" s="196"/>
-      <c r="E3" s="194"/>
+      <c r="B3" s="195"/>
+      <c r="C3" s="199"/>
+      <c r="D3" s="199"/>
+      <c r="E3" s="197"/>
       <c r="F3" s="97" t="s">
         <v>296</v>
       </c>
@@ -16090,31 +16126,31 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="191" t="s">
+      <c r="B2" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="195" t="s">
+      <c r="C2" s="198" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="195" t="s">
+      <c r="D2" s="198" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="193" t="s">
+      <c r="E2" s="196" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="189" t="s">
+      <c r="F2" s="192" t="s">
         <v>347</v>
       </c>
-      <c r="G2" s="189"/>
-      <c r="H2" s="189"/>
-      <c r="I2" s="197"/>
-      <c r="J2" s="190"/>
+      <c r="G2" s="192"/>
+      <c r="H2" s="192"/>
+      <c r="I2" s="200"/>
+      <c r="J2" s="193"/>
     </row>
     <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="192"/>
-      <c r="C3" s="196"/>
-      <c r="D3" s="196"/>
-      <c r="E3" s="194"/>
+      <c r="B3" s="195"/>
+      <c r="C3" s="199"/>
+      <c r="D3" s="199"/>
+      <c r="E3" s="197"/>
       <c r="F3" s="97" t="s">
         <v>346</v>
       </c>
@@ -16540,30 +16576,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="191" t="s">
+      <c r="B2" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="195" t="s">
+      <c r="C2" s="198" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="195" t="s">
+      <c r="D2" s="198" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="193" t="s">
+      <c r="E2" s="196" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="189" t="s">
+      <c r="F2" s="192" t="s">
         <v>373</v>
       </c>
-      <c r="G2" s="189"/>
-      <c r="H2" s="189"/>
-      <c r="I2" s="190"/>
+      <c r="G2" s="192"/>
+      <c r="H2" s="192"/>
+      <c r="I2" s="193"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="192"/>
-      <c r="C3" s="196"/>
-      <c r="D3" s="196"/>
-      <c r="E3" s="194"/>
+      <c r="B3" s="195"/>
+      <c r="C3" s="199"/>
+      <c r="D3" s="199"/>
+      <c r="E3" s="197"/>
       <c r="F3" s="97" t="s">
         <v>374</v>
       </c>
@@ -16577,7 +16613,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
       <c r="B4" s="151" t="s">
         <v>108</v>
       </c>
@@ -16590,12 +16626,16 @@
       <c r="E4" s="140" t="s">
         <v>140</v>
       </c>
-      <c r="F4" s="141"/>
-      <c r="G4" s="142"/>
+      <c r="F4" s="201" t="s">
+        <v>412</v>
+      </c>
+      <c r="G4" s="201" t="s">
+        <v>411</v>
+      </c>
       <c r="H4" s="88"/>
       <c r="I4" s="92"/>
     </row>
-    <row r="5" spans="1:9" ht="54" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
       <c r="B5" s="154" t="s">
         <v>181</v>
       </c>
@@ -16609,10 +16649,10 @@
         <v>161</v>
       </c>
       <c r="F5" s="123" t="s">
-        <v>357</v>
+        <v>408</v>
       </c>
       <c r="G5" s="123" t="s">
-        <v>392</v>
+        <v>409</v>
       </c>
       <c r="H5" s="123"/>
       <c r="I5" s="135"/>
@@ -16631,10 +16671,10 @@
         <v>161</v>
       </c>
       <c r="F6" s="123" t="s">
+        <v>397</v>
+      </c>
+      <c r="G6" s="123" t="s">
         <v>398</v>
-      </c>
-      <c r="G6" s="123" t="s">
-        <v>399</v>
       </c>
       <c r="H6" s="123"/>
       <c r="I6" s="135"/>
@@ -16650,13 +16690,13 @@
         <v>178</v>
       </c>
       <c r="E7" s="100" t="s">
-        <v>162</v>
+        <v>410</v>
       </c>
       <c r="F7" s="123" t="s">
         <v>386</v>
       </c>
       <c r="G7" s="105" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H7" s="89"/>
       <c r="I7" s="93"/>
@@ -16692,7 +16732,9 @@
       <c r="E9" s="91" t="s">
         <v>152</v>
       </c>
-      <c r="F9" s="114"/>
+      <c r="F9" s="114" t="s">
+        <v>405</v>
+      </c>
       <c r="G9" s="105"/>
       <c r="H9" s="138"/>
       <c r="I9" s="93"/>
@@ -16710,7 +16752,9 @@
       <c r="E10" s="91" t="s">
         <v>153</v>
       </c>
-      <c r="F10" s="114"/>
+      <c r="F10" s="114" t="s">
+        <v>405</v>
+      </c>
       <c r="G10" s="105"/>
       <c r="H10" s="89"/>
       <c r="I10" s="93"/>
@@ -16728,7 +16772,9 @@
       <c r="E11" s="91" t="s">
         <v>154</v>
       </c>
-      <c r="F11" s="114"/>
+      <c r="F11" s="114" t="s">
+        <v>406</v>
+      </c>
       <c r="G11" s="105"/>
       <c r="H11" s="89"/>
       <c r="I11" s="93"/>
@@ -16746,32 +16792,34 @@
       <c r="E12" s="91" t="s">
         <v>155</v>
       </c>
-      <c r="F12" s="114"/>
+      <c r="F12" s="114" t="s">
+        <v>407</v>
+      </c>
       <c r="G12" s="105"/>
       <c r="H12" s="138"/>
       <c r="I12" s="93"/>
     </row>
     <row r="13" spans="1:9" ht="94.5" x14ac:dyDescent="0.3">
       <c r="B13" s="132" t="s">
+        <v>399</v>
+      </c>
+      <c r="C13" s="117" t="s">
+        <v>402</v>
+      </c>
+      <c r="D13" s="117" t="s">
+        <v>403</v>
+      </c>
+      <c r="E13" s="91" t="s">
         <v>400</v>
       </c>
-      <c r="C13" s="117" t="s">
-        <v>403</v>
-      </c>
-      <c r="D13" s="117" t="s">
+      <c r="F13" s="123" t="s">
+        <v>401</v>
+      </c>
+      <c r="G13" s="182" t="s">
         <v>404</v>
       </c>
-      <c r="E13" s="91" t="s">
-        <v>401</v>
-      </c>
-      <c r="F13" s="123" t="s">
-        <v>402</v>
-      </c>
-      <c r="G13" s="198" t="s">
-        <v>405</v>
-      </c>
-      <c r="H13" s="199"/>
-      <c r="I13" s="200"/>
+      <c r="H13" s="183"/>
+      <c r="I13" s="184"/>
     </row>
     <row r="14" spans="1:9" ht="243" x14ac:dyDescent="0.3">
       <c r="B14" s="132" t="s">
@@ -16810,7 +16858,7 @@
         <v>389</v>
       </c>
       <c r="G15" s="157" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H15" s="105"/>
       <c r="I15" s="122"/>
@@ -16832,7 +16880,7 @@
         <v>387</v>
       </c>
       <c r="G16" s="157" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H16" s="157"/>
       <c r="I16" s="176"/>
@@ -16854,7 +16902,7 @@
         <v>391</v>
       </c>
       <c r="G17" s="157" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H17" s="157"/>
       <c r="I17" s="176"/>
@@ -16876,7 +16924,7 @@
         <v>388</v>
       </c>
       <c r="G18" s="169" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H18" s="169"/>
       <c r="I18" s="177"/>
@@ -16914,7 +16962,7 @@
         <v>263</v>
       </c>
       <c r="G20" s="157" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H20" s="133"/>
       <c r="I20" s="134"/>
@@ -16936,7 +16984,7 @@
         <v>263</v>
       </c>
       <c r="G21" s="106" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H21" s="180"/>
       <c r="I21" s="95"/>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Task\000_PJT\000_Heater\111_PTC\1.doc\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\일정\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="423">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -7636,40 +7636,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[임제훈 사원]
-1. 사이버 보안 관련 자료 회신 요청
-  [ 요청사항 ]
-    - 사이버 보안 QV와 동일한 이력으로 진행 요청 (공조시스템설계팀)
-    - BJ1 ES95489-21 성적서 회신
-    - 사이버보안관련성평가 작성 후 회신
-  [ 진행 및 검토 ]
-    - BJ1 ES95489-21, ESIR 때 성적서 없음
-      : QV 사이버 보안 협의 및 일정 지연으로 BJ1 ESIR때 진행 불가
-      : BJ1 ES95489-21 검증 진행
-    - 사이버보안관련성평가 작성 후 검토 요청</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[김진겸 사원]
-1. 국내 윈터 트립 (01/12 ~ 01/13)
-  [ 요청사항 ]
-    - 국내 윈터 트립 참석
-  [ 진행 및 검토 ]
-    - SVm P1(77호차) PTC 제어
-[임제훈 사원]
-1. ISIR 성적서 작성 (~02/12)
-  [ 요청사항 ]
-    - ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24 성적서
-  [ 진행 및 검토 ]
-    - 2월 중순까지 성적서 작성 완료
-    - ES90700-00 (100%)
-    - ES95411-00 (90%)
-    - ES95480-00 (100%)
-    - ES95489-21 (90%)
-    - ES95489-24 (90%)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">[임제훈 사원]
 1. </t>
@@ -8229,15 +8195,780 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>`[임제훈 사원]
-1. FAIL-SAFETY 로직 검증 (01/13)
+    <t>- 이슈 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 이슈 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 이슈 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 이슈 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고객사 요청</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 이슈 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- SWE.3 SDDS 후속 작업 (진행률 : 97%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- SWE.3 SDDS 후속 작업 (진행률 : 97%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Proto (진행 중)
+P1 (25/07/30)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">[조현진 전임]
+- LIN CheckList Application 작성 (진행률 : 70%)
+  : 번역 간 오역이나 스펙상 명확하지 않은 부분 TOA 통해 고객사와 협의
+- Heating Logic 수정
+  : 정격전압 동작범위(190~470)대로 동작하도록 변경완료(01/13)   </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[조현진 전임]
+- LIN CheckList Application 작성 (진행률 : 60%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- SWE.3 SDDS 후속 작업 (진행률 : 97%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 이슈 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. 사이버 보안 관련 자료 회신 요청
   [ 요청사항 ]
-    - 타 차종에서 문제 발생, BJ1 PTC FAIL-SAFETY 검증 및 결과 요청
+    - 사이버 보안 QV와 동일한 이력으로 진행 요청 (공조시스템설계팀)
+    - BJ1 ES95489-21 성적서 회신
+    - 사이버보안관련성평가 작성 후 회신
   [ 진행 및 검토 ]
-    - FAIL-SAFETY 로직 검증 완료
-     : S/W 문제 없음
-    - 검증 결과 회신 완료
-2. ISIR 성적서 작성 (~02/12)
+    - BJ1 ES95489-21, ESIR 때 성적서 없음
+      : QV 사이버 보안 협의 및 일정 지연으로 BJ1 ESIR때 진행 불가
+      : BJ1 ES95489-21 검증 진행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. HVAC 2EA 수령 (01/19)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 이슈 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. AY RHD Pilot 차량 실차 검증
+  [ 요청사항 ]
+    - AY RHD Pilot 차량 실차 검증
+  [ 진행 및 검토 ]
+    - 일정 미정
+     : 3월 ~ 4월 예상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NX5e C518 차량 PTC 리워크 (01/12)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 요청사항 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>국내 트립에서 문제 발생</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PTC 교체 요청</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 진행 및 검토 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Proto 사양 PTC로 교체 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>고품으로 나온 PTC 칼로리미터 검증 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>차량에서 Core Temp가 내려가지 않던 현상 없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PTC 단품 정상 상태 및 동작 확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S/W 설계 변경 (01/13)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 안건 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>변경점 반영된 최종 S/W 설계 변경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 진행 및 검토 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S/W 로직 검증 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S/W 문제 없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>설계변경 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NX5e FATC 테스트 진행 (01/15)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 안건 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>열에너지차량시험팀, 한온시스템 1월 15일 (목) FATC 테스트 진행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 진행 및 검토 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>우리산업 참석 예정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>동행자 EV HTR 개발팀 강상용 책임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>외부 환경으로 인해 PTC 영향이 있는지 분석</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>엔진 열 영향 확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HVAC 덕트 구조 확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HVAC 풍량이 PTC에 영향을 끼치는지 확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+4. 고객사 사이버 보안 기능 품확 활동 (~01/30)
+  [ 요청사항 ]
+    - 품확 진행 샘플
+  [ 진행 및 검토 ]
+    - 사이버보안품질연구팀에 보낼 샘플 준비
+     : PCB 1EA, Signal Connector 1EA, E2 Pin Connector 1EA</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. 실차 예상 문제점 의견 제시 (01/20)
+  [ 상황 ]
+    - FATC 테스트 결과 기반 예상 문제점 발견
+  [ 진행 및 검토 ]
+    - 공조시스템설계팀 정재근 책임 연구원에게 의견 제기
+     : 냉각수 온도가 Heater에 미치는 영향성
+    - 현 상황 인지하였고 전체 메일 발송 예정 (HKMC 공조시스템설계팀)
+2. 고객사 사이버 보안 기능 품확 활동 (~01/30)
+  [ 요청사항 ]
+    - 품확 진행 샘플
+  [ 진행 및 검토 ]
+    - 사이버보안품질연구팀에 보낼 샘플 준비
+     : PCB 1EA, Signal Connector 1EA, E2 Pin Connector 1EA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. PTC 제어 방향 문의 (~1/23)
+  [ 요청 사항 ]
+    - PTC Target Duty 수신 시 로직 (공조시스템설계팀 한별 책임 연구원)
+  [ 진행 및 검토 ]
+    - 급격한 Target Duty 변화 수신 (예시 80% → 40%)
+    - 급격한 Target Duty OFF 수신 (예시 80% → 0% (OFF))</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. PTC 제어 방향 문의 (~1/23)
+  [ 요청 사항 ]
+    - PTC Target Duty 수신 시 로직 (공조시스템설계팀 한별 책임 연구원)
+  [ 진행 및 검토 ]
+    - 급격한 Target Duty 변화 수신 (예시 80% → 40%)
+    - 급격한 Target Duty OFF 수신 (예시 80% → 0% (OFF))</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. ISIR 성적서 작성 (~2/12)
+  [ 요청사항 ]
+    - ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24 성적서
+  [ 진행 및 검토 ]
+    - 2월 중순까지 성적서 작성 완료
+    - ES90700-00 (100%)
+    - ES95411-00 (90%)
+    - ES95480-00 (100%)
+    - ES95489-21 (90%)
+    - ES95489-24 (90%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[김진겸 사원]
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>국내 윈터 트립 (01/12 ~ 01/13)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 요청사항 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>국내 윈터 트립 참석</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 진행 및 검토 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SVm P1(77호차) PTC 제어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+[임제훈 사원]
+1. ISIR 성적서 작성 (~2/12)
+  [ 요청사항 ]
+    - ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24 성적서
+  [ 진행 및 검토 ]
+    - 2월 중순까지 성적서 작성 완료
+    - ES90700-00 (100%)
+    - ES95411-00 (90%)
+    - ES95480-00 (100%)
+    - ES95489-21 (90%)
+    - ES95489-24 (90%)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. ATCU, HVAC, PTC 합동 벤치 테스트 (~2/6)
+  [ 요청사항 ]
+    - ATCU, HVAC, PTC 간 신호 정합성 및 로직 정합성 검증
+  [ 진행 및 검토 ]
+    - Fault 시뮬레이션 3개 항목
+     : Current Sensor Fault
+     : IGBT Open / Short Fault
+     : Over Current
+    - 타 항목은 벤치 테스트 진행하며 검증
+     : Sensor Fault (Open, Short 스위치 회로 준비 H/W)
+     : Low Voltage Protection
+     : High Voltage Protection
+     : Interlock
+     : CAN Timeout
+     : Core Temp Over Fault
+2. ISIR 성적서 작성 (~2/12)
   [ 요청사항 ]
     - ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24 성적서
   [ 진행 및 검토 ]
@@ -8255,130 +8986,180 @@
   [ 진행 및 검토 ]
     - BJ1 ES95489-21, ESIR 때 성적서 없음
       : QV 사이버 보안 협의 및 일정 지연으로 BJ1 ESIR때 진행 불가
-      : BJ1 ES95489-21 검증 진행
-    - 사이버보안관련성평가 작성 후 검토 요청</t>
+      : BJ1 ES95489-21 검증 진행</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[임제훈 사원]
-1. NX5e C518 차량 PTC 리워크 (01/12)
+1. 최대 난방 평가 성능 미달로 인한 성능 증대 계획 (~1/29)
   [ 요청사항 ]
-    - 국내 트립에서 문제 발생
-     : PTC 교체 요청
+    - SP1 적용 S/W 튜닝
   [ 진행 및 검토 ]
-    - Proto 사양 PTC로 교체 완료
-    - 고품으로 나온 PTC 칼로리미터 검증 완료
-     : 차량에서 Core Temp가 내려가지 않던 현상 없음
-     : PTC 단품 정상 상태 및 동작 확인
-2. S/W 설계 변경 (01/13)
-  [ 안건 ]
-    - 변경점 반영된 최종 S/W 설계 변경
+    - HVAC 수령 (1/20)
+    - MX5a 샘플 수령 (1/20)
+    - S/W 성능 튜닝 완료 (1/20)
+      : 전압 범위 변경
+      : LINEAR MAX Zone 당 4300W, Total 8600W 변경
+    - S/W 성능 튜닝 결과
+      : -30℃, 풍량 300kph 환경
+      : 최대 전력 21초 소요, IGBT 100% 도달 81초 소요
+      : 60초 IGBT 80% 도달
+      : 60초 ~ 81초 성능 7452W → 7480W
+    - R로직 튜닝 (~1/29)
+      : TC 변경건으로 인한 R로직 재튜닝
+2. 최대 난방 평가 재진행 (~2/5)
+  [ 요청사항 ]
+    - 최대 난방 평가
   [ 진행 및 검토 ]
-    - S/W 로직 검증 완료
-     : S/W 문제 없음
-    - 설계변경 완료
-3. NX5e FATC 테스트 진행 (01/15)
-  [ 안건 ]
-    - 열에너지차량시험팀, 한온시스템 1월 15일 (목) FATC 테스트 진행
+    - 2월 첫째 주 최대 난방 평가 예정
+      : S/W 성능 튜닝 완료되면 차주 진행 제안 (기구팀)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">`[임제훈 사원]
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FAIL-SAFETY 로직 검증 (01/13)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 요청사항 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>타 차종에서 문제 발생, BJ1 PTC FAIL-SAFETY 검증 및 결과 요청</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
   [ 진행 및 검토 ]
-    - 우리산업 참석 예정
-     : 동행자 EV HTR 개발팀 강상용 책임
-    - 외부 환경으로 인해 PTC 영향이 있는지 분석
-     : 엔진 열 영향 확인
-     : HVAC 덕트 구조 확인
-     : HVAC 풍량이 PTC에 영향을 끼치는지 확인
-4. 고객사 사이버 보안 기능 품확 활동 (~01/30)
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FAIL-SAFETY 로직 검증 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S/W 문제 없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>검증 결과 회신 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. ISIR 성적서 작성 (~2/12)
   [ 요청사항 ]
-    - 품확 진행 샘플
+    - ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24 성적서
   [ 진행 및 검토 ]
-    - 사이버보안품질연구팀에 보낼 샘플 준비
-     : PCB 1EA, Signal Connector 1EA, E2 Pin Connector 1EA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 이슈 없음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 이슈 없음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 이슈 없음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 이슈 없음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고객사 요청</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 이슈 없음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-1. PTC 제어 방향 문의 (~01/16)
-  [ 요청 사항 ]
-    - PTC Target Duty 수신 시 로직 (공조시스템설계팀 한별 책임 연구원)
+    - 2월 중순까지 성적서 작성 완료
+    - ES90700-00 (100%)
+    - ES95411-00 (90%)
+    - ES95480-00 (100%)
+    - ES95489-21 (90%)
+    - ES95489-24 (90%)
+3. 사이버 보안 관련 자료 회신 요청
+  [ 요청사항 ]
+    - 사이버 보안 QV와 동일한 이력으로 진행 요청 (공조시스템설계팀)
+    - BJ1 ES95489-21 성적서 회신
+    - 사이버보안관련성평가 작성 후 회신
   [ 진행 및 검토 ]
-    - 급격한 Target Duty 변화 수신 (예시 80% → 40%)
-    - 급격한 Target Duty OFF 수신 (예시 80% → 0% (OFF))</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- SWE.3 SDDS 후속 작업 (진행률 : 97%)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-- SWE.3 SDDS 후속 작업 (진행률 : 97%)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Proto (진행 중)
-P1 (25/07/30)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">[조현진 전임]
-- LIN CheckList Application 작성 (진행률 : 70%)
-  : 번역 간 오역이나 스펙상 명확하지 않은 부분 TOA 통해 고객사와 협의
-- Heating Logic 수정
-  : 정격전압 동작범위(190~470)대로 동작하도록 변경완료(01/13)   </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[조현진 전임]
-- LIN CheckList Application 작성 (진행률 : 60%)</t>
+    - BJ1 ES95489-21, ESIR 때 성적서 없음
+      : QV 사이버 보안 협의 및 일정 지연으로 BJ1 ESIR때 진행 불가
+      : BJ1 ES95489-21 검증 진행</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10394,21 +11175,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="81" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -10457,8 +11235,11 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="88" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -11125,90 +11906,90 @@
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="185" t="s">
+      <c r="B2" s="184" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="187" t="s">
+      <c r="C2" s="186" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="187" t="s">
+      <c r="D2" s="186" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="191">
+      <c r="E2" s="190">
         <v>23</v>
       </c>
-      <c r="F2" s="189"/>
-      <c r="G2" s="189"/>
-      <c r="H2" s="189"/>
-      <c r="I2" s="189"/>
-      <c r="J2" s="189"/>
-      <c r="K2" s="189"/>
-      <c r="L2" s="189"/>
-      <c r="M2" s="189"/>
-      <c r="N2" s="189"/>
-      <c r="O2" s="189"/>
-      <c r="P2" s="189"/>
-      <c r="Q2" s="189">
+      <c r="F2" s="188"/>
+      <c r="G2" s="188"/>
+      <c r="H2" s="188"/>
+      <c r="I2" s="188"/>
+      <c r="J2" s="188"/>
+      <c r="K2" s="188"/>
+      <c r="L2" s="188"/>
+      <c r="M2" s="188"/>
+      <c r="N2" s="188"/>
+      <c r="O2" s="188"/>
+      <c r="P2" s="188"/>
+      <c r="Q2" s="188">
         <v>24</v>
       </c>
-      <c r="R2" s="189"/>
-      <c r="S2" s="189"/>
-      <c r="T2" s="189"/>
-      <c r="U2" s="189"/>
-      <c r="V2" s="189"/>
-      <c r="W2" s="189"/>
-      <c r="X2" s="189"/>
-      <c r="Y2" s="189"/>
-      <c r="Z2" s="189"/>
-      <c r="AA2" s="189"/>
-      <c r="AB2" s="189"/>
-      <c r="AC2" s="189">
+      <c r="R2" s="188"/>
+      <c r="S2" s="188"/>
+      <c r="T2" s="188"/>
+      <c r="U2" s="188"/>
+      <c r="V2" s="188"/>
+      <c r="W2" s="188"/>
+      <c r="X2" s="188"/>
+      <c r="Y2" s="188"/>
+      <c r="Z2" s="188"/>
+      <c r="AA2" s="188"/>
+      <c r="AB2" s="188"/>
+      <c r="AC2" s="188">
         <v>25</v>
       </c>
-      <c r="AD2" s="189"/>
-      <c r="AE2" s="189"/>
-      <c r="AF2" s="189"/>
-      <c r="AG2" s="189"/>
-      <c r="AH2" s="189"/>
-      <c r="AI2" s="189"/>
-      <c r="AJ2" s="189"/>
-      <c r="AK2" s="189"/>
-      <c r="AL2" s="189"/>
-      <c r="AM2" s="189"/>
-      <c r="AN2" s="189"/>
-      <c r="AO2" s="189">
+      <c r="AD2" s="188"/>
+      <c r="AE2" s="188"/>
+      <c r="AF2" s="188"/>
+      <c r="AG2" s="188"/>
+      <c r="AH2" s="188"/>
+      <c r="AI2" s="188"/>
+      <c r="AJ2" s="188"/>
+      <c r="AK2" s="188"/>
+      <c r="AL2" s="188"/>
+      <c r="AM2" s="188"/>
+      <c r="AN2" s="188"/>
+      <c r="AO2" s="188">
         <v>26</v>
       </c>
-      <c r="AP2" s="189"/>
-      <c r="AQ2" s="189"/>
-      <c r="AR2" s="189"/>
-      <c r="AS2" s="189"/>
-      <c r="AT2" s="189"/>
-      <c r="AU2" s="189"/>
-      <c r="AV2" s="189"/>
-      <c r="AW2" s="189"/>
-      <c r="AX2" s="189"/>
-      <c r="AY2" s="189"/>
-      <c r="AZ2" s="190"/>
-      <c r="BA2" s="189">
+      <c r="AP2" s="188"/>
+      <c r="AQ2" s="188"/>
+      <c r="AR2" s="188"/>
+      <c r="AS2" s="188"/>
+      <c r="AT2" s="188"/>
+      <c r="AU2" s="188"/>
+      <c r="AV2" s="188"/>
+      <c r="AW2" s="188"/>
+      <c r="AX2" s="188"/>
+      <c r="AY2" s="188"/>
+      <c r="AZ2" s="189"/>
+      <c r="BA2" s="188">
         <v>27</v>
       </c>
-      <c r="BB2" s="189"/>
-      <c r="BC2" s="189"/>
-      <c r="BD2" s="189"/>
-      <c r="BE2" s="189"/>
-      <c r="BF2" s="189"/>
-      <c r="BG2" s="189"/>
-      <c r="BH2" s="189"/>
-      <c r="BI2" s="189"/>
-      <c r="BJ2" s="189"/>
-      <c r="BK2" s="189"/>
-      <c r="BL2" s="190"/>
+      <c r="BB2" s="188"/>
+      <c r="BC2" s="188"/>
+      <c r="BD2" s="188"/>
+      <c r="BE2" s="188"/>
+      <c r="BF2" s="188"/>
+      <c r="BG2" s="188"/>
+      <c r="BH2" s="188"/>
+      <c r="BI2" s="188"/>
+      <c r="BJ2" s="188"/>
+      <c r="BK2" s="188"/>
+      <c r="BL2" s="189"/>
     </row>
     <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="186"/>
-      <c r="C3" s="188"/>
-      <c r="D3" s="188"/>
+      <c r="B3" s="185"/>
+      <c r="C3" s="187"/>
+      <c r="D3" s="187"/>
       <c r="E3" s="22">
         <v>1</v>
       </c>
@@ -12526,7 +13307,7 @@
       </c>
       <c r="AX17" s="30"/>
       <c r="AY17" s="41"/>
-      <c r="AZ17" s="181" t="s">
+      <c r="AZ17" s="180" t="s">
         <v>381</v>
       </c>
       <c r="BA17" s="47"/>
@@ -13148,31 +13929,31 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="194" t="s">
+      <c r="B2" s="193" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="198" t="s">
+      <c r="C2" s="197" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="198" t="s">
+      <c r="D2" s="197" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="196" t="s">
+      <c r="E2" s="195" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="192" t="s">
+      <c r="F2" s="191" t="s">
         <v>378</v>
       </c>
-      <c r="G2" s="192"/>
-      <c r="H2" s="192"/>
-      <c r="I2" s="200"/>
-      <c r="J2" s="193"/>
+      <c r="G2" s="191"/>
+      <c r="H2" s="191"/>
+      <c r="I2" s="199"/>
+      <c r="J2" s="192"/>
     </row>
     <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="195"/>
-      <c r="C3" s="199"/>
-      <c r="D3" s="199"/>
-      <c r="E3" s="197"/>
+      <c r="B3" s="194"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="196"/>
       <c r="F3" s="97" t="s">
         <v>379</v>
       </c>
@@ -13678,39 +14459,39 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="194" t="s">
+      <c r="B2" s="193" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="198" t="s">
+      <c r="C2" s="197" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="198" t="s">
+      <c r="D2" s="197" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="196" t="s">
+      <c r="E2" s="195" t="s">
         <v>126</v>
       </c>
       <c r="F2" s="96" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="192" t="s">
+      <c r="G2" s="191" t="s">
         <v>113</v>
       </c>
-      <c r="H2" s="192"/>
-      <c r="I2" s="192"/>
-      <c r="J2" s="193"/>
-      <c r="K2" s="192" t="s">
+      <c r="H2" s="191"/>
+      <c r="I2" s="191"/>
+      <c r="J2" s="192"/>
+      <c r="K2" s="191" t="s">
         <v>182</v>
       </c>
-      <c r="L2" s="192"/>
-      <c r="M2" s="192"/>
-      <c r="N2" s="193"/>
+      <c r="L2" s="191"/>
+      <c r="M2" s="191"/>
+      <c r="N2" s="192"/>
     </row>
     <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="195"/>
-      <c r="C3" s="199"/>
-      <c r="D3" s="199"/>
-      <c r="E3" s="197"/>
+      <c r="B3" s="194"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="196"/>
       <c r="F3" s="97" t="s">
         <v>111</v>
       </c>
@@ -14453,30 +15234,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="194" t="s">
+      <c r="B2" s="193" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="198" t="s">
+      <c r="C2" s="197" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="198" t="s">
+      <c r="D2" s="197" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="196" t="s">
+      <c r="E2" s="195" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="192" t="s">
+      <c r="F2" s="191" t="s">
         <v>182</v>
       </c>
-      <c r="G2" s="192"/>
-      <c r="H2" s="192"/>
-      <c r="I2" s="193"/>
+      <c r="G2" s="191"/>
+      <c r="H2" s="191"/>
+      <c r="I2" s="192"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="195"/>
-      <c r="C3" s="199"/>
-      <c r="D3" s="199"/>
-      <c r="E3" s="197"/>
+      <c r="B3" s="194"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="196"/>
       <c r="F3" s="97" t="s">
         <v>114</v>
       </c>
@@ -14854,30 +15635,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="194" t="s">
+      <c r="B2" s="193" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="198" t="s">
+      <c r="C2" s="197" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="198" t="s">
+      <c r="D2" s="197" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="196" t="s">
+      <c r="E2" s="195" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="192" t="s">
+      <c r="F2" s="191" t="s">
         <v>224</v>
       </c>
-      <c r="G2" s="192"/>
-      <c r="H2" s="192"/>
-      <c r="I2" s="193"/>
+      <c r="G2" s="191"/>
+      <c r="H2" s="191"/>
+      <c r="I2" s="192"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="195"/>
-      <c r="C3" s="199"/>
-      <c r="D3" s="199"/>
-      <c r="E3" s="197"/>
+      <c r="B3" s="194"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="196"/>
       <c r="F3" s="97" t="s">
         <v>114</v>
       </c>
@@ -15261,30 +16042,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="194" t="s">
+      <c r="B2" s="193" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="198" t="s">
+      <c r="C2" s="197" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="198" t="s">
+      <c r="D2" s="197" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="196" t="s">
+      <c r="E2" s="195" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="192" t="s">
+      <c r="F2" s="191" t="s">
         <v>256</v>
       </c>
-      <c r="G2" s="192"/>
-      <c r="H2" s="192"/>
-      <c r="I2" s="193"/>
+      <c r="G2" s="191"/>
+      <c r="H2" s="191"/>
+      <c r="I2" s="192"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="195"/>
-      <c r="C3" s="199"/>
-      <c r="D3" s="199"/>
-      <c r="E3" s="197"/>
+      <c r="B3" s="194"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="196"/>
       <c r="F3" s="97" t="s">
         <v>277</v>
       </c>
@@ -15686,30 +16467,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="194" t="s">
+      <c r="B2" s="193" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="198" t="s">
+      <c r="C2" s="197" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="198" t="s">
+      <c r="D2" s="197" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="196" t="s">
+      <c r="E2" s="195" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="192" t="s">
+      <c r="F2" s="191" t="s">
         <v>276</v>
       </c>
-      <c r="G2" s="192"/>
-      <c r="H2" s="192"/>
-      <c r="I2" s="193"/>
+      <c r="G2" s="191"/>
+      <c r="H2" s="191"/>
+      <c r="I2" s="192"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="195"/>
-      <c r="C3" s="199"/>
-      <c r="D3" s="199"/>
-      <c r="E3" s="197"/>
+      <c r="B3" s="194"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="196"/>
       <c r="F3" s="97" t="s">
         <v>296</v>
       </c>
@@ -16126,31 +16907,31 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="194" t="s">
+      <c r="B2" s="193" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="198" t="s">
+      <c r="C2" s="197" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="198" t="s">
+      <c r="D2" s="197" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="196" t="s">
+      <c r="E2" s="195" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="192" t="s">
+      <c r="F2" s="191" t="s">
         <v>347</v>
       </c>
-      <c r="G2" s="192"/>
-      <c r="H2" s="192"/>
-      <c r="I2" s="200"/>
-      <c r="J2" s="193"/>
+      <c r="G2" s="191"/>
+      <c r="H2" s="191"/>
+      <c r="I2" s="199"/>
+      <c r="J2" s="192"/>
     </row>
     <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="195"/>
-      <c r="C3" s="199"/>
-      <c r="D3" s="199"/>
-      <c r="E3" s="197"/>
+      <c r="B3" s="194"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="196"/>
       <c r="F3" s="97" t="s">
         <v>346</v>
       </c>
@@ -16576,30 +17357,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="194" t="s">
+      <c r="B2" s="193" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="198" t="s">
+      <c r="C2" s="197" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="198" t="s">
+      <c r="D2" s="197" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="196" t="s">
+      <c r="E2" s="195" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="192" t="s">
+      <c r="F2" s="191" t="s">
         <v>373</v>
       </c>
-      <c r="G2" s="192"/>
-      <c r="H2" s="192"/>
-      <c r="I2" s="193"/>
+      <c r="G2" s="191"/>
+      <c r="H2" s="191"/>
+      <c r="I2" s="192"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="195"/>
-      <c r="C3" s="199"/>
-      <c r="D3" s="199"/>
-      <c r="E3" s="197"/>
+      <c r="B3" s="194"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="196"/>
       <c r="F3" s="97" t="s">
         <v>374</v>
       </c>
@@ -16626,11 +17407,11 @@
       <c r="E4" s="140" t="s">
         <v>140</v>
       </c>
-      <c r="F4" s="201" t="s">
-        <v>412</v>
-      </c>
-      <c r="G4" s="201" t="s">
-        <v>411</v>
+      <c r="F4" s="183" t="s">
+        <v>407</v>
+      </c>
+      <c r="G4" s="183" t="s">
+        <v>406</v>
       </c>
       <c r="H4" s="88"/>
       <c r="I4" s="92"/>
@@ -16649,12 +17430,14 @@
         <v>161</v>
       </c>
       <c r="F5" s="123" t="s">
+        <v>403</v>
+      </c>
+      <c r="G5" s="123" t="s">
+        <v>404</v>
+      </c>
+      <c r="H5" s="123" t="s">
         <v>408</v>
       </c>
-      <c r="G5" s="123" t="s">
-        <v>409</v>
-      </c>
-      <c r="H5" s="123"/>
       <c r="I5" s="135"/>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -16671,15 +17454,17 @@
         <v>161</v>
       </c>
       <c r="F6" s="123" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="G6" s="123" t="s">
-        <v>398</v>
-      </c>
-      <c r="H6" s="123"/>
+        <v>394</v>
+      </c>
+      <c r="H6" s="123" t="s">
+        <v>409</v>
+      </c>
       <c r="I6" s="135"/>
     </row>
-    <row r="7" spans="1:9" ht="162" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="310.5" x14ac:dyDescent="0.3">
       <c r="B7" s="152" t="s">
         <v>75</v>
       </c>
@@ -16690,15 +17475,17 @@
         <v>178</v>
       </c>
       <c r="E7" s="100" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="F7" s="123" t="s">
         <v>386</v>
       </c>
       <c r="G7" s="105" t="s">
-        <v>392</v>
-      </c>
-      <c r="H7" s="89"/>
+        <v>390</v>
+      </c>
+      <c r="H7" s="105" t="s">
+        <v>421</v>
+      </c>
       <c r="I7" s="93"/>
     </row>
     <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -16733,7 +17520,7 @@
         <v>152</v>
       </c>
       <c r="F9" s="114" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G9" s="105"/>
       <c r="H9" s="138"/>
@@ -16753,7 +17540,7 @@
         <v>153</v>
       </c>
       <c r="F10" s="114" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G10" s="105"/>
       <c r="H10" s="89"/>
@@ -16773,7 +17560,7 @@
         <v>154</v>
       </c>
       <c r="F11" s="114" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="G11" s="105"/>
       <c r="H11" s="89"/>
@@ -16793,7 +17580,7 @@
         <v>155</v>
       </c>
       <c r="F12" s="114" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="G12" s="105"/>
       <c r="H12" s="138"/>
@@ -16801,25 +17588,27 @@
     </row>
     <row r="13" spans="1:9" ht="94.5" x14ac:dyDescent="0.3">
       <c r="B13" s="132" t="s">
+        <v>395</v>
+      </c>
+      <c r="C13" s="117" t="s">
+        <v>398</v>
+      </c>
+      <c r="D13" s="117" t="s">
         <v>399</v>
       </c>
-      <c r="C13" s="117" t="s">
-        <v>402</v>
-      </c>
-      <c r="D13" s="117" t="s">
-        <v>403</v>
-      </c>
       <c r="E13" s="91" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="F13" s="123" t="s">
-        <v>401</v>
-      </c>
-      <c r="G13" s="182" t="s">
-        <v>404</v>
-      </c>
-      <c r="H13" s="183"/>
-      <c r="I13" s="184"/>
+        <v>397</v>
+      </c>
+      <c r="G13" s="181" t="s">
+        <v>416</v>
+      </c>
+      <c r="H13" s="200" t="s">
+        <v>417</v>
+      </c>
+      <c r="I13" s="182"/>
     </row>
     <row r="14" spans="1:9" ht="243" x14ac:dyDescent="0.3">
       <c r="B14" s="132" t="s">
@@ -16836,12 +17625,14 @@
       </c>
       <c r="F14" s="105"/>
       <c r="G14" s="157" t="s">
-        <v>390</v>
-      </c>
-      <c r="H14" s="105"/>
+        <v>419</v>
+      </c>
+      <c r="H14" s="105" t="s">
+        <v>418</v>
+      </c>
       <c r="I14" s="122"/>
     </row>
-    <row r="15" spans="1:9" ht="378" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
       <c r="B15" s="131" t="s">
         <v>73</v>
       </c>
@@ -16855,12 +17646,14 @@
         <v>261</v>
       </c>
       <c r="F15" s="105" t="s">
-        <v>389</v>
+        <v>410</v>
       </c>
       <c r="G15" s="157" t="s">
-        <v>393</v>
-      </c>
-      <c r="H15" s="105"/>
+        <v>422</v>
+      </c>
+      <c r="H15" s="105" t="s">
+        <v>420</v>
+      </c>
       <c r="I15" s="122"/>
     </row>
     <row r="16" spans="1:9" ht="108" x14ac:dyDescent="0.3">
@@ -16880,9 +17673,11 @@
         <v>387</v>
       </c>
       <c r="G16" s="157" t="s">
-        <v>397</v>
-      </c>
-      <c r="H16" s="157"/>
+        <v>393</v>
+      </c>
+      <c r="H16" s="157" t="s">
+        <v>413</v>
+      </c>
       <c r="I16" s="176"/>
     </row>
     <row r="17" spans="2:9" ht="409.5" x14ac:dyDescent="0.3">
@@ -16899,12 +17694,14 @@
         <v>262</v>
       </c>
       <c r="F17" s="105" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="G17" s="157" t="s">
-        <v>394</v>
-      </c>
-      <c r="H17" s="157"/>
+        <v>414</v>
+      </c>
+      <c r="H17" s="157" t="s">
+        <v>415</v>
+      </c>
       <c r="I17" s="176"/>
     </row>
     <row r="18" spans="2:9" ht="108" x14ac:dyDescent="0.3">
@@ -16924,9 +17721,11 @@
         <v>388</v>
       </c>
       <c r="G18" s="169" t="s">
-        <v>397</v>
-      </c>
-      <c r="H18" s="169"/>
+        <v>393</v>
+      </c>
+      <c r="H18" s="169" t="s">
+        <v>411</v>
+      </c>
       <c r="I18" s="177"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
@@ -16962,9 +17761,11 @@
         <v>263</v>
       </c>
       <c r="G20" s="157" t="s">
-        <v>395</v>
-      </c>
-      <c r="H20" s="133"/>
+        <v>391</v>
+      </c>
+      <c r="H20" s="105" t="s">
+        <v>412</v>
+      </c>
       <c r="I20" s="134"/>
     </row>
     <row r="21" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -16984,9 +17785,11 @@
         <v>263</v>
       </c>
       <c r="G21" s="106" t="s">
-        <v>396</v>
-      </c>
-      <c r="H21" s="180"/>
+        <v>392</v>
+      </c>
+      <c r="H21" s="201" t="s">
+        <v>409</v>
+      </c>
       <c r="I21" s="95"/>
     </row>
     <row r="22" spans="2:9" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -8990,32 +8990,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[임제훈 사원]
-1. 최대 난방 평가 성능 미달로 인한 성능 증대 계획 (~1/29)
-  [ 요청사항 ]
-    - SP1 적용 S/W 튜닝
-  [ 진행 및 검토 ]
-    - HVAC 수령 (1/20)
-    - MX5a 샘플 수령 (1/20)
-    - S/W 성능 튜닝 완료 (1/20)
-      : 전압 범위 변경
-      : LINEAR MAX Zone 당 4300W, Total 8600W 변경
-    - S/W 성능 튜닝 결과
-      : -30℃, 풍량 300kph 환경
-      : 최대 전력 21초 소요, IGBT 100% 도달 81초 소요
-      : 60초 IGBT 80% 도달
-      : 60초 ~ 81초 성능 7452W → 7480W
-    - R로직 튜닝 (~1/29)
-      : TC 변경건으로 인한 R로직 재튜닝
-2. 최대 난방 평가 재진행 (~2/5)
-  [ 요청사항 ]
-    - 최대 난방 평가
-  [ 진행 및 검토 ]
-    - 2월 첫째 주 최대 난방 평가 예정
-      : S/W 성능 튜닝 완료되면 차주 진행 제안 (기구팀)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">`[임제훈 사원]
 1. </t>
@@ -9160,6 +9134,32 @@
       : QV 사이버 보안 협의 및 일정 지연으로 BJ1 ESIR때 진행 불가
       : BJ1 ES95489-21 검증 진행</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. 최대 난방 평가 성능 미달로 인한 성능 증대 계획 (~1/29)
+  [ 요청사항 ]
+    - SP1 적용 S/W 튜닝
+  [ 진행 및 검토 ]
+    - HVAC 수령 (1/20)
+    - MX5a 샘플 수령 (1/20)
+    - S/W 성능 튜닝 완료 (1/20)
+      : 전압 범위 최소 작동 전압 268V Recovery 288V, 최대 640V, Recovery 620V
+      : LINEAR MAX Zone 당 4300W, Total 8600W 변경
+    - S/W 성능 튜닝 결과
+      : -30℃, 풍량 300kph 환경
+      : 최대 전력 21초 소요, IGBT 100% 도달 81초 소요
+      : 60초 IGBT 80% 도달
+      : 60초 ~ 81초 성능 7452W → 7480W
+    - R로직 튜닝 (~1/29)
+      : TC 변경건으로 인한 R로직 재튜닝
+2. 최대 난방 평가 재진행 (~2/5)
+  [ 요청사항 ]
+    - 최대 난방 평가
+  [ 진행 및 검토 ]
+    - 2월 첫째 주 최대 난방 평가 예정
+      : S/W 성능 튜닝 완료되면 차주 진행 제안 (기구팀)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11187,6 +11187,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="88" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -11234,12 +11240,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="88" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -11906,90 +11906,90 @@
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="184" t="s">
+      <c r="B2" s="186" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="186" t="s">
+      <c r="C2" s="188" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="186" t="s">
+      <c r="D2" s="188" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="190">
+      <c r="E2" s="192">
         <v>23</v>
       </c>
-      <c r="F2" s="188"/>
-      <c r="G2" s="188"/>
-      <c r="H2" s="188"/>
-      <c r="I2" s="188"/>
-      <c r="J2" s="188"/>
-      <c r="K2" s="188"/>
-      <c r="L2" s="188"/>
-      <c r="M2" s="188"/>
-      <c r="N2" s="188"/>
-      <c r="O2" s="188"/>
-      <c r="P2" s="188"/>
-      <c r="Q2" s="188">
+      <c r="F2" s="190"/>
+      <c r="G2" s="190"/>
+      <c r="H2" s="190"/>
+      <c r="I2" s="190"/>
+      <c r="J2" s="190"/>
+      <c r="K2" s="190"/>
+      <c r="L2" s="190"/>
+      <c r="M2" s="190"/>
+      <c r="N2" s="190"/>
+      <c r="O2" s="190"/>
+      <c r="P2" s="190"/>
+      <c r="Q2" s="190">
         <v>24</v>
       </c>
-      <c r="R2" s="188"/>
-      <c r="S2" s="188"/>
-      <c r="T2" s="188"/>
-      <c r="U2" s="188"/>
-      <c r="V2" s="188"/>
-      <c r="W2" s="188"/>
-      <c r="X2" s="188"/>
-      <c r="Y2" s="188"/>
-      <c r="Z2" s="188"/>
-      <c r="AA2" s="188"/>
-      <c r="AB2" s="188"/>
-      <c r="AC2" s="188">
+      <c r="R2" s="190"/>
+      <c r="S2" s="190"/>
+      <c r="T2" s="190"/>
+      <c r="U2" s="190"/>
+      <c r="V2" s="190"/>
+      <c r="W2" s="190"/>
+      <c r="X2" s="190"/>
+      <c r="Y2" s="190"/>
+      <c r="Z2" s="190"/>
+      <c r="AA2" s="190"/>
+      <c r="AB2" s="190"/>
+      <c r="AC2" s="190">
         <v>25</v>
       </c>
-      <c r="AD2" s="188"/>
-      <c r="AE2" s="188"/>
-      <c r="AF2" s="188"/>
-      <c r="AG2" s="188"/>
-      <c r="AH2" s="188"/>
-      <c r="AI2" s="188"/>
-      <c r="AJ2" s="188"/>
-      <c r="AK2" s="188"/>
-      <c r="AL2" s="188"/>
-      <c r="AM2" s="188"/>
-      <c r="AN2" s="188"/>
-      <c r="AO2" s="188">
+      <c r="AD2" s="190"/>
+      <c r="AE2" s="190"/>
+      <c r="AF2" s="190"/>
+      <c r="AG2" s="190"/>
+      <c r="AH2" s="190"/>
+      <c r="AI2" s="190"/>
+      <c r="AJ2" s="190"/>
+      <c r="AK2" s="190"/>
+      <c r="AL2" s="190"/>
+      <c r="AM2" s="190"/>
+      <c r="AN2" s="190"/>
+      <c r="AO2" s="190">
         <v>26</v>
       </c>
-      <c r="AP2" s="188"/>
-      <c r="AQ2" s="188"/>
-      <c r="AR2" s="188"/>
-      <c r="AS2" s="188"/>
-      <c r="AT2" s="188"/>
-      <c r="AU2" s="188"/>
-      <c r="AV2" s="188"/>
-      <c r="AW2" s="188"/>
-      <c r="AX2" s="188"/>
-      <c r="AY2" s="188"/>
-      <c r="AZ2" s="189"/>
-      <c r="BA2" s="188">
+      <c r="AP2" s="190"/>
+      <c r="AQ2" s="190"/>
+      <c r="AR2" s="190"/>
+      <c r="AS2" s="190"/>
+      <c r="AT2" s="190"/>
+      <c r="AU2" s="190"/>
+      <c r="AV2" s="190"/>
+      <c r="AW2" s="190"/>
+      <c r="AX2" s="190"/>
+      <c r="AY2" s="190"/>
+      <c r="AZ2" s="191"/>
+      <c r="BA2" s="190">
         <v>27</v>
       </c>
-      <c r="BB2" s="188"/>
-      <c r="BC2" s="188"/>
-      <c r="BD2" s="188"/>
-      <c r="BE2" s="188"/>
-      <c r="BF2" s="188"/>
-      <c r="BG2" s="188"/>
-      <c r="BH2" s="188"/>
-      <c r="BI2" s="188"/>
-      <c r="BJ2" s="188"/>
-      <c r="BK2" s="188"/>
-      <c r="BL2" s="189"/>
+      <c r="BB2" s="190"/>
+      <c r="BC2" s="190"/>
+      <c r="BD2" s="190"/>
+      <c r="BE2" s="190"/>
+      <c r="BF2" s="190"/>
+      <c r="BG2" s="190"/>
+      <c r="BH2" s="190"/>
+      <c r="BI2" s="190"/>
+      <c r="BJ2" s="190"/>
+      <c r="BK2" s="190"/>
+      <c r="BL2" s="191"/>
     </row>
     <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="185"/>
-      <c r="C3" s="187"/>
-      <c r="D3" s="187"/>
+      <c r="B3" s="187"/>
+      <c r="C3" s="189"/>
+      <c r="D3" s="189"/>
       <c r="E3" s="22">
         <v>1</v>
       </c>
@@ -13929,31 +13929,31 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="193" t="s">
+      <c r="B2" s="195" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="197" t="s">
+      <c r="C2" s="199" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="197" t="s">
+      <c r="D2" s="199" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="195" t="s">
+      <c r="E2" s="197" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="191" t="s">
+      <c r="F2" s="193" t="s">
         <v>378</v>
       </c>
-      <c r="G2" s="191"/>
-      <c r="H2" s="191"/>
-      <c r="I2" s="199"/>
-      <c r="J2" s="192"/>
+      <c r="G2" s="193"/>
+      <c r="H2" s="193"/>
+      <c r="I2" s="201"/>
+      <c r="J2" s="194"/>
     </row>
     <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="194"/>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="196"/>
+      <c r="B3" s="196"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="198"/>
       <c r="F3" s="97" t="s">
         <v>379</v>
       </c>
@@ -14459,39 +14459,39 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="193" t="s">
+      <c r="B2" s="195" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="197" t="s">
+      <c r="C2" s="199" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="197" t="s">
+      <c r="D2" s="199" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="195" t="s">
+      <c r="E2" s="197" t="s">
         <v>126</v>
       </c>
       <c r="F2" s="96" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="191" t="s">
+      <c r="G2" s="193" t="s">
         <v>113</v>
       </c>
-      <c r="H2" s="191"/>
-      <c r="I2" s="191"/>
-      <c r="J2" s="192"/>
-      <c r="K2" s="191" t="s">
+      <c r="H2" s="193"/>
+      <c r="I2" s="193"/>
+      <c r="J2" s="194"/>
+      <c r="K2" s="193" t="s">
         <v>182</v>
       </c>
-      <c r="L2" s="191"/>
-      <c r="M2" s="191"/>
-      <c r="N2" s="192"/>
+      <c r="L2" s="193"/>
+      <c r="M2" s="193"/>
+      <c r="N2" s="194"/>
     </row>
     <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="194"/>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="196"/>
+      <c r="B3" s="196"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="198"/>
       <c r="F3" s="97" t="s">
         <v>111</v>
       </c>
@@ -15234,30 +15234,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="193" t="s">
+      <c r="B2" s="195" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="197" t="s">
+      <c r="C2" s="199" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="197" t="s">
+      <c r="D2" s="199" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="195" t="s">
+      <c r="E2" s="197" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="191" t="s">
+      <c r="F2" s="193" t="s">
         <v>182</v>
       </c>
-      <c r="G2" s="191"/>
-      <c r="H2" s="191"/>
-      <c r="I2" s="192"/>
+      <c r="G2" s="193"/>
+      <c r="H2" s="193"/>
+      <c r="I2" s="194"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="194"/>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="196"/>
+      <c r="B3" s="196"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="198"/>
       <c r="F3" s="97" t="s">
         <v>114</v>
       </c>
@@ -15635,30 +15635,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="193" t="s">
+      <c r="B2" s="195" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="197" t="s">
+      <c r="C2" s="199" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="197" t="s">
+      <c r="D2" s="199" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="195" t="s">
+      <c r="E2" s="197" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="191" t="s">
+      <c r="F2" s="193" t="s">
         <v>224</v>
       </c>
-      <c r="G2" s="191"/>
-      <c r="H2" s="191"/>
-      <c r="I2" s="192"/>
+      <c r="G2" s="193"/>
+      <c r="H2" s="193"/>
+      <c r="I2" s="194"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="194"/>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="196"/>
+      <c r="B3" s="196"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="198"/>
       <c r="F3" s="97" t="s">
         <v>114</v>
       </c>
@@ -16042,30 +16042,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="193" t="s">
+      <c r="B2" s="195" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="197" t="s">
+      <c r="C2" s="199" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="197" t="s">
+      <c r="D2" s="199" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="195" t="s">
+      <c r="E2" s="197" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="191" t="s">
+      <c r="F2" s="193" t="s">
         <v>256</v>
       </c>
-      <c r="G2" s="191"/>
-      <c r="H2" s="191"/>
-      <c r="I2" s="192"/>
+      <c r="G2" s="193"/>
+      <c r="H2" s="193"/>
+      <c r="I2" s="194"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="194"/>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="196"/>
+      <c r="B3" s="196"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="198"/>
       <c r="F3" s="97" t="s">
         <v>277</v>
       </c>
@@ -16467,30 +16467,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="193" t="s">
+      <c r="B2" s="195" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="197" t="s">
+      <c r="C2" s="199" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="197" t="s">
+      <c r="D2" s="199" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="195" t="s">
+      <c r="E2" s="197" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="191" t="s">
+      <c r="F2" s="193" t="s">
         <v>276</v>
       </c>
-      <c r="G2" s="191"/>
-      <c r="H2" s="191"/>
-      <c r="I2" s="192"/>
+      <c r="G2" s="193"/>
+      <c r="H2" s="193"/>
+      <c r="I2" s="194"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="194"/>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="196"/>
+      <c r="B3" s="196"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="198"/>
       <c r="F3" s="97" t="s">
         <v>296</v>
       </c>
@@ -16907,31 +16907,31 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="193" t="s">
+      <c r="B2" s="195" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="197" t="s">
+      <c r="C2" s="199" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="197" t="s">
+      <c r="D2" s="199" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="195" t="s">
+      <c r="E2" s="197" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="191" t="s">
+      <c r="F2" s="193" t="s">
         <v>347</v>
       </c>
-      <c r="G2" s="191"/>
-      <c r="H2" s="191"/>
-      <c r="I2" s="199"/>
-      <c r="J2" s="192"/>
+      <c r="G2" s="193"/>
+      <c r="H2" s="193"/>
+      <c r="I2" s="201"/>
+      <c r="J2" s="194"/>
     </row>
     <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="194"/>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="196"/>
+      <c r="B3" s="196"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="198"/>
       <c r="F3" s="97" t="s">
         <v>346</v>
       </c>
@@ -17357,30 +17357,30 @@
       <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="193" t="s">
+      <c r="B2" s="195" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="197" t="s">
+      <c r="C2" s="199" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="197" t="s">
+      <c r="D2" s="199" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="195" t="s">
+      <c r="E2" s="197" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="191" t="s">
+      <c r="F2" s="193" t="s">
         <v>373</v>
       </c>
-      <c r="G2" s="191"/>
-      <c r="H2" s="191"/>
-      <c r="I2" s="192"/>
+      <c r="G2" s="193"/>
+      <c r="H2" s="193"/>
+      <c r="I2" s="194"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="194"/>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="196"/>
+      <c r="B3" s="196"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="198"/>
       <c r="F3" s="97" t="s">
         <v>374</v>
       </c>
@@ -17484,7 +17484,7 @@
         <v>390</v>
       </c>
       <c r="H7" s="105" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I7" s="93"/>
     </row>
@@ -17605,7 +17605,7 @@
       <c r="G13" s="181" t="s">
         <v>416</v>
       </c>
-      <c r="H13" s="200" t="s">
+      <c r="H13" s="184" t="s">
         <v>417</v>
       </c>
       <c r="I13" s="182"/>
@@ -17649,7 +17649,7 @@
         <v>410</v>
       </c>
       <c r="G15" s="157" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H15" s="105" t="s">
         <v>420</v>
@@ -17787,7 +17787,7 @@
       <c r="G21" s="106" t="s">
         <v>392</v>
       </c>
-      <c r="H21" s="201" t="s">
+      <c r="H21" s="185" t="s">
         <v>409</v>
       </c>
       <c r="I21" s="95"/>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\일정\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.Task\001.Woory\001.PTC\0.PTC\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A69427-E607-476D-8B7E-E6E425D89499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17685" activeTab="8"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="대일정" sheetId="1" r:id="rId1"/>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="425">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -9162,11 +9163,21 @@
       : S/W 성능 튜닝 완료되면 차주 진행 제안 (기구팀)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>P1 기본형 (25/07/15)
+P1 항속형 (25/09/15)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Proto (26/7/初)
+P1 (27/2/初)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
@@ -10634,7 +10645,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="202">
+  <cellXfs count="190">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -10722,18 +10733,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -10749,7 +10748,7 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10770,9 +10769,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -10848,21 +10844,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -10998,9 +10979,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -11049,9 +11027,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -11187,7 +11162,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="88" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
@@ -11285,7 +11260,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="그림 4"/>
+        <xdr:cNvPr id="5" name="그림 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -11323,7 +11304,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="3" name="직선 연결선 2"/>
+        <xdr:cNvPr id="3" name="직선 연결선 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -11386,6 +11373,9 @@
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s2049"/>
                 </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000001080000}"/>
+                </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
@@ -11445,6 +11435,9 @@
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s2050"/>
                 </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002080000}"/>
+                </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
@@ -11497,7 +11490,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 1"/>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -11535,7 +11534,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="그림 3"/>
+        <xdr:cNvPr id="4" name="그림 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -11593,7 +11598,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 1"/>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -11881,7 +11892,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BL25"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -11906,90 +11917,90 @@
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="186" t="s">
+      <c r="B2" s="174" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="188" t="s">
+      <c r="C2" s="176" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="188" t="s">
+      <c r="D2" s="176" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="192">
+      <c r="E2" s="180">
         <v>23</v>
       </c>
-      <c r="F2" s="190"/>
-      <c r="G2" s="190"/>
-      <c r="H2" s="190"/>
-      <c r="I2" s="190"/>
-      <c r="J2" s="190"/>
-      <c r="K2" s="190"/>
-      <c r="L2" s="190"/>
-      <c r="M2" s="190"/>
-      <c r="N2" s="190"/>
-      <c r="O2" s="190"/>
-      <c r="P2" s="190"/>
-      <c r="Q2" s="190">
+      <c r="F2" s="178"/>
+      <c r="G2" s="178"/>
+      <c r="H2" s="178"/>
+      <c r="I2" s="178"/>
+      <c r="J2" s="178"/>
+      <c r="K2" s="178"/>
+      <c r="L2" s="178"/>
+      <c r="M2" s="178"/>
+      <c r="N2" s="178"/>
+      <c r="O2" s="178"/>
+      <c r="P2" s="178"/>
+      <c r="Q2" s="178">
         <v>24</v>
       </c>
-      <c r="R2" s="190"/>
-      <c r="S2" s="190"/>
-      <c r="T2" s="190"/>
-      <c r="U2" s="190"/>
-      <c r="V2" s="190"/>
-      <c r="W2" s="190"/>
-      <c r="X2" s="190"/>
-      <c r="Y2" s="190"/>
-      <c r="Z2" s="190"/>
-      <c r="AA2" s="190"/>
-      <c r="AB2" s="190"/>
-      <c r="AC2" s="190">
+      <c r="R2" s="178"/>
+      <c r="S2" s="178"/>
+      <c r="T2" s="178"/>
+      <c r="U2" s="178"/>
+      <c r="V2" s="178"/>
+      <c r="W2" s="178"/>
+      <c r="X2" s="178"/>
+      <c r="Y2" s="178"/>
+      <c r="Z2" s="178"/>
+      <c r="AA2" s="178"/>
+      <c r="AB2" s="178"/>
+      <c r="AC2" s="178">
         <v>25</v>
       </c>
-      <c r="AD2" s="190"/>
-      <c r="AE2" s="190"/>
-      <c r="AF2" s="190"/>
-      <c r="AG2" s="190"/>
-      <c r="AH2" s="190"/>
-      <c r="AI2" s="190"/>
-      <c r="AJ2" s="190"/>
-      <c r="AK2" s="190"/>
-      <c r="AL2" s="190"/>
-      <c r="AM2" s="190"/>
-      <c r="AN2" s="190"/>
-      <c r="AO2" s="190">
+      <c r="AD2" s="178"/>
+      <c r="AE2" s="178"/>
+      <c r="AF2" s="178"/>
+      <c r="AG2" s="178"/>
+      <c r="AH2" s="178"/>
+      <c r="AI2" s="178"/>
+      <c r="AJ2" s="178"/>
+      <c r="AK2" s="178"/>
+      <c r="AL2" s="178"/>
+      <c r="AM2" s="178"/>
+      <c r="AN2" s="178"/>
+      <c r="AO2" s="178">
         <v>26</v>
       </c>
-      <c r="AP2" s="190"/>
-      <c r="AQ2" s="190"/>
-      <c r="AR2" s="190"/>
-      <c r="AS2" s="190"/>
-      <c r="AT2" s="190"/>
-      <c r="AU2" s="190"/>
-      <c r="AV2" s="190"/>
-      <c r="AW2" s="190"/>
-      <c r="AX2" s="190"/>
-      <c r="AY2" s="190"/>
-      <c r="AZ2" s="191"/>
-      <c r="BA2" s="190">
+      <c r="AP2" s="178"/>
+      <c r="AQ2" s="178"/>
+      <c r="AR2" s="178"/>
+      <c r="AS2" s="178"/>
+      <c r="AT2" s="178"/>
+      <c r="AU2" s="178"/>
+      <c r="AV2" s="178"/>
+      <c r="AW2" s="178"/>
+      <c r="AX2" s="178"/>
+      <c r="AY2" s="178"/>
+      <c r="AZ2" s="179"/>
+      <c r="BA2" s="178">
         <v>27</v>
       </c>
-      <c r="BB2" s="190"/>
-      <c r="BC2" s="190"/>
-      <c r="BD2" s="190"/>
-      <c r="BE2" s="190"/>
-      <c r="BF2" s="190"/>
-      <c r="BG2" s="190"/>
-      <c r="BH2" s="190"/>
-      <c r="BI2" s="190"/>
-      <c r="BJ2" s="190"/>
-      <c r="BK2" s="190"/>
-      <c r="BL2" s="191"/>
+      <c r="BB2" s="178"/>
+      <c r="BC2" s="178"/>
+      <c r="BD2" s="178"/>
+      <c r="BE2" s="178"/>
+      <c r="BF2" s="178"/>
+      <c r="BG2" s="178"/>
+      <c r="BH2" s="178"/>
+      <c r="BI2" s="178"/>
+      <c r="BJ2" s="178"/>
+      <c r="BK2" s="178"/>
+      <c r="BL2" s="179"/>
     </row>
     <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="187"/>
-      <c r="C3" s="189"/>
-      <c r="D3" s="189"/>
+      <c r="B3" s="175"/>
+      <c r="C3" s="177"/>
+      <c r="D3" s="177"/>
       <c r="E3" s="22">
         <v>1</v>
       </c>
@@ -12172,13 +12183,13 @@
       </c>
     </row>
     <row r="4" spans="1:64" ht="183" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="63" t="s">
+      <c r="B4" s="58" t="s">
         <v>119</v>
       </c>
-      <c r="C4" s="61" t="s">
+      <c r="C4" s="56" t="s">
         <v>79</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="31" t="s">
         <v>42</v>
       </c>
       <c r="E4" s="1"/>
@@ -12256,10 +12267,10 @@
       <c r="B5" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="C5" s="62" t="s">
+      <c r="C5" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="31" t="s">
         <v>41</v>
       </c>
       <c r="E5" s="6"/>
@@ -12319,26 +12330,26 @@
       <c r="AY5" s="7"/>
       <c r="AZ5" s="10"/>
       <c r="BA5" s="9"/>
-      <c r="BB5" s="31"/>
-      <c r="BC5" s="31"/>
-      <c r="BD5" s="31"/>
-      <c r="BE5" s="31"/>
-      <c r="BF5" s="31"/>
-      <c r="BG5" s="31"/>
-      <c r="BH5" s="31"/>
-      <c r="BI5" s="31"/>
-      <c r="BJ5" s="31"/>
-      <c r="BK5" s="31"/>
+      <c r="BB5" s="7"/>
+      <c r="BC5" s="7"/>
+      <c r="BD5" s="7"/>
+      <c r="BE5" s="7"/>
+      <c r="BF5" s="7"/>
+      <c r="BG5" s="7"/>
+      <c r="BH5" s="7"/>
+      <c r="BI5" s="7"/>
+      <c r="BJ5" s="7"/>
+      <c r="BK5" s="7"/>
       <c r="BL5" s="10"/>
     </row>
     <row r="6" spans="1:64" ht="67.5" x14ac:dyDescent="0.3">
       <c r="B6" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="D6" s="30" t="s">
         <v>40</v>
       </c>
       <c r="E6" s="6"/>
@@ -12402,26 +12413,26 @@
       <c r="AY6" s="7"/>
       <c r="AZ6" s="10"/>
       <c r="BA6" s="9"/>
-      <c r="BB6" s="31"/>
-      <c r="BC6" s="31"/>
-      <c r="BD6" s="31"/>
-      <c r="BE6" s="31"/>
-      <c r="BF6" s="31"/>
-      <c r="BG6" s="31"/>
-      <c r="BH6" s="31"/>
-      <c r="BI6" s="31"/>
-      <c r="BJ6" s="31"/>
-      <c r="BK6" s="31"/>
+      <c r="BB6" s="7"/>
+      <c r="BC6" s="7"/>
+      <c r="BD6" s="7"/>
+      <c r="BE6" s="7"/>
+      <c r="BF6" s="7"/>
+      <c r="BG6" s="7"/>
+      <c r="BH6" s="7"/>
+      <c r="BI6" s="7"/>
+      <c r="BJ6" s="7"/>
+      <c r="BK6" s="7"/>
       <c r="BL6" s="10"/>
     </row>
     <row r="7" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="D7" s="33"/>
+      <c r="D7" s="29"/>
       <c r="E7" s="6"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
@@ -12458,7 +12469,7 @@
         <v>27</v>
       </c>
       <c r="AB7" s="8"/>
-      <c r="AC7" s="29"/>
+      <c r="AC7" s="12"/>
       <c r="AD7" s="7"/>
       <c r="AE7" s="7"/>
       <c r="AF7" s="13"/>
@@ -12483,24 +12494,24 @@
       <c r="AY7" s="7"/>
       <c r="AZ7" s="10"/>
       <c r="BA7" s="9"/>
-      <c r="BB7" s="31"/>
-      <c r="BC7" s="31"/>
-      <c r="BD7" s="31"/>
-      <c r="BE7" s="31"/>
-      <c r="BF7" s="31"/>
-      <c r="BG7" s="31"/>
-      <c r="BH7" s="31"/>
-      <c r="BI7" s="31"/>
-      <c r="BJ7" s="31"/>
-      <c r="BK7" s="31"/>
+      <c r="BB7" s="7"/>
+      <c r="BC7" s="7"/>
+      <c r="BD7" s="7"/>
+      <c r="BE7" s="7"/>
+      <c r="BF7" s="7"/>
+      <c r="BG7" s="7"/>
+      <c r="BH7" s="7"/>
+      <c r="BI7" s="7"/>
+      <c r="BJ7" s="7"/>
+      <c r="BK7" s="7"/>
       <c r="BL7" s="10"/>
     </row>
     <row r="8" spans="1:64" ht="81" x14ac:dyDescent="0.3">
       <c r="B8" s="28" t="s">
         <v>218</v>
       </c>
-      <c r="C8" s="58"/>
-      <c r="D8" s="33"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="29"/>
       <c r="E8" s="6"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
@@ -12512,45 +12523,45 @@
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
-      <c r="P8" s="32"/>
-      <c r="Q8" s="29"/>
-      <c r="R8" s="31"/>
-      <c r="S8" s="31"/>
-      <c r="T8" s="31"/>
-      <c r="U8" s="31"/>
-      <c r="V8" s="30"/>
-      <c r="W8" s="30"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="13"/>
+      <c r="W8" s="13"/>
       <c r="X8" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="Y8" s="31"/>
-      <c r="Z8" s="30"/>
-      <c r="AA8" s="30"/>
-      <c r="AB8" s="121"/>
-      <c r="AC8" s="29"/>
-      <c r="AD8" s="31"/>
-      <c r="AE8" s="31"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="13"/>
+      <c r="AA8" s="13"/>
+      <c r="AB8" s="8"/>
+      <c r="AC8" s="12"/>
+      <c r="AD8" s="7"/>
+      <c r="AE8" s="7"/>
       <c r="AF8" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="AG8" s="31"/>
-      <c r="AH8" s="31"/>
+      <c r="AG8" s="7"/>
+      <c r="AH8" s="7"/>
       <c r="AI8" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="AJ8" s="31"/>
-      <c r="AK8" s="31"/>
-      <c r="AL8" s="31"/>
+      <c r="AJ8" s="7"/>
+      <c r="AK8" s="7"/>
+      <c r="AL8" s="7"/>
       <c r="AM8" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="AN8" s="121"/>
-      <c r="AO8" s="29" t="s">
+      <c r="AN8" s="8"/>
+      <c r="AO8" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="AP8" s="31"/>
-      <c r="AQ8" s="31"/>
-      <c r="AR8" s="31"/>
+      <c r="AP8" s="7"/>
+      <c r="AQ8" s="7"/>
+      <c r="AR8" s="7"/>
       <c r="AS8" s="7"/>
       <c r="AT8" s="7"/>
       <c r="AU8" s="7"/>
@@ -12560,26 +12571,26 @@
       <c r="AY8" s="7"/>
       <c r="AZ8" s="10"/>
       <c r="BA8" s="9"/>
-      <c r="BB8" s="31"/>
-      <c r="BC8" s="31"/>
-      <c r="BD8" s="31"/>
-      <c r="BE8" s="31"/>
-      <c r="BF8" s="31"/>
-      <c r="BG8" s="31"/>
-      <c r="BH8" s="31"/>
-      <c r="BI8" s="31"/>
-      <c r="BJ8" s="31"/>
-      <c r="BK8" s="31"/>
+      <c r="BB8" s="7"/>
+      <c r="BC8" s="7"/>
+      <c r="BD8" s="7"/>
+      <c r="BE8" s="7"/>
+      <c r="BF8" s="7"/>
+      <c r="BG8" s="7"/>
+      <c r="BH8" s="7"/>
+      <c r="BI8" s="7"/>
+      <c r="BJ8" s="7"/>
+      <c r="BK8" s="7"/>
       <c r="BL8" s="10"/>
     </row>
     <row r="9" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="59" t="s">
+      <c r="C9" s="54" t="s">
         <v>78</v>
       </c>
-      <c r="D9" s="33"/>
+      <c r="D9" s="29"/>
       <c r="E9" s="6"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
@@ -12633,26 +12644,26 @@
       <c r="AY9" s="7"/>
       <c r="AZ9" s="10"/>
       <c r="BA9" s="9"/>
-      <c r="BB9" s="31"/>
-      <c r="BC9" s="31"/>
-      <c r="BD9" s="31"/>
-      <c r="BE9" s="31"/>
-      <c r="BF9" s="31"/>
-      <c r="BG9" s="31"/>
-      <c r="BH9" s="31"/>
-      <c r="BI9" s="31"/>
-      <c r="BJ9" s="31"/>
-      <c r="BK9" s="31"/>
+      <c r="BB9" s="7"/>
+      <c r="BC9" s="7"/>
+      <c r="BD9" s="7"/>
+      <c r="BE9" s="7"/>
+      <c r="BF9" s="7"/>
+      <c r="BG9" s="7"/>
+      <c r="BH9" s="7"/>
+      <c r="BI9" s="7"/>
+      <c r="BJ9" s="7"/>
+      <c r="BK9" s="7"/>
       <c r="BL9" s="10"/>
     </row>
     <row r="10" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="53" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="33"/>
+      <c r="D10" s="29"/>
       <c r="E10" s="6"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
@@ -12710,26 +12721,26 @@
       <c r="AY10" s="7"/>
       <c r="AZ10" s="10"/>
       <c r="BA10" s="9"/>
-      <c r="BB10" s="31"/>
-      <c r="BC10" s="31"/>
-      <c r="BD10" s="31"/>
-      <c r="BE10" s="31"/>
-      <c r="BF10" s="31"/>
-      <c r="BG10" s="31"/>
-      <c r="BH10" s="31"/>
-      <c r="BI10" s="31"/>
-      <c r="BJ10" s="31"/>
-      <c r="BK10" s="31"/>
+      <c r="BB10" s="7"/>
+      <c r="BC10" s="7"/>
+      <c r="BD10" s="7"/>
+      <c r="BE10" s="7"/>
+      <c r="BF10" s="7"/>
+      <c r="BG10" s="7"/>
+      <c r="BH10" s="7"/>
+      <c r="BI10" s="7"/>
+      <c r="BJ10" s="7"/>
+      <c r="BK10" s="7"/>
       <c r="BL10" s="10"/>
     </row>
     <row r="11" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="53" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="160" t="s">
+      <c r="D11" s="148" t="s">
         <v>313</v>
       </c>
       <c r="E11" s="6"/>
@@ -12742,7 +12753,7 @@
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
-      <c r="O11" s="30"/>
+      <c r="O11" s="13"/>
       <c r="P11" s="14"/>
       <c r="Q11" s="9"/>
       <c r="R11" s="7"/>
@@ -12754,16 +12765,16 @@
       <c r="X11" s="7"/>
       <c r="Y11" s="7"/>
       <c r="Z11" s="7"/>
-      <c r="AA11" s="37" t="s">
+      <c r="AA11" s="33" t="s">
         <v>57</v>
       </c>
       <c r="AB11" s="14" t="s">
         <v>56</v>
       </c>
       <c r="AC11" s="9"/>
-      <c r="AD11" s="30"/>
-      <c r="AE11" s="31"/>
-      <c r="AF11" s="31"/>
+      <c r="AD11" s="13"/>
+      <c r="AE11" s="7"/>
+      <c r="AF11" s="7"/>
       <c r="AG11" s="13" t="s">
         <v>130</v>
       </c>
@@ -12793,26 +12804,26 @@
       <c r="AY11" s="7"/>
       <c r="AZ11" s="10"/>
       <c r="BA11" s="9"/>
-      <c r="BB11" s="31"/>
-      <c r="BC11" s="31"/>
-      <c r="BD11" s="31"/>
-      <c r="BE11" s="31"/>
-      <c r="BF11" s="31"/>
-      <c r="BG11" s="31"/>
-      <c r="BH11" s="31"/>
-      <c r="BI11" s="31"/>
-      <c r="BJ11" s="31"/>
-      <c r="BK11" s="31"/>
+      <c r="BB11" s="7"/>
+      <c r="BC11" s="7"/>
+      <c r="BD11" s="7"/>
+      <c r="BE11" s="7"/>
+      <c r="BF11" s="7"/>
+      <c r="BG11" s="7"/>
+      <c r="BH11" s="7"/>
+      <c r="BI11" s="7"/>
+      <c r="BJ11" s="7"/>
+      <c r="BK11" s="7"/>
       <c r="BL11" s="10"/>
     </row>
     <row r="12" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="D12" s="160" t="s">
+      <c r="D12" s="148" t="s">
         <v>313</v>
       </c>
       <c r="E12" s="6"/>
@@ -12825,7 +12836,7 @@
       <c r="L12" s="7"/>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
-      <c r="O12" s="30"/>
+      <c r="O12" s="13"/>
       <c r="P12" s="14"/>
       <c r="Q12" s="9"/>
       <c r="R12" s="7"/>
@@ -12837,19 +12848,19 @@
       <c r="X12" s="7"/>
       <c r="Y12" s="7"/>
       <c r="Z12" s="7"/>
-      <c r="AA12" s="37"/>
+      <c r="AA12" s="33"/>
       <c r="AB12" s="14"/>
       <c r="AC12" s="9"/>
-      <c r="AD12" s="30"/>
-      <c r="AE12" s="31"/>
-      <c r="AF12" s="31"/>
-      <c r="AG12" s="30"/>
+      <c r="AD12" s="13"/>
+      <c r="AE12" s="7"/>
+      <c r="AF12" s="7"/>
+      <c r="AG12" s="13"/>
       <c r="AH12" s="7"/>
       <c r="AI12" s="13"/>
-      <c r="AJ12" s="99" t="s">
+      <c r="AJ12" s="89" t="s">
         <v>129</v>
       </c>
-      <c r="AK12" s="36"/>
+      <c r="AK12" s="32"/>
       <c r="AL12" s="13"/>
       <c r="AM12" s="13" t="s">
         <v>134</v>
@@ -12874,26 +12885,26 @@
       <c r="AY12" s="7"/>
       <c r="AZ12" s="10"/>
       <c r="BA12" s="12"/>
-      <c r="BB12" s="31"/>
-      <c r="BC12" s="31"/>
-      <c r="BD12" s="31"/>
-      <c r="BE12" s="31"/>
-      <c r="BF12" s="31"/>
-      <c r="BG12" s="31"/>
-      <c r="BH12" s="31"/>
-      <c r="BI12" s="31"/>
-      <c r="BJ12" s="31"/>
-      <c r="BK12" s="31"/>
+      <c r="BB12" s="7"/>
+      <c r="BC12" s="7"/>
+      <c r="BD12" s="7"/>
+      <c r="BE12" s="7"/>
+      <c r="BF12" s="7"/>
+      <c r="BG12" s="7"/>
+      <c r="BH12" s="7"/>
+      <c r="BI12" s="7"/>
+      <c r="BJ12" s="7"/>
+      <c r="BK12" s="7"/>
       <c r="BL12" s="10"/>
     </row>
     <row r="13" spans="1:64" ht="228.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="59" t="s">
+      <c r="C13" s="54" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="34" t="s">
+      <c r="D13" s="30" t="s">
         <v>311</v>
       </c>
       <c r="E13" s="6"/>
@@ -12924,7 +12935,7 @@
       <c r="Z13" s="7"/>
       <c r="AA13" s="7"/>
       <c r="AB13" s="14"/>
-      <c r="AC13" s="29"/>
+      <c r="AC13" s="12"/>
       <c r="AD13" s="7"/>
       <c r="AE13" s="7"/>
       <c r="AF13" s="7"/>
@@ -12932,11 +12943,11 @@
       <c r="AH13" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="AI13" s="36"/>
+      <c r="AI13" s="32"/>
       <c r="AJ13" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="AK13" s="30"/>
+      <c r="AK13" s="13"/>
       <c r="AL13" s="7"/>
       <c r="AM13" s="13" t="s">
         <v>4</v>
@@ -12963,26 +12974,26 @@
       <c r="AY13" s="7"/>
       <c r="AZ13" s="10"/>
       <c r="BA13" s="9"/>
-      <c r="BB13" s="31"/>
-      <c r="BC13" s="30"/>
-      <c r="BD13" s="31"/>
-      <c r="BE13" s="30"/>
-      <c r="BF13" s="30"/>
-      <c r="BG13" s="31"/>
-      <c r="BH13" s="31"/>
-      <c r="BI13" s="31"/>
-      <c r="BJ13" s="31"/>
-      <c r="BK13" s="31"/>
+      <c r="BB13" s="7"/>
+      <c r="BC13" s="13"/>
+      <c r="BD13" s="7"/>
+      <c r="BE13" s="13"/>
+      <c r="BF13" s="13"/>
+      <c r="BG13" s="7"/>
+      <c r="BH13" s="7"/>
+      <c r="BI13" s="7"/>
+      <c r="BJ13" s="7"/>
+      <c r="BK13" s="7"/>
       <c r="BL13" s="10"/>
     </row>
     <row r="14" spans="1:64" ht="67.5" x14ac:dyDescent="0.3">
       <c r="B14" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="59" t="s">
+      <c r="C14" s="54" t="s">
         <v>83</v>
       </c>
-      <c r="D14" s="34" t="s">
+      <c r="D14" s="30" t="s">
         <v>74</v>
       </c>
       <c r="E14" s="6"/>
@@ -13052,26 +13063,26 @@
       <c r="AY14" s="7"/>
       <c r="AZ14" s="10"/>
       <c r="BA14" s="9"/>
-      <c r="BB14" s="31"/>
-      <c r="BC14" s="31"/>
-      <c r="BD14" s="30"/>
-      <c r="BE14" s="31"/>
-      <c r="BF14" s="30"/>
-      <c r="BG14" s="30"/>
-      <c r="BH14" s="31"/>
-      <c r="BI14" s="31"/>
-      <c r="BJ14" s="31"/>
-      <c r="BK14" s="31"/>
+      <c r="BB14" s="7"/>
+      <c r="BC14" s="7"/>
+      <c r="BD14" s="13"/>
+      <c r="BE14" s="7"/>
+      <c r="BF14" s="13"/>
+      <c r="BG14" s="13"/>
+      <c r="BH14" s="7"/>
+      <c r="BI14" s="7"/>
+      <c r="BJ14" s="7"/>
+      <c r="BK14" s="7"/>
       <c r="BL14" s="10"/>
     </row>
     <row r="15" spans="1:64" ht="285.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="59" t="s">
+      <c r="C15" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="D15" s="34" t="s">
+      <c r="D15" s="30" t="s">
         <v>281</v>
       </c>
       <c r="E15" s="6"/>
@@ -13099,21 +13110,21 @@
       </c>
       <c r="Z15" s="13"/>
       <c r="AA15" s="7"/>
-      <c r="AB15" s="32"/>
+      <c r="AB15" s="14"/>
       <c r="AC15" s="12"/>
       <c r="AD15" s="7"/>
       <c r="AE15" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="AF15" s="38"/>
-      <c r="AG15" s="37" t="s">
+      <c r="AF15" s="34"/>
+      <c r="AG15" s="33" t="s">
         <v>67</v>
       </c>
       <c r="AH15" s="7"/>
-      <c r="AI15" s="37" t="s">
+      <c r="AI15" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="AJ15" s="30"/>
+      <c r="AJ15" s="13"/>
       <c r="AK15" s="7"/>
       <c r="AL15" s="13"/>
       <c r="AM15" s="13"/>
@@ -13135,26 +13146,26 @@
       <c r="AY15" s="7"/>
       <c r="AZ15" s="10"/>
       <c r="BA15" s="9"/>
-      <c r="BB15" s="30"/>
-      <c r="BC15" s="30"/>
-      <c r="BD15" s="31"/>
-      <c r="BE15" s="31"/>
-      <c r="BF15" s="31"/>
-      <c r="BG15" s="31"/>
-      <c r="BH15" s="31"/>
-      <c r="BI15" s="31"/>
-      <c r="BJ15" s="31"/>
-      <c r="BK15" s="31"/>
+      <c r="BB15" s="13"/>
+      <c r="BC15" s="13"/>
+      <c r="BD15" s="7"/>
+      <c r="BE15" s="7"/>
+      <c r="BF15" s="7"/>
+      <c r="BG15" s="7"/>
+      <c r="BH15" s="7"/>
+      <c r="BI15" s="7"/>
+      <c r="BJ15" s="7"/>
+      <c r="BK15" s="7"/>
       <c r="BL15" s="10"/>
     </row>
     <row r="16" spans="1:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="59" t="s">
+      <c r="C16" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="33"/>
+      <c r="D16" s="29"/>
       <c r="E16" s="6"/>
       <c r="F16" s="7"/>
       <c r="G16" s="13"/>
@@ -13193,17 +13204,17 @@
       </c>
       <c r="AE16" s="7"/>
       <c r="AF16" s="7"/>
-      <c r="AG16" s="30"/>
+      <c r="AG16" s="13"/>
       <c r="AH16" s="7"/>
       <c r="AI16" s="13"/>
       <c r="AJ16" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="AK16" s="37" t="s">
+      <c r="AK16" s="33" t="s">
         <v>69</v>
       </c>
       <c r="AL16" s="7"/>
-      <c r="AM16" s="37" t="s">
+      <c r="AM16" s="33" t="s">
         <v>70</v>
       </c>
       <c r="AN16" s="8"/>
@@ -13224,665 +13235,665 @@
       <c r="AY16" s="7"/>
       <c r="AZ16" s="10"/>
       <c r="BA16" s="12"/>
-      <c r="BB16" s="30"/>
-      <c r="BC16" s="30"/>
-      <c r="BD16" s="30"/>
-      <c r="BE16" s="31"/>
-      <c r="BF16" s="30"/>
-      <c r="BG16" s="31"/>
-      <c r="BH16" s="31"/>
-      <c r="BI16" s="31"/>
-      <c r="BJ16" s="31"/>
-      <c r="BK16" s="31"/>
+      <c r="BB16" s="13"/>
+      <c r="BC16" s="13"/>
+      <c r="BD16" s="13"/>
+      <c r="BE16" s="7"/>
+      <c r="BF16" s="13"/>
+      <c r="BG16" s="7"/>
+      <c r="BH16" s="7"/>
+      <c r="BI16" s="7"/>
+      <c r="BJ16" s="7"/>
+      <c r="BK16" s="7"/>
       <c r="BL16" s="10"/>
     </row>
     <row r="17" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="57" t="s">
+      <c r="B17" s="52" t="s">
         <v>385</v>
       </c>
-      <c r="C17" s="60" t="s">
+      <c r="C17" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="D17" s="76" t="s">
+      <c r="D17" s="66" t="s">
         <v>103</v>
       </c>
-      <c r="E17" s="40"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="41"/>
-      <c r="J17" s="42"/>
-      <c r="K17" s="41"/>
-      <c r="L17" s="41"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="37"/>
       <c r="M17" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="N17" s="41"/>
-      <c r="O17" s="41"/>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="102" t="s">
+      <c r="N17" s="37"/>
+      <c r="O17" s="37"/>
+      <c r="P17" s="39"/>
+      <c r="Q17" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="R17" s="101"/>
-      <c r="S17" s="41"/>
-      <c r="T17" s="41"/>
-      <c r="U17" s="41"/>
-      <c r="V17" s="41"/>
-      <c r="W17" s="42"/>
-      <c r="X17" s="41"/>
-      <c r="Y17" s="30" t="s">
+      <c r="R17" s="91"/>
+      <c r="S17" s="37"/>
+      <c r="T17" s="37"/>
+      <c r="U17" s="37"/>
+      <c r="V17" s="37"/>
+      <c r="W17" s="38"/>
+      <c r="X17" s="37"/>
+      <c r="Y17" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="Z17" s="41"/>
-      <c r="AA17" s="41"/>
-      <c r="AB17" s="43"/>
-      <c r="AC17" s="44"/>
-      <c r="AD17" s="45"/>
+      <c r="Z17" s="37"/>
+      <c r="AA17" s="37"/>
+      <c r="AB17" s="39"/>
+      <c r="AC17" s="40"/>
+      <c r="AD17" s="38"/>
       <c r="AE17" s="13"/>
-      <c r="AF17" s="41"/>
-      <c r="AG17" s="37"/>
-      <c r="AH17" s="41"/>
-      <c r="AI17" s="37"/>
-      <c r="AJ17" s="30" t="s">
+      <c r="AF17" s="37"/>
+      <c r="AG17" s="33"/>
+      <c r="AH17" s="37"/>
+      <c r="AI17" s="33"/>
+      <c r="AJ17" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="AK17" s="46"/>
-      <c r="AL17" s="41"/>
-      <c r="AM17" s="46"/>
+      <c r="AK17" s="41"/>
+      <c r="AL17" s="37"/>
+      <c r="AM17" s="41"/>
       <c r="AN17" s="8"/>
-      <c r="AO17" s="47"/>
+      <c r="AO17" s="42"/>
       <c r="AP17" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="AQ17" s="42"/>
-      <c r="AR17" s="37" t="s">
+      <c r="AQ17" s="38"/>
+      <c r="AR17" s="33" t="s">
         <v>380</v>
       </c>
-      <c r="AS17" s="41"/>
-      <c r="AT17" s="42"/>
-      <c r="AU17" s="41"/>
-      <c r="AV17" s="41"/>
-      <c r="AW17" s="42" t="s">
+      <c r="AS17" s="37"/>
+      <c r="AT17" s="38"/>
+      <c r="AU17" s="37"/>
+      <c r="AV17" s="37"/>
+      <c r="AW17" s="38" t="s">
         <v>382</v>
       </c>
-      <c r="AX17" s="30"/>
-      <c r="AY17" s="41"/>
-      <c r="AZ17" s="180" t="s">
+      <c r="AX17" s="13"/>
+      <c r="AY17" s="37"/>
+      <c r="AZ17" s="168" t="s">
         <v>381</v>
       </c>
-      <c r="BA17" s="47"/>
-      <c r="BB17" s="45"/>
-      <c r="BC17" s="45" t="s">
+      <c r="BA17" s="42"/>
+      <c r="BB17" s="38"/>
+      <c r="BC17" s="38" t="s">
         <v>383</v>
       </c>
       <c r="BD17" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="BE17" s="71"/>
-      <c r="BF17" s="45"/>
-      <c r="BG17" s="71"/>
-      <c r="BH17" s="71"/>
-      <c r="BI17" s="71"/>
-      <c r="BJ17" s="71"/>
-      <c r="BK17" s="71"/>
-      <c r="BL17" s="48"/>
+      <c r="BE17" s="37"/>
+      <c r="BF17" s="38"/>
+      <c r="BG17" s="37"/>
+      <c r="BH17" s="37"/>
+      <c r="BI17" s="37"/>
+      <c r="BJ17" s="37"/>
+      <c r="BK17" s="37"/>
+      <c r="BL17" s="43"/>
     </row>
     <row r="18" spans="2:64" ht="179.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="59" t="s">
+      <c r="C18" s="54" t="s">
         <v>255</v>
       </c>
-      <c r="D18" s="160" t="s">
+      <c r="D18" s="148" t="s">
         <v>312</v>
       </c>
-      <c r="E18" s="64"/>
-      <c r="F18" s="65"/>
-      <c r="G18" s="65"/>
-      <c r="H18" s="65"/>
-      <c r="I18" s="65"/>
-      <c r="J18" s="65"/>
-      <c r="K18" s="65"/>
-      <c r="L18" s="65"/>
-      <c r="M18" s="65"/>
-      <c r="N18" s="65"/>
-      <c r="O18" s="65"/>
-      <c r="P18" s="66"/>
-      <c r="Q18" s="67"/>
-      <c r="R18" s="65"/>
-      <c r="S18" s="65"/>
-      <c r="T18" s="65"/>
-      <c r="U18" s="65"/>
-      <c r="V18" s="65"/>
-      <c r="W18" s="65"/>
-      <c r="X18" s="65"/>
-      <c r="Y18" s="65"/>
-      <c r="Z18" s="65"/>
-      <c r="AA18" s="65"/>
-      <c r="AB18" s="66"/>
-      <c r="AC18" s="67"/>
-      <c r="AD18" s="65"/>
-      <c r="AE18" s="68" t="s">
+      <c r="E18" s="59"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="60"/>
+      <c r="K18" s="60"/>
+      <c r="L18" s="60"/>
+      <c r="M18" s="60"/>
+      <c r="N18" s="60"/>
+      <c r="O18" s="60"/>
+      <c r="P18" s="61"/>
+      <c r="Q18" s="62"/>
+      <c r="R18" s="60"/>
+      <c r="S18" s="60"/>
+      <c r="T18" s="60"/>
+      <c r="U18" s="60"/>
+      <c r="V18" s="60"/>
+      <c r="W18" s="60"/>
+      <c r="X18" s="60"/>
+      <c r="Y18" s="60"/>
+      <c r="Z18" s="60"/>
+      <c r="AA18" s="60"/>
+      <c r="AB18" s="61"/>
+      <c r="AC18" s="62"/>
+      <c r="AD18" s="60"/>
+      <c r="AE18" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="AF18" s="65"/>
-      <c r="AG18" s="68"/>
-      <c r="AH18" s="56" t="s">
+      <c r="AF18" s="60"/>
+      <c r="AG18" s="63"/>
+      <c r="AH18" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="AI18" s="69"/>
-      <c r="AJ18" s="65"/>
-      <c r="AK18" s="65"/>
-      <c r="AL18" s="65"/>
-      <c r="AM18" s="65"/>
-      <c r="AN18" s="66"/>
-      <c r="AO18" s="67"/>
-      <c r="AP18" s="69" t="s">
+      <c r="AI18" s="64"/>
+      <c r="AJ18" s="60"/>
+      <c r="AK18" s="60"/>
+      <c r="AL18" s="60"/>
+      <c r="AM18" s="60"/>
+      <c r="AN18" s="61"/>
+      <c r="AO18" s="62"/>
+      <c r="AP18" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="AQ18" s="69"/>
-      <c r="AR18" s="65"/>
-      <c r="AS18" s="65"/>
-      <c r="AT18" s="69" t="s">
+      <c r="AQ18" s="64"/>
+      <c r="AR18" s="60"/>
+      <c r="AS18" s="60"/>
+      <c r="AT18" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="AU18" s="73"/>
-      <c r="AV18" s="65"/>
-      <c r="AW18" s="69" t="s">
+      <c r="AU18" s="64"/>
+      <c r="AV18" s="60"/>
+      <c r="AW18" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="AX18" s="69" t="s">
+      <c r="AX18" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="AY18" s="69" t="s">
+      <c r="AY18" s="64" t="s">
         <v>90</v>
       </c>
-      <c r="AZ18" s="70" t="s">
+      <c r="AZ18" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="BA18" s="67"/>
-      <c r="BB18" s="73" t="s">
+      <c r="BA18" s="62"/>
+      <c r="BB18" s="64" t="s">
         <v>92</v>
       </c>
-      <c r="BC18" s="73"/>
-      <c r="BD18" s="73" t="s">
+      <c r="BC18" s="64"/>
+      <c r="BD18" s="64" t="s">
         <v>93</v>
       </c>
-      <c r="BE18" s="73" t="s">
+      <c r="BE18" s="64" t="s">
         <v>94</v>
       </c>
-      <c r="BF18" s="72"/>
-      <c r="BG18" s="73"/>
-      <c r="BH18" s="72"/>
-      <c r="BI18" s="72"/>
-      <c r="BJ18" s="72"/>
-      <c r="BK18" s="73"/>
-      <c r="BL18" s="70"/>
+      <c r="BF18" s="60"/>
+      <c r="BG18" s="64"/>
+      <c r="BH18" s="60"/>
+      <c r="BI18" s="60"/>
+      <c r="BJ18" s="60"/>
+      <c r="BK18" s="64"/>
+      <c r="BL18" s="65"/>
     </row>
     <row r="19" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="77" t="s">
+      <c r="B19" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="C19" s="78" t="s">
+      <c r="C19" s="68" t="s">
         <v>104</v>
       </c>
-      <c r="D19" s="33"/>
-      <c r="E19" s="64"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="65"/>
-      <c r="H19" s="65"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="65"/>
-      <c r="K19" s="65"/>
-      <c r="L19" s="65"/>
-      <c r="M19" s="65"/>
-      <c r="N19" s="65"/>
-      <c r="O19" s="65"/>
-      <c r="P19" s="66"/>
-      <c r="Q19" s="67"/>
-      <c r="R19" s="65"/>
-      <c r="S19" s="65"/>
-      <c r="T19" s="65"/>
-      <c r="U19" s="65"/>
-      <c r="V19" s="65"/>
-      <c r="W19" s="65"/>
-      <c r="X19" s="65"/>
-      <c r="Y19" s="65"/>
-      <c r="Z19" s="65"/>
-      <c r="AA19" s="65"/>
-      <c r="AB19" s="66"/>
-      <c r="AC19" s="67"/>
-      <c r="AD19" s="65"/>
-      <c r="AE19" s="65"/>
-      <c r="AF19" s="65"/>
-      <c r="AG19" s="68"/>
-      <c r="AH19" s="65"/>
-      <c r="AI19" s="69"/>
-      <c r="AJ19" s="65"/>
-      <c r="AK19" s="65"/>
-      <c r="AL19" s="65"/>
-      <c r="AM19" s="65"/>
-      <c r="AN19" s="66"/>
-      <c r="AO19" s="67"/>
-      <c r="AP19" s="69" t="s">
+      <c r="D19" s="29"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="60"/>
+      <c r="L19" s="60"/>
+      <c r="M19" s="60"/>
+      <c r="N19" s="60"/>
+      <c r="O19" s="60"/>
+      <c r="P19" s="61"/>
+      <c r="Q19" s="62"/>
+      <c r="R19" s="60"/>
+      <c r="S19" s="60"/>
+      <c r="T19" s="60"/>
+      <c r="U19" s="60"/>
+      <c r="V19" s="60"/>
+      <c r="W19" s="60"/>
+      <c r="X19" s="60"/>
+      <c r="Y19" s="60"/>
+      <c r="Z19" s="60"/>
+      <c r="AA19" s="60"/>
+      <c r="AB19" s="61"/>
+      <c r="AC19" s="62"/>
+      <c r="AD19" s="60"/>
+      <c r="AE19" s="60"/>
+      <c r="AF19" s="60"/>
+      <c r="AG19" s="63"/>
+      <c r="AH19" s="60"/>
+      <c r="AI19" s="64"/>
+      <c r="AJ19" s="60"/>
+      <c r="AK19" s="60"/>
+      <c r="AL19" s="60"/>
+      <c r="AM19" s="60"/>
+      <c r="AN19" s="61"/>
+      <c r="AO19" s="62"/>
+      <c r="AP19" s="64" t="s">
         <v>95</v>
       </c>
-      <c r="AQ19" s="69"/>
-      <c r="AR19" s="69" t="s">
+      <c r="AQ19" s="64"/>
+      <c r="AR19" s="64" t="s">
         <v>96</v>
       </c>
-      <c r="AS19" s="65"/>
-      <c r="AT19" s="65"/>
-      <c r="AU19" s="69"/>
-      <c r="AV19" s="65"/>
-      <c r="AW19" s="65"/>
-      <c r="AX19" s="65"/>
-      <c r="AY19" s="69"/>
-      <c r="AZ19" s="70" t="s">
+      <c r="AS19" s="60"/>
+      <c r="AT19" s="60"/>
+      <c r="AU19" s="64"/>
+      <c r="AV19" s="60"/>
+      <c r="AW19" s="60"/>
+      <c r="AX19" s="60"/>
+      <c r="AY19" s="64"/>
+      <c r="AZ19" s="65" t="s">
         <v>97</v>
       </c>
-      <c r="BA19" s="67"/>
-      <c r="BB19" s="72"/>
-      <c r="BC19" s="73"/>
-      <c r="BD19" s="72"/>
-      <c r="BE19" s="72"/>
-      <c r="BF19" s="73" t="s">
+      <c r="BA19" s="62"/>
+      <c r="BB19" s="60"/>
+      <c r="BC19" s="64"/>
+      <c r="BD19" s="60"/>
+      <c r="BE19" s="60"/>
+      <c r="BF19" s="64" t="s">
         <v>98</v>
       </c>
-      <c r="BG19" s="73"/>
-      <c r="BH19" s="73" t="s">
+      <c r="BG19" s="64"/>
+      <c r="BH19" s="64" t="s">
         <v>99</v>
       </c>
-      <c r="BI19" s="73" t="s">
+      <c r="BI19" s="64" t="s">
         <v>100</v>
       </c>
-      <c r="BJ19" s="73" t="s">
+      <c r="BJ19" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="BK19" s="73"/>
-      <c r="BL19" s="70" t="s">
+      <c r="BK19" s="64"/>
+      <c r="BL19" s="65" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="20" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="77" t="s">
+      <c r="B20" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="C20" s="78" t="s">
+      <c r="C20" s="68" t="s">
         <v>104</v>
       </c>
-      <c r="D20" s="39"/>
-      <c r="E20" s="64"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="65"/>
-      <c r="H20" s="65"/>
-      <c r="I20" s="65"/>
-      <c r="J20" s="65"/>
-      <c r="K20" s="65"/>
-      <c r="L20" s="65"/>
-      <c r="M20" s="65"/>
-      <c r="N20" s="65"/>
-      <c r="O20" s="65"/>
-      <c r="P20" s="66"/>
-      <c r="Q20" s="67"/>
-      <c r="R20" s="65"/>
-      <c r="S20" s="65"/>
-      <c r="T20" s="65"/>
-      <c r="U20" s="65"/>
-      <c r="V20" s="65"/>
-      <c r="W20" s="65"/>
-      <c r="X20" s="65"/>
-      <c r="Y20" s="65"/>
-      <c r="Z20" s="65"/>
-      <c r="AA20" s="65"/>
-      <c r="AB20" s="66"/>
-      <c r="AC20" s="67"/>
-      <c r="AD20" s="65"/>
-      <c r="AE20" s="65"/>
-      <c r="AF20" s="65"/>
-      <c r="AG20" s="68"/>
-      <c r="AH20" s="65"/>
-      <c r="AI20" s="69"/>
-      <c r="AJ20" s="65"/>
-      <c r="AK20" s="65"/>
-      <c r="AL20" s="65"/>
-      <c r="AM20" s="65"/>
-      <c r="AN20" s="66"/>
-      <c r="AO20" s="67"/>
-      <c r="AP20" s="69"/>
-      <c r="AQ20" s="69"/>
-      <c r="AR20" s="69"/>
-      <c r="AS20" s="65"/>
-      <c r="AT20" s="65"/>
-      <c r="AU20" s="69"/>
-      <c r="AV20" s="65"/>
-      <c r="AW20" s="65"/>
-      <c r="AX20" s="65"/>
-      <c r="AY20" s="69"/>
-      <c r="AZ20" s="70"/>
-      <c r="BA20" s="67"/>
-      <c r="BB20" s="72"/>
-      <c r="BC20" s="73"/>
-      <c r="BD20" s="72"/>
-      <c r="BE20" s="72"/>
-      <c r="BF20" s="73"/>
-      <c r="BG20" s="73"/>
-      <c r="BH20" s="73"/>
-      <c r="BI20" s="73"/>
-      <c r="BJ20" s="73"/>
-      <c r="BK20" s="73"/>
-      <c r="BL20" s="70"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="60"/>
+      <c r="K20" s="60"/>
+      <c r="L20" s="60"/>
+      <c r="M20" s="60"/>
+      <c r="N20" s="60"/>
+      <c r="O20" s="60"/>
+      <c r="P20" s="61"/>
+      <c r="Q20" s="62"/>
+      <c r="R20" s="60"/>
+      <c r="S20" s="60"/>
+      <c r="T20" s="60"/>
+      <c r="U20" s="60"/>
+      <c r="V20" s="60"/>
+      <c r="W20" s="60"/>
+      <c r="X20" s="60"/>
+      <c r="Y20" s="60"/>
+      <c r="Z20" s="60"/>
+      <c r="AA20" s="60"/>
+      <c r="AB20" s="61"/>
+      <c r="AC20" s="62"/>
+      <c r="AD20" s="60"/>
+      <c r="AE20" s="60"/>
+      <c r="AF20" s="60"/>
+      <c r="AG20" s="63"/>
+      <c r="AH20" s="60"/>
+      <c r="AI20" s="64"/>
+      <c r="AJ20" s="60"/>
+      <c r="AK20" s="60"/>
+      <c r="AL20" s="60"/>
+      <c r="AM20" s="60"/>
+      <c r="AN20" s="61"/>
+      <c r="AO20" s="62"/>
+      <c r="AP20" s="64"/>
+      <c r="AQ20" s="64"/>
+      <c r="AR20" s="64"/>
+      <c r="AS20" s="60"/>
+      <c r="AT20" s="60"/>
+      <c r="AU20" s="64"/>
+      <c r="AV20" s="60"/>
+      <c r="AW20" s="60"/>
+      <c r="AX20" s="60"/>
+      <c r="AY20" s="64"/>
+      <c r="AZ20" s="65"/>
+      <c r="BA20" s="62"/>
+      <c r="BB20" s="60"/>
+      <c r="BC20" s="64"/>
+      <c r="BD20" s="60"/>
+      <c r="BE20" s="60"/>
+      <c r="BF20" s="64"/>
+      <c r="BG20" s="64"/>
+      <c r="BH20" s="64"/>
+      <c r="BI20" s="64"/>
+      <c r="BJ20" s="64"/>
+      <c r="BK20" s="64"/>
+      <c r="BL20" s="65"/>
     </row>
     <row r="21" spans="2:64" ht="189" x14ac:dyDescent="0.3">
-      <c r="B21" s="57" t="s">
+      <c r="B21" s="52" t="s">
         <v>109</v>
       </c>
-      <c r="C21" s="80" t="s">
+      <c r="C21" s="70" t="s">
         <v>107</v>
       </c>
-      <c r="D21" s="34" t="s">
+      <c r="D21" s="30" t="s">
         <v>365</v>
       </c>
-      <c r="E21" s="64"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="65"/>
-      <c r="H21" s="65"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="65"/>
-      <c r="K21" s="65"/>
-      <c r="L21" s="65"/>
-      <c r="M21" s="65"/>
-      <c r="N21" s="65"/>
-      <c r="O21" s="65"/>
-      <c r="P21" s="66"/>
-      <c r="Q21" s="67"/>
-      <c r="R21" s="65"/>
-      <c r="S21" s="65"/>
-      <c r="T21" s="65"/>
-      <c r="U21" s="65"/>
-      <c r="V21" s="65"/>
-      <c r="W21" s="65"/>
-      <c r="X21" s="65"/>
-      <c r="Y21" s="65"/>
-      <c r="Z21" s="65"/>
-      <c r="AA21" s="65"/>
-      <c r="AB21" s="66"/>
-      <c r="AC21" s="67"/>
-      <c r="AD21" s="65"/>
-      <c r="AE21" s="65"/>
-      <c r="AF21" s="65"/>
-      <c r="AG21" s="68"/>
-      <c r="AH21" s="65"/>
-      <c r="AI21" s="69"/>
-      <c r="AJ21" s="65"/>
-      <c r="AK21" s="65"/>
-      <c r="AL21" s="65"/>
-      <c r="AM21" s="65"/>
-      <c r="AN21" s="66"/>
-      <c r="AO21" s="67"/>
-      <c r="AP21" s="69"/>
-      <c r="AQ21" s="69" t="s">
+      <c r="E21" s="59"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="60"/>
+      <c r="L21" s="60"/>
+      <c r="M21" s="60"/>
+      <c r="N21" s="60"/>
+      <c r="O21" s="60"/>
+      <c r="P21" s="61"/>
+      <c r="Q21" s="62"/>
+      <c r="R21" s="60"/>
+      <c r="S21" s="60"/>
+      <c r="T21" s="60"/>
+      <c r="U21" s="60"/>
+      <c r="V21" s="60"/>
+      <c r="W21" s="60"/>
+      <c r="X21" s="60"/>
+      <c r="Y21" s="60"/>
+      <c r="Z21" s="60"/>
+      <c r="AA21" s="60"/>
+      <c r="AB21" s="61"/>
+      <c r="AC21" s="62"/>
+      <c r="AD21" s="60"/>
+      <c r="AE21" s="60"/>
+      <c r="AF21" s="60"/>
+      <c r="AG21" s="63"/>
+      <c r="AH21" s="60"/>
+      <c r="AI21" s="64"/>
+      <c r="AJ21" s="60"/>
+      <c r="AK21" s="60"/>
+      <c r="AL21" s="60"/>
+      <c r="AM21" s="60"/>
+      <c r="AN21" s="61"/>
+      <c r="AO21" s="62"/>
+      <c r="AP21" s="64"/>
+      <c r="AQ21" s="64" t="s">
         <v>229</v>
       </c>
-      <c r="AR21" s="69"/>
-      <c r="AS21" s="65"/>
-      <c r="AT21" s="65"/>
-      <c r="AU21" s="69"/>
+      <c r="AR21" s="64"/>
+      <c r="AS21" s="60"/>
+      <c r="AT21" s="60"/>
+      <c r="AU21" s="64"/>
       <c r="AV21" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="AW21" s="65"/>
-      <c r="AX21" s="65"/>
-      <c r="AY21" s="69"/>
-      <c r="AZ21" s="70"/>
-      <c r="BA21" s="67"/>
+      <c r="AW21" s="60"/>
+      <c r="AX21" s="60"/>
+      <c r="AY21" s="64"/>
+      <c r="AZ21" s="65"/>
+      <c r="BA21" s="62"/>
       <c r="BB21" s="13"/>
-      <c r="BC21" s="73"/>
-      <c r="BD21" s="69" t="s">
+      <c r="BC21" s="64"/>
+      <c r="BD21" s="64" t="s">
         <v>230</v>
       </c>
-      <c r="BE21" s="72"/>
-      <c r="BF21" s="73"/>
-      <c r="BG21" s="69" t="s">
+      <c r="BE21" s="60"/>
+      <c r="BF21" s="64"/>
+      <c r="BG21" s="64" t="s">
         <v>231</v>
       </c>
-      <c r="BH21" s="73" t="s">
+      <c r="BH21" s="64" t="s">
         <v>364</v>
       </c>
-      <c r="BI21" s="69" t="s">
+      <c r="BI21" s="64" t="s">
         <v>232</v>
       </c>
-      <c r="BJ21" s="73"/>
-      <c r="BK21" s="73"/>
-      <c r="BL21" s="70"/>
+      <c r="BJ21" s="64"/>
+      <c r="BK21" s="64"/>
+      <c r="BL21" s="65"/>
     </row>
     <row r="22" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="57" t="s">
+      <c r="B22" s="52" t="s">
         <v>166</v>
       </c>
-      <c r="C22" s="80" t="s">
+      <c r="C22" s="70" t="s">
         <v>107</v>
       </c>
-      <c r="D22" s="39"/>
-      <c r="E22" s="64"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="65"/>
-      <c r="H22" s="65"/>
-      <c r="I22" s="65"/>
-      <c r="J22" s="65"/>
-      <c r="K22" s="65"/>
-      <c r="L22" s="65"/>
-      <c r="M22" s="65"/>
-      <c r="N22" s="65"/>
-      <c r="O22" s="65"/>
-      <c r="P22" s="66"/>
-      <c r="Q22" s="67"/>
-      <c r="R22" s="65"/>
-      <c r="S22" s="65"/>
-      <c r="T22" s="65"/>
-      <c r="U22" s="65"/>
-      <c r="V22" s="65"/>
-      <c r="W22" s="65"/>
-      <c r="X22" s="65"/>
-      <c r="Y22" s="65"/>
-      <c r="Z22" s="65"/>
-      <c r="AA22" s="65"/>
-      <c r="AB22" s="66"/>
-      <c r="AC22" s="67"/>
-      <c r="AD22" s="65"/>
-      <c r="AE22" s="65"/>
-      <c r="AF22" s="65"/>
-      <c r="AG22" s="68"/>
-      <c r="AH22" s="65"/>
-      <c r="AI22" s="69"/>
-      <c r="AJ22" s="65"/>
-      <c r="AK22" s="65"/>
-      <c r="AL22" s="65"/>
-      <c r="AM22" s="65"/>
-      <c r="AN22" s="66"/>
-      <c r="AO22" s="67"/>
-      <c r="AP22" s="69"/>
-      <c r="AQ22" s="69"/>
-      <c r="AR22" s="69"/>
-      <c r="AS22" s="65"/>
-      <c r="AT22" s="65"/>
-      <c r="AU22" s="69"/>
-      <c r="AV22" s="65"/>
-      <c r="AW22" s="65"/>
-      <c r="AX22" s="65"/>
-      <c r="AY22" s="69"/>
-      <c r="AZ22" s="70"/>
-      <c r="BA22" s="67"/>
-      <c r="BB22" s="72"/>
-      <c r="BC22" s="73"/>
-      <c r="BD22" s="72"/>
-      <c r="BE22" s="72"/>
-      <c r="BF22" s="73"/>
-      <c r="BG22" s="73"/>
-      <c r="BH22" s="73"/>
-      <c r="BI22" s="73"/>
-      <c r="BJ22" s="73"/>
-      <c r="BK22" s="73"/>
-      <c r="BL22" s="70"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="60"/>
+      <c r="K22" s="60"/>
+      <c r="L22" s="60"/>
+      <c r="M22" s="60"/>
+      <c r="N22" s="60"/>
+      <c r="O22" s="60"/>
+      <c r="P22" s="61"/>
+      <c r="Q22" s="62"/>
+      <c r="R22" s="60"/>
+      <c r="S22" s="60"/>
+      <c r="T22" s="60"/>
+      <c r="U22" s="60"/>
+      <c r="V22" s="60"/>
+      <c r="W22" s="60"/>
+      <c r="X22" s="60"/>
+      <c r="Y22" s="60"/>
+      <c r="Z22" s="60"/>
+      <c r="AA22" s="60"/>
+      <c r="AB22" s="61"/>
+      <c r="AC22" s="62"/>
+      <c r="AD22" s="60"/>
+      <c r="AE22" s="60"/>
+      <c r="AF22" s="60"/>
+      <c r="AG22" s="63"/>
+      <c r="AH22" s="60"/>
+      <c r="AI22" s="64"/>
+      <c r="AJ22" s="60"/>
+      <c r="AK22" s="60"/>
+      <c r="AL22" s="60"/>
+      <c r="AM22" s="60"/>
+      <c r="AN22" s="61"/>
+      <c r="AO22" s="62"/>
+      <c r="AP22" s="64"/>
+      <c r="AQ22" s="64"/>
+      <c r="AR22" s="64"/>
+      <c r="AS22" s="60"/>
+      <c r="AT22" s="60"/>
+      <c r="AU22" s="64"/>
+      <c r="AV22" s="60"/>
+      <c r="AW22" s="60"/>
+      <c r="AX22" s="60"/>
+      <c r="AY22" s="64"/>
+      <c r="AZ22" s="65"/>
+      <c r="BA22" s="62"/>
+      <c r="BB22" s="60"/>
+      <c r="BC22" s="64"/>
+      <c r="BD22" s="60"/>
+      <c r="BE22" s="60"/>
+      <c r="BF22" s="64"/>
+      <c r="BG22" s="64"/>
+      <c r="BH22" s="64"/>
+      <c r="BI22" s="64"/>
+      <c r="BJ22" s="64"/>
+      <c r="BK22" s="64"/>
+      <c r="BL22" s="65"/>
     </row>
     <row r="23" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="57" t="s">
+      <c r="B23" s="52" t="s">
         <v>326</v>
       </c>
-      <c r="C23" s="80"/>
-      <c r="D23" s="165" t="s">
+      <c r="C23" s="70"/>
+      <c r="D23" s="153" t="s">
         <v>319</v>
       </c>
-      <c r="E23" s="64"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="65"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="65"/>
-      <c r="K23" s="65"/>
-      <c r="L23" s="65"/>
-      <c r="M23" s="65"/>
-      <c r="N23" s="65"/>
-      <c r="O23" s="65"/>
-      <c r="P23" s="66"/>
-      <c r="Q23" s="67"/>
-      <c r="R23" s="65"/>
-      <c r="S23" s="65"/>
-      <c r="T23" s="65"/>
-      <c r="U23" s="65"/>
-      <c r="V23" s="65"/>
-      <c r="W23" s="65"/>
-      <c r="X23" s="65"/>
-      <c r="Y23" s="65"/>
-      <c r="Z23" s="65"/>
-      <c r="AA23" s="65"/>
-      <c r="AB23" s="66"/>
-      <c r="AC23" s="67"/>
-      <c r="AD23" s="65"/>
-      <c r="AE23" s="65"/>
-      <c r="AF23" s="69" t="s">
+      <c r="E23" s="59"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="60"/>
+      <c r="J23" s="60"/>
+      <c r="K23" s="60"/>
+      <c r="L23" s="60"/>
+      <c r="M23" s="60"/>
+      <c r="N23" s="60"/>
+      <c r="O23" s="60"/>
+      <c r="P23" s="61"/>
+      <c r="Q23" s="62"/>
+      <c r="R23" s="60"/>
+      <c r="S23" s="60"/>
+      <c r="T23" s="60"/>
+      <c r="U23" s="60"/>
+      <c r="V23" s="60"/>
+      <c r="W23" s="60"/>
+      <c r="X23" s="60"/>
+      <c r="Y23" s="60"/>
+      <c r="Z23" s="60"/>
+      <c r="AA23" s="60"/>
+      <c r="AB23" s="61"/>
+      <c r="AC23" s="62"/>
+      <c r="AD23" s="60"/>
+      <c r="AE23" s="60"/>
+      <c r="AF23" s="64" t="s">
         <v>320</v>
       </c>
-      <c r="AG23" s="68"/>
-      <c r="AH23" s="65"/>
-      <c r="AI23" s="69"/>
-      <c r="AJ23" s="65"/>
-      <c r="AK23" s="65"/>
-      <c r="AL23" s="69" t="s">
+      <c r="AG23" s="63"/>
+      <c r="AH23" s="60"/>
+      <c r="AI23" s="64"/>
+      <c r="AJ23" s="60"/>
+      <c r="AK23" s="60"/>
+      <c r="AL23" s="64" t="s">
         <v>321</v>
       </c>
-      <c r="AM23" s="65"/>
-      <c r="AN23" s="66"/>
-      <c r="AO23" s="67"/>
-      <c r="AP23" s="69"/>
-      <c r="AQ23" s="69" t="s">
+      <c r="AM23" s="60"/>
+      <c r="AN23" s="61"/>
+      <c r="AO23" s="62"/>
+      <c r="AP23" s="64"/>
+      <c r="AQ23" s="64" t="s">
         <v>328</v>
       </c>
-      <c r="AR23" s="69"/>
-      <c r="AS23" s="65"/>
-      <c r="AT23" s="69" t="s">
+      <c r="AR23" s="64"/>
+      <c r="AS23" s="60"/>
+      <c r="AT23" s="64" t="s">
         <v>327</v>
       </c>
-      <c r="AU23" s="69"/>
-      <c r="AV23" s="65"/>
-      <c r="AW23" s="65"/>
-      <c r="AX23" s="69" t="s">
+      <c r="AU23" s="64"/>
+      <c r="AV23" s="60"/>
+      <c r="AW23" s="60"/>
+      <c r="AX23" s="64" t="s">
         <v>322</v>
       </c>
-      <c r="AY23" s="69"/>
-      <c r="AZ23" s="70"/>
-      <c r="BA23" s="166" t="s">
+      <c r="AY23" s="64"/>
+      <c r="AZ23" s="65"/>
+      <c r="BA23" s="154" t="s">
         <v>323</v>
       </c>
-      <c r="BB23" s="72"/>
-      <c r="BC23" s="73"/>
-      <c r="BD23" s="72"/>
-      <c r="BE23" s="72"/>
-      <c r="BF23" s="73"/>
-      <c r="BG23" s="73"/>
-      <c r="BH23" s="73"/>
-      <c r="BI23" s="73"/>
-      <c r="BJ23" s="73"/>
-      <c r="BK23" s="73"/>
-      <c r="BL23" s="70"/>
+      <c r="BB23" s="60"/>
+      <c r="BC23" s="64"/>
+      <c r="BD23" s="60"/>
+      <c r="BE23" s="60"/>
+      <c r="BF23" s="64"/>
+      <c r="BG23" s="64"/>
+      <c r="BH23" s="64"/>
+      <c r="BI23" s="64"/>
+      <c r="BJ23" s="64"/>
+      <c r="BK23" s="64"/>
+      <c r="BL23" s="65"/>
     </row>
     <row r="24" spans="2:64" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="79" t="s">
+      <c r="B24" s="69" t="s">
         <v>325</v>
       </c>
-      <c r="C24" s="164"/>
-      <c r="D24" s="162" t="s">
+      <c r="C24" s="152"/>
+      <c r="D24" s="150" t="s">
         <v>318</v>
       </c>
-      <c r="E24" s="49"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="50"/>
-      <c r="J24" s="50"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="50"/>
-      <c r="M24" s="50"/>
-      <c r="N24" s="50"/>
-      <c r="O24" s="50"/>
-      <c r="P24" s="51"/>
-      <c r="Q24" s="52"/>
-      <c r="R24" s="50"/>
-      <c r="S24" s="50"/>
-      <c r="T24" s="50"/>
-      <c r="U24" s="50"/>
-      <c r="V24" s="50"/>
-      <c r="W24" s="50"/>
-      <c r="X24" s="50"/>
-      <c r="Y24" s="50"/>
-      <c r="Z24" s="50"/>
-      <c r="AA24" s="50"/>
-      <c r="AB24" s="51"/>
-      <c r="AC24" s="52"/>
-      <c r="AD24" s="50"/>
-      <c r="AE24" s="50"/>
-      <c r="AF24" s="50"/>
-      <c r="AG24" s="53"/>
-      <c r="AH24" s="54" t="s">
+      <c r="E24" s="44"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="45"/>
+      <c r="M24" s="45"/>
+      <c r="N24" s="45"/>
+      <c r="O24" s="45"/>
+      <c r="P24" s="46"/>
+      <c r="Q24" s="47"/>
+      <c r="R24" s="45"/>
+      <c r="S24" s="45"/>
+      <c r="T24" s="45"/>
+      <c r="U24" s="45"/>
+      <c r="V24" s="45"/>
+      <c r="W24" s="45"/>
+      <c r="X24" s="45"/>
+      <c r="Y24" s="45"/>
+      <c r="Z24" s="45"/>
+      <c r="AA24" s="45"/>
+      <c r="AB24" s="46"/>
+      <c r="AC24" s="47"/>
+      <c r="AD24" s="45"/>
+      <c r="AE24" s="45"/>
+      <c r="AF24" s="45"/>
+      <c r="AG24" s="48"/>
+      <c r="AH24" s="49" t="s">
         <v>324</v>
       </c>
-      <c r="AI24" s="54"/>
-      <c r="AJ24" s="50"/>
-      <c r="AK24" s="50"/>
-      <c r="AL24" s="50"/>
-      <c r="AM24" s="50"/>
-      <c r="AN24" s="51"/>
-      <c r="AO24" s="52"/>
-      <c r="AP24" s="54"/>
-      <c r="AQ24" s="54"/>
-      <c r="AR24" s="54"/>
-      <c r="AS24" s="50"/>
-      <c r="AT24" s="54" t="s">
+      <c r="AI24" s="49"/>
+      <c r="AJ24" s="45"/>
+      <c r="AK24" s="45"/>
+      <c r="AL24" s="45"/>
+      <c r="AM24" s="45"/>
+      <c r="AN24" s="46"/>
+      <c r="AO24" s="47"/>
+      <c r="AP24" s="49"/>
+      <c r="AQ24" s="49"/>
+      <c r="AR24" s="49"/>
+      <c r="AS24" s="45"/>
+      <c r="AT24" s="49" t="s">
         <v>329</v>
       </c>
-      <c r="AU24" s="54"/>
-      <c r="AV24" s="50"/>
-      <c r="AW24" s="50"/>
-      <c r="AX24" s="54" t="s">
+      <c r="AU24" s="49"/>
+      <c r="AV24" s="45"/>
+      <c r="AW24" s="45"/>
+      <c r="AX24" s="49" t="s">
         <v>330</v>
       </c>
-      <c r="AY24" s="54"/>
-      <c r="AZ24" s="55"/>
-      <c r="BA24" s="167" t="s">
+      <c r="AY24" s="49"/>
+      <c r="AZ24" s="50"/>
+      <c r="BA24" s="155" t="s">
         <v>331</v>
       </c>
-      <c r="BB24" s="74"/>
-      <c r="BC24" s="75"/>
-      <c r="BD24" s="74"/>
-      <c r="BE24" s="74"/>
-      <c r="BF24" s="75"/>
-      <c r="BG24" s="75"/>
-      <c r="BH24" s="75"/>
-      <c r="BI24" s="75"/>
-      <c r="BJ24" s="75"/>
-      <c r="BK24" s="75"/>
-      <c r="BL24" s="55"/>
+      <c r="BB24" s="45"/>
+      <c r="BC24" s="49"/>
+      <c r="BD24" s="45"/>
+      <c r="BE24" s="45"/>
+      <c r="BF24" s="49"/>
+      <c r="BG24" s="49"/>
+      <c r="BH24" s="49"/>
+      <c r="BI24" s="49"/>
+      <c r="BJ24" s="49"/>
+      <c r="BK24" s="49"/>
+      <c r="BL24" s="50"/>
     </row>
     <row r="25" spans="2:64" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -13904,388 +13915,386 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:J20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
-    <col min="2" max="2" width="9" style="81"/>
-    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
-    <col min="5" max="5" width="43" style="81" customWidth="1"/>
-    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
-    <col min="7" max="10" width="62.125" style="81" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="81"/>
+    <col min="1" max="1" width="3.375" style="71" customWidth="1"/>
+    <col min="2" max="2" width="9" style="71"/>
+    <col min="3" max="4" width="14.75" style="71" customWidth="1"/>
+    <col min="5" max="5" width="43" style="71" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="71" customWidth="1"/>
+    <col min="7" max="10" width="62.125" style="71" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="71"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="109" t="s">
+      <c r="B1" s="99" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="107"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="97"/>
     </row>
     <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="195" t="s">
+      <c r="B2" s="183" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="199" t="s">
+      <c r="C2" s="187" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="199" t="s">
+      <c r="D2" s="187" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="197" t="s">
+      <c r="E2" s="185" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="193" t="s">
+      <c r="F2" s="181" t="s">
         <v>378</v>
       </c>
-      <c r="G2" s="193"/>
-      <c r="H2" s="193"/>
-      <c r="I2" s="201"/>
-      <c r="J2" s="194"/>
+      <c r="G2" s="181"/>
+      <c r="H2" s="181"/>
+      <c r="I2" s="189"/>
+      <c r="J2" s="182"/>
     </row>
     <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="196"/>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="97" t="s">
+      <c r="B3" s="184"/>
+      <c r="C3" s="188"/>
+      <c r="D3" s="188"/>
+      <c r="E3" s="186"/>
+      <c r="F3" s="87" t="s">
         <v>379</v>
       </c>
-      <c r="G3" s="97"/>
-      <c r="H3" s="97"/>
-      <c r="I3" s="170"/>
-      <c r="J3" s="98"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
+      <c r="I3" s="158"/>
+      <c r="J3" s="88"/>
     </row>
     <row r="4" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="151" t="s">
+      <c r="B4" s="139" t="s">
         <v>108</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="106" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="116" t="s">
+      <c r="D4" s="106" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="140" t="s">
+      <c r="E4" s="128" t="s">
         <v>140</v>
       </c>
-      <c r="F4" s="141"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="171"/>
-      <c r="J4" s="92"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="130"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="159"/>
+      <c r="J4" s="82"/>
     </row>
     <row r="5" spans="1:10" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="B5" s="154" t="s">
+      <c r="B5" s="142" t="s">
         <v>181</v>
       </c>
-      <c r="C5" s="117" t="s">
+      <c r="C5" s="107" t="s">
         <v>267</v>
       </c>
-      <c r="D5" s="117" t="s">
+      <c r="D5" s="107" t="s">
         <v>180</v>
       </c>
-      <c r="E5" s="100" t="s">
+      <c r="E5" s="90" t="s">
         <v>161</v>
       </c>
-      <c r="F5" s="123"/>
-      <c r="G5" s="123"/>
-      <c r="H5" s="123"/>
-      <c r="I5" s="172"/>
-      <c r="J5" s="135"/>
+      <c r="F5" s="112"/>
+      <c r="G5" s="112"/>
+      <c r="H5" s="112"/>
+      <c r="I5" s="160"/>
+      <c r="J5" s="124"/>
     </row>
     <row r="6" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="152" t="s">
+      <c r="B6" s="140" t="s">
         <v>118</v>
       </c>
-      <c r="C6" s="117" t="s">
+      <c r="C6" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D6" s="117" t="s">
+      <c r="D6" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E6" s="100" t="s">
+      <c r="E6" s="90" t="s">
         <v>161</v>
       </c>
-      <c r="F6" s="123"/>
-      <c r="G6" s="123"/>
-      <c r="H6" s="123"/>
-      <c r="I6" s="172"/>
-      <c r="J6" s="135"/>
+      <c r="F6" s="112"/>
+      <c r="G6" s="112"/>
+      <c r="H6" s="112"/>
+      <c r="I6" s="160"/>
+      <c r="J6" s="124"/>
     </row>
     <row r="7" spans="1:10" ht="138" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="152" t="s">
+      <c r="B7" s="140" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="117" t="s">
+      <c r="C7" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D7" s="117" t="s">
+      <c r="D7" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="100" t="s">
+      <c r="E7" s="90" t="s">
         <v>162</v>
       </c>
-      <c r="F7" s="123"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="89"/>
-      <c r="I7" s="173"/>
-      <c r="J7" s="93"/>
+      <c r="F7" s="112"/>
+      <c r="G7" s="95"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="161"/>
+      <c r="J7" s="83"/>
     </row>
     <row r="8" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="152" t="s">
+      <c r="B8" s="140" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="117" t="s">
+      <c r="C8" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D8" s="117" t="s">
+      <c r="D8" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E8" s="91" t="s">
+      <c r="E8" s="81" t="s">
         <v>139</v>
       </c>
-      <c r="F8" s="114"/>
-      <c r="G8" s="104"/>
-      <c r="H8" s="89"/>
-      <c r="I8" s="173"/>
-      <c r="J8" s="93"/>
+      <c r="F8" s="104"/>
+      <c r="G8" s="94"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="161"/>
+      <c r="J8" s="83"/>
     </row>
     <row r="9" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="153" t="s">
+      <c r="B9" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="117" t="s">
+      <c r="C9" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D9" s="117" t="s">
+      <c r="D9" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E9" s="91" t="s">
+      <c r="E9" s="81" t="s">
         <v>152</v>
       </c>
-      <c r="F9" s="114"/>
-      <c r="G9" s="105"/>
-      <c r="H9" s="138"/>
-      <c r="I9" s="89"/>
-      <c r="J9" s="93"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="95"/>
+      <c r="I9" s="79"/>
+      <c r="J9" s="83"/>
     </row>
     <row r="10" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="153" t="s">
+      <c r="B10" s="141" t="s">
         <v>123</v>
       </c>
-      <c r="C10" s="117" t="s">
+      <c r="C10" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D10" s="117" t="s">
+      <c r="D10" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E10" s="91" t="s">
+      <c r="E10" s="81" t="s">
         <v>153</v>
       </c>
-      <c r="F10" s="114"/>
-      <c r="G10" s="105"/>
-      <c r="H10" s="89"/>
-      <c r="I10" s="173"/>
-      <c r="J10" s="93"/>
+      <c r="F10" s="104"/>
+      <c r="G10" s="95"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="161"/>
+      <c r="J10" s="83"/>
     </row>
     <row r="11" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="153" t="s">
+      <c r="B11" s="141" t="s">
         <v>124</v>
       </c>
-      <c r="C11" s="117" t="s">
+      <c r="C11" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D11" s="117" t="s">
+      <c r="D11" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E11" s="91" t="s">
+      <c r="E11" s="81" t="s">
         <v>154</v>
       </c>
-      <c r="F11" s="114"/>
-      <c r="G11" s="105"/>
-      <c r="H11" s="89"/>
-      <c r="I11" s="173"/>
-      <c r="J11" s="93"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="95"/>
+      <c r="H11" s="79"/>
+      <c r="I11" s="161"/>
+      <c r="J11" s="83"/>
     </row>
     <row r="12" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="153" t="s">
+      <c r="B12" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="C12" s="117" t="s">
+      <c r="C12" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D12" s="117" t="s">
+      <c r="D12" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E12" s="91" t="s">
+      <c r="E12" s="81" t="s">
         <v>155</v>
       </c>
-      <c r="F12" s="114"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="138"/>
-      <c r="I12" s="89"/>
-      <c r="J12" s="93"/>
+      <c r="F12" s="104"/>
+      <c r="G12" s="95"/>
+      <c r="I12" s="79"/>
+      <c r="J12" s="83"/>
     </row>
     <row r="13" spans="1:10" ht="27" x14ac:dyDescent="0.3">
-      <c r="B13" s="132" t="s">
+      <c r="B13" s="121" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="117" t="s">
+      <c r="C13" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="D13" s="117" t="s">
+      <c r="D13" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="100" t="s">
+      <c r="E13" s="90" t="s">
         <v>260</v>
       </c>
-      <c r="F13" s="105"/>
-      <c r="G13" s="157"/>
-      <c r="H13" s="105"/>
-      <c r="I13" s="105"/>
-      <c r="J13" s="122"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="145"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="111"/>
     </row>
     <row r="14" spans="1:10" ht="27" x14ac:dyDescent="0.3">
-      <c r="B14" s="131" t="s">
+      <c r="B14" s="120" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="117" t="s">
+      <c r="C14" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="D14" s="117" t="s">
+      <c r="D14" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E14" s="100" t="s">
+      <c r="E14" s="90" t="s">
         <v>261</v>
       </c>
-      <c r="F14" s="105"/>
-      <c r="G14" s="157"/>
-      <c r="H14" s="105"/>
-      <c r="I14" s="105"/>
-      <c r="J14" s="122"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="145"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="111"/>
     </row>
     <row r="15" spans="1:10" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="B15" s="131" t="s">
+      <c r="B15" s="120" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="117" t="s">
+      <c r="C15" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="D15" s="117" t="s">
+      <c r="D15" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E15" s="100" t="s">
+      <c r="E15" s="90" t="s">
         <v>259</v>
       </c>
-      <c r="F15" s="105"/>
-      <c r="G15" s="157"/>
-      <c r="H15" s="157"/>
-      <c r="I15" s="157"/>
-      <c r="J15" s="122"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="145"/>
+      <c r="H15" s="145"/>
+      <c r="I15" s="145"/>
+      <c r="J15" s="111"/>
     </row>
     <row r="16" spans="1:10" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="B16" s="131" t="s">
+      <c r="B16" s="120" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="117" t="s">
+      <c r="C16" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="D16" s="117" t="s">
+      <c r="D16" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E16" s="100" t="s">
+      <c r="E16" s="90" t="s">
         <v>262</v>
       </c>
-      <c r="F16" s="105"/>
-      <c r="G16" s="157"/>
-      <c r="H16" s="157"/>
-      <c r="I16" s="157"/>
-      <c r="J16" s="122"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="145"/>
+      <c r="H16" s="145"/>
+      <c r="I16" s="145"/>
+      <c r="J16" s="111"/>
     </row>
     <row r="17" spans="2:10" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="B17" s="130" t="s">
+      <c r="B17" s="119" t="s">
         <v>167</v>
       </c>
-      <c r="C17" s="117" t="s">
+      <c r="C17" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="D17" s="117" t="s">
+      <c r="D17" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E17" s="113" t="s">
+      <c r="E17" s="103" t="s">
         <v>303</v>
       </c>
-      <c r="F17" s="119"/>
-      <c r="G17" s="169"/>
-      <c r="H17" s="169"/>
-      <c r="I17" s="169"/>
-      <c r="J17" s="168"/>
+      <c r="F17" s="109"/>
+      <c r="G17" s="157"/>
+      <c r="H17" s="157"/>
+      <c r="I17" s="157"/>
+      <c r="J17" s="156"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B18" s="131" t="s">
+      <c r="B18" s="120" t="s">
         <v>141</v>
       </c>
-      <c r="C18" s="117" t="s">
+      <c r="C18" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="D18" s="117" t="s">
+      <c r="D18" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E18" s="113"/>
-      <c r="F18" s="155"/>
-      <c r="G18" s="158"/>
-      <c r="H18" s="133"/>
-      <c r="I18" s="129"/>
-      <c r="J18" s="136"/>
+      <c r="E18" s="103"/>
+      <c r="F18" s="143"/>
+      <c r="G18" s="146"/>
+      <c r="H18" s="122"/>
+      <c r="I18" s="118"/>
+      <c r="J18" s="125"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B19" s="150" t="s">
+      <c r="B19" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="139" t="s">
+      <c r="C19" s="127" t="s">
         <v>270</v>
       </c>
-      <c r="D19" s="139" t="s">
+      <c r="D19" s="127" t="s">
         <v>178</v>
       </c>
-      <c r="E19" s="91" t="s">
+      <c r="E19" s="81" t="s">
         <v>156</v>
       </c>
-      <c r="F19" s="105" t="s">
+      <c r="F19" s="95" t="s">
         <v>263</v>
       </c>
-      <c r="G19" s="158"/>
-      <c r="H19" s="133"/>
-      <c r="I19" s="174"/>
-      <c r="J19" s="134"/>
+      <c r="G19" s="146"/>
+      <c r="H19" s="122"/>
+      <c r="I19" s="162"/>
+      <c r="J19" s="123"/>
     </row>
     <row r="20" spans="2:10" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="143" t="s">
+      <c r="B20" s="131" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="144" t="s">
+      <c r="C20" s="132" t="s">
         <v>270</v>
       </c>
-      <c r="D20" s="144" t="s">
+      <c r="D20" s="132" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="145" t="s">
+      <c r="E20" s="133" t="s">
         <v>258</v>
       </c>
-      <c r="F20" s="161" t="s">
+      <c r="F20" s="149" t="s">
         <v>263</v>
       </c>
-      <c r="G20" s="147"/>
-      <c r="H20" s="148"/>
-      <c r="I20" s="175"/>
-      <c r="J20" s="149"/>
+      <c r="G20" s="135"/>
+      <c r="H20" s="136"/>
+      <c r="I20" s="163"/>
+      <c r="J20" s="137"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -14302,7 +14311,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -14319,13 +14328,13 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="124" t="s">
+      <c r="A2" s="113" t="s">
         <v>237</v>
       </c>
       <c r="B2" t="s">
         <v>238</v>
       </c>
-      <c r="C2" s="125" t="s">
+      <c r="C2" s="114" t="s">
         <v>239</v>
       </c>
       <c r="D2" t="s">
@@ -14333,13 +14342,13 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="124" t="s">
+      <c r="A3" s="113" t="s">
         <v>241</v>
       </c>
       <c r="B3" t="s">
         <v>238</v>
       </c>
-      <c r="C3" s="126" t="s">
+      <c r="C3" s="115" t="s">
         <v>242</v>
       </c>
       <c r="D3" t="s">
@@ -14347,13 +14356,13 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="124" t="s">
+      <c r="A4" s="113" t="s">
         <v>243</v>
       </c>
       <c r="B4" t="s">
         <v>238</v>
       </c>
-      <c r="C4" s="126" t="s">
+      <c r="C4" s="115" t="s">
         <v>244</v>
       </c>
       <c r="D4" t="s">
@@ -14361,13 +14370,13 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="116" t="s">
         <v>245</v>
       </c>
       <c r="B5" t="s">
         <v>238</v>
       </c>
-      <c r="C5" s="126" t="s">
+      <c r="C5" s="115" t="s">
         <v>246</v>
       </c>
       <c r="D5" t="s">
@@ -14375,13 +14384,13 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="125" t="s">
+      <c r="A6" s="114" t="s">
         <v>247</v>
       </c>
       <c r="B6" t="s">
         <v>240</v>
       </c>
-      <c r="C6" s="128" t="s">
+      <c r="C6" s="117" t="s">
         <v>248</v>
       </c>
       <c r="D6" t="s">
@@ -14389,13 +14398,13 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="125" t="s">
+      <c r="A7" s="114" t="s">
         <v>249</v>
       </c>
       <c r="B7" t="s">
         <v>240</v>
       </c>
-      <c r="C7" s="128" t="s">
+      <c r="C7" s="117" t="s">
         <v>250</v>
       </c>
       <c r="D7" t="s">
@@ -14403,7 +14412,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C8" s="124" t="s">
+      <c r="C8" s="113" t="s">
         <v>251</v>
       </c>
       <c r="D8" t="s">
@@ -14411,7 +14420,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C9" s="124" t="s">
+      <c r="C9" s="113" t="s">
         <v>252</v>
       </c>
       <c r="D9" t="s">
@@ -14419,7 +14428,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C10" s="128" t="s">
+      <c r="C10" s="117" t="s">
         <v>253</v>
       </c>
       <c r="D10" t="s">
@@ -14433,710 +14442,710 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:N22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
-    <col min="2" max="2" width="9" style="81"/>
-    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
-    <col min="5" max="5" width="43" style="81" customWidth="1"/>
-    <col min="6" max="6" width="62.125" style="81" customWidth="1"/>
-    <col min="7" max="7" width="61.875" style="81" customWidth="1"/>
-    <col min="8" max="14" width="62.125" style="81" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="81"/>
+    <col min="1" max="1" width="3.375" style="71" customWidth="1"/>
+    <col min="2" max="2" width="9" style="71"/>
+    <col min="3" max="4" width="14.75" style="71" customWidth="1"/>
+    <col min="5" max="5" width="43" style="71" customWidth="1"/>
+    <col min="6" max="6" width="62.125" style="71" customWidth="1"/>
+    <col min="7" max="7" width="61.875" style="71" customWidth="1"/>
+    <col min="8" max="14" width="62.125" style="71" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="71"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="98" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="109" t="s">
+      <c r="B1" s="99" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="107"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="97"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="195" t="s">
+      <c r="B2" s="183" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="199" t="s">
+      <c r="C2" s="187" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="199" t="s">
+      <c r="D2" s="187" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="197" t="s">
+      <c r="E2" s="185" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="96" t="s">
+      <c r="F2" s="86" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="193" t="s">
+      <c r="G2" s="181" t="s">
         <v>113</v>
       </c>
-      <c r="H2" s="193"/>
-      <c r="I2" s="193"/>
-      <c r="J2" s="194"/>
-      <c r="K2" s="193" t="s">
+      <c r="H2" s="181"/>
+      <c r="I2" s="181"/>
+      <c r="J2" s="182"/>
+      <c r="K2" s="181" t="s">
         <v>182</v>
       </c>
-      <c r="L2" s="193"/>
-      <c r="M2" s="193"/>
-      <c r="N2" s="194"/>
+      <c r="L2" s="181"/>
+      <c r="M2" s="181"/>
+      <c r="N2" s="182"/>
     </row>
     <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="196"/>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="97" t="s">
+      <c r="B3" s="184"/>
+      <c r="C3" s="188"/>
+      <c r="D3" s="188"/>
+      <c r="E3" s="186"/>
+      <c r="F3" s="87" t="s">
         <v>111</v>
       </c>
-      <c r="G3" s="97" t="s">
+      <c r="G3" s="87" t="s">
         <v>114</v>
       </c>
-      <c r="H3" s="97" t="s">
+      <c r="H3" s="87" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="97" t="s">
+      <c r="I3" s="87" t="s">
         <v>116</v>
       </c>
-      <c r="J3" s="98" t="s">
+      <c r="J3" s="88" t="s">
         <v>110</v>
       </c>
-      <c r="K3" s="97" t="s">
+      <c r="K3" s="87" t="s">
         <v>212</v>
       </c>
-      <c r="L3" s="97" t="s">
+      <c r="L3" s="87" t="s">
         <v>115</v>
       </c>
-      <c r="M3" s="97" t="s">
+      <c r="M3" s="87" t="s">
         <v>116</v>
       </c>
-      <c r="N3" s="98" t="s">
+      <c r="N3" s="88" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="108" x14ac:dyDescent="0.3">
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="72" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="106" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="116" t="s">
+      <c r="D4" s="106" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="90" t="s">
+      <c r="E4" s="80" t="s">
         <v>152</v>
       </c>
-      <c r="F4" s="105" t="s">
+      <c r="F4" s="95" t="s">
         <v>143</v>
       </c>
-      <c r="G4" s="114" t="s">
+      <c r="G4" s="104" t="s">
         <v>171</v>
       </c>
-      <c r="H4" s="105" t="s">
+      <c r="H4" s="95" t="s">
         <v>184</v>
       </c>
-      <c r="I4" s="105" t="s">
+      <c r="I4" s="95" t="s">
         <v>198</v>
       </c>
-      <c r="J4" s="92"/>
-      <c r="K4" s="105" t="s">
+      <c r="J4" s="82"/>
+      <c r="K4" s="95" t="s">
         <v>205</v>
       </c>
-      <c r="L4" s="105" t="s">
+      <c r="L4" s="95" t="s">
         <v>174</v>
       </c>
-      <c r="M4" s="105"/>
-      <c r="N4" s="92"/>
+      <c r="M4" s="95"/>
+      <c r="N4" s="82"/>
     </row>
     <row r="5" spans="1:14" ht="108" x14ac:dyDescent="0.3">
-      <c r="B5" s="83" t="s">
+      <c r="B5" s="73" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="117" t="s">
+      <c r="C5" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="117" t="s">
+      <c r="D5" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="91" t="s">
+      <c r="E5" s="81" t="s">
         <v>153</v>
       </c>
-      <c r="F5" s="105" t="s">
+      <c r="F5" s="95" t="s">
         <v>143</v>
       </c>
-      <c r="G5" s="114" t="s">
+      <c r="G5" s="104" t="s">
         <v>171</v>
       </c>
-      <c r="H5" s="105" t="s">
+      <c r="H5" s="95" t="s">
         <v>184</v>
       </c>
-      <c r="I5" s="105" t="s">
+      <c r="I5" s="95" t="s">
         <v>198</v>
       </c>
-      <c r="J5" s="93"/>
-      <c r="K5" s="105" t="s">
+      <c r="J5" s="83"/>
+      <c r="K5" s="95" t="s">
         <v>205</v>
       </c>
-      <c r="L5" s="105" t="s">
+      <c r="L5" s="95" t="s">
         <v>174</v>
       </c>
-      <c r="M5" s="105"/>
-      <c r="N5" s="93"/>
+      <c r="M5" s="95"/>
+      <c r="N5" s="83"/>
     </row>
     <row r="6" spans="1:14" ht="108" x14ac:dyDescent="0.3">
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="73" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="117" t="s">
+      <c r="C6" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D6" s="117" t="s">
+      <c r="D6" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E6" s="91" t="s">
+      <c r="E6" s="81" t="s">
         <v>154</v>
       </c>
-      <c r="F6" s="105" t="s">
+      <c r="F6" s="95" t="s">
         <v>143</v>
       </c>
-      <c r="G6" s="114" t="s">
+      <c r="G6" s="104" t="s">
         <v>171</v>
       </c>
-      <c r="H6" s="105" t="s">
+      <c r="H6" s="95" t="s">
         <v>184</v>
       </c>
-      <c r="I6" s="105" t="s">
+      <c r="I6" s="95" t="s">
         <v>198</v>
       </c>
-      <c r="J6" s="93"/>
-      <c r="K6" s="105" t="s">
+      <c r="J6" s="83"/>
+      <c r="K6" s="95" t="s">
         <v>205</v>
       </c>
-      <c r="L6" s="105" t="s">
+      <c r="L6" s="95" t="s">
         <v>174</v>
       </c>
-      <c r="M6" s="105"/>
-      <c r="N6" s="93"/>
+      <c r="M6" s="95"/>
+      <c r="N6" s="83"/>
     </row>
     <row r="7" spans="1:14" ht="108" x14ac:dyDescent="0.3">
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="73" t="s">
         <v>125</v>
       </c>
-      <c r="C7" s="117" t="s">
+      <c r="C7" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D7" s="117" t="s">
+      <c r="D7" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="91" t="s">
+      <c r="E7" s="81" t="s">
         <v>155</v>
       </c>
-      <c r="F7" s="105" t="s">
+      <c r="F7" s="95" t="s">
         <v>143</v>
       </c>
-      <c r="G7" s="114" t="s">
+      <c r="G7" s="104" t="s">
         <v>171</v>
       </c>
-      <c r="H7" s="105" t="s">
+      <c r="H7" s="95" t="s">
         <v>184</v>
       </c>
-      <c r="I7" s="105" t="s">
+      <c r="I7" s="95" t="s">
         <v>198</v>
       </c>
-      <c r="J7" s="93"/>
-      <c r="K7" s="105" t="s">
+      <c r="J7" s="83"/>
+      <c r="K7" s="95" t="s">
         <v>205</v>
       </c>
-      <c r="L7" s="105" t="s">
+      <c r="L7" s="95" t="s">
         <v>174</v>
       </c>
-      <c r="M7" s="105"/>
-      <c r="N7" s="93"/>
+      <c r="M7" s="95"/>
+      <c r="N7" s="83"/>
     </row>
     <row r="8" spans="1:14" ht="108" x14ac:dyDescent="0.3">
-      <c r="B8" s="84" t="s">
+      <c r="B8" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="117" t="s">
+      <c r="C8" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D8" s="117" t="s">
+      <c r="D8" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E8" s="91" t="s">
+      <c r="E8" s="81" t="s">
         <v>156</v>
       </c>
-      <c r="F8" s="105" t="s">
+      <c r="F8" s="95" t="s">
         <v>144</v>
       </c>
-      <c r="G8" s="114" t="s">
+      <c r="G8" s="104" t="s">
         <v>171</v>
       </c>
-      <c r="H8" s="105" t="s">
+      <c r="H8" s="95" t="s">
         <v>184</v>
       </c>
-      <c r="I8" s="105" t="s">
+      <c r="I8" s="95" t="s">
         <v>198</v>
       </c>
-      <c r="J8" s="93"/>
-      <c r="K8" s="105" t="s">
+      <c r="J8" s="83"/>
+      <c r="K8" s="95" t="s">
         <v>205</v>
       </c>
-      <c r="L8" s="105" t="s">
+      <c r="L8" s="95" t="s">
         <v>174</v>
       </c>
-      <c r="M8" s="105"/>
-      <c r="N8" s="93"/>
+      <c r="M8" s="95"/>
+      <c r="N8" s="83"/>
     </row>
     <row r="9" spans="1:14" ht="175.5" x14ac:dyDescent="0.3">
-      <c r="B9" s="84" t="s">
+      <c r="B9" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="117" t="s">
+      <c r="C9" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D9" s="117" t="s">
+      <c r="D9" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E9" s="100" t="s">
+      <c r="E9" s="90" t="s">
         <v>157</v>
       </c>
-      <c r="F9" s="105" t="s">
+      <c r="F9" s="95" t="s">
         <v>145</v>
       </c>
-      <c r="G9" s="114" t="s">
+      <c r="G9" s="104" t="s">
         <v>171</v>
       </c>
-      <c r="H9" s="105" t="s">
+      <c r="H9" s="95" t="s">
         <v>185</v>
       </c>
-      <c r="I9" s="105" t="s">
+      <c r="I9" s="95" t="s">
         <v>199</v>
       </c>
-      <c r="J9" s="93"/>
-      <c r="K9" s="105" t="s">
+      <c r="J9" s="83"/>
+      <c r="K9" s="95" t="s">
         <v>206</v>
       </c>
-      <c r="L9" s="105" t="s">
+      <c r="L9" s="95" t="s">
         <v>213</v>
       </c>
-      <c r="M9" s="105"/>
-      <c r="N9" s="93"/>
+      <c r="M9" s="95"/>
+      <c r="N9" s="83"/>
     </row>
     <row r="10" spans="1:14" ht="121.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="84" t="s">
+      <c r="B10" s="74" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="117" t="s">
+      <c r="C10" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D10" s="117" t="s">
+      <c r="D10" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E10" s="100" t="s">
+      <c r="E10" s="90" t="s">
         <v>158</v>
       </c>
-      <c r="F10" s="105" t="s">
+      <c r="F10" s="95" t="s">
         <v>144</v>
       </c>
-      <c r="G10" s="114" t="s">
+      <c r="G10" s="104" t="s">
         <v>171</v>
       </c>
-      <c r="H10" s="105" t="s">
+      <c r="H10" s="95" t="s">
         <v>184</v>
       </c>
-      <c r="I10" s="105" t="s">
+      <c r="I10" s="95" t="s">
         <v>200</v>
       </c>
-      <c r="J10" s="93"/>
-      <c r="K10" s="105" t="s">
+      <c r="J10" s="83"/>
+      <c r="K10" s="95" t="s">
         <v>205</v>
       </c>
-      <c r="L10" s="105" t="s">
+      <c r="L10" s="95" t="s">
         <v>174</v>
       </c>
-      <c r="M10" s="105"/>
-      <c r="N10" s="93"/>
+      <c r="M10" s="95"/>
+      <c r="N10" s="83"/>
     </row>
     <row r="11" spans="1:14" ht="108" x14ac:dyDescent="0.3">
-      <c r="B11" s="83" t="s">
+      <c r="B11" s="73" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="117" t="s">
+      <c r="C11" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D11" s="117" t="s">
+      <c r="D11" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E11" s="100" t="s">
+      <c r="E11" s="90" t="s">
         <v>159</v>
       </c>
-      <c r="F11" s="105" t="s">
+      <c r="F11" s="95" t="s">
         <v>142</v>
       </c>
-      <c r="G11" s="114" t="s">
+      <c r="G11" s="104" t="s">
         <v>171</v>
       </c>
-      <c r="H11" s="105" t="s">
+      <c r="H11" s="95" t="s">
         <v>183</v>
       </c>
-      <c r="I11" s="105" t="s">
+      <c r="I11" s="95" t="s">
         <v>194</v>
       </c>
-      <c r="J11" s="93"/>
-      <c r="K11" s="105" t="s">
+      <c r="J11" s="83"/>
+      <c r="K11" s="95" t="s">
         <v>207</v>
       </c>
-      <c r="L11" s="105" t="s">
+      <c r="L11" s="95" t="s">
         <v>174</v>
       </c>
-      <c r="M11" s="105"/>
-      <c r="N11" s="93"/>
+      <c r="M11" s="95"/>
+      <c r="N11" s="83"/>
     </row>
     <row r="12" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="84" t="s">
+      <c r="B12" s="74" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="117" t="s">
+      <c r="C12" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D12" s="117" t="s">
+      <c r="D12" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E12" s="100" t="s">
+      <c r="E12" s="90" t="s">
         <v>160</v>
       </c>
-      <c r="F12" s="105" t="s">
+      <c r="F12" s="95" t="s">
         <v>146</v>
       </c>
-      <c r="G12" s="114" t="s">
+      <c r="G12" s="104" t="s">
         <v>171</v>
       </c>
-      <c r="H12" s="105" t="s">
+      <c r="H12" s="95" t="s">
         <v>174</v>
       </c>
-      <c r="I12" s="105" t="s">
+      <c r="I12" s="95" t="s">
         <v>174</v>
       </c>
-      <c r="J12" s="93"/>
-      <c r="K12" s="105" t="s">
+      <c r="J12" s="83"/>
+      <c r="K12" s="95" t="s">
         <v>174</v>
       </c>
-      <c r="L12" s="105" t="s">
+      <c r="L12" s="95" t="s">
         <v>174</v>
       </c>
-      <c r="M12" s="105"/>
-      <c r="N12" s="93"/>
+      <c r="M12" s="95"/>
+      <c r="N12" s="83"/>
     </row>
     <row r="13" spans="1:14" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="84" t="s">
+      <c r="B13" s="74" t="s">
         <v>118</v>
       </c>
-      <c r="C13" s="117" t="s">
+      <c r="C13" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D13" s="117" t="s">
+      <c r="D13" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="100" t="s">
+      <c r="E13" s="90" t="s">
         <v>161</v>
       </c>
-      <c r="F13" s="105" t="s">
+      <c r="F13" s="95" t="s">
         <v>165</v>
       </c>
-      <c r="G13" s="114" t="s">
+      <c r="G13" s="104" t="s">
         <v>171</v>
       </c>
-      <c r="H13" s="105" t="s">
+      <c r="H13" s="95" t="s">
         <v>191</v>
       </c>
-      <c r="I13" s="105" t="s">
+      <c r="I13" s="95" t="s">
         <v>201</v>
       </c>
-      <c r="J13" s="93"/>
-      <c r="K13" s="105" t="s">
+      <c r="J13" s="83"/>
+      <c r="K13" s="95" t="s">
         <v>211</v>
       </c>
-      <c r="L13" s="105" t="s">
+      <c r="L13" s="95" t="s">
         <v>215</v>
       </c>
-      <c r="M13" s="105"/>
-      <c r="N13" s="93"/>
+      <c r="M13" s="95"/>
+      <c r="N13" s="83"/>
     </row>
     <row r="14" spans="1:14" ht="175.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="85" t="s">
+      <c r="B14" s="75" t="s">
         <v>181</v>
       </c>
-      <c r="C14" s="117" t="s">
+      <c r="C14" s="107" t="s">
         <v>179</v>
       </c>
-      <c r="D14" s="117" t="s">
+      <c r="D14" s="107" t="s">
         <v>180</v>
       </c>
-      <c r="E14" s="100"/>
-      <c r="F14" s="105"/>
-      <c r="G14" s="114"/>
-      <c r="H14" s="105" t="s">
+      <c r="E14" s="90"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="104"/>
+      <c r="H14" s="95" t="s">
         <v>197</v>
       </c>
-      <c r="I14" s="105" t="s">
+      <c r="I14" s="95" t="s">
         <v>204</v>
       </c>
-      <c r="J14" s="93"/>
-      <c r="K14" s="105" t="s">
+      <c r="J14" s="83"/>
+      <c r="K14" s="95" t="s">
         <v>208</v>
       </c>
-      <c r="L14" s="105" t="s">
+      <c r="L14" s="95" t="s">
         <v>214</v>
       </c>
-      <c r="M14" s="105"/>
-      <c r="N14" s="93"/>
+      <c r="M14" s="95"/>
+      <c r="N14" s="83"/>
     </row>
     <row r="15" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="85" t="s">
+      <c r="B15" s="75" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="117" t="s">
+      <c r="C15" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D15" s="117" t="s">
+      <c r="D15" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E15" s="100" t="s">
+      <c r="E15" s="90" t="s">
         <v>162</v>
       </c>
-      <c r="F15" s="105" t="s">
+      <c r="F15" s="95" t="s">
         <v>172</v>
       </c>
-      <c r="G15" s="114" t="s">
+      <c r="G15" s="104" t="s">
         <v>171</v>
       </c>
-      <c r="H15" s="105" t="s">
+      <c r="H15" s="95" t="s">
         <v>190</v>
       </c>
-      <c r="I15" s="105" t="s">
+      <c r="I15" s="95" t="s">
         <v>174</v>
       </c>
-      <c r="J15" s="93"/>
-      <c r="K15" s="105" t="s">
+      <c r="J15" s="83"/>
+      <c r="K15" s="95" t="s">
         <v>174</v>
       </c>
-      <c r="L15" s="105"/>
-      <c r="M15" s="105"/>
-      <c r="N15" s="93"/>
+      <c r="L15" s="95"/>
+      <c r="M15" s="95"/>
+      <c r="N15" s="83"/>
     </row>
     <row r="16" spans="1:14" ht="121.5" x14ac:dyDescent="0.3">
-      <c r="B16" s="84" t="s">
+      <c r="B16" s="74" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="117" t="s">
+      <c r="C16" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D16" s="117" t="s">
+      <c r="D16" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E16" s="91" t="s">
+      <c r="E16" s="81" t="s">
         <v>163</v>
       </c>
-      <c r="F16" s="105" t="s">
+      <c r="F16" s="95" t="s">
         <v>173</v>
       </c>
-      <c r="G16" s="114" t="s">
+      <c r="G16" s="104" t="s">
         <v>171</v>
       </c>
-      <c r="H16" s="105" t="s">
+      <c r="H16" s="95" t="s">
         <v>195</v>
       </c>
-      <c r="I16" s="105" t="s">
+      <c r="I16" s="95" t="s">
         <v>203</v>
       </c>
-      <c r="J16" s="93"/>
-      <c r="K16" s="105" t="s">
+      <c r="J16" s="83"/>
+      <c r="K16" s="95" t="s">
         <v>210</v>
       </c>
-      <c r="L16" s="105"/>
-      <c r="M16" s="105"/>
-      <c r="N16" s="93"/>
+      <c r="L16" s="95"/>
+      <c r="M16" s="95"/>
+      <c r="N16" s="83"/>
     </row>
     <row r="17" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="86" t="s">
+      <c r="B17" s="76" t="s">
         <v>141</v>
       </c>
-      <c r="C17" s="117" t="s">
+      <c r="C17" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D17" s="117" t="s">
+      <c r="D17" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E17" s="91" t="s">
+      <c r="E17" s="81" t="s">
         <v>138</v>
       </c>
-      <c r="F17" s="89"/>
-      <c r="G17" s="114" t="s">
+      <c r="F17" s="79"/>
+      <c r="G17" s="104" t="s">
         <v>171</v>
       </c>
-      <c r="H17" s="89" t="s">
+      <c r="H17" s="79" t="s">
         <v>196</v>
       </c>
-      <c r="I17" s="89" t="s">
+      <c r="I17" s="79" t="s">
         <v>196</v>
       </c>
-      <c r="J17" s="93"/>
-      <c r="K17" s="89" t="s">
+      <c r="J17" s="83"/>
+      <c r="K17" s="79" t="s">
         <v>105</v>
       </c>
-      <c r="L17" s="89" t="s">
+      <c r="L17" s="79" t="s">
         <v>105</v>
       </c>
-      <c r="M17" s="89"/>
-      <c r="N17" s="93"/>
+      <c r="M17" s="79"/>
+      <c r="N17" s="83"/>
     </row>
     <row r="18" spans="2:14" ht="162" x14ac:dyDescent="0.3">
-      <c r="B18" s="86" t="s">
+      <c r="B18" s="76" t="s">
         <v>106</v>
       </c>
-      <c r="C18" s="117" t="s">
+      <c r="C18" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D18" s="117" t="s">
+      <c r="D18" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E18" s="100" t="s">
+      <c r="E18" s="90" t="s">
         <v>164</v>
       </c>
-      <c r="F18" s="105" t="s">
+      <c r="F18" s="95" t="s">
         <v>147</v>
       </c>
-      <c r="G18" s="114" t="s">
+      <c r="G18" s="104" t="s">
         <v>171</v>
       </c>
-      <c r="H18" s="105" t="s">
+      <c r="H18" s="95" t="s">
         <v>189</v>
       </c>
-      <c r="I18" s="105" t="s">
+      <c r="I18" s="95" t="s">
         <v>202</v>
       </c>
-      <c r="J18" s="93"/>
-      <c r="K18" s="105" t="s">
+      <c r="J18" s="83"/>
+      <c r="K18" s="95" t="s">
         <v>209</v>
       </c>
-      <c r="L18" s="105" t="s">
+      <c r="L18" s="95" t="s">
         <v>209</v>
       </c>
-      <c r="M18" s="105"/>
-      <c r="N18" s="93"/>
+      <c r="M18" s="95"/>
+      <c r="N18" s="83"/>
     </row>
     <row r="19" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="85" t="s">
+      <c r="B19" s="75" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="117" t="s">
+      <c r="C19" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D19" s="117" t="s">
+      <c r="D19" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E19" s="91" t="s">
+      <c r="E19" s="81" t="s">
         <v>139</v>
       </c>
-      <c r="F19" s="104" t="s">
+      <c r="F19" s="94" t="s">
         <v>150</v>
       </c>
-      <c r="G19" s="114" t="s">
+      <c r="G19" s="104" t="s">
         <v>171</v>
       </c>
-      <c r="H19" s="105" t="s">
+      <c r="H19" s="95" t="s">
         <v>188</v>
       </c>
-      <c r="I19" s="105" t="s">
+      <c r="I19" s="95" t="s">
         <v>174</v>
       </c>
-      <c r="J19" s="93"/>
-      <c r="K19" s="105" t="s">
+      <c r="J19" s="83"/>
+      <c r="K19" s="95" t="s">
         <v>174</v>
       </c>
-      <c r="L19" s="105" t="s">
+      <c r="L19" s="95" t="s">
         <v>174</v>
       </c>
-      <c r="M19" s="105"/>
-      <c r="N19" s="93"/>
+      <c r="M19" s="95"/>
+      <c r="N19" s="83"/>
     </row>
     <row r="20" spans="2:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="85" t="s">
+      <c r="B20" s="75" t="s">
         <v>168</v>
       </c>
-      <c r="C20" s="117" t="s">
+      <c r="C20" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D20" s="117" t="s">
+      <c r="D20" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="113" t="s">
+      <c r="E20" s="103" t="s">
         <v>169</v>
       </c>
-      <c r="F20" s="110" t="s">
+      <c r="F20" s="100" t="s">
         <v>170</v>
       </c>
-      <c r="G20" s="114" t="s">
+      <c r="G20" s="104" t="s">
         <v>171</v>
       </c>
-      <c r="H20" s="119" t="s">
+      <c r="H20" s="109" t="s">
         <v>187</v>
       </c>
-      <c r="I20" s="105" t="s">
+      <c r="I20" s="95" t="s">
         <v>174</v>
       </c>
-      <c r="J20" s="112"/>
-      <c r="K20" s="105" t="s">
+      <c r="J20" s="102"/>
+      <c r="K20" s="95" t="s">
         <v>174</v>
       </c>
-      <c r="L20" s="105" t="s">
+      <c r="L20" s="95" t="s">
         <v>174</v>
       </c>
-      <c r="M20" s="105"/>
-      <c r="N20" s="112"/>
+      <c r="M20" s="95"/>
+      <c r="N20" s="102"/>
     </row>
     <row r="21" spans="2:14" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="87" t="s">
+      <c r="B21" s="77" t="s">
         <v>108</v>
       </c>
-      <c r="C21" s="118" t="s">
+      <c r="C21" s="108" t="s">
         <v>175</v>
       </c>
-      <c r="D21" s="118" t="s">
+      <c r="D21" s="108" t="s">
         <v>178</v>
       </c>
-      <c r="E21" s="103" t="s">
+      <c r="E21" s="93" t="s">
         <v>140</v>
       </c>
-      <c r="F21" s="106" t="s">
+      <c r="F21" s="96" t="s">
         <v>151</v>
       </c>
-      <c r="G21" s="115" t="s">
+      <c r="G21" s="105" t="s">
         <v>171</v>
       </c>
-      <c r="H21" s="120" t="s">
+      <c r="H21" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="I21" s="120" t="s">
+      <c r="I21" s="110" t="s">
         <v>174</v>
       </c>
-      <c r="J21" s="95"/>
-      <c r="K21" s="120" t="s">
+      <c r="J21" s="85"/>
+      <c r="K21" s="110" t="s">
         <v>174</v>
       </c>
-      <c r="L21" s="120" t="s">
+      <c r="L21" s="110" t="s">
         <v>174</v>
       </c>
-      <c r="M21" s="120"/>
-      <c r="N21" s="95"/>
+      <c r="M21" s="110"/>
+      <c r="N21" s="85"/>
     </row>
     <row r="22" spans="2:14" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -15209,391 +15218,391 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
-    <col min="2" max="2" width="9" style="81"/>
-    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
-    <col min="5" max="5" width="43" style="81" customWidth="1"/>
-    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
-    <col min="7" max="9" width="62.125" style="81" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="81"/>
+    <col min="1" max="1" width="3.375" style="71" customWidth="1"/>
+    <col min="2" max="2" width="9" style="71"/>
+    <col min="3" max="4" width="14.75" style="71" customWidth="1"/>
+    <col min="5" max="5" width="43" style="71" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="71" customWidth="1"/>
+    <col min="7" max="9" width="62.125" style="71" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="71"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="109" t="s">
+      <c r="B1" s="99" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="107"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="97"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="195" t="s">
+      <c r="B2" s="183" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="199" t="s">
+      <c r="C2" s="187" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="199" t="s">
+      <c r="D2" s="187" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="197" t="s">
+      <c r="E2" s="185" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="193" t="s">
+      <c r="F2" s="181" t="s">
         <v>182</v>
       </c>
-      <c r="G2" s="193"/>
-      <c r="H2" s="193"/>
-      <c r="I2" s="194"/>
+      <c r="G2" s="181"/>
+      <c r="H2" s="181"/>
+      <c r="I2" s="182"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="196"/>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="97" t="s">
+      <c r="B3" s="184"/>
+      <c r="C3" s="188"/>
+      <c r="D3" s="188"/>
+      <c r="E3" s="186"/>
+      <c r="F3" s="87" t="s">
         <v>114</v>
       </c>
-      <c r="G3" s="97" t="s">
+      <c r="G3" s="87" t="s">
         <v>115</v>
       </c>
-      <c r="H3" s="97" t="s">
+      <c r="H3" s="87" t="s">
         <v>116</v>
       </c>
-      <c r="I3" s="98" t="s">
+      <c r="I3" s="88" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="72" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="106" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="116" t="s">
+      <c r="D4" s="106" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="90" t="s">
+      <c r="E4" s="80" t="s">
         <v>152</v>
       </c>
-      <c r="F4" s="114"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="92"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="95"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="82"/>
     </row>
     <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="83" t="s">
+      <c r="B5" s="73" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="117" t="s">
+      <c r="C5" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="117" t="s">
+      <c r="D5" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="91" t="s">
+      <c r="E5" s="81" t="s">
         <v>153</v>
       </c>
-      <c r="F5" s="114"/>
-      <c r="G5" s="105"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="93"/>
+      <c r="F5" s="104"/>
+      <c r="G5" s="95"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="83"/>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="73" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="117" t="s">
+      <c r="C6" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D6" s="117" t="s">
+      <c r="D6" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E6" s="91" t="s">
+      <c r="E6" s="81" t="s">
         <v>154</v>
       </c>
-      <c r="F6" s="114"/>
-      <c r="G6" s="105"/>
-      <c r="H6" s="89"/>
-      <c r="I6" s="93"/>
+      <c r="F6" s="104"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="83"/>
     </row>
     <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="73" t="s">
         <v>125</v>
       </c>
-      <c r="C7" s="117" t="s">
+      <c r="C7" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D7" s="117" t="s">
+      <c r="D7" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="91" t="s">
+      <c r="E7" s="81" t="s">
         <v>155</v>
       </c>
-      <c r="F7" s="114"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="89"/>
-      <c r="I7" s="93"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="95"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="83"/>
     </row>
     <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="84" t="s">
+      <c r="B8" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="117" t="s">
+      <c r="C8" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D8" s="117" t="s">
+      <c r="D8" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E8" s="91" t="s">
+      <c r="E8" s="81" t="s">
         <v>156</v>
       </c>
-      <c r="F8" s="114"/>
-      <c r="G8" s="105"/>
-      <c r="H8" s="89"/>
-      <c r="I8" s="93"/>
+      <c r="F8" s="104"/>
+      <c r="G8" s="95"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="83"/>
     </row>
     <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.3">
-      <c r="B9" s="84" t="s">
+      <c r="B9" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="117" t="s">
+      <c r="C9" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D9" s="117" t="s">
+      <c r="D9" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E9" s="100" t="s">
+      <c r="E9" s="90" t="s">
         <v>157</v>
       </c>
-      <c r="F9" s="114"/>
-      <c r="G9" s="105"/>
-      <c r="H9" s="89"/>
-      <c r="I9" s="93"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="95"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="83"/>
     </row>
     <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="84" t="s">
+      <c r="B10" s="74" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="117" t="s">
+      <c r="C10" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D10" s="117" t="s">
+      <c r="D10" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E10" s="100" t="s">
+      <c r="E10" s="90" t="s">
         <v>158</v>
       </c>
-      <c r="F10" s="114"/>
-      <c r="G10" s="105"/>
-      <c r="H10" s="89"/>
-      <c r="I10" s="93"/>
+      <c r="F10" s="104"/>
+      <c r="G10" s="95"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="83"/>
     </row>
     <row r="11" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="B11" s="83" t="s">
+      <c r="B11" s="73" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="117" t="s">
+      <c r="C11" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D11" s="117" t="s">
+      <c r="D11" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E11" s="100" t="s">
+      <c r="E11" s="90" t="s">
         <v>159</v>
       </c>
-      <c r="F11" s="114"/>
-      <c r="G11" s="105"/>
-      <c r="H11" s="89"/>
-      <c r="I11" s="93"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="95"/>
+      <c r="H11" s="79"/>
+      <c r="I11" s="83"/>
     </row>
     <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="84" t="s">
+      <c r="B12" s="74" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="117" t="s">
+      <c r="C12" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D12" s="117" t="s">
+      <c r="D12" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E12" s="100" t="s">
+      <c r="E12" s="90" t="s">
         <v>160</v>
       </c>
-      <c r="F12" s="114"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="89"/>
-      <c r="I12" s="93"/>
+      <c r="F12" s="104"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="79"/>
+      <c r="I12" s="83"/>
     </row>
     <row r="13" spans="1:9" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="84" t="s">
+      <c r="B13" s="74" t="s">
         <v>118</v>
       </c>
-      <c r="C13" s="117" t="s">
+      <c r="C13" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D13" s="117" t="s">
+      <c r="D13" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="100" t="s">
+      <c r="E13" s="90" t="s">
         <v>161</v>
       </c>
-      <c r="F13" s="114"/>
-      <c r="G13" s="105"/>
-      <c r="H13" s="89"/>
-      <c r="I13" s="93"/>
+      <c r="F13" s="104"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="79"/>
+      <c r="I13" s="83"/>
     </row>
     <row r="14" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="85" t="s">
+      <c r="B14" s="75" t="s">
         <v>181</v>
       </c>
-      <c r="C14" s="117" t="s">
+      <c r="C14" s="107" t="s">
         <v>179</v>
       </c>
-      <c r="D14" s="117" t="s">
+      <c r="D14" s="107" t="s">
         <v>180</v>
       </c>
-      <c r="E14" s="100"/>
-      <c r="F14" s="114"/>
-      <c r="G14" s="105"/>
-      <c r="H14" s="89"/>
-      <c r="I14" s="122" t="s">
+      <c r="E14" s="90"/>
+      <c r="F14" s="104"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="79"/>
+      <c r="I14" s="111" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="85" t="s">
+      <c r="B15" s="75" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="117" t="s">
+      <c r="C15" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D15" s="117" t="s">
+      <c r="D15" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E15" s="100" t="s">
+      <c r="E15" s="90" t="s">
         <v>162</v>
       </c>
-      <c r="F15" s="114"/>
-      <c r="G15" s="105"/>
-      <c r="H15" s="89"/>
-      <c r="I15" s="93"/>
+      <c r="F15" s="104"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="79"/>
+      <c r="I15" s="83"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="84" t="s">
+      <c r="B16" s="74" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="117" t="s">
+      <c r="C16" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D16" s="117" t="s">
+      <c r="D16" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E16" s="91" t="s">
+      <c r="E16" s="81" t="s">
         <v>163</v>
       </c>
-      <c r="F16" s="114"/>
-      <c r="G16" s="105"/>
-      <c r="H16" s="89"/>
-      <c r="I16" s="93"/>
+      <c r="F16" s="104"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="79"/>
+      <c r="I16" s="83"/>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="86" t="s">
+      <c r="B17" s="76" t="s">
         <v>141</v>
       </c>
-      <c r="C17" s="117" t="s">
+      <c r="C17" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D17" s="117" t="s">
+      <c r="D17" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E17" s="91" t="s">
+      <c r="E17" s="81" t="s">
         <v>105</v>
       </c>
-      <c r="F17" s="114"/>
-      <c r="G17" s="89"/>
-      <c r="H17" s="89"/>
-      <c r="I17" s="93"/>
+      <c r="F17" s="104"/>
+      <c r="G17" s="79"/>
+      <c r="H17" s="79"/>
+      <c r="I17" s="83"/>
     </row>
     <row r="18" spans="2:9" ht="27" x14ac:dyDescent="0.3">
-      <c r="B18" s="86" t="s">
+      <c r="B18" s="76" t="s">
         <v>106</v>
       </c>
-      <c r="C18" s="117" t="s">
+      <c r="C18" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D18" s="117" t="s">
+      <c r="D18" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E18" s="100" t="s">
+      <c r="E18" s="90" t="s">
         <v>164</v>
       </c>
-      <c r="F18" s="114"/>
-      <c r="G18" s="105"/>
-      <c r="H18" s="89"/>
-      <c r="I18" s="93"/>
+      <c r="F18" s="104"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="79"/>
+      <c r="I18" s="83"/>
     </row>
     <row r="19" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="85" t="s">
+      <c r="B19" s="75" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="117" t="s">
+      <c r="C19" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D19" s="117" t="s">
+      <c r="D19" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E19" s="91" t="s">
+      <c r="E19" s="81" t="s">
         <v>139</v>
       </c>
-      <c r="F19" s="114"/>
-      <c r="G19" s="104"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="93"/>
+      <c r="F19" s="104"/>
+      <c r="G19" s="94"/>
+      <c r="H19" s="79"/>
+      <c r="I19" s="83"/>
     </row>
     <row r="20" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="85" t="s">
+      <c r="B20" s="75" t="s">
         <v>167</v>
       </c>
-      <c r="C20" s="117" t="s">
+      <c r="C20" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D20" s="117" t="s">
+      <c r="D20" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="113" t="s">
+      <c r="E20" s="103" t="s">
         <v>169</v>
       </c>
-      <c r="F20" s="114"/>
-      <c r="G20" s="110"/>
-      <c r="H20" s="111"/>
-      <c r="I20" s="112"/>
+      <c r="F20" s="104"/>
+      <c r="G20" s="100"/>
+      <c r="H20" s="101"/>
+      <c r="I20" s="102"/>
     </row>
     <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="87" t="s">
+      <c r="B21" s="77" t="s">
         <v>108</v>
       </c>
-      <c r="C21" s="118" t="s">
+      <c r="C21" s="108" t="s">
         <v>175</v>
       </c>
-      <c r="D21" s="118" t="s">
+      <c r="D21" s="108" t="s">
         <v>178</v>
       </c>
-      <c r="E21" s="103" t="s">
+      <c r="E21" s="93" t="s">
         <v>140</v>
       </c>
-      <c r="F21" s="115"/>
-      <c r="G21" s="106"/>
-      <c r="H21" s="94"/>
-      <c r="I21" s="95"/>
+      <c r="F21" s="105"/>
+      <c r="G21" s="96"/>
+      <c r="H21" s="84"/>
+      <c r="I21" s="85"/>
     </row>
     <row r="22" spans="2:9" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -15610,397 +15619,397 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
-    <col min="2" max="2" width="9" style="81"/>
-    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
-    <col min="5" max="5" width="43" style="81" customWidth="1"/>
-    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
-    <col min="7" max="9" width="62.125" style="81" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="81"/>
+    <col min="1" max="1" width="3.375" style="71" customWidth="1"/>
+    <col min="2" max="2" width="9" style="71"/>
+    <col min="3" max="4" width="14.75" style="71" customWidth="1"/>
+    <col min="5" max="5" width="43" style="71" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="71" customWidth="1"/>
+    <col min="7" max="9" width="62.125" style="71" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="71"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="109" t="s">
+      <c r="B1" s="99" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="107"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="97"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="195" t="s">
+      <c r="B2" s="183" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="199" t="s">
+      <c r="C2" s="187" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="199" t="s">
+      <c r="D2" s="187" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="197" t="s">
+      <c r="E2" s="185" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="193" t="s">
+      <c r="F2" s="181" t="s">
         <v>224</v>
       </c>
-      <c r="G2" s="193"/>
-      <c r="H2" s="193"/>
-      <c r="I2" s="194"/>
+      <c r="G2" s="181"/>
+      <c r="H2" s="181"/>
+      <c r="I2" s="182"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="196"/>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="97" t="s">
+      <c r="B3" s="184"/>
+      <c r="C3" s="188"/>
+      <c r="D3" s="188"/>
+      <c r="E3" s="186"/>
+      <c r="F3" s="87" t="s">
         <v>114</v>
       </c>
-      <c r="G3" s="97" t="s">
+      <c r="G3" s="87" t="s">
         <v>115</v>
       </c>
-      <c r="H3" s="97" t="s">
+      <c r="H3" s="87" t="s">
         <v>116</v>
       </c>
-      <c r="I3" s="98" t="s">
+      <c r="I3" s="88" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="72" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="106" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="116" t="s">
+      <c r="D4" s="106" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="90" t="s">
+      <c r="E4" s="80" t="s">
         <v>152</v>
       </c>
-      <c r="F4" s="114"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="92"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="95"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="82"/>
     </row>
     <row r="5" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="83" t="s">
+      <c r="B5" s="73" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="117" t="s">
+      <c r="C5" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="117" t="s">
+      <c r="D5" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="91" t="s">
+      <c r="E5" s="81" t="s">
         <v>153</v>
       </c>
-      <c r="F5" s="114"/>
-      <c r="G5" s="105"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="93"/>
+      <c r="F5" s="104"/>
+      <c r="G5" s="95"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="83"/>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="73" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="117" t="s">
+      <c r="C6" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D6" s="117" t="s">
+      <c r="D6" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E6" s="91" t="s">
+      <c r="E6" s="81" t="s">
         <v>154</v>
       </c>
-      <c r="F6" s="114"/>
-      <c r="G6" s="105"/>
-      <c r="H6" s="89"/>
-      <c r="I6" s="93"/>
+      <c r="F6" s="104"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="83"/>
     </row>
     <row r="7" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="73" t="s">
         <v>125</v>
       </c>
-      <c r="C7" s="117" t="s">
+      <c r="C7" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D7" s="117" t="s">
+      <c r="D7" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="91" t="s">
+      <c r="E7" s="81" t="s">
         <v>155</v>
       </c>
-      <c r="F7" s="114"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="89"/>
-      <c r="I7" s="93"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="95"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="83"/>
     </row>
     <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="84" t="s">
+      <c r="B8" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="117" t="s">
+      <c r="C8" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D8" s="117" t="s">
+      <c r="D8" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E8" s="91" t="s">
+      <c r="E8" s="81" t="s">
         <v>156</v>
       </c>
-      <c r="F8" s="114"/>
-      <c r="G8" s="105"/>
-      <c r="H8" s="89"/>
-      <c r="I8" s="93"/>
+      <c r="F8" s="104"/>
+      <c r="G8" s="95"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="83"/>
     </row>
     <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.3">
-      <c r="B9" s="84" t="s">
+      <c r="B9" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="117" t="s">
+      <c r="C9" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D9" s="117" t="s">
+      <c r="D9" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E9" s="100" t="s">
+      <c r="E9" s="90" t="s">
         <v>157</v>
       </c>
-      <c r="F9" s="114"/>
-      <c r="G9" s="105"/>
-      <c r="H9" s="89"/>
-      <c r="I9" s="93"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="95"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="83"/>
     </row>
     <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="84" t="s">
+      <c r="B10" s="74" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="117" t="s">
+      <c r="C10" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D10" s="117" t="s">
+      <c r="D10" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E10" s="100" t="s">
+      <c r="E10" s="90" t="s">
         <v>158</v>
       </c>
-      <c r="F10" s="114"/>
-      <c r="G10" s="105"/>
-      <c r="H10" s="89"/>
-      <c r="I10" s="93"/>
+      <c r="F10" s="104"/>
+      <c r="G10" s="95"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="83"/>
     </row>
     <row r="11" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="B11" s="83" t="s">
+      <c r="B11" s="73" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="117" t="s">
+      <c r="C11" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D11" s="117" t="s">
+      <c r="D11" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E11" s="100" t="s">
+      <c r="E11" s="90" t="s">
         <v>159</v>
       </c>
-      <c r="F11" s="114"/>
-      <c r="G11" s="105"/>
-      <c r="H11" s="89"/>
-      <c r="I11" s="93"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="95"/>
+      <c r="H11" s="79"/>
+      <c r="I11" s="83"/>
     </row>
     <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="84" t="s">
+      <c r="B12" s="74" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="117" t="s">
+      <c r="C12" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D12" s="117" t="s">
+      <c r="D12" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E12" s="100" t="s">
+      <c r="E12" s="90" t="s">
         <v>160</v>
       </c>
-      <c r="F12" s="114"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="89"/>
-      <c r="I12" s="93"/>
+      <c r="F12" s="104"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="79"/>
+      <c r="I12" s="83"/>
     </row>
     <row r="13" spans="1:9" ht="347.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="84" t="s">
+      <c r="B13" s="74" t="s">
         <v>118</v>
       </c>
-      <c r="C13" s="117" t="s">
+      <c r="C13" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D13" s="117" t="s">
+      <c r="D13" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="100" t="s">
+      <c r="E13" s="90" t="s">
         <v>161</v>
       </c>
-      <c r="F13" s="114"/>
-      <c r="G13" s="105"/>
-      <c r="H13" s="89"/>
-      <c r="I13" s="93"/>
+      <c r="F13" s="104"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="79"/>
+      <c r="I13" s="83"/>
     </row>
     <row r="14" spans="1:9" ht="337.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="85" t="s">
+      <c r="B14" s="75" t="s">
         <v>181</v>
       </c>
-      <c r="C14" s="117" t="s">
+      <c r="C14" s="107" t="s">
         <v>179</v>
       </c>
-      <c r="D14" s="117" t="s">
+      <c r="D14" s="107" t="s">
         <v>180</v>
       </c>
-      <c r="E14" s="100"/>
-      <c r="F14" s="123" t="s">
+      <c r="E14" s="90"/>
+      <c r="F14" s="112" t="s">
         <v>226</v>
       </c>
-      <c r="G14" s="123" t="s">
+      <c r="G14" s="112" t="s">
         <v>227</v>
       </c>
-      <c r="H14" s="123" t="s">
+      <c r="H14" s="112" t="s">
         <v>228</v>
       </c>
-      <c r="I14" s="123" t="s">
+      <c r="I14" s="112" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="85" t="s">
+      <c r="B15" s="75" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="117" t="s">
+      <c r="C15" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D15" s="117" t="s">
+      <c r="D15" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E15" s="100" t="s">
+      <c r="E15" s="90" t="s">
         <v>162</v>
       </c>
-      <c r="F15" s="114"/>
-      <c r="G15" s="105"/>
-      <c r="H15" s="89"/>
-      <c r="I15" s="93"/>
+      <c r="F15" s="104"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="79"/>
+      <c r="I15" s="83"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="84" t="s">
+      <c r="B16" s="74" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="117" t="s">
+      <c r="C16" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D16" s="117" t="s">
+      <c r="D16" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E16" s="91" t="s">
+      <c r="E16" s="81" t="s">
         <v>163</v>
       </c>
-      <c r="F16" s="114"/>
-      <c r="G16" s="105"/>
-      <c r="H16" s="89"/>
-      <c r="I16" s="93"/>
+      <c r="F16" s="104"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="79"/>
+      <c r="I16" s="83"/>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="86" t="s">
+      <c r="B17" s="76" t="s">
         <v>141</v>
       </c>
-      <c r="C17" s="117" t="s">
+      <c r="C17" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D17" s="117" t="s">
+      <c r="D17" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E17" s="91" t="s">
+      <c r="E17" s="81" t="s">
         <v>105</v>
       </c>
-      <c r="F17" s="114"/>
-      <c r="G17" s="89"/>
-      <c r="H17" s="89"/>
-      <c r="I17" s="93"/>
+      <c r="F17" s="104"/>
+      <c r="G17" s="79"/>
+      <c r="H17" s="79"/>
+      <c r="I17" s="83"/>
     </row>
     <row r="18" spans="2:9" ht="27" x14ac:dyDescent="0.3">
-      <c r="B18" s="86" t="s">
+      <c r="B18" s="76" t="s">
         <v>106</v>
       </c>
-      <c r="C18" s="117" t="s">
+      <c r="C18" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D18" s="117" t="s">
+      <c r="D18" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E18" s="100" t="s">
+      <c r="E18" s="90" t="s">
         <v>164</v>
       </c>
-      <c r="F18" s="114"/>
-      <c r="G18" s="105"/>
-      <c r="H18" s="89"/>
-      <c r="I18" s="93"/>
+      <c r="F18" s="104"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="79"/>
+      <c r="I18" s="83"/>
     </row>
     <row r="19" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="85" t="s">
+      <c r="B19" s="75" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="117" t="s">
+      <c r="C19" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D19" s="117" t="s">
+      <c r="D19" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E19" s="91" t="s">
+      <c r="E19" s="81" t="s">
         <v>139</v>
       </c>
-      <c r="F19" s="114"/>
-      <c r="G19" s="104"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="93"/>
+      <c r="F19" s="104"/>
+      <c r="G19" s="94"/>
+      <c r="H19" s="79"/>
+      <c r="I19" s="83"/>
     </row>
     <row r="20" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="85" t="s">
+      <c r="B20" s="75" t="s">
         <v>167</v>
       </c>
-      <c r="C20" s="117" t="s">
+      <c r="C20" s="107" t="s">
         <v>175</v>
       </c>
-      <c r="D20" s="117" t="s">
+      <c r="D20" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="113" t="s">
+      <c r="E20" s="103" t="s">
         <v>169</v>
       </c>
-      <c r="F20" s="114"/>
-      <c r="G20" s="110"/>
-      <c r="H20" s="111"/>
-      <c r="I20" s="112"/>
+      <c r="F20" s="104"/>
+      <c r="G20" s="100"/>
+      <c r="H20" s="101"/>
+      <c r="I20" s="102"/>
     </row>
     <row r="21" spans="2:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="87" t="s">
+      <c r="B21" s="77" t="s">
         <v>108</v>
       </c>
-      <c r="C21" s="118" t="s">
+      <c r="C21" s="108" t="s">
         <v>175</v>
       </c>
-      <c r="D21" s="118" t="s">
+      <c r="D21" s="108" t="s">
         <v>178</v>
       </c>
-      <c r="E21" s="103" t="s">
+      <c r="E21" s="93" t="s">
         <v>140</v>
       </c>
-      <c r="F21" s="115"/>
-      <c r="G21" s="106"/>
-      <c r="H21" s="94"/>
-      <c r="I21" s="95"/>
+      <c r="F21" s="105"/>
+      <c r="G21" s="96"/>
+      <c r="H21" s="84"/>
+      <c r="I21" s="85"/>
     </row>
     <row r="22" spans="2:9" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -16017,415 +16026,413 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
-    <col min="2" max="2" width="9" style="81"/>
-    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
-    <col min="5" max="5" width="43" style="81" customWidth="1"/>
-    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
-    <col min="7" max="9" width="62.125" style="81" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="81"/>
+    <col min="1" max="1" width="3.375" style="71" customWidth="1"/>
+    <col min="2" max="2" width="9" style="71"/>
+    <col min="3" max="4" width="14.75" style="71" customWidth="1"/>
+    <col min="5" max="5" width="43" style="71" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="71" customWidth="1"/>
+    <col min="7" max="9" width="62.125" style="71" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="71"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="109" t="s">
+      <c r="B1" s="99" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="107"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="97"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="195" t="s">
+      <c r="B2" s="183" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="199" t="s">
+      <c r="C2" s="187" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="199" t="s">
+      <c r="D2" s="187" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="197" t="s">
+      <c r="E2" s="185" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="193" t="s">
+      <c r="F2" s="181" t="s">
         <v>256</v>
       </c>
-      <c r="G2" s="193"/>
-      <c r="H2" s="193"/>
-      <c r="I2" s="194"/>
+      <c r="G2" s="181"/>
+      <c r="H2" s="181"/>
+      <c r="I2" s="182"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="196"/>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="97" t="s">
+      <c r="B3" s="184"/>
+      <c r="C3" s="188"/>
+      <c r="D3" s="188"/>
+      <c r="E3" s="186"/>
+      <c r="F3" s="87" t="s">
         <v>277</v>
       </c>
-      <c r="G3" s="97" t="s">
+      <c r="G3" s="87" t="s">
         <v>295</v>
       </c>
-      <c r="H3" s="97" t="s">
+      <c r="H3" s="87" t="s">
         <v>294</v>
       </c>
-      <c r="I3" s="98" t="s">
+      <c r="I3" s="88" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="151" t="s">
+      <c r="B4" s="139" t="s">
         <v>108</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="106" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="116" t="s">
+      <c r="D4" s="106" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="140" t="s">
+      <c r="E4" s="128" t="s">
         <v>140</v>
       </c>
-      <c r="F4" s="141"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="92"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="130"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="82"/>
     </row>
     <row r="5" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="B5" s="154" t="s">
+      <c r="B5" s="142" t="s">
         <v>181</v>
       </c>
-      <c r="C5" s="117" t="s">
+      <c r="C5" s="107" t="s">
         <v>267</v>
       </c>
-      <c r="D5" s="117" t="s">
+      <c r="D5" s="107" t="s">
         <v>180</v>
       </c>
-      <c r="E5" s="100" t="s">
+      <c r="E5" s="90" t="s">
         <v>161</v>
       </c>
-      <c r="F5" s="114"/>
-      <c r="G5" s="105"/>
-      <c r="H5" s="123" t="s">
+      <c r="F5" s="104"/>
+      <c r="G5" s="95"/>
+      <c r="H5" s="112" t="s">
         <v>290</v>
       </c>
-      <c r="I5" s="135" t="s">
+      <c r="I5" s="124" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="152" t="s">
+      <c r="B6" s="140" t="s">
         <v>275</v>
       </c>
-      <c r="C6" s="117" t="s">
+      <c r="C6" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D6" s="117" t="s">
+      <c r="D6" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E6" s="100" t="s">
+      <c r="E6" s="90" t="s">
         <v>161</v>
       </c>
-      <c r="F6" s="123"/>
-      <c r="G6" s="123"/>
-      <c r="H6" s="133" t="s">
+      <c r="F6" s="112"/>
+      <c r="G6" s="112"/>
+      <c r="H6" s="122" t="s">
         <v>289</v>
       </c>
-      <c r="I6" s="156"/>
+      <c r="I6" s="144"/>
     </row>
     <row r="7" spans="1:9" ht="93" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="152" t="s">
+      <c r="B7" s="140" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="117" t="s">
+      <c r="C7" s="107" t="s">
         <v>269</v>
       </c>
-      <c r="D7" s="117" t="s">
+      <c r="D7" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="100" t="s">
+      <c r="E7" s="90" t="s">
         <v>280</v>
       </c>
-      <c r="F7" s="114"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="89"/>
-      <c r="I7" s="134" t="s">
+      <c r="F7" s="104"/>
+      <c r="G7" s="95"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="123" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="87.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="152" t="s">
+      <c r="B8" s="140" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="117" t="s">
+      <c r="C8" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D8" s="117" t="s">
+      <c r="D8" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E8" s="100" t="s">
+      <c r="E8" s="90" t="s">
         <v>279</v>
       </c>
-      <c r="F8" s="114"/>
-      <c r="G8" s="104"/>
-      <c r="H8" s="89"/>
-      <c r="I8" s="134" t="s">
+      <c r="F8" s="104"/>
+      <c r="G8" s="94"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="123" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="153" t="s">
+      <c r="B9" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="117" t="s">
+      <c r="C9" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D9" s="117" t="s">
+      <c r="D9" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E9" s="91" t="s">
+      <c r="E9" s="81" t="s">
         <v>152</v>
       </c>
-      <c r="F9" s="114"/>
-      <c r="G9" s="105"/>
-      <c r="H9" s="138"/>
-      <c r="I9" s="93"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="95"/>
+      <c r="I9" s="83"/>
     </row>
     <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="153" t="s">
+      <c r="B10" s="141" t="s">
         <v>123</v>
       </c>
-      <c r="C10" s="117" t="s">
+      <c r="C10" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D10" s="117" t="s">
+      <c r="D10" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E10" s="91" t="s">
+      <c r="E10" s="81" t="s">
         <v>153</v>
       </c>
-      <c r="F10" s="114"/>
-      <c r="G10" s="105"/>
-      <c r="H10" s="89"/>
-      <c r="I10" s="93"/>
+      <c r="F10" s="104"/>
+      <c r="G10" s="95"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="83"/>
     </row>
     <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="153" t="s">
+      <c r="B11" s="141" t="s">
         <v>124</v>
       </c>
-      <c r="C11" s="117" t="s">
+      <c r="C11" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D11" s="117" t="s">
+      <c r="D11" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E11" s="91" t="s">
+      <c r="E11" s="81" t="s">
         <v>154</v>
       </c>
-      <c r="F11" s="114"/>
-      <c r="G11" s="105"/>
-      <c r="H11" s="89"/>
-      <c r="I11" s="93"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="95"/>
+      <c r="H11" s="79"/>
+      <c r="I11" s="83"/>
     </row>
     <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="153" t="s">
+      <c r="B12" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="C12" s="117" t="s">
+      <c r="C12" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D12" s="117" t="s">
+      <c r="D12" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E12" s="91" t="s">
+      <c r="E12" s="81" t="s">
         <v>155</v>
       </c>
-      <c r="F12" s="114"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="138"/>
-      <c r="I12" s="93"/>
+      <c r="F12" s="104"/>
+      <c r="G12" s="95"/>
+      <c r="I12" s="83"/>
     </row>
     <row r="13" spans="1:9" ht="222" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="132" t="s">
+      <c r="B13" s="121" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="117" t="s">
+      <c r="C13" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="D13" s="117" t="s">
+      <c r="D13" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="100" t="s">
+      <c r="E13" s="90" t="s">
         <v>260</v>
       </c>
-      <c r="F13" s="114"/>
-      <c r="G13" s="105"/>
-      <c r="H13" s="133" t="s">
+      <c r="F13" s="104"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="122" t="s">
         <v>285</v>
       </c>
-      <c r="I13" s="134" t="s">
+      <c r="I13" s="123" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="131" t="s">
+      <c r="B14" s="120" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="117" t="s">
+      <c r="C14" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="D14" s="117" t="s">
+      <c r="D14" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E14" s="100" t="s">
+      <c r="E14" s="90" t="s">
         <v>261</v>
       </c>
-      <c r="F14" s="114"/>
-      <c r="G14" s="105"/>
-      <c r="H14" s="133" t="s">
+      <c r="F14" s="104"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="122" t="s">
         <v>282</v>
       </c>
-      <c r="I14" s="134" t="s">
+      <c r="I14" s="123" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="B15" s="131" t="s">
+      <c r="B15" s="120" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="117" t="s">
+      <c r="C15" s="107" t="s">
         <v>271</v>
       </c>
-      <c r="D15" s="117" t="s">
+      <c r="D15" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E15" s="100" t="s">
+      <c r="E15" s="90" t="s">
         <v>259</v>
       </c>
-      <c r="F15" s="114"/>
-      <c r="G15" s="133" t="s">
+      <c r="F15" s="104"/>
+      <c r="G15" s="122" t="s">
         <v>265</v>
       </c>
-      <c r="H15" s="137" t="s">
+      <c r="H15" s="126" t="s">
         <v>283</v>
       </c>
-      <c r="I15" s="159" t="s">
+      <c r="I15" s="147" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="228.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="131" t="s">
+      <c r="B16" s="120" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="117" t="s">
+      <c r="C16" s="107" t="s">
         <v>272</v>
       </c>
-      <c r="D16" s="117" t="s">
+      <c r="D16" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E16" s="100" t="s">
+      <c r="E16" s="90" t="s">
         <v>262</v>
       </c>
-      <c r="F16" s="114"/>
-      <c r="G16" s="105"/>
-      <c r="H16" s="133" t="s">
+      <c r="F16" s="104"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="122" t="s">
         <v>287</v>
       </c>
-      <c r="I16" s="134" t="s">
+      <c r="I16" s="123" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="130" t="s">
+      <c r="B17" s="119" t="s">
         <v>167</v>
       </c>
-      <c r="C17" s="117" t="s">
+      <c r="C17" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="D17" s="117" t="s">
+      <c r="D17" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E17" s="113" t="s">
+      <c r="E17" s="103" t="s">
         <v>266</v>
       </c>
-      <c r="F17" s="114"/>
-      <c r="G17" s="129" t="s">
+      <c r="F17" s="104"/>
+      <c r="G17" s="118" t="s">
         <v>257</v>
       </c>
-      <c r="H17" s="155" t="s">
+      <c r="H17" s="143" t="s">
         <v>308</v>
       </c>
-      <c r="I17" s="136" t="s">
+      <c r="I17" s="125" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="18" spans="2:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="131" t="s">
+      <c r="B18" s="120" t="s">
         <v>141</v>
       </c>
-      <c r="C18" s="117" t="s">
+      <c r="C18" s="107" t="s">
         <v>273</v>
       </c>
-      <c r="D18" s="117" t="s">
+      <c r="D18" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E18" s="113" t="s">
+      <c r="E18" s="103" t="s">
         <v>278</v>
       </c>
-      <c r="F18" s="114"/>
-      <c r="G18" s="129"/>
-      <c r="H18" s="133"/>
-      <c r="I18" s="136"/>
+      <c r="F18" s="104"/>
+      <c r="G18" s="118"/>
+      <c r="H18" s="122"/>
+      <c r="I18" s="125"/>
     </row>
     <row r="19" spans="2:9" ht="108" x14ac:dyDescent="0.3">
-      <c r="B19" s="150" t="s">
+      <c r="B19" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="139" t="s">
+      <c r="C19" s="127" t="s">
         <v>270</v>
       </c>
-      <c r="D19" s="139" t="s">
+      <c r="D19" s="127" t="s">
         <v>178</v>
       </c>
-      <c r="E19" s="91" t="s">
+      <c r="E19" s="81" t="s">
         <v>156</v>
       </c>
-      <c r="F19" s="114"/>
-      <c r="G19" s="133" t="s">
+      <c r="F19" s="104"/>
+      <c r="G19" s="122" t="s">
         <v>264</v>
       </c>
-      <c r="H19" s="133" t="s">
+      <c r="H19" s="122" t="s">
         <v>284</v>
       </c>
-      <c r="I19" s="134" t="s">
+      <c r="I19" s="123" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="143" t="s">
+      <c r="B20" s="131" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="144" t="s">
+      <c r="C20" s="132" t="s">
         <v>274</v>
       </c>
-      <c r="D20" s="144" t="s">
+      <c r="D20" s="132" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="145" t="s">
+      <c r="E20" s="133" t="s">
         <v>258</v>
       </c>
-      <c r="F20" s="146"/>
-      <c r="G20" s="147" t="s">
+      <c r="F20" s="134"/>
+      <c r="G20" s="135" t="s">
         <v>263</v>
       </c>
-      <c r="H20" s="148"/>
-      <c r="I20" s="149"/>
+      <c r="H20" s="136"/>
+      <c r="I20" s="137"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -16442,429 +16449,427 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
-    <col min="2" max="2" width="9" style="81"/>
-    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
-    <col min="5" max="5" width="43" style="81" customWidth="1"/>
-    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
-    <col min="7" max="9" width="62.125" style="81" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="81"/>
+    <col min="1" max="1" width="3.375" style="71" customWidth="1"/>
+    <col min="2" max="2" width="9" style="71"/>
+    <col min="3" max="4" width="14.75" style="71" customWidth="1"/>
+    <col min="5" max="5" width="43" style="71" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="71" customWidth="1"/>
+    <col min="7" max="9" width="62.125" style="71" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="71"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="109" t="s">
+      <c r="B1" s="99" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="107"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="97"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="195" t="s">
+      <c r="B2" s="183" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="199" t="s">
+      <c r="C2" s="187" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="199" t="s">
+      <c r="D2" s="187" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="197" t="s">
+      <c r="E2" s="185" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="193" t="s">
+      <c r="F2" s="181" t="s">
         <v>276</v>
       </c>
-      <c r="G2" s="193"/>
-      <c r="H2" s="193"/>
-      <c r="I2" s="194"/>
+      <c r="G2" s="181"/>
+      <c r="H2" s="181"/>
+      <c r="I2" s="182"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="196"/>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="97" t="s">
+      <c r="B3" s="184"/>
+      <c r="C3" s="188"/>
+      <c r="D3" s="188"/>
+      <c r="E3" s="186"/>
+      <c r="F3" s="87" t="s">
         <v>296</v>
       </c>
-      <c r="G3" s="97" t="s">
+      <c r="G3" s="87" t="s">
         <v>297</v>
       </c>
-      <c r="H3" s="97" t="s">
+      <c r="H3" s="87" t="s">
         <v>298</v>
       </c>
-      <c r="I3" s="98" t="s">
+      <c r="I3" s="88" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="151" t="s">
+      <c r="B4" s="139" t="s">
         <v>108</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="106" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="116" t="s">
+      <c r="D4" s="106" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="140" t="s">
+      <c r="E4" s="128" t="s">
         <v>140</v>
       </c>
-      <c r="F4" s="141"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="92"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="130"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="82"/>
     </row>
     <row r="5" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="B5" s="154" t="s">
+      <c r="B5" s="142" t="s">
         <v>181</v>
       </c>
-      <c r="C5" s="117" t="s">
+      <c r="C5" s="107" t="s">
         <v>267</v>
       </c>
-      <c r="D5" s="117" t="s">
+      <c r="D5" s="107" t="s">
         <v>180</v>
       </c>
-      <c r="E5" s="100" t="s">
+      <c r="E5" s="90" t="s">
         <v>161</v>
       </c>
-      <c r="F5" s="123" t="s">
+      <c r="F5" s="112" t="s">
         <v>300</v>
       </c>
-      <c r="G5" s="157"/>
-      <c r="H5" s="123"/>
-      <c r="I5" s="135" t="s">
+      <c r="G5" s="145"/>
+      <c r="H5" s="112"/>
+      <c r="I5" s="124" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="152" t="s">
+      <c r="B6" s="140" t="s">
         <v>275</v>
       </c>
-      <c r="C6" s="117" t="s">
+      <c r="C6" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D6" s="117" t="s">
+      <c r="D6" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E6" s="100" t="s">
+      <c r="E6" s="90" t="s">
         <v>161</v>
       </c>
-      <c r="F6" s="123"/>
-      <c r="G6" s="123"/>
-      <c r="H6" s="123"/>
-      <c r="I6" s="135"/>
+      <c r="F6" s="112"/>
+      <c r="G6" s="112"/>
+      <c r="H6" s="112"/>
+      <c r="I6" s="124"/>
     </row>
     <row r="7" spans="1:9" ht="138" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="152" t="s">
+      <c r="B7" s="140" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="117" t="s">
+      <c r="C7" s="107" t="s">
         <v>269</v>
       </c>
-      <c r="D7" s="117" t="s">
+      <c r="D7" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="100" t="s">
+      <c r="E7" s="90" t="s">
         <v>162</v>
       </c>
-      <c r="F7" s="123" t="s">
+      <c r="F7" s="112" t="s">
         <v>307</v>
       </c>
-      <c r="G7" s="105" t="s">
+      <c r="G7" s="95" t="s">
         <v>332</v>
       </c>
-      <c r="H7" s="89"/>
-      <c r="I7" s="93"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="83"/>
     </row>
     <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="152" t="s">
+      <c r="B8" s="140" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="117" t="s">
+      <c r="C8" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D8" s="117" t="s">
+      <c r="D8" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E8" s="91" t="s">
+      <c r="E8" s="81" t="s">
         <v>139</v>
       </c>
-      <c r="F8" s="114"/>
-      <c r="G8" s="104"/>
-      <c r="H8" s="89"/>
-      <c r="I8" s="93"/>
+      <c r="F8" s="104"/>
+      <c r="G8" s="94"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="83"/>
     </row>
     <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="153" t="s">
+      <c r="B9" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="117" t="s">
+      <c r="C9" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D9" s="117" t="s">
+      <c r="D9" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E9" s="91" t="s">
+      <c r="E9" s="81" t="s">
         <v>152</v>
       </c>
-      <c r="F9" s="114"/>
-      <c r="G9" s="105"/>
-      <c r="H9" s="138"/>
-      <c r="I9" s="93"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="95"/>
+      <c r="I9" s="83"/>
     </row>
     <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="153" t="s">
+      <c r="B10" s="141" t="s">
         <v>123</v>
       </c>
-      <c r="C10" s="117" t="s">
+      <c r="C10" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D10" s="117" t="s">
+      <c r="D10" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E10" s="91" t="s">
+      <c r="E10" s="81" t="s">
         <v>153</v>
       </c>
-      <c r="F10" s="114"/>
-      <c r="G10" s="105"/>
-      <c r="H10" s="89"/>
-      <c r="I10" s="93"/>
+      <c r="F10" s="104"/>
+      <c r="G10" s="95"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="83"/>
     </row>
     <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="153" t="s">
+      <c r="B11" s="141" t="s">
         <v>124</v>
       </c>
-      <c r="C11" s="117" t="s">
+      <c r="C11" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D11" s="117" t="s">
+      <c r="D11" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E11" s="91" t="s">
+      <c r="E11" s="81" t="s">
         <v>154</v>
       </c>
-      <c r="F11" s="114"/>
-      <c r="G11" s="105"/>
-      <c r="H11" s="89"/>
-      <c r="I11" s="93"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="95"/>
+      <c r="H11" s="79"/>
+      <c r="I11" s="83"/>
     </row>
     <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="153" t="s">
+      <c r="B12" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="C12" s="117" t="s">
+      <c r="C12" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D12" s="117" t="s">
+      <c r="D12" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E12" s="91" t="s">
+      <c r="E12" s="81" t="s">
         <v>155</v>
       </c>
-      <c r="F12" s="114"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="138"/>
-      <c r="I12" s="93"/>
+      <c r="F12" s="104"/>
+      <c r="G12" s="95"/>
+      <c r="I12" s="83"/>
     </row>
     <row r="13" spans="1:9" ht="283.5" x14ac:dyDescent="0.3">
-      <c r="B13" s="132" t="s">
+      <c r="B13" s="121" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="117" t="s">
+      <c r="C13" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="D13" s="117" t="s">
+      <c r="D13" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="100" t="s">
+      <c r="E13" s="90" t="s">
         <v>260</v>
       </c>
-      <c r="F13" s="133" t="s">
+      <c r="F13" s="122" t="s">
         <v>314</v>
       </c>
-      <c r="G13" s="157" t="s">
+      <c r="G13" s="145" t="s">
         <v>333</v>
       </c>
-      <c r="H13" s="105" t="s">
+      <c r="H13" s="95" t="s">
         <v>338</v>
       </c>
-      <c r="I13" s="122" t="s">
+      <c r="I13" s="111" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="131" t="s">
+      <c r="B14" s="120" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="117" t="s">
+      <c r="C14" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="D14" s="117" t="s">
+      <c r="D14" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E14" s="100" t="s">
+      <c r="E14" s="90" t="s">
         <v>261</v>
       </c>
-      <c r="F14" s="133" t="s">
+      <c r="F14" s="122" t="s">
         <v>306</v>
       </c>
-      <c r="G14" s="157" t="s">
+      <c r="G14" s="145" t="s">
         <v>334</v>
       </c>
-      <c r="H14" s="105" t="s">
+      <c r="H14" s="95" t="s">
         <v>354</v>
       </c>
-      <c r="I14" s="122" t="s">
+      <c r="I14" s="111" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="175.5" x14ac:dyDescent="0.3">
-      <c r="B15" s="131" t="s">
+      <c r="B15" s="120" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="117" t="s">
+      <c r="C15" s="107" t="s">
         <v>271</v>
       </c>
-      <c r="D15" s="117" t="s">
+      <c r="D15" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E15" s="100" t="s">
+      <c r="E15" s="90" t="s">
         <v>259</v>
       </c>
-      <c r="F15" s="133" t="s">
+      <c r="F15" s="122" t="s">
         <v>315</v>
       </c>
-      <c r="G15" s="133" t="s">
+      <c r="G15" s="122" t="s">
         <v>315</v>
       </c>
-      <c r="H15" s="163" t="s">
+      <c r="H15" s="151" t="s">
         <v>344</v>
       </c>
-      <c r="I15" s="122" t="s">
+      <c r="I15" s="111" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
-      <c r="B16" s="131" t="s">
+      <c r="B16" s="120" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="117" t="s">
+      <c r="C16" s="107" t="s">
         <v>272</v>
       </c>
-      <c r="D16" s="117" t="s">
+      <c r="D16" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E16" s="100" t="s">
+      <c r="E16" s="90" t="s">
         <v>262</v>
       </c>
-      <c r="F16" s="133" t="s">
+      <c r="F16" s="122" t="s">
         <v>316</v>
       </c>
-      <c r="G16" s="157" t="s">
+      <c r="G16" s="145" t="s">
         <v>335</v>
       </c>
-      <c r="H16" s="157" t="s">
+      <c r="H16" s="145" t="s">
         <v>339</v>
       </c>
-      <c r="I16" s="122" t="s">
+      <c r="I16" s="111" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="162" x14ac:dyDescent="0.3">
-      <c r="B17" s="130" t="s">
+      <c r="B17" s="119" t="s">
         <v>167</v>
       </c>
-      <c r="C17" s="117" t="s">
+      <c r="C17" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="D17" s="117" t="s">
+      <c r="D17" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E17" s="113" t="s">
+      <c r="E17" s="103" t="s">
         <v>303</v>
       </c>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="143" t="s">
         <v>317</v>
       </c>
-      <c r="G17" s="119" t="s">
+      <c r="G17" s="109" t="s">
         <v>336</v>
       </c>
-      <c r="H17" s="163" t="s">
+      <c r="H17" s="151" t="s">
         <v>340</v>
       </c>
-      <c r="I17" s="168" t="s">
+      <c r="I17" s="156" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="131" t="s">
+      <c r="B18" s="120" t="s">
         <v>141</v>
       </c>
-      <c r="C18" s="117" t="s">
+      <c r="C18" s="107" t="s">
         <v>273</v>
       </c>
-      <c r="D18" s="117" t="s">
+      <c r="D18" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E18" s="113"/>
-      <c r="F18" s="155"/>
-      <c r="G18" s="133"/>
-      <c r="H18" s="133"/>
-      <c r="I18" s="136"/>
+      <c r="E18" s="103"/>
+      <c r="F18" s="143"/>
+      <c r="G18" s="122"/>
+      <c r="H18" s="122"/>
+      <c r="I18" s="125"/>
     </row>
     <row r="19" spans="2:9" ht="54" x14ac:dyDescent="0.3">
-      <c r="B19" s="150" t="s">
+      <c r="B19" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="139" t="s">
+      <c r="C19" s="127" t="s">
         <v>270</v>
       </c>
-      <c r="D19" s="139" t="s">
+      <c r="D19" s="127" t="s">
         <v>178</v>
       </c>
-      <c r="E19" s="91" t="s">
+      <c r="E19" s="81" t="s">
         <v>156</v>
       </c>
-      <c r="F19" s="133" t="s">
+      <c r="F19" s="122" t="s">
         <v>286</v>
       </c>
-      <c r="G19" s="158" t="s">
+      <c r="G19" s="146" t="s">
         <v>286</v>
       </c>
-      <c r="H19" s="133" t="s">
+      <c r="H19" s="122" t="s">
         <v>337</v>
       </c>
-      <c r="I19" s="134" t="s">
+      <c r="I19" s="123" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="143" t="s">
+      <c r="B20" s="131" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="144" t="s">
+      <c r="C20" s="132" t="s">
         <v>274</v>
       </c>
-      <c r="D20" s="144" t="s">
+      <c r="D20" s="132" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="145" t="s">
+      <c r="E20" s="133" t="s">
         <v>258</v>
       </c>
-      <c r="F20" s="161" t="s">
+      <c r="F20" s="149" t="s">
         <v>310</v>
       </c>
-      <c r="G20" s="147"/>
-      <c r="H20" s="148"/>
-      <c r="I20" s="149"/>
+      <c r="G20" s="135"/>
+      <c r="H20" s="136"/>
+      <c r="I20" s="137"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -16882,440 +16887,438 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:J20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
-    <col min="2" max="2" width="9" style="81"/>
-    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
-    <col min="5" max="5" width="43" style="81" customWidth="1"/>
-    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
-    <col min="7" max="10" width="62.125" style="81" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="81"/>
+    <col min="1" max="1" width="3.375" style="71" customWidth="1"/>
+    <col min="2" max="2" width="9" style="71"/>
+    <col min="3" max="4" width="14.75" style="71" customWidth="1"/>
+    <col min="5" max="5" width="43" style="71" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="71" customWidth="1"/>
+    <col min="7" max="10" width="62.125" style="71" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="71"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="109" t="s">
+      <c r="B1" s="99" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="107"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="97"/>
     </row>
     <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="195" t="s">
+      <c r="B2" s="183" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="199" t="s">
+      <c r="C2" s="187" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="199" t="s">
+      <c r="D2" s="187" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="197" t="s">
+      <c r="E2" s="185" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="193" t="s">
+      <c r="F2" s="181" t="s">
         <v>347</v>
       </c>
-      <c r="G2" s="193"/>
-      <c r="H2" s="193"/>
-      <c r="I2" s="201"/>
-      <c r="J2" s="194"/>
+      <c r="G2" s="181"/>
+      <c r="H2" s="181"/>
+      <c r="I2" s="189"/>
+      <c r="J2" s="182"/>
     </row>
     <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="196"/>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="97" t="s">
+      <c r="B3" s="184"/>
+      <c r="C3" s="188"/>
+      <c r="D3" s="188"/>
+      <c r="E3" s="186"/>
+      <c r="F3" s="87" t="s">
         <v>346</v>
       </c>
-      <c r="G3" s="97" t="s">
+      <c r="G3" s="87" t="s">
         <v>348</v>
       </c>
-      <c r="H3" s="97" t="s">
+      <c r="H3" s="87" t="s">
         <v>349</v>
       </c>
-      <c r="I3" s="170" t="s">
+      <c r="I3" s="158" t="s">
         <v>350</v>
       </c>
-      <c r="J3" s="98" t="s">
+      <c r="J3" s="88" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="151" t="s">
+      <c r="B4" s="139" t="s">
         <v>108</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="106" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="116" t="s">
+      <c r="D4" s="106" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="140" t="s">
+      <c r="E4" s="128" t="s">
         <v>140</v>
       </c>
-      <c r="F4" s="141"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="171"/>
-      <c r="J4" s="92"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="130"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="159"/>
+      <c r="J4" s="82"/>
     </row>
     <row r="5" spans="1:10" ht="54" x14ac:dyDescent="0.3">
-      <c r="B5" s="154" t="s">
+      <c r="B5" s="142" t="s">
         <v>181</v>
       </c>
-      <c r="C5" s="117" t="s">
+      <c r="C5" s="107" t="s">
         <v>267</v>
       </c>
-      <c r="D5" s="117" t="s">
+      <c r="D5" s="107" t="s">
         <v>180</v>
       </c>
-      <c r="E5" s="100" t="s">
+      <c r="E5" s="90" t="s">
         <v>161</v>
       </c>
-      <c r="F5" s="123" t="s">
+      <c r="F5" s="112" t="s">
         <v>357</v>
       </c>
-      <c r="G5" s="123" t="s">
+      <c r="G5" s="112" t="s">
         <v>357</v>
       </c>
-      <c r="H5" s="123"/>
-      <c r="I5" s="172"/>
-      <c r="J5" s="135"/>
+      <c r="H5" s="112"/>
+      <c r="I5" s="160"/>
+      <c r="J5" s="124"/>
     </row>
     <row r="6" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="152" t="s">
+      <c r="B6" s="140" t="s">
         <v>118</v>
       </c>
-      <c r="C6" s="117" t="s">
+      <c r="C6" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D6" s="117" t="s">
+      <c r="D6" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E6" s="100" t="s">
+      <c r="E6" s="90" t="s">
         <v>161</v>
       </c>
-      <c r="F6" s="123"/>
-      <c r="G6" s="123"/>
-      <c r="H6" s="123"/>
-      <c r="I6" s="172"/>
-      <c r="J6" s="135"/>
+      <c r="F6" s="112"/>
+      <c r="G6" s="112"/>
+      <c r="H6" s="112"/>
+      <c r="I6" s="160"/>
+      <c r="J6" s="124"/>
     </row>
     <row r="7" spans="1:10" ht="138" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="152" t="s">
+      <c r="B7" s="140" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="117" t="s">
+      <c r="C7" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D7" s="117" t="s">
+      <c r="D7" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="100" t="s">
+      <c r="E7" s="90" t="s">
         <v>162</v>
       </c>
-      <c r="F7" s="123"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="89"/>
-      <c r="I7" s="173"/>
-      <c r="J7" s="93"/>
+      <c r="F7" s="112"/>
+      <c r="G7" s="95"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="161"/>
+      <c r="J7" s="83"/>
     </row>
     <row r="8" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="152" t="s">
+      <c r="B8" s="140" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="117" t="s">
+      <c r="C8" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D8" s="117" t="s">
+      <c r="D8" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E8" s="91" t="s">
+      <c r="E8" s="81" t="s">
         <v>139</v>
       </c>
-      <c r="F8" s="114"/>
-      <c r="G8" s="104"/>
-      <c r="H8" s="89"/>
-      <c r="I8" s="173"/>
-      <c r="J8" s="93"/>
+      <c r="F8" s="104"/>
+      <c r="G8" s="94"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="161"/>
+      <c r="J8" s="83"/>
     </row>
     <row r="9" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="153" t="s">
+      <c r="B9" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="117" t="s">
+      <c r="C9" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D9" s="117" t="s">
+      <c r="D9" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E9" s="91" t="s">
+      <c r="E9" s="81" t="s">
         <v>152</v>
       </c>
-      <c r="F9" s="114"/>
-      <c r="G9" s="105"/>
-      <c r="H9" s="138"/>
-      <c r="I9" s="89"/>
-      <c r="J9" s="93"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="95"/>
+      <c r="I9" s="79"/>
+      <c r="J9" s="83"/>
     </row>
     <row r="10" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="153" t="s">
+      <c r="B10" s="141" t="s">
         <v>123</v>
       </c>
-      <c r="C10" s="117" t="s">
+      <c r="C10" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D10" s="117" t="s">
+      <c r="D10" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E10" s="91" t="s">
+      <c r="E10" s="81" t="s">
         <v>153</v>
       </c>
-      <c r="F10" s="114"/>
-      <c r="G10" s="105"/>
-      <c r="H10" s="89"/>
-      <c r="I10" s="173"/>
-      <c r="J10" s="93"/>
+      <c r="F10" s="104"/>
+      <c r="G10" s="95"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="161"/>
+      <c r="J10" s="83"/>
     </row>
     <row r="11" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="153" t="s">
+      <c r="B11" s="141" t="s">
         <v>124</v>
       </c>
-      <c r="C11" s="117" t="s">
+      <c r="C11" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D11" s="117" t="s">
+      <c r="D11" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E11" s="91" t="s">
+      <c r="E11" s="81" t="s">
         <v>154</v>
       </c>
-      <c r="F11" s="114"/>
-      <c r="G11" s="105"/>
-      <c r="H11" s="89"/>
-      <c r="I11" s="173"/>
-      <c r="J11" s="93"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="95"/>
+      <c r="H11" s="79"/>
+      <c r="I11" s="161"/>
+      <c r="J11" s="83"/>
     </row>
     <row r="12" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="153" t="s">
+      <c r="B12" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="C12" s="117" t="s">
+      <c r="C12" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D12" s="117" t="s">
+      <c r="D12" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E12" s="91" t="s">
+      <c r="E12" s="81" t="s">
         <v>155</v>
       </c>
-      <c r="F12" s="114"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="138"/>
-      <c r="I12" s="89"/>
-      <c r="J12" s="93"/>
+      <c r="F12" s="104"/>
+      <c r="G12" s="95"/>
+      <c r="I12" s="79"/>
+      <c r="J12" s="83"/>
     </row>
     <row r="13" spans="1:10" ht="364.5" x14ac:dyDescent="0.3">
-      <c r="B13" s="132" t="s">
+      <c r="B13" s="121" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="117" t="s">
+      <c r="C13" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="D13" s="117" t="s">
+      <c r="D13" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="100" t="s">
+      <c r="E13" s="90" t="s">
         <v>260</v>
       </c>
-      <c r="F13" s="105" t="s">
+      <c r="F13" s="95" t="s">
         <v>366</v>
       </c>
-      <c r="G13" s="157" t="s">
+      <c r="G13" s="145" t="s">
         <v>367</v>
       </c>
-      <c r="H13" s="105" t="s">
+      <c r="H13" s="95" t="s">
         <v>368</v>
       </c>
-      <c r="I13" s="105" t="s">
+      <c r="I13" s="95" t="s">
         <v>368</v>
       </c>
-      <c r="J13" s="122"/>
+      <c r="J13" s="111"/>
     </row>
     <row r="14" spans="1:10" ht="310.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="131" t="s">
+      <c r="B14" s="120" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="117" t="s">
+      <c r="C14" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="D14" s="117" t="s">
+      <c r="D14" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E14" s="100" t="s">
+      <c r="E14" s="90" t="s">
         <v>261</v>
       </c>
-      <c r="F14" s="105" t="s">
+      <c r="F14" s="95" t="s">
         <v>361</v>
       </c>
-      <c r="G14" s="157" t="s">
+      <c r="G14" s="145" t="s">
         <v>369</v>
       </c>
-      <c r="H14" s="105" t="s">
+      <c r="H14" s="95" t="s">
         <v>370</v>
       </c>
-      <c r="I14" s="105" t="s">
+      <c r="I14" s="95" t="s">
         <v>371</v>
       </c>
-      <c r="J14" s="122"/>
+      <c r="J14" s="111"/>
     </row>
     <row r="15" spans="1:10" ht="243" x14ac:dyDescent="0.3">
-      <c r="B15" s="131" t="s">
+      <c r="B15" s="120" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="117" t="s">
+      <c r="C15" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="D15" s="117" t="s">
+      <c r="D15" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E15" s="100" t="s">
+      <c r="E15" s="90" t="s">
         <v>259</v>
       </c>
-      <c r="F15" s="105" t="s">
+      <c r="F15" s="95" t="s">
         <v>355</v>
       </c>
-      <c r="G15" s="157" t="s">
+      <c r="G15" s="145" t="s">
         <v>358</v>
       </c>
-      <c r="H15" s="157" t="s">
+      <c r="H15" s="145" t="s">
         <v>358</v>
       </c>
-      <c r="I15" s="157" t="s">
+      <c r="I15" s="145" t="s">
         <v>358</v>
       </c>
-      <c r="J15" s="122"/>
+      <c r="J15" s="111"/>
     </row>
     <row r="16" spans="1:10" ht="378" x14ac:dyDescent="0.3">
-      <c r="B16" s="131" t="s">
+      <c r="B16" s="120" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="117" t="s">
+      <c r="C16" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="D16" s="117" t="s">
+      <c r="D16" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E16" s="100" t="s">
+      <c r="E16" s="90" t="s">
         <v>262</v>
       </c>
-      <c r="F16" s="105" t="s">
+      <c r="F16" s="95" t="s">
         <v>359</v>
       </c>
-      <c r="G16" s="157" t="s">
+      <c r="G16" s="145" t="s">
         <v>360</v>
       </c>
-      <c r="H16" s="157" t="s">
+      <c r="H16" s="145" t="s">
         <v>359</v>
       </c>
-      <c r="I16" s="157" t="s">
+      <c r="I16" s="145" t="s">
         <v>372</v>
       </c>
-      <c r="J16" s="122"/>
+      <c r="J16" s="111"/>
     </row>
     <row r="17" spans="2:10" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="B17" s="130" t="s">
+      <c r="B17" s="119" t="s">
         <v>167</v>
       </c>
-      <c r="C17" s="117" t="s">
+      <c r="C17" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="D17" s="117" t="s">
+      <c r="D17" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E17" s="113" t="s">
+      <c r="E17" s="103" t="s">
         <v>303</v>
       </c>
-      <c r="F17" s="119" t="s">
+      <c r="F17" s="109" t="s">
         <v>341</v>
       </c>
-      <c r="G17" s="169" t="s">
+      <c r="G17" s="157" t="s">
         <v>362</v>
       </c>
-      <c r="H17" s="169" t="s">
+      <c r="H17" s="157" t="s">
         <v>362</v>
       </c>
-      <c r="I17" s="169" t="s">
+      <c r="I17" s="157" t="s">
         <v>362</v>
       </c>
-      <c r="J17" s="168"/>
+      <c r="J17" s="156"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B18" s="131" t="s">
+      <c r="B18" s="120" t="s">
         <v>141</v>
       </c>
-      <c r="C18" s="117" t="s">
+      <c r="C18" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="D18" s="117" t="s">
+      <c r="D18" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E18" s="113"/>
-      <c r="F18" s="155"/>
-      <c r="G18" s="158"/>
-      <c r="H18" s="133"/>
-      <c r="I18" s="129"/>
-      <c r="J18" s="136"/>
+      <c r="E18" s="103"/>
+      <c r="F18" s="143"/>
+      <c r="G18" s="146"/>
+      <c r="H18" s="122"/>
+      <c r="I18" s="118"/>
+      <c r="J18" s="125"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B19" s="150" t="s">
+      <c r="B19" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="139" t="s">
+      <c r="C19" s="127" t="s">
         <v>270</v>
       </c>
-      <c r="D19" s="139" t="s">
+      <c r="D19" s="127" t="s">
         <v>178</v>
       </c>
-      <c r="E19" s="91" t="s">
+      <c r="E19" s="81" t="s">
         <v>156</v>
       </c>
-      <c r="F19" s="105" t="s">
+      <c r="F19" s="95" t="s">
         <v>363</v>
       </c>
-      <c r="G19" s="158"/>
-      <c r="H19" s="133"/>
-      <c r="I19" s="174"/>
-      <c r="J19" s="134"/>
+      <c r="G19" s="146"/>
+      <c r="H19" s="122"/>
+      <c r="I19" s="162"/>
+      <c r="J19" s="123"/>
     </row>
     <row r="20" spans="2:10" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="143" t="s">
+      <c r="B20" s="131" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="144" t="s">
+      <c r="C20" s="132" t="s">
         <v>270</v>
       </c>
-      <c r="D20" s="144" t="s">
+      <c r="D20" s="132" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="145" t="s">
+      <c r="E20" s="133" t="s">
         <v>258</v>
       </c>
-      <c r="F20" s="161" t="s">
+      <c r="F20" s="149" t="s">
         <v>263</v>
       </c>
-      <c r="G20" s="147"/>
-      <c r="H20" s="148"/>
-      <c r="I20" s="175"/>
-      <c r="J20" s="149"/>
+      <c r="G20" s="135"/>
+      <c r="H20" s="136"/>
+      <c r="I20" s="163"/>
+      <c r="J20" s="137"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -17332,465 +17335,463 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="81" customWidth="1"/>
-    <col min="2" max="2" width="10.125" style="81" customWidth="1"/>
-    <col min="3" max="4" width="14.75" style="81" customWidth="1"/>
-    <col min="5" max="5" width="43" style="81" customWidth="1"/>
-    <col min="6" max="6" width="61.875" style="81" customWidth="1"/>
-    <col min="7" max="9" width="62.125" style="81" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="81"/>
+    <col min="1" max="1" width="3.375" style="71" customWidth="1"/>
+    <col min="2" max="2" width="10.125" style="71" customWidth="1"/>
+    <col min="3" max="4" width="14.75" style="71" customWidth="1"/>
+    <col min="5" max="5" width="43" style="71" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="71" customWidth="1"/>
+    <col min="7" max="9" width="62.125" style="71" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="71"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="109" t="s">
+      <c r="B1" s="99" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="107"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="97"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="195" t="s">
+      <c r="B2" s="183" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="199" t="s">
+      <c r="C2" s="187" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="199" t="s">
+      <c r="D2" s="187" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="197" t="s">
+      <c r="E2" s="185" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="193" t="s">
+      <c r="F2" s="181" t="s">
         <v>373</v>
       </c>
-      <c r="G2" s="193"/>
-      <c r="H2" s="193"/>
-      <c r="I2" s="194"/>
+      <c r="G2" s="181"/>
+      <c r="H2" s="181"/>
+      <c r="I2" s="182"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="196"/>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="97" t="s">
+      <c r="B3" s="184"/>
+      <c r="C3" s="188"/>
+      <c r="D3" s="188"/>
+      <c r="E3" s="186"/>
+      <c r="F3" s="87" t="s">
         <v>374</v>
       </c>
-      <c r="G3" s="97" t="s">
+      <c r="G3" s="87" t="s">
         <v>375</v>
       </c>
-      <c r="H3" s="97" t="s">
+      <c r="H3" s="87" t="s">
         <v>376</v>
       </c>
-      <c r="I3" s="98" t="s">
+      <c r="I3" s="88" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="B4" s="151" t="s">
+      <c r="B4" s="139" t="s">
         <v>108</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="106" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="116" t="s">
+      <c r="D4" s="106" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="140" t="s">
-        <v>140</v>
-      </c>
-      <c r="F4" s="183" t="s">
+      <c r="E4" s="128" t="s">
+        <v>424</v>
+      </c>
+      <c r="F4" s="171" t="s">
         <v>407</v>
       </c>
-      <c r="G4" s="183" t="s">
+      <c r="G4" s="171" t="s">
         <v>406</v>
       </c>
-      <c r="H4" s="88"/>
-      <c r="I4" s="92"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="82"/>
     </row>
     <row r="5" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="B5" s="154" t="s">
+      <c r="B5" s="142" t="s">
         <v>181</v>
       </c>
-      <c r="C5" s="117" t="s">
+      <c r="C5" s="107" t="s">
         <v>267</v>
       </c>
-      <c r="D5" s="117" t="s">
+      <c r="D5" s="107" t="s">
         <v>180</v>
       </c>
-      <c r="E5" s="100" t="s">
-        <v>161</v>
-      </c>
-      <c r="F5" s="123" t="s">
+      <c r="E5" s="90" t="s">
+        <v>423</v>
+      </c>
+      <c r="F5" s="112" t="s">
         <v>403</v>
       </c>
-      <c r="G5" s="123" t="s">
+      <c r="G5" s="112" t="s">
         <v>404</v>
       </c>
-      <c r="H5" s="123" t="s">
+      <c r="H5" s="112" t="s">
         <v>408</v>
       </c>
-      <c r="I5" s="135"/>
+      <c r="I5" s="124"/>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="152" t="s">
+      <c r="B6" s="140" t="s">
         <v>118</v>
       </c>
-      <c r="C6" s="117" t="s">
+      <c r="C6" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D6" s="117" t="s">
+      <c r="D6" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E6" s="100" t="s">
-        <v>161</v>
-      </c>
-      <c r="F6" s="123" t="s">
+      <c r="E6" s="90" t="s">
+        <v>423</v>
+      </c>
+      <c r="F6" s="112" t="s">
         <v>393</v>
       </c>
-      <c r="G6" s="123" t="s">
+      <c r="G6" s="112" t="s">
         <v>394</v>
       </c>
-      <c r="H6" s="123" t="s">
+      <c r="H6" s="112" t="s">
         <v>409</v>
       </c>
-      <c r="I6" s="135"/>
+      <c r="I6" s="124"/>
     </row>
     <row r="7" spans="1:9" ht="310.5" x14ac:dyDescent="0.3">
-      <c r="B7" s="152" t="s">
+      <c r="B7" s="140" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="117" t="s">
+      <c r="C7" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D7" s="117" t="s">
+      <c r="D7" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="100" t="s">
+      <c r="E7" s="90" t="s">
         <v>405</v>
       </c>
-      <c r="F7" s="123" t="s">
+      <c r="F7" s="112" t="s">
         <v>386</v>
       </c>
-      <c r="G7" s="105" t="s">
+      <c r="G7" s="95" t="s">
         <v>390</v>
       </c>
-      <c r="H7" s="105" t="s">
+      <c r="H7" s="95" t="s">
         <v>422</v>
       </c>
-      <c r="I7" s="93"/>
+      <c r="I7" s="83"/>
     </row>
     <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="152" t="s">
+      <c r="B8" s="140" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="117" t="s">
+      <c r="C8" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D8" s="117" t="s">
+      <c r="D8" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E8" s="91" t="s">
+      <c r="E8" s="81" t="s">
         <v>139</v>
       </c>
-      <c r="F8" s="114"/>
-      <c r="G8" s="104"/>
-      <c r="H8" s="89"/>
-      <c r="I8" s="93"/>
+      <c r="F8" s="104"/>
+      <c r="G8" s="94"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="83"/>
     </row>
     <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="153" t="s">
+      <c r="B9" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="117" t="s">
+      <c r="C9" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D9" s="117" t="s">
+      <c r="D9" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E9" s="91" t="s">
+      <c r="E9" s="81" t="s">
         <v>152</v>
       </c>
-      <c r="F9" s="114" t="s">
+      <c r="F9" s="104" t="s">
         <v>400</v>
       </c>
-      <c r="G9" s="105"/>
-      <c r="H9" s="138"/>
-      <c r="I9" s="93"/>
+      <c r="G9" s="95"/>
+      <c r="I9" s="83"/>
     </row>
     <row r="10" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="153" t="s">
+      <c r="B10" s="141" t="s">
         <v>123</v>
       </c>
-      <c r="C10" s="117" t="s">
+      <c r="C10" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D10" s="117" t="s">
+      <c r="D10" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E10" s="91" t="s">
+      <c r="E10" s="81" t="s">
         <v>153</v>
       </c>
-      <c r="F10" s="114" t="s">
+      <c r="F10" s="104" t="s">
         <v>400</v>
       </c>
-      <c r="G10" s="105"/>
-      <c r="H10" s="89"/>
-      <c r="I10" s="93"/>
+      <c r="G10" s="95"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="83"/>
     </row>
     <row r="11" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="153" t="s">
+      <c r="B11" s="141" t="s">
         <v>124</v>
       </c>
-      <c r="C11" s="117" t="s">
+      <c r="C11" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D11" s="117" t="s">
+      <c r="D11" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E11" s="91" t="s">
+      <c r="E11" s="81" t="s">
         <v>154</v>
       </c>
-      <c r="F11" s="114" t="s">
+      <c r="F11" s="104" t="s">
         <v>401</v>
       </c>
-      <c r="G11" s="105"/>
-      <c r="H11" s="89"/>
-      <c r="I11" s="93"/>
+      <c r="G11" s="95"/>
+      <c r="H11" s="79"/>
+      <c r="I11" s="83"/>
     </row>
     <row r="12" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="153" t="s">
+      <c r="B12" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="C12" s="117" t="s">
+      <c r="C12" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D12" s="117" t="s">
+      <c r="D12" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E12" s="91" t="s">
+      <c r="E12" s="81" t="s">
         <v>155</v>
       </c>
-      <c r="F12" s="114" t="s">
+      <c r="F12" s="104" t="s">
         <v>402</v>
       </c>
-      <c r="G12" s="105"/>
-      <c r="H12" s="138"/>
-      <c r="I12" s="93"/>
+      <c r="G12" s="95"/>
+      <c r="I12" s="83"/>
     </row>
     <row r="13" spans="1:9" ht="94.5" x14ac:dyDescent="0.3">
-      <c r="B13" s="132" t="s">
+      <c r="B13" s="121" t="s">
         <v>395</v>
       </c>
-      <c r="C13" s="117" t="s">
+      <c r="C13" s="107" t="s">
         <v>398</v>
       </c>
-      <c r="D13" s="117" t="s">
+      <c r="D13" s="107" t="s">
         <v>399</v>
       </c>
-      <c r="E13" s="91" t="s">
+      <c r="E13" s="81" t="s">
         <v>396</v>
       </c>
-      <c r="F13" s="123" t="s">
+      <c r="F13" s="112" t="s">
         <v>397</v>
       </c>
-      <c r="G13" s="181" t="s">
+      <c r="G13" s="169" t="s">
         <v>416</v>
       </c>
-      <c r="H13" s="184" t="s">
+      <c r="H13" s="172" t="s">
         <v>417</v>
       </c>
-      <c r="I13" s="182"/>
+      <c r="I13" s="170"/>
     </row>
     <row r="14" spans="1:9" ht="243" x14ac:dyDescent="0.3">
-      <c r="B14" s="132" t="s">
+      <c r="B14" s="121" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="117" t="s">
+      <c r="C14" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="D14" s="117" t="s">
+      <c r="D14" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E14" s="100" t="s">
+      <c r="E14" s="90" t="s">
         <v>260</v>
       </c>
-      <c r="F14" s="105"/>
-      <c r="G14" s="157" t="s">
+      <c r="F14" s="95"/>
+      <c r="G14" s="145" t="s">
         <v>419</v>
       </c>
-      <c r="H14" s="105" t="s">
+      <c r="H14" s="95" t="s">
         <v>418</v>
       </c>
-      <c r="I14" s="122"/>
+      <c r="I14" s="111"/>
     </row>
     <row r="15" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
-      <c r="B15" s="131" t="s">
+      <c r="B15" s="120" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="117" t="s">
+      <c r="C15" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="D15" s="117" t="s">
+      <c r="D15" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E15" s="100" t="s">
+      <c r="E15" s="90" t="s">
         <v>261</v>
       </c>
-      <c r="F15" s="105" t="s">
+      <c r="F15" s="95" t="s">
         <v>410</v>
       </c>
-      <c r="G15" s="157" t="s">
+      <c r="G15" s="145" t="s">
         <v>421</v>
       </c>
-      <c r="H15" s="105" t="s">
+      <c r="H15" s="95" t="s">
         <v>420</v>
       </c>
-      <c r="I15" s="122"/>
+      <c r="I15" s="111"/>
     </row>
     <row r="16" spans="1:9" ht="108" x14ac:dyDescent="0.3">
-      <c r="B16" s="131" t="s">
+      <c r="B16" s="120" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="117" t="s">
+      <c r="C16" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="D16" s="117" t="s">
+      <c r="D16" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E16" s="100" t="s">
+      <c r="E16" s="90" t="s">
         <v>259</v>
       </c>
-      <c r="F16" s="105" t="s">
+      <c r="F16" s="95" t="s">
         <v>387</v>
       </c>
-      <c r="G16" s="157" t="s">
+      <c r="G16" s="145" t="s">
         <v>393</v>
       </c>
-      <c r="H16" s="157" t="s">
+      <c r="H16" s="145" t="s">
         <v>413</v>
       </c>
-      <c r="I16" s="176"/>
+      <c r="I16" s="164"/>
     </row>
     <row r="17" spans="2:9" ht="409.5" x14ac:dyDescent="0.3">
-      <c r="B17" s="131" t="s">
+      <c r="B17" s="120" t="s">
         <v>85</v>
       </c>
-      <c r="C17" s="117" t="s">
+      <c r="C17" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="D17" s="117" t="s">
+      <c r="D17" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E17" s="100" t="s">
+      <c r="E17" s="90" t="s">
         <v>262</v>
       </c>
-      <c r="F17" s="105" t="s">
+      <c r="F17" s="95" t="s">
         <v>389</v>
       </c>
-      <c r="G17" s="157" t="s">
+      <c r="G17" s="145" t="s">
         <v>414</v>
       </c>
-      <c r="H17" s="157" t="s">
+      <c r="H17" s="145" t="s">
         <v>415</v>
       </c>
-      <c r="I17" s="176"/>
+      <c r="I17" s="164"/>
     </row>
     <row r="18" spans="2:9" ht="108" x14ac:dyDescent="0.3">
-      <c r="B18" s="130" t="s">
+      <c r="B18" s="119" t="s">
         <v>167</v>
       </c>
-      <c r="C18" s="117" t="s">
+      <c r="C18" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="D18" s="117" t="s">
+      <c r="D18" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E18" s="113" t="s">
+      <c r="E18" s="103" t="s">
         <v>303</v>
       </c>
-      <c r="F18" s="119" t="s">
+      <c r="F18" s="109" t="s">
         <v>388</v>
       </c>
-      <c r="G18" s="169" t="s">
+      <c r="G18" s="157" t="s">
         <v>393</v>
       </c>
-      <c r="H18" s="169" t="s">
+      <c r="H18" s="157" t="s">
         <v>411</v>
       </c>
-      <c r="I18" s="177"/>
+      <c r="I18" s="165"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B19" s="131" t="s">
+      <c r="B19" s="120" t="s">
         <v>141</v>
       </c>
-      <c r="C19" s="117" t="s">
+      <c r="C19" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="D19" s="117" t="s">
+      <c r="D19" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="E19" s="113"/>
-      <c r="F19" s="155"/>
-      <c r="G19" s="158"/>
-      <c r="H19" s="133"/>
-      <c r="I19" s="136"/>
+      <c r="E19" s="103"/>
+      <c r="F19" s="143"/>
+      <c r="G19" s="146"/>
+      <c r="H19" s="122"/>
+      <c r="I19" s="125"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B20" s="150" t="s">
+      <c r="B20" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="139" t="s">
+      <c r="C20" s="127" t="s">
         <v>270</v>
       </c>
-      <c r="D20" s="139" t="s">
+      <c r="D20" s="127" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="91" t="s">
+      <c r="E20" s="81" t="s">
         <v>156</v>
       </c>
-      <c r="F20" s="105" t="s">
+      <c r="F20" s="95" t="s">
         <v>263</v>
       </c>
-      <c r="G20" s="157" t="s">
+      <c r="G20" s="145" t="s">
         <v>391</v>
       </c>
-      <c r="H20" s="105" t="s">
+      <c r="H20" s="95" t="s">
         <v>412</v>
       </c>
-      <c r="I20" s="134"/>
+      <c r="I20" s="123"/>
     </row>
     <row r="21" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="178" t="s">
+      <c r="B21" s="166" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="118" t="s">
+      <c r="C21" s="108" t="s">
         <v>270</v>
       </c>
-      <c r="D21" s="118" t="s">
+      <c r="D21" s="108" t="s">
         <v>178</v>
       </c>
-      <c r="E21" s="103" t="s">
+      <c r="E21" s="93" t="s">
         <v>258</v>
       </c>
-      <c r="F21" s="179" t="s">
+      <c r="F21" s="167" t="s">
         <v>263</v>
       </c>
-      <c r="G21" s="106" t="s">
+      <c r="G21" s="96" t="s">
         <v>392</v>
       </c>
-      <c r="H21" s="185" t="s">
+      <c r="H21" s="173" t="s">
         <v>409</v>
       </c>
-      <c r="I21" s="95"/>
+      <c r="I21" s="85"/>
     </row>
     <row r="22" spans="2:9" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.Task\001.Woory\001.PTC\0.PTC\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\일정\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A69427-E607-476D-8B7E-E6E425D89499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="대일정" sheetId="1" r:id="rId1"/>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="434">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -8272,11 +8271,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[임제훈 사원]
-- SWE.3 SDDS 후속 작업 (진행률 : 97%)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>- 이슈 없음</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8291,25 +8285,6 @@
     - BJ1 ES95489-21, ESIR 때 성적서 없음
       : QV 사이버 보안 협의 및 일정 지연으로 BJ1 ESIR때 진행 불가
       : BJ1 ES95489-21 검증 진행</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-1. HVAC 2EA 수령 (01/19)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 이슈 없음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[임제훈 사원]
-1. AY RHD Pilot 차량 실차 검증
-  [ 요청사항 ]
-    - AY RHD Pilot 차량 실차 검증
-  [ 진행 및 검토 ]
-    - 일정 미정
-     : 3월 ~ 4월 예상</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -8838,13 +8813,620 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">[김진겸 사원]
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>국내 윈터 트립 (01/12 ~ 01/13)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 요청사항 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>국내 윈터 트립 참석</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 진행 및 검토 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SVm P1(77호차) PTC 제어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+[임제훈 사원]
+1. ISIR 성적서 작성 (~2/12)
+  [ 요청사항 ]
+    - ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24 성적서
+  [ 진행 및 검토 ]
+    - 2월 중순까지 성적서 작성 완료
+    - ES90700-00 (100%)
+    - ES95411-00 (90%)
+    - ES95480-00 (100%)
+    - ES95489-21 (90%)
+    - ES95489-24 (90%)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">`[임제훈 사원]
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FAIL-SAFETY 로직 검증 (01/13)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 요청사항 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>타 차종에서 문제 발생, BJ1 PTC FAIL-SAFETY 검증 및 결과 요청</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  [ 진행 및 검토 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FAIL-SAFETY 로직 검증 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S/W 문제 없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>검증 결과 회신 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. ISIR 성적서 작성 (~2/12)
+  [ 요청사항 ]
+    - ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24 성적서
+  [ 진행 및 검토 ]
+    - 2월 중순까지 성적서 작성 완료
+    - ES90700-00 (100%)
+    - ES95411-00 (90%)
+    - ES95480-00 (100%)
+    - ES95489-21 (90%)
+    - ES95489-24 (90%)
+3. 사이버 보안 관련 자료 회신 요청
+  [ 요청사항 ]
+    - 사이버 보안 QV와 동일한 이력으로 진행 요청 (공조시스템설계팀)
+    - BJ1 ES95489-21 성적서 회신
+    - 사이버보안관련성평가 작성 후 회신
+  [ 진행 및 검토 ]
+    - BJ1 ES95489-21, ESIR 때 성적서 없음
+      : QV 사이버 보안 협의 및 일정 지연으로 BJ1 ESIR때 진행 불가
+      : BJ1 ES95489-21 검증 진행</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P1 기본형 (25/07/15)
+P1 항속형 (25/09/15)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Proto (26/7/初)
+P1 (27/2/初)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>[임제훈 사원]
-1. PTC 제어 방향 문의 (~1/23)
+- SWE.3 SDDS 후속 작업 (진행률 : 97%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- SWE.3 SDDS 후속 작업 (진행률 : 97%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 이슈 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 이슈 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+1. 최대 난방 평가 성능 미달로 인한 성능 증대 계획 (~1/29)
+  [ 요청사항 ]
+    - SP1 적용 S/W 튜닝
+  [ 진행 및 검토 ]
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HVAC 수령 (1/20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">)
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MX5a 샘플 수령 (1/20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">)
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S/W 성능 튜닝 완료 (1/20)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>전압 범위 최소 작동 전압 268V Recovery 288V, 최대 640V, Recovery 620V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LINEAR MAX Zone 당 4300W, Total 8600W 변경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S/W 성능 튜닝 결과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-30℃, 풍량 300kph 환경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>최대 전력 21초 소요, IGBT 100% 도달 81초 소요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>60초 IGBT 80% 도달</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      : </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>60초 ~ 81초 성능 7452W → 7480W</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - R로직 튜닝 (~1/29)
+      : TC 변경건으로 인한 R로직 재튜닝
+2. 최대 난방 평가 재진행 (~2/5)
+  [ 요청사항 ]
+    - 최대 난방 평가
+  [ 진행 및 검토 ]
+    - 2월 첫째 주 최대 난방 평가 예정
+      : S/W 성능 튜닝 완료되면 차주 진행 제안 (기구팀)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[임제훈 사원]
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PTC 제어 방향 문의 (~1/23)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
   [ 요청 사항 ]
-    - PTC Target Duty 수신 시 로직 (공조시스템설계팀 한별 책임 연구원)
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PTC Target Duty 수신 시 로직 (공조시스템설계팀 한별 책임 연구원)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
   [ 진행 및 검토 ]
-    - 급격한 Target Duty 변화 수신 (예시 80% → 40%)
-    - 급격한 Target Duty OFF 수신 (예시 80% → 0% (OFF))</t>
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>급격한 Target Duty 변화 수신 (예시 80% → 40%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    - </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>급격한 Target Duty OFF 수신 (예시 80% → 0% (OFF))</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -8862,84 +9444,29 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">[김진겸 사원]
-1. </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>국내 윈터 트립 (01/12 ~ 01/13)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  [ 요청사항 ]
-    - </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>국내 윈터 트립 참석</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t>[임제훈 사원]
+1. SVm 공조 제어기 검증 양식 작성 (~2/3)
+  [ 요청 사항 ]
+    - SVm 공조 제어기 검증양식 작성
+    - SVm 2월 정기회의시 해당 파일로 제어기 검증 리뷰 진행
   [ 진행 및 검토 ]
-    - </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SVm P1(77호차) PTC 제어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-[임제훈 사원]
-1. ISIR 성적서 작성 (~2/12)
+    - 변경점 확인 (기존차 대비 변경점 포함)
+    - 고장코드 및 진단 조건
+     : 고장코드 별 상세 내용 점검
+     : 고장진단 적합성 확인 (진입 및 판정조건)
+    - 전원변동 검증 / 제어기 문제 발생시 로그저장 유무 확인
+     : 파워 모드 천이 등
+    - 시뮬레이션 검증 결과 (★RHD 차량 포함)
+    - 완성차 시스템 평가 결과 (★RHD 차량 포함)
+     : 완성차 평가를 통한 고객 실사용 조건 검증
+     : 장시간 전원ON상태 검증 (유틸리티 모드)
+     : 환경 악조건(저/고온) 상태 시동시 전압 변동에 따른 경고등 로직 강건성 확인
+    - 제어기별 해당 법규 만족 여부 점검
+    - 사이버보안 활성화 사전 검증 (최소 5대)
+     : BJ1은 QV 평가로 대체 되었음, SVm 도 QV 대체인지 확인
+    - OTA 적합성 확인
+     : OTA 미적용
+2. ISIR 성적서 작성 (~2/12)
   [ 요청사항 ]
     - ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24 성적서
   [ 진행 및 검토 ]
@@ -8949,7 +9476,6 @@
     - ES95480-00 (100%)
     - ES95489-21 (90%)
     - ES95489-24 (90%)</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -8991,130 +9517,22 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">`[임제훈 사원]
-1. </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>FAIL-SAFETY 로직 검증 (01/13)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t>[임제훈 사원]
+1. ATCU, HVAC, PTC 합동 벤치 테스트 (~2/6)
   [ 요청사항 ]
-    - </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>타 차종에서 문제 발생, BJ1 PTC FAIL-SAFETY 검증 및 결과 요청</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
+    - ATCU, HVAC, PTC 간 신호 정합성 및 로직 정합성 검증
   [ 진행 및 검토 ]
-    - </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>FAIL-SAFETY 로직 검증 완료</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-     : </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S/W 문제 없음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-    - </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>검증 결과 회신 완료</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
+    - Fault 시뮬레이션 3개 항목
+     : Current Sensor Fault
+     : IGBT Open / Short Fault
+     : Over Current
+    - 타 항목은 벤치 테스트 진행하며 검증
+     : Sensor Fault (Open, Short 스위치 회로 준비 H/W)
+     : Low Voltage Protection
+     : High Voltage Protection
+     : Interlock
+     : CAN Timeout
+     : Core Temp Over Fault
 2. ISIR 성적서 작성 (~2/12)
   [ 요청사항 ]
     - ES90700-00, ES95411-00, ES95480-00, ES95489-21, ES95489-24 성적서
@@ -9134,50 +9552,89 @@
     - BJ1 ES95489-21, ESIR 때 성적서 없음
       : QV 사이버 보안 협의 및 일정 지연으로 BJ1 ESIR때 진행 불가
       : BJ1 ES95489-21 검증 진행</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[임제훈 사원]
-1. 최대 난방 평가 성능 미달로 인한 성능 증대 계획 (~1/29)
+1. AY RHD Pilot 차량 실차 검증
   [ 요청사항 ]
-    - SP1 적용 S/W 튜닝
+    - AY RHD Pilot 차량 실차 검증
   [ 진행 및 검토 ]
-    - HVAC 수령 (1/20)
-    - MX5a 샘플 수령 (1/20)
-    - S/W 성능 튜닝 완료 (1/20)
-      : 전압 범위 최소 작동 전압 268V Recovery 288V, 최대 640V, Recovery 620V
-      : LINEAR MAX Zone 당 4300W, Total 8600W 변경
-    - S/W 성능 튜닝 결과
-      : -30℃, 풍량 300kph 환경
-      : 최대 전력 21초 소요, IGBT 100% 도달 81초 소요
-      : 60초 IGBT 80% 도달
-      : 60초 ~ 81초 성능 7452W → 7480W
-    - R로직 튜닝 (~1/29)
-      : TC 변경건으로 인한 R로직 재튜닝
-2. 최대 난방 평가 재진행 (~2/5)
+    - 일정 미정
+     : 3월 ~ 4월 예상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. AY RHD Pilot 차량 실차 검증
+  [ 요청사항 ]
+    - AY RHD Pilot 차량 실차 검증
+  [ 진행 및 검토 ]
+    - 일정 미정
+     : 3월 ~ 4월 예상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. 실차 예상 문제점 의견 제시 (01/20)
+  [ 상황 ]
+    - FATC 테스트 결과 기반 예상 문제점 발견
+  [ 진행 및 검토 ]
+    - 공조시스템설계팀 정재근 책임 연구원에게 의견 제기
+     : 냉각수 온도가 Heater에 미치는 영향성
+    - 현 상황 인지하였고 전체 메일 발송 예정 (HKMC 공조시스템설계팀)
+    - 정재근 부재, 명일 재연락
+2. 고객사 사이버 보안 기능 품확 활동 (~01/30)
+  [ 요청사항 ]
+    - 품확 진행 샘플
+  [ 진행 및 검토 ]
+    - 사이버보안품질연구팀에 보낼 샘플 준비
+     : PCB 1EA, Signal Connector 1EA, E2 Pin Connector 1EA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. HVAC 2EA 수령 (01/19)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. R로직 튜닝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 이슈 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+1. SP1 S/W 설계변경 (~2/6)
+  [ 진행 및 검토 ]
+    - R로직 튜닝
+     : TC 변경건으로 R로직 재튜닝
+    - MVa Over Current Spec 29.5A
+     : MX5a도 그대로 29.5A 하는지, 4300 / 268 = 17A로 하는지 확인
+2. 최대 난방 평가 재진행 (~2/6)
   [ 요청사항 ]
     - 최대 난방 평가
   [ 진행 및 검토 ]
     - 2월 첫째 주 최대 난방 평가 예정
-      : S/W 성능 튜닝 완료되면 차주 진행 제안 (기구팀)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>P1 기본형 (25/07/15)
-P1 항속형 (25/09/15)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Proto (26/7/初)
-P1 (27/2/初)</t>
+     : S/W 성능 튜닝 완료되면 차주 진행 제안 (기구팀)
+3. MX5a EREV 차량 테스트 중 화재 데이터 분석
+  [ 요청사항 ]
+    - Main Relay 차단 후, PTC 상태는 Normal인 이유 확인 요청
+  [ 진행 및 검토 ]
+    - 테스트 진행 시 저장된 LOG 요청 및 분석
+     : 로그 데이터 수신 (1/26)
+     : CAN DBC 파일 미수신
+    - CAN DBC 파일 재요청</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
@@ -10645,7 +11102,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="190">
+  <cellXfs count="191">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -11215,6 +11672,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -11892,7 +12352,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BL25"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -13915,7 +14375,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -14311,7 +14771,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -14442,7 +14902,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -15218,7 +15678,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -15619,7 +16079,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16026,7 +16486,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16449,7 +16909,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16887,7 +17347,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -17335,7 +17795,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -17408,7 +17868,7 @@
         <v>178</v>
       </c>
       <c r="E4" s="128" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="F4" s="171" t="s">
         <v>407</v>
@@ -17430,7 +17890,7 @@
         <v>180</v>
       </c>
       <c r="E5" s="90" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="F5" s="112" t="s">
         <v>403</v>
@@ -17439,9 +17899,11 @@
         <v>404</v>
       </c>
       <c r="H5" s="112" t="s">
-        <v>408</v>
-      </c>
-      <c r="I5" s="124"/>
+        <v>417</v>
+      </c>
+      <c r="I5" s="124" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="140" t="s">
@@ -17454,7 +17916,7 @@
         <v>178</v>
       </c>
       <c r="E6" s="90" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="F6" s="112" t="s">
         <v>393</v>
@@ -17463,9 +17925,11 @@
         <v>394</v>
       </c>
       <c r="H6" s="112" t="s">
-        <v>409</v>
-      </c>
-      <c r="I6" s="124"/>
+        <v>419</v>
+      </c>
+      <c r="I6" s="124" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="7" spans="1:9" ht="310.5" x14ac:dyDescent="0.3">
       <c r="B7" s="140" t="s">
@@ -17487,9 +17951,11 @@
         <v>390</v>
       </c>
       <c r="H7" s="95" t="s">
-        <v>422</v>
-      </c>
-      <c r="I7" s="83"/>
+        <v>421</v>
+      </c>
+      <c r="I7" s="111" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="140" t="s">
@@ -17604,14 +18070,14 @@
         <v>397</v>
       </c>
       <c r="G13" s="169" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="H13" s="172" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="I13" s="170"/>
     </row>
-    <row r="14" spans="1:9" ht="243" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
       <c r="B14" s="121" t="s">
         <v>62</v>
       </c>
@@ -17626,12 +18092,14 @@
       </c>
       <c r="F14" s="95"/>
       <c r="G14" s="145" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="H14" s="95" t="s">
-        <v>418</v>
-      </c>
-      <c r="I14" s="111"/>
+        <v>423</v>
+      </c>
+      <c r="I14" s="111" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="15" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
       <c r="B15" s="120" t="s">
@@ -17647,15 +18115,17 @@
         <v>261</v>
       </c>
       <c r="F15" s="95" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G15" s="145" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="H15" s="95" t="s">
-        <v>420</v>
-      </c>
-      <c r="I15" s="111"/>
+        <v>425</v>
+      </c>
+      <c r="I15" s="111" t="s">
+        <v>426</v>
+      </c>
     </row>
     <row r="16" spans="1:9" ht="108" x14ac:dyDescent="0.3">
       <c r="B16" s="120" t="s">
@@ -17677,9 +18147,11 @@
         <v>393</v>
       </c>
       <c r="H16" s="145" t="s">
-        <v>413</v>
-      </c>
-      <c r="I16" s="164"/>
+        <v>427</v>
+      </c>
+      <c r="I16" s="164" t="s">
+        <v>428</v>
+      </c>
     </row>
     <row r="17" spans="2:9" ht="409.5" x14ac:dyDescent="0.3">
       <c r="B17" s="120" t="s">
@@ -17698,12 +18170,14 @@
         <v>389</v>
       </c>
       <c r="G17" s="145" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="H17" s="145" t="s">
-        <v>415</v>
-      </c>
-      <c r="I17" s="164"/>
+        <v>411</v>
+      </c>
+      <c r="I17" s="164" t="s">
+        <v>429</v>
+      </c>
     </row>
     <row r="18" spans="2:9" ht="108" x14ac:dyDescent="0.3">
       <c r="B18" s="119" t="s">
@@ -17725,9 +18199,11 @@
         <v>393</v>
       </c>
       <c r="H18" s="157" t="s">
-        <v>411</v>
-      </c>
-      <c r="I18" s="165"/>
+        <v>430</v>
+      </c>
+      <c r="I18" s="165" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="120" t="s">
@@ -17765,9 +18241,11 @@
         <v>391</v>
       </c>
       <c r="H20" s="95" t="s">
-        <v>412</v>
-      </c>
-      <c r="I20" s="123"/>
+        <v>432</v>
+      </c>
+      <c r="I20" s="111" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="21" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="166" t="s">
@@ -17789,9 +18267,11 @@
         <v>392</v>
       </c>
       <c r="H21" s="173" t="s">
-        <v>409</v>
-      </c>
-      <c r="I21" s="85"/>
+        <v>408</v>
+      </c>
+      <c r="I21" s="190" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="22" spans="2:9" ht="14.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>

--- a/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
+++ b/1. 일정/1. Weekly Plan/Air PTC Heater Weekly Plan.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\일정\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.Task\001.Woory\001.PTC\0.PTC\ptc_heater_doc\1. 일정\1. Weekly Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F9226E-15F0-451A-8FF0-B2CDE4AF76C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="8"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="대일정" sheetId="1" r:id="rId1"/>
@@ -23,17 +24,28 @@
     <sheet name="2026.1" sheetId="10" r:id="rId9"/>
     <sheet name="2026.2" sheetId="11" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="441">
   <si>
     <t>■</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1699,17 +1711,6 @@
     <t>Proto (진행 중)
 P1 (26/04/01)
 P2 (26/10/01)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">[우리산업]
-PM : 유정호, 기구 : 공준석, HW : 신지훈, 
-제조 : 전진호, 품질 : 박상철, 일렉스 : 남시온, 류상근, 박철수, 슬로박법인 : 김예현
-[공조설계팀]
-안성민 책임연구원 010-2207-9180
-freshair@hyundai.com
-[신차 품질팀]
-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -9630,11 +9631,68 @@
     - CAN DBC 파일 재요청</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>[조현진 전임]
+- LIN CheckList Application 제출 (1/30)
+- MCU 변경 (Renesas RH850 -&gt; ST STM8AF5288TCY)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[임제훈 사원]
+- SWE.3 SDDS 후속 작업 완료
+[조현진 전임]
+- SWE.4, SWE.5 후속 작업 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XV1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[우리산업]
+PM : 
+부품개발 :
+제조기술 :
+품질 : 
+기구 :
+[HKMC]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[우리산업]
+PM : 유정호 
+기구 : 공준석
+HW : 신지훈 
+제조 : 전진호
+품질 : 박상철
+일렉스 : 남시온, 류상근, 박철수
+슬로박법인 : 김예현
+[공조설계팀]
+안성민 책임연구원 010-2207-9180
+freshair@hyundai.com
+[신차 품질팀]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALL출도
+5/31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통합P
+4/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M
+9/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
@@ -11625,6 +11683,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="88" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -11672,9 +11733,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -11751,15 +11809,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>39</xdr:col>
-      <xdr:colOff>283550</xdr:colOff>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>297157</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>39</xdr:col>
-      <xdr:colOff>313563</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>327170</xdr:colOff>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>176893</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -11775,8 +11833,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="13754621" y="0"/>
-          <a:ext cx="30013" cy="27350357"/>
+          <a:off x="15047300" y="0"/>
+          <a:ext cx="30013" cy="28003500"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -12352,8 +12410,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BL25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:BL26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.375" customWidth="1"/>
@@ -12377,90 +12435,90 @@
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:64" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="174" t="s">
+      <c r="B2" s="175" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="176" t="s">
+      <c r="C2" s="177" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="176" t="s">
+      <c r="D2" s="177" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="180">
+      <c r="E2" s="181">
         <v>23</v>
       </c>
-      <c r="F2" s="178"/>
-      <c r="G2" s="178"/>
-      <c r="H2" s="178"/>
-      <c r="I2" s="178"/>
-      <c r="J2" s="178"/>
-      <c r="K2" s="178"/>
-      <c r="L2" s="178"/>
-      <c r="M2" s="178"/>
-      <c r="N2" s="178"/>
-      <c r="O2" s="178"/>
-      <c r="P2" s="178"/>
-      <c r="Q2" s="178">
+      <c r="F2" s="179"/>
+      <c r="G2" s="179"/>
+      <c r="H2" s="179"/>
+      <c r="I2" s="179"/>
+      <c r="J2" s="179"/>
+      <c r="K2" s="179"/>
+      <c r="L2" s="179"/>
+      <c r="M2" s="179"/>
+      <c r="N2" s="179"/>
+      <c r="O2" s="179"/>
+      <c r="P2" s="179"/>
+      <c r="Q2" s="179">
         <v>24</v>
       </c>
-      <c r="R2" s="178"/>
-      <c r="S2" s="178"/>
-      <c r="T2" s="178"/>
-      <c r="U2" s="178"/>
-      <c r="V2" s="178"/>
-      <c r="W2" s="178"/>
-      <c r="X2" s="178"/>
-      <c r="Y2" s="178"/>
-      <c r="Z2" s="178"/>
-      <c r="AA2" s="178"/>
-      <c r="AB2" s="178"/>
-      <c r="AC2" s="178">
+      <c r="R2" s="179"/>
+      <c r="S2" s="179"/>
+      <c r="T2" s="179"/>
+      <c r="U2" s="179"/>
+      <c r="V2" s="179"/>
+      <c r="W2" s="179"/>
+      <c r="X2" s="179"/>
+      <c r="Y2" s="179"/>
+      <c r="Z2" s="179"/>
+      <c r="AA2" s="179"/>
+      <c r="AB2" s="179"/>
+      <c r="AC2" s="179">
         <v>25</v>
       </c>
-      <c r="AD2" s="178"/>
-      <c r="AE2" s="178"/>
-      <c r="AF2" s="178"/>
-      <c r="AG2" s="178"/>
-      <c r="AH2" s="178"/>
-      <c r="AI2" s="178"/>
-      <c r="AJ2" s="178"/>
-      <c r="AK2" s="178"/>
-      <c r="AL2" s="178"/>
-      <c r="AM2" s="178"/>
-      <c r="AN2" s="178"/>
-      <c r="AO2" s="178">
+      <c r="AD2" s="179"/>
+      <c r="AE2" s="179"/>
+      <c r="AF2" s="179"/>
+      <c r="AG2" s="179"/>
+      <c r="AH2" s="179"/>
+      <c r="AI2" s="179"/>
+      <c r="AJ2" s="179"/>
+      <c r="AK2" s="179"/>
+      <c r="AL2" s="179"/>
+      <c r="AM2" s="179"/>
+      <c r="AN2" s="179"/>
+      <c r="AO2" s="179">
         <v>26</v>
       </c>
-      <c r="AP2" s="178"/>
-      <c r="AQ2" s="178"/>
-      <c r="AR2" s="178"/>
-      <c r="AS2" s="178"/>
-      <c r="AT2" s="178"/>
-      <c r="AU2" s="178"/>
-      <c r="AV2" s="178"/>
-      <c r="AW2" s="178"/>
-      <c r="AX2" s="178"/>
-      <c r="AY2" s="178"/>
-      <c r="AZ2" s="179"/>
-      <c r="BA2" s="178">
+      <c r="AP2" s="179"/>
+      <c r="AQ2" s="179"/>
+      <c r="AR2" s="179"/>
+      <c r="AS2" s="179"/>
+      <c r="AT2" s="179"/>
+      <c r="AU2" s="179"/>
+      <c r="AV2" s="179"/>
+      <c r="AW2" s="179"/>
+      <c r="AX2" s="179"/>
+      <c r="AY2" s="179"/>
+      <c r="AZ2" s="180"/>
+      <c r="BA2" s="179">
         <v>27</v>
       </c>
-      <c r="BB2" s="178"/>
-      <c r="BC2" s="178"/>
-      <c r="BD2" s="178"/>
-      <c r="BE2" s="178"/>
-      <c r="BF2" s="178"/>
-      <c r="BG2" s="178"/>
-      <c r="BH2" s="178"/>
-      <c r="BI2" s="178"/>
-      <c r="BJ2" s="178"/>
-      <c r="BK2" s="178"/>
-      <c r="BL2" s="179"/>
+      <c r="BB2" s="179"/>
+      <c r="BC2" s="179"/>
+      <c r="BD2" s="179"/>
+      <c r="BE2" s="179"/>
+      <c r="BF2" s="179"/>
+      <c r="BG2" s="179"/>
+      <c r="BH2" s="179"/>
+      <c r="BI2" s="179"/>
+      <c r="BJ2" s="179"/>
+      <c r="BK2" s="179"/>
+      <c r="BL2" s="180"/>
     </row>
     <row r="3" spans="1:64" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="175"/>
-      <c r="C3" s="177"/>
-      <c r="D3" s="177"/>
+      <c r="B3" s="176"/>
+      <c r="C3" s="178"/>
+      <c r="D3" s="178"/>
       <c r="E3" s="22">
         <v>1</v>
       </c>
@@ -13201,7 +13259,7 @@
         <v>77</v>
       </c>
       <c r="D11" s="148" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="7"/>
@@ -13284,7 +13342,7 @@
         <v>105</v>
       </c>
       <c r="D12" s="148" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="7"/>
@@ -13365,7 +13423,7 @@
         <v>82</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="7"/>
@@ -13535,7 +13593,7 @@
       <c r="BK14" s="7"/>
       <c r="BL14" s="10"/>
     </row>
-    <row r="15" spans="1:64" ht="285.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:64" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="27" t="s">
         <v>64</v>
       </c>
@@ -13543,7 +13601,7 @@
         <v>84</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>281</v>
+        <v>437</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="7"/>
@@ -13709,7 +13767,7 @@
     </row>
     <row r="17" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="52" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C17" s="55" t="s">
         <v>104</v>
@@ -13755,7 +13813,7 @@
       <c r="AH17" s="37"/>
       <c r="AI17" s="33"/>
       <c r="AJ17" s="13" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AK17" s="41"/>
       <c r="AL17" s="37"/>
@@ -13767,24 +13825,24 @@
       </c>
       <c r="AQ17" s="38"/>
       <c r="AR17" s="33" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AS17" s="37"/>
       <c r="AT17" s="38"/>
       <c r="AU17" s="37"/>
       <c r="AV17" s="37"/>
       <c r="AW17" s="38" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AX17" s="13"/>
       <c r="AY17" s="37"/>
       <c r="AZ17" s="168" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="BA17" s="42"/>
       <c r="BB17" s="38"/>
       <c r="BC17" s="38" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="BD17" s="13" t="s">
         <v>192</v>
@@ -13806,7 +13864,7 @@
         <v>255</v>
       </c>
       <c r="D18" s="148" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E18" s="59"/>
       <c r="F18" s="60"/>
@@ -14053,7 +14111,7 @@
         <v>107</v>
       </c>
       <c r="D21" s="30" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E21" s="59"/>
       <c r="F21" s="60"/>
@@ -14100,7 +14158,7 @@
       <c r="AS21" s="60"/>
       <c r="AT21" s="60"/>
       <c r="AU21" s="64"/>
-      <c r="AV21" s="13" t="s">
+      <c r="AV21" s="64" t="s">
         <v>219</v>
       </c>
       <c r="AW21" s="60"/>
@@ -14108,7 +14166,7 @@
       <c r="AY21" s="64"/>
       <c r="AZ21" s="65"/>
       <c r="BA21" s="62"/>
-      <c r="BB21" s="13"/>
+      <c r="BB21" s="64"/>
       <c r="BC21" s="64"/>
       <c r="BD21" s="64" t="s">
         <v>230</v>
@@ -14119,7 +14177,7 @@
         <v>231</v>
       </c>
       <c r="BH21" s="64" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="BI21" s="64" t="s">
         <v>232</v>
@@ -14128,14 +14186,16 @@
       <c r="BK21" s="64"/>
       <c r="BL21" s="65"/>
     </row>
-    <row r="22" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:64" ht="108" x14ac:dyDescent="0.3">
       <c r="B22" s="52" t="s">
-        <v>166</v>
+        <v>435</v>
       </c>
       <c r="C22" s="70" t="s">
-        <v>107</v>
-      </c>
-      <c r="D22" s="35"/>
+        <v>104</v>
+      </c>
+      <c r="D22" s="66" t="s">
+        <v>436</v>
+      </c>
       <c r="E22" s="59"/>
       <c r="F22" s="60"/>
       <c r="G22" s="60"/>
@@ -14176,35 +14236,43 @@
       <c r="AP22" s="64"/>
       <c r="AQ22" s="64"/>
       <c r="AR22" s="64"/>
-      <c r="AS22" s="60"/>
+      <c r="AS22" s="64" t="s">
+        <v>438</v>
+      </c>
       <c r="AT22" s="60"/>
       <c r="AU22" s="64"/>
-      <c r="AV22" s="60"/>
+      <c r="AV22" s="64" t="s">
+        <v>219</v>
+      </c>
       <c r="AW22" s="60"/>
       <c r="AX22" s="60"/>
       <c r="AY22" s="64"/>
       <c r="AZ22" s="65"/>
       <c r="BA22" s="62"/>
-      <c r="BB22" s="60"/>
+      <c r="BB22" s="64"/>
       <c r="BC22" s="64"/>
-      <c r="BD22" s="60"/>
+      <c r="BD22" s="64" t="s">
+        <v>439</v>
+      </c>
       <c r="BE22" s="60"/>
       <c r="BF22" s="64"/>
       <c r="BG22" s="64"/>
       <c r="BH22" s="64"/>
-      <c r="BI22" s="64"/>
+      <c r="BI22" s="64" t="s">
+        <v>440</v>
+      </c>
       <c r="BJ22" s="64"/>
       <c r="BK22" s="64"/>
       <c r="BL22" s="65"/>
     </row>
     <row r="23" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="52" t="s">
-        <v>326</v>
-      </c>
-      <c r="C23" s="70"/>
-      <c r="D23" s="153" t="s">
-        <v>319</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="C23" s="70" t="s">
+        <v>107</v>
+      </c>
+      <c r="D23" s="35"/>
       <c r="E23" s="59"/>
       <c r="F23" s="60"/>
       <c r="G23" s="60"/>
@@ -14232,40 +14300,28 @@
       <c r="AC23" s="62"/>
       <c r="AD23" s="60"/>
       <c r="AE23" s="60"/>
-      <c r="AF23" s="64" t="s">
-        <v>320</v>
-      </c>
+      <c r="AF23" s="60"/>
       <c r="AG23" s="63"/>
       <c r="AH23" s="60"/>
       <c r="AI23" s="64"/>
       <c r="AJ23" s="60"/>
       <c r="AK23" s="60"/>
-      <c r="AL23" s="64" t="s">
-        <v>321</v>
-      </c>
+      <c r="AL23" s="60"/>
       <c r="AM23" s="60"/>
       <c r="AN23" s="61"/>
       <c r="AO23" s="62"/>
       <c r="AP23" s="64"/>
-      <c r="AQ23" s="64" t="s">
-        <v>328</v>
-      </c>
+      <c r="AQ23" s="64"/>
       <c r="AR23" s="64"/>
       <c r="AS23" s="60"/>
-      <c r="AT23" s="64" t="s">
-        <v>327</v>
-      </c>
+      <c r="AT23" s="60"/>
       <c r="AU23" s="64"/>
       <c r="AV23" s="60"/>
       <c r="AW23" s="60"/>
-      <c r="AX23" s="64" t="s">
-        <v>322</v>
-      </c>
+      <c r="AX23" s="60"/>
       <c r="AY23" s="64"/>
       <c r="AZ23" s="65"/>
-      <c r="BA23" s="154" t="s">
-        <v>323</v>
-      </c>
+      <c r="BA23" s="62"/>
       <c r="BB23" s="60"/>
       <c r="BC23" s="64"/>
       <c r="BD23" s="60"/>
@@ -14278,84 +14334,165 @@
       <c r="BK23" s="64"/>
       <c r="BL23" s="65"/>
     </row>
-    <row r="24" spans="2:64" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="69" t="s">
+    <row r="24" spans="2:64" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="52" t="s">
         <v>325</v>
       </c>
-      <c r="C24" s="152"/>
-      <c r="D24" s="150" t="s">
+      <c r="C24" s="70"/>
+      <c r="D24" s="153" t="s">
         <v>318</v>
       </c>
-      <c r="E24" s="44"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="45"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="45"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="45"/>
-      <c r="M24" s="45"/>
-      <c r="N24" s="45"/>
-      <c r="O24" s="45"/>
-      <c r="P24" s="46"/>
-      <c r="Q24" s="47"/>
-      <c r="R24" s="45"/>
-      <c r="S24" s="45"/>
-      <c r="T24" s="45"/>
-      <c r="U24" s="45"/>
-      <c r="V24" s="45"/>
-      <c r="W24" s="45"/>
-      <c r="X24" s="45"/>
-      <c r="Y24" s="45"/>
-      <c r="Z24" s="45"/>
-      <c r="AA24" s="45"/>
-      <c r="AB24" s="46"/>
-      <c r="AC24" s="47"/>
-      <c r="AD24" s="45"/>
-      <c r="AE24" s="45"/>
-      <c r="AF24" s="45"/>
-      <c r="AG24" s="48"/>
-      <c r="AH24" s="49" t="s">
+      <c r="E24" s="59"/>
+      <c r="F24" s="60"/>
+      <c r="G24" s="60"/>
+      <c r="H24" s="60"/>
+      <c r="I24" s="60"/>
+      <c r="J24" s="60"/>
+      <c r="K24" s="60"/>
+      <c r="L24" s="60"/>
+      <c r="M24" s="60"/>
+      <c r="N24" s="60"/>
+      <c r="O24" s="60"/>
+      <c r="P24" s="61"/>
+      <c r="Q24" s="62"/>
+      <c r="R24" s="60"/>
+      <c r="S24" s="60"/>
+      <c r="T24" s="60"/>
+      <c r="U24" s="60"/>
+      <c r="V24" s="60"/>
+      <c r="W24" s="60"/>
+      <c r="X24" s="60"/>
+      <c r="Y24" s="60"/>
+      <c r="Z24" s="60"/>
+      <c r="AA24" s="60"/>
+      <c r="AB24" s="61"/>
+      <c r="AC24" s="62"/>
+      <c r="AD24" s="60"/>
+      <c r="AE24" s="60"/>
+      <c r="AF24" s="64" t="s">
+        <v>319</v>
+      </c>
+      <c r="AG24" s="63"/>
+      <c r="AH24" s="60"/>
+      <c r="AI24" s="64"/>
+      <c r="AJ24" s="60"/>
+      <c r="AK24" s="60"/>
+      <c r="AL24" s="64" t="s">
+        <v>320</v>
+      </c>
+      <c r="AM24" s="60"/>
+      <c r="AN24" s="61"/>
+      <c r="AO24" s="62"/>
+      <c r="AP24" s="64"/>
+      <c r="AQ24" s="64" t="s">
+        <v>327</v>
+      </c>
+      <c r="AR24" s="64"/>
+      <c r="AS24" s="60"/>
+      <c r="AT24" s="64" t="s">
+        <v>326</v>
+      </c>
+      <c r="AU24" s="64"/>
+      <c r="AV24" s="60"/>
+      <c r="AW24" s="60"/>
+      <c r="AX24" s="64" t="s">
+        <v>321</v>
+      </c>
+      <c r="AY24" s="64"/>
+      <c r="AZ24" s="65"/>
+      <c r="BA24" s="154" t="s">
+        <v>322</v>
+      </c>
+      <c r="BB24" s="60"/>
+      <c r="BC24" s="64"/>
+      <c r="BD24" s="60"/>
+      <c r="BE24" s="60"/>
+      <c r="BF24" s="64"/>
+      <c r="BG24" s="64"/>
+      <c r="BH24" s="64"/>
+      <c r="BI24" s="64"/>
+      <c r="BJ24" s="64"/>
+      <c r="BK24" s="64"/>
+      <c r="BL24" s="65"/>
+    </row>
+    <row r="25" spans="2:64" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="69" t="s">
         <v>324</v>
       </c>
-      <c r="AI24" s="49"/>
-      <c r="AJ24" s="45"/>
-      <c r="AK24" s="45"/>
-      <c r="AL24" s="45"/>
-      <c r="AM24" s="45"/>
-      <c r="AN24" s="46"/>
-      <c r="AO24" s="47"/>
-      <c r="AP24" s="49"/>
-      <c r="AQ24" s="49"/>
-      <c r="AR24" s="49"/>
-      <c r="AS24" s="45"/>
-      <c r="AT24" s="49" t="s">
+      <c r="C25" s="152"/>
+      <c r="D25" s="150" t="s">
+        <v>317</v>
+      </c>
+      <c r="E25" s="44"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="45"/>
+      <c r="M25" s="45"/>
+      <c r="N25" s="45"/>
+      <c r="O25" s="45"/>
+      <c r="P25" s="46"/>
+      <c r="Q25" s="47"/>
+      <c r="R25" s="45"/>
+      <c r="S25" s="45"/>
+      <c r="T25" s="45"/>
+      <c r="U25" s="45"/>
+      <c r="V25" s="45"/>
+      <c r="W25" s="45"/>
+      <c r="X25" s="45"/>
+      <c r="Y25" s="45"/>
+      <c r="Z25" s="45"/>
+      <c r="AA25" s="45"/>
+      <c r="AB25" s="46"/>
+      <c r="AC25" s="47"/>
+      <c r="AD25" s="45"/>
+      <c r="AE25" s="45"/>
+      <c r="AF25" s="45"/>
+      <c r="AG25" s="48"/>
+      <c r="AH25" s="49" t="s">
+        <v>323</v>
+      </c>
+      <c r="AI25" s="49"/>
+      <c r="AJ25" s="45"/>
+      <c r="AK25" s="45"/>
+      <c r="AL25" s="45"/>
+      <c r="AM25" s="45"/>
+      <c r="AN25" s="46"/>
+      <c r="AO25" s="47"/>
+      <c r="AP25" s="49"/>
+      <c r="AQ25" s="49"/>
+      <c r="AR25" s="49"/>
+      <c r="AS25" s="45"/>
+      <c r="AT25" s="49" t="s">
+        <v>328</v>
+      </c>
+      <c r="AU25" s="49"/>
+      <c r="AV25" s="45"/>
+      <c r="AW25" s="45"/>
+      <c r="AX25" s="49" t="s">
         <v>329</v>
       </c>
-      <c r="AU24" s="49"/>
-      <c r="AV24" s="45"/>
-      <c r="AW24" s="45"/>
-      <c r="AX24" s="49" t="s">
+      <c r="AY25" s="49"/>
+      <c r="AZ25" s="50"/>
+      <c r="BA25" s="155" t="s">
         <v>330</v>
       </c>
-      <c r="AY24" s="49"/>
-      <c r="AZ24" s="50"/>
-      <c r="BA24" s="155" t="s">
-        <v>331</v>
-      </c>
-      <c r="BB24" s="45"/>
-      <c r="BC24" s="49"/>
-      <c r="BD24" s="45"/>
-      <c r="BE24" s="45"/>
-      <c r="BF24" s="49"/>
-      <c r="BG24" s="49"/>
-      <c r="BH24" s="49"/>
-      <c r="BI24" s="49"/>
-      <c r="BJ24" s="49"/>
-      <c r="BK24" s="49"/>
-      <c r="BL24" s="50"/>
-    </row>
-    <row r="25" spans="2:64" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="BB25" s="45"/>
+      <c r="BC25" s="49"/>
+      <c r="BD25" s="45"/>
+      <c r="BE25" s="45"/>
+      <c r="BF25" s="49"/>
+      <c r="BG25" s="49"/>
+      <c r="BH25" s="49"/>
+      <c r="BI25" s="49"/>
+      <c r="BJ25" s="49"/>
+      <c r="BK25" s="49"/>
+      <c r="BL25" s="50"/>
+    </row>
+    <row r="26" spans="2:64" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B2:B3"/>
@@ -14375,7 +14512,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:J20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -14400,33 +14537,33 @@
       <c r="E1" s="97"/>
     </row>
     <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="184" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="187" t="s">
+      <c r="C2" s="188" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="187" t="s">
+      <c r="D2" s="188" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="185" t="s">
+      <c r="E2" s="186" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="181" t="s">
+      <c r="F2" s="182" t="s">
+        <v>377</v>
+      </c>
+      <c r="G2" s="182"/>
+      <c r="H2" s="182"/>
+      <c r="I2" s="190"/>
+      <c r="J2" s="183"/>
+    </row>
+    <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="185"/>
+      <c r="C3" s="189"/>
+      <c r="D3" s="189"/>
+      <c r="E3" s="187"/>
+      <c r="F3" s="87" t="s">
         <v>378</v>
-      </c>
-      <c r="G2" s="181"/>
-      <c r="H2" s="181"/>
-      <c r="I2" s="189"/>
-      <c r="J2" s="182"/>
-    </row>
-    <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="184"/>
-      <c r="C3" s="188"/>
-      <c r="D3" s="188"/>
-      <c r="E3" s="186"/>
-      <c r="F3" s="87" t="s">
-        <v>379</v>
       </c>
       <c r="G3" s="87"/>
       <c r="H3" s="87"/>
@@ -14446,13 +14583,15 @@
       <c r="E4" s="128" t="s">
         <v>140</v>
       </c>
-      <c r="F4" s="129"/>
+      <c r="F4" s="171" t="s">
+        <v>433</v>
+      </c>
       <c r="G4" s="130"/>
       <c r="H4" s="78"/>
       <c r="I4" s="159"/>
       <c r="J4" s="82"/>
     </row>
-    <row r="5" spans="1:10" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="54" x14ac:dyDescent="0.3">
       <c r="B5" s="142" t="s">
         <v>181</v>
       </c>
@@ -14465,7 +14604,9 @@
       <c r="E5" s="90" t="s">
         <v>161</v>
       </c>
-      <c r="F5" s="112"/>
+      <c r="F5" s="112" t="s">
+        <v>434</v>
+      </c>
       <c r="G5" s="112"/>
       <c r="H5" s="112"/>
       <c r="I5" s="160"/>
@@ -14689,7 +14830,7 @@
         <v>178</v>
       </c>
       <c r="E17" s="103" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F17" s="109"/>
       <c r="G17" s="157"/>
@@ -14771,7 +14912,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -14902,7 +15043,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:N22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -14928,39 +15069,39 @@
       <c r="E1" s="97"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="184" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="187" t="s">
+      <c r="C2" s="188" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="187" t="s">
+      <c r="D2" s="188" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="185" t="s">
+      <c r="E2" s="186" t="s">
         <v>126</v>
       </c>
       <c r="F2" s="86" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="181" t="s">
+      <c r="G2" s="182" t="s">
         <v>113</v>
       </c>
-      <c r="H2" s="181"/>
-      <c r="I2" s="181"/>
-      <c r="J2" s="182"/>
-      <c r="K2" s="181" t="s">
+      <c r="H2" s="182"/>
+      <c r="I2" s="182"/>
+      <c r="J2" s="183"/>
+      <c r="K2" s="182" t="s">
         <v>182</v>
       </c>
-      <c r="L2" s="181"/>
-      <c r="M2" s="181"/>
-      <c r="N2" s="182"/>
+      <c r="L2" s="182"/>
+      <c r="M2" s="182"/>
+      <c r="N2" s="183"/>
     </row>
     <row r="3" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="184"/>
-      <c r="C3" s="188"/>
-      <c r="D3" s="188"/>
-      <c r="E3" s="186"/>
+      <c r="B3" s="185"/>
+      <c r="C3" s="189"/>
+      <c r="D3" s="189"/>
+      <c r="E3" s="187"/>
       <c r="F3" s="87" t="s">
         <v>111</v>
       </c>
@@ -15678,7 +15819,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -15703,30 +15844,30 @@
       <c r="E1" s="97"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="184" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="187" t="s">
+      <c r="C2" s="188" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="187" t="s">
+      <c r="D2" s="188" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="185" t="s">
+      <c r="E2" s="186" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="181" t="s">
+      <c r="F2" s="182" t="s">
         <v>182</v>
       </c>
-      <c r="G2" s="181"/>
-      <c r="H2" s="181"/>
-      <c r="I2" s="182"/>
+      <c r="G2" s="182"/>
+      <c r="H2" s="182"/>
+      <c r="I2" s="183"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="184"/>
-      <c r="C3" s="188"/>
-      <c r="D3" s="188"/>
-      <c r="E3" s="186"/>
+      <c r="B3" s="185"/>
+      <c r="C3" s="189"/>
+      <c r="D3" s="189"/>
+      <c r="E3" s="187"/>
       <c r="F3" s="87" t="s">
         <v>114</v>
       </c>
@@ -16079,7 +16220,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16104,30 +16245,30 @@
       <c r="E1" s="97"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="184" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="187" t="s">
+      <c r="C2" s="188" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="187" t="s">
+      <c r="D2" s="188" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="185" t="s">
+      <c r="E2" s="186" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="181" t="s">
+      <c r="F2" s="182" t="s">
         <v>224</v>
       </c>
-      <c r="G2" s="181"/>
-      <c r="H2" s="181"/>
-      <c r="I2" s="182"/>
+      <c r="G2" s="182"/>
+      <c r="H2" s="182"/>
+      <c r="I2" s="183"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="184"/>
-      <c r="C3" s="188"/>
-      <c r="D3" s="188"/>
-      <c r="E3" s="186"/>
+      <c r="B3" s="185"/>
+      <c r="C3" s="189"/>
+      <c r="D3" s="189"/>
+      <c r="E3" s="187"/>
       <c r="F3" s="87" t="s">
         <v>114</v>
       </c>
@@ -16486,7 +16627,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16511,41 +16652,41 @@
       <c r="E1" s="97"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="184" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="187" t="s">
+      <c r="C2" s="188" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="187" t="s">
+      <c r="D2" s="188" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="185" t="s">
+      <c r="E2" s="186" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="181" t="s">
+      <c r="F2" s="182" t="s">
         <v>256</v>
       </c>
-      <c r="G2" s="181"/>
-      <c r="H2" s="181"/>
-      <c r="I2" s="182"/>
+      <c r="G2" s="182"/>
+      <c r="H2" s="182"/>
+      <c r="I2" s="183"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="184"/>
-      <c r="C3" s="188"/>
-      <c r="D3" s="188"/>
-      <c r="E3" s="186"/>
+      <c r="B3" s="185"/>
+      <c r="C3" s="189"/>
+      <c r="D3" s="189"/>
+      <c r="E3" s="187"/>
       <c r="F3" s="87" t="s">
         <v>277</v>
       </c>
       <c r="G3" s="87" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H3" s="87" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I3" s="88" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -16582,10 +16723,10 @@
       <c r="F5" s="104"/>
       <c r="G5" s="95"/>
       <c r="H5" s="112" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I5" s="124" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -16604,7 +16745,7 @@
       <c r="F6" s="112"/>
       <c r="G6" s="112"/>
       <c r="H6" s="122" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I6" s="144"/>
     </row>
@@ -16625,7 +16766,7 @@
       <c r="G7" s="95"/>
       <c r="H7" s="79"/>
       <c r="I7" s="123" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="87.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -16645,7 +16786,7 @@
       <c r="G8" s="94"/>
       <c r="H8" s="79"/>
       <c r="I8" s="123" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -16734,10 +16875,10 @@
       <c r="F13" s="104"/>
       <c r="G13" s="95"/>
       <c r="H13" s="122" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I13" s="123" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -16756,10 +16897,10 @@
       <c r="F14" s="104"/>
       <c r="G14" s="95"/>
       <c r="H14" s="122" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I14" s="123" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -16780,10 +16921,10 @@
         <v>265</v>
       </c>
       <c r="H15" s="126" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I15" s="147" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="228.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -16802,10 +16943,10 @@
       <c r="F16" s="104"/>
       <c r="G16" s="95"/>
       <c r="H16" s="122" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I16" s="123" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -16826,10 +16967,10 @@
         <v>257</v>
       </c>
       <c r="H17" s="143" t="s">
+        <v>307</v>
+      </c>
+      <c r="I17" s="125" t="s">
         <v>308</v>
-      </c>
-      <c r="I17" s="125" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="18" spans="2:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -16868,10 +17009,10 @@
         <v>264</v>
       </c>
       <c r="H19" s="122" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I19" s="123" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -16909,7 +17050,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16934,41 +17075,41 @@
       <c r="E1" s="97"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="184" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="187" t="s">
+      <c r="C2" s="188" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="187" t="s">
+      <c r="D2" s="188" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="185" t="s">
+      <c r="E2" s="186" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="181" t="s">
+      <c r="F2" s="182" t="s">
         <v>276</v>
       </c>
-      <c r="G2" s="181"/>
-      <c r="H2" s="181"/>
-      <c r="I2" s="182"/>
+      <c r="G2" s="182"/>
+      <c r="H2" s="182"/>
+      <c r="I2" s="183"/>
     </row>
     <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="184"/>
-      <c r="C3" s="188"/>
-      <c r="D3" s="188"/>
-      <c r="E3" s="186"/>
+      <c r="B3" s="185"/>
+      <c r="C3" s="189"/>
+      <c r="D3" s="189"/>
+      <c r="E3" s="187"/>
       <c r="F3" s="87" t="s">
+        <v>295</v>
+      </c>
+      <c r="G3" s="87" t="s">
         <v>296</v>
       </c>
-      <c r="G3" s="87" t="s">
+      <c r="H3" s="87" t="s">
         <v>297</v>
       </c>
-      <c r="H3" s="87" t="s">
+      <c r="I3" s="88" t="s">
         <v>298</v>
-      </c>
-      <c r="I3" s="88" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -17003,12 +17144,12 @@
         <v>161</v>
       </c>
       <c r="F5" s="112" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G5" s="145"/>
       <c r="H5" s="112"/>
       <c r="I5" s="124" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -17043,10 +17184,10 @@
         <v>162</v>
       </c>
       <c r="F7" s="112" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G7" s="95" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H7" s="79"/>
       <c r="I7" s="83"/>
@@ -17153,16 +17294,16 @@
         <v>260</v>
       </c>
       <c r="F13" s="122" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G13" s="145" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H13" s="95" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I13" s="111" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
@@ -17179,16 +17320,16 @@
         <v>261</v>
       </c>
       <c r="F14" s="122" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G14" s="145" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H14" s="95" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I14" s="111" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="175.5" x14ac:dyDescent="0.3">
@@ -17205,16 +17346,16 @@
         <v>259</v>
       </c>
       <c r="F15" s="122" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G15" s="122" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H15" s="151" t="s">
+        <v>343</v>
+      </c>
+      <c r="I15" s="111" t="s">
         <v>344</v>
-      </c>
-      <c r="I15" s="111" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
@@ -17231,16 +17372,16 @@
         <v>262</v>
       </c>
       <c r="F16" s="122" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G16" s="145" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H16" s="145" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I16" s="111" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="162" x14ac:dyDescent="0.3">
@@ -17254,19 +17395,19 @@
         <v>178</v>
       </c>
       <c r="E17" s="103" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F17" s="143" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G17" s="109" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H17" s="151" t="s">
+        <v>339</v>
+      </c>
+      <c r="I17" s="156" t="s">
         <v>340</v>
-      </c>
-      <c r="I17" s="156" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
@@ -17299,16 +17440,16 @@
         <v>156</v>
       </c>
       <c r="F19" s="122" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G19" s="146" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H19" s="122" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="I19" s="123" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -17325,7 +17466,7 @@
         <v>258</v>
       </c>
       <c r="F20" s="149" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G20" s="135"/>
       <c r="H20" s="136"/>
@@ -17347,7 +17488,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:J20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -17372,45 +17513,45 @@
       <c r="E1" s="97"/>
     </row>
     <row r="2" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="184" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="187" t="s">
+      <c r="C2" s="188" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="187" t="s">
+      <c r="D2" s="188" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="185" t="s">
+      <c r="E2" s="186" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="181" t="s">
+      <c r="F2" s="182" t="s">
+        <v>346</v>
+      </c>
+      <c r="G2" s="182"/>
+      <c r="H2" s="182"/>
+      <c r="I2" s="190"/>
+      <c r="J2" s="183"/>
+    </row>
+    <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="185"/>
+      <c r="C3" s="189"/>
+      <c r="D3" s="189"/>
+      <c r="E3" s="187"/>
+      <c r="F3" s="87" t="s">
+        <v>345</v>
+      </c>
+      <c r="G3" s="87" t="s">
         <v>347</v>
       </c>
-      <c r="G2" s="181"/>
-      <c r="H2" s="181"/>
-      <c r="I2" s="189"/>
-      <c r="J2" s="182"/>
-    </row>
-    <row r="3" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="184"/>
-      <c r="C3" s="188"/>
-      <c r="D3" s="188"/>
-      <c r="E3" s="186"/>
-      <c r="F3" s="87" t="s">
-        <v>346</v>
-      </c>
-      <c r="G3" s="87" t="s">
+      <c r="H3" s="87" t="s">
         <v>348</v>
       </c>
-      <c r="H3" 